--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L132"/>
+  <dimension ref="A1:L160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -652,7 +652,7 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CALCULATION INVENTORY · Phase 1 — Net worth, Performance and the 8 screens they open · 130 calculations · generated from commit 3063b21 on 2026-08-17. GREY columns are generated from the code and are overwritten on every regeneration — never edit them. CREAM columns are written by hand and preserved across regenerations. A row is not documented until its probe passes.</t>
+          <t>CALCULATION INVENTORY · Phase 1 — Net worth, Performance and the 8 screens they open · 158 calculations · generated from commit 57a37b4 on 2026-08-17  ⚠ TREE WAS DIRTY. GREY columns are generated from the code and are overwritten on every regeneration — never edit them. CREAM columns are written by hand and preserved across regenerations. A row is not documented until its probe passes.</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       <c r="A4" s="3" t="inlineStr"/>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>newEntityId</t>
+          <t>formatMoney</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
@@ -767,22 +767,22 @@
       <c r="H4" s="3" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>ImportHoldings</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>assetsFromOnboarding, debtsFromOnboarding</t>
+          <t>money</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>EntityId</t>
+          <t>string</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>src/domain/_shared/ids.ts:6</t>
+          <t>src/domain/_shared/money.ts:58</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
       <c r="A5" s="3" t="inlineStr"/>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>toNum</t>
+          <t>formatMoneyCents</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -806,17 +806,17 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>assetsFromOnboarding, debtsFromOnboarding, employerMatchMonthly, equityRowValue, monthlyContributionsFromOnboarding, plannedMonthlySpend, retirementIncomeMonthly, retirementSpendMonthly, rsuAnnual, salaryGrossByMonth, stateRateOf, tipsAnnual, totalGrossAnnual</t>
+          <t>money2</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>src/domain/_shared/num.ts:4</t>
+          <t>src/domain/_shared/money.ts:74</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       <c r="A6" s="3" t="inlineStr"/>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>isAlternative</t>
+          <t>newEntityId</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -835,22 +835,22 @@
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>ImportHoldings</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>assetsFromOnboarding, debtsFromOnboarding, ingestSync</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>EntityId</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>src/domain/alternatives/index.ts:15</t>
+          <t>src/domain/_shared/ids.ts:6</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       <c r="A7" s="3" t="inlineStr"/>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>accountAllowsTicker</t>
+          <t>toNum</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -869,22 +869,22 @@
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>assetsFromOnboarding, debtsFromOnboarding, employerMatchMonthly, equityRowValue, monthlyContributionsFromOnboarding, plannedMonthlySpend, retirementIncomeMonthly, retirementSpendMonthly, rsuAnnual, salaryGrossByMonth, stateRateOf, tipsAnnual, totalGrossAnnual</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:116</t>
+          <t>src/domain/_shared/num.ts:4</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       <c r="A8" s="3" t="inlineStr"/>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>accountClassBreakdown</t>
+          <t>isAlternative</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr"/>
@@ -903,22 +903,22 @@
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>AccountDetail, NetWorth</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>assetAllocation, cashTotal</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>Record&lt;AssetClass, number&gt; | null</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:416</t>
+          <t>src/domain/alternatives/index.ts:15</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       <c r="A9" s="3" t="inlineStr"/>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>accountDisplayNames</t>
+          <t>accountAllowsTicker</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
@@ -937,7 +937,7 @@
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>AccountDetail, NetWorth, Performance</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Map&lt;string, string&gt;</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:394</t>
+          <t>src/domain/assets/index.ts:116</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,7 @@
       <c r="A10" s="3" t="inlineStr"/>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>assetAllocation</t>
+          <t>accountClassBreakdown</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr"/>
@@ -971,22 +971,22 @@
       <c r="H10" s="3" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>NetWorth</t>
+          <t>AccountDetail, NetWorth</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>assetAllocation, cashTotal</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>Record&lt;AssetClass, number&gt;</t>
+          <t>Record&lt;AssetClass, number&gt; | null</t>
         </is>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:517</t>
+          <t>src/domain/assets/index.ts:416</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       <c r="A11" s="3" t="inlineStr"/>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>assetClassOf</t>
+          <t>accountDisplayNames</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr"/>
@@ -1010,17 +1010,17 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>accountAllowsTicker, accountClassBreakdown, assetAllocation, cashTotal, earmarkDefault, investmentsTotal, isBond, isRealAsset, primaryCarIdOf</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>AssetClass</t>
+          <t>Map&lt;string, string&gt;</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:236</t>
+          <t>src/domain/assets/index.ts:394</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       <c r="A12" s="3" t="inlineStr"/>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>assetKind</t>
+          <t>assetAllocation</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr"/>
@@ -1039,22 +1039,22 @@
       <c r="H12" s="3" t="inlineStr"/>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>AccountDetail, NetWorth, Performance</t>
+          <t>NetWorth</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>benchmarkReturn, isCashKind</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>(inferred)</t>
+          <t>Record&lt;AssetClass, number&gt;</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:165</t>
+          <t>src/domain/assets/index.ts:517</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       <c r="A13" s="3" t="inlineStr"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>assetsFromOnboarding</t>
+          <t>assetClassOf</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
@@ -1073,22 +1073,22 @@
       <c r="H13" s="3" t="inlineStr"/>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AccountDetail, NetWorth, Performance</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>resolveNetWorthRows</t>
+          <t>accountAllowsTicker, accountClassBreakdown, assetAllocation, cashTotal, earmarkDefault, investmentsTotal, isBond, isRealAsset, primaryCarIdOf</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>AssetsDoc</t>
+          <t>AssetClass</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:690</t>
+          <t>src/domain/assets/index.ts:236</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       <c r="A14" s="3" t="inlineStr"/>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>benchmarkReturn</t>
+          <t>assetKind</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr"/>
@@ -1107,22 +1107,22 @@
       <c r="H14" s="3" t="inlineStr"/>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>AccountDetail, Performance</t>
+          <t>AccountDetail, NetWorth, Performance</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>blendedReturn</t>
+          <t>benchmarkReturn, isCashKind</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>(inferred)</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:569</t>
+          <t>src/domain/assets/index.ts:165</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       <c r="A15" s="3" t="inlineStr"/>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>blendedReturn</t>
+          <t>assetsFromOnboarding</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr"/>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>willItLastInputs</t>
+          <t>resolveNetWorthRows</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>AssetsDoc</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:653</t>
+          <t>src/domain/assets/index.ts:690</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       <c r="A16" s="3" t="inlineStr"/>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>blendedVolatility</t>
+          <t>benchmarkReturn</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
@@ -1175,12 +1175,12 @@
       <c r="H16" s="3" t="inlineStr"/>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AccountDetail, Performance</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>willItLastInputs</t>
+          <t>blendedReturn</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="L16" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:612</t>
+          <t>src/domain/assets/index.ts:569</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       <c r="A17" s="3" t="inlineStr"/>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>buildAssetsState</t>
+          <t>blendedReturn</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
@@ -1209,22 +1209,22 @@
       <c r="H17" s="3" t="inlineStr"/>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>NetWorth</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>willItLastInputs</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>AssetsState</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:678</t>
+          <t>src/domain/assets/index.ts:653</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       <c r="A18" s="3" t="inlineStr"/>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>buildItemizedAccounts</t>
+          <t>blendedVolatility</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr"/>
@@ -1243,22 +1243,22 @@
       <c r="H18" s="3" t="inlineStr"/>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Itemize</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>willItLastInputs</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>Omit&lt;AssetAccount, 'asset_id'&gt;[]</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/itemize.ts:48</t>
+          <t>src/domain/assets/index.ts:612</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       <c r="A19" s="3" t="inlineStr"/>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>cashTotal</t>
+          <t>buildAssetsState</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>AssetsState</t>
         </is>
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:286</t>
+          <t>src/domain/assets/index.ts:678</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       <c r="A20" s="3" t="inlineStr"/>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>earmarkDefault</t>
+          <t>buildItemizedAccounts</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr"/>
@@ -1311,22 +1311,22 @@
       <c r="H20" s="3" t="inlineStr"/>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Itemize</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>earmarkedAmount</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>Omit&lt;AssetAccount, 'asset_id'&gt;[]</t>
         </is>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:543</t>
+          <t>src/domain/assets/itemize.ts:48</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       <c r="A21" s="3" t="inlineStr"/>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>earmarkedAmount</t>
+          <t>cashTotal</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
@@ -1345,12 +1345,12 @@
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NetWorth</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>blendedReturn, blendedVolatility, portfolioActualReturn, retirementEarmarkedValue, taxBucketSplit</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:558</t>
+          <t>src/domain/assets/index.ts:286</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       <c r="A22" s="3" t="inlineStr"/>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>incomeBearingClassOf</t>
+          <t>classPortionLabel</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr"/>
@@ -1379,22 +1379,22 @@
       <c r="H22" s="3" t="inlineStr"/>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NetWorth</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>accountClassBreakdown, assetClassOf, classifyHolding</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>AssetClass | null</t>
+          <t>string</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:202</t>
+          <t>src/domain/assets/index.ts:480</t>
         </is>
       </c>
     </row>
@@ -1402,7 +1402,7 @@
       <c r="A23" s="3" t="inlineStr"/>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>investableAssets</t>
+          <t>earmarkDefault</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr"/>
@@ -1413,12 +1413,12 @@
       <c r="H23" s="3" t="inlineStr"/>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>NetWorth</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>earmarkedAmount</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:311</t>
+          <t>src/domain/assets/index.ts:543</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       <c r="A24" s="3" t="inlineStr"/>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>investmentsTotal</t>
+          <t>earmarkedAmount</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr"/>
@@ -1447,12 +1447,12 @@
       <c r="H24" s="3" t="inlineStr"/>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>blendedReturn, blendedVolatility, portfolioActualReturn, retirementEarmarkedValue, taxBucketSplit</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:306</t>
+          <t>src/domain/assets/index.ts:558</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       <c r="A25" s="3" t="inlineStr"/>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>isCashKind</t>
+          <t>incomeBearingClassOf</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
@@ -1481,22 +1481,22 @@
       <c r="H25" s="3" t="inlineStr"/>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>NetWorth</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>accountClassBreakdown, assetClassOf, classifyHolding</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>(inferred)</t>
+          <t>AssetClass | null</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:164</t>
+          <t>src/domain/assets/index.ts:202</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       <c r="A26" s="3" t="inlineStr"/>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>isRealAsset</t>
+          <t>investableAssets</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr"/>
@@ -1515,22 +1515,22 @@
       <c r="H26" s="3" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NetWorth</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>investableAssets</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:268</t>
+          <t>src/domain/assets/index.ts:311</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       <c r="A27" s="3" t="inlineStr"/>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>itemizedTotal</t>
+          <t>investmentsTotal</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
@@ -1549,12 +1549,12 @@
       <c r="H27" s="3" t="inlineStr"/>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Itemize</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>itemizeRemainder</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/itemize.ts:28</t>
+          <t>src/domain/assets/index.ts:306</t>
         </is>
       </c>
     </row>
@@ -1572,7 +1572,7 @@
       <c r="A28" s="3" t="inlineStr"/>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>itemizeRemainder</t>
+          <t>isCashKind</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr"/>
@@ -1583,22 +1583,22 @@
       <c r="H28" s="3" t="inlineStr"/>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Itemize</t>
+          <t>NetWorth</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>buildItemizedAccounts</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>(inferred)</t>
         </is>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/itemize.ts:32</t>
+          <t>src/domain/assets/index.ts:164</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       <c r="A29" s="3" t="inlineStr"/>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>maturityClass</t>
+          <t>isRealAsset</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
@@ -1617,22 +1617,22 @@
       <c r="H29" s="3" t="inlineStr"/>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>NetWorth</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>investableAssets</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>'cash' | 'bonds'</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:215</t>
+          <t>src/domain/assets/index.ts:268</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       <c r="A30" s="3" t="inlineStr"/>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>monthlyContributionsFromOnboarding</t>
+          <t>itemizedTotal</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr"/>
@@ -1651,12 +1651,12 @@
       <c r="H30" s="3" t="inlineStr"/>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Itemize</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>willItLastInputs</t>
+          <t>itemizeRemainder</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:710</t>
+          <t>src/domain/assets/itemize.ts:28</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       <c r="A31" s="3" t="inlineStr"/>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>portfolioActualReturn</t>
+          <t>itemizeRemainder</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr"/>
@@ -1685,22 +1685,22 @@
       <c r="H31" s="3" t="inlineStr"/>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Itemize</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>willItLastInputs</t>
+          <t>buildItemizedAccounts</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:106</t>
+          <t>src/domain/assets/itemize.ts:32</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       <c r="A32" s="3" t="inlineStr"/>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>primaryCarIdOf</t>
+          <t>maturityClass</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr"/>
@@ -1719,22 +1719,22 @@
       <c r="H32" s="3" t="inlineStr"/>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NetWorth</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>blendedReturn, blendedVolatility, retirementEarmarkedValue</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>string | undefined</t>
+          <t>'cash' | 'bonds'</t>
         </is>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:552</t>
+          <t>src/domain/assets/index.ts:215</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       <c r="A33" s="3" t="inlineStr"/>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>realEstateUseOf</t>
+          <t>monthlyContributionsFromOnboarding</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr"/>
@@ -1758,17 +1758,17 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>earmarkDefault</t>
+          <t>willItLastInputs</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>RealEstateUse</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:262</t>
+          <t>src/domain/assets/index.ts:710</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       <c r="A34" s="3" t="inlineStr"/>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>retirementEarmarkedValue</t>
+          <t>portfolioActualReturn</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr"/>
@@ -1792,17 +1792,17 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>planDoor, selectWillItLast, willItLastInputs</t>
+          <t>willItLastInputs</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>number | null</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:563</t>
+          <t>src/domain/assets/index.ts:106</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       <c r="A35" s="3" t="inlineStr"/>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>taxTreatmentOf</t>
+          <t>primaryCarIdOf</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr"/>
@@ -1821,22 +1821,22 @@
       <c r="H35" s="3" t="inlineStr"/>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>AccountDetail</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>blendedReturn, blendedVolatility, retirementEarmarkedValue</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>TaxTreatment</t>
+          <t>string | undefined</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:253</t>
+          <t>src/domain/assets/index.ts:552</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       <c r="A36" s="3" t="inlineStr"/>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>uberGroupRows</t>
+          <t>realEstateUseOf</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr"/>
@@ -1855,22 +1855,22 @@
       <c r="H36" s="3" t="inlineStr"/>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>NetWorth</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>earmarkDefault</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>(inferred)</t>
+          <t>RealEstateUse</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:794</t>
+          <t>src/domain/assets/index.ts:262</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       <c r="A37" s="3" t="inlineStr"/>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>valueFreshness</t>
+          <t>retirementEarmarkedValue</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr"/>
@@ -1889,22 +1889,22 @@
       <c r="H37" s="3" t="inlineStr"/>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>AccountDetail, Performance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>planDoor, selectWillItLast, willItLastInputs</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>(inferred)</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:95</t>
+          <t>src/domain/assets/index.ts:563</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       <c r="A38" s="3" t="inlineStr"/>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>wrapperAccount</t>
+          <t>sourceWording</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       <c r="H38" s="3" t="inlineStr"/>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>NetWorth</t>
+          <t>AccountDetail, NetWorth</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>(inferred)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>src/domain/assets/index.ts:223</t>
+          <t>src/domain/assets/index.ts:726</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       <c r="A39" s="3" t="inlineStr"/>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>annualCoupon</t>
+          <t>taxTreatmentOf</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr"/>
@@ -1962,17 +1962,17 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>approxYTM, currentYield</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>TaxTreatment</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>src/domain/bonds/index.ts:21</t>
+          <t>src/domain/assets/index.ts:253</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       <c r="A40" s="3" t="inlineStr"/>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>approxYTM</t>
+          <t>uberGroupRows</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr"/>
@@ -1991,22 +1991,22 @@
       <c r="H40" s="3" t="inlineStr"/>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>AccountDetail</t>
+          <t>NetWorth</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>bondRateSensitivity</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>(inferred)</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>src/domain/bonds/index.ts:33</t>
+          <t>src/domain/assets/index.ts:794</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2014,7 @@
       <c r="A41" s="3" t="inlineStr"/>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>bondInfo</t>
+          <t>valueFreshness</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr"/>
@@ -2025,7 +2025,7 @@
       <c r="H41" s="3" t="inlineStr"/>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>AccountDetail</t>
+          <t>AccountDetail, Performance</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>BondInfo</t>
+          <t>(inferred)</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>src/domain/bonds/index.ts:16</t>
+          <t>src/domain/assets/index.ts:95</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2048,7 @@
       <c r="A42" s="3" t="inlineStr"/>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>bondRateSensitivity</t>
+          <t>wrapperAccount</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr"/>
@@ -2059,7 +2059,7 @@
       <c r="H42" s="3" t="inlineStr"/>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>AccountDetail</t>
+          <t>NetWorth</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>RateSensitivity | null</t>
+          <t>(inferred)</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>src/domain/bonds/index.ts:97</t>
+          <t>src/domain/assets/index.ts:223</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       <c r="A43" s="3" t="inlineStr"/>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>currentYield</t>
+          <t>annualCoupon</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr"/>
@@ -2098,17 +2098,17 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>approxYTM, currentYield</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>src/domain/bonds/index.ts:29</t>
+          <t>src/domain/bonds/index.ts:21</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       <c r="A44" s="3" t="inlineStr"/>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>isBond</t>
+          <t>approxYTM</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr"/>
@@ -2127,22 +2127,22 @@
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>AccountDetail</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>bondRateSensitivity</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>number | null</t>
         </is>
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>src/domain/bonds/index.ts:13</t>
+          <t>src/domain/bonds/index.ts:33</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       <c r="A45" s="3" t="inlineStr"/>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>yearsToMaturity</t>
+          <t>bondInfo</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr"/>
@@ -2166,17 +2166,17 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>approxYTM</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>BondInfo</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>src/domain/bonds/index.ts:24</t>
+          <t>src/domain/bonds/index.ts:16</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       <c r="A46" s="3" t="inlineStr"/>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>plannedMonthlySpend</t>
+          <t>bondRateSensitivity</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr"/>
@@ -2195,7 +2195,7 @@
       <c r="H46" s="3" t="inlineStr"/>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>NetWorth</t>
+          <t>AccountDetail</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
@@ -2205,12 +2205,12 @@
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>RateSensitivity | null</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>src/domain/budget/index.ts:45</t>
+          <t>src/domain/bonds/index.ts:97</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       <c r="A47" s="3" t="inlineStr"/>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>spendBuckets</t>
+          <t>currentYield</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr"/>
@@ -2229,22 +2229,22 @@
       <c r="H47" s="3" t="inlineStr"/>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>AccountDetail</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>plannedMonthlySpend</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>(inferred)</t>
+          <t>number | null</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>src/domain/budget/index.ts:72</t>
+          <t>src/domain/bonds/index.ts:29</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       <c r="A48" s="3" t="inlineStr"/>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>actualDebtPayment</t>
+          <t>isBond</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr"/>
@@ -2263,22 +2263,22 @@
       <c r="H48" s="3" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>buildDebtState</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>src/domain/debt/index.ts:59</t>
+          <t>src/domain/bonds/index.ts:13</t>
         </is>
       </c>
     </row>
@@ -2286,7 +2286,7 @@
       <c r="A49" s="3" t="inlineStr"/>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>buildDebtState</t>
+          <t>yearsToMaturity</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr"/>
@@ -2297,22 +2297,22 @@
       <c r="H49" s="3" t="inlineStr"/>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>NetWorth</t>
+          <t>AccountDetail</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>approxYTM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>DebtState</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>src/domain/debt/index.ts:214</t>
+          <t>src/domain/bonds/index.ts:24</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       <c r="A50" s="3" t="inlineStr"/>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>debtKind</t>
+          <t>plannedMonthlySpend</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr"/>
@@ -2341,12 +2341,12 @@
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>(inferred)</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>src/domain/debt/index.ts:197</t>
+          <t>src/domain/budget/index.ts:45</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2354,7 @@
       <c r="A51" s="3" t="inlineStr"/>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>debtsFromOnboarding</t>
+          <t>spendBuckets</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr"/>
@@ -2370,17 +2370,17 @@
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>resolveNetWorthRows</t>
+          <t>plannedMonthlySpend</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>DebtDoc</t>
+          <t>(inferred)</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>src/domain/debt/index.ts:240</t>
+          <t>src/domain/budget/index.ts:72</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2388,7 @@
       <c r="A52" s="3" t="inlineStr"/>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>defaultPaymentType</t>
+          <t>actualDebtPayment</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr"/>
@@ -2404,17 +2404,17 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>paymentShape</t>
+          <t>buildDebtState</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>NonNullable&lt;Debt['payment_type']&gt;</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>src/domain/debt/index.ts:35</t>
+          <t>src/domain/debt/index.ts:59</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       <c r="A53" s="3" t="inlineStr"/>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>inferDebtType</t>
+          <t>buildDebtState</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr"/>
@@ -2433,22 +2433,22 @@
       <c r="H53" s="3" t="inlineStr"/>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NetWorth</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>debtsFromOnboarding</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>DebtType</t>
+          <t>DebtState</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>src/domain/debt/index.ts:228</t>
+          <t>src/domain/debt/index.ts:214</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       <c r="A54" s="3" t="inlineStr"/>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>minimumDebtService</t>
+          <t>debtKind</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr"/>
@@ -2467,22 +2467,22 @@
       <c r="H54" s="3" t="inlineStr"/>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NetWorth</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>buildDebtState</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>(inferred)</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>src/domain/debt/index.ts:55</t>
+          <t>src/domain/debt/index.ts:197</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       <c r="A55" s="3" t="inlineStr"/>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>paymentShape</t>
+          <t>debtsFromOnboarding</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr"/>
@@ -2506,17 +2506,17 @@
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>minimumDebtService, requiredPayment</t>
+          <t>resolveNetWorthRows</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>NonNullable&lt;Debt['payment_type']&gt;</t>
+          <t>DebtDoc</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>src/domain/debt/index.ts:38</t>
+          <t>src/domain/debt/index.ts:240</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       <c r="A56" s="3" t="inlineStr"/>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>requiredPayment</t>
+          <t>defaultPaymentType</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr"/>
@@ -2540,17 +2540,17 @@
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>totalDebtMonthly</t>
+          <t>paymentShape</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>NonNullable&lt;Debt['payment_type']&gt;</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>src/domain/debt/index.ts:44</t>
+          <t>src/domain/debt/index.ts:35</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       <c r="A57" s="3" t="inlineStr"/>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>totalDebtMonthly</t>
+          <t>inferDebtType</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr"/>
@@ -2574,17 +2574,17 @@
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>actualDebtPayment</t>
+          <t>debtsFromOnboarding</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>DebtType</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>src/domain/debt/index.ts:49</t>
+          <t>src/domain/debt/index.ts:228</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       <c r="A58" s="3" t="inlineStr"/>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>taxBucketSplit</t>
+          <t>minimumDebtService</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr"/>
@@ -2608,17 +2608,17 @@
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>willItLastInputs</t>
+          <t>buildDebtState</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
-          <t>BucketSplit</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>src/domain/decumulation/index.ts:10</t>
+          <t>src/domain/debt/index.ts:55</t>
         </is>
       </c>
     </row>
@@ -2626,7 +2626,7 @@
       <c r="A59" s="3" t="inlineStr"/>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>dataGaps</t>
+          <t>paymentShape</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr"/>
@@ -2637,22 +2637,22 @@
       <c r="H59" s="3" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>NetWorth, Performance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>minimumDebtService, requiredPayment</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t>DataGap[]</t>
+          <t>NonNullable&lt;Debt['payment_type']&gt;</t>
         </is>
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>src/domain/gaps/index.ts:57</t>
+          <t>src/domain/debt/index.ts:38</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       <c r="A60" s="3" t="inlineStr"/>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>buildChangeWalk</t>
+          <t>requiredPayment</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr"/>
@@ -2671,22 +2671,22 @@
       <c r="H60" s="3" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>NetWorth, Performance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>totalDebtMonthly</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
-          <t>(inferred)</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>src/domain/history.ts:144</t>
+          <t>src/domain/debt/index.ts:44</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       <c r="A61" s="3" t="inlineStr"/>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>investableChangePct</t>
+          <t>totalDebtMonthly</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr"/>
@@ -2705,22 +2705,22 @@
       <c r="H61" s="3" t="inlineStr"/>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>NetWorth</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>actualDebtPayment</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>src/domain/history.ts:118</t>
+          <t>src/domain/debt/index.ts:49</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       <c r="A62" s="3" t="inlineStr"/>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>normalizeSnapshot</t>
+          <t>taxBucketSplit</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr"/>
@@ -2744,17 +2744,17 @@
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>readHistory</t>
+          <t>willItLastInputs</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
-          <t>MonthlySnapshot | null</t>
+          <t>BucketSplit</t>
         </is>
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>src/domain/history.ts:77</t>
+          <t>src/domain/decumulation/index.ts:10</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       <c r="A63" s="3" t="inlineStr"/>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>readHistory</t>
+          <t>dataGaps</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr"/>
@@ -2773,41 +2773,65 @@
       <c r="H63" s="3" t="inlineStr"/>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NetWorth, Performance</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>trendPoints</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
-          <t>MonthlySnapshot[]</t>
+          <t>DataGap[]</t>
         </is>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>src/domain/history.ts:107</t>
+          <t>src/domain/gaps/index.ts:57</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr"/>
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>What drove my net worth from one date to another?</t>
+        </is>
+      </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>trendPoints</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr"/>
-      <c r="D64" s="3" t="inlineStr"/>
-      <c r="E64" s="3" t="inlineStr"/>
-      <c r="F64" s="3" t="inlineStr"/>
-      <c r="G64" s="3" t="inlineStr"/>
+          <t>buildChangeWalk</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>wealthGenerated = (ending − beginning) − contributions + withdrawals − debtPrincipal;  marketChange = wealthGenerated − dividends − interest</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>beginning · ending · contributions · withdrawals · dividends · interest · debtPrincipal</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>beginning = a SAVED net-worth snapshot; ending = today's computed net worth; the other five = sums over the transaction ledger inside the window</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>DEFECT — marketChange is a RESIDUAL, not a measurement: whatever the ledger cannot explain lands there, labelled "change in investment value". With beginning = ending, a $500 contribution manufactures a $500 "market loss" that never happened, and it is indistinguishable from a real one. All five ledger inputs are floored at zero on the way in.</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>Calculation Module code/probes/broken-family.probe.test.ts</t>
+        </is>
+      </c>
       <c r="H64" s="3" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>NetWorth</t>
+          <t>NetWorth, Performance</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
@@ -2817,46 +2841,70 @@
       </c>
       <c r="K64" s="5" t="inlineStr">
         <is>
-          <t>TrendPoint[]</t>
+          <t>(inferred)</t>
         </is>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>src/domain/history.ts:43</t>
+          <t>src/domain/history.ts:144</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr"/>
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>What is my return on cash + investments since the baseline?</t>
+        </is>
+      </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>classifyHolding</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr"/>
-      <c r="D65" s="3" t="inlineStr"/>
-      <c r="E65" s="3" t="inlineStr"/>
-      <c r="F65" s="3" t="inlineStr"/>
-      <c r="G65" s="3" t="inlineStr"/>
+          <t>investableChangePct</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>(currentInvestable − baseline) ÷ baseline, to 1 decimal place</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>invDaily (saved daily points) · currentInvestable · sinceKey</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>invDaily = written on every Home open; currentInvestable = investableAssets(today); sinceKey = the change line's own baseline date</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>baseline = the EARLIEST daily point on or after sinceKey. Property is excluded because it only moves when retyped. DEFECT — the baseline is whatever day the app happened to be opened, not a meaningful date; if the only stored point was written after a fall, the fall is invisible and the recovery since reads as a gain. This is why a −4.2% year showed +2.0%.</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Calculation Module code/probes/broken-family.probe.test.ts</t>
+        </is>
+      </c>
       <c r="H65" s="3" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NetWorth</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>importHoldings</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K65" s="5" t="inlineStr">
         <is>
-          <t>AssetClass</t>
+          <t>number | null</t>
         </is>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>src/domain/import/holdingsImport.ts:154</t>
+          <t>src/domain/history.ts:118</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2912,7 @@
       <c r="A66" s="3" t="inlineStr"/>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>importHoldings</t>
+          <t>normalizeSnapshot</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr"/>
@@ -2875,22 +2923,22 @@
       <c r="H66" s="3" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>ImportHoldings</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>readHistory</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
-          <t>ImportResult</t>
+          <t>MonthlySnapshot | null</t>
         </is>
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>src/domain/import/holdingsImport.ts:183</t>
+          <t>src/domain/history.ts:77</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2946,7 @@
       <c r="A67" s="3" t="inlineStr"/>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>matchImportAccount</t>
+          <t>readHistory</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr"/>
@@ -2909,22 +2957,22 @@
       <c r="H67" s="3" t="inlineStr"/>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>ImportHoldings</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>trendPoints</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>AssetAccount | null</t>
+          <t>MonthlySnapshot[]</t>
         </is>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>src/domain/import/holdingsImport.ts:254</t>
+          <t>src/domain/history.ts:107</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2980,7 @@
       <c r="A68" s="3" t="inlineStr"/>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>parseCsv</t>
+          <t>trendPoints</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr"/>
@@ -2943,22 +2991,22 @@
       <c r="H68" s="3" t="inlineStr"/>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NetWorth</t>
         </is>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>importHoldings</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
-          <t>string[][]</t>
+          <t>TrendPoint[]</t>
         </is>
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>src/domain/import/holdingsImport.ts:74</t>
+          <t>src/domain/history.ts:43</t>
         </is>
       </c>
     </row>
@@ -2966,7 +3014,7 @@
       <c r="A69" s="3" t="inlineStr"/>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>currentRetirementIncomeMonthly</t>
+          <t>classifyHolding</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr"/>
@@ -2982,17 +3030,17 @@
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>resolveLens, totalGrossAnnual</t>
+          <t>importHoldings</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>AssetClass</t>
         </is>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/onboarding.ts:191</t>
+          <t>src/domain/import/holdingsImport.ts:154</t>
         </is>
       </c>
     </row>
@@ -3000,7 +3048,7 @@
       <c r="A70" s="3" t="inlineStr"/>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>effectiveRateOnGrossFor</t>
+          <t>decodeCsvBase64</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr"/>
@@ -3011,22 +3059,22 @@
       <c r="H70" s="3" t="inlineStr"/>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ImportHoldings</t>
         </is>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>willItLastInputs</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>string</t>
         </is>
       </c>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/tax.ts:107</t>
+          <t>src/domain/import/holdingsImport.ts:61</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3082,7 @@
       <c r="A71" s="3" t="inlineStr"/>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>employerMatchMonthly</t>
+          <t>importHoldings</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr"/>
@@ -3045,22 +3093,22 @@
       <c r="H71" s="3" t="inlineStr"/>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ImportHoldings</t>
         </is>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>monthlyContributionsFromOnboarding</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>ImportResult</t>
         </is>
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/onboarding.ts:242</t>
+          <t>src/domain/import/holdingsImport.ts:183</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3116,7 @@
       <c r="A72" s="3" t="inlineStr"/>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>equityRowValue</t>
+          <t>matchImportAccount</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr"/>
@@ -3079,22 +3127,22 @@
       <c r="H72" s="3" t="inlineStr"/>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ImportHoldings</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>rsuAnnual</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>AssetAccount | null</t>
         </is>
       </c>
       <c r="L72" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/onboarding.ts:68</t>
+          <t>src/domain/import/holdingsImport.ts:254</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3150,7 @@
       <c r="A73" s="3" t="inlineStr"/>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>extraIncome</t>
+          <t>parseCsv</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr"/>
@@ -3118,17 +3166,17 @@
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>totalGrossAnnual</t>
+          <t>importHoldings</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
-          <t>(inferred)</t>
+          <t>string[][]</t>
         </is>
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/onboarding.ts:161</t>
+          <t>src/domain/import/holdingsImport.ts:74</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3184,7 @@
       <c r="A74" s="3" t="inlineStr"/>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>filingStatusOf</t>
+          <t>currentRetirementIncomeMonthly</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr"/>
@@ -3152,17 +3200,17 @@
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>willItLastInputs</t>
+          <t>resolveLens, totalGrossAnnual</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
-          <t>import('./tax').FilingStatus</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/onboarding.ts:333</t>
+          <t>src/domain/income/onboarding.ts:191</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3218,7 @@
       <c r="A75" s="3" t="inlineStr"/>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>grossFromNet</t>
+          <t>effectiveRateOnGrossFor</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr"/>
@@ -3186,7 +3234,7 @@
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>salaryGrossByMonth</t>
+          <t>willItLastInputs</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr">
@@ -3196,7 +3244,7 @@
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/tax.ts:47</t>
+          <t>src/domain/income/tax.ts:107</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3252,7 @@
       <c r="A76" s="3" t="inlineStr"/>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>rentalList</t>
+          <t>employerMatchMonthly</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr"/>
@@ -3220,17 +3268,17 @@
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>rentalNetAnnual</t>
+          <t>monthlyContributionsFromOnboarding</t>
         </is>
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
-          <t>(inferred)</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/onboarding.ts:129</t>
+          <t>src/domain/income/onboarding.ts:242</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3286,7 @@
       <c r="A77" s="3" t="inlineStr"/>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>rentalNetAnnual</t>
+          <t>equityRowValue</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr"/>
@@ -3254,7 +3302,7 @@
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>totalGrossAnnual</t>
+          <t>rsuAnnual</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr">
@@ -3264,7 +3312,7 @@
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/onboarding.ts:142</t>
+          <t>src/domain/income/onboarding.ts:68</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3320,7 @@
       <c r="A78" s="3" t="inlineStr"/>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>retirementIncomeMonthly</t>
+          <t>extraIncome</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr"/>
@@ -3288,17 +3336,17 @@
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>currentRetirementIncomeMonthly, willItLastInputs</t>
+          <t>totalGrossAnnual</t>
         </is>
       </c>
       <c r="K78" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>(inferred)</t>
         </is>
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/onboarding.ts:213</t>
+          <t>src/domain/income/onboarding.ts:161</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3354,7 @@
       <c r="A79" s="3" t="inlineStr"/>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>rowVestYear</t>
+          <t>filingStatusOf</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr"/>
@@ -3322,17 +3370,17 @@
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>rsuAnnual</t>
+          <t>willItLastInputs</t>
         </is>
       </c>
       <c r="K79" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>import('./tax').FilingStatus</t>
         </is>
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/onboarding.ts:74</t>
+          <t>src/domain/income/onboarding.ts:333</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3388,7 @@
       <c r="A80" s="3" t="inlineStr"/>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>rsuAnnual</t>
+          <t>grossFromNet</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr"/>
@@ -3356,7 +3404,7 @@
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>totalGrossAnnual</t>
+          <t>salaryGrossByMonth</t>
         </is>
       </c>
       <c r="K80" s="5" t="inlineStr">
@@ -3366,7 +3414,7 @@
       </c>
       <c r="L80" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/onboarding.ts:114</t>
+          <t>src/domain/income/tax.ts:47</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3422,7 @@
       <c r="A81" s="3" t="inlineStr"/>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>salaryActiveMonths</t>
+          <t>rentalList</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr"/>
@@ -3390,17 +3438,17 @@
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>tipsAnnual</t>
+          <t>rentalNetAnnual</t>
         </is>
       </c>
       <c r="K81" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>(inferred)</t>
         </is>
       </c>
       <c r="L81" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/onboarding.ts:306</t>
+          <t>src/domain/income/onboarding.ts:129</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3456,7 @@
       <c r="A82" s="3" t="inlineStr"/>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>salaryAnnual</t>
+          <t>rentalNetAnnual</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr"/>
@@ -3434,7 +3482,7 @@
       </c>
       <c r="L82" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/onboarding.ts:310</t>
+          <t>src/domain/income/onboarding.ts:142</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3490,7 @@
       <c r="A83" s="3" t="inlineStr"/>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>salaryGrossByMonth</t>
+          <t>retirementIncomeMonthly</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr"/>
@@ -3458,17 +3506,17 @@
       </c>
       <c r="J83" s="5" t="inlineStr">
         <is>
-          <t>salaryActiveMonths, salaryAnnual</t>
+          <t>currentRetirementIncomeMonthly, willItLastInputs</t>
         </is>
       </c>
       <c r="K83" s="5" t="inlineStr">
         <is>
-          <t>number[]</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/onboarding.ts:46</t>
+          <t>src/domain/income/onboarding.ts:213</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3524,7 @@
       <c r="A84" s="3" t="inlineStr"/>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>stateRateOf</t>
+          <t>rowVestYear</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr"/>
@@ -3492,7 +3540,7 @@
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>willItLastInputs</t>
+          <t>rsuAnnual</t>
         </is>
       </c>
       <c r="K84" s="5" t="inlineStr">
@@ -3502,7 +3550,7 @@
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/onboarding.ts:337</t>
+          <t>src/domain/income/onboarding.ts:74</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3558,7 @@
       <c r="A85" s="3" t="inlineStr"/>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>taxableIncome</t>
+          <t>rsuAnnual</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr"/>
@@ -3526,7 +3574,7 @@
       </c>
       <c r="J85" s="5" t="inlineStr">
         <is>
-          <t>taxOwed</t>
+          <t>totalGrossAnnual</t>
         </is>
       </c>
       <c r="K85" s="5" t="inlineStr">
@@ -3536,7 +3584,7 @@
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/tax.ts:17</t>
+          <t>src/domain/income/onboarding.ts:114</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3592,7 @@
       <c r="A86" s="3" t="inlineStr"/>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>taxableIncomeFor</t>
+          <t>salaryActiveMonths</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr"/>
@@ -3560,7 +3608,7 @@
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>taxOwedFor</t>
+          <t>tipsAnnual</t>
         </is>
       </c>
       <c r="K86" s="5" t="inlineStr">
@@ -3570,7 +3618,7 @@
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/tax.ts:88</t>
+          <t>src/domain/income/onboarding.ts:306</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3626,7 @@
       <c r="A87" s="3" t="inlineStr"/>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>taxOwed</t>
+          <t>salaryAnnual</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr"/>
@@ -3594,7 +3642,7 @@
       </c>
       <c r="J87" s="5" t="inlineStr">
         <is>
-          <t>grossFromNet</t>
+          <t>totalGrossAnnual</t>
         </is>
       </c>
       <c r="K87" s="5" t="inlineStr">
@@ -3604,7 +3652,7 @@
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/tax.ts:29</t>
+          <t>src/domain/income/onboarding.ts:310</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3660,7 @@
       <c r="A88" s="3" t="inlineStr"/>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>taxOwedFor</t>
+          <t>salaryGrossByMonth</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr"/>
@@ -3628,17 +3676,17 @@
       </c>
       <c r="J88" s="5" t="inlineStr">
         <is>
-          <t>effectiveRateOnGrossFor</t>
+          <t>salaryActiveMonths, salaryAnnual</t>
         </is>
       </c>
       <c r="K88" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>number[]</t>
         </is>
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/tax.ts:94</t>
+          <t>src/domain/income/onboarding.ts:46</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3694,7 @@
       <c r="A89" s="3" t="inlineStr"/>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>tipsAnnual</t>
+          <t>stateRateOf</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr"/>
@@ -3662,7 +3710,7 @@
       </c>
       <c r="J89" s="5" t="inlineStr">
         <is>
-          <t>totalGrossAnnual</t>
+          <t>willItLastInputs</t>
         </is>
       </c>
       <c r="K89" s="5" t="inlineStr">
@@ -3672,7 +3720,7 @@
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/onboarding.ts:204</t>
+          <t>src/domain/income/onboarding.ts:337</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3728,7 @@
       <c r="A90" s="3" t="inlineStr"/>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>totalGrossAnnual</t>
+          <t>taxableIncome</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr"/>
@@ -3696,7 +3744,7 @@
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t>willItLastInputs</t>
+          <t>taxOwed</t>
         </is>
       </c>
       <c r="K90" s="5" t="inlineStr">
@@ -3706,7 +3754,7 @@
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/onboarding.ts:316</t>
+          <t>src/domain/income/tax.ts:17</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3762,7 @@
       <c r="A91" s="3" t="inlineStr"/>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>userCapGainsRates</t>
+          <t>taxableIncomeFor</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr"/>
@@ -3725,22 +3773,22 @@
       <c r="H91" s="3" t="inlineStr"/>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>HoldingDetail, Performance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J91" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>taxOwedFor</t>
         </is>
       </c>
       <c r="K91" s="5" t="inlineStr">
         <is>
-          <t>(inferred)</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>src/domain/income/onboarding.ts:390</t>
+          <t>src/domain/income/tax.ts:88</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3796,7 @@
       <c r="A92" s="3" t="inlineStr"/>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>buildNetWorth</t>
+          <t>taxOwed</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr"/>
@@ -3759,22 +3807,22 @@
       <c r="H92" s="3" t="inlineStr"/>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>NetWorth</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J92" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>grossFromNet</t>
         </is>
       </c>
       <c r="K92" s="5" t="inlineStr">
         <is>
-          <t>NetWorthState</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L92" s="5" t="inlineStr">
         <is>
-          <t>src/domain/networth/index.ts:12</t>
+          <t>src/domain/income/tax.ts:29</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3830,7 @@
       <c r="A93" s="3" t="inlineStr"/>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>allocation</t>
+          <t>taxOwedFor</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr"/>
@@ -3793,22 +3841,22 @@
       <c r="H93" s="3" t="inlineStr"/>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J93" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>effectiveRateOnGrossFor</t>
         </is>
       </c>
       <c r="K93" s="5" t="inlineStr">
         <is>
-          <t>AllocSlice[]</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L93" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:226</t>
+          <t>src/domain/income/tax.ts:94</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3864,7 @@
       <c r="A94" s="3" t="inlineStr"/>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>attribution</t>
+          <t>tipsAnnual</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr"/>
@@ -3827,22 +3875,22 @@
       <c r="H94" s="3" t="inlineStr"/>
       <c r="I94" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J94" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>totalGrossAnnual</t>
         </is>
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
-          <t>(inferred)</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:215</t>
+          <t>src/domain/income/onboarding.ts:204</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3898,7 @@
       <c r="A95" s="3" t="inlineStr"/>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>buildPerformance</t>
+          <t>totalGrossAnnual</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr"/>
@@ -3861,22 +3909,22 @@
       <c r="H95" s="3" t="inlineStr"/>
       <c r="I95" s="5" t="inlineStr">
         <is>
-          <t>HoldingDetail, Performance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J95" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>willItLastInputs</t>
         </is>
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
-          <t>PerformanceRow[]</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L95" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:173</t>
+          <t>src/domain/income/onboarding.ts:316</t>
         </is>
       </c>
     </row>
@@ -3884,7 +3932,7 @@
       <c r="A96" s="3" t="inlineStr"/>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>capGains</t>
+          <t>userCapGainsRates</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr"/>
@@ -3905,12 +3953,12 @@
       </c>
       <c r="K96" s="5" t="inlineStr">
         <is>
-          <t>CapGains</t>
+          <t>(inferred)</t>
         </is>
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:55</t>
+          <t>src/domain/income/onboarding.ts:390</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3966,7 @@
       <c r="A97" s="3" t="inlineStr"/>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>capGainsTax</t>
+          <t>analyzeExpenses</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr"/>
@@ -3929,7 +3977,7 @@
       <c r="H97" s="3" t="inlineStr"/>
       <c r="I97" s="5" t="inlineStr">
         <is>
-          <t>HoldingDetail, Performance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J97" s="5" t="inlineStr">
@@ -3939,12 +3987,12 @@
       </c>
       <c r="K97" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>Promise&lt;ExpenseAnalysis&gt;</t>
         </is>
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:69</t>
+          <t>src/services/economicData.ts:109</t>
         </is>
       </c>
     </row>
@@ -3952,7 +4000,7 @@
       <c r="A98" s="3" t="inlineStr"/>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>costBasis</t>
+          <t>fetchEconomicData</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr"/>
@@ -3963,22 +4011,22 @@
       <c r="H98" s="3" t="inlineStr"/>
       <c r="I98" s="5" t="inlineStr">
         <is>
-          <t>HoldingDetail, Performance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J98" s="5" t="inlineStr">
         <is>
-          <t>buildPerformance, totalROI, unrealizedGain</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K98" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>Promise&lt;EconomicData&gt;</t>
         </is>
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:38</t>
+          <t>src/services/economicData.ts:47</t>
         </is>
       </c>
     </row>
@@ -3986,7 +4034,7 @@
       <c r="A99" s="3" t="inlineStr"/>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>earliestPurchaseDate</t>
+          <t>parseReceipt</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr"/>
@@ -4002,17 +4050,17 @@
       </c>
       <c r="J99" s="5" t="inlineStr">
         <is>
-          <t>buildPerformance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K99" s="5" t="inlineStr">
         <is>
-          <t>string | null</t>
+          <t>Promise&lt;</t>
         </is>
       </c>
       <c r="L99" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:128</t>
+          <t>src/services/economicData.ts:158</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4068,7 @@
       <c r="A100" s="3" t="inlineStr"/>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>factorOverMonths</t>
+          <t>confirmWrapper</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr"/>
@@ -4036,17 +4084,17 @@
       </c>
       <c r="J100" s="5" t="inlineStr">
         <is>
-          <t>lookBack</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K100" s="5" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>AssetAccount[]</t>
         </is>
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/lookBack.ts:19</t>
+          <t>src/services/sync/ingest.ts:173</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4102,7 @@
       <c r="A101" s="3" t="inlineStr"/>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>historyIsComplete</t>
+          <t>ingestSync</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr"/>
@@ -4070,17 +4118,17 @@
       </c>
       <c r="J101" s="5" t="inlineStr">
         <is>
-          <t>moneyWeightedReturn</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K101" s="5" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>SyncResult</t>
         </is>
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/moneyWeighted.ts:60</t>
+          <t>src/services/sync/ingest.ts:31</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4136,7 @@
       <c r="A102" s="3" t="inlineStr"/>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>isMoneyWeighted</t>
+          <t>stAssetId</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr"/>
@@ -4099,22 +4147,22 @@
       <c r="H102" s="3" t="inlineStr"/>
       <c r="I102" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J102" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ingestSync</t>
         </is>
       </c>
       <c r="K102" s="5" t="inlineStr">
         <is>
-          <t>r is MoneyWeighted</t>
+          <t>(inferred)</t>
         </is>
       </c>
       <c r="L102" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/moneyWeighted.ts:110</t>
+          <t>src/services/sync/ingest.ts:29</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4170,7 @@
       <c r="A103" s="3" t="inlineStr"/>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>latestClose</t>
+          <t>fetchPriceSeries</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr"/>
@@ -4138,17 +4186,17 @@
       </c>
       <c r="J103" s="5" t="inlineStr">
         <is>
-          <t>buildPerformance, periodReturn, periodReturnSince</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K103" s="5" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>Promise&lt;Record&lt;string, PriceSeries&gt;&gt;</t>
         </is>
       </c>
       <c r="L103" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:102</t>
+          <t>src/services/marketData.ts:71</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4204,7 @@
       <c r="A104" s="3" t="inlineStr"/>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>lookBack</t>
+          <t>isPlausibleTicker</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr"/>
@@ -4167,7 +4215,7 @@
       <c r="H104" s="3" t="inlineStr"/>
       <c r="I104" s="5" t="inlineStr">
         <is>
-          <t>LookBack</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J104" s="5" t="inlineStr">
@@ -4177,12 +4225,12 @@
       </c>
       <c r="K104" s="5" t="inlineStr">
         <is>
-          <t>LookBackResult | null</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="L104" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/lookBack.ts:32</t>
+          <t>src/services/marketData.ts:53</t>
         </is>
       </c>
     </row>
@@ -4190,7 +4238,7 @@
       <c r="A105" s="3" t="inlineStr"/>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>marketValue</t>
+          <t>priceFreshness</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr"/>
@@ -4206,33 +4254,61 @@
       </c>
       <c r="J105" s="5" t="inlineStr">
         <is>
-          <t>buildPerformance, unrealizedGain</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K105" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>PriceFreshness</t>
         </is>
       </c>
       <c r="L105" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:45</t>
+          <t>src/services/marketData.ts:60</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="inlineStr"/>
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>INGEST_ACTIVITY_KEY</t>
+        </is>
+      </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>periodReturn</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr"/>
-      <c r="D106" s="3" t="inlineStr"/>
-      <c r="E106" s="3" t="inlineStr"/>
-      <c r="F106" s="3" t="inlineStr"/>
-      <c r="G106" s="3" t="inlineStr"/>
-      <c r="H106" s="3" t="inlineStr"/>
+          <t>activityKey</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>Have we already ingested this activity?</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>accountId + date + type + symbol + amount</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>accountId · trade_date or settlement_date · type · symbol · amount</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>the broker payload plus our own account id</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>The ACCOUNT ID is part of the key, so the same trade in two accounts is correctly two activities. CORRECTED BY PROBE — I first documented this as taking the activity alone.</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>Calculation Module code/probes/broken-family.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I106" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -4240,32 +4316,56 @@
       </c>
       <c r="J106" s="5" t="inlineStr">
         <is>
-          <t>buildPerformance</t>
+          <t>dedupeActivities, ingestSync</t>
         </is>
       </c>
       <c r="K106" s="5" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>string</t>
         </is>
       </c>
       <c r="L106" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:107</t>
+          <t>src/services/sync/snaptrade.ts:243</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="inlineStr"/>
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>Which of these activities are new since the last sync?</t>
+        </is>
+      </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>periodReturnSince</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr"/>
-      <c r="D107" s="3" t="inlineStr"/>
-      <c r="E107" s="3" t="inlineStr"/>
-      <c r="F107" s="3" t="inlineStr"/>
-      <c r="G107" s="3" t="inlineStr"/>
+          <t>dedupeActivities</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>keep an activity only if its key is unseen</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>accountId · incoming activities · seenKeys (persisted)</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>seenKeys is stored between syncs</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>Stateful ACROSS syncs, not just within one batch — otherwise every refresh would re-add the same trades and inflate contributions without limit. Repeats inside one batch are caught too. CORRECTED BY PROBE — I first documented it as batch-only.</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>Calculation Module code/probes/broken-family.probe.test.ts</t>
+        </is>
+      </c>
       <c r="H107" s="3" t="inlineStr"/>
       <c r="I107" s="5" t="inlineStr">
         <is>
@@ -4274,17 +4374,17 @@
       </c>
       <c r="J107" s="5" t="inlineStr">
         <is>
-          <t>buildPerformance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K107" s="5" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>StActivity[]</t>
         </is>
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:119</t>
+          <t>src/services/sync/snaptrade.ts:255</t>
         </is>
       </c>
     </row>
@@ -4292,7 +4392,7 @@
       <c r="A108" s="3" t="inlineStr"/>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>portfolioBenchReturn</t>
+          <t>mapAccountType</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr"/>
@@ -4303,56 +4403,80 @@
       <c r="H108" s="3" t="inlineStr"/>
       <c r="I108" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J108" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ingestSync</t>
         </is>
       </c>
       <c r="K108" s="5" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>WrapperGuess</t>
         </is>
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:275</t>
+          <t>src/services/sync/snaptrade.ts:71</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="inlineStr"/>
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>Is this broker activity money arriving, money leaving, or an internal move?</t>
+        </is>
+      </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>portfolioPeriodReturn</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr"/>
-      <c r="D109" s="3" t="inlineStr"/>
-      <c r="E109" s="3" t="inlineStr"/>
-      <c r="F109" s="3" t="inlineStr"/>
-      <c r="G109" s="3" t="inlineStr"/>
+          <t>mapActivityType</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>a lookup table from the broker activity type to our transaction type</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>activity type · option_symbol / option_type</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>the broker payload (SnapTrade activity)</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>THE RULE THAT BROKE VANGUARD. Only CONTRIBUTION is external money IN and only WITHDRAWAL is external money OUT. A BUY or SELL is INTERNAL and must never become either, because deposits feed the personal-return figure and faking them corrupts it. Option trades map to BUY/SELL for the same reason. The table itself is CORRECT — verified by probe — so the $1.4m of phantom contributions enters somewhere else and is still being traced.</t>
+        </is>
+      </c>
+      <c r="G109" s="3" t="inlineStr">
+        <is>
+          <t>Calculation Module code/probes/broken-family.probe.test.ts</t>
+        </is>
+      </c>
       <c r="H109" s="3" t="inlineStr"/>
       <c r="I109" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J109" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ingestSync</t>
         </is>
       </c>
       <c r="K109" s="5" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>MappedActivity</t>
         </is>
       </c>
       <c r="L109" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:265</t>
+          <t>src/services/sync/snaptrade.ts:184</t>
         </is>
       </c>
     </row>
@@ -4360,7 +4484,7 @@
       <c r="A110" s="3" t="inlineStr"/>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>portfolioTrend</t>
+          <t>mapOptionHolding</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr"/>
@@ -4371,41 +4495,65 @@
       <c r="H110" s="3" t="inlineStr"/>
       <c r="I110" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J110" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ingestSync</t>
         </is>
       </c>
       <c r="K110" s="5" t="inlineStr">
         <is>
-          <t>TrendPoint[]</t>
+          <t>MappedOption | null</t>
         </is>
       </c>
       <c r="L110" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:239</t>
+          <t>src/services/sync/snaptrade.ts:159</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="inlineStr"/>
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>What asset class is this holding, and what is it worth?</t>
+        </is>
+      </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>realizedFromLedger</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr"/>
-      <c r="D111" s="3" t="inlineStr"/>
-      <c r="E111" s="3" t="inlineStr"/>
-      <c r="F111" s="3" t="inlineStr"/>
-      <c r="G111" s="3" t="inlineStr"/>
+          <t>mapPosition</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>assetClass = bonds if type=bnd or the DESCRIPTION looks fixed-income or the ticker is a T-bill ETF; alternatives if crypto; else stocks_etf</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>symbol · description · type code · units · price · average_purchase_price · cash_equivalent · tax_lots</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>all from the broker payload (SnapTrade position)</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>FOUNDER RULE 2026-08-04 — cash means cash only: anything paying dividends or interest goes to a MEASURED bucket, or the return maths silently loses its income. A CD arrives with a CUSIP and no bond type code, and its maturity is ONLY inside the description text, so the description is parsed. No symbol or zero units returns null rather than a zero-value holding.</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>Calculation Module code/probes/broken-family.probe.test.ts</t>
+        </is>
+      </c>
       <c r="H111" s="3" t="inlineStr"/>
       <c r="I111" s="5" t="inlineStr">
         <is>
-          <t>HoldingDetail</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J111" s="5" t="inlineStr">
@@ -4415,12 +4563,12 @@
       </c>
       <c r="K111" s="5" t="inlineStr">
         <is>
-          <t>RealizedResult</t>
+          <t>MappedPosition | null</t>
         </is>
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/realized.ts:14</t>
+          <t>src/services/sync/snaptrade.ts:116</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4576,7 @@
       <c r="A112" s="3" t="inlineStr"/>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>startDateFor</t>
+          <t>mergeHistoryFrom</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr"/>
@@ -4439,56 +4587,80 @@
       <c r="H112" s="3" t="inlineStr"/>
       <c r="I112" s="5" t="inlineStr">
         <is>
-          <t>HoldingDetail</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J112" s="5" t="inlineStr">
         <is>
-          <t>buildPerformance, periodReturn, portfolioTrend</t>
+          <t>ingestSync</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>string | undefined</t>
         </is>
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:81</t>
+          <t>src/services/sync/snaptrade.ts:282</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="inlineStr"/>
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>How much uninvested cash does this account really hold?</t>
+        </is>
+      </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>topHoldingConcentration</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="inlineStr"/>
-      <c r="D113" s="3" t="inlineStr"/>
-      <c r="E113" s="3" t="inlineStr"/>
-      <c r="F113" s="3" t="inlineStr"/>
-      <c r="G113" s="3" t="inlineStr"/>
+          <t>netCashSleeve</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>sleeve = balances.cash − Σ(cash-equivalent position values), floored only for rounding dust</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>balances.cash · every position flagged cash_equivalent (price × shares)</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>the broker payload</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>The broker's cash figure INCLUDES money-market funds that also appear as holdings, so they are subtracted or the same money is counted twice. A genuine margin debit stays NEGATIVE — flooring it overstated the account (audit fix); only sub-dollar dust clamps to zero.</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>Calculation Module code/probes/broken-family.probe.test.ts</t>
+        </is>
+      </c>
       <c r="H113" s="3" t="inlineStr"/>
       <c r="I113" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J113" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ingestSync</t>
         </is>
       </c>
       <c r="K113" s="5" t="inlineStr">
         <is>
-          <t>(inferred)</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L113" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:205</t>
+          <t>src/services/sync/snaptrade.ts:269</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4668,7 @@
       <c r="A114" s="3" t="inlineStr"/>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>totalROI</t>
+          <t>buildNetWorth</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr"/>
@@ -4507,22 +4679,22 @@
       <c r="H114" s="3" t="inlineStr"/>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>NetWorth</t>
         </is>
       </c>
       <c r="J114" s="5" t="inlineStr">
         <is>
-          <t>buildPerformance</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K114" s="5" t="inlineStr">
         <is>
-          <t>number | null</t>
+          <t>NetWorthState</t>
         </is>
       </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:74</t>
+          <t>src/domain/networth/index.ts:12</t>
         </is>
       </c>
     </row>
@@ -4530,7 +4702,7 @@
       <c r="A115" s="3" t="inlineStr"/>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>totalShares</t>
+          <t>allocation</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr"/>
@@ -4541,22 +4713,22 @@
       <c r="H115" s="3" t="inlineStr"/>
       <c r="I115" s="5" t="inlineStr">
         <is>
-          <t>HoldingDetail, Performance</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="J115" s="5" t="inlineStr">
         <is>
-          <t>marketValue, portfolioTrend</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K115" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>AllocSlice[]</t>
         </is>
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:35</t>
+          <t>src/domain/performance/index.ts:226</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4736,7 @@
       <c r="A116" s="3" t="inlineStr"/>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>unrealizedGain</t>
+          <t>attribution</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr"/>
@@ -4575,22 +4747,22 @@
       <c r="H116" s="3" t="inlineStr"/>
       <c r="I116" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="J116" s="5" t="inlineStr">
         <is>
-          <t>buildPerformance, totalROI</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>(inferred)</t>
         </is>
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:49</t>
+          <t>src/domain/performance/index.ts:215</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4770,7 @@
       <c r="A117" s="3" t="inlineStr"/>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>userFlows</t>
+          <t>benchmarkTicker</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr"/>
@@ -4609,22 +4781,22 @@
       <c r="H117" s="3" t="inlineStr"/>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HoldingDetail, Performance</t>
         </is>
       </c>
       <c r="J117" s="5" t="inlineStr">
         <is>
-          <t>moneyWeightedReturn</t>
+          <t>buildPerformance</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr">
         <is>
-          <t>(inferred)</t>
+          <t>string</t>
         </is>
       </c>
       <c r="L117" s="5" t="inlineStr">
         <is>
-          <t>src/domain/performance/moneyWeighted.ts:27</t>
+          <t>src/domain/performance/index.ts:149</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4804,7 @@
       <c r="A118" s="3" t="inlineStr"/>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>onCourseSentence</t>
+          <t>buildPerformance</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr"/>
@@ -4643,7 +4815,7 @@
       <c r="H118" s="3" t="inlineStr"/>
       <c r="I118" s="5" t="inlineStr">
         <is>
-          <t>NetWorth</t>
+          <t>HoldingDetail, Performance</t>
         </is>
       </c>
       <c r="J118" s="5" t="inlineStr">
@@ -4653,12 +4825,12 @@
       </c>
       <c r="K118" s="5" t="inlineStr">
         <is>
-          <t>(inferred)</t>
+          <t>PerformanceRow[]</t>
         </is>
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>src/domain/planning/hub.ts:165</t>
+          <t>src/domain/performance/index.ts:173</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4838,7 @@
       <c r="A119" s="3" t="inlineStr"/>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>planDoor</t>
+          <t>capGains</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr"/>
@@ -4677,7 +4849,7 @@
       <c r="H119" s="3" t="inlineStr"/>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>NetWorth</t>
+          <t>HoldingDetail, Performance</t>
         </is>
       </c>
       <c r="J119" s="5" t="inlineStr">
@@ -4687,12 +4859,12 @@
       </c>
       <c r="K119" s="5" t="inlineStr">
         <is>
-          <t>PlanDoor</t>
+          <t>CapGains</t>
         </is>
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>src/domain/planning/hub.ts:44</t>
+          <t>src/domain/performance/index.ts:55</t>
         </is>
       </c>
     </row>
@@ -4700,7 +4872,7 @@
       <c r="A120" s="3" t="inlineStr"/>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>shortfallAgeFromBand</t>
+          <t>capGainsTax</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr"/>
@@ -4711,7 +4883,7 @@
       <c r="H120" s="3" t="inlineStr"/>
       <c r="I120" s="5" t="inlineStr">
         <is>
-          <t>NetWorth</t>
+          <t>HoldingDetail, Performance</t>
         </is>
       </c>
       <c r="J120" s="5" t="inlineStr">
@@ -4721,12 +4893,12 @@
       </c>
       <c r="K120" s="5" t="inlineStr">
         <is>
-          <t>(inferred)</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>src/domain/planning/hub.ts:162</t>
+          <t>src/domain/performance/index.ts:69</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4906,7 @@
       <c r="A121" s="3" t="inlineStr"/>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>resolveLens</t>
+          <t>costBasis</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr"/>
@@ -4745,22 +4917,22 @@
       <c r="H121" s="3" t="inlineStr"/>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>NetWorth</t>
+          <t>HoldingDetail, Performance</t>
         </is>
       </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>buildPerformance, totalROI, unrealizedGain</t>
         </is>
       </c>
       <c r="K121" s="5" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>src/domain/profile/lens.ts:17</t>
+          <t>src/domain/performance/index.ts:38</t>
         </is>
       </c>
     </row>
@@ -4768,7 +4940,7 @@
       <c r="A122" s="3" t="inlineStr"/>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>colFactor</t>
+          <t>earliestPurchaseDate</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr"/>
@@ -4784,17 +4956,17 @@
       </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
-          <t>retirementSpendMonthly</t>
+          <t>buildPerformance</t>
         </is>
       </c>
       <c r="K122" s="5" t="inlineStr">
         <is>
-          <t>ColMatch</t>
+          <t>string | null</t>
         </is>
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>src/domain/retirement/col.ts:53</t>
+          <t>src/domain/performance/index.ts:128</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4974,7 @@
       <c r="A123" s="3" t="inlineStr"/>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>projectNestEgg</t>
+          <t>factorOverMonths</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr"/>
@@ -4813,22 +4985,22 @@
       <c r="H123" s="3" t="inlineStr"/>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>NetWorth, WhatIf</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J123" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>lookBack</t>
         </is>
       </c>
       <c r="K123" s="5" t="inlineStr">
         <is>
-          <t>NestEggProjection</t>
+          <t>number | null</t>
         </is>
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>src/domain/retirement/index.ts:294</t>
+          <t>src/domain/performance/lookBack.ts:19</t>
         </is>
       </c>
     </row>
@@ -4836,7 +5008,7 @@
       <c r="A124" s="3" t="inlineStr"/>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>retirementSpendMonthly</t>
+          <t>historyIsComplete</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr"/>
@@ -4852,17 +5024,17 @@
       </c>
       <c r="J124" s="5" t="inlineStr">
         <is>
-          <t>selectWillItLast, willItLastInputs</t>
+          <t>moneyWeightedReturn</t>
         </is>
       </c>
       <c r="K124" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>src/domain/retirement/index.ts:48</t>
+          <t>src/domain/performance/moneyWeighted.ts:60</t>
         </is>
       </c>
     </row>
@@ -4870,7 +5042,7 @@
       <c r="A125" s="3" t="inlineStr"/>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>selectWillItLast</t>
+          <t>isMoneyWeighted</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr"/>
@@ -4881,7 +5053,7 @@
       <c r="H125" s="3" t="inlineStr"/>
       <c r="I125" s="5" t="inlineStr">
         <is>
-          <t>NetWorth</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="J125" s="5" t="inlineStr">
@@ -4891,12 +5063,12 @@
       </c>
       <c r="K125" s="5" t="inlineStr">
         <is>
-          <t>WillItLastResult</t>
+          <t>r is MoneyWeighted</t>
         </is>
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>src/domain/retirement/willItLast.ts:115</t>
+          <t>src/domain/performance/moneyWeighted.ts:110</t>
         </is>
       </c>
     </row>
@@ -4904,7 +5076,7 @@
       <c r="A126" s="3" t="inlineStr"/>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>simulate</t>
+          <t>latestClose</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr"/>
@@ -4915,22 +5087,22 @@
       <c r="H126" s="3" t="inlineStr"/>
       <c r="I126" s="5" t="inlineStr">
         <is>
-          <t>NetWorth, WhatIf</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J126" s="5" t="inlineStr">
         <is>
-          <t>selectWillItLast</t>
+          <t>buildPerformance, periodReturn, periodReturnSince</t>
         </is>
       </c>
       <c r="K126" s="5" t="inlineStr">
         <is>
-          <t>(inferred)</t>
+          <t>number | null</t>
         </is>
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>src/domain/retirement/index.ts:160</t>
+          <t>src/domain/performance/index.ts:102</t>
         </is>
       </c>
     </row>
@@ -4938,7 +5110,7 @@
       <c r="A127" s="3" t="inlineStr"/>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>ssBenefitAtClaimAge</t>
+          <t>lookBack</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr"/>
@@ -4949,22 +5121,22 @@
       <c r="H127" s="3" t="inlineStr"/>
       <c r="I127" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LookBack</t>
         </is>
       </c>
       <c r="J127" s="5" t="inlineStr">
         <is>
-          <t>willItLastInputs</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K127" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>LookBackResult | null</t>
         </is>
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>src/domain/retirement/ssTiming.ts:25</t>
+          <t>src/domain/performance/lookBack.ts:32</t>
         </is>
       </c>
     </row>
@@ -4972,7 +5144,7 @@
       <c r="A128" s="3" t="inlineStr"/>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>ssClaimFactor</t>
+          <t>marketValue</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr"/>
@@ -4988,7 +5160,7 @@
       </c>
       <c r="J128" s="5" t="inlineStr">
         <is>
-          <t>ssBenefitAtClaimAge</t>
+          <t>buildPerformance, unrealizedGain</t>
         </is>
       </c>
       <c r="K128" s="5" t="inlineStr">
@@ -4998,7 +5170,7 @@
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>src/domain/retirement/ssTiming.ts:12</t>
+          <t>src/domain/performance/index.ts:45</t>
         </is>
       </c>
     </row>
@@ -5006,7 +5178,7 @@
       <c r="A129" s="3" t="inlineStr"/>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>volOf</t>
+          <t>moneyWeightedReturn</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr"/>
@@ -5017,56 +5189,80 @@
       <c r="H129" s="3" t="inlineStr"/>
       <c r="I129" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="J129" s="5" t="inlineStr">
         <is>
-          <t>willItLastInputs</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K129" s="5" t="inlineStr">
         <is>
-          <t>(inferred)</t>
+          <t>MoneyWeighted | MoneyWeightedMiss</t>
         </is>
       </c>
       <c r="L129" s="5" t="inlineStr">
         <is>
-          <t>src/domain/retirement/willItLast.ts:19</t>
+          <t>src/domain/performance/moneyWeighted.ts:80</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="inlineStr"/>
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>What did this holding do over the chosen window?</t>
+        </is>
+      </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr"/>
-      <c r="D130" s="3" t="inlineStr"/>
-      <c r="E130" s="3" t="inlineStr"/>
-      <c r="F130" s="3" t="inlineStr"/>
-      <c r="G130" s="3" t="inlineStr"/>
+          <t>periodReturn</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>(latest close ÷ close at the window start) − 1</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>price series · named period · now</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>price series from the market-data service; period from the chips on Performance</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>It takes a NAMED period only (1M · 3M · 6M · YTD · 1Y · 3Y) and works the start date out itself. CONSEQUENCE WORTH KNOWING — it cannot answer an arbitrary window, so Vanguard's own statement range (1 Jan → 14 Aug) is not directly reproducible. No series returns null, never zero: "no data" and "no change" are different answers. CORRECTED BY PROBE — I first documented it as taking two dates.</t>
+        </is>
+      </c>
+      <c r="G130" s="3" t="inlineStr">
+        <is>
+          <t>Calculation Module code/probes/broken-family.probe.test.ts</t>
+        </is>
+      </c>
       <c r="H130" s="3" t="inlineStr"/>
       <c r="I130" s="5" t="inlineStr">
         <is>
-          <t>NetWorth, WhatIf</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J130" s="5" t="inlineStr">
         <is>
-          <t>selectWillItLast</t>
+          <t>buildPerformance</t>
         </is>
       </c>
       <c r="K130" s="5" t="inlineStr">
         <is>
-          <t>RetirementInputs | null</t>
+          <t>number | null</t>
         </is>
       </c>
       <c r="L130" s="5" t="inlineStr">
         <is>
-          <t>src/domain/retirement/willItLast.ts:47</t>
+          <t>src/domain/performance/index.ts:107</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5270,7 @@
       <c r="A131" s="3" t="inlineStr"/>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>resolveNetWorthRows</t>
+          <t>periodReturnSince</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr"/>
@@ -5085,22 +5281,22 @@
       <c r="H131" s="3" t="inlineStr"/>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>Performance, WhatIf</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J131" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>buildPerformance</t>
         </is>
       </c>
       <c r="K131" s="5" t="inlineStr">
         <is>
-          <t>NetWorthRows</t>
+          <t>number | null</t>
         </is>
       </c>
       <c r="L131" s="5" t="inlineStr">
         <is>
-          <t>src/domain/snapshot.ts:121</t>
+          <t>src/domain/performance/index.ts:119</t>
         </is>
       </c>
     </row>
@@ -5108,7 +5304,7 @@
       <c r="A132" s="3" t="inlineStr"/>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>cashEffect</t>
+          <t>portfolioBenchReturn</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr"/>
@@ -5119,22 +5315,974 @@
       <c r="H132" s="3" t="inlineStr"/>
       <c r="I132" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="J132" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="inlineStr">
+        <is>
+          <t>number | null</t>
+        </is>
+      </c>
+      <c r="L132" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:275</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr"/>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>portfolioPeriodReturn</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr"/>
+      <c r="D133" s="3" t="inlineStr"/>
+      <c r="E133" s="3" t="inlineStr"/>
+      <c r="F133" s="3" t="inlineStr"/>
+      <c r="G133" s="3" t="inlineStr"/>
+      <c r="H133" s="3" t="inlineStr"/>
+      <c r="I133" s="5" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="J133" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="inlineStr">
+        <is>
+          <t>number | null</t>
+        </is>
+      </c>
+      <c r="L133" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:265</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr"/>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>portfolioTrend</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr"/>
+      <c r="D134" s="3" t="inlineStr"/>
+      <c r="E134" s="3" t="inlineStr"/>
+      <c r="F134" s="3" t="inlineStr"/>
+      <c r="G134" s="3" t="inlineStr"/>
+      <c r="H134" s="3" t="inlineStr"/>
+      <c r="I134" s="5" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="J134" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="inlineStr">
+        <is>
+          <t>TrendPoint[]</t>
+        </is>
+      </c>
+      <c r="L134" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:239</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr"/>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>realizedFromLedger</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr"/>
+      <c r="D135" s="3" t="inlineStr"/>
+      <c r="E135" s="3" t="inlineStr"/>
+      <c r="F135" s="3" t="inlineStr"/>
+      <c r="G135" s="3" t="inlineStr"/>
+      <c r="H135" s="3" t="inlineStr"/>
+      <c r="I135" s="5" t="inlineStr">
+        <is>
+          <t>HoldingDetail</t>
+        </is>
+      </c>
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="inlineStr">
+        <is>
+          <t>RealizedResult</t>
+        </is>
+      </c>
+      <c r="L135" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/performance/realized.ts:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr"/>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>startDateFor</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr"/>
+      <c r="D136" s="3" t="inlineStr"/>
+      <c r="E136" s="3" t="inlineStr"/>
+      <c r="F136" s="3" t="inlineStr"/>
+      <c r="G136" s="3" t="inlineStr"/>
+      <c r="H136" s="3" t="inlineStr"/>
+      <c r="I136" s="5" t="inlineStr">
+        <is>
+          <t>HoldingDetail</t>
+        </is>
+      </c>
+      <c r="J136" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance, periodReturn, portfolioTrend</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="L136" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:81</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr"/>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>topHoldingConcentration</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr"/>
+      <c r="D137" s="3" t="inlineStr"/>
+      <c r="E137" s="3" t="inlineStr"/>
+      <c r="F137" s="3" t="inlineStr"/>
+      <c r="G137" s="3" t="inlineStr"/>
+      <c r="H137" s="3" t="inlineStr"/>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="J137" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="inlineStr">
+        <is>
+          <t>(inferred)</t>
+        </is>
+      </c>
+      <c r="L137" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:205</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr"/>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>totalROI</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr"/>
+      <c r="D138" s="3" t="inlineStr"/>
+      <c r="E138" s="3" t="inlineStr"/>
+      <c r="F138" s="3" t="inlineStr"/>
+      <c r="G138" s="3" t="inlineStr"/>
+      <c r="H138" s="3" t="inlineStr"/>
+      <c r="I138" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J138" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="inlineStr">
+        <is>
+          <t>number | null</t>
+        </is>
+      </c>
+      <c r="L138" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:74</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr"/>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>totalShares</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr"/>
+      <c r="D139" s="3" t="inlineStr"/>
+      <c r="E139" s="3" t="inlineStr"/>
+      <c r="F139" s="3" t="inlineStr"/>
+      <c r="G139" s="3" t="inlineStr"/>
+      <c r="H139" s="3" t="inlineStr"/>
+      <c r="I139" s="5" t="inlineStr">
+        <is>
+          <t>HoldingDetail, Performance</t>
+        </is>
+      </c>
+      <c r="J139" s="5" t="inlineStr">
+        <is>
+          <t>marketValue, portfolioTrend</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="L139" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr"/>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>unrealizedGain</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr"/>
+      <c r="D140" s="3" t="inlineStr"/>
+      <c r="E140" s="3" t="inlineStr"/>
+      <c r="F140" s="3" t="inlineStr"/>
+      <c r="G140" s="3" t="inlineStr"/>
+      <c r="H140" s="3" t="inlineStr"/>
+      <c r="I140" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J140" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance, totalROI</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="L140" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr"/>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>userFlows</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr"/>
+      <c r="D141" s="3" t="inlineStr"/>
+      <c r="E141" s="3" t="inlineStr"/>
+      <c r="F141" s="3" t="inlineStr"/>
+      <c r="G141" s="3" t="inlineStr"/>
+      <c r="H141" s="3" t="inlineStr"/>
+      <c r="I141" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J141" s="5" t="inlineStr">
+        <is>
+          <t>moneyWeightedReturn</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="inlineStr">
+        <is>
+          <t>(inferred)</t>
+        </is>
+      </c>
+      <c r="L141" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/performance/moneyWeighted.ts:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr"/>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>oddsLine</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr"/>
+      <c r="D142" s="3" t="inlineStr"/>
+      <c r="E142" s="3" t="inlineStr"/>
+      <c r="F142" s="3" t="inlineStr"/>
+      <c r="G142" s="3" t="inlineStr"/>
+      <c r="H142" s="3" t="inlineStr"/>
+      <c r="I142" s="5" t="inlineStr">
+        <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="J142" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L142" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/planning/hub.ts:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr"/>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>onCourseSentence</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr"/>
+      <c r="D143" s="3" t="inlineStr"/>
+      <c r="E143" s="3" t="inlineStr"/>
+      <c r="F143" s="3" t="inlineStr"/>
+      <c r="G143" s="3" t="inlineStr"/>
+      <c r="H143" s="3" t="inlineStr"/>
+      <c r="I143" s="5" t="inlineStr">
+        <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="J143" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="inlineStr">
+        <is>
+          <t>(inferred)</t>
+        </is>
+      </c>
+      <c r="L143" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/planning/hub.ts:165</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="3" t="inlineStr"/>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>planDoor</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr"/>
+      <c r="D144" s="3" t="inlineStr"/>
+      <c r="E144" s="3" t="inlineStr"/>
+      <c r="F144" s="3" t="inlineStr"/>
+      <c r="G144" s="3" t="inlineStr"/>
+      <c r="H144" s="3" t="inlineStr"/>
+      <c r="I144" s="5" t="inlineStr">
+        <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="J144" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="inlineStr">
+        <is>
+          <t>PlanDoor</t>
+        </is>
+      </c>
+      <c r="L144" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/planning/hub.ts:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="3" t="inlineStr"/>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>sampleAskLine</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr"/>
+      <c r="D145" s="3" t="inlineStr"/>
+      <c r="E145" s="3" t="inlineStr"/>
+      <c r="F145" s="3" t="inlineStr"/>
+      <c r="G145" s="3" t="inlineStr"/>
+      <c r="H145" s="3" t="inlineStr"/>
+      <c r="I145" s="5" t="inlineStr">
+        <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="J145" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L145" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/planning/hub.ts:152</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="3" t="inlineStr"/>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>sampleOddsLine</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr"/>
+      <c r="D146" s="3" t="inlineStr"/>
+      <c r="E146" s="3" t="inlineStr"/>
+      <c r="F146" s="3" t="inlineStr"/>
+      <c r="G146" s="3" t="inlineStr"/>
+      <c r="H146" s="3" t="inlineStr"/>
+      <c r="I146" s="5" t="inlineStr">
+        <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="J146" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L146" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/planning/hub.ts:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="3" t="inlineStr"/>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>shortfallAgeFromBand</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr"/>
+      <c r="D147" s="3" t="inlineStr"/>
+      <c r="E147" s="3" t="inlineStr"/>
+      <c r="F147" s="3" t="inlineStr"/>
+      <c r="G147" s="3" t="inlineStr"/>
+      <c r="H147" s="3" t="inlineStr"/>
+      <c r="I147" s="5" t="inlineStr">
+        <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="J147" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="inlineStr">
+        <is>
+          <t>(inferred)</t>
+        </is>
+      </c>
+      <c r="L147" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/planning/hub.ts:162</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr"/>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>resolveLens</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr"/>
+      <c r="D148" s="3" t="inlineStr"/>
+      <c r="E148" s="3" t="inlineStr"/>
+      <c r="F148" s="3" t="inlineStr"/>
+      <c r="G148" s="3" t="inlineStr"/>
+      <c r="H148" s="3" t="inlineStr"/>
+      <c r="I148" s="5" t="inlineStr">
+        <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="J148" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="L148" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/profile/lens.ts:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="inlineStr"/>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>colFactor</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr"/>
+      <c r="D149" s="3" t="inlineStr"/>
+      <c r="E149" s="3" t="inlineStr"/>
+      <c r="F149" s="3" t="inlineStr"/>
+      <c r="G149" s="3" t="inlineStr"/>
+      <c r="H149" s="3" t="inlineStr"/>
+      <c r="I149" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J149" s="5" t="inlineStr">
+        <is>
+          <t>retirementSpendMonthly</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="inlineStr">
+        <is>
+          <t>ColMatch</t>
+        </is>
+      </c>
+      <c r="L149" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/retirement/col.ts:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="inlineStr"/>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>projectNestEgg</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr"/>
+      <c r="D150" s="3" t="inlineStr"/>
+      <c r="E150" s="3" t="inlineStr"/>
+      <c r="F150" s="3" t="inlineStr"/>
+      <c r="G150" s="3" t="inlineStr"/>
+      <c r="H150" s="3" t="inlineStr"/>
+      <c r="I150" s="5" t="inlineStr">
+        <is>
+          <t>NetWorth, WhatIf</t>
+        </is>
+      </c>
+      <c r="J150" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="inlineStr">
+        <is>
+          <t>NestEggProjection</t>
+        </is>
+      </c>
+      <c r="L150" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/retirement/index.ts:294</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="inlineStr"/>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>retirementSpendMonthly</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr"/>
+      <c r="D151" s="3" t="inlineStr"/>
+      <c r="E151" s="3" t="inlineStr"/>
+      <c r="F151" s="3" t="inlineStr"/>
+      <c r="G151" s="3" t="inlineStr"/>
+      <c r="H151" s="3" t="inlineStr"/>
+      <c r="I151" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J151" s="5" t="inlineStr">
+        <is>
+          <t>selectWillItLast, willItLastInputs</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="L151" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/retirement/index.ts:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr"/>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>selectWillItLast</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr"/>
+      <c r="D152" s="3" t="inlineStr"/>
+      <c r="E152" s="3" t="inlineStr"/>
+      <c r="F152" s="3" t="inlineStr"/>
+      <c r="G152" s="3" t="inlineStr"/>
+      <c r="H152" s="3" t="inlineStr"/>
+      <c r="I152" s="5" t="inlineStr">
+        <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="J152" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="inlineStr">
+        <is>
+          <t>WillItLastResult</t>
+        </is>
+      </c>
+      <c r="L152" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/retirement/willItLast.ts:115</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr"/>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>simulate</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr"/>
+      <c r="D153" s="3" t="inlineStr"/>
+      <c r="E153" s="3" t="inlineStr"/>
+      <c r="F153" s="3" t="inlineStr"/>
+      <c r="G153" s="3" t="inlineStr"/>
+      <c r="H153" s="3" t="inlineStr"/>
+      <c r="I153" s="5" t="inlineStr">
+        <is>
+          <t>NetWorth, WhatIf</t>
+        </is>
+      </c>
+      <c r="J153" s="5" t="inlineStr">
+        <is>
+          <t>selectWillItLast</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="inlineStr">
+        <is>
+          <t>(inferred)</t>
+        </is>
+      </c>
+      <c r="L153" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/retirement/index.ts:160</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr"/>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>ssBenefitAtClaimAge</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr"/>
+      <c r="D154" s="3" t="inlineStr"/>
+      <c r="E154" s="3" t="inlineStr"/>
+      <c r="F154" s="3" t="inlineStr"/>
+      <c r="G154" s="3" t="inlineStr"/>
+      <c r="H154" s="3" t="inlineStr"/>
+      <c r="I154" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J154" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="L154" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/retirement/ssTiming.ts:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="3" t="inlineStr"/>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>ssClaimFactor</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr"/>
+      <c r="D155" s="3" t="inlineStr"/>
+      <c r="E155" s="3" t="inlineStr"/>
+      <c r="F155" s="3" t="inlineStr"/>
+      <c r="G155" s="3" t="inlineStr"/>
+      <c r="H155" s="3" t="inlineStr"/>
+      <c r="I155" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J155" s="5" t="inlineStr">
+        <is>
+          <t>ssBenefitAtClaimAge</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="L155" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/retirement/ssTiming.ts:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="3" t="inlineStr"/>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>volOf</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr"/>
+      <c r="D156" s="3" t="inlineStr"/>
+      <c r="E156" s="3" t="inlineStr"/>
+      <c r="F156" s="3" t="inlineStr"/>
+      <c r="G156" s="3" t="inlineStr"/>
+      <c r="H156" s="3" t="inlineStr"/>
+      <c r="I156" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J156" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="inlineStr">
+        <is>
+          <t>(inferred)</t>
+        </is>
+      </c>
+      <c r="L156" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/retirement/willItLast.ts:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="3" t="inlineStr"/>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr"/>
+      <c r="D157" s="3" t="inlineStr"/>
+      <c r="E157" s="3" t="inlineStr"/>
+      <c r="F157" s="3" t="inlineStr"/>
+      <c r="G157" s="3" t="inlineStr"/>
+      <c r="H157" s="3" t="inlineStr"/>
+      <c r="I157" s="5" t="inlineStr">
+        <is>
+          <t>NetWorth, WhatIf</t>
+        </is>
+      </c>
+      <c r="J157" s="5" t="inlineStr">
+        <is>
+          <t>selectWillItLast</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="inlineStr">
+        <is>
+          <t>RetirementInputs | null</t>
+        </is>
+      </c>
+      <c r="L157" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/retirement/willItLast.ts:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="3" t="inlineStr"/>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>resolveNetWorthRows</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr"/>
+      <c r="D158" s="3" t="inlineStr"/>
+      <c r="E158" s="3" t="inlineStr"/>
+      <c r="F158" s="3" t="inlineStr"/>
+      <c r="G158" s="3" t="inlineStr"/>
+      <c r="H158" s="3" t="inlineStr"/>
+      <c r="I158" s="5" t="inlineStr">
+        <is>
+          <t>Performance, WhatIf</t>
+        </is>
+      </c>
+      <c r="J158" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="inlineStr">
+        <is>
+          <t>NetWorthRows</t>
+        </is>
+      </c>
+      <c r="L158" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/snapshot.ts:121</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr"/>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>cashEffect</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr"/>
+      <c r="D159" s="3" t="inlineStr"/>
+      <c r="E159" s="3" t="inlineStr"/>
+      <c r="F159" s="3" t="inlineStr"/>
+      <c r="G159" s="3" t="inlineStr"/>
+      <c r="H159" s="3" t="inlineStr"/>
+      <c r="I159" s="5" t="inlineStr">
+        <is>
           <t>AccountDetail, Performance</t>
         </is>
       </c>
-      <c r="J132" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K132" s="5" t="inlineStr">
+      <c r="J159" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L132" s="5" t="inlineStr">
+      <c r="L159" s="5" t="inlineStr">
         <is>
           <t>src/domain/transactions/index.ts:227</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr"/>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>txnLabel</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr"/>
+      <c r="D160" s="3" t="inlineStr"/>
+      <c r="E160" s="3" t="inlineStr"/>
+      <c r="F160" s="3" t="inlineStr"/>
+      <c r="G160" s="3" t="inlineStr"/>
+      <c r="H160" s="3" t="inlineStr"/>
+      <c r="I160" s="5" t="inlineStr">
+        <is>
+          <t>AccountDetail, Performance</t>
+        </is>
+      </c>
+      <c r="J160" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L160" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/transactions/index.ts:224</t>
         </is>
       </c>
     </row>
@@ -5154,7 +6302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5174,7 +6322,7 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FORMATTING HELPERS · 16 · they shape numbers rather than compute them, but they are listed because a rounding or masking rule can change what a person reads.</t>
+          <t>FORMATTING HELPERS · 5 · they shape numbers rather than compute them, but they are listed because a rounding or masking rule can change what a person reads.</t>
         </is>
       </c>
     </row>
@@ -5278,7 +6426,7 @@
       <c r="A4" s="3" t="inlineStr"/>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>formatMoney</t>
+          <t>money</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr"/>
@@ -5289,12 +6437,12 @@
       <c r="H4" s="3" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HoldingDetail, Itemize, NetWorth, Performance</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>money</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -5304,7 +6452,7 @@
       </c>
       <c r="L4" s="5" t="inlineStr">
         <is>
-          <t>src/domain/_shared/money.ts:58</t>
+          <t>src/domain/_shared/num.ts:9</t>
         </is>
       </c>
     </row>
@@ -5312,7 +6460,7 @@
       <c r="A5" s="3" t="inlineStr"/>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>formatMoneyCents</t>
+          <t>money2</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
@@ -5323,12 +6471,12 @@
       <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ImportHoldings, Performance</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>money2</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -5338,7 +6486,7 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>src/domain/_shared/money.ts:74</t>
+          <t>src/domain/_shared/num.ts:11</t>
         </is>
       </c>
     </row>
@@ -5346,7 +6494,7 @@
       <c r="A6" s="3" t="inlineStr"/>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>money</t>
+          <t>moneyCompact</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr"/>
@@ -5357,7 +6505,7 @@
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>HoldingDetail, Itemize, NetWorth, Performance</t>
+          <t>NetWorth, Performance</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -5372,7 +6520,7 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>src/domain/_shared/num.ts:9</t>
+          <t>src/domain/_shared/money.ts:88</t>
         </is>
       </c>
     </row>
@@ -5380,7 +6528,7 @@
       <c r="A7" s="3" t="inlineStr"/>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>money2</t>
+          <t>round2</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
@@ -5391,396 +6539,22 @@
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>ImportHoldings, Performance</t>
+          <t>ImportHoldings</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>accountClassBreakdown, actualDebtPayment, allocation, annualCoupon, assetAllocation, buildAssetsState, buildDebtState, buildItemizedAccounts, buildNetWorth, capGains, capGainsTax, cashTotal, costBasis, earmarkedAmount, itemizeRemainder, itemizedTotal, lookBack, marketValue, minimumDebtService, normalizeSnapshot, planDoor, projectNestEgg, retirementEarmarkedValue, retirementSpendMonthly, salaryGrossByMonth, simulate, taxBucketSplit, trendPoints, unrealizedGain</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>number</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>src/domain/_shared/num.ts:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr"/>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>moneyCompact</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>NetWorth, Performance</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/_shared/money.ts:88</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr"/>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>round2</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>ImportHoldings</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>accountClassBreakdown, actualDebtPayment, allocation, annualCoupon, assetAllocation, buildAssetsState, buildDebtState, buildItemizedAccounts, buildNetWorth, capGains, capGainsTax, cashTotal, costBasis, earmarkedAmount, itemizeRemainder, itemizedTotal, lookBack, marketValue, minimumDebtService, normalizeSnapshot, planDoor, projectNestEgg, retirementEarmarkedValue, retirementSpendMonthly, salaryGrossByMonth, simulate, taxBucketSplit, trendPoints, unrealizedGain</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
           <t>src/domain/_shared/num.ts:12</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>classPortionLabel</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="3" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/assets/index.ts:480</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr"/>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>sourceWording</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr"/>
-      <c r="D11" s="3" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>AccountDetail, NetWorth</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/assets/index.ts:726</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>decodeCsvBase64</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>ImportHoldings</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="L12" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/import/holdingsImport.ts:61</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr"/>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>benchmarkTicker</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>HoldingDetail, Performance</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>buildPerformance</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/performance/index.ts:149</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr"/>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>moneyWeightedReturn</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>MoneyWeighted | MoneyWeightedMiss</t>
-        </is>
-      </c>
-      <c r="L14" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/performance/moneyWeighted.ts:80</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr"/>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>oddsLine</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/planning/hub.ts:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr"/>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>sampleAskLine</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="L16" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/planning/hub.ts:152</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>sampleOddsLine</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/planning/hub.ts:34</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>txnLabel</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>AccountDetail, Performance</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/transactions/index.ts:224</t>
         </is>
       </c>
     </row>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -250,20 +250,30 @@
     </comment>
     <comment ref="I2" authorId="0" shapeId="0">
       <text>
-        <t>Screens in scope that import it directly.</t>
+        <t>CORRECT · DEFECT · UNRESOLVED. What the code does today, judged against what it should do. Everything left of this column describes the code AS IT IS — including its bugs — because a probe can only execute what exists.</t>
       </text>
     </comment>
     <comment ref="J2" authorId="0" shapeId="0">
       <text>
-        <t>Other calculations that use it.</t>
+        <t>Only filled where Status is DEFECT. The corrected formula or rule. The difference between this column and the Formula column IS the work list — so the target never lives only in someone's head or a commit message.</t>
       </text>
     </comment>
     <comment ref="K2" authorId="0" shapeId="0">
       <text>
+        <t>Screens in scope that import it directly.</t>
+      </text>
+    </comment>
+    <comment ref="L2" authorId="0" shapeId="0">
+      <text>
+        <t>Other calculations that use it.</t>
+      </text>
+    </comment>
+    <comment ref="M2" authorId="0" shapeId="0">
+      <text>
         <t>Declared return type.</t>
       </text>
     </comment>
-    <comment ref="L2" authorId="0" shapeId="0">
+    <comment ref="N2" authorId="0" shapeId="0">
       <text>
         <t>file:line at the stamped commit.</t>
       </text>
@@ -320,20 +330,30 @@
     </comment>
     <comment ref="I2" authorId="0" shapeId="0">
       <text>
-        <t>Screens in scope that import it directly.</t>
+        <t>CORRECT · DEFECT · UNRESOLVED. What the code does today, judged against what it should do. Everything left of this column describes the code AS IT IS — including its bugs — because a probe can only execute what exists.</t>
       </text>
     </comment>
     <comment ref="J2" authorId="0" shapeId="0">
       <text>
-        <t>Other calculations that use it.</t>
+        <t>Only filled where Status is DEFECT. The corrected formula or rule. The difference between this column and the Formula column IS the work list — so the target never lives only in someone's head or a commit message.</t>
       </text>
     </comment>
     <comment ref="K2" authorId="0" shapeId="0">
       <text>
+        <t>Screens in scope that import it directly.</t>
+      </text>
+    </comment>
+    <comment ref="L2" authorId="0" shapeId="0">
+      <text>
+        <t>Other calculations that use it.</t>
+      </text>
+    </comment>
+    <comment ref="M2" authorId="0" shapeId="0">
+      <text>
         <t>Declared return type.</t>
       </text>
     </comment>
-    <comment ref="L2" authorId="0" shapeId="0">
+    <comment ref="N2" authorId="0" shapeId="0">
       <text>
         <t>file:line at the stamped commit.</t>
       </text>
@@ -632,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L160"/>
+  <dimension ref="A1:N160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -643,16 +663,18 @@
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="52" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CALCULATION INVENTORY · Phase 1 — Net worth, Performance and the 8 screens they open · 158 calculations · generated from commit 57a37b4 on 2026-08-17  ⚠ TREE WAS DIRTY. GREY columns are generated from the code and are overwritten on every regeneration — never edit them. CREAM columns are written by hand and preserved across regenerations. A row is not documented until its probe passes.</t>
+          <t>CALCULATION INVENTORY · Phase 1 — Net worth, Performance and the 8 screens they open · 158 calculations · generated from commit 57a37b4 on 2026-08-17  ⚠ TREE WAS DIRTY. EVERY FORMULA HERE DESCRIBES THE CODE AS IT IS TODAY, BUGS INCLUDED — you cannot fix what you have not described, and a probe can only execute what exists. Where the current behaviour is wrong, Status says DEFECT and the corrected version sits in WHAT IT SHOULD BE; the difference between those two columns is the work list. GREY columns are generated from the code and overwritten on every regeneration — never edit them. CREAM columns are written by hand and preserved. A row is not documented until its probe passes.</t>
         </is>
       </c>
     </row>
@@ -699,20 +721,30 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>WHAT IT SHOULD BE</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
           <t>Screens</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Called by</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Returns</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -731,22 +763,32 @@
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>currencySymbol</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>currencySymbol</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>src/domain/_shared/money.ts:49</t>
         </is>
@@ -765,22 +807,32 @@
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>money</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>money</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>src/domain/_shared/money.ts:58</t>
         </is>
@@ -799,22 +851,32 @@
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>money2</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>money2</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>src/domain/_shared/money.ts:74</t>
         </is>
@@ -833,22 +895,32 @@
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>ImportHoldings</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>assetsFromOnboarding, debtsFromOnboarding, ingestSync</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
+          <t>ImportHoldings</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>assetsFromOnboarding, debtsFromOnboarding, ingestSync</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
           <t>EntityId</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>src/domain/_shared/ids.ts:6</t>
         </is>
@@ -867,22 +939,32 @@
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>assetsFromOnboarding, debtsFromOnboarding, employerMatchMonthly, equityRowValue, monthlyContributionsFromOnboarding, plannedMonthlySpend, retirementIncomeMonthly, retirementSpendMonthly, rsuAnnual, salaryGrossByMonth, stateRateOf, tipsAnnual, totalGrossAnnual</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>assetsFromOnboarding, debtsFromOnboarding, employerMatchMonthly, equityRowValue, monthlyContributionsFromOnboarding, plannedMonthlySpend, retirementIncomeMonthly, retirementSpendMonthly, rsuAnnual, salaryGrossByMonth, stateRateOf, tipsAnnual, totalGrossAnnual</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>src/domain/_shared/num.ts:4</t>
         </is>
@@ -901,22 +983,32 @@
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="N8" s="5" t="inlineStr">
         <is>
           <t>src/domain/alternatives/index.ts:15</t>
         </is>
@@ -935,22 +1027,32 @@
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:116</t>
         </is>
@@ -969,22 +1071,32 @@
       <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>AccountDetail, NetWorth</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>assetAllocation, cashTotal</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail, NetWorth</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>assetAllocation, cashTotal</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
           <t>Record&lt;AssetClass, number&gt; | null</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:416</t>
         </is>
@@ -1003,22 +1115,32 @@
       <c r="F11" s="3" t="inlineStr"/>
       <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>AccountDetail, NetWorth, Performance</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail, NetWorth, Performance</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
           <t>Map&lt;string, string&gt;</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:394</t>
         </is>
@@ -1037,22 +1159,32 @@
       <c r="F12" s="3" t="inlineStr"/>
       <c r="G12" s="3" t="inlineStr"/>
       <c r="H12" s="3" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
           <t>Record&lt;AssetClass, number&gt;</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:517</t>
         </is>
@@ -1071,22 +1203,32 @@
       <c r="F13" s="3" t="inlineStr"/>
       <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>AccountDetail, NetWorth, Performance</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>accountAllowsTicker, accountClassBreakdown, assetAllocation, cashTotal, earmarkDefault, investmentsTotal, isBond, isRealAsset, primaryCarIdOf</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail, NetWorth, Performance</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>accountAllowsTicker, accountClassBreakdown, assetAllocation, cashTotal, earmarkDefault, investmentsTotal, isBond, isRealAsset, primaryCarIdOf</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
           <t>AssetClass</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:236</t>
         </is>
@@ -1105,22 +1247,32 @@
       <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>AccountDetail, NetWorth, Performance</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="J14" s="3" t="inlineStr">
         <is>
           <t>benchmarkReturn, isCashKind</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail, NetWorth, Performance</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
+          <t>benchmarkReturn, isCashKind</t>
+        </is>
+      </c>
+      <c r="M14" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:165</t>
         </is>
@@ -1139,22 +1291,32 @@
       <c r="F15" s="3" t="inlineStr"/>
       <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
         <is>
           <t>resolveNetWorthRows</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>resolveNetWorthRows</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="inlineStr">
+        <is>
           <t>AssetsDoc</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:690</t>
         </is>
@@ -1173,22 +1335,32 @@
       <c r="F16" s="3" t="inlineStr"/>
       <c r="G16" s="3" t="inlineStr"/>
       <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>AccountDetail, Performance</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>blendedReturn</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail, Performance</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>blendedReturn</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:569</t>
         </is>
@@ -1207,22 +1379,32 @@
       <c r="F17" s="3" t="inlineStr"/>
       <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:653</t>
         </is>
@@ -1241,22 +1423,32 @@
       <c r="F18" s="3" t="inlineStr"/>
       <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:612</t>
         </is>
@@ -1275,22 +1467,32 @@
       <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
           <t>AssetsState</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:678</t>
         </is>
@@ -1309,22 +1511,32 @@
       <c r="F20" s="3" t="inlineStr"/>
       <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>Itemize</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
+          <t>Itemize</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
           <t>Omit&lt;AssetAccount, 'asset_id'&gt;[]</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/itemize.ts:48</t>
         </is>
@@ -1343,22 +1555,32 @@
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:286</t>
         </is>
@@ -1377,22 +1599,32 @@
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr"/>
       <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:480</t>
         </is>
@@ -1411,22 +1643,32 @@
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="3" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
         <is>
           <t>earmarkedAmount</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>earmarkedAmount</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:543</t>
         </is>
@@ -1445,22 +1687,32 @@
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr"/>
       <c r="H24" s="3" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>blendedReturn, blendedVolatility, portfolioActualReturn, retirementEarmarkedValue, taxBucketSplit</t>
         </is>
       </c>
       <c r="K24" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>blendedReturn, blendedVolatility, portfolioActualReturn, retirementEarmarkedValue, taxBucketSplit</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr">
+      <c r="N24" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:558</t>
         </is>
@@ -1479,22 +1731,32 @@
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
         <is>
           <t>accountClassBreakdown, assetClassOf, classifyHolding</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>accountClassBreakdown, assetClassOf, classifyHolding</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
           <t>AssetClass | null</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="N25" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:202</t>
         </is>
@@ -1513,22 +1775,32 @@
       <c r="F26" s="3" t="inlineStr"/>
       <c r="G26" s="3" t="inlineStr"/>
       <c r="H26" s="3" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="N26" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:311</t>
         </is>
@@ -1547,22 +1819,32 @@
       <c r="F27" s="3" t="inlineStr"/>
       <c r="G27" s="3" t="inlineStr"/>
       <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="J27" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="N27" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:306</t>
         </is>
@@ -1581,22 +1863,32 @@
       <c r="F28" s="3" t="inlineStr"/>
       <c r="G28" s="3" t="inlineStr"/>
       <c r="H28" s="3" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="L28" s="5" t="inlineStr">
+      <c r="N28" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:164</t>
         </is>
@@ -1615,22 +1907,32 @@
       <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="3" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>investableAssets</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>investableAssets</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="N29" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:268</t>
         </is>
@@ -1649,22 +1951,32 @@
       <c r="F30" s="3" t="inlineStr"/>
       <c r="G30" s="3" t="inlineStr"/>
       <c r="H30" s="3" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>Itemize</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>itemizeRemainder</t>
         </is>
       </c>
       <c r="K30" s="5" t="inlineStr">
         <is>
+          <t>Itemize</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>itemizeRemainder</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr">
+      <c r="N30" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/itemize.ts:28</t>
         </is>
@@ -1683,22 +1995,32 @@
       <c r="F31" s="3" t="inlineStr"/>
       <c r="G31" s="3" t="inlineStr"/>
       <c r="H31" s="3" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>Itemize</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>buildItemizedAccounts</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
+          <t>Itemize</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>buildItemizedAccounts</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr">
+      <c r="N31" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/itemize.ts:32</t>
         </is>
@@ -1717,22 +2039,32 @@
       <c r="F32" s="3" t="inlineStr"/>
       <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="3" t="inlineStr"/>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
           <t>'cash' | 'bonds'</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr">
+      <c r="N32" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:215</t>
         </is>
@@ -1751,22 +2083,32 @@
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="3" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="N33" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:710</t>
         </is>
@@ -1785,22 +2127,32 @@
       <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" s="3" t="inlineStr"/>
       <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:106</t>
         </is>
@@ -1819,22 +2171,32 @@
       <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="3" t="inlineStr"/>
       <c r="H35" s="3" t="inlineStr"/>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
         <is>
           <t>blendedReturn, blendedVolatility, retirementEarmarkedValue</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>blendedReturn, blendedVolatility, retirementEarmarkedValue</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
           <t>string | undefined</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr">
+      <c r="N35" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:552</t>
         </is>
@@ -1853,22 +2215,32 @@
       <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" s="3" t="inlineStr"/>
       <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>earmarkDefault</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>earmarkDefault</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
           <t>RealEstateUse</t>
         </is>
       </c>
-      <c r="L36" s="5" t="inlineStr">
+      <c r="N36" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:262</t>
         </is>
@@ -1887,22 +2259,32 @@
       <c r="F37" s="3" t="inlineStr"/>
       <c r="G37" s="3" t="inlineStr"/>
       <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
         <is>
           <t>planDoor, selectWillItLast, willItLastInputs</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>planDoor, selectWillItLast, willItLastInputs</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L37" s="5" t="inlineStr">
+      <c r="N37" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:563</t>
         </is>
@@ -1921,22 +2303,32 @@
       <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" s="3" t="inlineStr"/>
       <c r="H38" s="3" t="inlineStr"/>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="I38" s="3" t="inlineStr">
         <is>
           <t>AccountDetail, NetWorth</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail, NetWorth</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L38" s="5" t="inlineStr">
+      <c r="N38" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:726</t>
         </is>
@@ -1955,22 +2347,32 @@
       <c r="F39" s="3" t="inlineStr"/>
       <c r="G39" s="3" t="inlineStr"/>
       <c r="H39" s="3" t="inlineStr"/>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
           <t>TaxTreatment</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="N39" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:253</t>
         </is>
@@ -1989,22 +2391,32 @@
       <c r="F40" s="3" t="inlineStr"/>
       <c r="G40" s="3" t="inlineStr"/>
       <c r="H40" s="3" t="inlineStr"/>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="I40" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J40" s="5" t="inlineStr">
+      <c r="J40" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="N40" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:794</t>
         </is>
@@ -2023,22 +2435,32 @@
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="3" t="inlineStr"/>
       <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="I41" s="3" t="inlineStr">
         <is>
           <t>AccountDetail, Performance</t>
         </is>
       </c>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="J41" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail, Performance</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr">
+      <c r="N41" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:95</t>
         </is>
@@ -2057,22 +2479,32 @@
       <c r="F42" s="3" t="inlineStr"/>
       <c r="G42" s="3" t="inlineStr"/>
       <c r="H42" s="3" t="inlineStr"/>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J42" s="5" t="inlineStr">
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="L42" s="5" t="inlineStr">
+      <c r="N42" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:223</t>
         </is>
@@ -2091,22 +2523,32 @@
       <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="I43" s="3" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="J43" s="5" t="inlineStr">
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>approxYTM, currentYield</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>approxYTM, currentYield</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L43" s="5" t="inlineStr">
+      <c r="N43" s="5" t="inlineStr">
         <is>
           <t>src/domain/bonds/index.ts:21</t>
         </is>
@@ -2125,22 +2567,32 @@
       <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="I44" s="3" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="J44" s="5" t="inlineStr">
+      <c r="J44" s="3" t="inlineStr">
         <is>
           <t>bondRateSensitivity</t>
         </is>
       </c>
       <c r="K44" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail</t>
+        </is>
+      </c>
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>bondRateSensitivity</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="L44" s="5" t="inlineStr">
+      <c r="N44" s="5" t="inlineStr">
         <is>
           <t>src/domain/bonds/index.ts:33</t>
         </is>
@@ -2159,22 +2611,32 @@
       <c r="F45" s="3" t="inlineStr"/>
       <c r="G45" s="3" t="inlineStr"/>
       <c r="H45" s="3" t="inlineStr"/>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="J45" s="5" t="inlineStr">
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
           <t>BondInfo</t>
         </is>
       </c>
-      <c r="L45" s="5" t="inlineStr">
+      <c r="N45" s="5" t="inlineStr">
         <is>
           <t>src/domain/bonds/index.ts:16</t>
         </is>
@@ -2193,22 +2655,32 @@
       <c r="F46" s="3" t="inlineStr"/>
       <c r="G46" s="3" t="inlineStr"/>
       <c r="H46" s="3" t="inlineStr"/>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="J46" s="5" t="inlineStr">
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail</t>
+        </is>
+      </c>
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
           <t>RateSensitivity | null</t>
         </is>
       </c>
-      <c r="L46" s="5" t="inlineStr">
+      <c r="N46" s="5" t="inlineStr">
         <is>
           <t>src/domain/bonds/index.ts:97</t>
         </is>
@@ -2227,22 +2699,32 @@
       <c r="F47" s="3" t="inlineStr"/>
       <c r="G47" s="3" t="inlineStr"/>
       <c r="H47" s="3" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="I47" s="3" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="J47" s="5" t="inlineStr">
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="L47" s="5" t="inlineStr">
+      <c r="N47" s="5" t="inlineStr">
         <is>
           <t>src/domain/bonds/index.ts:29</t>
         </is>
@@ -2261,22 +2743,32 @@
       <c r="F48" s="3" t="inlineStr"/>
       <c r="G48" s="3" t="inlineStr"/>
       <c r="H48" s="3" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="I48" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="J48" s="5" t="inlineStr">
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="L48" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="L48" s="5" t="inlineStr">
+      <c r="N48" s="5" t="inlineStr">
         <is>
           <t>src/domain/bonds/index.ts:13</t>
         </is>
@@ -2295,22 +2787,32 @@
       <c r="F49" s="3" t="inlineStr"/>
       <c r="G49" s="3" t="inlineStr"/>
       <c r="H49" s="3" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="I49" s="3" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="J49" s="5" t="inlineStr">
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>approxYTM</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>approxYTM</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L49" s="5" t="inlineStr">
+      <c r="N49" s="5" t="inlineStr">
         <is>
           <t>src/domain/bonds/index.ts:24</t>
         </is>
@@ -2329,22 +2831,32 @@
       <c r="F50" s="3" t="inlineStr"/>
       <c r="G50" s="3" t="inlineStr"/>
       <c r="H50" s="3" t="inlineStr"/>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="I50" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J50" s="5" t="inlineStr">
+      <c r="J50" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M50" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L50" s="5" t="inlineStr">
+      <c r="N50" s="5" t="inlineStr">
         <is>
           <t>src/domain/budget/index.ts:45</t>
         </is>
@@ -2363,22 +2875,32 @@
       <c r="F51" s="3" t="inlineStr"/>
       <c r="G51" s="3" t="inlineStr"/>
       <c r="H51" s="3" t="inlineStr"/>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
         <is>
           <t>plannedMonthlySpend</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>plannedMonthlySpend</t>
+        </is>
+      </c>
+      <c r="M51" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="L51" s="5" t="inlineStr">
+      <c r="N51" s="5" t="inlineStr">
         <is>
           <t>src/domain/budget/index.ts:72</t>
         </is>
@@ -2397,22 +2919,32 @@
       <c r="F52" s="3" t="inlineStr"/>
       <c r="G52" s="3" t="inlineStr"/>
       <c r="H52" s="3" t="inlineStr"/>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
         <is>
           <t>buildDebtState</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>buildDebtState</t>
+        </is>
+      </c>
+      <c r="M52" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L52" s="5" t="inlineStr">
+      <c r="N52" s="5" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:59</t>
         </is>
@@ -2431,22 +2963,32 @@
       <c r="F53" s="3" t="inlineStr"/>
       <c r="G53" s="3" t="inlineStr"/>
       <c r="H53" s="3" t="inlineStr"/>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="I53" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J53" s="5" t="inlineStr">
+      <c r="J53" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
           <t>DebtState</t>
         </is>
       </c>
-      <c r="L53" s="5" t="inlineStr">
+      <c r="N53" s="5" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:214</t>
         </is>
@@ -2465,22 +3007,32 @@
       <c r="F54" s="3" t="inlineStr"/>
       <c r="G54" s="3" t="inlineStr"/>
       <c r="H54" s="3" t="inlineStr"/>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="I54" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J54" s="5" t="inlineStr">
+      <c r="J54" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M54" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="L54" s="5" t="inlineStr">
+      <c r="N54" s="5" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:197</t>
         </is>
@@ -2499,22 +3051,32 @@
       <c r="F55" s="3" t="inlineStr"/>
       <c r="G55" s="3" t="inlineStr"/>
       <c r="H55" s="3" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J55" s="5" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
         <is>
           <t>resolveNetWorthRows</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>resolveNetWorthRows</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
           <t>DebtDoc</t>
         </is>
       </c>
-      <c r="L55" s="5" t="inlineStr">
+      <c r="N55" s="5" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:240</t>
         </is>
@@ -2533,22 +3095,32 @@
       <c r="F56" s="3" t="inlineStr"/>
       <c r="G56" s="3" t="inlineStr"/>
       <c r="H56" s="3" t="inlineStr"/>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
         <is>
           <t>paymentShape</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>paymentShape</t>
+        </is>
+      </c>
+      <c r="M56" s="5" t="inlineStr">
+        <is>
           <t>NonNullable&lt;Debt['payment_type']&gt;</t>
         </is>
       </c>
-      <c r="L56" s="5" t="inlineStr">
+      <c r="N56" s="5" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:35</t>
         </is>
@@ -2567,22 +3139,32 @@
       <c r="F57" s="3" t="inlineStr"/>
       <c r="G57" s="3" t="inlineStr"/>
       <c r="H57" s="3" t="inlineStr"/>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
         <is>
           <t>debtsFromOnboarding</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>debtsFromOnboarding</t>
+        </is>
+      </c>
+      <c r="M57" s="5" t="inlineStr">
+        <is>
           <t>DebtType</t>
         </is>
       </c>
-      <c r="L57" s="5" t="inlineStr">
+      <c r="N57" s="5" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:228</t>
         </is>
@@ -2601,22 +3183,32 @@
       <c r="F58" s="3" t="inlineStr"/>
       <c r="G58" s="3" t="inlineStr"/>
       <c r="H58" s="3" t="inlineStr"/>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J58" s="5" t="inlineStr">
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
         <is>
           <t>buildDebtState</t>
         </is>
       </c>
       <c r="K58" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>buildDebtState</t>
+        </is>
+      </c>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L58" s="5" t="inlineStr">
+      <c r="N58" s="5" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:55</t>
         </is>
@@ -2635,22 +3227,32 @@
       <c r="F59" s="3" t="inlineStr"/>
       <c r="G59" s="3" t="inlineStr"/>
       <c r="H59" s="3" t="inlineStr"/>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J59" s="5" t="inlineStr">
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
         <is>
           <t>minimumDebtService, requiredPayment</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>minimumDebtService, requiredPayment</t>
+        </is>
+      </c>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
           <t>NonNullable&lt;Debt['payment_type']&gt;</t>
         </is>
       </c>
-      <c r="L59" s="5" t="inlineStr">
+      <c r="N59" s="5" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:38</t>
         </is>
@@ -2669,22 +3271,32 @@
       <c r="F60" s="3" t="inlineStr"/>
       <c r="G60" s="3" t="inlineStr"/>
       <c r="H60" s="3" t="inlineStr"/>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J60" s="5" t="inlineStr">
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
         <is>
           <t>totalDebtMonthly</t>
         </is>
       </c>
       <c r="K60" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L60" s="5" t="inlineStr">
+        <is>
+          <t>totalDebtMonthly</t>
+        </is>
+      </c>
+      <c r="M60" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L60" s="5" t="inlineStr">
+      <c r="N60" s="5" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:44</t>
         </is>
@@ -2703,22 +3315,32 @@
       <c r="F61" s="3" t="inlineStr"/>
       <c r="G61" s="3" t="inlineStr"/>
       <c r="H61" s="3" t="inlineStr"/>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J61" s="5" t="inlineStr">
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
         <is>
           <t>actualDebtPayment</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>actualDebtPayment</t>
+        </is>
+      </c>
+      <c r="M61" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L61" s="5" t="inlineStr">
+      <c r="N61" s="5" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:49</t>
         </is>
@@ -2737,22 +3359,32 @@
       <c r="F62" s="3" t="inlineStr"/>
       <c r="G62" s="3" t="inlineStr"/>
       <c r="H62" s="3" t="inlineStr"/>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J62" s="5" t="inlineStr">
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="K62" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="M62" s="5" t="inlineStr">
+        <is>
           <t>BucketSplit</t>
         </is>
       </c>
-      <c r="L62" s="5" t="inlineStr">
+      <c r="N62" s="5" t="inlineStr">
         <is>
           <t>src/domain/decumulation/index.ts:10</t>
         </is>
@@ -2771,22 +3403,32 @@
       <c r="F63" s="3" t="inlineStr"/>
       <c r="G63" s="3" t="inlineStr"/>
       <c r="H63" s="3" t="inlineStr"/>
-      <c r="I63" s="5" t="inlineStr">
+      <c r="I63" s="3" t="inlineStr">
         <is>
           <t>NetWorth, Performance</t>
         </is>
       </c>
-      <c r="J63" s="5" t="inlineStr">
+      <c r="J63" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K63" s="5" t="inlineStr">
         <is>
+          <t>NetWorth, Performance</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M63" s="5" t="inlineStr">
+        <is>
           <t>DataGap[]</t>
         </is>
       </c>
-      <c r="L63" s="5" t="inlineStr">
+      <c r="N63" s="5" t="inlineStr">
         <is>
           <t>src/domain/gaps/index.ts:57</t>
         </is>
@@ -2829,22 +3471,32 @@
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr"/>
-      <c r="I64" s="5" t="inlineStr">
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>STOP CALLING THE RESIDUAL A MEASUREMENT. Two changes. (1) The unexplained remainder gets its own honest row — "we could not account for $X" — instead of being printed as "change in investment value". A person can act on "unexplained"; they cannot act on a market loss that never happened. (2) Market movement is MEASURED where the evidence exists — from stored per-holding values — and the row is simply absent when it does not, rather than being inferred. Absent beats invented.</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="inlineStr">
         <is>
           <t>NetWorth, Performance</t>
         </is>
       </c>
-      <c r="J64" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K64" s="5" t="inlineStr">
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M64" s="5" t="inlineStr">
         <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="L64" s="5" t="inlineStr">
+      <c r="N64" s="5" t="inlineStr">
         <is>
           <t>src/domain/history.ts:144</t>
         </is>
@@ -2887,22 +3539,32 @@
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr"/>
-      <c r="I65" s="5" t="inlineStr">
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>THE BASELINE MUST BE A CHOSEN DATE, NOT AN ACCIDENT. Today it is whatever day the app happened to be opened. It should be a stated window the person picks (this month · this year · since I started), and where no snapshot exists at that date the app says so instead of quietly using a later one. Also: never overwrite the earliest point of a period — see the snapshot defect — or the baseline keeps moving toward today.</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J65" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K65" s="5" t="inlineStr">
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
         <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="L65" s="5" t="inlineStr">
+      <c r="N65" s="5" t="inlineStr">
         <is>
           <t>src/domain/history.ts:118</t>
         </is>
@@ -2921,22 +3583,32 @@
       <c r="F66" s="3" t="inlineStr"/>
       <c r="G66" s="3" t="inlineStr"/>
       <c r="H66" s="3" t="inlineStr"/>
-      <c r="I66" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J66" s="5" t="inlineStr">
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
         <is>
           <t>readHistory</t>
         </is>
       </c>
       <c r="K66" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>readHistory</t>
+        </is>
+      </c>
+      <c r="M66" s="5" t="inlineStr">
+        <is>
           <t>MonthlySnapshot | null</t>
         </is>
       </c>
-      <c r="L66" s="5" t="inlineStr">
+      <c r="N66" s="5" t="inlineStr">
         <is>
           <t>src/domain/history.ts:77</t>
         </is>
@@ -2955,22 +3627,32 @@
       <c r="F67" s="3" t="inlineStr"/>
       <c r="G67" s="3" t="inlineStr"/>
       <c r="H67" s="3" t="inlineStr"/>
-      <c r="I67" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J67" s="5" t="inlineStr">
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
         <is>
           <t>trendPoints</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>trendPoints</t>
+        </is>
+      </c>
+      <c r="M67" s="5" t="inlineStr">
+        <is>
           <t>MonthlySnapshot[]</t>
         </is>
       </c>
-      <c r="L67" s="5" t="inlineStr">
+      <c r="N67" s="5" t="inlineStr">
         <is>
           <t>src/domain/history.ts:107</t>
         </is>
@@ -2989,22 +3671,32 @@
       <c r="F68" s="3" t="inlineStr"/>
       <c r="G68" s="3" t="inlineStr"/>
       <c r="H68" s="3" t="inlineStr"/>
-      <c r="I68" s="5" t="inlineStr">
+      <c r="I68" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J68" s="5" t="inlineStr">
+      <c r="J68" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K68" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="5" t="inlineStr">
+        <is>
           <t>TrendPoint[]</t>
         </is>
       </c>
-      <c r="L68" s="5" t="inlineStr">
+      <c r="N68" s="5" t="inlineStr">
         <is>
           <t>src/domain/history.ts:43</t>
         </is>
@@ -3023,22 +3715,32 @@
       <c r="F69" s="3" t="inlineStr"/>
       <c r="G69" s="3" t="inlineStr"/>
       <c r="H69" s="3" t="inlineStr"/>
-      <c r="I69" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J69" s="5" t="inlineStr">
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
         <is>
           <t>importHoldings</t>
         </is>
       </c>
       <c r="K69" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>importHoldings</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
           <t>AssetClass</t>
         </is>
       </c>
-      <c r="L69" s="5" t="inlineStr">
+      <c r="N69" s="5" t="inlineStr">
         <is>
           <t>src/domain/import/holdingsImport.ts:154</t>
         </is>
@@ -3057,22 +3759,32 @@
       <c r="F70" s="3" t="inlineStr"/>
       <c r="G70" s="3" t="inlineStr"/>
       <c r="H70" s="3" t="inlineStr"/>
-      <c r="I70" s="5" t="inlineStr">
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t>ImportHoldings</t>
         </is>
       </c>
-      <c r="J70" s="5" t="inlineStr">
+      <c r="J70" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K70" s="5" t="inlineStr">
         <is>
+          <t>ImportHoldings</t>
+        </is>
+      </c>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L70" s="5" t="inlineStr">
+      <c r="N70" s="5" t="inlineStr">
         <is>
           <t>src/domain/import/holdingsImport.ts:61</t>
         </is>
@@ -3091,22 +3803,32 @@
       <c r="F71" s="3" t="inlineStr"/>
       <c r="G71" s="3" t="inlineStr"/>
       <c r="H71" s="3" t="inlineStr"/>
-      <c r="I71" s="5" t="inlineStr">
+      <c r="I71" s="3" t="inlineStr">
         <is>
           <t>ImportHoldings</t>
         </is>
       </c>
-      <c r="J71" s="5" t="inlineStr">
+      <c r="J71" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K71" s="5" t="inlineStr">
         <is>
+          <t>ImportHoldings</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
+        <is>
           <t>ImportResult</t>
         </is>
       </c>
-      <c r="L71" s="5" t="inlineStr">
+      <c r="N71" s="5" t="inlineStr">
         <is>
           <t>src/domain/import/holdingsImport.ts:183</t>
         </is>
@@ -3125,22 +3847,32 @@
       <c r="F72" s="3" t="inlineStr"/>
       <c r="G72" s="3" t="inlineStr"/>
       <c r="H72" s="3" t="inlineStr"/>
-      <c r="I72" s="5" t="inlineStr">
+      <c r="I72" s="3" t="inlineStr">
         <is>
           <t>ImportHoldings</t>
         </is>
       </c>
-      <c r="J72" s="5" t="inlineStr">
+      <c r="J72" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K72" s="5" t="inlineStr">
         <is>
+          <t>ImportHoldings</t>
+        </is>
+      </c>
+      <c r="L72" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr">
+        <is>
           <t>AssetAccount | null</t>
         </is>
       </c>
-      <c r="L72" s="5" t="inlineStr">
+      <c r="N72" s="5" t="inlineStr">
         <is>
           <t>src/domain/import/holdingsImport.ts:254</t>
         </is>
@@ -3159,22 +3891,32 @@
       <c r="F73" s="3" t="inlineStr"/>
       <c r="G73" s="3" t="inlineStr"/>
       <c r="H73" s="3" t="inlineStr"/>
-      <c r="I73" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J73" s="5" t="inlineStr">
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
         <is>
           <t>importHoldings</t>
         </is>
       </c>
       <c r="K73" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>importHoldings</t>
+        </is>
+      </c>
+      <c r="M73" s="5" t="inlineStr">
+        <is>
           <t>string[][]</t>
         </is>
       </c>
-      <c r="L73" s="5" t="inlineStr">
+      <c r="N73" s="5" t="inlineStr">
         <is>
           <t>src/domain/import/holdingsImport.ts:74</t>
         </is>
@@ -3193,22 +3935,32 @@
       <c r="F74" s="3" t="inlineStr"/>
       <c r="G74" s="3" t="inlineStr"/>
       <c r="H74" s="3" t="inlineStr"/>
-      <c r="I74" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J74" s="5" t="inlineStr">
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
         <is>
           <t>resolveLens, totalGrossAnnual</t>
         </is>
       </c>
       <c r="K74" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>resolveLens, totalGrossAnnual</t>
+        </is>
+      </c>
+      <c r="M74" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L74" s="5" t="inlineStr">
+      <c r="N74" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:191</t>
         </is>
@@ -3227,22 +3979,32 @@
       <c r="F75" s="3" t="inlineStr"/>
       <c r="G75" s="3" t="inlineStr"/>
       <c r="H75" s="3" t="inlineStr"/>
-      <c r="I75" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J75" s="5" t="inlineStr">
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="K75" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="M75" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L75" s="5" t="inlineStr">
+      <c r="N75" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/tax.ts:107</t>
         </is>
@@ -3261,22 +4023,32 @@
       <c r="F76" s="3" t="inlineStr"/>
       <c r="G76" s="3" t="inlineStr"/>
       <c r="H76" s="3" t="inlineStr"/>
-      <c r="I76" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J76" s="5" t="inlineStr">
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
         <is>
           <t>monthlyContributionsFromOnboarding</t>
         </is>
       </c>
       <c r="K76" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="5" t="inlineStr">
+        <is>
+          <t>monthlyContributionsFromOnboarding</t>
+        </is>
+      </c>
+      <c r="M76" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L76" s="5" t="inlineStr">
+      <c r="N76" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:242</t>
         </is>
@@ -3295,22 +4067,32 @@
       <c r="F77" s="3" t="inlineStr"/>
       <c r="G77" s="3" t="inlineStr"/>
       <c r="H77" s="3" t="inlineStr"/>
-      <c r="I77" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J77" s="5" t="inlineStr">
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
         <is>
           <t>rsuAnnual</t>
         </is>
       </c>
       <c r="K77" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>rsuAnnual</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L77" s="5" t="inlineStr">
+      <c r="N77" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:68</t>
         </is>
@@ -3329,22 +4111,32 @@
       <c r="F78" s="3" t="inlineStr"/>
       <c r="G78" s="3" t="inlineStr"/>
       <c r="H78" s="3" t="inlineStr"/>
-      <c r="I78" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J78" s="5" t="inlineStr">
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
         <is>
           <t>totalGrossAnnual</t>
         </is>
       </c>
       <c r="K78" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>totalGrossAnnual</t>
+        </is>
+      </c>
+      <c r="M78" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="L78" s="5" t="inlineStr">
+      <c r="N78" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:161</t>
         </is>
@@ -3363,22 +4155,32 @@
       <c r="F79" s="3" t="inlineStr"/>
       <c r="G79" s="3" t="inlineStr"/>
       <c r="H79" s="3" t="inlineStr"/>
-      <c r="I79" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J79" s="5" t="inlineStr">
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J79" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="K79" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="M79" s="5" t="inlineStr">
+        <is>
           <t>import('./tax').FilingStatus</t>
         </is>
       </c>
-      <c r="L79" s="5" t="inlineStr">
+      <c r="N79" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:333</t>
         </is>
@@ -3397,22 +4199,32 @@
       <c r="F80" s="3" t="inlineStr"/>
       <c r="G80" s="3" t="inlineStr"/>
       <c r="H80" s="3" t="inlineStr"/>
-      <c r="I80" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J80" s="5" t="inlineStr">
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
         <is>
           <t>salaryGrossByMonth</t>
         </is>
       </c>
       <c r="K80" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>salaryGrossByMonth</t>
+        </is>
+      </c>
+      <c r="M80" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L80" s="5" t="inlineStr">
+      <c r="N80" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/tax.ts:47</t>
         </is>
@@ -3431,22 +4243,32 @@
       <c r="F81" s="3" t="inlineStr"/>
       <c r="G81" s="3" t="inlineStr"/>
       <c r="H81" s="3" t="inlineStr"/>
-      <c r="I81" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J81" s="5" t="inlineStr">
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
         <is>
           <t>rentalNetAnnual</t>
         </is>
       </c>
       <c r="K81" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>rentalNetAnnual</t>
+        </is>
+      </c>
+      <c r="M81" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="L81" s="5" t="inlineStr">
+      <c r="N81" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:129</t>
         </is>
@@ -3465,22 +4287,32 @@
       <c r="F82" s="3" t="inlineStr"/>
       <c r="G82" s="3" t="inlineStr"/>
       <c r="H82" s="3" t="inlineStr"/>
-      <c r="I82" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J82" s="5" t="inlineStr">
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
         <is>
           <t>totalGrossAnnual</t>
         </is>
       </c>
       <c r="K82" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>totalGrossAnnual</t>
+        </is>
+      </c>
+      <c r="M82" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L82" s="5" t="inlineStr">
+      <c r="N82" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:142</t>
         </is>
@@ -3499,22 +4331,32 @@
       <c r="F83" s="3" t="inlineStr"/>
       <c r="G83" s="3" t="inlineStr"/>
       <c r="H83" s="3" t="inlineStr"/>
-      <c r="I83" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J83" s="5" t="inlineStr">
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
         <is>
           <t>currentRetirementIncomeMonthly, willItLastInputs</t>
         </is>
       </c>
       <c r="K83" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>currentRetirementIncomeMonthly, willItLastInputs</t>
+        </is>
+      </c>
+      <c r="M83" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L83" s="5" t="inlineStr">
+      <c r="N83" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:213</t>
         </is>
@@ -3533,22 +4375,32 @@
       <c r="F84" s="3" t="inlineStr"/>
       <c r="G84" s="3" t="inlineStr"/>
       <c r="H84" s="3" t="inlineStr"/>
-      <c r="I84" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J84" s="5" t="inlineStr">
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
         <is>
           <t>rsuAnnual</t>
         </is>
       </c>
       <c r="K84" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L84" s="5" t="inlineStr">
+        <is>
+          <t>rsuAnnual</t>
+        </is>
+      </c>
+      <c r="M84" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L84" s="5" t="inlineStr">
+      <c r="N84" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:74</t>
         </is>
@@ -3567,22 +4419,32 @@
       <c r="F85" s="3" t="inlineStr"/>
       <c r="G85" s="3" t="inlineStr"/>
       <c r="H85" s="3" t="inlineStr"/>
-      <c r="I85" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J85" s="5" t="inlineStr">
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
         <is>
           <t>totalGrossAnnual</t>
         </is>
       </c>
       <c r="K85" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="inlineStr">
+        <is>
+          <t>totalGrossAnnual</t>
+        </is>
+      </c>
+      <c r="M85" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L85" s="5" t="inlineStr">
+      <c r="N85" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:114</t>
         </is>
@@ -3601,22 +4463,32 @@
       <c r="F86" s="3" t="inlineStr"/>
       <c r="G86" s="3" t="inlineStr"/>
       <c r="H86" s="3" t="inlineStr"/>
-      <c r="I86" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J86" s="5" t="inlineStr">
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
         <is>
           <t>tipsAnnual</t>
         </is>
       </c>
       <c r="K86" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L86" s="5" t="inlineStr">
+        <is>
+          <t>tipsAnnual</t>
+        </is>
+      </c>
+      <c r="M86" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L86" s="5" t="inlineStr">
+      <c r="N86" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:306</t>
         </is>
@@ -3635,22 +4507,32 @@
       <c r="F87" s="3" t="inlineStr"/>
       <c r="G87" s="3" t="inlineStr"/>
       <c r="H87" s="3" t="inlineStr"/>
-      <c r="I87" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J87" s="5" t="inlineStr">
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
         <is>
           <t>totalGrossAnnual</t>
         </is>
       </c>
       <c r="K87" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L87" s="5" t="inlineStr">
+        <is>
+          <t>totalGrossAnnual</t>
+        </is>
+      </c>
+      <c r="M87" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L87" s="5" t="inlineStr">
+      <c r="N87" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:310</t>
         </is>
@@ -3669,22 +4551,32 @@
       <c r="F88" s="3" t="inlineStr"/>
       <c r="G88" s="3" t="inlineStr"/>
       <c r="H88" s="3" t="inlineStr"/>
-      <c r="I88" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J88" s="5" t="inlineStr">
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
         <is>
           <t>salaryActiveMonths, salaryAnnual</t>
         </is>
       </c>
       <c r="K88" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>salaryActiveMonths, salaryAnnual</t>
+        </is>
+      </c>
+      <c r="M88" s="5" t="inlineStr">
+        <is>
           <t>number[]</t>
         </is>
       </c>
-      <c r="L88" s="5" t="inlineStr">
+      <c r="N88" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:46</t>
         </is>
@@ -3703,22 +4595,32 @@
       <c r="F89" s="3" t="inlineStr"/>
       <c r="G89" s="3" t="inlineStr"/>
       <c r="H89" s="3" t="inlineStr"/>
-      <c r="I89" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J89" s="5" t="inlineStr">
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="K89" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L89" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="M89" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L89" s="5" t="inlineStr">
+      <c r="N89" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:337</t>
         </is>
@@ -3737,22 +4639,32 @@
       <c r="F90" s="3" t="inlineStr"/>
       <c r="G90" s="3" t="inlineStr"/>
       <c r="H90" s="3" t="inlineStr"/>
-      <c r="I90" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J90" s="5" t="inlineStr">
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
         <is>
           <t>taxOwed</t>
         </is>
       </c>
       <c r="K90" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L90" s="5" t="inlineStr">
+        <is>
+          <t>taxOwed</t>
+        </is>
+      </c>
+      <c r="M90" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L90" s="5" t="inlineStr">
+      <c r="N90" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/tax.ts:17</t>
         </is>
@@ -3771,22 +4683,32 @@
       <c r="F91" s="3" t="inlineStr"/>
       <c r="G91" s="3" t="inlineStr"/>
       <c r="H91" s="3" t="inlineStr"/>
-      <c r="I91" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J91" s="5" t="inlineStr">
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
         <is>
           <t>taxOwedFor</t>
         </is>
       </c>
       <c r="K91" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L91" s="5" t="inlineStr">
+        <is>
+          <t>taxOwedFor</t>
+        </is>
+      </c>
+      <c r="M91" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L91" s="5" t="inlineStr">
+      <c r="N91" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/tax.ts:88</t>
         </is>
@@ -3805,22 +4727,32 @@
       <c r="F92" s="3" t="inlineStr"/>
       <c r="G92" s="3" t="inlineStr"/>
       <c r="H92" s="3" t="inlineStr"/>
-      <c r="I92" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J92" s="5" t="inlineStr">
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
         <is>
           <t>grossFromNet</t>
         </is>
       </c>
       <c r="K92" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L92" s="5" t="inlineStr">
+        <is>
+          <t>grossFromNet</t>
+        </is>
+      </c>
+      <c r="M92" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L92" s="5" t="inlineStr">
+      <c r="N92" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/tax.ts:29</t>
         </is>
@@ -3839,22 +4771,32 @@
       <c r="F93" s="3" t="inlineStr"/>
       <c r="G93" s="3" t="inlineStr"/>
       <c r="H93" s="3" t="inlineStr"/>
-      <c r="I93" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J93" s="5" t="inlineStr">
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
         <is>
           <t>effectiveRateOnGrossFor</t>
         </is>
       </c>
       <c r="K93" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L93" s="5" t="inlineStr">
+        <is>
+          <t>effectiveRateOnGrossFor</t>
+        </is>
+      </c>
+      <c r="M93" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L93" s="5" t="inlineStr">
+      <c r="N93" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/tax.ts:94</t>
         </is>
@@ -3873,22 +4815,32 @@
       <c r="F94" s="3" t="inlineStr"/>
       <c r="G94" s="3" t="inlineStr"/>
       <c r="H94" s="3" t="inlineStr"/>
-      <c r="I94" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J94" s="5" t="inlineStr">
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
         <is>
           <t>totalGrossAnnual</t>
         </is>
       </c>
       <c r="K94" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L94" s="5" t="inlineStr">
+        <is>
+          <t>totalGrossAnnual</t>
+        </is>
+      </c>
+      <c r="M94" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L94" s="5" t="inlineStr">
+      <c r="N94" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:204</t>
         </is>
@@ -3907,22 +4859,32 @@
       <c r="F95" s="3" t="inlineStr"/>
       <c r="G95" s="3" t="inlineStr"/>
       <c r="H95" s="3" t="inlineStr"/>
-      <c r="I95" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J95" s="5" t="inlineStr">
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="K95" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L95" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="M95" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L95" s="5" t="inlineStr">
+      <c r="N95" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:316</t>
         </is>
@@ -3941,22 +4903,32 @@
       <c r="F96" s="3" t="inlineStr"/>
       <c r="G96" s="3" t="inlineStr"/>
       <c r="H96" s="3" t="inlineStr"/>
-      <c r="I96" s="5" t="inlineStr">
+      <c r="I96" s="3" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="J96" s="5" t="inlineStr">
+      <c r="J96" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K96" s="5" t="inlineStr">
         <is>
+          <t>HoldingDetail, Performance</t>
+        </is>
+      </c>
+      <c r="L96" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M96" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="L96" s="5" t="inlineStr">
+      <c r="N96" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:390</t>
         </is>
@@ -3975,22 +4947,32 @@
       <c r="F97" s="3" t="inlineStr"/>
       <c r="G97" s="3" t="inlineStr"/>
       <c r="H97" s="3" t="inlineStr"/>
-      <c r="I97" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J97" s="5" t="inlineStr">
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K97" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L97" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M97" s="5" t="inlineStr">
+        <is>
           <t>Promise&lt;ExpenseAnalysis&gt;</t>
         </is>
       </c>
-      <c r="L97" s="5" t="inlineStr">
+      <c r="N97" s="5" t="inlineStr">
         <is>
           <t>src/services/economicData.ts:109</t>
         </is>
@@ -4009,22 +4991,32 @@
       <c r="F98" s="3" t="inlineStr"/>
       <c r="G98" s="3" t="inlineStr"/>
       <c r="H98" s="3" t="inlineStr"/>
-      <c r="I98" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J98" s="5" t="inlineStr">
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K98" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L98" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M98" s="5" t="inlineStr">
+        <is>
           <t>Promise&lt;EconomicData&gt;</t>
         </is>
       </c>
-      <c r="L98" s="5" t="inlineStr">
+      <c r="N98" s="5" t="inlineStr">
         <is>
           <t>src/services/economicData.ts:47</t>
         </is>
@@ -4043,22 +5035,32 @@
       <c r="F99" s="3" t="inlineStr"/>
       <c r="G99" s="3" t="inlineStr"/>
       <c r="H99" s="3" t="inlineStr"/>
-      <c r="I99" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J99" s="5" t="inlineStr">
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K99" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L99" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M99" s="5" t="inlineStr">
+        <is>
           <t>Promise&lt;</t>
         </is>
       </c>
-      <c r="L99" s="5" t="inlineStr">
+      <c r="N99" s="5" t="inlineStr">
         <is>
           <t>src/services/economicData.ts:158</t>
         </is>
@@ -4077,22 +5079,32 @@
       <c r="F100" s="3" t="inlineStr"/>
       <c r="G100" s="3" t="inlineStr"/>
       <c r="H100" s="3" t="inlineStr"/>
-      <c r="I100" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J100" s="5" t="inlineStr">
+      <c r="I100" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K100" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L100" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M100" s="5" t="inlineStr">
+        <is>
           <t>AssetAccount[]</t>
         </is>
       </c>
-      <c r="L100" s="5" t="inlineStr">
+      <c r="N100" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/ingest.ts:173</t>
         </is>
@@ -4111,22 +5123,32 @@
       <c r="F101" s="3" t="inlineStr"/>
       <c r="G101" s="3" t="inlineStr"/>
       <c r="H101" s="3" t="inlineStr"/>
-      <c r="I101" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J101" s="5" t="inlineStr">
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K101" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L101" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M101" s="5" t="inlineStr">
+        <is>
           <t>SyncResult</t>
         </is>
       </c>
-      <c r="L101" s="5" t="inlineStr">
+      <c r="N101" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/ingest.ts:31</t>
         </is>
@@ -4145,22 +5167,32 @@
       <c r="F102" s="3" t="inlineStr"/>
       <c r="G102" s="3" t="inlineStr"/>
       <c r="H102" s="3" t="inlineStr"/>
-      <c r="I102" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J102" s="5" t="inlineStr">
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
         <is>
           <t>ingestSync</t>
         </is>
       </c>
       <c r="K102" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L102" s="5" t="inlineStr">
+        <is>
+          <t>ingestSync</t>
+        </is>
+      </c>
+      <c r="M102" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="L102" s="5" t="inlineStr">
+      <c r="N102" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/ingest.ts:29</t>
         </is>
@@ -4179,22 +5211,32 @@
       <c r="F103" s="3" t="inlineStr"/>
       <c r="G103" s="3" t="inlineStr"/>
       <c r="H103" s="3" t="inlineStr"/>
-      <c r="I103" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J103" s="5" t="inlineStr">
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K103" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L103" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M103" s="5" t="inlineStr">
+        <is>
           <t>Promise&lt;Record&lt;string, PriceSeries&gt;&gt;</t>
         </is>
       </c>
-      <c r="L103" s="5" t="inlineStr">
+      <c r="N103" s="5" t="inlineStr">
         <is>
           <t>src/services/marketData.ts:71</t>
         </is>
@@ -4213,22 +5255,32 @@
       <c r="F104" s="3" t="inlineStr"/>
       <c r="G104" s="3" t="inlineStr"/>
       <c r="H104" s="3" t="inlineStr"/>
-      <c r="I104" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J104" s="5" t="inlineStr">
+      <c r="I104" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K104" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L104" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M104" s="5" t="inlineStr">
+        <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="L104" s="5" t="inlineStr">
+      <c r="N104" s="5" t="inlineStr">
         <is>
           <t>src/services/marketData.ts:53</t>
         </is>
@@ -4247,22 +5299,32 @@
       <c r="F105" s="3" t="inlineStr"/>
       <c r="G105" s="3" t="inlineStr"/>
       <c r="H105" s="3" t="inlineStr"/>
-      <c r="I105" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J105" s="5" t="inlineStr">
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K105" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L105" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M105" s="5" t="inlineStr">
+        <is>
           <t>PriceFreshness</t>
         </is>
       </c>
-      <c r="L105" s="5" t="inlineStr">
+      <c r="N105" s="5" t="inlineStr">
         <is>
           <t>src/services/marketData.ts:60</t>
         </is>
@@ -4309,22 +5371,28 @@
           <t>Calculation Module code/probes/broken-family.probe.test.ts</t>
         </is>
       </c>
-      <c r="I106" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J106" s="5" t="inlineStr">
+      <c r="I106" s="3" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J106" s="3" t="inlineStr"/>
+      <c r="K106" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L106" s="5" t="inlineStr">
         <is>
           <t>dedupeActivities, ingestSync</t>
         </is>
       </c>
-      <c r="K106" s="5" t="inlineStr">
+      <c r="M106" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L106" s="5" t="inlineStr">
+      <c r="N106" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:243</t>
         </is>
@@ -4367,22 +5435,28 @@
         </is>
       </c>
       <c r="H107" s="3" t="inlineStr"/>
-      <c r="I107" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J107" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="inlineStr"/>
       <c r="K107" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L107" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M107" s="5" t="inlineStr">
+        <is>
           <t>StActivity[]</t>
         </is>
       </c>
-      <c r="L107" s="5" t="inlineStr">
+      <c r="N107" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:255</t>
         </is>
@@ -4401,22 +5475,32 @@
       <c r="F108" s="3" t="inlineStr"/>
       <c r="G108" s="3" t="inlineStr"/>
       <c r="H108" s="3" t="inlineStr"/>
-      <c r="I108" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J108" s="5" t="inlineStr">
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
         <is>
           <t>ingestSync</t>
         </is>
       </c>
       <c r="K108" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L108" s="5" t="inlineStr">
+        <is>
+          <t>ingestSync</t>
+        </is>
+      </c>
+      <c r="M108" s="5" t="inlineStr">
+        <is>
           <t>WrapperGuess</t>
         </is>
       </c>
-      <c r="L108" s="5" t="inlineStr">
+      <c r="N108" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:71</t>
         </is>
@@ -4459,22 +5543,28 @@
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr"/>
-      <c r="I109" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J109" s="5" t="inlineStr">
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J109" s="3" t="inlineStr"/>
+      <c r="K109" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L109" s="5" t="inlineStr">
         <is>
           <t>ingestSync</t>
         </is>
       </c>
-      <c r="K109" s="5" t="inlineStr">
+      <c r="M109" s="5" t="inlineStr">
         <is>
           <t>MappedActivity</t>
         </is>
       </c>
-      <c r="L109" s="5" t="inlineStr">
+      <c r="N109" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:184</t>
         </is>
@@ -4493,22 +5583,32 @@
       <c r="F110" s="3" t="inlineStr"/>
       <c r="G110" s="3" t="inlineStr"/>
       <c r="H110" s="3" t="inlineStr"/>
-      <c r="I110" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J110" s="5" t="inlineStr">
+      <c r="I110" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
         <is>
           <t>ingestSync</t>
         </is>
       </c>
       <c r="K110" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L110" s="5" t="inlineStr">
+        <is>
+          <t>ingestSync</t>
+        </is>
+      </c>
+      <c r="M110" s="5" t="inlineStr">
+        <is>
           <t>MappedOption | null</t>
         </is>
       </c>
-      <c r="L110" s="5" t="inlineStr">
+      <c r="N110" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:159</t>
         </is>
@@ -4551,22 +5651,28 @@
         </is>
       </c>
       <c r="H111" s="3" t="inlineStr"/>
-      <c r="I111" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J111" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr"/>
       <c r="K111" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L111" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M111" s="5" t="inlineStr">
+        <is>
           <t>MappedPosition | null</t>
         </is>
       </c>
-      <c r="L111" s="5" t="inlineStr">
+      <c r="N111" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:116</t>
         </is>
@@ -4585,22 +5691,32 @@
       <c r="F112" s="3" t="inlineStr"/>
       <c r="G112" s="3" t="inlineStr"/>
       <c r="H112" s="3" t="inlineStr"/>
-      <c r="I112" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J112" s="5" t="inlineStr">
+      <c r="I112" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
         <is>
           <t>ingestSync</t>
         </is>
       </c>
       <c r="K112" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L112" s="5" t="inlineStr">
+        <is>
+          <t>ingestSync</t>
+        </is>
+      </c>
+      <c r="M112" s="5" t="inlineStr">
+        <is>
           <t>string | undefined</t>
         </is>
       </c>
-      <c r="L112" s="5" t="inlineStr">
+      <c r="N112" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:282</t>
         </is>
@@ -4643,22 +5759,32 @@
         </is>
       </c>
       <c r="H113" s="3" t="inlineStr"/>
-      <c r="I113" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J113" s="5" t="inlineStr">
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>UNRESOLVED</t>
+        </is>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>The netting is right, but ingest.ts ALSO drops every cash-equivalent position from the holdings list. Both run, so for a broker that flags the fund, the money is subtracted from cash AND missing from holdings. One of the two must go: either show the fund as a holding and net the sleeve (the honest option), or keep it in the sleeve and do not net. Needs a decision, not a patch.</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L113" s="5" t="inlineStr">
         <is>
           <t>ingestSync</t>
         </is>
       </c>
-      <c r="K113" s="5" t="inlineStr">
+      <c r="M113" s="5" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L113" s="5" t="inlineStr">
+      <c r="N113" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:269</t>
         </is>
@@ -4677,22 +5803,32 @@
       <c r="F114" s="3" t="inlineStr"/>
       <c r="G114" s="3" t="inlineStr"/>
       <c r="H114" s="3" t="inlineStr"/>
-      <c r="I114" s="5" t="inlineStr">
+      <c r="I114" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J114" s="5" t="inlineStr">
+      <c r="J114" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K114" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L114" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M114" s="5" t="inlineStr">
+        <is>
           <t>NetWorthState</t>
         </is>
       </c>
-      <c r="L114" s="5" t="inlineStr">
+      <c r="N114" s="5" t="inlineStr">
         <is>
           <t>src/domain/networth/index.ts:12</t>
         </is>
@@ -4711,22 +5847,32 @@
       <c r="F115" s="3" t="inlineStr"/>
       <c r="G115" s="3" t="inlineStr"/>
       <c r="H115" s="3" t="inlineStr"/>
-      <c r="I115" s="5" t="inlineStr">
+      <c r="I115" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="J115" s="5" t="inlineStr">
+      <c r="J115" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K115" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="L115" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M115" s="5" t="inlineStr">
+        <is>
           <t>AllocSlice[]</t>
         </is>
       </c>
-      <c r="L115" s="5" t="inlineStr">
+      <c r="N115" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:226</t>
         </is>
@@ -4745,22 +5891,32 @@
       <c r="F116" s="3" t="inlineStr"/>
       <c r="G116" s="3" t="inlineStr"/>
       <c r="H116" s="3" t="inlineStr"/>
-      <c r="I116" s="5" t="inlineStr">
+      <c r="I116" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="J116" s="5" t="inlineStr">
+      <c r="J116" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K116" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="L116" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M116" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="L116" s="5" t="inlineStr">
+      <c r="N116" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:215</t>
         </is>
@@ -4779,22 +5935,32 @@
       <c r="F117" s="3" t="inlineStr"/>
       <c r="G117" s="3" t="inlineStr"/>
       <c r="H117" s="3" t="inlineStr"/>
-      <c r="I117" s="5" t="inlineStr">
+      <c r="I117" s="3" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="J117" s="5" t="inlineStr">
+      <c r="J117" s="3" t="inlineStr">
         <is>
           <t>buildPerformance</t>
         </is>
       </c>
       <c r="K117" s="5" t="inlineStr">
         <is>
+          <t>HoldingDetail, Performance</t>
+        </is>
+      </c>
+      <c r="L117" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance</t>
+        </is>
+      </c>
+      <c r="M117" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L117" s="5" t="inlineStr">
+      <c r="N117" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:149</t>
         </is>
@@ -4813,22 +5979,32 @@
       <c r="F118" s="3" t="inlineStr"/>
       <c r="G118" s="3" t="inlineStr"/>
       <c r="H118" s="3" t="inlineStr"/>
-      <c r="I118" s="5" t="inlineStr">
+      <c r="I118" s="3" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="J118" s="5" t="inlineStr">
+      <c r="J118" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K118" s="5" t="inlineStr">
         <is>
+          <t>HoldingDetail, Performance</t>
+        </is>
+      </c>
+      <c r="L118" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M118" s="5" t="inlineStr">
+        <is>
           <t>PerformanceRow[]</t>
         </is>
       </c>
-      <c r="L118" s="5" t="inlineStr">
+      <c r="N118" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:173</t>
         </is>
@@ -4847,22 +6023,32 @@
       <c r="F119" s="3" t="inlineStr"/>
       <c r="G119" s="3" t="inlineStr"/>
       <c r="H119" s="3" t="inlineStr"/>
-      <c r="I119" s="5" t="inlineStr">
+      <c r="I119" s="3" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="J119" s="5" t="inlineStr">
+      <c r="J119" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K119" s="5" t="inlineStr">
         <is>
+          <t>HoldingDetail, Performance</t>
+        </is>
+      </c>
+      <c r="L119" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M119" s="5" t="inlineStr">
+        <is>
           <t>CapGains</t>
         </is>
       </c>
-      <c r="L119" s="5" t="inlineStr">
+      <c r="N119" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:55</t>
         </is>
@@ -4881,22 +6067,32 @@
       <c r="F120" s="3" t="inlineStr"/>
       <c r="G120" s="3" t="inlineStr"/>
       <c r="H120" s="3" t="inlineStr"/>
-      <c r="I120" s="5" t="inlineStr">
+      <c r="I120" s="3" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="J120" s="5" t="inlineStr">
+      <c r="J120" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K120" s="5" t="inlineStr">
         <is>
+          <t>HoldingDetail, Performance</t>
+        </is>
+      </c>
+      <c r="L120" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M120" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L120" s="5" t="inlineStr">
+      <c r="N120" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:69</t>
         </is>
@@ -4915,22 +6111,32 @@
       <c r="F121" s="3" t="inlineStr"/>
       <c r="G121" s="3" t="inlineStr"/>
       <c r="H121" s="3" t="inlineStr"/>
-      <c r="I121" s="5" t="inlineStr">
+      <c r="I121" s="3" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="J121" s="5" t="inlineStr">
+      <c r="J121" s="3" t="inlineStr">
         <is>
           <t>buildPerformance, totalROI, unrealizedGain</t>
         </is>
       </c>
       <c r="K121" s="5" t="inlineStr">
         <is>
+          <t>HoldingDetail, Performance</t>
+        </is>
+      </c>
+      <c r="L121" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance, totalROI, unrealizedGain</t>
+        </is>
+      </c>
+      <c r="M121" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L121" s="5" t="inlineStr">
+      <c r="N121" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:38</t>
         </is>
@@ -4949,22 +6155,32 @@
       <c r="F122" s="3" t="inlineStr"/>
       <c r="G122" s="3" t="inlineStr"/>
       <c r="H122" s="3" t="inlineStr"/>
-      <c r="I122" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J122" s="5" t="inlineStr">
+      <c r="I122" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
         <is>
           <t>buildPerformance</t>
         </is>
       </c>
       <c r="K122" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L122" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance</t>
+        </is>
+      </c>
+      <c r="M122" s="5" t="inlineStr">
+        <is>
           <t>string | null</t>
         </is>
       </c>
-      <c r="L122" s="5" t="inlineStr">
+      <c r="N122" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:128</t>
         </is>
@@ -4983,22 +6199,32 @@
       <c r="F123" s="3" t="inlineStr"/>
       <c r="G123" s="3" t="inlineStr"/>
       <c r="H123" s="3" t="inlineStr"/>
-      <c r="I123" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J123" s="5" t="inlineStr">
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
         <is>
           <t>lookBack</t>
         </is>
       </c>
       <c r="K123" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L123" s="5" t="inlineStr">
+        <is>
+          <t>lookBack</t>
+        </is>
+      </c>
+      <c r="M123" s="5" t="inlineStr">
+        <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="L123" s="5" t="inlineStr">
+      <c r="N123" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/lookBack.ts:19</t>
         </is>
@@ -5017,22 +6243,32 @@
       <c r="F124" s="3" t="inlineStr"/>
       <c r="G124" s="3" t="inlineStr"/>
       <c r="H124" s="3" t="inlineStr"/>
-      <c r="I124" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J124" s="5" t="inlineStr">
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
         <is>
           <t>moneyWeightedReturn</t>
         </is>
       </c>
       <c r="K124" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L124" s="5" t="inlineStr">
+        <is>
+          <t>moneyWeightedReturn</t>
+        </is>
+      </c>
+      <c r="M124" s="5" t="inlineStr">
+        <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="L124" s="5" t="inlineStr">
+      <c r="N124" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/moneyWeighted.ts:60</t>
         </is>
@@ -5051,22 +6287,32 @@
       <c r="F125" s="3" t="inlineStr"/>
       <c r="G125" s="3" t="inlineStr"/>
       <c r="H125" s="3" t="inlineStr"/>
-      <c r="I125" s="5" t="inlineStr">
+      <c r="I125" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="J125" s="5" t="inlineStr">
+      <c r="J125" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K125" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="L125" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M125" s="5" t="inlineStr">
+        <is>
           <t>r is MoneyWeighted</t>
         </is>
       </c>
-      <c r="L125" s="5" t="inlineStr">
+      <c r="N125" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/moneyWeighted.ts:110</t>
         </is>
@@ -5085,22 +6331,32 @@
       <c r="F126" s="3" t="inlineStr"/>
       <c r="G126" s="3" t="inlineStr"/>
       <c r="H126" s="3" t="inlineStr"/>
-      <c r="I126" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J126" s="5" t="inlineStr">
+      <c r="I126" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
         <is>
           <t>buildPerformance, periodReturn, periodReturnSince</t>
         </is>
       </c>
       <c r="K126" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L126" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance, periodReturn, periodReturnSince</t>
+        </is>
+      </c>
+      <c r="M126" s="5" t="inlineStr">
+        <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="L126" s="5" t="inlineStr">
+      <c r="N126" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:102</t>
         </is>
@@ -5119,22 +6375,32 @@
       <c r="F127" s="3" t="inlineStr"/>
       <c r="G127" s="3" t="inlineStr"/>
       <c r="H127" s="3" t="inlineStr"/>
-      <c r="I127" s="5" t="inlineStr">
+      <c r="I127" s="3" t="inlineStr">
         <is>
           <t>LookBack</t>
         </is>
       </c>
-      <c r="J127" s="5" t="inlineStr">
+      <c r="J127" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K127" s="5" t="inlineStr">
         <is>
+          <t>LookBack</t>
+        </is>
+      </c>
+      <c r="L127" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M127" s="5" t="inlineStr">
+        <is>
           <t>LookBackResult | null</t>
         </is>
       </c>
-      <c r="L127" s="5" t="inlineStr">
+      <c r="N127" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/lookBack.ts:32</t>
         </is>
@@ -5153,22 +6419,32 @@
       <c r="F128" s="3" t="inlineStr"/>
       <c r="G128" s="3" t="inlineStr"/>
       <c r="H128" s="3" t="inlineStr"/>
-      <c r="I128" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J128" s="5" t="inlineStr">
+      <c r="I128" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
         <is>
           <t>buildPerformance, unrealizedGain</t>
         </is>
       </c>
       <c r="K128" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L128" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance, unrealizedGain</t>
+        </is>
+      </c>
+      <c r="M128" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L128" s="5" t="inlineStr">
+      <c r="N128" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:45</t>
         </is>
@@ -5187,22 +6463,32 @@
       <c r="F129" s="3" t="inlineStr"/>
       <c r="G129" s="3" t="inlineStr"/>
       <c r="H129" s="3" t="inlineStr"/>
-      <c r="I129" s="5" t="inlineStr">
+      <c r="I129" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="J129" s="5" t="inlineStr">
+      <c r="J129" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K129" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="L129" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M129" s="5" t="inlineStr">
+        <is>
           <t>MoneyWeighted | MoneyWeightedMiss</t>
         </is>
       </c>
-      <c r="L129" s="5" t="inlineStr">
+      <c r="N129" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/moneyWeighted.ts:80</t>
         </is>
@@ -5245,22 +6531,32 @@
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr"/>
-      <c r="I130" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J130" s="5" t="inlineStr">
+      <c r="I130" s="3" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>IT CANNOT ANSWER AN ARBITRARY WINDOW. Only 1M · 3M · 6M · YTD · 1Y · 3Y. That means a person can never line the app up against their own broker statement, which is the one comparison that would build trust. It should accept an explicit start and end date, with the named periods becoming presets over the same function.</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L130" s="5" t="inlineStr">
         <is>
           <t>buildPerformance</t>
         </is>
       </c>
-      <c r="K130" s="5" t="inlineStr">
+      <c r="M130" s="5" t="inlineStr">
         <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="L130" s="5" t="inlineStr">
+      <c r="N130" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:107</t>
         </is>
@@ -5279,22 +6575,32 @@
       <c r="F131" s="3" t="inlineStr"/>
       <c r="G131" s="3" t="inlineStr"/>
       <c r="H131" s="3" t="inlineStr"/>
-      <c r="I131" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J131" s="5" t="inlineStr">
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
         <is>
           <t>buildPerformance</t>
         </is>
       </c>
       <c r="K131" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L131" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance</t>
+        </is>
+      </c>
+      <c r="M131" s="5" t="inlineStr">
+        <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="L131" s="5" t="inlineStr">
+      <c r="N131" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:119</t>
         </is>
@@ -5313,22 +6619,32 @@
       <c r="F132" s="3" t="inlineStr"/>
       <c r="G132" s="3" t="inlineStr"/>
       <c r="H132" s="3" t="inlineStr"/>
-      <c r="I132" s="5" t="inlineStr">
+      <c r="I132" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="J132" s="5" t="inlineStr">
+      <c r="J132" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K132" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="L132" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M132" s="5" t="inlineStr">
+        <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="L132" s="5" t="inlineStr">
+      <c r="N132" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:275</t>
         </is>
@@ -5347,22 +6663,32 @@
       <c r="F133" s="3" t="inlineStr"/>
       <c r="G133" s="3" t="inlineStr"/>
       <c r="H133" s="3" t="inlineStr"/>
-      <c r="I133" s="5" t="inlineStr">
+      <c r="I133" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="J133" s="5" t="inlineStr">
+      <c r="J133" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K133" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="L133" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M133" s="5" t="inlineStr">
+        <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="L133" s="5" t="inlineStr">
+      <c r="N133" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:265</t>
         </is>
@@ -5381,22 +6707,32 @@
       <c r="F134" s="3" t="inlineStr"/>
       <c r="G134" s="3" t="inlineStr"/>
       <c r="H134" s="3" t="inlineStr"/>
-      <c r="I134" s="5" t="inlineStr">
+      <c r="I134" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="J134" s="5" t="inlineStr">
+      <c r="J134" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K134" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="L134" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M134" s="5" t="inlineStr">
+        <is>
           <t>TrendPoint[]</t>
         </is>
       </c>
-      <c r="L134" s="5" t="inlineStr">
+      <c r="N134" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:239</t>
         </is>
@@ -5415,22 +6751,32 @@
       <c r="F135" s="3" t="inlineStr"/>
       <c r="G135" s="3" t="inlineStr"/>
       <c r="H135" s="3" t="inlineStr"/>
-      <c r="I135" s="5" t="inlineStr">
+      <c r="I135" s="3" t="inlineStr">
         <is>
           <t>HoldingDetail</t>
         </is>
       </c>
-      <c r="J135" s="5" t="inlineStr">
+      <c r="J135" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K135" s="5" t="inlineStr">
         <is>
+          <t>HoldingDetail</t>
+        </is>
+      </c>
+      <c r="L135" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M135" s="5" t="inlineStr">
+        <is>
           <t>RealizedResult</t>
         </is>
       </c>
-      <c r="L135" s="5" t="inlineStr">
+      <c r="N135" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/realized.ts:14</t>
         </is>
@@ -5449,22 +6795,32 @@
       <c r="F136" s="3" t="inlineStr"/>
       <c r="G136" s="3" t="inlineStr"/>
       <c r="H136" s="3" t="inlineStr"/>
-      <c r="I136" s="5" t="inlineStr">
+      <c r="I136" s="3" t="inlineStr">
         <is>
           <t>HoldingDetail</t>
         </is>
       </c>
-      <c r="J136" s="5" t="inlineStr">
+      <c r="J136" s="3" t="inlineStr">
         <is>
           <t>buildPerformance, periodReturn, portfolioTrend</t>
         </is>
       </c>
       <c r="K136" s="5" t="inlineStr">
         <is>
+          <t>HoldingDetail</t>
+        </is>
+      </c>
+      <c r="L136" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance, periodReturn, portfolioTrend</t>
+        </is>
+      </c>
+      <c r="M136" s="5" t="inlineStr">
+        <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="L136" s="5" t="inlineStr">
+      <c r="N136" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:81</t>
         </is>
@@ -5483,22 +6839,32 @@
       <c r="F137" s="3" t="inlineStr"/>
       <c r="G137" s="3" t="inlineStr"/>
       <c r="H137" s="3" t="inlineStr"/>
-      <c r="I137" s="5" t="inlineStr">
+      <c r="I137" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="J137" s="5" t="inlineStr">
+      <c r="J137" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K137" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="L137" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M137" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="L137" s="5" t="inlineStr">
+      <c r="N137" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:205</t>
         </is>
@@ -5517,22 +6883,32 @@
       <c r="F138" s="3" t="inlineStr"/>
       <c r="G138" s="3" t="inlineStr"/>
       <c r="H138" s="3" t="inlineStr"/>
-      <c r="I138" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J138" s="5" t="inlineStr">
+      <c r="I138" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
         <is>
           <t>buildPerformance</t>
         </is>
       </c>
       <c r="K138" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L138" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance</t>
+        </is>
+      </c>
+      <c r="M138" s="5" t="inlineStr">
+        <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="L138" s="5" t="inlineStr">
+      <c r="N138" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:74</t>
         </is>
@@ -5551,22 +6927,32 @@
       <c r="F139" s="3" t="inlineStr"/>
       <c r="G139" s="3" t="inlineStr"/>
       <c r="H139" s="3" t="inlineStr"/>
-      <c r="I139" s="5" t="inlineStr">
+      <c r="I139" s="3" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="J139" s="5" t="inlineStr">
+      <c r="J139" s="3" t="inlineStr">
         <is>
           <t>marketValue, portfolioTrend</t>
         </is>
       </c>
       <c r="K139" s="5" t="inlineStr">
         <is>
+          <t>HoldingDetail, Performance</t>
+        </is>
+      </c>
+      <c r="L139" s="5" t="inlineStr">
+        <is>
+          <t>marketValue, portfolioTrend</t>
+        </is>
+      </c>
+      <c r="M139" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L139" s="5" t="inlineStr">
+      <c r="N139" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:35</t>
         </is>
@@ -5585,22 +6971,32 @@
       <c r="F140" s="3" t="inlineStr"/>
       <c r="G140" s="3" t="inlineStr"/>
       <c r="H140" s="3" t="inlineStr"/>
-      <c r="I140" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J140" s="5" t="inlineStr">
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
         <is>
           <t>buildPerformance, totalROI</t>
         </is>
       </c>
       <c r="K140" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L140" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance, totalROI</t>
+        </is>
+      </c>
+      <c r="M140" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L140" s="5" t="inlineStr">
+      <c r="N140" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:49</t>
         </is>
@@ -5619,22 +7015,32 @@
       <c r="F141" s="3" t="inlineStr"/>
       <c r="G141" s="3" t="inlineStr"/>
       <c r="H141" s="3" t="inlineStr"/>
-      <c r="I141" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J141" s="5" t="inlineStr">
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
         <is>
           <t>moneyWeightedReturn</t>
         </is>
       </c>
       <c r="K141" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L141" s="5" t="inlineStr">
+        <is>
+          <t>moneyWeightedReturn</t>
+        </is>
+      </c>
+      <c r="M141" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="L141" s="5" t="inlineStr">
+      <c r="N141" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/moneyWeighted.ts:27</t>
         </is>
@@ -5653,22 +7059,32 @@
       <c r="F142" s="3" t="inlineStr"/>
       <c r="G142" s="3" t="inlineStr"/>
       <c r="H142" s="3" t="inlineStr"/>
-      <c r="I142" s="5" t="inlineStr">
+      <c r="I142" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J142" s="5" t="inlineStr">
+      <c r="J142" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K142" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L142" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M142" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L142" s="5" t="inlineStr">
+      <c r="N142" s="5" t="inlineStr">
         <is>
           <t>src/domain/planning/hub.ts:30</t>
         </is>
@@ -5687,22 +7103,32 @@
       <c r="F143" s="3" t="inlineStr"/>
       <c r="G143" s="3" t="inlineStr"/>
       <c r="H143" s="3" t="inlineStr"/>
-      <c r="I143" s="5" t="inlineStr">
+      <c r="I143" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J143" s="5" t="inlineStr">
+      <c r="J143" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K143" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L143" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M143" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="L143" s="5" t="inlineStr">
+      <c r="N143" s="5" t="inlineStr">
         <is>
           <t>src/domain/planning/hub.ts:165</t>
         </is>
@@ -5721,22 +7147,32 @@
       <c r="F144" s="3" t="inlineStr"/>
       <c r="G144" s="3" t="inlineStr"/>
       <c r="H144" s="3" t="inlineStr"/>
-      <c r="I144" s="5" t="inlineStr">
+      <c r="I144" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J144" s="5" t="inlineStr">
+      <c r="J144" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K144" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L144" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M144" s="5" t="inlineStr">
+        <is>
           <t>PlanDoor</t>
         </is>
       </c>
-      <c r="L144" s="5" t="inlineStr">
+      <c r="N144" s="5" t="inlineStr">
         <is>
           <t>src/domain/planning/hub.ts:44</t>
         </is>
@@ -5755,22 +7191,32 @@
       <c r="F145" s="3" t="inlineStr"/>
       <c r="G145" s="3" t="inlineStr"/>
       <c r="H145" s="3" t="inlineStr"/>
-      <c r="I145" s="5" t="inlineStr">
+      <c r="I145" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J145" s="5" t="inlineStr">
+      <c r="J145" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K145" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L145" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M145" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L145" s="5" t="inlineStr">
+      <c r="N145" s="5" t="inlineStr">
         <is>
           <t>src/domain/planning/hub.ts:152</t>
         </is>
@@ -5789,22 +7235,32 @@
       <c r="F146" s="3" t="inlineStr"/>
       <c r="G146" s="3" t="inlineStr"/>
       <c r="H146" s="3" t="inlineStr"/>
-      <c r="I146" s="5" t="inlineStr">
+      <c r="I146" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J146" s="5" t="inlineStr">
+      <c r="J146" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K146" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L146" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M146" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L146" s="5" t="inlineStr">
+      <c r="N146" s="5" t="inlineStr">
         <is>
           <t>src/domain/planning/hub.ts:34</t>
         </is>
@@ -5823,22 +7279,32 @@
       <c r="F147" s="3" t="inlineStr"/>
       <c r="G147" s="3" t="inlineStr"/>
       <c r="H147" s="3" t="inlineStr"/>
-      <c r="I147" s="5" t="inlineStr">
+      <c r="I147" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J147" s="5" t="inlineStr">
+      <c r="J147" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K147" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L147" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M147" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="L147" s="5" t="inlineStr">
+      <c r="N147" s="5" t="inlineStr">
         <is>
           <t>src/domain/planning/hub.ts:162</t>
         </is>
@@ -5857,22 +7323,32 @@
       <c r="F148" s="3" t="inlineStr"/>
       <c r="G148" s="3" t="inlineStr"/>
       <c r="H148" s="3" t="inlineStr"/>
-      <c r="I148" s="5" t="inlineStr">
+      <c r="I148" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J148" s="5" t="inlineStr">
+      <c r="J148" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K148" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L148" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M148" s="5" t="inlineStr">
+        <is>
           <t>Lens</t>
         </is>
       </c>
-      <c r="L148" s="5" t="inlineStr">
+      <c r="N148" s="5" t="inlineStr">
         <is>
           <t>src/domain/profile/lens.ts:17</t>
         </is>
@@ -5891,22 +7367,32 @@
       <c r="F149" s="3" t="inlineStr"/>
       <c r="G149" s="3" t="inlineStr"/>
       <c r="H149" s="3" t="inlineStr"/>
-      <c r="I149" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J149" s="5" t="inlineStr">
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
         <is>
           <t>retirementSpendMonthly</t>
         </is>
       </c>
       <c r="K149" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L149" s="5" t="inlineStr">
+        <is>
+          <t>retirementSpendMonthly</t>
+        </is>
+      </c>
+      <c r="M149" s="5" t="inlineStr">
+        <is>
           <t>ColMatch</t>
         </is>
       </c>
-      <c r="L149" s="5" t="inlineStr">
+      <c r="N149" s="5" t="inlineStr">
         <is>
           <t>src/domain/retirement/col.ts:53</t>
         </is>
@@ -5925,22 +7411,32 @@
       <c r="F150" s="3" t="inlineStr"/>
       <c r="G150" s="3" t="inlineStr"/>
       <c r="H150" s="3" t="inlineStr"/>
-      <c r="I150" s="5" t="inlineStr">
+      <c r="I150" s="3" t="inlineStr">
         <is>
           <t>NetWorth, WhatIf</t>
         </is>
       </c>
-      <c r="J150" s="5" t="inlineStr">
+      <c r="J150" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K150" s="5" t="inlineStr">
         <is>
+          <t>NetWorth, WhatIf</t>
+        </is>
+      </c>
+      <c r="L150" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M150" s="5" t="inlineStr">
+        <is>
           <t>NestEggProjection</t>
         </is>
       </c>
-      <c r="L150" s="5" t="inlineStr">
+      <c r="N150" s="5" t="inlineStr">
         <is>
           <t>src/domain/retirement/index.ts:294</t>
         </is>
@@ -5959,22 +7455,32 @@
       <c r="F151" s="3" t="inlineStr"/>
       <c r="G151" s="3" t="inlineStr"/>
       <c r="H151" s="3" t="inlineStr"/>
-      <c r="I151" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J151" s="5" t="inlineStr">
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
         <is>
           <t>selectWillItLast, willItLastInputs</t>
         </is>
       </c>
       <c r="K151" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L151" s="5" t="inlineStr">
+        <is>
+          <t>selectWillItLast, willItLastInputs</t>
+        </is>
+      </c>
+      <c r="M151" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L151" s="5" t="inlineStr">
+      <c r="N151" s="5" t="inlineStr">
         <is>
           <t>src/domain/retirement/index.ts:48</t>
         </is>
@@ -5993,22 +7499,32 @@
       <c r="F152" s="3" t="inlineStr"/>
       <c r="G152" s="3" t="inlineStr"/>
       <c r="H152" s="3" t="inlineStr"/>
-      <c r="I152" s="5" t="inlineStr">
+      <c r="I152" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J152" s="5" t="inlineStr">
+      <c r="J152" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K152" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="L152" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M152" s="5" t="inlineStr">
+        <is>
           <t>WillItLastResult</t>
         </is>
       </c>
-      <c r="L152" s="5" t="inlineStr">
+      <c r="N152" s="5" t="inlineStr">
         <is>
           <t>src/domain/retirement/willItLast.ts:115</t>
         </is>
@@ -6027,22 +7543,32 @@
       <c r="F153" s="3" t="inlineStr"/>
       <c r="G153" s="3" t="inlineStr"/>
       <c r="H153" s="3" t="inlineStr"/>
-      <c r="I153" s="5" t="inlineStr">
+      <c r="I153" s="3" t="inlineStr">
         <is>
           <t>NetWorth, WhatIf</t>
         </is>
       </c>
-      <c r="J153" s="5" t="inlineStr">
+      <c r="J153" s="3" t="inlineStr">
         <is>
           <t>selectWillItLast</t>
         </is>
       </c>
       <c r="K153" s="5" t="inlineStr">
         <is>
+          <t>NetWorth, WhatIf</t>
+        </is>
+      </c>
+      <c r="L153" s="5" t="inlineStr">
+        <is>
+          <t>selectWillItLast</t>
+        </is>
+      </c>
+      <c r="M153" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="L153" s="5" t="inlineStr">
+      <c r="N153" s="5" t="inlineStr">
         <is>
           <t>src/domain/retirement/index.ts:160</t>
         </is>
@@ -6061,22 +7587,32 @@
       <c r="F154" s="3" t="inlineStr"/>
       <c r="G154" s="3" t="inlineStr"/>
       <c r="H154" s="3" t="inlineStr"/>
-      <c r="I154" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J154" s="5" t="inlineStr">
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="K154" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L154" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="M154" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L154" s="5" t="inlineStr">
+      <c r="N154" s="5" t="inlineStr">
         <is>
           <t>src/domain/retirement/ssTiming.ts:25</t>
         </is>
@@ -6095,22 +7631,32 @@
       <c r="F155" s="3" t="inlineStr"/>
       <c r="G155" s="3" t="inlineStr"/>
       <c r="H155" s="3" t="inlineStr"/>
-      <c r="I155" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J155" s="5" t="inlineStr">
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
         <is>
           <t>ssBenefitAtClaimAge</t>
         </is>
       </c>
       <c r="K155" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L155" s="5" t="inlineStr">
+        <is>
+          <t>ssBenefitAtClaimAge</t>
+        </is>
+      </c>
+      <c r="M155" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L155" s="5" t="inlineStr">
+      <c r="N155" s="5" t="inlineStr">
         <is>
           <t>src/domain/retirement/ssTiming.ts:12</t>
         </is>
@@ -6129,22 +7675,32 @@
       <c r="F156" s="3" t="inlineStr"/>
       <c r="G156" s="3" t="inlineStr"/>
       <c r="H156" s="3" t="inlineStr"/>
-      <c r="I156" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J156" s="5" t="inlineStr">
+      <c r="I156" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="K156" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L156" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="M156" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="L156" s="5" t="inlineStr">
+      <c r="N156" s="5" t="inlineStr">
         <is>
           <t>src/domain/retirement/willItLast.ts:19</t>
         </is>
@@ -6163,22 +7719,32 @@
       <c r="F157" s="3" t="inlineStr"/>
       <c r="G157" s="3" t="inlineStr"/>
       <c r="H157" s="3" t="inlineStr"/>
-      <c r="I157" s="5" t="inlineStr">
+      <c r="I157" s="3" t="inlineStr">
         <is>
           <t>NetWorth, WhatIf</t>
         </is>
       </c>
-      <c r="J157" s="5" t="inlineStr">
+      <c r="J157" s="3" t="inlineStr">
         <is>
           <t>selectWillItLast</t>
         </is>
       </c>
       <c r="K157" s="5" t="inlineStr">
         <is>
+          <t>NetWorth, WhatIf</t>
+        </is>
+      </c>
+      <c r="L157" s="5" t="inlineStr">
+        <is>
+          <t>selectWillItLast</t>
+        </is>
+      </c>
+      <c r="M157" s="5" t="inlineStr">
+        <is>
           <t>RetirementInputs | null</t>
         </is>
       </c>
-      <c r="L157" s="5" t="inlineStr">
+      <c r="N157" s="5" t="inlineStr">
         <is>
           <t>src/domain/retirement/willItLast.ts:47</t>
         </is>
@@ -6197,22 +7763,32 @@
       <c r="F158" s="3" t="inlineStr"/>
       <c r="G158" s="3" t="inlineStr"/>
       <c r="H158" s="3" t="inlineStr"/>
-      <c r="I158" s="5" t="inlineStr">
+      <c r="I158" s="3" t="inlineStr">
         <is>
           <t>Performance, WhatIf</t>
         </is>
       </c>
-      <c r="J158" s="5" t="inlineStr">
+      <c r="J158" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K158" s="5" t="inlineStr">
         <is>
+          <t>Performance, WhatIf</t>
+        </is>
+      </c>
+      <c r="L158" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M158" s="5" t="inlineStr">
+        <is>
           <t>NetWorthRows</t>
         </is>
       </c>
-      <c r="L158" s="5" t="inlineStr">
+      <c r="N158" s="5" t="inlineStr">
         <is>
           <t>src/domain/snapshot.ts:121</t>
         </is>
@@ -6231,22 +7807,32 @@
       <c r="F159" s="3" t="inlineStr"/>
       <c r="G159" s="3" t="inlineStr"/>
       <c r="H159" s="3" t="inlineStr"/>
-      <c r="I159" s="5" t="inlineStr">
+      <c r="I159" s="3" t="inlineStr">
         <is>
           <t>AccountDetail, Performance</t>
         </is>
       </c>
-      <c r="J159" s="5" t="inlineStr">
+      <c r="J159" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K159" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail, Performance</t>
+        </is>
+      </c>
+      <c r="L159" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M159" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L159" s="5" t="inlineStr">
+      <c r="N159" s="5" t="inlineStr">
         <is>
           <t>src/domain/transactions/index.ts:227</t>
         </is>
@@ -6265,22 +7851,32 @@
       <c r="F160" s="3" t="inlineStr"/>
       <c r="G160" s="3" t="inlineStr"/>
       <c r="H160" s="3" t="inlineStr"/>
-      <c r="I160" s="5" t="inlineStr">
+      <c r="I160" s="3" t="inlineStr">
         <is>
           <t>AccountDetail, Performance</t>
         </is>
       </c>
-      <c r="J160" s="5" t="inlineStr">
+      <c r="J160" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K160" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail, Performance</t>
+        </is>
+      </c>
+      <c r="L160" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M160" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L160" s="5" t="inlineStr">
+      <c r="N160" s="5" t="inlineStr">
         <is>
           <t>src/domain/transactions/index.ts:224</t>
         </is>
@@ -6288,7 +7884,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -6302,7 +7898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6313,10 +7909,12 @@
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="52" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="40" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="46" customHeight="1">
@@ -6369,20 +7967,30 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>WHAT IT SHOULD BE</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
           <t>Screens</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Called by</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Returns</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -6401,22 +8009,32 @@
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>AccountDetail, Itemize, LookBack, NetWorth</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>formatMoney, formatMoneyCents, moneyCompact</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail, Itemize, LookBack, NetWorth</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>formatMoney, formatMoneyCents, moneyCompact</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>src/domain/_shared/money.ts:52</t>
         </is>
@@ -6435,22 +8053,32 @@
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>HoldingDetail, Itemize, NetWorth, Performance</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
+          <t>HoldingDetail, Itemize, NetWorth, Performance</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>src/domain/_shared/num.ts:9</t>
         </is>
@@ -6469,22 +8097,32 @@
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>ImportHoldings, Performance</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
+          <t>ImportHoldings, Performance</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>src/domain/_shared/num.ts:11</t>
         </is>
@@ -6503,22 +8141,32 @@
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>NetWorth, Performance</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
+          <t>NetWorth, Performance</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>src/domain/_shared/money.ts:88</t>
         </is>
@@ -6537,22 +8185,32 @@
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>ImportHoldings</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>accountClassBreakdown, actualDebtPayment, allocation, annualCoupon, assetAllocation, buildAssetsState, buildDebtState, buildItemizedAccounts, buildNetWorth, capGains, capGainsTax, cashTotal, costBasis, earmarkedAmount, itemizeRemainder, itemizedTotal, lookBack, marketValue, minimumDebtService, normalizeSnapshot, planDoor, projectNestEgg, retirementEarmarkedValue, retirementSpendMonthly, salaryGrossByMonth, simulate, taxBucketSplit, trendPoints, unrealizedGain</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
+          <t>ImportHoldings</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>accountClassBreakdown, actualDebtPayment, allocation, annualCoupon, assetAllocation, buildAssetsState, buildDebtState, buildItemizedAccounts, buildNetWorth, capGains, capGainsTax, cashTotal, costBasis, earmarkedAmount, itemizeRemainder, itemizedTotal, lookBack, marketValue, minimumDebtService, normalizeSnapshot, planDoor, projectNestEgg, retirementEarmarkedValue, retirementSpendMonthly, salaryGrossByMonth, simulate, taxBucketSplit, trendPoints, unrealizedGain</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>src/domain/_shared/num.ts:12</t>
         </is>
@@ -6560,7 +8218,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -255,25 +255,35 @@
     </comment>
     <comment ref="J2" authorId="0" shapeId="0">
       <text>
-        <t>Only filled where Status is DEFECT. The corrected formula or rule. The difference between this column and the Formula column IS the work list — so the target never lives only in someone's head or a commit message.</t>
+        <t>The correct BEHAVIOUR — the spec. What the number ought to be, stated so it could be handed to anyone. Only filled where the current behaviour is wrong.</t>
       </text>
     </comment>
     <comment ref="K2" authorId="0" shapeId="0">
       <text>
-        <t>Screens in scope that import it directly.</t>
+        <t>Y or N. The filterable flag — sort on this to get the work list in one move. UNRESOLVED rows are Y: they need a decision before they need code.</t>
       </text>
     </comment>
     <comment ref="L2" authorId="0" shapeId="0">
       <text>
-        <t>Other calculations that use it.</t>
+        <t>HOW to get there — the action, not the spec. 'What it should be' says the money must appear in exactly one place; this says which of the two code paths to delete. Where a founder decision is needed first, this names the decision instead of a change.</t>
       </text>
     </comment>
     <comment ref="M2" authorId="0" shapeId="0">
       <text>
+        <t>Screens in scope that import it directly.</t>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="0" shapeId="0">
+      <text>
+        <t>Other calculations that use it.</t>
+      </text>
+    </comment>
+    <comment ref="O2" authorId="0" shapeId="0">
+      <text>
         <t>Declared return type.</t>
       </text>
     </comment>
-    <comment ref="N2" authorId="0" shapeId="0">
+    <comment ref="P2" authorId="0" shapeId="0">
       <text>
         <t>file:line at the stamped commit.</t>
       </text>
@@ -335,25 +345,35 @@
     </comment>
     <comment ref="J2" authorId="0" shapeId="0">
       <text>
-        <t>Only filled where Status is DEFECT. The corrected formula or rule. The difference between this column and the Formula column IS the work list — so the target never lives only in someone's head or a commit message.</t>
+        <t>The correct BEHAVIOUR — the spec. What the number ought to be, stated so it could be handed to anyone. Only filled where the current behaviour is wrong.</t>
       </text>
     </comment>
     <comment ref="K2" authorId="0" shapeId="0">
       <text>
-        <t>Screens in scope that import it directly.</t>
+        <t>Y or N. The filterable flag — sort on this to get the work list in one move. UNRESOLVED rows are Y: they need a decision before they need code.</t>
       </text>
     </comment>
     <comment ref="L2" authorId="0" shapeId="0">
       <text>
-        <t>Other calculations that use it.</t>
+        <t>HOW to get there — the action, not the spec. 'What it should be' says the money must appear in exactly one place; this says which of the two code paths to delete. Where a founder decision is needed first, this names the decision instead of a change.</t>
       </text>
     </comment>
     <comment ref="M2" authorId="0" shapeId="0">
       <text>
+        <t>Screens in scope that import it directly.</t>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="0" shapeId="0">
+      <text>
+        <t>Other calculations that use it.</t>
+      </text>
+    </comment>
+    <comment ref="O2" authorId="0" shapeId="0">
+      <text>
         <t>Declared return type.</t>
       </text>
     </comment>
-    <comment ref="N2" authorId="0" shapeId="0">
+    <comment ref="P2" authorId="0" shapeId="0">
       <text>
         <t>file:line at the stamped commit.</t>
       </text>
@@ -652,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N160"/>
+  <dimension ref="A1:P160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -665,10 +685,12 @@
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="52" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="52" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="46" customHeight="1">
@@ -731,20 +753,30 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
+          <t>Fix needed?</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>RECOMMENDED FIX</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
           <t>Screens</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Called by</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Returns</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -773,22 +805,32 @@
           <t>currencySymbol</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>currencySymbol</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>currencySymbol</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>src/domain/_shared/money.ts:49</t>
         </is>
@@ -817,22 +859,32 @@
           <t>money</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>money</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>money</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>src/domain/_shared/money.ts:58</t>
         </is>
@@ -861,22 +913,32 @@
           <t>money2</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>money2</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>money2</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>src/domain/_shared/money.ts:74</t>
         </is>
@@ -905,22 +967,32 @@
           <t>assetsFromOnboarding, debtsFromOnboarding, ingestSync</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>ImportHoldings</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>assetsFromOnboarding, debtsFromOnboarding, ingestSync</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
+          <t>ImportHoldings</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>assetsFromOnboarding, debtsFromOnboarding, ingestSync</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
           <t>EntityId</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>src/domain/_shared/ids.ts:6</t>
         </is>
@@ -949,22 +1021,32 @@
           <t>assetsFromOnboarding, debtsFromOnboarding, employerMatchMonthly, equityRowValue, monthlyContributionsFromOnboarding, plannedMonthlySpend, retirementIncomeMonthly, retirementSpendMonthly, rsuAnnual, salaryGrossByMonth, stateRateOf, tipsAnnual, totalGrossAnnual</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>assetsFromOnboarding, debtsFromOnboarding, employerMatchMonthly, equityRowValue, monthlyContributionsFromOnboarding, plannedMonthlySpend, retirementIncomeMonthly, retirementSpendMonthly, rsuAnnual, salaryGrossByMonth, stateRateOf, tipsAnnual, totalGrossAnnual</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>assetsFromOnboarding, debtsFromOnboarding, employerMatchMonthly, equityRowValue, monthlyContributionsFromOnboarding, plannedMonthlySpend, retirementIncomeMonthly, retirementSpendMonthly, rsuAnnual, salaryGrossByMonth, stateRateOf, tipsAnnual, totalGrossAnnual</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>src/domain/_shared/num.ts:4</t>
         </is>
@@ -993,22 +1075,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="P8" s="5" t="inlineStr">
         <is>
           <t>src/domain/alternatives/index.ts:15</t>
         </is>
@@ -1037,22 +1129,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="P9" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:116</t>
         </is>
@@ -1081,22 +1183,32 @@
           <t>assetAllocation, cashTotal</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>AccountDetail, NetWorth</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>assetAllocation, cashTotal</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail, NetWorth</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr">
+        <is>
+          <t>assetAllocation, cashTotal</t>
+        </is>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
           <t>Record&lt;AssetClass, number&gt; | null</t>
         </is>
       </c>
-      <c r="N10" s="5" t="inlineStr">
+      <c r="P10" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:416</t>
         </is>
@@ -1125,22 +1237,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>AccountDetail, NetWorth, Performance</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail, NetWorth, Performance</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
           <t>Map&lt;string, string&gt;</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="P11" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:394</t>
         </is>
@@ -1169,22 +1291,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
           <t>Record&lt;AssetClass, number&gt;</t>
         </is>
       </c>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="P12" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:517</t>
         </is>
@@ -1213,22 +1345,32 @@
           <t>accountAllowsTicker, accountClassBreakdown, assetAllocation, cashTotal, earmarkDefault, investmentsTotal, isBond, isRealAsset, primaryCarIdOf</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>AccountDetail, NetWorth, Performance</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>accountAllowsTicker, accountClassBreakdown, assetAllocation, cashTotal, earmarkDefault, investmentsTotal, isBond, isRealAsset, primaryCarIdOf</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail, NetWorth, Performance</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>accountAllowsTicker, accountClassBreakdown, assetAllocation, cashTotal, earmarkDefault, investmentsTotal, isBond, isRealAsset, primaryCarIdOf</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
           <t>AssetClass</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="P13" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:236</t>
         </is>
@@ -1257,22 +1399,32 @@
           <t>benchmarkReturn, isCashKind</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="K14" s="3" t="inlineStr">
         <is>
           <t>AccountDetail, NetWorth, Performance</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>benchmarkReturn, isCashKind</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail, NetWorth, Performance</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="inlineStr">
+        <is>
+          <t>benchmarkReturn, isCashKind</t>
+        </is>
+      </c>
+      <c r="O14" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="P14" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:165</t>
         </is>
@@ -1301,22 +1453,32 @@
           <t>resolveNetWorthRows</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>resolveNetWorthRows</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>resolveNetWorthRows</t>
+        </is>
+      </c>
+      <c r="O15" s="5" t="inlineStr">
+        <is>
           <t>AssetsDoc</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="P15" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:690</t>
         </is>
@@ -1345,22 +1507,32 @@
           <t>blendedReturn</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K16" s="3" t="inlineStr">
         <is>
           <t>AccountDetail, Performance</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>blendedReturn</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail, Performance</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>blendedReturn</t>
+        </is>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="P16" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:569</t>
         </is>
@@ -1389,22 +1561,32 @@
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="P17" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:653</t>
         </is>
@@ -1433,22 +1615,32 @@
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="O18" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="P18" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:612</t>
         </is>
@@ -1477,22 +1669,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O19" s="5" t="inlineStr">
+        <is>
           <t>AssetsState</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="P19" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:678</t>
         </is>
@@ -1521,22 +1723,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>Itemize</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
+          <t>Itemize</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O20" s="5" t="inlineStr">
+        <is>
           <t>Omit&lt;AssetAccount, 'asset_id'&gt;[]</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="P20" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/itemize.ts:48</t>
         </is>
@@ -1565,22 +1777,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O21" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="P21" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:286</t>
         </is>
@@ -1609,22 +1831,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O22" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="P22" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:480</t>
         </is>
@@ -1653,22 +1885,32 @@
           <t>earmarkedAmount</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>earmarkedAmount</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>earmarkedAmount</t>
+        </is>
+      </c>
+      <c r="O23" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N23" s="5" t="inlineStr">
+      <c r="P23" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:543</t>
         </is>
@@ -1697,22 +1939,32 @@
           <t>blendedReturn, blendedVolatility, portfolioActualReturn, retirementEarmarkedValue, taxBucketSplit</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L24" s="5" t="inlineStr">
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>blendedReturn, blendedVolatility, portfolioActualReturn, retirementEarmarkedValue, taxBucketSplit</t>
         </is>
       </c>
       <c r="M24" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>blendedReturn, blendedVolatility, portfolioActualReturn, retirementEarmarkedValue, taxBucketSplit</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N24" s="5" t="inlineStr">
+      <c r="P24" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:558</t>
         </is>
@@ -1741,22 +1993,32 @@
           <t>accountClassBreakdown, assetClassOf, classifyHolding</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>accountClassBreakdown, assetClassOf, classifyHolding</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>accountClassBreakdown, assetClassOf, classifyHolding</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
           <t>AssetClass | null</t>
         </is>
       </c>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="P25" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:202</t>
         </is>
@@ -1785,22 +2047,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N26" s="5" t="inlineStr">
+      <c r="P26" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:311</t>
         </is>
@@ -1829,22 +2101,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N27" s="5" t="inlineStr">
+      <c r="P27" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:306</t>
         </is>
@@ -1873,22 +2155,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L28" s="5" t="inlineStr">
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O28" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="N28" s="5" t="inlineStr">
+      <c r="P28" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:164</t>
         </is>
@@ -1917,22 +2209,32 @@
           <t>investableAssets</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t>investableAssets</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>investableAssets</t>
+        </is>
+      </c>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="N29" s="5" t="inlineStr">
+      <c r="P29" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:268</t>
         </is>
@@ -1961,22 +2263,32 @@
           <t>itemizeRemainder</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>Itemize</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr">
+      <c r="L30" s="3" t="inlineStr">
         <is>
           <t>itemizeRemainder</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
         <is>
+          <t>Itemize</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>itemizeRemainder</t>
+        </is>
+      </c>
+      <c r="O30" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N30" s="5" t="inlineStr">
+      <c r="P30" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/itemize.ts:28</t>
         </is>
@@ -2005,22 +2317,32 @@
           <t>buildItemizedAccounts</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>Itemize</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr">
+      <c r="L31" s="3" t="inlineStr">
         <is>
           <t>buildItemizedAccounts</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
+          <t>Itemize</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>buildItemizedAccounts</t>
+        </is>
+      </c>
+      <c r="O31" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N31" s="5" t="inlineStr">
+      <c r="P31" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/itemize.ts:32</t>
         </is>
@@ -2049,22 +2371,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr">
+      <c r="L32" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O32" s="5" t="inlineStr">
+        <is>
           <t>'cash' | 'bonds'</t>
         </is>
       </c>
-      <c r="N32" s="5" t="inlineStr">
+      <c r="P32" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:215</t>
         </is>
@@ -2093,22 +2425,32 @@
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="O33" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N33" s="5" t="inlineStr">
+      <c r="P33" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:710</t>
         </is>
@@ -2137,22 +2479,32 @@
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="M34" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="O34" s="5" t="inlineStr">
+        <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="P34" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:106</t>
         </is>
@@ -2181,22 +2533,32 @@
           <t>blendedReturn, blendedVolatility, retirementEarmarkedValue</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L35" s="5" t="inlineStr">
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
         <is>
           <t>blendedReturn, blendedVolatility, retirementEarmarkedValue</t>
         </is>
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>blendedReturn, blendedVolatility, retirementEarmarkedValue</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="inlineStr">
+        <is>
           <t>string | undefined</t>
         </is>
       </c>
-      <c r="N35" s="5" t="inlineStr">
+      <c r="P35" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:552</t>
         </is>
@@ -2225,22 +2587,32 @@
           <t>earmarkDefault</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L36" s="5" t="inlineStr">
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
         <is>
           <t>earmarkDefault</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>earmarkDefault</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
           <t>RealEstateUse</t>
         </is>
       </c>
-      <c r="N36" s="5" t="inlineStr">
+      <c r="P36" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:262</t>
         </is>
@@ -2269,22 +2641,32 @@
           <t>planDoor, selectWillItLast, willItLastInputs</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L37" s="5" t="inlineStr">
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
         <is>
           <t>planDoor, selectWillItLast, willItLastInputs</t>
         </is>
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>planDoor, selectWillItLast, willItLastInputs</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N37" s="5" t="inlineStr">
+      <c r="P37" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:563</t>
         </is>
@@ -2313,22 +2695,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="K38" s="3" t="inlineStr">
         <is>
           <t>AccountDetail, NetWorth</t>
         </is>
       </c>
-      <c r="L38" s="5" t="inlineStr">
+      <c r="L38" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M38" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail, NetWorth</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O38" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N38" s="5" t="inlineStr">
+      <c r="P38" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:726</t>
         </is>
@@ -2357,22 +2749,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="K39" s="3" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="L39" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail</t>
+        </is>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O39" s="5" t="inlineStr">
+        <is>
           <t>TaxTreatment</t>
         </is>
       </c>
-      <c r="N39" s="5" t="inlineStr">
+      <c r="P39" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:253</t>
         </is>
@@ -2401,22 +2803,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="K40" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="L40" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O40" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="N40" s="5" t="inlineStr">
+      <c r="P40" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:794</t>
         </is>
@@ -2445,22 +2857,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="K41" s="3" t="inlineStr">
         <is>
           <t>AccountDetail, Performance</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr">
+      <c r="L41" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail, Performance</t>
+        </is>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O41" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="N41" s="5" t="inlineStr">
+      <c r="P41" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:95</t>
         </is>
@@ -2489,22 +2911,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K42" s="5" t="inlineStr">
+      <c r="K42" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L42" s="5" t="inlineStr">
+      <c r="L42" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M42" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="N42" s="5" t="inlineStr">
+      <c r="P42" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:223</t>
         </is>
@@ -2533,22 +2965,32 @@
           <t>approxYTM, currentYield</t>
         </is>
       </c>
-      <c r="K43" s="5" t="inlineStr">
+      <c r="K43" s="3" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="L43" s="5" t="inlineStr">
+      <c r="L43" s="3" t="inlineStr">
         <is>
           <t>approxYTM, currentYield</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail</t>
+        </is>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>approxYTM, currentYield</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="P43" s="5" t="inlineStr">
         <is>
           <t>src/domain/bonds/index.ts:21</t>
         </is>
@@ -2577,22 +3019,32 @@
           <t>bondRateSensitivity</t>
         </is>
       </c>
-      <c r="K44" s="5" t="inlineStr">
+      <c r="K44" s="3" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="L44" s="5" t="inlineStr">
+      <c r="L44" s="3" t="inlineStr">
         <is>
           <t>bondRateSensitivity</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>bondRateSensitivity</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="N44" s="5" t="inlineStr">
+      <c r="P44" s="5" t="inlineStr">
         <is>
           <t>src/domain/bonds/index.ts:33</t>
         </is>
@@ -2621,22 +3073,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K45" s="5" t="inlineStr">
+      <c r="K45" s="3" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="L45" s="5" t="inlineStr">
+      <c r="L45" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail</t>
+        </is>
+      </c>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O45" s="5" t="inlineStr">
+        <is>
           <t>BondInfo</t>
         </is>
       </c>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="P45" s="5" t="inlineStr">
         <is>
           <t>src/domain/bonds/index.ts:16</t>
         </is>
@@ -2665,22 +3127,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K46" s="5" t="inlineStr">
+      <c r="K46" s="3" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="L46" s="5" t="inlineStr">
+      <c r="L46" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M46" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail</t>
+        </is>
+      </c>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
           <t>RateSensitivity | null</t>
         </is>
       </c>
-      <c r="N46" s="5" t="inlineStr">
+      <c r="P46" s="5" t="inlineStr">
         <is>
           <t>src/domain/bonds/index.ts:97</t>
         </is>
@@ -2709,22 +3181,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K47" s="5" t="inlineStr">
+      <c r="K47" s="3" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="L47" s="5" t="inlineStr">
+      <c r="L47" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail</t>
+        </is>
+      </c>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="inlineStr">
+        <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="P47" s="5" t="inlineStr">
         <is>
           <t>src/domain/bonds/index.ts:29</t>
         </is>
@@ -2753,22 +3235,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K48" s="5" t="inlineStr">
+      <c r="K48" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="L48" s="5" t="inlineStr">
+      <c r="L48" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="N48" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O48" s="5" t="inlineStr">
+        <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="N48" s="5" t="inlineStr">
+      <c r="P48" s="5" t="inlineStr">
         <is>
           <t>src/domain/bonds/index.ts:13</t>
         </is>
@@ -2797,22 +3289,32 @@
           <t>approxYTM</t>
         </is>
       </c>
-      <c r="K49" s="5" t="inlineStr">
+      <c r="K49" s="3" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="L49" s="5" t="inlineStr">
+      <c r="L49" s="3" t="inlineStr">
         <is>
           <t>approxYTM</t>
         </is>
       </c>
       <c r="M49" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail</t>
+        </is>
+      </c>
+      <c r="N49" s="5" t="inlineStr">
+        <is>
+          <t>approxYTM</t>
+        </is>
+      </c>
+      <c r="O49" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N49" s="5" t="inlineStr">
+      <c r="P49" s="5" t="inlineStr">
         <is>
           <t>src/domain/bonds/index.ts:24</t>
         </is>
@@ -2841,22 +3343,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="K50" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L50" s="5" t="inlineStr">
+      <c r="L50" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N50" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O50" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N50" s="5" t="inlineStr">
+      <c r="P50" s="5" t="inlineStr">
         <is>
           <t>src/domain/budget/index.ts:45</t>
         </is>
@@ -2885,22 +3397,32 @@
           <t>plannedMonthlySpend</t>
         </is>
       </c>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L51" s="5" t="inlineStr">
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
         <is>
           <t>plannedMonthlySpend</t>
         </is>
       </c>
       <c r="M51" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N51" s="5" t="inlineStr">
+        <is>
+          <t>plannedMonthlySpend</t>
+        </is>
+      </c>
+      <c r="O51" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="N51" s="5" t="inlineStr">
+      <c r="P51" s="5" t="inlineStr">
         <is>
           <t>src/domain/budget/index.ts:72</t>
         </is>
@@ -2929,22 +3451,32 @@
           <t>buildDebtState</t>
         </is>
       </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L52" s="5" t="inlineStr">
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
         <is>
           <t>buildDebtState</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N52" s="5" t="inlineStr">
+        <is>
+          <t>buildDebtState</t>
+        </is>
+      </c>
+      <c r="O52" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N52" s="5" t="inlineStr">
+      <c r="P52" s="5" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:59</t>
         </is>
@@ -2973,22 +3505,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K53" s="5" t="inlineStr">
+      <c r="K53" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L53" s="5" t="inlineStr">
+      <c r="L53" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M53" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N53" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O53" s="5" t="inlineStr">
+        <is>
           <t>DebtState</t>
         </is>
       </c>
-      <c r="N53" s="5" t="inlineStr">
+      <c r="P53" s="5" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:214</t>
         </is>
@@ -3017,22 +3559,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="K54" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L54" s="5" t="inlineStr">
+      <c r="L54" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M54" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N54" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O54" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="N54" s="5" t="inlineStr">
+      <c r="P54" s="5" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:197</t>
         </is>
@@ -3061,22 +3613,32 @@
           <t>resolveNetWorthRows</t>
         </is>
       </c>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L55" s="5" t="inlineStr">
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
         <is>
           <t>resolveNetWorthRows</t>
         </is>
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N55" s="5" t="inlineStr">
+        <is>
+          <t>resolveNetWorthRows</t>
+        </is>
+      </c>
+      <c r="O55" s="5" t="inlineStr">
+        <is>
           <t>DebtDoc</t>
         </is>
       </c>
-      <c r="N55" s="5" t="inlineStr">
+      <c r="P55" s="5" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:240</t>
         </is>
@@ -3105,22 +3667,32 @@
           <t>paymentShape</t>
         </is>
       </c>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L56" s="5" t="inlineStr">
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
         <is>
           <t>paymentShape</t>
         </is>
       </c>
       <c r="M56" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N56" s="5" t="inlineStr">
+        <is>
+          <t>paymentShape</t>
+        </is>
+      </c>
+      <c r="O56" s="5" t="inlineStr">
+        <is>
           <t>NonNullable&lt;Debt['payment_type']&gt;</t>
         </is>
       </c>
-      <c r="N56" s="5" t="inlineStr">
+      <c r="P56" s="5" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:35</t>
         </is>
@@ -3149,22 +3721,32 @@
           <t>debtsFromOnboarding</t>
         </is>
       </c>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L57" s="5" t="inlineStr">
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
         <is>
           <t>debtsFromOnboarding</t>
         </is>
       </c>
       <c r="M57" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N57" s="5" t="inlineStr">
+        <is>
+          <t>debtsFromOnboarding</t>
+        </is>
+      </c>
+      <c r="O57" s="5" t="inlineStr">
+        <is>
           <t>DebtType</t>
         </is>
       </c>
-      <c r="N57" s="5" t="inlineStr">
+      <c r="P57" s="5" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:228</t>
         </is>
@@ -3193,22 +3775,32 @@
           <t>buildDebtState</t>
         </is>
       </c>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L58" s="5" t="inlineStr">
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
         <is>
           <t>buildDebtState</t>
         </is>
       </c>
       <c r="M58" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N58" s="5" t="inlineStr">
+        <is>
+          <t>buildDebtState</t>
+        </is>
+      </c>
+      <c r="O58" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N58" s="5" t="inlineStr">
+      <c r="P58" s="5" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:55</t>
         </is>
@@ -3237,22 +3829,32 @@
           <t>minimumDebtService, requiredPayment</t>
         </is>
       </c>
-      <c r="K59" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L59" s="5" t="inlineStr">
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
         <is>
           <t>minimumDebtService, requiredPayment</t>
         </is>
       </c>
       <c r="M59" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N59" s="5" t="inlineStr">
+        <is>
+          <t>minimumDebtService, requiredPayment</t>
+        </is>
+      </c>
+      <c r="O59" s="5" t="inlineStr">
+        <is>
           <t>NonNullable&lt;Debt['payment_type']&gt;</t>
         </is>
       </c>
-      <c r="N59" s="5" t="inlineStr">
+      <c r="P59" s="5" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:38</t>
         </is>
@@ -3281,22 +3883,32 @@
           <t>totalDebtMonthly</t>
         </is>
       </c>
-      <c r="K60" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L60" s="5" t="inlineStr">
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
         <is>
           <t>totalDebtMonthly</t>
         </is>
       </c>
       <c r="M60" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N60" s="5" t="inlineStr">
+        <is>
+          <t>totalDebtMonthly</t>
+        </is>
+      </c>
+      <c r="O60" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N60" s="5" t="inlineStr">
+      <c r="P60" s="5" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:44</t>
         </is>
@@ -3325,22 +3937,32 @@
           <t>actualDebtPayment</t>
         </is>
       </c>
-      <c r="K61" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L61" s="5" t="inlineStr">
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
         <is>
           <t>actualDebtPayment</t>
         </is>
       </c>
       <c r="M61" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N61" s="5" t="inlineStr">
+        <is>
+          <t>actualDebtPayment</t>
+        </is>
+      </c>
+      <c r="O61" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N61" s="5" t="inlineStr">
+      <c r="P61" s="5" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:49</t>
         </is>
@@ -3369,22 +3991,32 @@
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="K62" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L62" s="5" t="inlineStr">
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="M62" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N62" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="O62" s="5" t="inlineStr">
+        <is>
           <t>BucketSplit</t>
         </is>
       </c>
-      <c r="N62" s="5" t="inlineStr">
+      <c r="P62" s="5" t="inlineStr">
         <is>
           <t>src/domain/decumulation/index.ts:10</t>
         </is>
@@ -3413,22 +4045,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K63" s="5" t="inlineStr">
+      <c r="K63" s="3" t="inlineStr">
         <is>
           <t>NetWorth, Performance</t>
         </is>
       </c>
-      <c r="L63" s="5" t="inlineStr">
+      <c r="L63" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M63" s="5" t="inlineStr">
         <is>
+          <t>NetWorth, Performance</t>
+        </is>
+      </c>
+      <c r="N63" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O63" s="5" t="inlineStr">
+        <is>
           <t>DataGap[]</t>
         </is>
       </c>
-      <c r="N63" s="5" t="inlineStr">
+      <c r="P63" s="5" t="inlineStr">
         <is>
           <t>src/domain/gaps/index.ts:57</t>
         </is>
@@ -3481,22 +4123,32 @@
           <t>STOP CALLING THE RESIDUAL A MEASUREMENT. Two changes. (1) The unexplained remainder gets its own honest row — "we could not account for $X" — instead of being printed as "change in investment value". A person can act on "unexplained"; they cannot act on a market loss that never happened. (2) Market movement is MEASURED where the evidence exists — from stored per-holding values — and the row is simply absent when it does not, rather than being inferred. Absent beats invented.</t>
         </is>
       </c>
-      <c r="K64" s="5" t="inlineStr">
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>Split the function in two. Keep the balancing arithmetic (it is sound and the rows must always sum), but return the unexplained remainder under its own name — unexplained — and let the screen print it as such. Then add a SEPARATE measured market-movement figure sourced from stored per-holding values, shown only when that history exists. Two small changes, no new engine.</t>
+        </is>
+      </c>
+      <c r="M64" s="5" t="inlineStr">
         <is>
           <t>NetWorth, Performance</t>
         </is>
       </c>
-      <c r="L64" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M64" s="5" t="inlineStr">
+      <c r="N64" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O64" s="5" t="inlineStr">
         <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="N64" s="5" t="inlineStr">
+      <c r="P64" s="5" t="inlineStr">
         <is>
           <t>src/domain/history.ts:144</t>
         </is>
@@ -3549,22 +4201,32 @@
           <t>THE BASELINE MUST BE A CHOSEN DATE, NOT AN ACCIDENT. Today it is whatever day the app happened to be opened. It should be a stated window the person picks (this month · this year · since I started), and where no snapshot exists at that date the app says so instead of quietly using a later one. Also: never overwrite the earliest point of a period — see the snapshot defect — or the baseline keeps moving toward today.</t>
         </is>
       </c>
-      <c r="K65" s="5" t="inlineStr">
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>Change the signature to take an explicit start date rather than inferring one, and return null with a reason when no snapshot exists at that date so the screen can say "no record that far back" instead of silently using a nearer one. Depends on the snapshot fix below — do that one first or the baseline keeps sliding toward today.</t>
+        </is>
+      </c>
+      <c r="M65" s="5" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L65" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M65" s="5" t="inlineStr">
+      <c r="N65" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O65" s="5" t="inlineStr">
         <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="N65" s="5" t="inlineStr">
+      <c r="P65" s="5" t="inlineStr">
         <is>
           <t>src/domain/history.ts:118</t>
         </is>
@@ -3593,22 +4255,32 @@
           <t>readHistory</t>
         </is>
       </c>
-      <c r="K66" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L66" s="5" t="inlineStr">
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
         <is>
           <t>readHistory</t>
         </is>
       </c>
       <c r="M66" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N66" s="5" t="inlineStr">
+        <is>
+          <t>readHistory</t>
+        </is>
+      </c>
+      <c r="O66" s="5" t="inlineStr">
+        <is>
           <t>MonthlySnapshot | null</t>
         </is>
       </c>
-      <c r="N66" s="5" t="inlineStr">
+      <c r="P66" s="5" t="inlineStr">
         <is>
           <t>src/domain/history.ts:77</t>
         </is>
@@ -3637,22 +4309,32 @@
           <t>trendPoints</t>
         </is>
       </c>
-      <c r="K67" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L67" s="5" t="inlineStr">
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
         <is>
           <t>trendPoints</t>
         </is>
       </c>
       <c r="M67" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N67" s="5" t="inlineStr">
+        <is>
+          <t>trendPoints</t>
+        </is>
+      </c>
+      <c r="O67" s="5" t="inlineStr">
+        <is>
           <t>MonthlySnapshot[]</t>
         </is>
       </c>
-      <c r="N67" s="5" t="inlineStr">
+      <c r="P67" s="5" t="inlineStr">
         <is>
           <t>src/domain/history.ts:107</t>
         </is>
@@ -3681,22 +4363,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K68" s="5" t="inlineStr">
+      <c r="K68" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L68" s="5" t="inlineStr">
+      <c r="L68" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N68" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O68" s="5" t="inlineStr">
+        <is>
           <t>TrendPoint[]</t>
         </is>
       </c>
-      <c r="N68" s="5" t="inlineStr">
+      <c r="P68" s="5" t="inlineStr">
         <is>
           <t>src/domain/history.ts:43</t>
         </is>
@@ -3725,22 +4417,32 @@
           <t>importHoldings</t>
         </is>
       </c>
-      <c r="K69" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="5" t="inlineStr">
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
         <is>
           <t>importHoldings</t>
         </is>
       </c>
       <c r="M69" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="5" t="inlineStr">
+        <is>
+          <t>importHoldings</t>
+        </is>
+      </c>
+      <c r="O69" s="5" t="inlineStr">
+        <is>
           <t>AssetClass</t>
         </is>
       </c>
-      <c r="N69" s="5" t="inlineStr">
+      <c r="P69" s="5" t="inlineStr">
         <is>
           <t>src/domain/import/holdingsImport.ts:154</t>
         </is>
@@ -3769,22 +4471,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K70" s="5" t="inlineStr">
+      <c r="K70" s="3" t="inlineStr">
         <is>
           <t>ImportHoldings</t>
         </is>
       </c>
-      <c r="L70" s="5" t="inlineStr">
+      <c r="L70" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M70" s="5" t="inlineStr">
         <is>
+          <t>ImportHoldings</t>
+        </is>
+      </c>
+      <c r="N70" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N70" s="5" t="inlineStr">
+      <c r="P70" s="5" t="inlineStr">
         <is>
           <t>src/domain/import/holdingsImport.ts:61</t>
         </is>
@@ -3813,22 +4525,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K71" s="5" t="inlineStr">
+      <c r="K71" s="3" t="inlineStr">
         <is>
           <t>ImportHoldings</t>
         </is>
       </c>
-      <c r="L71" s="5" t="inlineStr">
+      <c r="L71" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M71" s="5" t="inlineStr">
         <is>
+          <t>ImportHoldings</t>
+        </is>
+      </c>
+      <c r="N71" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="5" t="inlineStr">
+        <is>
           <t>ImportResult</t>
         </is>
       </c>
-      <c r="N71" s="5" t="inlineStr">
+      <c r="P71" s="5" t="inlineStr">
         <is>
           <t>src/domain/import/holdingsImport.ts:183</t>
         </is>
@@ -3857,22 +4579,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K72" s="5" t="inlineStr">
+      <c r="K72" s="3" t="inlineStr">
         <is>
           <t>ImportHoldings</t>
         </is>
       </c>
-      <c r="L72" s="5" t="inlineStr">
+      <c r="L72" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M72" s="5" t="inlineStr">
         <is>
+          <t>ImportHoldings</t>
+        </is>
+      </c>
+      <c r="N72" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="5" t="inlineStr">
+        <is>
           <t>AssetAccount | null</t>
         </is>
       </c>
-      <c r="N72" s="5" t="inlineStr">
+      <c r="P72" s="5" t="inlineStr">
         <is>
           <t>src/domain/import/holdingsImport.ts:254</t>
         </is>
@@ -3901,22 +4633,32 @@
           <t>importHoldings</t>
         </is>
       </c>
-      <c r="K73" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="5" t="inlineStr">
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
         <is>
           <t>importHoldings</t>
         </is>
       </c>
       <c r="M73" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="5" t="inlineStr">
+        <is>
+          <t>importHoldings</t>
+        </is>
+      </c>
+      <c r="O73" s="5" t="inlineStr">
+        <is>
           <t>string[][]</t>
         </is>
       </c>
-      <c r="N73" s="5" t="inlineStr">
+      <c r="P73" s="5" t="inlineStr">
         <is>
           <t>src/domain/import/holdingsImport.ts:74</t>
         </is>
@@ -3945,22 +4687,32 @@
           <t>resolveLens, totalGrossAnnual</t>
         </is>
       </c>
-      <c r="K74" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="5" t="inlineStr">
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
         <is>
           <t>resolveLens, totalGrossAnnual</t>
         </is>
       </c>
       <c r="M74" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="5" t="inlineStr">
+        <is>
+          <t>resolveLens, totalGrossAnnual</t>
+        </is>
+      </c>
+      <c r="O74" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N74" s="5" t="inlineStr">
+      <c r="P74" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:191</t>
         </is>
@@ -3989,22 +4741,32 @@
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="K75" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="5" t="inlineStr">
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="M75" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N75" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="O75" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N75" s="5" t="inlineStr">
+      <c r="P75" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/tax.ts:107</t>
         </is>
@@ -4033,22 +4795,32 @@
           <t>monthlyContributionsFromOnboarding</t>
         </is>
       </c>
-      <c r="K76" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L76" s="5" t="inlineStr">
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
         <is>
           <t>monthlyContributionsFromOnboarding</t>
         </is>
       </c>
       <c r="M76" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N76" s="5" t="inlineStr">
+        <is>
+          <t>monthlyContributionsFromOnboarding</t>
+        </is>
+      </c>
+      <c r="O76" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N76" s="5" t="inlineStr">
+      <c r="P76" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:242</t>
         </is>
@@ -4077,22 +4849,32 @@
           <t>rsuAnnual</t>
         </is>
       </c>
-      <c r="K77" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L77" s="5" t="inlineStr">
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L77" s="3" t="inlineStr">
         <is>
           <t>rsuAnnual</t>
         </is>
       </c>
       <c r="M77" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N77" s="5" t="inlineStr">
+        <is>
+          <t>rsuAnnual</t>
+        </is>
+      </c>
+      <c r="O77" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N77" s="5" t="inlineStr">
+      <c r="P77" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:68</t>
         </is>
@@ -4121,22 +4903,32 @@
           <t>totalGrossAnnual</t>
         </is>
       </c>
-      <c r="K78" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L78" s="5" t="inlineStr">
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
         <is>
           <t>totalGrossAnnual</t>
         </is>
       </c>
       <c r="M78" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N78" s="5" t="inlineStr">
+        <is>
+          <t>totalGrossAnnual</t>
+        </is>
+      </c>
+      <c r="O78" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="N78" s="5" t="inlineStr">
+      <c r="P78" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:161</t>
         </is>
@@ -4165,22 +4957,32 @@
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="K79" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L79" s="5" t="inlineStr">
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="M79" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="O79" s="5" t="inlineStr">
+        <is>
           <t>import('./tax').FilingStatus</t>
         </is>
       </c>
-      <c r="N79" s="5" t="inlineStr">
+      <c r="P79" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:333</t>
         </is>
@@ -4209,22 +5011,32 @@
           <t>salaryGrossByMonth</t>
         </is>
       </c>
-      <c r="K80" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L80" s="5" t="inlineStr">
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
         <is>
           <t>salaryGrossByMonth</t>
         </is>
       </c>
       <c r="M80" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="5" t="inlineStr">
+        <is>
+          <t>salaryGrossByMonth</t>
+        </is>
+      </c>
+      <c r="O80" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N80" s="5" t="inlineStr">
+      <c r="P80" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/tax.ts:47</t>
         </is>
@@ -4253,22 +5065,32 @@
           <t>rentalNetAnnual</t>
         </is>
       </c>
-      <c r="K81" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L81" s="5" t="inlineStr">
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="3" t="inlineStr">
         <is>
           <t>rentalNetAnnual</t>
         </is>
       </c>
       <c r="M81" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="5" t="inlineStr">
+        <is>
+          <t>rentalNetAnnual</t>
+        </is>
+      </c>
+      <c r="O81" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="N81" s="5" t="inlineStr">
+      <c r="P81" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:129</t>
         </is>
@@ -4297,22 +5119,32 @@
           <t>totalGrossAnnual</t>
         </is>
       </c>
-      <c r="K82" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L82" s="5" t="inlineStr">
+      <c r="K82" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="3" t="inlineStr">
         <is>
           <t>totalGrossAnnual</t>
         </is>
       </c>
       <c r="M82" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="5" t="inlineStr">
+        <is>
+          <t>totalGrossAnnual</t>
+        </is>
+      </c>
+      <c r="O82" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N82" s="5" t="inlineStr">
+      <c r="P82" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:142</t>
         </is>
@@ -4341,22 +5173,32 @@
           <t>currentRetirementIncomeMonthly, willItLastInputs</t>
         </is>
       </c>
-      <c r="K83" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L83" s="5" t="inlineStr">
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
         <is>
           <t>currentRetirementIncomeMonthly, willItLastInputs</t>
         </is>
       </c>
       <c r="M83" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N83" s="5" t="inlineStr">
+        <is>
+          <t>currentRetirementIncomeMonthly, willItLastInputs</t>
+        </is>
+      </c>
+      <c r="O83" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N83" s="5" t="inlineStr">
+      <c r="P83" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:213</t>
         </is>
@@ -4385,22 +5227,32 @@
           <t>rsuAnnual</t>
         </is>
       </c>
-      <c r="K84" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L84" s="5" t="inlineStr">
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L84" s="3" t="inlineStr">
         <is>
           <t>rsuAnnual</t>
         </is>
       </c>
       <c r="M84" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N84" s="5" t="inlineStr">
+        <is>
+          <t>rsuAnnual</t>
+        </is>
+      </c>
+      <c r="O84" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N84" s="5" t="inlineStr">
+      <c r="P84" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:74</t>
         </is>
@@ -4429,22 +5281,32 @@
           <t>totalGrossAnnual</t>
         </is>
       </c>
-      <c r="K85" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L85" s="5" t="inlineStr">
+      <c r="K85" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="inlineStr">
         <is>
           <t>totalGrossAnnual</t>
         </is>
       </c>
       <c r="M85" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N85" s="5" t="inlineStr">
+        <is>
+          <t>totalGrossAnnual</t>
+        </is>
+      </c>
+      <c r="O85" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N85" s="5" t="inlineStr">
+      <c r="P85" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:114</t>
         </is>
@@ -4473,22 +5335,32 @@
           <t>tipsAnnual</t>
         </is>
       </c>
-      <c r="K86" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L86" s="5" t="inlineStr">
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="inlineStr">
         <is>
           <t>tipsAnnual</t>
         </is>
       </c>
       <c r="M86" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N86" s="5" t="inlineStr">
+        <is>
+          <t>tipsAnnual</t>
+        </is>
+      </c>
+      <c r="O86" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N86" s="5" t="inlineStr">
+      <c r="P86" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:306</t>
         </is>
@@ -4517,22 +5389,32 @@
           <t>totalGrossAnnual</t>
         </is>
       </c>
-      <c r="K87" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L87" s="5" t="inlineStr">
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L87" s="3" t="inlineStr">
         <is>
           <t>totalGrossAnnual</t>
         </is>
       </c>
       <c r="M87" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N87" s="5" t="inlineStr">
+        <is>
+          <t>totalGrossAnnual</t>
+        </is>
+      </c>
+      <c r="O87" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N87" s="5" t="inlineStr">
+      <c r="P87" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:310</t>
         </is>
@@ -4561,22 +5443,32 @@
           <t>salaryActiveMonths, salaryAnnual</t>
         </is>
       </c>
-      <c r="K88" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L88" s="5" t="inlineStr">
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L88" s="3" t="inlineStr">
         <is>
           <t>salaryActiveMonths, salaryAnnual</t>
         </is>
       </c>
       <c r="M88" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N88" s="5" t="inlineStr">
+        <is>
+          <t>salaryActiveMonths, salaryAnnual</t>
+        </is>
+      </c>
+      <c r="O88" s="5" t="inlineStr">
+        <is>
           <t>number[]</t>
         </is>
       </c>
-      <c r="N88" s="5" t="inlineStr">
+      <c r="P88" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:46</t>
         </is>
@@ -4605,22 +5497,32 @@
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="K89" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L89" s="5" t="inlineStr">
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L89" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="M89" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N89" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="O89" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N89" s="5" t="inlineStr">
+      <c r="P89" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:337</t>
         </is>
@@ -4649,22 +5551,32 @@
           <t>taxOwed</t>
         </is>
       </c>
-      <c r="K90" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L90" s="5" t="inlineStr">
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L90" s="3" t="inlineStr">
         <is>
           <t>taxOwed</t>
         </is>
       </c>
       <c r="M90" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N90" s="5" t="inlineStr">
+        <is>
+          <t>taxOwed</t>
+        </is>
+      </c>
+      <c r="O90" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N90" s="5" t="inlineStr">
+      <c r="P90" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/tax.ts:17</t>
         </is>
@@ -4693,22 +5605,32 @@
           <t>taxOwedFor</t>
         </is>
       </c>
-      <c r="K91" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L91" s="5" t="inlineStr">
+      <c r="K91" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L91" s="3" t="inlineStr">
         <is>
           <t>taxOwedFor</t>
         </is>
       </c>
       <c r="M91" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N91" s="5" t="inlineStr">
+        <is>
+          <t>taxOwedFor</t>
+        </is>
+      </c>
+      <c r="O91" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N91" s="5" t="inlineStr">
+      <c r="P91" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/tax.ts:88</t>
         </is>
@@ -4737,22 +5659,32 @@
           <t>grossFromNet</t>
         </is>
       </c>
-      <c r="K92" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L92" s="5" t="inlineStr">
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L92" s="3" t="inlineStr">
         <is>
           <t>grossFromNet</t>
         </is>
       </c>
       <c r="M92" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N92" s="5" t="inlineStr">
+        <is>
+          <t>grossFromNet</t>
+        </is>
+      </c>
+      <c r="O92" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N92" s="5" t="inlineStr">
+      <c r="P92" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/tax.ts:29</t>
         </is>
@@ -4781,22 +5713,32 @@
           <t>effectiveRateOnGrossFor</t>
         </is>
       </c>
-      <c r="K93" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L93" s="5" t="inlineStr">
+      <c r="K93" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L93" s="3" t="inlineStr">
         <is>
           <t>effectiveRateOnGrossFor</t>
         </is>
       </c>
       <c r="M93" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N93" s="5" t="inlineStr">
+        <is>
+          <t>effectiveRateOnGrossFor</t>
+        </is>
+      </c>
+      <c r="O93" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N93" s="5" t="inlineStr">
+      <c r="P93" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/tax.ts:94</t>
         </is>
@@ -4825,22 +5767,32 @@
           <t>totalGrossAnnual</t>
         </is>
       </c>
-      <c r="K94" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L94" s="5" t="inlineStr">
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
         <is>
           <t>totalGrossAnnual</t>
         </is>
       </c>
       <c r="M94" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N94" s="5" t="inlineStr">
+        <is>
+          <t>totalGrossAnnual</t>
+        </is>
+      </c>
+      <c r="O94" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N94" s="5" t="inlineStr">
+      <c r="P94" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:204</t>
         </is>
@@ -4869,22 +5821,32 @@
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="K95" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L95" s="5" t="inlineStr">
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L95" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="M95" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N95" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="O95" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N95" s="5" t="inlineStr">
+      <c r="P95" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:316</t>
         </is>
@@ -4913,22 +5875,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K96" s="5" t="inlineStr">
+      <c r="K96" s="3" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="L96" s="5" t="inlineStr">
+      <c r="L96" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M96" s="5" t="inlineStr">
         <is>
+          <t>HoldingDetail, Performance</t>
+        </is>
+      </c>
+      <c r="N96" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O96" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="N96" s="5" t="inlineStr">
+      <c r="P96" s="5" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:390</t>
         </is>
@@ -4957,22 +5929,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K97" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L97" s="5" t="inlineStr">
+      <c r="K97" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L97" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M97" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N97" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O97" s="5" t="inlineStr">
+        <is>
           <t>Promise&lt;ExpenseAnalysis&gt;</t>
         </is>
       </c>
-      <c r="N97" s="5" t="inlineStr">
+      <c r="P97" s="5" t="inlineStr">
         <is>
           <t>src/services/economicData.ts:109</t>
         </is>
@@ -5001,22 +5983,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K98" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L98" s="5" t="inlineStr">
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L98" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M98" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N98" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O98" s="5" t="inlineStr">
+        <is>
           <t>Promise&lt;EconomicData&gt;</t>
         </is>
       </c>
-      <c r="N98" s="5" t="inlineStr">
+      <c r="P98" s="5" t="inlineStr">
         <is>
           <t>src/services/economicData.ts:47</t>
         </is>
@@ -5045,22 +6037,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K99" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L99" s="5" t="inlineStr">
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M99" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N99" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O99" s="5" t="inlineStr">
+        <is>
           <t>Promise&lt;</t>
         </is>
       </c>
-      <c r="N99" s="5" t="inlineStr">
+      <c r="P99" s="5" t="inlineStr">
         <is>
           <t>src/services/economicData.ts:158</t>
         </is>
@@ -5089,22 +6091,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K100" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L100" s="5" t="inlineStr">
+      <c r="K100" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L100" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M100" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N100" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O100" s="5" t="inlineStr">
+        <is>
           <t>AssetAccount[]</t>
         </is>
       </c>
-      <c r="N100" s="5" t="inlineStr">
+      <c r="P100" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/ingest.ts:173</t>
         </is>
@@ -5133,22 +6145,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K101" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L101" s="5" t="inlineStr">
+      <c r="K101" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M101" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N101" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O101" s="5" t="inlineStr">
+        <is>
           <t>SyncResult</t>
         </is>
       </c>
-      <c r="N101" s="5" t="inlineStr">
+      <c r="P101" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/ingest.ts:31</t>
         </is>
@@ -5177,22 +6199,32 @@
           <t>ingestSync</t>
         </is>
       </c>
-      <c r="K102" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L102" s="5" t="inlineStr">
+      <c r="K102" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
         <is>
           <t>ingestSync</t>
         </is>
       </c>
       <c r="M102" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N102" s="5" t="inlineStr">
+        <is>
+          <t>ingestSync</t>
+        </is>
+      </c>
+      <c r="O102" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="N102" s="5" t="inlineStr">
+      <c r="P102" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/ingest.ts:29</t>
         </is>
@@ -5221,22 +6253,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K103" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L103" s="5" t="inlineStr">
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M103" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N103" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O103" s="5" t="inlineStr">
+        <is>
           <t>Promise&lt;Record&lt;string, PriceSeries&gt;&gt;</t>
         </is>
       </c>
-      <c r="N103" s="5" t="inlineStr">
+      <c r="P103" s="5" t="inlineStr">
         <is>
           <t>src/services/marketData.ts:71</t>
         </is>
@@ -5265,22 +6307,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K104" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L104" s="5" t="inlineStr">
+      <c r="K104" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M104" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N104" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O104" s="5" t="inlineStr">
+        <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="N104" s="5" t="inlineStr">
+      <c r="P104" s="5" t="inlineStr">
         <is>
           <t>src/services/marketData.ts:53</t>
         </is>
@@ -5309,22 +6361,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K105" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L105" s="5" t="inlineStr">
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M105" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N105" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O105" s="5" t="inlineStr">
+        <is>
           <t>PriceFreshness</t>
         </is>
       </c>
-      <c r="N105" s="5" t="inlineStr">
+      <c r="P105" s="5" t="inlineStr">
         <is>
           <t>src/services/marketData.ts:60</t>
         </is>
@@ -5377,22 +6439,28 @@
         </is>
       </c>
       <c r="J106" s="3" t="inlineStr"/>
-      <c r="K106" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L106" s="5" t="inlineStr">
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr"/>
+      <c r="M106" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N106" s="5" t="inlineStr">
         <is>
           <t>dedupeActivities, ingestSync</t>
         </is>
       </c>
-      <c r="M106" s="5" t="inlineStr">
+      <c r="O106" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N106" s="5" t="inlineStr">
+      <c r="P106" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:243</t>
         </is>
@@ -5441,22 +6509,28 @@
         </is>
       </c>
       <c r="J107" s="3" t="inlineStr"/>
-      <c r="K107" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L107" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="K107" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L107" s="3" t="inlineStr"/>
       <c r="M107" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N107" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O107" s="5" t="inlineStr">
+        <is>
           <t>StActivity[]</t>
         </is>
       </c>
-      <c r="N107" s="5" t="inlineStr">
+      <c r="P107" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:255</t>
         </is>
@@ -5485,22 +6559,32 @@
           <t>ingestSync</t>
         </is>
       </c>
-      <c r="K108" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L108" s="5" t="inlineStr">
+      <c r="K108" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L108" s="3" t="inlineStr">
         <is>
           <t>ingestSync</t>
         </is>
       </c>
       <c r="M108" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N108" s="5" t="inlineStr">
+        <is>
+          <t>ingestSync</t>
+        </is>
+      </c>
+      <c r="O108" s="5" t="inlineStr">
+        <is>
           <t>WrapperGuess</t>
         </is>
       </c>
-      <c r="N108" s="5" t="inlineStr">
+      <c r="P108" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:71</t>
         </is>
@@ -5549,22 +6633,32 @@
         </is>
       </c>
       <c r="J109" s="3" t="inlineStr"/>
-      <c r="K109" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L109" s="5" t="inlineStr">
+      <c r="K109" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>Nothing to change here. But it is the prime suspect for the $1.4m of phantom contributions and is proved innocent, so the search moves to whatever else writes DEPOSIT rows — manual entry, the CSV importer, or a transfer path. Trace that before touching anything.</t>
+        </is>
+      </c>
+      <c r="M109" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N109" s="5" t="inlineStr">
         <is>
           <t>ingestSync</t>
         </is>
       </c>
-      <c r="M109" s="5" t="inlineStr">
+      <c r="O109" s="5" t="inlineStr">
         <is>
           <t>MappedActivity</t>
         </is>
       </c>
-      <c r="N109" s="5" t="inlineStr">
+      <c r="P109" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:184</t>
         </is>
@@ -5593,22 +6687,32 @@
           <t>ingestSync</t>
         </is>
       </c>
-      <c r="K110" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L110" s="5" t="inlineStr">
+      <c r="K110" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L110" s="3" t="inlineStr">
         <is>
           <t>ingestSync</t>
         </is>
       </c>
       <c r="M110" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N110" s="5" t="inlineStr">
+        <is>
+          <t>ingestSync</t>
+        </is>
+      </c>
+      <c r="O110" s="5" t="inlineStr">
+        <is>
           <t>MappedOption | null</t>
         </is>
       </c>
-      <c r="N110" s="5" t="inlineStr">
+      <c r="P110" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:159</t>
         </is>
@@ -5657,22 +6761,28 @@
         </is>
       </c>
       <c r="J111" s="3" t="inlineStr"/>
-      <c r="K111" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L111" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr"/>
       <c r="M111" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N111" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O111" s="5" t="inlineStr">
+        <is>
           <t>MappedPosition | null</t>
         </is>
       </c>
-      <c r="N111" s="5" t="inlineStr">
+      <c r="P111" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:116</t>
         </is>
@@ -5701,22 +6811,32 @@
           <t>ingestSync</t>
         </is>
       </c>
-      <c r="K112" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L112" s="5" t="inlineStr">
+      <c r="K112" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L112" s="3" t="inlineStr">
         <is>
           <t>ingestSync</t>
         </is>
       </c>
       <c r="M112" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N112" s="5" t="inlineStr">
+        <is>
+          <t>ingestSync</t>
+        </is>
+      </c>
+      <c r="O112" s="5" t="inlineStr">
+        <is>
           <t>string | undefined</t>
         </is>
       </c>
-      <c r="N112" s="5" t="inlineStr">
+      <c r="P112" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:282</t>
         </is>
@@ -5769,22 +6889,32 @@
           <t>The netting is right, but ingest.ts ALSO drops every cash-equivalent position from the holdings list. Both run, so for a broker that flags the fund, the money is subtracted from cash AND missing from holdings. One of the two must go: either show the fund as a holding and net the sleeve (the honest option), or keep it in the sleeve and do not net. Needs a decision, not a patch.</t>
         </is>
       </c>
-      <c r="K113" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L113" s="5" t="inlineStr">
+      <c r="K113" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L113" s="3" t="inlineStr">
+        <is>
+          <t>FOUNDER DECISION FIRST, then a one-line change. Recommend: show the money-market fund as a holding (it pays dividends and belongs in the measured bucket per the 2026-08-04 rule), keep netCashSleeve exactly as it is, and DELETE the .filter((m) =&gt; !m.cashEquivalent) in ingest.ts:67. That leaves the money in exactly one place. The alternative — keep it in the sleeve and stop netting — contradicts the cash-means-cash rule, so I do not recommend it.</t>
+        </is>
+      </c>
+      <c r="M113" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N113" s="5" t="inlineStr">
         <is>
           <t>ingestSync</t>
         </is>
       </c>
-      <c r="M113" s="5" t="inlineStr">
+      <c r="O113" s="5" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N113" s="5" t="inlineStr">
+      <c r="P113" s="5" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:269</t>
         </is>
@@ -5813,22 +6943,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K114" s="5" t="inlineStr">
+      <c r="K114" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L114" s="5" t="inlineStr">
+      <c r="L114" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M114" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N114" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O114" s="5" t="inlineStr">
+        <is>
           <t>NetWorthState</t>
         </is>
       </c>
-      <c r="N114" s="5" t="inlineStr">
+      <c r="P114" s="5" t="inlineStr">
         <is>
           <t>src/domain/networth/index.ts:12</t>
         </is>
@@ -5857,22 +6997,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K115" s="5" t="inlineStr">
+      <c r="K115" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="L115" s="5" t="inlineStr">
+      <c r="L115" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M115" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="N115" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O115" s="5" t="inlineStr">
+        <is>
           <t>AllocSlice[]</t>
         </is>
       </c>
-      <c r="N115" s="5" t="inlineStr">
+      <c r="P115" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:226</t>
         </is>
@@ -5901,22 +7051,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K116" s="5" t="inlineStr">
+      <c r="K116" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="L116" s="5" t="inlineStr">
+      <c r="L116" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M116" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="N116" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O116" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="N116" s="5" t="inlineStr">
+      <c r="P116" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:215</t>
         </is>
@@ -5945,22 +7105,32 @@
           <t>buildPerformance</t>
         </is>
       </c>
-      <c r="K117" s="5" t="inlineStr">
+      <c r="K117" s="3" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="L117" s="5" t="inlineStr">
+      <c r="L117" s="3" t="inlineStr">
         <is>
           <t>buildPerformance</t>
         </is>
       </c>
       <c r="M117" s="5" t="inlineStr">
         <is>
+          <t>HoldingDetail, Performance</t>
+        </is>
+      </c>
+      <c r="N117" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance</t>
+        </is>
+      </c>
+      <c r="O117" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N117" s="5" t="inlineStr">
+      <c r="P117" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:149</t>
         </is>
@@ -5989,22 +7159,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K118" s="5" t="inlineStr">
+      <c r="K118" s="3" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="L118" s="5" t="inlineStr">
+      <c r="L118" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M118" s="5" t="inlineStr">
         <is>
+          <t>HoldingDetail, Performance</t>
+        </is>
+      </c>
+      <c r="N118" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O118" s="5" t="inlineStr">
+        <is>
           <t>PerformanceRow[]</t>
         </is>
       </c>
-      <c r="N118" s="5" t="inlineStr">
+      <c r="P118" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:173</t>
         </is>
@@ -6033,22 +7213,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K119" s="5" t="inlineStr">
+      <c r="K119" s="3" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="L119" s="5" t="inlineStr">
+      <c r="L119" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M119" s="5" t="inlineStr">
         <is>
+          <t>HoldingDetail, Performance</t>
+        </is>
+      </c>
+      <c r="N119" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O119" s="5" t="inlineStr">
+        <is>
           <t>CapGains</t>
         </is>
       </c>
-      <c r="N119" s="5" t="inlineStr">
+      <c r="P119" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:55</t>
         </is>
@@ -6077,22 +7267,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K120" s="5" t="inlineStr">
+      <c r="K120" s="3" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="L120" s="5" t="inlineStr">
+      <c r="L120" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M120" s="5" t="inlineStr">
         <is>
+          <t>HoldingDetail, Performance</t>
+        </is>
+      </c>
+      <c r="N120" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O120" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N120" s="5" t="inlineStr">
+      <c r="P120" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:69</t>
         </is>
@@ -6121,22 +7321,32 @@
           <t>buildPerformance, totalROI, unrealizedGain</t>
         </is>
       </c>
-      <c r="K121" s="5" t="inlineStr">
+      <c r="K121" s="3" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="L121" s="5" t="inlineStr">
+      <c r="L121" s="3" t="inlineStr">
         <is>
           <t>buildPerformance, totalROI, unrealizedGain</t>
         </is>
       </c>
       <c r="M121" s="5" t="inlineStr">
         <is>
+          <t>HoldingDetail, Performance</t>
+        </is>
+      </c>
+      <c r="N121" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance, totalROI, unrealizedGain</t>
+        </is>
+      </c>
+      <c r="O121" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N121" s="5" t="inlineStr">
+      <c r="P121" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:38</t>
         </is>
@@ -6165,22 +7375,32 @@
           <t>buildPerformance</t>
         </is>
       </c>
-      <c r="K122" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L122" s="5" t="inlineStr">
+      <c r="K122" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr">
         <is>
           <t>buildPerformance</t>
         </is>
       </c>
       <c r="M122" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N122" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance</t>
+        </is>
+      </c>
+      <c r="O122" s="5" t="inlineStr">
+        <is>
           <t>string | null</t>
         </is>
       </c>
-      <c r="N122" s="5" t="inlineStr">
+      <c r="P122" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:128</t>
         </is>
@@ -6209,22 +7429,32 @@
           <t>lookBack</t>
         </is>
       </c>
-      <c r="K123" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L123" s="5" t="inlineStr">
+      <c r="K123" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L123" s="3" t="inlineStr">
         <is>
           <t>lookBack</t>
         </is>
       </c>
       <c r="M123" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N123" s="5" t="inlineStr">
+        <is>
+          <t>lookBack</t>
+        </is>
+      </c>
+      <c r="O123" s="5" t="inlineStr">
+        <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="N123" s="5" t="inlineStr">
+      <c r="P123" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/lookBack.ts:19</t>
         </is>
@@ -6253,22 +7483,32 @@
           <t>moneyWeightedReturn</t>
         </is>
       </c>
-      <c r="K124" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L124" s="5" t="inlineStr">
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="inlineStr">
         <is>
           <t>moneyWeightedReturn</t>
         </is>
       </c>
       <c r="M124" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N124" s="5" t="inlineStr">
+        <is>
+          <t>moneyWeightedReturn</t>
+        </is>
+      </c>
+      <c r="O124" s="5" t="inlineStr">
+        <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="N124" s="5" t="inlineStr">
+      <c r="P124" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/moneyWeighted.ts:60</t>
         </is>
@@ -6297,22 +7537,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K125" s="5" t="inlineStr">
+      <c r="K125" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="L125" s="5" t="inlineStr">
+      <c r="L125" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M125" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="N125" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O125" s="5" t="inlineStr">
+        <is>
           <t>r is MoneyWeighted</t>
         </is>
       </c>
-      <c r="N125" s="5" t="inlineStr">
+      <c r="P125" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/moneyWeighted.ts:110</t>
         </is>
@@ -6341,22 +7591,32 @@
           <t>buildPerformance, periodReturn, periodReturnSince</t>
         </is>
       </c>
-      <c r="K126" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L126" s="5" t="inlineStr">
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr">
         <is>
           <t>buildPerformance, periodReturn, periodReturnSince</t>
         </is>
       </c>
       <c r="M126" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N126" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance, periodReturn, periodReturnSince</t>
+        </is>
+      </c>
+      <c r="O126" s="5" t="inlineStr">
+        <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="N126" s="5" t="inlineStr">
+      <c r="P126" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:102</t>
         </is>
@@ -6385,22 +7645,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K127" s="5" t="inlineStr">
+      <c r="K127" s="3" t="inlineStr">
         <is>
           <t>LookBack</t>
         </is>
       </c>
-      <c r="L127" s="5" t="inlineStr">
+      <c r="L127" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M127" s="5" t="inlineStr">
         <is>
+          <t>LookBack</t>
+        </is>
+      </c>
+      <c r="N127" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O127" s="5" t="inlineStr">
+        <is>
           <t>LookBackResult | null</t>
         </is>
       </c>
-      <c r="N127" s="5" t="inlineStr">
+      <c r="P127" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/lookBack.ts:32</t>
         </is>
@@ -6429,22 +7699,32 @@
           <t>buildPerformance, unrealizedGain</t>
         </is>
       </c>
-      <c r="K128" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L128" s="5" t="inlineStr">
+      <c r="K128" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr">
         <is>
           <t>buildPerformance, unrealizedGain</t>
         </is>
       </c>
       <c r="M128" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N128" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance, unrealizedGain</t>
+        </is>
+      </c>
+      <c r="O128" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N128" s="5" t="inlineStr">
+      <c r="P128" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:45</t>
         </is>
@@ -6473,22 +7753,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K129" s="5" t="inlineStr">
+      <c r="K129" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="L129" s="5" t="inlineStr">
+      <c r="L129" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M129" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="N129" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O129" s="5" t="inlineStr">
+        <is>
           <t>MoneyWeighted | MoneyWeightedMiss</t>
         </is>
       </c>
-      <c r="N129" s="5" t="inlineStr">
+      <c r="P129" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/moneyWeighted.ts:80</t>
         </is>
@@ -6541,22 +7831,32 @@
           <t>IT CANNOT ANSWER AN ARBITRARY WINDOW. Only 1M · 3M · 6M · YTD · 1Y · 3Y. That means a person can never line the app up against their own broker statement, which is the one comparison that would build trust. It should accept an explicit start and end date, with the named periods becoming presets over the same function.</t>
         </is>
       </c>
-      <c r="K130" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L130" s="5" t="inlineStr">
+      <c r="K130" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L130" s="3" t="inlineStr">
+        <is>
+          <t>Add periodReturnBetween(series, startISO, endISO) as the real function, and make the six named periods thin presets that call it. Low risk — the existing callers keep working — and it is what lets the founder put the app beside his own statement on the same dates.</t>
+        </is>
+      </c>
+      <c r="M130" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N130" s="5" t="inlineStr">
         <is>
           <t>buildPerformance</t>
         </is>
       </c>
-      <c r="M130" s="5" t="inlineStr">
+      <c r="O130" s="5" t="inlineStr">
         <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="N130" s="5" t="inlineStr">
+      <c r="P130" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:107</t>
         </is>
@@ -6585,22 +7885,32 @@
           <t>buildPerformance</t>
         </is>
       </c>
-      <c r="K131" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L131" s="5" t="inlineStr">
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
         <is>
           <t>buildPerformance</t>
         </is>
       </c>
       <c r="M131" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N131" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance</t>
+        </is>
+      </c>
+      <c r="O131" s="5" t="inlineStr">
+        <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="N131" s="5" t="inlineStr">
+      <c r="P131" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:119</t>
         </is>
@@ -6629,22 +7939,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K132" s="5" t="inlineStr">
+      <c r="K132" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="L132" s="5" t="inlineStr">
+      <c r="L132" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M132" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="N132" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O132" s="5" t="inlineStr">
+        <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="N132" s="5" t="inlineStr">
+      <c r="P132" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:275</t>
         </is>
@@ -6673,22 +7993,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K133" s="5" t="inlineStr">
+      <c r="K133" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="L133" s="5" t="inlineStr">
+      <c r="L133" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M133" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="N133" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O133" s="5" t="inlineStr">
+        <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="N133" s="5" t="inlineStr">
+      <c r="P133" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:265</t>
         </is>
@@ -6717,22 +8047,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K134" s="5" t="inlineStr">
+      <c r="K134" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="L134" s="5" t="inlineStr">
+      <c r="L134" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M134" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="N134" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O134" s="5" t="inlineStr">
+        <is>
           <t>TrendPoint[]</t>
         </is>
       </c>
-      <c r="N134" s="5" t="inlineStr">
+      <c r="P134" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:239</t>
         </is>
@@ -6761,22 +8101,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K135" s="5" t="inlineStr">
+      <c r="K135" s="3" t="inlineStr">
         <is>
           <t>HoldingDetail</t>
         </is>
       </c>
-      <c r="L135" s="5" t="inlineStr">
+      <c r="L135" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M135" s="5" t="inlineStr">
         <is>
+          <t>HoldingDetail</t>
+        </is>
+      </c>
+      <c r="N135" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O135" s="5" t="inlineStr">
+        <is>
           <t>RealizedResult</t>
         </is>
       </c>
-      <c r="N135" s="5" t="inlineStr">
+      <c r="P135" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/realized.ts:14</t>
         </is>
@@ -6805,22 +8155,32 @@
           <t>buildPerformance, periodReturn, portfolioTrend</t>
         </is>
       </c>
-      <c r="K136" s="5" t="inlineStr">
+      <c r="K136" s="3" t="inlineStr">
         <is>
           <t>HoldingDetail</t>
         </is>
       </c>
-      <c r="L136" s="5" t="inlineStr">
+      <c r="L136" s="3" t="inlineStr">
         <is>
           <t>buildPerformance, periodReturn, portfolioTrend</t>
         </is>
       </c>
       <c r="M136" s="5" t="inlineStr">
         <is>
+          <t>HoldingDetail</t>
+        </is>
+      </c>
+      <c r="N136" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance, periodReturn, portfolioTrend</t>
+        </is>
+      </c>
+      <c r="O136" s="5" t="inlineStr">
+        <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="N136" s="5" t="inlineStr">
+      <c r="P136" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:81</t>
         </is>
@@ -6849,22 +8209,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K137" s="5" t="inlineStr">
+      <c r="K137" s="3" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="L137" s="5" t="inlineStr">
+      <c r="L137" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M137" s="5" t="inlineStr">
         <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="N137" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O137" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="N137" s="5" t="inlineStr">
+      <c r="P137" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:205</t>
         </is>
@@ -6893,22 +8263,32 @@
           <t>buildPerformance</t>
         </is>
       </c>
-      <c r="K138" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L138" s="5" t="inlineStr">
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
         <is>
           <t>buildPerformance</t>
         </is>
       </c>
       <c r="M138" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N138" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance</t>
+        </is>
+      </c>
+      <c r="O138" s="5" t="inlineStr">
+        <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="N138" s="5" t="inlineStr">
+      <c r="P138" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:74</t>
         </is>
@@ -6937,22 +8317,32 @@
           <t>marketValue, portfolioTrend</t>
         </is>
       </c>
-      <c r="K139" s="5" t="inlineStr">
+      <c r="K139" s="3" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="L139" s="5" t="inlineStr">
+      <c r="L139" s="3" t="inlineStr">
         <is>
           <t>marketValue, portfolioTrend</t>
         </is>
       </c>
       <c r="M139" s="5" t="inlineStr">
         <is>
+          <t>HoldingDetail, Performance</t>
+        </is>
+      </c>
+      <c r="N139" s="5" t="inlineStr">
+        <is>
+          <t>marketValue, portfolioTrend</t>
+        </is>
+      </c>
+      <c r="O139" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N139" s="5" t="inlineStr">
+      <c r="P139" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:35</t>
         </is>
@@ -6981,22 +8371,32 @@
           <t>buildPerformance, totalROI</t>
         </is>
       </c>
-      <c r="K140" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L140" s="5" t="inlineStr">
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr">
         <is>
           <t>buildPerformance, totalROI</t>
         </is>
       </c>
       <c r="M140" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N140" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance, totalROI</t>
+        </is>
+      </c>
+      <c r="O140" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N140" s="5" t="inlineStr">
+      <c r="P140" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:49</t>
         </is>
@@ -7025,22 +8425,32 @@
           <t>moneyWeightedReturn</t>
         </is>
       </c>
-      <c r="K141" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L141" s="5" t="inlineStr">
+      <c r="K141" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L141" s="3" t="inlineStr">
         <is>
           <t>moneyWeightedReturn</t>
         </is>
       </c>
       <c r="M141" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N141" s="5" t="inlineStr">
+        <is>
+          <t>moneyWeightedReturn</t>
+        </is>
+      </c>
+      <c r="O141" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="N141" s="5" t="inlineStr">
+      <c r="P141" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/moneyWeighted.ts:27</t>
         </is>
@@ -7069,22 +8479,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K142" s="5" t="inlineStr">
+      <c r="K142" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L142" s="5" t="inlineStr">
+      <c r="L142" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M142" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N142" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O142" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N142" s="5" t="inlineStr">
+      <c r="P142" s="5" t="inlineStr">
         <is>
           <t>src/domain/planning/hub.ts:30</t>
         </is>
@@ -7113,22 +8533,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K143" s="5" t="inlineStr">
+      <c r="K143" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L143" s="5" t="inlineStr">
+      <c r="L143" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M143" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N143" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O143" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="N143" s="5" t="inlineStr">
+      <c r="P143" s="5" t="inlineStr">
         <is>
           <t>src/domain/planning/hub.ts:165</t>
         </is>
@@ -7157,22 +8587,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K144" s="5" t="inlineStr">
+      <c r="K144" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L144" s="5" t="inlineStr">
+      <c r="L144" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M144" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N144" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O144" s="5" t="inlineStr">
+        <is>
           <t>PlanDoor</t>
         </is>
       </c>
-      <c r="N144" s="5" t="inlineStr">
+      <c r="P144" s="5" t="inlineStr">
         <is>
           <t>src/domain/planning/hub.ts:44</t>
         </is>
@@ -7201,22 +8641,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K145" s="5" t="inlineStr">
+      <c r="K145" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L145" s="5" t="inlineStr">
+      <c r="L145" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M145" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N145" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O145" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N145" s="5" t="inlineStr">
+      <c r="P145" s="5" t="inlineStr">
         <is>
           <t>src/domain/planning/hub.ts:152</t>
         </is>
@@ -7245,22 +8695,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K146" s="5" t="inlineStr">
+      <c r="K146" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L146" s="5" t="inlineStr">
+      <c r="L146" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M146" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N146" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O146" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N146" s="5" t="inlineStr">
+      <c r="P146" s="5" t="inlineStr">
         <is>
           <t>src/domain/planning/hub.ts:34</t>
         </is>
@@ -7289,22 +8749,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K147" s="5" t="inlineStr">
+      <c r="K147" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L147" s="5" t="inlineStr">
+      <c r="L147" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M147" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N147" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O147" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="N147" s="5" t="inlineStr">
+      <c r="P147" s="5" t="inlineStr">
         <is>
           <t>src/domain/planning/hub.ts:162</t>
         </is>
@@ -7333,22 +8803,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K148" s="5" t="inlineStr">
+      <c r="K148" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L148" s="5" t="inlineStr">
+      <c r="L148" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M148" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N148" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O148" s="5" t="inlineStr">
+        <is>
           <t>Lens</t>
         </is>
       </c>
-      <c r="N148" s="5" t="inlineStr">
+      <c r="P148" s="5" t="inlineStr">
         <is>
           <t>src/domain/profile/lens.ts:17</t>
         </is>
@@ -7377,22 +8857,32 @@
           <t>retirementSpendMonthly</t>
         </is>
       </c>
-      <c r="K149" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L149" s="5" t="inlineStr">
+      <c r="K149" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L149" s="3" t="inlineStr">
         <is>
           <t>retirementSpendMonthly</t>
         </is>
       </c>
       <c r="M149" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N149" s="5" t="inlineStr">
+        <is>
+          <t>retirementSpendMonthly</t>
+        </is>
+      </c>
+      <c r="O149" s="5" t="inlineStr">
+        <is>
           <t>ColMatch</t>
         </is>
       </c>
-      <c r="N149" s="5" t="inlineStr">
+      <c r="P149" s="5" t="inlineStr">
         <is>
           <t>src/domain/retirement/col.ts:53</t>
         </is>
@@ -7421,22 +8911,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K150" s="5" t="inlineStr">
+      <c r="K150" s="3" t="inlineStr">
         <is>
           <t>NetWorth, WhatIf</t>
         </is>
       </c>
-      <c r="L150" s="5" t="inlineStr">
+      <c r="L150" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M150" s="5" t="inlineStr">
         <is>
+          <t>NetWorth, WhatIf</t>
+        </is>
+      </c>
+      <c r="N150" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O150" s="5" t="inlineStr">
+        <is>
           <t>NestEggProjection</t>
         </is>
       </c>
-      <c r="N150" s="5" t="inlineStr">
+      <c r="P150" s="5" t="inlineStr">
         <is>
           <t>src/domain/retirement/index.ts:294</t>
         </is>
@@ -7465,22 +8965,32 @@
           <t>selectWillItLast, willItLastInputs</t>
         </is>
       </c>
-      <c r="K151" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L151" s="5" t="inlineStr">
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L151" s="3" t="inlineStr">
         <is>
           <t>selectWillItLast, willItLastInputs</t>
         </is>
       </c>
       <c r="M151" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N151" s="5" t="inlineStr">
+        <is>
+          <t>selectWillItLast, willItLastInputs</t>
+        </is>
+      </c>
+      <c r="O151" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N151" s="5" t="inlineStr">
+      <c r="P151" s="5" t="inlineStr">
         <is>
           <t>src/domain/retirement/index.ts:48</t>
         </is>
@@ -7509,22 +9019,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K152" s="5" t="inlineStr">
+      <c r="K152" s="3" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="L152" s="5" t="inlineStr">
+      <c r="L152" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M152" s="5" t="inlineStr">
         <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N152" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O152" s="5" t="inlineStr">
+        <is>
           <t>WillItLastResult</t>
         </is>
       </c>
-      <c r="N152" s="5" t="inlineStr">
+      <c r="P152" s="5" t="inlineStr">
         <is>
           <t>src/domain/retirement/willItLast.ts:115</t>
         </is>
@@ -7553,22 +9073,32 @@
           <t>selectWillItLast</t>
         </is>
       </c>
-      <c r="K153" s="5" t="inlineStr">
+      <c r="K153" s="3" t="inlineStr">
         <is>
           <t>NetWorth, WhatIf</t>
         </is>
       </c>
-      <c r="L153" s="5" t="inlineStr">
+      <c r="L153" s="3" t="inlineStr">
         <is>
           <t>selectWillItLast</t>
         </is>
       </c>
       <c r="M153" s="5" t="inlineStr">
         <is>
+          <t>NetWorth, WhatIf</t>
+        </is>
+      </c>
+      <c r="N153" s="5" t="inlineStr">
+        <is>
+          <t>selectWillItLast</t>
+        </is>
+      </c>
+      <c r="O153" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="N153" s="5" t="inlineStr">
+      <c r="P153" s="5" t="inlineStr">
         <is>
           <t>src/domain/retirement/index.ts:160</t>
         </is>
@@ -7597,22 +9127,32 @@
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="K154" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L154" s="5" t="inlineStr">
+      <c r="K154" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L154" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="M154" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N154" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="O154" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N154" s="5" t="inlineStr">
+      <c r="P154" s="5" t="inlineStr">
         <is>
           <t>src/domain/retirement/ssTiming.ts:25</t>
         </is>
@@ -7641,22 +9181,32 @@
           <t>ssBenefitAtClaimAge</t>
         </is>
       </c>
-      <c r="K155" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L155" s="5" t="inlineStr">
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L155" s="3" t="inlineStr">
         <is>
           <t>ssBenefitAtClaimAge</t>
         </is>
       </c>
       <c r="M155" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N155" s="5" t="inlineStr">
+        <is>
+          <t>ssBenefitAtClaimAge</t>
+        </is>
+      </c>
+      <c r="O155" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N155" s="5" t="inlineStr">
+      <c r="P155" s="5" t="inlineStr">
         <is>
           <t>src/domain/retirement/ssTiming.ts:12</t>
         </is>
@@ -7685,22 +9235,32 @@
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="K156" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L156" s="5" t="inlineStr">
+      <c r="K156" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L156" s="3" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
       <c r="M156" s="5" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N156" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="O156" s="5" t="inlineStr">
+        <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="N156" s="5" t="inlineStr">
+      <c r="P156" s="5" t="inlineStr">
         <is>
           <t>src/domain/retirement/willItLast.ts:19</t>
         </is>
@@ -7729,22 +9289,32 @@
           <t>selectWillItLast</t>
         </is>
       </c>
-      <c r="K157" s="5" t="inlineStr">
+      <c r="K157" s="3" t="inlineStr">
         <is>
           <t>NetWorth, WhatIf</t>
         </is>
       </c>
-      <c r="L157" s="5" t="inlineStr">
+      <c r="L157" s="3" t="inlineStr">
         <is>
           <t>selectWillItLast</t>
         </is>
       </c>
       <c r="M157" s="5" t="inlineStr">
         <is>
+          <t>NetWorth, WhatIf</t>
+        </is>
+      </c>
+      <c r="N157" s="5" t="inlineStr">
+        <is>
+          <t>selectWillItLast</t>
+        </is>
+      </c>
+      <c r="O157" s="5" t="inlineStr">
+        <is>
           <t>RetirementInputs | null</t>
         </is>
       </c>
-      <c r="N157" s="5" t="inlineStr">
+      <c r="P157" s="5" t="inlineStr">
         <is>
           <t>src/domain/retirement/willItLast.ts:47</t>
         </is>
@@ -7773,22 +9343,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K158" s="5" t="inlineStr">
+      <c r="K158" s="3" t="inlineStr">
         <is>
           <t>Performance, WhatIf</t>
         </is>
       </c>
-      <c r="L158" s="5" t="inlineStr">
+      <c r="L158" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M158" s="5" t="inlineStr">
         <is>
+          <t>Performance, WhatIf</t>
+        </is>
+      </c>
+      <c r="N158" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O158" s="5" t="inlineStr">
+        <is>
           <t>NetWorthRows</t>
         </is>
       </c>
-      <c r="N158" s="5" t="inlineStr">
+      <c r="P158" s="5" t="inlineStr">
         <is>
           <t>src/domain/snapshot.ts:121</t>
         </is>
@@ -7817,22 +9397,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K159" s="5" t="inlineStr">
+      <c r="K159" s="3" t="inlineStr">
         <is>
           <t>AccountDetail, Performance</t>
         </is>
       </c>
-      <c r="L159" s="5" t="inlineStr">
+      <c r="L159" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M159" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail, Performance</t>
+        </is>
+      </c>
+      <c r="N159" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O159" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N159" s="5" t="inlineStr">
+      <c r="P159" s="5" t="inlineStr">
         <is>
           <t>src/domain/transactions/index.ts:227</t>
         </is>
@@ -7861,22 +9451,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K160" s="5" t="inlineStr">
+      <c r="K160" s="3" t="inlineStr">
         <is>
           <t>AccountDetail, Performance</t>
         </is>
       </c>
-      <c r="L160" s="5" t="inlineStr">
+      <c r="L160" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M160" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail, Performance</t>
+        </is>
+      </c>
+      <c r="N160" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O160" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N160" s="5" t="inlineStr">
+      <c r="P160" s="5" t="inlineStr">
         <is>
           <t>src/domain/transactions/index.ts:224</t>
         </is>
@@ -7884,7 +9484,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:P1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -7898,7 +9498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7911,10 +9511,12 @@
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="52" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="52" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="46" customHeight="1">
@@ -7977,20 +9579,30 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
+          <t>Fix needed?</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>RECOMMENDED FIX</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
           <t>Screens</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Called by</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Returns</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -8019,22 +9631,32 @@
           <t>formatMoney, formatMoneyCents, moneyCompact</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>AccountDetail, Itemize, LookBack, NetWorth</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>formatMoney, formatMoneyCents, moneyCompact</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
+          <t>AccountDetail, Itemize, LookBack, NetWorth</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>formatMoney, formatMoneyCents, moneyCompact</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>src/domain/_shared/money.ts:52</t>
         </is>
@@ -8063,22 +9685,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>HoldingDetail, Itemize, NetWorth, Performance</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
+          <t>HoldingDetail, Itemize, NetWorth, Performance</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>src/domain/_shared/num.ts:9</t>
         </is>
@@ -8107,22 +9739,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>ImportHoldings, Performance</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
+          <t>ImportHoldings, Performance</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>src/domain/_shared/num.ts:11</t>
         </is>
@@ -8151,22 +9793,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>NetWorth, Performance</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
+          <t>NetWorth, Performance</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>src/domain/_shared/money.ts:88</t>
         </is>
@@ -8195,22 +9847,32 @@
           <t>accountClassBreakdown, actualDebtPayment, allocation, annualCoupon, assetAllocation, buildAssetsState, buildDebtState, buildItemizedAccounts, buildNetWorth, capGains, capGainsTax, cashTotal, costBasis, earmarkedAmount, itemizeRemainder, itemizedTotal, lookBack, marketValue, minimumDebtService, normalizeSnapshot, planDoor, projectNestEgg, retirementEarmarkedValue, retirementSpendMonthly, salaryGrossByMonth, simulate, taxBucketSplit, trendPoints, unrealizedGain</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>ImportHoldings</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>accountClassBreakdown, actualDebtPayment, allocation, annualCoupon, assetAllocation, buildAssetsState, buildDebtState, buildItemizedAccounts, buildNetWorth, capGains, capGainsTax, cashTotal, costBasis, earmarkedAmount, itemizeRemainder, itemizedTotal, lookBack, marketValue, minimumDebtService, normalizeSnapshot, planDoor, projectNestEgg, retirementEarmarkedValue, retirementSpendMonthly, salaryGrossByMonth, simulate, taxBucketSplit, trendPoints, unrealizedGain</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
+          <t>ImportHoldings</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>accountClassBreakdown, actualDebtPayment, allocation, annualCoupon, assetAllocation, buildAssetsState, buildDebtState, buildItemizedAccounts, buildNetWorth, capGains, capGainsTax, cashTotal, costBasis, earmarkedAmount, itemizeRemainder, itemizedTotal, lookBack, marketValue, minimumDebtService, normalizeSnapshot, planDoor, projectNestEgg, retirementEarmarkedValue, retirementSpendMonthly, salaryGrossByMonth, simulate, taxBucketSplit, trendPoints, unrealizedGain</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
           <t>number</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>src/domain/_shared/num.ts:12</t>
         </is>
@@ -8218,7 +9880,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:P1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -7191,161 +7191,221 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="inlineStr"/>
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>HOLDING_CAP_GAINS</t>
+        </is>
+      </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
           <t>capGains</t>
         </is>
       </c>
-      <c r="C119" s="3" t="inlineStr"/>
-      <c r="D119" s="3" t="inlineStr"/>
-      <c r="E119" s="3" t="inlineStr"/>
-      <c r="F119" s="3" t="inlineStr"/>
-      <c r="G119" s="3" t="inlineStr"/>
-      <c r="H119" s="3" t="inlineStr"/>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>If I sold today, how much of my gain is long-term?</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>per lot: shares × (price − cost_per_share); long if held ≥ 12 whole months, else short</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>lots (shares, cost, purchase date) · price · today</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>lots from the broker or manual entry; price from market data</t>
+        </is>
+      </c>
+      <c r="G119" s="3" t="inlineStr">
+        <is>
+          <t>Judged PER LOT from its own purchase date, never per position — the same holding can be part long and part short. Lots with no cost basis are SKIPPED rather than treated as free shares, which would report the whole value as gain. An unparseable date is treated as SHORT-term, the cautious side, because understating a tax bill is the worse error.</t>
+        </is>
+      </c>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-lot-math.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J119" s="3" t="inlineStr"/>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr"/>
+      <c r="M119" s="5" t="inlineStr">
+        <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K119" s="3" t="inlineStr">
+      <c r="N119" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O119" s="5" t="inlineStr">
+        <is>
+          <t>CapGains</t>
+        </is>
+      </c>
+      <c r="P119" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>CAP_GAINS_TAX</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>capGainsTax</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>Roughly what tax would a sale cost?</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>max(0,long)×ltRate + max(0,short)×ordinaryRate</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>long gain · short gain · long-term rate (default 15%) · ordinary rate (default 24%)</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>gains derived; rates from the user's own tax settings where set</t>
+        </is>
+      </c>
+      <c r="G120" s="3" t="inlineStr">
+        <is>
+          <t>Losses never create a positive tax bill — each side is floored at zero independently, so a long loss cannot offset a short gain here. It is an estimate of a sale today, not a tax return.</t>
+        </is>
+      </c>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-lot-math.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J120" s="3" t="inlineStr"/>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L120" s="3" t="inlineStr"/>
+      <c r="M120" s="5" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="L119" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M119" s="5" t="inlineStr">
+      <c r="N120" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O120" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="P120" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/performance/index.ts:69</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>HOLDING_COST_BASIS</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>costBasis</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>What did I pay for this holding?</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>Σ over lots of (shares × cost_per_share), to the cent</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>the position's lots</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>same as shares</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>Lots with no cost contribute zero to basis but still count toward shares — you own them either way. Rounded to the cent at the total, not per lot.</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-lot-math.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J121" s="3" t="inlineStr"/>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L121" s="3" t="inlineStr"/>
+      <c r="M121" s="5" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="N119" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O119" s="5" t="inlineStr">
-        <is>
-          <t>CapGains</t>
-        </is>
-      </c>
-      <c r="P119" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/performance/index.ts:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr"/>
-      <c r="B120" s="4" t="inlineStr">
-        <is>
-          <t>capGainsTax</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr"/>
-      <c r="D120" s="3" t="inlineStr"/>
-      <c r="E120" s="3" t="inlineStr"/>
-      <c r="F120" s="3" t="inlineStr"/>
-      <c r="G120" s="3" t="inlineStr"/>
-      <c r="H120" s="3" t="inlineStr"/>
-      <c r="I120" s="3" t="inlineStr">
-        <is>
-          <t>HoldingDetail, Performance</t>
-        </is>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K120" s="3" t="inlineStr">
-        <is>
-          <t>HoldingDetail, Performance</t>
-        </is>
-      </c>
-      <c r="L120" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M120" s="5" t="inlineStr">
-        <is>
-          <t>HoldingDetail, Performance</t>
-        </is>
-      </c>
-      <c r="N120" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O120" s="5" t="inlineStr">
+      <c r="N121" s="5" t="inlineStr">
+        <is>
+          <t>buildPerformance, totalROI, unrealizedGain</t>
+        </is>
+      </c>
+      <c r="O121" s="5" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P120" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/performance/index.ts:69</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="inlineStr"/>
-      <c r="B121" s="4" t="inlineStr">
-        <is>
-          <t>costBasis</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="inlineStr"/>
-      <c r="D121" s="3" t="inlineStr"/>
-      <c r="E121" s="3" t="inlineStr"/>
-      <c r="F121" s="3" t="inlineStr"/>
-      <c r="G121" s="3" t="inlineStr"/>
-      <c r="H121" s="3" t="inlineStr"/>
-      <c r="I121" s="3" t="inlineStr">
-        <is>
-          <t>HoldingDetail, Performance</t>
-        </is>
-      </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>buildPerformance, totalROI, unrealizedGain</t>
-        </is>
-      </c>
-      <c r="K121" s="3" t="inlineStr">
-        <is>
-          <t>HoldingDetail, Performance</t>
-        </is>
-      </c>
-      <c r="L121" s="3" t="inlineStr">
-        <is>
-          <t>buildPerformance, totalROI, unrealizedGain</t>
-        </is>
-      </c>
-      <c r="M121" s="5" t="inlineStr">
-        <is>
-          <t>HoldingDetail, Performance</t>
-        </is>
-      </c>
-      <c r="N121" s="5" t="inlineStr">
-        <is>
-          <t>buildPerformance, totalROI, unrealizedGain</t>
-        </is>
-      </c>
-      <c r="O121" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
       <c r="P121" s="5" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:38</t>
@@ -7353,38 +7413,58 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="inlineStr"/>
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>HOLDING_FIRST_BOUGHT</t>
+        </is>
+      </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
           <t>earliestPurchaseDate</t>
         </is>
       </c>
-      <c r="C122" s="3" t="inlineStr"/>
-      <c r="D122" s="3" t="inlineStr"/>
-      <c r="E122" s="3" t="inlineStr"/>
-      <c r="F122" s="3" t="inlineStr"/>
-      <c r="G122" s="3" t="inlineStr"/>
-      <c r="H122" s="3" t="inlineStr"/>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>When did I first buy this?</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>the oldest dated lot</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>the position's lots</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>lots</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>Undated lots are ignored rather than treated as today, which would make a long-held position look new and flip its tax treatment.</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-lot-math.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I122" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>buildPerformance</t>
-        </is>
-      </c>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J122" s="3" t="inlineStr"/>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L122" s="3" t="inlineStr">
-        <is>
-          <t>buildPerformance</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L122" s="3" t="inlineStr"/>
       <c r="M122" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -7569,38 +7649,58 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="inlineStr"/>
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>PRICE_LATEST</t>
+        </is>
+      </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
           <t>latestClose</t>
         </is>
       </c>
-      <c r="C126" s="3" t="inlineStr"/>
-      <c r="D126" s="3" t="inlineStr"/>
-      <c r="E126" s="3" t="inlineStr"/>
-      <c r="F126" s="3" t="inlineStr"/>
-      <c r="G126" s="3" t="inlineStr"/>
-      <c r="H126" s="3" t="inlineStr"/>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>What is the most recent price we have?</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>the last point in the series</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>price series</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>market-data service</t>
+        </is>
+      </c>
+      <c r="G126" s="3" t="inlineStr">
+        <is>
+          <t>An empty series returns null, never zero. "No price" and "worth nothing" are different answers and must not share a value.</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-lot-math.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I126" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>buildPerformance, periodReturn, periodReturnSince</t>
-        </is>
-      </c>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J126" s="3" t="inlineStr"/>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L126" s="3" t="inlineStr">
-        <is>
-          <t>buildPerformance, periodReturn, periodReturnSince</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="inlineStr"/>
       <c r="M126" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -7677,38 +7777,58 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="inlineStr"/>
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>HOLDING_MARKET_VALUE</t>
+        </is>
+      </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
           <t>marketValue</t>
         </is>
       </c>
-      <c r="C128" s="3" t="inlineStr"/>
-      <c r="D128" s="3" t="inlineStr"/>
-      <c r="E128" s="3" t="inlineStr"/>
-      <c r="F128" s="3" t="inlineStr"/>
-      <c r="G128" s="3" t="inlineStr"/>
-      <c r="H128" s="3" t="inlineStr"/>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>What is this holding worth today?</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>total shares × latest price</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>total shares · latest close</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="inlineStr">
+        <is>
+          <t>price series from the market-data service</t>
+        </is>
+      </c>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>NO PRICE MEANS ZERO, NOT A GUESS. An unpriced holding contributes nothing rather than falling back to what it cost — the screen says the price is missing instead of inventing one.</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-lot-math.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I128" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>buildPerformance, unrealizedGain</t>
-        </is>
-      </c>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J128" s="3" t="inlineStr"/>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L128" s="3" t="inlineStr">
-        <is>
-          <t>buildPerformance, unrealizedGain</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L128" s="3" t="inlineStr"/>
       <c r="M128" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -8133,38 +8253,58 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="inlineStr"/>
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>PERIOD_START_DATE</t>
+        </is>
+      </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
           <t>startDateFor</t>
         </is>
       </c>
-      <c r="C136" s="3" t="inlineStr"/>
-      <c r="D136" s="3" t="inlineStr"/>
-      <c r="E136" s="3" t="inlineStr"/>
-      <c r="F136" s="3" t="inlineStr"/>
-      <c r="G136" s="3" t="inlineStr"/>
-      <c r="H136" s="3" t="inlineStr"/>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>What date does the chosen window begin?</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>1M/3M/6M subtract months · 1Y/3Y subtract years · YTD = 1 January of the current year</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>named period · today</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>the chips on Performance</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>YTD is calendar year-to-date, not trailing twelve months.</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-lot-math.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>HoldingDetail</t>
-        </is>
-      </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>buildPerformance, periodReturn, portfolioTrend</t>
-        </is>
-      </c>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J136" s="3" t="inlineStr"/>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>HoldingDetail</t>
-        </is>
-      </c>
-      <c r="L136" s="3" t="inlineStr">
-        <is>
-          <t>buildPerformance, periodReturn, portfolioTrend</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr"/>
       <c r="M136" s="5" t="inlineStr">
         <is>
           <t>HoldingDetail</t>
@@ -8241,48 +8381,72 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="inlineStr"/>
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>HOLDING_TOTAL_ROI</t>
+        </is>
+      </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
           <t>totalROI</t>
         </is>
       </c>
-      <c r="C138" s="3" t="inlineStr"/>
-      <c r="D138" s="3" t="inlineStr"/>
-      <c r="E138" s="3" t="inlineStr"/>
-      <c r="F138" s="3" t="inlineStr"/>
-      <c r="G138" s="3" t="inlineStr"/>
-      <c r="H138" s="3" t="inlineStr"/>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>How has this holding done since I bought it?</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>unrealised gain ÷ cost basis</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>unrealised gain · cost basis</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>SINCE PURCHASE, not annualised, and NOT comparable to a period return — a five-year 50% is not a yearly 50%. A zero basis returns null rather than infinity.</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-lot-math.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I138" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J138" s="3" t="inlineStr">
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J138" s="3" t="inlineStr"/>
+      <c r="K138" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L138" s="3" t="inlineStr">
+        <is>
+          <t>Not a defect, but the screen must never place this beside a period return without saying they measure different things.</t>
+        </is>
+      </c>
+      <c r="M138" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N138" s="5" t="inlineStr">
         <is>
           <t>buildPerformance</t>
         </is>
       </c>
-      <c r="K138" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L138" s="3" t="inlineStr">
-        <is>
-          <t>buildPerformance</t>
-        </is>
-      </c>
-      <c r="M138" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N138" s="5" t="inlineStr">
-        <is>
-          <t>buildPerformance</t>
-        </is>
-      </c>
       <c r="O138" s="5" t="inlineStr">
         <is>
           <t>number | null</t>
@@ -8295,48 +8459,68 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="inlineStr"/>
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>HOLDING_SHARES</t>
+        </is>
+      </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
           <t>totalShares</t>
         </is>
       </c>
-      <c r="C139" s="3" t="inlineStr"/>
-      <c r="D139" s="3" t="inlineStr"/>
-      <c r="E139" s="3" t="inlineStr"/>
-      <c r="F139" s="3" t="inlineStr"/>
-      <c r="G139" s="3" t="inlineStr"/>
-      <c r="H139" s="3" t="inlineStr"/>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>How many shares do I hold?</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>Σ over lots of lot.shares</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>the position's lots</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>broker payload, file import, or manual entry</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>A position is the SUM OF ITS LOTS, never a single stored number. A broker sending no lots gets ONE synthetic lot built from the average price, so gain-since-purchase stays exact even with no purchase history.</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-lot-math.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I139" s="3" t="inlineStr">
         <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J139" s="3" t="inlineStr"/>
+      <c r="K139" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L139" s="3" t="inlineStr"/>
+      <c r="M139" s="5" t="inlineStr">
+        <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="J139" s="3" t="inlineStr">
+      <c r="N139" s="5" t="inlineStr">
         <is>
           <t>marketValue, portfolioTrend</t>
         </is>
       </c>
-      <c r="K139" s="3" t="inlineStr">
-        <is>
-          <t>HoldingDetail, Performance</t>
-        </is>
-      </c>
-      <c r="L139" s="3" t="inlineStr">
-        <is>
-          <t>marketValue, portfolioTrend</t>
-        </is>
-      </c>
-      <c r="M139" s="5" t="inlineStr">
-        <is>
-          <t>HoldingDetail, Performance</t>
-        </is>
-      </c>
-      <c r="N139" s="5" t="inlineStr">
-        <is>
-          <t>marketValue, portfolioTrend</t>
-        </is>
-      </c>
       <c r="O139" s="5" t="inlineStr">
         <is>
           <t>number</t>
@@ -8349,38 +8533,58 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="inlineStr"/>
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>HOLDING_UNREALISED_GAIN</t>
+        </is>
+      </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
           <t>unrealizedGain</t>
         </is>
       </c>
-      <c r="C140" s="3" t="inlineStr"/>
-      <c r="D140" s="3" t="inlineStr"/>
-      <c r="E140" s="3" t="inlineStr"/>
-      <c r="F140" s="3" t="inlineStr"/>
-      <c r="G140" s="3" t="inlineStr"/>
-      <c r="H140" s="3" t="inlineStr"/>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>How much am I up or down on this holding?</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>market value − cost basis</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>market value · cost basis</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>A loss is a real negative and is never floored. No price returns zero rather than showing the full basis as a loss.</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-lot-math.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I140" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>buildPerformance, totalROI</t>
-        </is>
-      </c>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J140" s="3" t="inlineStr"/>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L140" s="3" t="inlineStr">
-        <is>
-          <t>buildPerformance, totalROI</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L140" s="3" t="inlineStr"/>
       <c r="M140" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -9953,7 +10157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9991,6 +10195,66 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Where do $1,462,462 of "contributions" come from, when Vanguard says $0 moved all year?</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>It is the single largest wrong number found. Until it is traced, the Performance walk cannot be trusted on any account.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RULED OUT SO FAR, each by probe or by reading the code: the activity mapping table is correct (BUY stays BUY; only CONTRIBUTION becomes a deposit) · option trades stay internal · dedupe persists across syncs via snaptradeSeenKeys and is keyed by account · nothing in the connect flow creates OPENING_CASH or OPENING_POSITION rows. STILL OPEN — needs the founder's actual transaction ledger to settle. Prime remaining suspect: if an account's internal id changes between connections, every activity key changes with it and the whole history re-ingests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Money-market funds: shown as a holding, or folded into the cash sleeve? Both currently happen.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>For a broker that flags the fund, the money is subtracted from cash AND dropped from holdings — it is in neither place.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Recommend showing it as a holding and keeping the netting, per the 2026-08-04 cash-means-cash rule. Founder decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Should Performance be able to answer an arbitrary date range?</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Today it offers only 1M/3M/6M/YTD/1Y/3Y, so the app can never be lined up against a broker statement, which is the one comparison that would build trust.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Recommend yes — add a start/end function and make the named periods presets over it.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -1269,43 +1269,63 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>ALLOCATION_BY_CLASS</t>
+        </is>
+      </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
           <t>assetAllocation</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>How is my money split across classes?</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Σ balances grouped by class</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>every account · its class</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>accounts</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Sums exactly to total assets, so the donut can never leak or double-count.</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-classification.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="5" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -1323,38 +1343,58 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr"/>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>ACCOUNT_CLASS</t>
+        </is>
+      </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
           <t>assetClassOf</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Which asset class does this account belong to?</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>first match wins: explicit class → label rule → maturity date → kind → positions present → tax bucket → "mixed"</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>asset_class · label · maturity_date · kind · positions · tax_bucket</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>the account record</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>THE ORDER IS THE RULE. A person's own answer is never overridden. A wrapper whose contents are unknown becomes "mixed", never pretended to be stocks, so the allocation stays honest.</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-classification.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>AccountDetail, NetWorth, Performance</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>accountAllowsTicker, accountClassBreakdown, assetAllocation, cashTotal, earmarkDefault, investmentsTotal, isBond, isRealAsset, primaryCarIdOf</t>
-        </is>
-      </c>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>AccountDetail, NetWorth, Performance</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>accountAllowsTicker, accountClassBreakdown, assetAllocation, cashTotal, earmarkDefault, investmentsTotal, isBond, isRealAsset, primaryCarIdOf</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr"/>
       <c r="M13" s="5" t="inlineStr">
         <is>
           <t>AccountDetail, NetWorth, Performance</t>
@@ -1485,107 +1525,151 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr"/>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>EXPECTED_RETURN_BY_KIND</t>
+        </is>
+      </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
           <t>benchmarkReturn</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>What return do we expect from this kind of holding?</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>a user override if set, else the ASSET_KINDS default</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>kind · user overrides</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>ASSET_KINDS table; overrides from settings</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Long-run figures per class, all stated in the glossary so a person can see what the projection assumes.</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-classification.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
           <t>AccountDetail, Performance</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>blendedReturn</t>
         </is>
       </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>AccountDetail, Performance</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts:569</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>EXPECTED_RETURN_BLENDED</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>blendedReturn</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
-        <is>
-          <t>AccountDetail, Performance</t>
-        </is>
-      </c>
-      <c r="N16" s="5" t="inlineStr">
-        <is>
-          <t>blendedReturn</t>
-        </is>
-      </c>
-      <c r="O16" s="5" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>What return does MY mix expect?</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Σ(balance × kind return) ÷ Σ balance</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>every account balance · each kind's expected return</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>accounts and the ASSET_KINDS table</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>THE MIX DECIDES THE NUMBER, which is why a persona or a plan must state its holdings: growth-heavy accounts and cash-heavy accounts differ by several points a year, and every odds figure moves with it. No accounts falls back to a stated default rather than zero.</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-classification.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Not a defect, but it must never be hidden: any screen or document quoting odds should be able to show the return behind them, because the same balance at 5.85% and 8.65% gives completely different answers.</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>willItLastInputs</t>
+        </is>
+      </c>
+      <c r="O17" s="5" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P16" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/assets/index.ts:569</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>blendedReturn</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr"/>
-      <c r="D17" s="3" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
-      <c r="O17" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
       <c r="P17" s="5" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:653</t>
@@ -1593,38 +1677,58 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>EXPECTED_SWING_BLENDED</t>
+        </is>
+      </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
           <t>blendedVolatility</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>How much does my mix typically swing?</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Σ(balance × kind volatility) ÷ Σ balance</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>every account balance · each kind's volatility</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>accounts and the ASSET_KINDS table</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>The swing is what makes the 400 simulated futures differ from one another — without it every future would be identical.</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-classification.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr"/>
       <c r="M18" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -1755,38 +1859,58 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr"/>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL_CASH</t>
+        </is>
+      </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
           <t>cashTotal</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>How much cash do I hold?</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Σ over accounts of the cash slice, or the whole balance if the account is cash</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>every account · its class breakdown</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>accounts</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>An account holding several classes is SPLIT by its own breakdown rather than counted whole in one bucket.</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-classification.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr"/>
       <c r="M21" s="5" t="inlineStr">
         <is>
           <t>NetWorth</t>
@@ -1863,313 +1987,441 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>EARMARK_DEFAULT</t>
+        </is>
+      </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
           <t>earmarkDefault</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Does this account count toward retirement by default?</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>0 for a 529, the primary home and the car you drive; 100 otherwise</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>kind · class · real-estate use · primary car id</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>the account record</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Everything counts EXCEPT the home you live in, the car you drive and a 529. The default is only a default — a saved percentage always wins.</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-classification.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>earmarkedAmount</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="O23" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts:543</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>EARMARK_AMOUNT</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>earmarkedAmount</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="5" t="inlineStr">
-        <is>
-          <t>earmarkedAmount</t>
-        </is>
-      </c>
-      <c r="O23" s="5" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>How much of this account is earmarked for retirement?</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>balance × clamp(saved % or default, 0, 100) ÷ 100</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>balance · saved percentage · default</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>the account record</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>The saved percentage always beats the default, and is clamped to 0-100 so a bad value cannot exceed the balance or go negative.</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-classification.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr"/>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>blendedReturn, blendedVolatility, portfolioActualReturn, retirementEarmarkedValue, taxBucketSplit</t>
+        </is>
+      </c>
+      <c r="O24" s="5" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P23" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/assets/index.ts:543</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr"/>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>earmarkedAmount</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr"/>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>blendedReturn, blendedVolatility, portfolioActualReturn, retirementEarmarkedValue, taxBucketSplit</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>blendedReturn, blendedVolatility, portfolioActualReturn, retirementEarmarkedValue, taxBucketSplit</t>
-        </is>
-      </c>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N24" s="5" t="inlineStr">
-        <is>
-          <t>blendedReturn, blendedVolatility, portfolioActualReturn, retirementEarmarkedValue, taxBucketSplit</t>
-        </is>
-      </c>
-      <c r="O24" s="5" t="inlineStr">
+      <c r="P24" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts:558</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>INCOME_BEARING_CLASS</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>incomeBearingClassOf</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Is this cash, or something that pays income?</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>sweep/settlement → cash · money-market by name OR ticker → stocks_etf · CD/T-bill → bonds · else null</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>the account or holding label</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>label from the broker, an import, or typing</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>FOUNDER RULE 2026-08-04 — cash means cash only. The name rule alone missed brokers that send a TICKER and no name, which put money-market funds straight back into cash, so a curated ticker list backs it up.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-classification.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>accountClassBreakdown, assetClassOf, classifyHolding</t>
+        </is>
+      </c>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>AssetClass | null</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts:202</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL_INVESTABLE</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>investableAssets</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>How much money could actually fund something?</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Σ of every account that is not a real asset</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>every account</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>accounts</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Excludes the home and the car — they are wealth, not money you can spend without moving house.</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-classification.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>NetWorth</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O26" s="5" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P24" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/assets/index.ts:558</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr"/>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>incomeBearingClassOf</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>accountClassBreakdown, assetClassOf, classifyHolding</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>accountClassBreakdown, assetClassOf, classifyHolding</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="5" t="inlineStr">
-        <is>
-          <t>accountClassBreakdown, assetClassOf, classifyHolding</t>
-        </is>
-      </c>
-      <c r="O25" s="5" t="inlineStr">
-        <is>
-          <t>AssetClass | null</t>
-        </is>
-      </c>
-      <c r="P25" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/assets/index.ts:202</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>investableAssets</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr"/>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="P26" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts:311</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL_INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>investmentsTotal</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>How much do I hold in investments?</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Σ of accounts classed stocks_etf, bonds, alternatives or mixed</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>every account · its class</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>accounts</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Counts ACROSS wrappers, so a 401(k)'s stocks count. Excludes cash and real assets.</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-classification.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr"/>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O27" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="P27" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/assets/index.ts:306</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>KIND_IS_CASH</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>isCashKind</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Does this kind sit in the Cash section?</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>the kind's declared bucket === CASH</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>the ASSET_KINDS table</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>DEFECT — money_market declares bucket CASH and section Cash while its CLASS is stocks_etf. Two sources of truth, disagreeing, and Net worth groups by this one.</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-classification.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>The kind metadata must agree with the class rule: a money-market fund belongs in the measured section, not Cash.</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Change money_market in ASSET_KINDS from bucket CASH / section Cash to the investments section, then run the existing reclassify migration so accounts ALREADY stored under the old rule move too. A rule change that only affects new data leaves the founder looking at the old answer.</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O26" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="P26" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/assets/index.ts:311</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr"/>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>investmentsTotal</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="N27" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O27" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="P27" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/assets/index.ts:306</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr"/>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>isCashKind</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="3" t="inlineStr"/>
-      <c r="E28" s="3" t="inlineStr"/>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="3" t="inlineStr"/>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M28" s="5" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -2187,38 +2439,58 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr"/>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>IS_REAL_ASSET</t>
+        </is>
+      </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
           <t>isRealAsset</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="inlineStr"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Is this property rather than money?</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>class is real_estate or personal_property</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>the account's class</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Real assets are excluded from investable and from the nest egg by default.</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-classification.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>investableAssets</t>
-        </is>
-      </c>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr"/>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>investableAssets</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -2349,38 +2621,58 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr"/>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>MATURITY_CLASS</t>
+        </is>
+      </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
           <t>maturityClass</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="3" t="inlineStr"/>
-      <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" s="3" t="inlineStr"/>
-      <c r="G32" s="3" t="inlineStr"/>
-      <c r="H32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Does a maturity date make this cash or a bond?</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>anything with a maturity date is a bond</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>maturity_date</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>the account record</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>A CD is not cash however short it is — it pays interest, so it is measured.</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-classification.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr"/>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr"/>
       <c r="M32" s="5" t="inlineStr">
         <is>
           <t>NetWorth</t>
@@ -2511,38 +2803,58 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr"/>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>PRIMARY_CAR</t>
+        </is>
+      </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
           <t>primaryCarIdOf</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Which car is "the car you drive"?</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>the most valuable vehicle; ties break on id</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>every vehicle or personal-property account</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>accounts</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Only ONE car is excluded — a second car stays a real asset you could sell. Ties break on id so the choice never shuffles between renders.</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-classification.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>blendedReturn, blendedVolatility, retirementEarmarkedValue</t>
-        </is>
-      </c>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr"/>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>blendedReturn, blendedVolatility, retirementEarmarkedValue</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -2619,38 +2931,58 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr"/>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>NEST_EGG</t>
+        </is>
+      </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
           <t>retirementEarmarkedValue</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr"/>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>What is my nest egg?</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Σ of every account's earmarked portion</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>every account</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>accounts</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>THIS, not net worth, is what funds retirement — the number every odds figure stands on.</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-classification.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>planDoor, selectWillItLast, willItLastInputs</t>
-        </is>
-      </c>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L37" s="3" t="inlineStr">
-        <is>
-          <t>planDoor, selectWillItLast, willItLastInputs</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr"/>
       <c r="M37" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -2727,38 +3059,58 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr"/>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>TAX_TREATMENT</t>
+        </is>
+      </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
           <t>taxTreatmentOf</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr"/>
-      <c r="E39" s="3" t="inlineStr"/>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr"/>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>How is this account taxed?</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>explicit treatment, else PRE_TAX→deferred · ROTH→free · everything else→taxable</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>tax_treatment · tax_bucket</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>the account record</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Drives the Roth row and the required-withdrawal figures.</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-classification.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>AccountDetail</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>AccountDetail</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr"/>
       <c r="M39" s="5" t="inlineStr">
         <is>
           <t>AccountDetail</t>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -3295,102 +3295,142 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr"/>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>BOND_COUPON</t>
+        </is>
+      </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
           <t>annualCoupon</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="3" t="inlineStr"/>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>What income does this bond pay a year?</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>face value × coupon rate</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>face value · coupon rate</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>the bond record — from the holding description for a brokered CD</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>PAID ON FACE, NOT ON VALUE. A $10,000 bond at 4% pays $400 whether it is worth $9,800 or $11,000. Using the value here is the classic bond error and it flatters a discounted holding.</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>probes/bonds-and-freshness.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr">
+      <c r="N43" s="5" t="inlineStr">
         <is>
           <t>approxYTM, currentYield</t>
         </is>
       </c>
-      <c r="K43" s="3" t="inlineStr">
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="P43" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/bonds/index.ts:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>BOND_YIELD_TO_MATURITY</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>approxYTM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>What will this bond yield if I hold it to the end?</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>(coupon + (face − value) ÷ years) ÷ ((face + value) ÷ 2)</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>coupon · face · value · years remaining</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>derived from the bond record</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>The standard approximation, not an exact solve. It adds the pull back to face as maturity nears, so it exceeds the current yield on a discount bond. A MATURED bond returns null — never zero, which would read as "yields nothing".</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>probes/bonds-and-freshness.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="5" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t>approxYTM, currentYield</t>
-        </is>
-      </c>
-      <c r="M43" s="5" t="inlineStr">
-        <is>
-          <t>AccountDetail</t>
-        </is>
-      </c>
-      <c r="N43" s="5" t="inlineStr">
-        <is>
-          <t>approxYTM, currentYield</t>
-        </is>
-      </c>
-      <c r="O43" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="P43" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/bonds/index.ts:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr"/>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>approxYTM</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="3" t="inlineStr"/>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>AccountDetail</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
+      <c r="N44" s="5" t="inlineStr">
         <is>
           <t>bondRateSensitivity</t>
         </is>
       </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>AccountDetail</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>bondRateSensitivity</t>
-        </is>
-      </c>
-      <c r="M44" s="5" t="inlineStr">
-        <is>
-          <t>AccountDetail</t>
-        </is>
-      </c>
-      <c r="N44" s="5" t="inlineStr">
-        <is>
-          <t>bondRateSensitivity</t>
-        </is>
-      </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
           <t>number | null</t>
@@ -3403,38 +3443,58 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr"/>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>BOND_FACTS</t>
+        </is>
+      </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
           <t>bondInfo</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr"/>
-      <c r="D45" s="3" t="inlineStr"/>
-      <c r="E45" s="3" t="inlineStr"/>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr"/>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>What are this bond's own facts?</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>face · coupon rate · maturity · current value, straight off the record</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>the account record</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>broker payload or manual entry</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Missing fields become zero or empty rather than undefined, so every downstream calculation has something defined to work with.</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>probes/bonds-and-freshness.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>AccountDetail</t>
-        </is>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr"/>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>AccountDetail</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr"/>
       <c r="M45" s="5" t="inlineStr">
         <is>
           <t>AccountDetail</t>
@@ -3511,43 +3571,63 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr"/>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>BOND_CURRENT_YIELD</t>
+        </is>
+      </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
           <t>currentYield</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr"/>
-      <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr"/>
-      <c r="G47" s="3" t="inlineStr"/>
-      <c r="H47" s="3" t="inlineStr"/>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>What is this bond yielding on what it is worth now?</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>annual coupon ÷ current value</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>annual coupon · current value</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Measured against VALUE, not face — which is why a bond bought at a discount yields more than its coupon. No value returns null rather than dividing by zero.</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>probes/bonds-and-freshness.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr"/>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K47" s="3" t="inlineStr">
-        <is>
-          <t>AccountDetail</t>
-        </is>
-      </c>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M47" s="5" t="inlineStr">
-        <is>
-          <t>AccountDetail</t>
-        </is>
-      </c>
       <c r="N47" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -3565,43 +3645,63 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr"/>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>IS_BOND</t>
+        </is>
+      </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
           <t>isBond</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr"/>
-      <c r="D48" s="3" t="inlineStr"/>
-      <c r="E48" s="3" t="inlineStr"/>
-      <c r="F48" s="3" t="inlineStr"/>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="3" t="inlineStr"/>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Is this holding a bond?</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>its class is bonds</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>the account's class</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Reads the one classification rule rather than testing the kind itself, so a CD reaching bonds by its DESCRIPTION is included too.</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>probes/bonds-and-freshness.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr"/>
+      <c r="M48" s="5" t="inlineStr">
+        <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K48" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="L48" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M48" s="5" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
       <c r="N48" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -3619,38 +3719,58 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr"/>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>BOND_YEARS_LEFT</t>
+        </is>
+      </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
           <t>yearsToMaturity</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr"/>
-      <c r="D49" s="3" t="inlineStr"/>
-      <c r="E49" s="3" t="inlineStr"/>
-      <c r="F49" s="3" t="inlineStr"/>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="3" t="inlineStr"/>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>How long until this matures?</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>(maturity − today) ÷ 365.25 days, floored at zero</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>maturity date · today</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>the maturity parsed OUT OF THE DESCRIPTION TEXT — brokers send no maturity field</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Never negative: a matured bond is zero years, not minus two. No date at all is zero rather than forever.</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>probes/bonds-and-freshness.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>AccountDetail</t>
-        </is>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>approxYTM</t>
-        </is>
-      </c>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr"/>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>AccountDetail</t>
-        </is>
-      </c>
-      <c r="L49" s="3" t="inlineStr">
-        <is>
-          <t>approxYTM</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr">
         <is>
           <t>AccountDetail</t>
@@ -6637,38 +6757,58 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr"/>
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>TICKER_PLAUSIBLE</t>
+        </is>
+      </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
           <t>isPlausibleTicker</t>
         </is>
       </c>
-      <c r="C104" s="3" t="inlineStr"/>
-      <c r="D104" s="3" t="inlineStr"/>
-      <c r="E104" s="3" t="inlineStr"/>
-      <c r="F104" s="3" t="inlineStr"/>
-      <c r="G104" s="3" t="inlineStr"/>
-      <c r="H104" s="3" t="inlineStr"/>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Does this look like a real ticker?</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>1-6 letters, optionally a dot or dash plus 1-4 more</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>the ticker string</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>typed by the person, or from an import</t>
+        </is>
+      </c>
+      <c r="G104" s="3" t="inlineStr">
+        <is>
+          <t>It catches a TYPO before it becomes a silent zero. A CUSIP is deliberately NOT plausible — nine characters with digits — because a CD must never be sent to a share-price feed and come back worthless.</t>
+        </is>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>probes/bonds-and-freshness.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J104" s="3" t="inlineStr"/>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L104" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="inlineStr"/>
       <c r="M104" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -6691,38 +6831,58 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="inlineStr"/>
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>PRICE_FRESHNESS</t>
+        </is>
+      </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
           <t>priceFreshness</t>
         </is>
       </c>
-      <c r="C105" s="3" t="inlineStr"/>
-      <c r="D105" s="3" t="inlineStr"/>
-      <c r="E105" s="3" t="inlineStr"/>
-      <c r="F105" s="3" t="inlineStr"/>
-      <c r="G105" s="3" t="inlineStr"/>
-      <c r="H105" s="3" t="inlineStr"/>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>How old is this price, and should we warn about it?</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>days or hours since fetched; stale once four days old</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>fetched-at timestamp · now</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>the market-data cache</t>
+        </is>
+      </c>
+      <c r="G105" s="3" t="inlineStr">
+        <is>
+          <t>FOUR DAYS IS THE LINE, because a long weekend or a holiday can put three days between two perfectly normal updates and a false alarm teaches people to ignore real ones. Never fetched is STALE, not fresh — silence is not good news. A timestamp in the future is treated as unknown rather than as very fresh.</t>
+        </is>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>probes/bonds-and-freshness.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J105" s="3" t="inlineStr"/>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L105" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr"/>
       <c r="M105" s="5" t="inlineStr">
         <is>
           <t>—</t>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -4117,38 +4117,58 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr"/>
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_SHAPE_DEFAULT</t>
+        </is>
+      </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
           <t>defaultPaymentType</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr"/>
-      <c r="D56" s="3" t="inlineStr"/>
-      <c r="E56" s="3" t="inlineStr"/>
-      <c r="F56" s="3" t="inlineStr"/>
-      <c r="G56" s="3" t="inlineStr"/>
-      <c r="H56" s="3" t="inlineStr"/>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>How is this kind of debt normally repaid?</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>cards and lines of credit revolve; everything else is an installment</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>debt type</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>the debt record</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>How a debt is REPAID decides how it is modelled — a card revolves, a loan amortises.</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>probes/debt.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>paymentShape</t>
-        </is>
-      </c>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr"/>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L56" s="3" t="inlineStr">
-        <is>
-          <t>paymentShape</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr"/>
       <c r="M56" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -4225,48 +4245,68 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr"/>
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_MINIMUM_TOTAL</t>
+        </is>
+      </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
           <t>minimumDebtService</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr"/>
-      <c r="D58" s="3" t="inlineStr"/>
-      <c r="E58" s="3" t="inlineStr"/>
-      <c r="F58" s="3" t="inlineStr"/>
-      <c r="G58" s="3" t="inlineStr"/>
-      <c r="H58" s="3" t="inlineStr"/>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>What must I pay across all debts to stay current?</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Σ of minimums, excluding due-in-full debts</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>every debt</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>debt records</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>This is the AFFORDABILITY number — what must go out. Distinct from what is actually going out.</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>probes/debt.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr"/>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr"/>
+      <c r="M58" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N58" s="5" t="inlineStr">
         <is>
           <t>buildDebtState</t>
         </is>
       </c>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L58" s="3" t="inlineStr">
-        <is>
-          <t>buildDebtState</t>
-        </is>
-      </c>
-      <c r="M58" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N58" s="5" t="inlineStr">
-        <is>
-          <t>buildDebtState</t>
-        </is>
-      </c>
       <c r="O58" s="5" t="inlineStr">
         <is>
           <t>number</t>
@@ -4279,48 +4319,68 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr"/>
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_SHAPE</t>
+        </is>
+      </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
           <t>paymentShape</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr"/>
-      <c r="D59" s="3" t="inlineStr"/>
-      <c r="E59" s="3" t="inlineStr"/>
-      <c r="F59" s="3" t="inlineStr"/>
-      <c r="G59" s="3" t="inlineStr"/>
-      <c r="H59" s="3" t="inlineStr"/>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>How is THIS debt repaid?</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>a stored shape if set, else the default for its type</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>payment_type · debt type</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>the debt record</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>The person's own answer always wins over the default.</t>
+        </is>
+      </c>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>probes/debt.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J59" s="3" t="inlineStr">
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr"/>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr"/>
+      <c r="M59" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N59" s="5" t="inlineStr">
         <is>
           <t>minimumDebtService, requiredPayment</t>
         </is>
       </c>
-      <c r="K59" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L59" s="3" t="inlineStr">
-        <is>
-          <t>minimumDebtService, requiredPayment</t>
-        </is>
-      </c>
-      <c r="M59" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N59" s="5" t="inlineStr">
-        <is>
-          <t>minimumDebtService, requiredPayment</t>
-        </is>
-      </c>
       <c r="O59" s="5" t="inlineStr">
         <is>
           <t>NonNullable&lt;Debt['payment_type']&gt;</t>
@@ -4333,92 +4393,132 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr"/>
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_REQUIRED_PAYMENT</t>
+        </is>
+      </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
           <t>requiredPayment</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr"/>
-      <c r="D60" s="3" t="inlineStr"/>
-      <c r="E60" s="3" t="inlineStr"/>
-      <c r="F60" s="3" t="inlineStr"/>
-      <c r="G60" s="3" t="inlineStr"/>
-      <c r="H60" s="3" t="inlineStr"/>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>What must I pay on this each month?</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>0 if due in full; otherwise the LARGER of the minimum and the chosen payment</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>payment shape · minimum · chosen monthly payment</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>the debt record</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>A DUE-IN-FULL debt has no monthly payment at all — it is a dated bill, not a repayment, and treating it as monthly would overstate what a person is committed to.</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>probes/debt.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr"/>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr"/>
+      <c r="M60" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N60" s="5" t="inlineStr">
         <is>
           <t>totalDebtMonthly</t>
         </is>
       </c>
-      <c r="K60" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L60" s="3" t="inlineStr">
+      <c r="O60" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="P60" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/debt/index.ts:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_ACTUAL_TOTAL</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>totalDebtMonthly</t>
         </is>
       </c>
-      <c r="M60" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N60" s="5" t="inlineStr">
-        <is>
-          <t>totalDebtMonthly</t>
-        </is>
-      </c>
-      <c r="O60" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="P60" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/debt/index.ts:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr"/>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>totalDebtMonthly</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr"/>
-      <c r="D61" s="3" t="inlineStr"/>
-      <c r="E61" s="3" t="inlineStr"/>
-      <c r="F61" s="3" t="inlineStr"/>
-      <c r="G61" s="3" t="inlineStr"/>
-      <c r="H61" s="3" t="inlineStr"/>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>What am I actually paying across all debts?</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Σ of required payments</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>every debt</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>debt records</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Counts the chosen payment where one is set, so overpaying shows up. Confusing this with the minimum misstates affordability in one direction or the other.</t>
+        </is>
+      </c>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>probes/debt.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>actualDebtPayment</t>
-        </is>
-      </c>
+          <t>CORRECT</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr"/>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L61" s="3" t="inlineStr">
-        <is>
-          <t>actualDebtPayment</t>
-        </is>
-      </c>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr"/>
       <c r="M61" s="5" t="inlineStr">
         <is>
           <t>—</t>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet name="Calculations" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Formatting helpers" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Field dictionary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Open questions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="How a line becomes a class" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Field dictionary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Open questions" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,6 +45,11 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="001B4D8F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00854F0B"/>
       <sz val="11"/>
     </font>
@@ -53,7 +59,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +79,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEEEE9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBE3E3"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -122,8 +138,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -210,7 +238,7 @@
   <commentList>
     <comment ref="A2" authorId="0" shapeId="0">
       <text>
-        <t>The name we will call it by. One concept, one name.</t>
+        <t>The name we will call it by. One concept, one name — and the name must match the concept, not the file it happens to live in. Where the same question is answered in more than one place, each gets a name saying WHICH DOOR it serves (…_FROM_FILE, …_FROM_BROKER), because that is how you find the one that is wrong.</t>
       </text>
     </comment>
     <comment ref="B2" authorId="0" shapeId="0">
@@ -220,22 +248,22 @@
     </comment>
     <comment ref="C2" authorId="0" shapeId="0">
       <text>
-        <t>In plain English. What question does this number answer?</t>
+        <t>In plain English — the question AND the list of possible answers. 'Which asset class is this?' is not enough: the row must name the classes. If a reader cannot tell from this cell what the answer could be, the cell is wrong.</t>
       </text>
     </comment>
     <comment ref="D2" authorId="0" shapeId="0">
       <text>
-        <t>The arithmetic, written out.</t>
+        <t>The rules as they are applied to REAL data, in order, written so you could follow them by hand against a downloaded file. Literal words, tickers and patterns — not an abstract chain of internal field names. 'label rule → maturity → kind' says nothing; 'name contains CD, CERTIFICATE OF DEPOSIT, T-BILL or TREASURY BILL → Bonds &amp; CDs' is a rule.</t>
       </text>
     </comment>
     <comment ref="E2" authorId="0" shapeId="0">
       <text>
-        <t>Every variable that goes in.</t>
+        <t>Every variable that goes in, written as THE INSTITUTION'S FIELD → what we call it. The left side is what a person would see in their own download; the right side is our name for it.</t>
       </text>
     </comment>
     <comment ref="F2" authorId="0" shapeId="0">
       <text>
-        <t>Where each variable comes from.</t>
+        <t>The actual origin: WHICH file or feed, WHICH field in it, and HOW that field is identified when institutions name it differently. 'The account record' is not a source — the account record is where it ended up. Name the download column, the payload path, or the screen and box it was typed into.</t>
       </text>
     </comment>
     <comment ref="G2" authorId="0" shapeId="0">
@@ -300,7 +328,7 @@
   <commentList>
     <comment ref="A2" authorId="0" shapeId="0">
       <text>
-        <t>The name we will call it by. One concept, one name.</t>
+        <t>The name we will call it by. One concept, one name — and the name must match the concept, not the file it happens to live in. Where the same question is answered in more than one place, each gets a name saying WHICH DOOR it serves (…_FROM_FILE, …_FROM_BROKER), because that is how you find the one that is wrong.</t>
       </text>
     </comment>
     <comment ref="B2" authorId="0" shapeId="0">
@@ -310,22 +338,22 @@
     </comment>
     <comment ref="C2" authorId="0" shapeId="0">
       <text>
-        <t>In plain English. What question does this number answer?</t>
+        <t>In plain English — the question AND the list of possible answers. 'Which asset class is this?' is not enough: the row must name the classes. If a reader cannot tell from this cell what the answer could be, the cell is wrong.</t>
       </text>
     </comment>
     <comment ref="D2" authorId="0" shapeId="0">
       <text>
-        <t>The arithmetic, written out.</t>
+        <t>The rules as they are applied to REAL data, in order, written so you could follow them by hand against a downloaded file. Literal words, tickers and patterns — not an abstract chain of internal field names. 'label rule → maturity → kind' says nothing; 'name contains CD, CERTIFICATE OF DEPOSIT, T-BILL or TREASURY BILL → Bonds &amp; CDs' is a rule.</t>
       </text>
     </comment>
     <comment ref="E2" authorId="0" shapeId="0">
       <text>
-        <t>Every variable that goes in.</t>
+        <t>Every variable that goes in, written as THE INSTITUTION'S FIELD → what we call it. The left side is what a person would see in their own download; the right side is our name for it.</t>
       </text>
     </comment>
     <comment ref="F2" authorId="0" shapeId="0">
       <text>
-        <t>Where each variable comes from.</t>
+        <t>The actual origin: WHICH file or feed, WHICH field in it, and HOW that field is identified when institutions name it differently. 'The account record' is not a source — the account record is where it ended up. Name the download column, the payload path, or the screen and box it was typed into.</t>
       </text>
     </comment>
     <comment ref="G2" authorId="0" shapeId="0">
@@ -675,12 +703,12 @@
   <dimension ref="A1:P160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
     <col width="52" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
@@ -696,7 +724,7 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CALCULATION INVENTORY · Phase 1 — Net worth, Performance and the 8 screens they open · 158 calculations · generated from commit 57a37b4 on 2026-08-17  ⚠ TREE WAS DIRTY. EVERY FORMULA HERE DESCRIBES THE CODE AS IT IS TODAY, BUGS INCLUDED — you cannot fix what you have not described, and a probe can only execute what exists. Where the current behaviour is wrong, Status says DEFECT and the corrected version sits in WHAT IT SHOULD BE; the difference between those two columns is the work list. GREY columns are generated from the code and overwritten on every regeneration — never edit them. CREAM columns are written by hand and preserved. A row is not documented until its probe passes.</t>
+          <t>CALCULATION INVENTORY · Phase 1 — Net worth, Performance and the 8 screens they open · 158 calculations · generated from commit 247201d on 2026-08-17  ⚠ TREE WAS DIRTY. EVERY FORMULA HERE DESCRIBES THE CODE AS IT IS TODAY, BUGS INCLUDED — you cannot fix what you have not described, and a probe can only execute what exists. Where the current behaviour is wrong, Status says DEFECT and the corrected version sits in WHAT IT SHOULD BE; the difference between those two columns is the work list. GREY columns are generated from the code and overwritten on every regeneration — never edit them. CREAM columns are written by hand and preserved. A row is not documented until its probe passes.</t>
         </is>
       </c>
     </row>
@@ -718,17 +746,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Formula</t>
+          <t>Formula — the actual rules</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Input variables</t>
+          <t>Input variables (raw → ours)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Source of each</t>
+          <t>Where each comes from — file, feed, field</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1281,22 +1309,29 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>How is my money split across classes?</t>
+          <t>How much money sits in each of the seven classes?  Answer: a dollar figure for each of Cash · Bonds &amp; CDs · Stocks / ETFs · Alternatives · Real estate · Personal property · Unclassified.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Σ balances grouped by class</t>
+          <t>For every account: if it has its own breakdown (an account holding several classes at once), add each piece to its own class. Otherwise put the WHOLE balance in the one class the account resolves to. Round each total to the cent at the end, never during.
+The totals must add to total assets — this is what the donut draws, so any leak shows as a wrong slice.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>every account · its class</t>
+          <t>each account's class → assetClassOf
+each account's money → balance
+any split → accountClassBreakdown</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>accounts</t>
+          <t>The account's balance. THREE doors, and the field differs by door:
+• CONNECTED BROKER — SnapTrade account payload, balance.total.amount
+• FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
+• TYPED — the Balance box on Add account
+The class comes from ASSET_CLASS_OF_ACCOUNT (see that row).</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1345,7 +1380,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>ACCOUNT_CLASS</t>
+          <t>ASSET_CLASS_OF_ACCOUNT</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1355,22 +1390,48 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Which asset class does this account belong to?</t>
+          <t>Which of the seven classes does a whole ACCOUNT belong to?
+The answer is one of: Cash · Bonds &amp; CDs · Stocks / ETFs · Alternatives · Real estate · Personal property · Unclassified (we were never told what is inside it).</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>first match wins: explicit class → label rule → maturity date → kind → positions present → tax bucket → "mixed"</t>
+          <t>The first rule that matches wins. Read top to bottom against a real account:
+1. A class was set by hand, or written by the file importer → use it. A person's own answer is never overridden.
+2. Otherwise read the NAME:
+   • contains SWEEP or SETTLEMENT → Cash
+   • contains MONEY MARKET / MMKT / MMF, or IS one of 17 known money-market tickers (VMFXX VMRXX VUSXX VMSXX SPAXX FDRXX FZFXX FZDXX SPRXX SWVXX SNVXX SNSXX SWGXX TTTXX MVRXX GOFXX FGXXX) → Stocks / ETFs
+   • contains CD / CERTIFICATE OF DEPOSIT / T-BILL / TREASURY BILL → Bonds &amp; CDs
+3. Otherwise, if it carries a maturity date → Bonds &amp; CDs (that is what a maturity means)
+4. Otherwise read the account TYPE picked on Add account:
+   Checking · Savings · High-yield savings · Cash management → Cash
+   Money market → Stocks / ETFs   |   CD · Fixed income → Bonds &amp; CDs
+   Stocks &amp; ETFs → Stocks / ETFs
+   Private equity · Hedge funds · Commodities · Crypto · Annuities · Options · Other → Alternatives
+   Home → Real estate   |   Vehicle → Personal property
+5. Otherwise, if holdings are listed inside it → Stocks / ETFs
+6. Otherwise, a cash wrapper → Cash; a property wrapper → Real estate
+7. Otherwise → Unclassified. NOT "stocks" — we do not guess what is in a 401(k) we cannot see.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>asset_class · label · maturity_date · kind · positions · tax_bucket</t>
+          <t>explicit class → asset_class
+name / description → label
+maturity → maturity_date
+account type → kind
+holdings inside → positions
+wrapper → tax_bucket</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>the account record</t>
+          <t>An explicit class on the account: either chosen by the person on the account screen, or set by the file importer when it recognised the holding (classifyHolding writes it).
+The account or holding NAME. Broker: symbol.description in the positions payload, else the account nickname. File: the name column, found by header pattern — Description / Security / Investment Name / Fund / Holding / Instrument. Typed: the Name box on Add account.
+maturity_date: typed on the bond form, or parsed out of the description text.
+The account TYPE, picked by the person from the list on Add account (Checking, Savings, High-yield savings, Money market, CD, Stocks &amp; ETFs, Fixed income, Crypto, Options, Home, Vehicle…). Never sent by an institution — a connected account is given a type at connect time.
+positions: the holdings list — from the broker feed, an uploaded file, or added by hand.
+tax_bucket — set from the wrapper chosen on Add account (Taxable / 401(k) / Traditional IRA / Roth / HSA → TAXABLE, PRE_TAX, ROTH, CASH, PROPERTY). Never sent by an institution.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1537,22 +1598,25 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>What return do we expect from this kind of holding?</t>
+          <t>What return do we assume for this kind of account?  Answer: a yearly rate, e.g. 0.024 for savings.</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>a user override if set, else the ASSET_KINDS default</t>
+          <t>If the person has set their own rate for this account type, use it. Otherwise take the rate from our own ASSET_KINDS table (checking 0.5% · savings 2.4% · high-yield 4.2% · money market 4.5% · CD 4.2% …). If the type is unknown, fall back to 6%.
+These are NOMINAL — inflation is applied separately by the retirement engine, so applying it here too would double-count it.</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>kind · user overrides</t>
+          <t>account type → kind
+any override → overrides</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>ASSET_KINDS table; overrides from settings</t>
+          <t>OUR OWN TABLE — ASSET_KINDS in src/domain/assets/index.ts. Not from any institution and not from the market: a hand-maintained list of account types, each with a bucket, a screen section and a long-run return. If a number here is wrong, every projection is wrong.
+Overrides: typed by the person in Settings → assumptions.</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1611,22 +1675,28 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>What return does MY mix expect?</t>
+          <t>What return should I expect on everything I hold together?  Answer: one yearly rate.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Σ(balance × kind return) ÷ Σ balance</t>
+          <t>Weight each account type's rate by how much money sits in it, and add: Σ(balance × rate) ÷ Σ(balance). With no accounts at all, fall back to a stated default rather than zero.
+THIS IS THE NUMBER EVERY PROJECTION STANDS ON. It is why a cash-heavy pot and a stock-heavy pot of the same size do not reach the same place, and why any headline odds figure must state the mix it assumed.</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>every account balance · each kind's expected return</t>
+          <t>each account's money → balance
+each account's rate → benchmarkReturn(kind)</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>accounts and the ASSET_KINDS table</t>
+          <t>The account's balance. THREE doors, and the field differs by door:
+• CONNECTED BROKER — SnapTrade account payload, balance.total.amount
+• FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
+• TYPED — the Balance box on Add account
+OUR OWN TABLE — ASSET_KINDS in src/domain/assets/index.ts. Not from any institution and not from the market: a hand-maintained list of account types, each with a bucket, a screen section and a long-run return. If a number here is wrong, every projection is wrong.</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1689,22 +1759,28 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>How much does my mix typically swing?</t>
+          <t>How much does a year's return typically swing around that average?  Answer: one yearly figure, e.g. 0.15 meaning about 15 points either side in a typical year.</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Σ(balance × kind volatility) ÷ Σ balance</t>
+          <t>Same money-weighted blend as the return, but over each type's volatility rather than its return.
+Added 2026-08-11 to replace a rule of thumb (volatility = return × 1.7) that made a cash-heavy pot look almost risk-free.</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>every account balance · each kind's volatility</t>
+          <t>each account's money → balance
+each type's swing → ASSET_KINDS vol</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>accounts and the ASSET_KINDS table</t>
+          <t>The account's balance. THREE doors, and the field differs by door:
+• CONNECTED BROKER — SnapTrade account payload, balance.total.amount
+• FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
+• TYPED — the Balance box on Add account
+OUR OWN TABLE — ASSET_KINDS in src/domain/assets/index.ts. Not from any institution and not from the market: a hand-maintained list of account types, each with a bucket, a screen section and a long-run return. If a number here is wrong, every projection is wrong.</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -1871,22 +1947,26 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>How much cash do I hold?</t>
+          <t>How much actual cash do I have?  Answer: one dollar figure.</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Σ over accounts of the cash slice, or the whole balance if the account is cash</t>
+          <t>Add up the balances of every account whose class is Cash. Under the founder's 2026-08-04 rule that means checking, savings, high-yield savings and the uninvested sweep at a broker — and NOT money-market funds, which pay dividends and are measured with the investments.</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>every account · its class breakdown</t>
+          <t>each account's class → assetClassOf
+each account's money → balance</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>accounts</t>
+          <t>The account's balance. THREE doors, and the field differs by door:
+• CONNECTED BROKER — SnapTrade account payload, balance.total.amount
+• FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
+• TYPED — the Balance box on Add account</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1999,22 +2079,32 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Does this account count toward retirement by default?</t>
+          <t>How much of this account counts toward retirement, before anyone changes it?  Answer: 0% or 100%.</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>0 for a 529, the primary home and the car you drive; 100 otherwise</t>
+          <t>FOUNDER RULE 2026-08-11 — everything you own counts, except the roof you live under and the car you drive:
+• a 529 → 0% (legally someone else's education, not a choice)
+• your PRIMARY home → 0%
+• your most valuable car → 0%
+• everything else, cash included → 100%
+A rental counts (you could sell it). A second car counts.</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>kind · class · real-estate use · primary car id</t>
+          <t>account type → kind
+class → assetClassOf
+home use → re_use
+the main car → primaryCarId</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>the account record</t>
+          <t>The account TYPE, picked by the person from the list on Add account (Checking, Savings, High-yield savings, Money market, CD, Stocks &amp; ETFs, Fixed income, Crypto, Options, Home, Vehicle…). Never sent by an institution — a connected account is given a type at connect time.
+re_use: picked on the property screen (primary / rental / second home / land), defaulting to primary — the cautious side.
+primaryCarId: computed by PRIMARY_CAR below.</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2073,22 +2163,29 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>How much of this account is earmarked for retirement?</t>
+          <t>How many dollars of this account count toward retirement?  Answer: a dollar figure.</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>balance × clamp(saved % or default, 0, 100) ÷ 100</t>
+          <t>balance × (the saved percentage if there is one, otherwise the default above) ÷ 100.
+The saved percentage always beats the default, and is clamped to 0–100 so a typo cannot earmark three times an account.</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>balance · saved percentage · default</t>
+          <t>money → balance
+saved share → retirement_pct
+fallback → EARMARK_DEFAULT</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>the account record</t>
+          <t>The account's balance. THREE doors, and the field differs by door:
+• CONNECTED BROKER — SnapTrade account payload, balance.total.amount
+• FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
+• TYPED — the Balance box on Add account
+retirement_pct: a slider on the Plan tab, per account. The person's own answer.</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -2137,7 +2234,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>INCOME_BEARING_CLASS</t>
+          <t>CLASS_FROM_NAME_TEXT</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -2147,22 +2244,28 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Is this cash, or something that pays income?</t>
+          <t>Reading the NAME alone, is this cash, a money-market fund, or a CD / T-bill?
+Answers: Cash · Stocks / ETFs · Bonds &amp; CDs · no answer at all (the name says nothing, so the next rule decides).</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>sweep/settlement → cash · money-market by name OR ticker → stocks_etf · CD/T-bill → bonds · else null</t>
+          <t>Applied to the name text, in this order:
+• the word SWEEP or SETTLEMENT → Cash. This is the ONLY thing that counts as cash — uninvested money sitting at the broker.
+• MONEY MARKET / MONEY-MARKET / MMKT / MMF → Stocks / ETFs
+• any word in the name is a known money-market ticker (17 of them) → Stocks / ETFs. This second test exists because a broker that sends only a ticker sends no words to match on — which is exactly how VMFXX got back into Cash.
+• CD / CERTIFICATE OF DEPOSIT / T-BILL / TREASURY BILL → Bonds &amp; CDs
+• nothing matched → no answer, and the caller moves on to its next rule.</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>the account or holding label</t>
+          <t>name or description text → label</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>label from the broker, an import, or typing</t>
+          <t>The account or holding NAME. Broker: symbol.description in the positions payload, else the account nickname. File: the name column, found by header pattern — Description / Security / Investment Name / Fund / Holding / Instrument. Typed: the Name box on Add account.</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2221,22 +2324,26 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>How much money could actually fund something?</t>
+          <t>How much money could actually fund something?  Answer: one dollar figure.</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Σ of every account that is not a real asset</t>
+          <t>Cash + investments — everything except the house and the car. Selling the roof you live under is not a plan, so physical assets are excluded by CLASS, not by wrapper.</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>every account</t>
+          <t>each account's class → assetClassOf
+each account's money → balance</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>accounts</t>
+          <t>The account's balance. THREE doors, and the field differs by door:
+• CONNECTED BROKER — SnapTrade account payload, balance.total.amount
+• FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
+• TYPED — the Balance box on Add account</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -2295,22 +2402,26 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>How much do I hold in investments?</t>
+          <t>How much do I have invested?  Answer: one dollar figure.</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Σ of accounts classed stocks_etf, bonds, alternatives or mixed</t>
+          <t>Add up the balances of every account whose class is Stocks / ETFs, Bonds &amp; CDs, Alternatives or Unclassified. Excludes cash, the house and the car.</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>every account · its class</t>
+          <t>each account's class → assetClassOf
+each account's money → balance</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>accounts</t>
+          <t>The account's balance. THREE doors, and the field differs by door:
+• CONNECTED BROKER — SnapTrade account payload, balance.total.amount
+• FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
+• TYPED — the Balance box on Add account</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2369,22 +2480,24 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Does this kind sit in the Cash section?</t>
+          <t>Does this account type sit under the Cash heading on screen?  Answers: yes · no.</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>the kind's declared bucket === CASH</t>
+          <t>Look the account type up in our own ASSET_KINDS table and ask whether its bucket is CASH.
+Checking · Savings · High-yield savings · Money market · CD → yes. Everything else → no.
+THIS DISAGREES WITH THE CLASS RULE ABOVE. Money market and CD are marked CASH here, while ASSET_CLASS_OF_ACCOUNT calls them Stocks / ETFs and Bonds &amp; CDs. Net worth groups by THIS, so a money-market fund still reads as cash on the screen — the founder's F6.</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>kind</t>
+          <t>account type → kind</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>the ASSET_KINDS table</t>
+          <t>OUR OWN TABLE — ASSET_KINDS in src/domain/assets/index.ts. Not from any institution and not from the market: a hand-maintained list of account types, each with a bucket, a screen section and a long-run return. If a number here is wrong, every projection is wrong.</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -2441,7 +2554,7 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>IS_REAL_ASSET</t>
+          <t>IS_PHYSICAL_ASSET</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -2451,22 +2564,23 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Is this property rather than money?</t>
+          <t>Is this something physical you own rather than money you could spend?  Answers: yes · no.</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>class is real_estate or personal_property</t>
+          <t>Run ASSET_CLASS_OF_ACCOUNT, then answer yes if the class is Real estate or Personal property.
+Used to keep the house and the car OUT of investable assets and out of the nest egg.</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>the account's class</t>
+          <t>the account → a, via its class</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>Derived from ASSET_CLASS_OF_ACCOUNT — see that row for where each of its inputs comes from.</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2623,7 +2737,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>MATURITY_CLASS</t>
+          <t>MATURITY_MEANS_BOND</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -2633,22 +2747,23 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Does a maturity date make this cash or a bond?</t>
+          <t>Does having a maturity date make this a bond?  Answers: Bonds &amp; CDs · Cash.</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>anything with a maturity date is a bond</t>
+          <t>A non-empty maturity date → Bonds &amp; CDs. No maturity date → Cash.
+That is the whole rule: an instrument with a date on which it pays back is fixed income, whatever it is called.</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>maturity_date</t>
+          <t>maturity date → maturityDate</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>the account record</t>
+          <t>Typed on the bond / CD form, or parsed out of a brokered CD's description text ("KEYBANK NA 4.00% CD 08/24/26" → 2026-08-24). No institution sends maturity as its own field.</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -2815,22 +2930,27 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Which car is "the car you drive"?</t>
+          <t>Which car is "the car you drive"?  Answer: one account id, or none if no vehicles are held.</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>the most valuable vehicle; ties break on id</t>
+          <t>Among accounts whose type is Vehicle, take the most valuable one. If two are worth the same, take the one whose id sorts first — so the answer never shuffles between two screens showing the same data.</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>every vehicle or personal-property account</t>
+          <t>vehicle accounts → accounts
+value of each → balance</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>accounts</t>
+          <t>The account's balance. THREE doors, and the field differs by door:
+• CONNECTED BROKER — SnapTrade account payload, balance.total.amount
+• FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
+• TYPED — the Balance box on Add account
+Vehicles are identified by the account type picked on Add account.</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -2943,22 +3063,22 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>What is my nest egg?</t>
+          <t>What is my retirement pot worth?  Answer: one dollar figure.</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Σ of every account's earmarked portion</t>
+          <t>Add up the earmarked portion of every account. NOT net worth, and NOT total assets — the home and the main car are out at 0%, and debts are not subtracted here.</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>every account</t>
+          <t>every account → accounts, via EARMARK_AMOUNT</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>accounts</t>
+          <t>Derived — see EARMARK_AMOUNT and EARMARK_DEFAULT for where each input comes from.</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -3071,22 +3191,23 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>How is this account taxed?</t>
+          <t>How is this account taxed?  Answers: taxable · tax-deferred (tax due when you take it out) · tax-free (Roth).</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>explicit treatment, else PRE_TAX→deferred · ROTH→free · everything else→taxable</t>
+          <t>An explicitly set treatment wins. Otherwise: a PRE_TAX wrapper → tax-deferred; a ROTH wrapper → tax-free; everything else → taxable. Taxable is the default, which is the cautious side — it assumes tax is owed rather than assuming it is not.</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>tax_treatment · tax_bucket</t>
+          <t>explicit treatment → tax_treatment
+wrapper → tax_bucket</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>the account record</t>
+          <t>Both set from the wrapper picked on Add account (Taxable / 401(k) / Traditional IRA / Roth / HSA). No institution tells us this reliably, so it is always the person's own answer.</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -3307,22 +3428,23 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>What income does this bond pay a year?</t>
+          <t>How much income does this bond pay in a year?  Answer: a dollar figure.</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>face value × coupon rate</t>
+          <t>face value × coupon rate. NOT what the bond is worth today × the rate — a $10,000 bond paying 4% pays $400 whether it is trading at $9,800 or $11,000.</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>face value · coupon rate</t>
+          <t>face value → face
+coupon rate → couponRate</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>the bond record — from the holding description for a brokered CD</t>
+          <t>Bond facts. For a BROKERED bond or CD these are parsed OUT OF THE DESCRIPTION TEXT — 'KEYBANK NA 4.00% CD 08/24/26' — because no institution sends coupon or maturity as its own field. Typed bonds get them from the Add bond form: Face value, Coupon %, Maturity date.</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -3381,22 +3503,28 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>What will this bond yield if I hold it to the end?</t>
+          <t>What will this bond earn me a year if I hold it to the end?  Answer: a rate, or no answer for a bond that has already matured.</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>(coupon + (face − value) ÷ years) ÷ ((face + value) ÷ 2)</t>
+          <t>Adds the pull back to face value to the running income:
+(annual coupon + (face − value) ÷ years left) ÷ ((face + value) ÷ 2).
+A bond bought below face gains as it matures, so this comes out above the current yield. Already matured, or no value → no answer, never zero.</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>coupon · face · value · years remaining</t>
+          <t>coupon → annualCoupon
+face → face
+value → value
+years left → yearsToMaturity</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>derived from the bond record</t>
+          <t>Bond facts. For a BROKERED bond or CD these are parsed OUT OF THE DESCRIPTION TEXT — 'KEYBANK NA 4.00% CD 08/24/26' — because no institution sends coupon or maturity as its own field. Typed bonds get them from the Add bond form: Face value, Coupon %, Maturity date.
+Today's date, for the years remaining.</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -3455,22 +3583,22 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>What are this bond's own facts?</t>
+          <t>What are this holding's bond facts?  Answer: face, coupon, maturity and yields — or nothing if it is not a bond.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>face · coupon rate · maturity · current value, straight off the record</t>
+          <t>Reads the stored bond fields off the holding and computes its yields. A holding with none of them is not a bond and returns nothing.</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>the account record</t>
+          <t>the holding → position/account</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>broker payload or manual entry</t>
+          <t>Bond facts. For a BROKERED bond or CD these are parsed OUT OF THE DESCRIPTION TEXT — 'KEYBANK NA 4.00% CD 08/24/26' — because no institution sends coupon or maturity as its own field. Typed bonds get them from the Add bond form: Face value, Coupon %, Maturity date.</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -3583,22 +3711,24 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>What is this bond yielding on what it is worth now?</t>
+          <t>What is this bond paying me, measured against what it is worth today?  Answer: a rate, or no answer if it has no value.</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>annual coupon ÷ current value</t>
+          <t>annual coupon ÷ current value. A bond bought at a discount yields MORE than its stated coupon; one bought at a premium yields less. No value → no answer, never a division by zero.</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>annual coupon · current value</t>
+          <t>coupon → annualCoupon
+what it is worth → value</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>Bond facts. For a BROKERED bond or CD these are parsed OUT OF THE DESCRIPTION TEXT — 'KEYBANK NA 4.00% CD 08/24/26' — because no institution sends coupon or maturity as its own field. Typed bonds get them from the Add bond form: Face value, Coupon %, Maturity date.
+value: the broker's market value for the position, or the Value box for a typed bond.</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -3657,22 +3787,22 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Is this holding a bond?</t>
+          <t>Is this holding a bond or CD?  Answers: yes · no.</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>its class is bonds</t>
+          <t>Yes if it carries bond facts — a maturity, or a coupon rate — or its class is already Bonds &amp; CDs.</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>the account's class</t>
+          <t>the holding → position/account</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>Derived from the same fields as BOND_FACTS; see that row.</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -3731,22 +3861,23 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>How long until this matures?</t>
+          <t>How long until this bond pays back?  Answer: a number of years, never negative.</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>(maturity − today) ÷ 365.25 days, floored at zero</t>
+          <t>maturity date − today, in years. Anything already past → 0. No maturity date → 0, treated as due now rather than as never.</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>maturity date · today</t>
+          <t>maturity → maturity
+today → now</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>the maturity parsed OUT OF THE DESCRIPTION TEXT — brokers send no maturity field</t>
+          <t>THE MATURITY IS PARSED OUT OF THE DESCRIPTION TEXT for a brokered CD — no institution sends it as its own field. "KEYBANK NA 4.00% CD 08/24/26" → 2026-08-24. Typed bonds get it from the Maturity date box. Confirmed against live E*TRADE and Vanguard downloads, 2026-08-04.</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -4129,22 +4260,22 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>How is this kind of debt normally repaid?</t>
+          <t>How is this KIND of debt normally repaid?  Answers: revolving (a balance you carry) · installment (a fixed payment until it clears).</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>cards and lines of credit revolve; everything else is an installment</t>
+          <t>Credit card → revolving. HELOC → revolving. Everything else — mortgage, student loan, auto, personal, medical → installment.</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>debt type</t>
+          <t>debt type → debt_type</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>the debt record</t>
+          <t>The debt as entered on the Debts screen: Balance, Interest rate, Minimum payment, and the repayment shape. No institution supplies these — every debt in the app is typed by hand.</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -4257,22 +4388,23 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>What must I pay across all debts to stay current?</t>
+          <t>What must I pay across all debts to stay current?  Answer: a dollar figure.</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Σ of minimums, excluding due-in-full debts</t>
+          <t>Add the minimum on every debt, skipping any that is due in full. This is the AFFORDABILITY number — the floor beneath which a plan does not work.</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>every debt</t>
+          <t>every debt → debts
+each minimum → minimum_monthly_payment</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>debt records</t>
+          <t>The debt as entered on the Debts screen: Balance, Interest rate, Minimum payment, and the repayment shape. No institution supplies these — every debt in the app is typed by hand.</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -4331,22 +4463,23 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>How is THIS debt repaid?</t>
+          <t>How is THIS debt repaid?  Answers: revolving · installment · due in full (a dated bill, not a monthly repayment).</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>a stored shape if set, else the default for its type</t>
+          <t>If a shape was chosen for this debt, use it. Otherwise use the default for its kind. The person's own answer always wins.</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>payment_type · debt type</t>
+          <t>chosen shape → payment_type
+debt type → debt_type</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>the debt record</t>
+          <t>The debt as entered on the Debts screen: Balance, Interest rate, Minimum payment, and the repayment shape. No institution supplies these — every debt in the app is typed by hand.</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -4405,22 +4538,24 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>What must I pay on this each month?</t>
+          <t>What must I pay on this each month?  Answer: a dollar figure, which may be zero.</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>0 if due in full; otherwise the LARGER of the minimum and the chosen payment</t>
+          <t>Due in full → 0. It is a dated bill, and calling it a monthly payment overstates what a person is committed to. Otherwise the LARGER of the minimum and whatever payment they have chosen, so overpaying on purpose shows up.</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
         <is>
-          <t>payment shape · minimum · chosen monthly payment</t>
+          <t>shape → paymentShape
+minimum → minimum_monthly_payment
+chosen → monthly_payment</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>the debt record</t>
+          <t>The debt as entered on the Debts screen: Balance, Interest rate, Minimum payment, and the repayment shape. No institution supplies these — every debt in the app is typed by hand.</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -4479,22 +4614,22 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>What am I actually paying across all debts?</t>
+          <t>What am I actually paying across all debts?  Answer: a dollar figure.</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Σ of required payments</t>
+          <t>Add the required payment on every debt, which counts the chosen payment where one is set. Confusing this with the minimum misstates affordability in one direction or the other.</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>every debt</t>
+          <t>every debt → debts, via requiredPayment</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>debt records</t>
+          <t>The debt as entered on the Debts screen: Balance, Interest rate, Minimum payment, and the repayment shape. No institution supplies these — every debt in the app is typed by hand.</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -4651,7 +4786,7 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>What drove my net worth from one date to another?</t>
+          <t>NW_CHANGE_WALK</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -4661,22 +4796,33 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>wealthGenerated = (ending − beginning) − contributions + withdrawals − debtPrincipal;  marketChange = wealthGenerated − dividends − interest</t>
+          <t>What drove my net worth from one date to the next?  Answer: a set of rows that add up — starting value · money you put in · money you took out · dividends · interest · debt paid down · change in investment value · ending value.</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>beginning · ending · contributions · withdrawals · dividends · interest · debtPrincipal</t>
+          <t>total       = ending − beginning
+wealth made = total − money in + money out − debt paid down
+change in investment value = wealth made − dividends − interest
+THE DEFECT IS IN THAT LAST LINE. "Change in investment value" is not measured against any price. It is whatever is left over once everything else is accounted for, so every error anywhere else in the ledger lands in it wearing the label of a market movement. With nothing actually moved, a $500 deposit manufactures a $500 "market loss" — and a real $500 loss looks identical.</t>
         </is>
       </c>
       <c r="E64" s="3" t="inlineStr">
         <is>
-          <t>beginning = a SAVED net-worth snapshot; ending = today's computed net worth; the other five = sums over the transaction ledger inside the window</t>
+          <t>starting value → beginning
+ending value → ending
+money in → contributions
+money out → withdrawals
+dividends → dividends
+interest → interest
+debt paid down → debtPrincipal</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>DEFECT — marketChange is a RESIDUAL, not a measurement: whatever the ledger cannot explain lands there, labelled "change in investment value". With beginning = ending, a $500 contribution manufactures a $500 "market loss" that never happened, and it is indistinguishable from a real one. All five ledger inputs are floored at zero on the way in.</t>
+          <t>beginning / ending: Net-worth snapshots the app writes itself — a dated map of what things were worth. Written on app open. NOT from any institution: nobody sends us history, so this is the only record of what yesterday looked like, which is why its gaps matter so much.
+money in, money out, dividends, interest: summed from the transaction ledger, which is built from the broker feed by the activity rules below. Any mis-mapping there arrives here as a fake market movement.
+debt paid down: from payments logged on the Debts screen.</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -4729,7 +4875,7 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>What is my return on cash + investments since the baseline?</t>
+          <t>NW_CHANGE_PCT</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
@@ -4739,22 +4885,29 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>(currentInvestable − baseline) ÷ baseline, to 1 decimal place</t>
+          <t>What is my return on cash and investments since the baseline?  Answer: a percentage to one decimal, or no answer at all when there is no history to compare against.</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>invDaily (saved daily points) · currentInvestable · sinceKey</t>
+          <t>(today's investable − the baseline value) ÷ the baseline value.
+The baseline is the EARLIEST stored daily point on or after the baseline date. The house is left out because it only moves when someone retypes it, which would otherwise read as a market gain.
+No history → NO percentage. It is never back-guessed, which is right.
+THE DEFECT IS WHAT THE BASELINE IS. It is whatever day the app happened to be opened, not a date a person chose. If the only stored point was written after a fall, the fall is invisible and the small recovery since reads as a gain — which is exactly how a −4.2% year showed as +2.0%.</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>invDaily = written on every Home open; currentInvestable = investableAssets(today); sinceKey = the change line's own baseline date</t>
+          <t>stored history → daily
+today's value → currentInvestable
+baseline date → sinceKey</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>baseline = the EARLIEST daily point on or after sinceKey. Property is excluded because it only moves when retyped. DEFECT — the baseline is whatever day the app happened to be opened, not a meaningful date; if the only stored point was written after a fall, the fall is invisible and the recovery since reads as a gain. This is why a −4.2% year showed +2.0%.</t>
+          <t>daily: Net-worth snapshots the app writes itself — a dated map of what things were worth. Written on app open. NOT from any institution: nobody sends us history, so this is the only record of what yesterday looked like, which is why its gaps matter so much.
+currentInvestable: TOTAL_INVESTABLE, computed live from today's balances.
+sinceKey: the date the change line itself is labelled with.</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -4967,205 +5120,340 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr"/>
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>CLASS_FROM_FILE</t>
+        </is>
+      </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
           <t>classifyHolding</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr"/>
-      <c r="D69" s="3" t="inlineStr"/>
-      <c r="E69" s="3" t="inlineStr"/>
-      <c r="F69" s="3" t="inlineStr"/>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>For a line in a FILE you upload: which class is it?
+Answers: Stocks / ETFs · Bonds &amp; CDs · Alternatives · Cash. (Real estate and Personal property never come from a positions file.)</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Read the ticker and the name together. The first rule that matches wins:
+1. the ticker is a known MONEY-MARKET fund (VMFXX VMRXX SPAXX SPRXX SWVXX SNVXX FDRXX FZFXX TTTXX) → Stocks / ETFs
+2. the ticker is SGOV or BIL (short-Treasury ETFs) → Bonds &amp; CDs
+3. the NAME says what it is: MONEY MARKET / MMKT / MMF → Stocks / ETFs; CD / CERTIFICATE OF DEPOSIT / T-BILL / TREASURY BILL → Bonds &amp; CDs
+4. the symbol is an OPTION — the standard brokerage shape, root + 6-digit date + C or P + strike, e.g. AAPL250117C00220000 — or a date-style option, or the words PUT or CALL → Alternatives
+5. CRYPTO: ticker is BTC ETH GBTC ETHE IBIT FBTC BITO ARKB HODL, or the name says BITCOIN / ETHEREUM / CRYPTO → Alternatives. (COIN is deliberately absent — Coinbase is a company.)
+6. COMMODITY: ticker is GLD SLV IAU SGOL GLDM PPLT PALL USO UNG DBC PDBC, or the name says GOLD / SILVER / PLATINUM / PALLADIUM / COMMODITY — UNLESS the name also contains a company word (CORP, INC, LTD, PLC, MINING, MINERS, RESOURCES, COMPANY), because Barrick Gold Corp is a mining share, not bullion → Alternatives
+7. CURRENCY: the name says CURRENCY, CURRENCIES or FOREX → Alternatives
+8. FIXED INCOME: the name says BOND, NOTE, TREASURY, T-NOTE, MUNI or DEBENTURE → Bonds &amp; CDs
+9. nothing matched → Stocks / ETFs, the default for an ordinary ticker.
+A line whose symbol is literally CASH is handled before this and becomes Cash, but only when it carries a real balance.
+THE CURRENCY RULE IS BROKEN. It needs the word "currency" standing alone, and brokers shorten the name to CURRENCYSHARES — one word, so it never matches. There is no currency ticker list either, unlike crypto and commodities. FXE and FXY both import as ordinary shares.</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>ticker → symbol
+name / description → name</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>A file you download from your institution and upload — Fidelity, Vanguard, E*TRADE, Schwab and Chase all export a positions CSV, and none of them agree on the column names. So the columns are FOUND BY PATTERN, not assumed:
+• ticker  ← a header matching Symbol or Ticker
+• name    ← Description / Security / Name / Fund / Investment / Holding / Instrument
+• shares  ← Quantity / Shares / Qty / Units
+• value   ← Value / Market Value / Current Value
+• cost    ← Cost Per Share / Cost/Sh / Average Cost / Price Paid / Purchase Price / Unit Cost,
+            falling back to Cost Basis / Total Cost / Book Cost ÷ Quantity
+• date    ← Purchase Date / Acquired / Acquisition / Trade Date / Date
+The header row itself is found by looking for the first row that has BOTH a symbol and a quantity column, which is how the brokerage preamble ('Account Summary', 'As of 08/15/2026') is skipped. The importer reports back which header it used for each field, so a wrong guess is visible rather than silent.</t>
+        </is>
+      </c>
       <c r="G69" s="3" t="inlineStr"/>
-      <c r="H69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>probes/classification-crosspath.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DEFECT</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>A currency fund must classify as Alternatives however the broker abbreviates its name — the same way crypto and commodities already do, by ticker as well as by word.</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>Add a currency ticker list (FXE FXY FXB FXF FXA FXC UUP UDN) and loosen the word rule to match CURRENCYSHARES as well as CURRENCY. Ten minutes; the shape already exists twice over for crypto and commodities.</t>
+        </is>
+      </c>
+      <c r="M69" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N69" s="5" t="inlineStr">
+        <is>
           <t>importHoldings</t>
         </is>
       </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L69" s="3" t="inlineStr">
+      <c r="O69" s="5" t="inlineStr">
+        <is>
+          <t>AssetClass</t>
+        </is>
+      </c>
+      <c r="P69" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/import/holdingsImport.ts:154</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>FILE_DECODE</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>decodeCsvBase64</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>What is the text of the file that was picked?  Answer: the file as text.</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Decode the encoded file the picker hands over into plain text.</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>the picked file → b64</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>The file picker on the Import holdings screen. Files arrive encoded, not as text.</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>probes/classification-crosspath.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>ImportHoldings</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>ImportHoldings</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="5" t="inlineStr">
+        <is>
+          <t>ImportHoldings</t>
+        </is>
+      </c>
+      <c r="N70" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="5" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="P70" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/import/holdingsImport.ts:61</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>FILE_IMPORT</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>importHoldings</t>
         </is>
       </c>
-      <c r="M69" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="5" t="inlineStr">
-        <is>
-          <t>importHoldings</t>
-        </is>
-      </c>
-      <c r="O69" s="5" t="inlineStr">
-        <is>
-          <t>AssetClass</t>
-        </is>
-      </c>
-      <c r="P69" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/import/holdingsImport.ts:154</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr"/>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>decodeCsvBase64</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr"/>
-      <c r="D70" s="3" t="inlineStr"/>
-      <c r="E70" s="3" t="inlineStr"/>
-      <c r="F70" s="3" t="inlineStr"/>
-      <c r="G70" s="3" t="inlineStr"/>
-      <c r="H70" s="3" t="inlineStr"/>
-      <c r="I70" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>What holdings are in this file?  Answer: a list of holdings with shares, cost, value, date and class — plus how many rows were read, how many skipped, and which column was used for each field.</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Find the header row (the first with both a symbol and a quantity column), match each column by pattern, then for every data row:
+• skip TOTAL, SUBTOTAL, NET ACCOUNT and ACCOUNT rows — a file total must never import as a holding
+• skip anything with no shares AND no value
+• a CASH line imports only if it carries a real balance
+• cost per share comes from the per-share column, else total cost ÷ shares, else zero
+• class comes from CLASS_FROM_FILE
+• a ticker is kept ONLY for equities — a CD's CUSIP is never stored as a ticker, so it is never sent to the share-price feed
+Dates are normalised from either YYYY-MM-DD or MM/DD/YYYY; anything else is left blank rather than guessed.</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>the uploaded file → text
+(each column as listed opposite)</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>A file you download from your institution and upload — Fidelity, Vanguard, E*TRADE, Schwab and Chase all export a positions CSV, and none of them agree on the column names. So the columns are FOUND BY PATTERN, not assumed:
+• ticker  ← a header matching Symbol or Ticker
+• name    ← Description / Security / Name / Fund / Investment / Holding / Instrument
+• shares  ← Quantity / Shares / Qty / Units
+• value   ← Value / Market Value / Current Value
+• cost    ← Cost Per Share / Cost/Sh / Average Cost / Price Paid / Purchase Price / Unit Cost,
+            falling back to Cost Basis / Total Cost / Book Cost ÷ Quantity
+• date    ← Purchase Date / Acquired / Acquisition / Trade Date / Date
+The header row itself is found by looking for the first row that has BOTH a symbol and a quantity column, which is how the brokerage preamble ('Account Summary', 'As of 08/15/2026') is skipped. The importer reports back which header it used for each field, so a wrong guess is visible rather than silent.</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>probes/classification-crosspath.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
         <is>
           <t>ImportHoldings</t>
         </is>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="3" t="inlineStr">
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
         <is>
           <t>ImportHoldings</t>
         </is>
       </c>
-      <c r="L70" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="5" t="inlineStr">
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="5" t="inlineStr">
         <is>
           <t>ImportHoldings</t>
         </is>
       </c>
-      <c r="N70" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="5" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="P70" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/import/holdingsImport.ts:61</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="3" t="inlineStr"/>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>importHoldings</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr"/>
-      <c r="D71" s="3" t="inlineStr"/>
-      <c r="E71" s="3" t="inlineStr"/>
-      <c r="F71" s="3" t="inlineStr"/>
-      <c r="G71" s="3" t="inlineStr"/>
-      <c r="H71" s="3" t="inlineStr"/>
-      <c r="I71" s="3" t="inlineStr">
+      <c r="N71" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="5" t="inlineStr">
+        <is>
+          <t>ImportResult</t>
+        </is>
+      </c>
+      <c r="P71" s="5" t="inlineStr">
+        <is>
+          <t>src/domain/import/holdingsImport.ts:183</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>IMPORT_ACCOUNT_MATCH</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>matchImportAccount</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Which existing account should this file update?  Answer: one account, or none — in which case a new one is created.</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Compare the institution name with the institution on each existing investment account, ignoring case, spaces and punctuation ("E*TRADE" and "etrade" are the same). First match wins.
+The rule exists so that re-importing next quarter's file REFRESHES the account instead of twinning it — the same rule the connect flow uses. We never double an account.</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>existing accounts → accounts
+the file's institution → institution</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>The institution is chosen on the Import screen, or read from the file. The existing accounts are ours.</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr"/>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>probes/classification-crosspath.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
         <is>
           <t>ImportHoldings</t>
         </is>
       </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K71" s="3" t="inlineStr">
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
         <is>
           <t>ImportHoldings</t>
         </is>
       </c>
-      <c r="L71" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M71" s="5" t="inlineStr">
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="5" t="inlineStr">
         <is>
           <t>ImportHoldings</t>
         </is>
       </c>
-      <c r="N71" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="5" t="inlineStr">
-        <is>
-          <t>ImportResult</t>
-        </is>
-      </c>
-      <c r="P71" s="5" t="inlineStr">
-        <is>
-          <t>src/domain/import/holdingsImport.ts:183</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="3" t="inlineStr"/>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>matchImportAccount</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr"/>
-      <c r="D72" s="3" t="inlineStr"/>
-      <c r="E72" s="3" t="inlineStr"/>
-      <c r="F72" s="3" t="inlineStr"/>
-      <c r="G72" s="3" t="inlineStr"/>
-      <c r="H72" s="3" t="inlineStr"/>
-      <c r="I72" s="3" t="inlineStr">
-        <is>
-          <t>ImportHoldings</t>
-        </is>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="3" t="inlineStr">
-        <is>
-          <t>ImportHoldings</t>
-        </is>
-      </c>
-      <c r="L72" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="5" t="inlineStr">
-        <is>
-          <t>ImportHoldings</t>
-        </is>
-      </c>
       <c r="N72" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -5183,18 +5471,50 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr"/>
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>FILE_PARSE</t>
+        </is>
+      </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
           <t>parseCsv</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr"/>
-      <c r="D73" s="3" t="inlineStr"/>
-      <c r="E73" s="3" t="inlineStr"/>
-      <c r="F73" s="3" t="inlineStr"/>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>What are the rows and cells in this file?  Answer: a grid of text.</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Split into rows and cells, honouring quoted fields so a name containing a comma ("VANGUARD, INC") is not split into two cells.</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>the file text → text</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>A file you download from your institution and upload — Fidelity, Vanguard, E*TRADE, Schwab and Chase all export a positions CSV, and none of them agree on the column names. So the columns are FOUND BY PATTERN, not assumed:
+• ticker  ← a header matching Symbol or Ticker
+• name    ← Description / Security / Name / Fund / Investment / Holding / Instrument
+• shares  ← Quantity / Shares / Qty / Units
+• value   ← Value / Market Value / Current Value
+• cost    ← Cost Per Share / Cost/Sh / Average Cost / Price Paid / Purchase Price / Unit Cost,
+            falling back to Cost Basis / Total Cost / Book Cost ÷ Quantity
+• date    ← Purchase Date / Acquired / Acquisition / Trade Date / Date
+The header row itself is found by looking for the first row that has BOTH a symbol and a quantity column, which is how the brokerage preamble ('Account Summary', 'As of 08/15/2026') is skipped. The importer reports back which header it used for each field, so a wrong guess is visible rather than silent.</t>
+        </is>
+      </c>
       <c r="G73" s="3" t="inlineStr"/>
-      <c r="H73" s="3" t="inlineStr"/>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>probes/classification-crosspath.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
           <t>—</t>
@@ -6869,22 +7189,23 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>Does this look like a real ticker?</t>
+          <t>Could this be a real tradeable ticker?  Answers: yes · no.</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>1-6 letters, optionally a dot or dash plus 1-4 more</t>
+          <t>1 to 10 characters, letters and digits with dots or hyphens allowed, at least one letter, no spaces. Rejects the words TOTAL, CASH, SUBTOTAL, N/A, SYMBOL and TICKER.
+A nine-character CUSIP with digits is deliberately NOT plausible — a CD must never be sent to a share-price feed, where it would come back with no price and read as worth nothing.</t>
         </is>
       </c>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>the ticker string</t>
+          <t>the symbol → t</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>typed by the person, or from an import</t>
+          <t>Typed into the holding form, or read from the Symbol / Ticker column of an uploaded file.</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -6943,22 +7264,24 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>How old is this price, and should we warn about it?</t>
+          <t>How old is the price we are showing?  Answer: a phrase — "just now", "3h ago", "2 days ago", "not updated yet" — and whether it counts as stale.</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>days or hours since fetched; stale once four days old</t>
+          <t>Time since the last successful fetch, in words. Four days or more → stale. Four, because a long weekend or a holiday can put three days between two perfectly normal updates, and a false alarm teaches people to ignore the real one.
+Never fetched, unreadable, or dated in the future → STALE. Silence is not good news.</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>fetched-at timestamp · now</t>
+          <t>when it was fetched → fetchedAt
+now → now</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>the market-data cache</t>
+          <t>The market-data cache (Tiingo / Yahoo), keyed by ticker, with the timestamp of the last successful fetch. NOT from the broker — brokers send a price, but it is only as fresh as the last sync, so prices are fetched separately.</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
@@ -7017,22 +7340,25 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>Have we already ingested this activity?</t>
+          <t>What identifies this activity so it is not recorded twice?  Answer: one text key.</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>accountId + date + type + symbol + amount</t>
+          <t>The account id, then the broker's own id for the activity where it sends one; otherwise a key built from the date, type, ticker and amount together.
+The ACCOUNT ID COMES FIRST, which matters: if an account's internal id ever changes between connections, every key changes with it and the entire history re-imports as new. That is the leading remaining suspect for the $1.4m of contributions that Vanguard says never happened.</t>
         </is>
       </c>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>accountId · trade_date or settlement_date · type · symbol · amount</t>
+          <t>our account id → accountId
+the activity → a (its id, date, type, ticker, amount)</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>the broker payload plus our own account id</t>
+          <t>The broker feed. SnapTrade activities endpoint, one row per event, with `type` carrying the broker's own word for what happened (BUY, SELL, CONTRIBUTION, WITHDRAWAL, DIVIDEND, INTEREST, TRANSFER, OPTIONEXPIRATION…). Every institution uses its own vocabulary; this is the table that turns their word into ours.
+The account id is OURS, assigned when the account is first created.</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
@@ -7081,7 +7407,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t>Which of these activities are new since the last sync?</t>
+          <t>INGEST_DEDUPE</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
@@ -7091,22 +7417,26 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>keep an activity only if its key is unseen</t>
+          <t>Which of these activities are new since the last sync?  Answer: the new ones, plus the updated set of keys already seen.</t>
         </is>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>accountId · incoming activities · seenKeys (persisted)</t>
+          <t>Build a key for each incoming activity; keep only those whose key has not been seen before; add the kept keys to the seen set.
+The seen set PERSISTS ACROSS SYNCS — it is stored, not rebuilt each time. Deduping only within one batch would let every past activity re-import on the next connection.</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>seenKeys is stored between syncs</t>
+          <t>our account id → accountId
+the new activities → incoming
+keys already seen → seenKeys</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>Stateful ACROSS syncs, not just within one batch — otherwise every refresh would re-add the same trades and inflate contributions without limit. Repeats inside one batch are caught too. CORRECTED BY PROBE — I first documented it as batch-only.</t>
+          <t>The broker feed. SnapTrade activities endpoint, one row per event, with `type` carrying the broker's own word for what happened (BUY, SELL, CONTRIBUTION, WITHDRAWAL, DIVIDEND, INTEREST, TRANSFER, OPTIONEXPIRATION…). Every institution uses its own vocabulary; this is the table that turns their word into ours.
+seenKeys: stored by the app between syncs (snaptradeSeenKeys). Our own record, not the broker's.</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
@@ -7205,7 +7535,7 @@
     <row r="109">
       <c r="A109" s="3" t="inlineStr">
         <is>
-          <t>Is this broker activity money arriving, money leaving, or an internal move?</t>
+          <t>INGEST_ACTIVITY_TYPE</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
@@ -7215,22 +7545,31 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>a lookup table from the broker activity type to our transaction type</t>
+          <t>Is this broker activity money arriving from outside, money leaving, or a move inside the account?
+Answers: DEPOSIT · WITHDRAWAL · BUY · SELL · DIVIDEND · INTEREST · ADJUST (a note, no money) · SKIP (not recorded).</t>
         </is>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>activity type · option_symbol / option_type</t>
+          <t>The broker's own word decides, and only two of them mean money crossing the boundary:
+• CONTRIBUTION → DEPOSIT  — external money in
+• WITHDRAWAL → WITHDRAWAL — external money out
+• BUY → BUY, SELL → SELL  — INTERNAL. Cash became shares or shares became cash; nothing entered or left, so neither may ever be counted as a deposit or a withdrawal.
+• DIVIDEND → DIVIDEND, INTEREST → INTEREST — income, counted as income
+• option trades → BUY / SELL (internal), never deposits
+• OPTIONEXPIRATION, OPTIONEXERCISE → SKIP (no cash moves; shares arrive on the paired trade row)
+THIS IS THE RULE THAT BROKE VANGUARD. Deposits feed the personal-return figure, so anything wrongly called a deposit corrupts the return. The mapping table itself is correct — verified by probe.</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>the broker payload (SnapTrade activity)</t>
+          <t>the broker's word → type
+option markers → option_symbol, option_type</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>THE RULE THAT BROKE VANGUARD. Only CONTRIBUTION is external money IN and only WITHDRAWAL is external money OUT. A BUY or SELL is INTERNAL and must never become either, because deposits feed the personal-return figure and faking them corrupts it. Option trades map to BUY/SELL for the same reason. The table itself is CORRECT — verified by probe — so the $1.4m of phantom contributions enters somewhere else and is still being traced.</t>
+          <t>The broker feed. SnapTrade activities endpoint, one row per event, with `type` carrying the broker's own word for what happened (BUY, SELL, CONTRIBUTION, WITHDRAWAL, DIVIDEND, INTEREST, TRANSFER, OPTIONEXPIRATION…). Every institution uses its own vocabulary; this is the table that turns their word into ours.</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
@@ -7333,7 +7672,7 @@
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
         <is>
-          <t>What asset class is this holding, and what is it worth?</t>
+          <t>CLASS_FROM_BROKER</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
@@ -7343,22 +7682,37 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>assetClass = bonds if type=bnd or the DESCRIPTION looks fixed-income or the ticker is a T-bill ETF; alternatives if crypto; else stocks_etf</t>
+          <t>For a holding arriving from a CONNECTED broker: what class is it, and what is it worth?
+Class answers: Stocks / ETFs · Bonds &amp; CDs · Alternatives. (Cash is never an answer here — the uninvested balance is handled separately.)</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>symbol · description · type code · units · price · average_purchase_price · cash_equivalent · tax_lots</t>
+          <t>Read the broker's type code and the description text, first match wins:
+• type code is bnd → Bonds &amp; CDs
+• the description contains CD, CERTIFICATE OF DEP, TREASURY, or T-BILL → Bonds &amp; CDs
+• the description matches a rate-and-date shape — a percentage followed by DUE or a year, e.g. "4.00% DUE 2028" → Bonds &amp; CDs. This catches a bond whose description never uses the word "bond".
+• the ticker is SGOV or BIL (short-Treasury ETFs) → Bonds &amp; CDs
+• type code is crypto → Alternatives
+• everything else → Stocks / ETFs. That includes cs, et, mf, oef, cef, adr, money-market funds, and anything unrecognised.
+WHY THE DESCRIPTION MATTERS MORE THAN THE TYPE CODE: brokered CDs arrive from Vanguard with an ORDINARY EQUITY type code and a CUSIP instead of a ticker. The words in the description are the only thing identifying them. Verified against live E*TRADE and Vanguard downloads, 2026-08-04.
+WHAT IS MISSING: there is no commodity rule, no currency rule and no option-symbol rule here, though the file importer has all three. A gold fund, a spot-bitcoin ETF or an option written into the positions list is classed as an ordinary share.</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>all from the broker payload (SnapTrade position)</t>
+          <t>ticker → symbol.raw_symbol
+name → symbol.description
+broker type → symbol.type.code
+shares → units
+price → price
+cost → average_purchase_price
+purchase history → tax_lots[]</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>FOUNDER RULE 2026-08-04 — cash means cash only: anything paying dividends or interest goes to a MEASURED bucket, or the return maths silently loses its income. A CD arrives with a CUSIP and no bond type code, and its maturity is ONLY inside the description text, so the description is parsed. No symbol or zero units returns null rather than a zero-value holding.</t>
+          <t>SnapTrade positions payload, per holding: symbol.raw_symbol (the ticker), symbol.description (the name — where a CD's maturity and coupon actually live), symbol.type.code (the broker's own type: cs = common share, et = ETF, mf = mutual fund, oef/cef = open/closed-end fund, bnd = bond, crypto), units, price, average_purchase_price, cash_equivalent, tax_lots[].</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -7369,16 +7723,24 @@
       <c r="H111" s="3" t="inlineStr"/>
       <c r="I111" s="3" t="inlineStr">
         <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
-      <c r="J111" s="3" t="inlineStr"/>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>A holding must land in the same class whichever door it came through. A gold fund, a spot-bitcoin ETF and an option are Alternatives whether you uploaded a file or connected the broker.</t>
+        </is>
+      </c>
       <c r="K111" s="3" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L111" s="3" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>THE REAL FIX IS ONE CLASSIFIER, NOT TWO. The file path already knows commodities, crypto tickers, options and (once fixed) currencies; the broker path knows only the broker type code. Have the broker path call the same rules the file path uses, keeping the type code as a first pass where the broker is explicit. One engine, one answer — the whole point of this exercise.</t>
+        </is>
+      </c>
       <c r="M111" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -7457,7 +7819,7 @@
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>How much uninvested cash does this account really hold?</t>
+          <t>CASH_SLEEVE</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
@@ -7467,22 +7829,26 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>sleeve = balances.cash − Σ(cash-equivalent position values), floored only for rounding dust</t>
+          <t>How much genuinely uninvested cash does this account hold?  Answer: a dollar figure, never negative.</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
         <is>
-          <t>balances.cash · every position flagged cash_equivalent (price × shares)</t>
+          <t>the broker's cash figure − the value of any money-market funds listed as holdings.
+The broker counts a money-market fund in BOTH places — as a position and inside the cash balance — so adding them straight would double it. Floored at zero.
+BUT: the ingest step ALSO drops every cash-equivalent holding from the holdings list. So the fund is subtracted from cash AND removed from holdings, and the money is in neither place. This is the second half of the founder's F6, and it is a disappearance, not a mislabelling.</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>the broker payload</t>
+          <t>broker cash → balances.cash
+money-market holdings → positions where cash_equivalent is true</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>The broker's cash figure INCLUDES money-market funds that also appear as holdings, so they are subtracted or the same money is counted twice. A genuine margin debit stays NEGATIVE — flooring it overstated the account (audit fix); only sub-dollar dust clamps to zero.</t>
+          <t>SnapTrade positions payload, per holding: symbol.raw_symbol (the ticker), symbol.description (the name — where a CD's maturity and coupon actually live), symbol.type.code (the broker's own type: cs = common share, et = ETF, mf = mutual fund, oef/cef = open/closed-end fund, bnd = bond, crypto), units, price, average_purchase_price, cash_equivalent, tax_lots[].
+balances.cash: the account's cash balance in the same payload.</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
@@ -7815,22 +8181,27 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>If I sold today, how much of my gain is long-term?</t>
+          <t>If I sold this today, how much of the gain is long-term and how much short-term?  Answer: two dollar figures and their total.</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>per lot: shares × (price − cost_per_share); long if held ≥ 12 whole months, else short</t>
+          <t>Each LOT is judged on its OWN purchase date, not the position's: held twelve whole months or more → long-term, otherwise short-term. Gain per lot = shares × (price − cost per share).
+A lot with no cost recorded is SKIPPED, not treated as free shares — treating it as free would report the entire value as gain and tax it.
+An unreadable purchase date is treated as SHORT-term: the cautious side, since understating a tax bill is the worse mistake.</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>lots (shares, cost, purchase date) · price · today</t>
+          <t>each lot → lots[]
+price → the latest close
+today → now</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>lots from the broker or manual entry; price from market data</t>
+          <t>Tax lots. Broker: tax_lots[] on the position — original_purchase_date, quantity, purchased_price. Most brokers send NONE, in which case ONE synthetic lot is built from average_purchase_price so the gain stays exact while the per-lot history is honestly absent. File: the cost column (Cost Per Share / Average Cost / Price Paid), or Cost Basis ÷ Quantity when only a total is given. Typed: the Add holding form.
+The market-data cache (Tiingo / Yahoo), keyed by ticker, with the timestamp of the last successful fetch. NOT from the broker — brokers send a price, but it is only as fresh as the last sync, so prices are fetched separately.</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr">
@@ -7889,22 +8260,24 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>Roughly what tax would a sale cost?</t>
+          <t>What tax would that gain cost?  Answer: a dollar figure, never negative.</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>max(0,long)×ltRate + max(0,short)×ordinaryRate</t>
+          <t>long-term gain × the long-term rate + short-term gain × the short-term rate. Losses never produce a positive tax bill — the result is floored at zero.</t>
         </is>
       </c>
       <c r="E120" s="3" t="inlineStr">
         <is>
-          <t>long gain · short gain · long-term rate (default 15%) · ordinary rate (default 24%)</t>
+          <t>long gain → longGain
+short gain → shortGain
+rates → the tax settings</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>gains derived; rates from the user's own tax settings where set</t>
+          <t>The gains come from HOLDING_CAP_GAINS. The rates come from the tax settings — the person's own bracket where they have given it, otherwise a stated default.</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr">
@@ -7963,22 +8336,22 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>What did I pay for this holding?</t>
+          <t>What did I pay for this in total?  Answer: a dollar figure.</t>
         </is>
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>Σ over lots of (shares × cost_per_share), to the cent</t>
+          <t>Add shares × cost per share across every lot. A lot with no cost recorded contributes nothing, but its shares still count as owned.</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>the position's lots</t>
+          <t>each lot's shares and cost → lots[].shares, lots[].cost_per_share</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
-          <t>same as shares</t>
+          <t>Tax lots. Broker: tax_lots[] on the position — original_purchase_date, quantity, purchased_price. Most brokers send NONE, in which case ONE synthetic lot is built from average_purchase_price so the gain stays exact while the per-lot history is honestly absent. File: the cost column (Cost Per Share / Average Cost / Price Paid), or Cost Basis ÷ Quantity when only a total is given. Typed: the Add holding form.</t>
         </is>
       </c>
       <c r="G121" s="3" t="inlineStr">
@@ -8037,22 +8410,23 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>When did I first buy this?</t>
+          <t>When did I first buy this?  Answer: a date, or no answer when no lot carries one.</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>the oldest dated lot</t>
+          <t>The oldest purchase date across the lots. Nothing dated → no answer rather than today.</t>
         </is>
       </c>
       <c r="E122" s="3" t="inlineStr">
         <is>
-          <t>the position's lots</t>
+          <t>each lot's date → lots[].purchase_date</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>lots</t>
+          <t>Tax lots. Broker: tax_lots[] on the position — original_purchase_date, quantity, purchased_price. Most brokers send NONE, in which case ONE synthetic lot is built from average_purchase_price so the gain stays exact while the per-lot history is honestly absent. File: the cost column (Cost Per Share / Average Cost / Price Paid), or Cost Basis ÷ Quantity when only a total is given. Typed: the Add holding form.
+Most brokers send no purchase dates at all, so this is often genuinely unknown.</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -8273,22 +8647,22 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>What is the most recent price we have?</t>
+          <t>What is the most recent price we hold for this?  Answer: a price, or no answer when we have none.</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>the last point in the series</t>
+          <t>The last point in the stored price series. An empty series → no answer, never zero — a price we do not have and a price of nothing are different things.</t>
         </is>
       </c>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>price series</t>
+          <t>the price series → series.points[]</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>market-data service</t>
+          <t>The market-data cache (Tiingo / Yahoo), keyed by ticker, with the timestamp of the last successful fetch. NOT from the broker — brokers send a price, but it is only as fresh as the last sync, so prices are fetched separately.</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
@@ -8401,22 +8775,25 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>What is this holding worth today?</t>
+          <t>What is this holding worth right now?  Answer: a dollar figure.</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>total shares × latest price</t>
+          <t>shares × latest price.
+NO PRICE MEANS ZERO, NOT A GUESS. An unpriced holding contributes nothing and the screen says the price is missing — it is never valued at what it cost, which would silently report a gain of exactly zero.</t>
         </is>
       </c>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>total shares · latest close</t>
+          <t>shares → totalShares
+price → the latest close</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>price series from the market-data service</t>
+          <t>Tax lots. Broker: tax_lots[] on the position — original_purchase_date, quantity, purchased_price. Most brokers send NONE, in which case ONE synthetic lot is built from average_purchase_price so the gain stays exact while the per-lot history is honestly absent. File: the cost column (Cost Per Share / Average Cost / Price Paid), or Cost Basis ÷ Quantity when only a total is given. Typed: the Add holding form.
+The market-data cache (Tiingo / Yahoo), keyed by ticker, with the timestamp of the last successful fetch. NOT from the broker — brokers send a price, but it is only as fresh as the last sync, so prices are fetched separately.</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
@@ -8519,7 +8896,7 @@
     <row r="130">
       <c r="A130" s="3" t="inlineStr">
         <is>
-          <t>What did this holding do over the chosen window?</t>
+          <t>PERIOD_RETURN</t>
         </is>
       </c>
       <c r="B130" s="4" t="inlineStr">
@@ -8529,22 +8906,26 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>(latest close ÷ close at the window start) − 1</t>
+          <t>What did this holding do over the chosen period?  Answer: a percentage, or no answer when there is not enough price history.</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>price series · named period · now</t>
+          <t>latest price ÷ price at the start of the period − 1. Three-year returns are turned into a per-year figure so they sit fairly beside a one-year one.
+THE LIMIT: it accepts only the six NAMED periods. A statement covering, say, 1 April to 30 June cannot be asked for — so the app's return can never be lined up beside a brokerage statement.
+A sister function that DOES take any two dates (periodReturnSince) is already written and exported, and nothing in the app calls it.</t>
         </is>
       </c>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>price series from the market-data service; period from the chips on Performance</t>
+          <t>the price series → series
+the chosen chip → period
+today → now</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>It takes a NAMED period only (1M · 3M · 6M · YTD · 1Y · 3Y) and works the start date out itself. CONSEQUENCE WORTH KNOWING — it cannot answer an arbitrary window, so Vanguard's own statement range (1 Jan → 14 Aug) is not directly reproducible. No series returns null, never zero: "no data" and "no change" are different answers. CORRECTED BY PROBE — I first documented it as taking two dates.</t>
+          <t>The market-data cache (Tiingo / Yahoo), keyed by ticker, with the timestamp of the last successful fetch. NOT from the broker — brokers send a price, but it is only as fresh as the last sync, so prices are fetched separately.</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
@@ -8560,7 +8941,7 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>IT CANNOT ANSWER AN ARBITRARY WINDOW. Only 1M · 3M · 6M · YTD · 1Y · 3Y. That means a person can never line the app up against their own broker statement, which is the one comparison that would build trust. It should accept an explicit start and end date, with the named periods becoming presets over the same function.</t>
+          <t>A person must be able to ask for the exact window their statement covers, so the app's number can be laid beside the institution's and checked.</t>
         </is>
       </c>
       <c r="K130" s="3" t="inlineStr">
@@ -8570,7 +8951,7 @@
       </c>
       <c r="L130" s="3" t="inlineStr">
         <is>
-          <t>Add periodReturnBetween(series, startISO, endISO) as the real function, and make the six named periods thin presets that call it. Low risk — the existing callers keep working — and it is what lets the founder put the app beside his own statement on the same dates.</t>
+          <t>CHEAPER THAN IT LOOKS — the function already exists. periodReturnSince takes any two dates, is exported, and is called from nowhere. Wire it to a date-range option on the Performance chips. No new maths, and the Vanguard statement window becomes answerable.</t>
         </is>
       </c>
       <c r="M130" s="5" t="inlineStr">
@@ -8877,22 +9258,23 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>What date does the chosen window begin?</t>
+          <t>Which date does the chosen period start from?  Answer: a date. Periods offered: 1M · 3M · 6M · YTD · 1Y · 3Y.</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>1M/3M/6M subtract months · 1Y/3Y subtract years · YTD = 1 January of the current year</t>
+          <t>Count back from today by the named period. Year-to-date is the 1st of January of this year.</t>
         </is>
       </c>
       <c r="E136" s="3" t="inlineStr">
         <is>
-          <t>named period · today</t>
+          <t>the chosen chip → period
+today → now</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
-          <t>the chips on Performance</t>
+          <t>The period chips on the Performance screen. Today's date from the device clock.</t>
         </is>
       </c>
       <c r="G136" s="3" t="inlineStr">
@@ -9005,22 +9387,24 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>How has this holding done since I bought it?</t>
+          <t>How much am I up on this in percentage terms, since I bought it?  Answer: a percentage, or no answer when nothing was paid or no price is known.</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>unrealised gain ÷ cost basis</t>
+          <t>gain ÷ what I paid. SINCE PURCHASE and NOT annualised — so it is not comparable with a 1-year return and must never be shown beside one as if it were. Nothing paid → no answer, never infinity.</t>
         </is>
       </c>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>unrealised gain · cost basis</t>
+          <t>gain → unrealizedGain
+cost → costBasis</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>Tax lots. Broker: tax_lots[] on the position — original_purchase_date, quantity, purchased_price. Most brokers send NONE, in which case ONE synthetic lot is built from average_purchase_price so the gain stays exact while the per-lot history is honestly absent. File: the cost column (Cost Per Share / Average Cost / Price Paid), or Cost Basis ÷ Quantity when only a total is given. Typed: the Add holding form.
+The market-data cache (Tiingo / Yahoo), keyed by ticker, with the timestamp of the last successful fetch. NOT from the broker — brokers send a price, but it is only as fresh as the last sync, so prices are fetched separately.</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -9083,22 +9467,22 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>How many shares do I hold?</t>
+          <t>How many shares of this do I own?  Answer: a number of shares.</t>
         </is>
       </c>
       <c r="D139" s="3" t="inlineStr">
         <is>
-          <t>Σ over lots of lot.shares</t>
+          <t>Add the shares across every purchase lot. A position is the SUM OF ITS LOTS, never one stored figure — that is what makes gain-since-purchase possible.</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>the position's lots</t>
+          <t>each lot's shares → lots[].shares</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
         <is>
-          <t>broker payload, file import, or manual entry</t>
+          <t>Tax lots. Broker: tax_lots[] on the position — original_purchase_date, quantity, purchased_price. Most brokers send NONE, in which case ONE synthetic lot is built from average_purchase_price so the gain stays exact while the per-lot history is honestly absent. File: the cost column (Cost Per Share / Average Cost / Price Paid), or Cost Basis ÷ Quantity when only a total is given. Typed: the Add holding form.</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
@@ -9157,22 +9541,24 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>How much am I up or down on this holding?</t>
+          <t>How much am I up or down on this?  Answer: a dollar figure, positive or negative.</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>market value − cost basis</t>
+          <t>what it is worth − what I paid. A loss is a real negative and is never floored at zero. No price → zero, not a fabricated loss.</t>
         </is>
       </c>
       <c r="E140" s="3" t="inlineStr">
         <is>
-          <t>market value · cost basis</t>
+          <t>value → marketValue
+cost → costBasis</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>Tax lots. Broker: tax_lots[] on the position — original_purchase_date, quantity, purchased_price. Most brokers send NONE, in which case ONE synthetic lot is built from average_purchase_price so the gain stays exact while the per-lot history is honestly absent. File: the cost column (Cost Per Share / Average Cost / Price Paid), or Cost Basis ÷ Quantity when only a total is given. Typed: the Add holding form.
+The market-data cache (Tiingo / Yahoo), keyed by ticker, with the timestamp of the last successful fetch. NOT from the broker — brokers send a price, but it is only as fresh as the last sync, so prices are fetched separately.</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -10317,12 +10703,12 @@
   <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
     <col width="52" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
@@ -10360,17 +10746,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Formula</t>
+          <t>Formula — the actual rules</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Input variables</t>
+          <t>Input variables (raw → ours)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Source of each</t>
+          <t>Where each comes from — file, feed, field</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -10704,6 +11090,632 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001B4D8F"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="60" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>HOW A LINE BECOMES A CLASS — every row below is a real holding as an institution actually sends it, run through the live code. The last two columns are what the app decides, and they do not always agree: a holding you UPLOAD and the same holding from a CONNECTED broker go through two different classifiers. Where they differ, the row is a defect and it is named as one. Proved by probes/classification-crosspath.probe.test.ts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>What you hold</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Ticker as sent</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Name / description as sent</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Which rule fires</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Class from a FILE you upload</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Class from a CONNECTED broker</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Agree?</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>A share in a company</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>APPLE INC</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>nothing else matches → the default is Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>A stock-market ETF</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>VTI</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>VANGUARD TOTAL STOCK MARKET ETF</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>nothing else matches → the default is Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>A money-market fund</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>VMFXX</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>VANGUARD FEDERAL MONEY MARKET FUND</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>the ticker is on the money-market list, AND the name contains MONEY MARKET → Stocks / ETFs (founder rule 2026-08-04: it pays dividends, so it must be measured)</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Uninvested cash at the broker</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>SETTLEMENT FUND / SWEEP</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>the name contains SWEEP or SETTLEMENT → Cash. This is the only thing that counts as cash.</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>A brokered CD</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>06418AAA1</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>KEYBANK NA 4.00% CD 08/24/26</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>the description contains CD → Bonds &amp; CDs. Note it arrives with an equity type code and a CUSIP, not a ticker — the words in the description are the only thing that identifies it.</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Bonds &amp; CDs</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Bonds &amp; CDs</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>A Treasury bill</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>912797TZ8</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>US TREASURY BILL 02/12/27</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>the description contains TREASURY or T-BILL → Bonds &amp; CDs</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Bonds &amp; CDs</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Bonds &amp; CDs</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>A short-Treasury ETF</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>SGOV</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>ISHARES 0-3 MONTH TREASURY BOND ETF</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>the ticker is on the T-bill ETF list (SGOV, BIL) → Bonds &amp; CDs</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Bonds &amp; CDs</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Bonds &amp; CDs</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>A corporate bond</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>APPLE INC 3.85% DUE 2043</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>a percentage followed by DUE or a year → Bonds &amp; CDs. This pattern is what catches a bond whose description never uses the word 'bond'.</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>Bonds &amp; CDs</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Bonds &amp; CDs</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Bitcoin held at the broker</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>BTC</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>BITCOIN</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>the broker's own type code says crypto → Alternatives</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Alternatives</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Alternatives</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>A gold fund</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>SPDR GOLD SHARES</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>FILE: the ticker is on the commodity list → Alternatives. BROKER: no commodity rule exists, so it falls through to the equity default.</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Alternatives</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>NO — defect</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>A spot-bitcoin ETF</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>IBIT</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>ISHARES BITCOIN TRUST</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>FILE: the ticker is on the crypto list → Alternatives. BROKER: it arrives with the ordinary equity type code, and only the type code is checked.</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Alternatives</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>NO — defect</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>An option contract</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>AAPL250117C00220000</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>AAPL JAN 17 25 CALL 220</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>FILE: the symbol matches the standard option shape (root + date + C/P + strike) → Alternatives. BROKER: options normally arrive on a separate feed and are handled correctly there; one written into the ordinary positions list is read as a share.</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Alternatives</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>NO — defect</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>A currency fund</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>FXE</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>INVESCO CURRENCYSHARES EURO TRUST</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>NEITHER path catches it. The only currency rule looks for the word CURRENCY standing alone, and brokers shorten the name to CURRENCYSHARES — one word. There is no currency ticker list, unlike crypto and commodities.</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>NO — both wrong</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>A gold mining company</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>GOLD</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>BARRICK GOLD CORP</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>the name contains GOLD, but also CORP — a company word, so the commodity rule is deliberately skipped and it stays a share. This one is RIGHT and worth keeping.</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>A whole account with nothing itemised</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>e.g. a 401(k) with no holdings listed</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>no positions, no explicit class → Unclassified. It is NOT assumed to be stocks — the honest answer is that we do not know what is inside it.</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00854F0B"/>
@@ -10721,34 +11733,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>FIELD DICTIONARY — one canonical name per concept, used identically on every screen. Filled during Phase 3, for founder approval BEFORE any renaming happens.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>Canonical name</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>What it means, plainly</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>Names it replaces</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>Where it is shown</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>Decided</t>
         </is>
@@ -10762,7 +11774,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00A32D2D"/>
@@ -10779,93 +11791,84 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>OPEN QUESTIONS — anything I could not settle from the code alone. A question here is better than a guess in the inventory.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>Why it matters</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Where do $1,462,462 of "contributions" come from, when Vanguard says $0 moved all year?</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>It is the single largest wrong number found. Until it is traced, the Performance walk cannot be trusted on any account.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>RULED OUT SO FAR, each by probe or by reading the code: the activity mapping table is correct (BUY stays BUY; only CONTRIBUTION becomes a deposit) · option trades stay internal · dedupe persists across syncs via snaptradeSeenKeys and is keyed by account · nothing in the connect flow creates OPENING_CASH or OPENING_POSITION rows. STILL OPEN — needs the founder's actual transaction ledger to settle. Prime remaining suspect: if an account's internal id changes between connections, every activity key changes with it and the whole history re-ingests.</t>
-        </is>
-      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>The account id is first in the dedupe key. If a broker's internal account id changes between connections, every key changes and the whole history re-imports. Did the Vanguard account get disconnected and reconnected at any point?</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>This is the last standing explanation for the $1.4m of contributions Vanguard says never happened. Everything else has been ruled out by running the code: the activity mapping is correct, option trades stay internal, the dedupe set persists across syncs, and nothing in the connect flow writes opening rows.</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Money-market funds: shown as a holding, or folded into the cash sleeve? Both currently happen.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>For a broker that flags the fund, the money is subtracted from cash AND dropped from holdings — it is in neither place.</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Recommend showing it as a holding and keeping the netting, per the 2026-08-04 cash-means-cash rule. Founder decision.</t>
-        </is>
-      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>You named FIVE asset classes. The code has SEVEN. Which do you want?
+Yours: Stocks and Funds · Bonds and CDs · Alternatives · Cash or Cash Equivalent · Personal Property.
+The code's: Cash · Bonds &amp; CDs · Stocks / ETFs · Alternatives · Real estate · Personal property · Unclassified.
+Two real differences: the code separates Real estate from Personal property (you have one class for both), and it has "Unclassified" for an account whose contents we were never told.</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>This is the top of the taxonomy — every total, every donut slice and every projection sits under it. It has to be settled before names are fixed, not after.</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Should Performance be able to answer an arbitrary date range?</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Today it offers only 1M/3M/6M/YTD/1Y/3Y, so the app can never be lined up against a broker statement, which is the one comparison that would build trust.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Recommend yes — add a start/end function and make the named periods presets over it.</t>
-        </is>
-      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Your wording was "Cash or Cash Equivalent". A money-market fund IS a cash equivalent in ordinary usage — but your own rule of 2026-08-04 moved money-market funds OUT of cash and into Stocks / ETFs, so their dividends get measured. Is that rule still what you want?</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>It decides where VMFXX lands, which is the founder finding F6. The rules currently disagree with themselves: the class rule says measured, the on-screen grouping still says Cash.</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -149,9 +149,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -724,7 +721,7 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CALCULATION INVENTORY · Phase 1 — Net worth, Performance and the 8 screens they open · 158 calculations · generated from commit 247201d on 2026-08-17  ⚠ TREE WAS DIRTY. EVERY FORMULA HERE DESCRIBES THE CODE AS IT IS TODAY, BUGS INCLUDED — you cannot fix what you have not described, and a probe can only execute what exists. Where the current behaviour is wrong, Status says DEFECT and the corrected version sits in WHAT IT SHOULD BE; the difference between those two columns is the work list. GREY columns are generated from the code and overwritten on every regeneration — never edit them. CREAM columns are written by hand and preserved. A row is not documented until its probe passes.</t>
+          <t>CALCULATION INVENTORY · Phase 1 — Net worth, Performance and the 8 screens they open · 158 calculations · generated from commit 09c3aaa on 2026-08-17  ⚠ TREE WAS DIRTY. EVERY FORMULA HERE DESCRIBES THE CODE AS IT IS TODAY, BUGS INCLUDED — you cannot fix what you have not described, and a probe can only execute what exists. Where the current behaviour is wrong, Status says DEFECT and the corrected version sits in WHAT IT SHOULD BE; the difference between those two columns is the work list. GREY columns are generated from the code and overwritten on every regeneration — never edit them. CREAM columns are written by hand and preserved. A row is not documented until its probe passes.</t>
         </is>
       </c>
     </row>
@@ -11781,7 +11778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -11819,57 +11816,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>The account id is first in the dedupe key. If a broker's internal account id changes between connections, every key changes and the whole history re-imports. Did the Vanguard account get disconnected and reconnected at any point?</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>This is the last standing explanation for the $1.4m of contributions Vanguard says never happened. Everything else has been ruled out by running the code: the activity mapping is correct, option trades stay internal, the dedupe set persists across syncs, and nothing in the connect flow writes opening rows.</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>You named FIVE asset classes. The code has SEVEN. Which do you want?
-Yours: Stocks and Funds · Bonds and CDs · Alternatives · Cash or Cash Equivalent · Personal Property.
-The code's: Cash · Bonds &amp; CDs · Stocks / ETFs · Alternatives · Real estate · Personal property · Unclassified.
-Two real differences: the code separates Real estate from Personal property (you have one class for both), and it has "Unclassified" for an account whose contents we were never told.</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>This is the top of the taxonomy — every total, every donut slice and every projection sits under it. It has to be settled before names are fixed, not after.</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Your wording was "Cash or Cash Equivalent". A money-market fund IS a cash equivalent in ordinary usage — but your own rule of 2026-08-04 moved money-market funds OUT of cash and into Stocks / ETFs, so their dividends get measured. Is that rule still what you want?</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>It decides where VMFXX lands, which is the founder finding F6. The rules currently disagree with themselves: the class rule says measured, the on-screen grouping still says Cash.</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr"/>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>How much money sits in each of the seven classes?  Answer: a dollar figure for each of Cash · Bonds &amp; CDs · Stocks / ETFs · Alternatives · Real estate · Personal property · Unclassified.</t>
+          <t>How much money sits in each of the seven classes?  Answer: a dollar figure for each of Cash · Bonds &amp; CDs · Stocks / Funds · Alternatives · Real estate · Personal property · Unclassified.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1388,7 +1388,7 @@
       <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Which of the seven classes does a whole ACCOUNT belong to?
-The answer is one of: Cash · Bonds &amp; CDs · Stocks / ETFs · Alternatives · Real estate · Personal property · Unclassified (we were never told what is inside it).</t>
+The answer is one of: Cash · Bonds &amp; CDs · Stocks / Funds · Alternatives · Real estate · Personal property · Unclassified (we were never told what is inside it).</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1397,16 +1397,16 @@
 1. A class was set by hand, or written by the file importer → use it. A person's own answer is never overridden.
 2. Otherwise read the NAME:
    • contains SWEEP or SETTLEMENT → Cash
-   • contains MONEY MARKET / MMKT / MMF, or IS one of 17 known money-market tickers (VMFXX VMRXX VUSXX VMSXX SPAXX FDRXX FZFXX FZDXX SPRXX SWVXX SNVXX SNSXX SWGXX TTTXX MVRXX GOFXX FGXXX) → Stocks / ETFs
+   • contains MONEY MARKET / MMKT / MMF, or IS one of 17 known money-market tickers (VMFXX VMRXX VUSXX VMSXX SPAXX FDRXX FZFXX FZDXX SPRXX SWVXX SNVXX SNSXX SWGXX TTTXX MVRXX GOFXX FGXXX) → Stocks / Funds
    • contains CD / CERTIFICATE OF DEPOSIT / T-BILL / TREASURY BILL → Bonds &amp; CDs
 3. Otherwise, if it carries a maturity date → Bonds &amp; CDs (that is what a maturity means)
 4. Otherwise read the account TYPE picked on Add account:
    Checking · Savings · High-yield savings · Cash management → Cash
-   Money market → Stocks / ETFs   |   CD · Fixed income → Bonds &amp; CDs
-   Stocks &amp; ETFs → Stocks / ETFs
+   Money market → Stocks / Funds   |   CD · Fixed income → Bonds &amp; CDs
+   Stocks &amp; ETFs → Stocks / Funds
    Private equity · Hedge funds · Commodities · Crypto · Annuities · Options · Other → Alternatives
    Home → Real estate   |   Vehicle → Personal property
-5. Otherwise, if holdings are listed inside it → Stocks / ETFs
+5. Otherwise, if holdings are listed inside it → Stocks / Funds
 6. Otherwise, a cash wrapper → Cash; a property wrapper → Real estate
 7. Otherwise → Unclassified. NOT "stocks" — we do not guess what is in a 401(k) we cannot see.</t>
         </is>
@@ -2242,15 +2242,15 @@
       <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Reading the NAME alone, is this cash, a money-market fund, or a CD / T-bill?
-Answers: Cash · Stocks / ETFs · Bonds &amp; CDs · no answer at all (the name says nothing, so the next rule decides).</t>
+Answers: Cash · Stocks / Funds · Bonds &amp; CDs · no answer at all (the name says nothing, so the next rule decides).</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Applied to the name text, in this order:
 • the word SWEEP or SETTLEMENT → Cash. This is the ONLY thing that counts as cash — uninvested money sitting at the broker.
-• MONEY MARKET / MONEY-MARKET / MMKT / MMF → Stocks / ETFs
-• any word in the name is a known money-market ticker (17 of them) → Stocks / ETFs. This second test exists because a broker that sends only a ticker sends no words to match on — which is exactly how VMFXX got back into Cash.
+• MONEY MARKET / MONEY-MARKET / MMKT / MMF → Stocks / Funds
+• any word in the name is a known money-market ticker (17 of them) → Stocks / Funds. This second test exists because a broker that sends only a ticker sends no words to match on — which is exactly how VMFXX got back into Cash.
 • CD / CERTIFICATE OF DEPOSIT / T-BILL / TREASURY BILL → Bonds &amp; CDs
 • nothing matched → no answer, and the caller moves on to its next rule.</t>
         </is>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Add up the balances of every account whose class is Stocks / ETFs, Bonds &amp; CDs, Alternatives or Unclassified. Excludes cash, the house and the car.</t>
+          <t>Add up the balances of every account whose class is Stocks / Funds, Bonds &amp; CDs, Alternatives or Unclassified. Excludes cash, the house and the car.</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -2484,7 +2484,7 @@
         <is>
           <t>Look the account type up in our own ASSET_KINDS table and ask whether its bucket is CASH.
 Checking · Savings · High-yield savings · Money market · CD → yes. Everything else → no.
-THIS DISAGREES WITH THE CLASS RULE ABOVE. Money market and CD are marked CASH here, while ASSET_CLASS_OF_ACCOUNT calls them Stocks / ETFs and Bonds &amp; CDs. Net worth groups by THIS, so a money-market fund still reads as cash on the screen — the founder's F6.</t>
+THIS DISAGREES WITH THE CLASS RULE ABOVE. Money market and CD are marked CASH here, while ASSET_CLASS_OF_ACCOUNT calls them Stocks / Funds and Bonds &amp; CDs. Net worth groups by THIS, so a money-market fund still reads as cash on the screen — the founder's F6.</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -5130,21 +5130,21 @@
       <c r="C69" s="3" t="inlineStr">
         <is>
           <t>For a line in a FILE you upload: which class is it?
-Answers: Stocks / ETFs · Bonds &amp; CDs · Alternatives · Cash. (Real estate and Personal property never come from a positions file.)</t>
+Answers: Stocks / Funds · Bonds &amp; CDs · Alternatives · Cash. (Real estate and Personal property never come from a positions file.)</t>
         </is>
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Read the ticker and the name together. The first rule that matches wins:
-1. the ticker is a known MONEY-MARKET fund (VMFXX VMRXX SPAXX SPRXX SWVXX SNVXX FDRXX FZFXX TTTXX) → Stocks / ETFs
+1. the ticker is a known MONEY-MARKET fund (VMFXX VMRXX SPAXX SPRXX SWVXX SNVXX FDRXX FZFXX TTTXX) → Stocks / Funds
 2. the ticker is SGOV or BIL (short-Treasury ETFs) → Bonds &amp; CDs
-3. the NAME says what it is: MONEY MARKET / MMKT / MMF → Stocks / ETFs; CD / CERTIFICATE OF DEPOSIT / T-BILL / TREASURY BILL → Bonds &amp; CDs
+3. the NAME says what it is: MONEY MARKET / MMKT / MMF → Stocks / Funds; CD / CERTIFICATE OF DEPOSIT / T-BILL / TREASURY BILL → Bonds &amp; CDs
 4. the symbol is an OPTION — the standard brokerage shape, root + 6-digit date + C or P + strike, e.g. AAPL250117C00220000 — or a date-style option, or the words PUT or CALL → Alternatives
 5. CRYPTO: ticker is BTC ETH GBTC ETHE IBIT FBTC BITO ARKB HODL, or the name says BITCOIN / ETHEREUM / CRYPTO → Alternatives. (COIN is deliberately absent — Coinbase is a company.)
 6. COMMODITY: ticker is GLD SLV IAU SGOL GLDM PPLT PALL USO UNG DBC PDBC, or the name says GOLD / SILVER / PLATINUM / PALLADIUM / COMMODITY — UNLESS the name also contains a company word (CORP, INC, LTD, PLC, MINING, MINERS, RESOURCES, COMPANY), because Barrick Gold Corp is a mining share, not bullion → Alternatives
 7. CURRENCY: the name says CURRENCY, CURRENCIES or FOREX → Alternatives
 8. FIXED INCOME: the name says BOND, NOTE, TREASURY, T-NOTE, MUNI or DEBENTURE → Bonds &amp; CDs
-9. nothing matched → Stocks / ETFs, the default for an ordinary ticker.
+9. nothing matched → Stocks / Funds, the default for an ordinary ticker.
 A line whose symbol is literally CASH is handled before this and becomes Cash, but only when it carries a real balance.
 THE CURRENCY RULE IS BROKEN. It needs the word "currency" standing alone, and brokers shorten the name to CURRENCYSHARES — one word, so it never matches. There is no currency ticker list either, unlike crypto and commodities. FXE and FXY both import as ordinary shares.</t>
         </is>
@@ -7680,7 +7680,7 @@
       <c r="C111" s="3" t="inlineStr">
         <is>
           <t>For a holding arriving from a CONNECTED broker: what class is it, and what is it worth?
-Class answers: Stocks / ETFs · Bonds &amp; CDs · Alternatives. (Cash is never an answer here — the uninvested balance is handled separately.)</t>
+Class answers: Stocks / Funds · Bonds &amp; CDs · Alternatives. (Cash is never an answer here — the uninvested balance is handled separately.)</t>
         </is>
       </c>
       <c r="D111" s="3" t="inlineStr">
@@ -7691,7 +7691,7 @@
 • the description matches a rate-and-date shape — a percentage followed by DUE or a year, e.g. "4.00% DUE 2028" → Bonds &amp; CDs. This catches a bond whose description never uses the word "bond".
 • the ticker is SGOV or BIL (short-Treasury ETFs) → Bonds &amp; CDs
 • type code is crypto → Alternatives
-• everything else → Stocks / ETFs. That includes cs, et, mf, oef, cef, adr, money-market funds, and anything unrecognised.
+• everything else → Stocks / Funds. That includes cs, et, mf, oef, cef, adr, money-market funds, and anything unrecognised.
 WHY THE DESCRIPTION MATTERS MORE THAN THE TYPE CODE: brokered CDs arrive from Vanguard with an ORDINARY EQUITY type code and a CUSIP instead of a ticker. The words in the description are the only thing identifying them. Verified against live E*TRADE and Vanguard downloads, 2026-08-04.
 WHAT IS MISSING: there is no commodity rule, no currency rule and no option-symbol rule here, though the file importer has all three. A gold fund, a spot-bitcoin ETF or an option written into the positions list is classed as an ordinary share.</t>
         </is>
@@ -11167,17 +11167,17 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>nothing else matches → the default is Stocks / ETFs</t>
+          <t>nothing else matches → the default is Stocks / Funds</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>Stocks / ETFs</t>
+          <t>Stocks / Funds</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>Stocks / ETFs</t>
+          <t>Stocks / Funds</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
@@ -11204,17 +11204,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>nothing else matches → the default is Stocks / ETFs</t>
+          <t>nothing else matches → the default is Stocks / Funds</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Stocks / ETFs</t>
+          <t>Stocks / Funds</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>Stocks / ETFs</t>
+          <t>Stocks / Funds</t>
         </is>
       </c>
       <c r="G4" s="7" t="inlineStr">
@@ -11241,17 +11241,17 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>the ticker is on the money-market list, AND the name contains MONEY MARKET → Stocks / ETFs (founder rule 2026-08-04: it pays dividends, so it must be measured)</t>
+          <t>the ticker is on the money-market list, AND the name contains MONEY MARKET → Stocks / Funds (founder rule 2026-08-04: it pays dividends, so it must be measured)</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Stocks / ETFs</t>
+          <t>Stocks / Funds</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Stocks / ETFs</t>
+          <t>Stocks / Funds</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>Stocks / ETFs</t>
+          <t>Stocks / Funds</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -11547,7 +11547,7 @@
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>Stocks / ETFs</t>
+          <t>Stocks / Funds</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -11584,7 +11584,7 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>Stocks / ETFs</t>
+          <t>Stocks / Funds</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
@@ -11616,12 +11616,12 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Stocks / ETFs</t>
+          <t>Stocks / Funds</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>Stocks / ETFs</t>
+          <t>Stocks / Funds</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -11653,12 +11653,12 @@
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>Stocks / ETFs</t>
+          <t>Stocks / Funds</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>Stocks / ETFs</t>
+          <t>Stocks / Funds</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -59,7 +59,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -79,6 +79,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEEEE9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F0FB"/>
       </patternFill>
     </fill>
     <fill>
@@ -118,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -132,16 +137,19 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -295,20 +303,30 @@
     </comment>
     <comment ref="M2" authorId="0" shapeId="0">
       <text>
-        <t>Screens in scope that import it directly.</t>
+        <t>YOURS. Write anything here - a question, a disagreement, 'this is not what I meant', 'where does this number show up'. Nothing I run ever writes to this column or clears it; it survives every regeneration. You can also attach an Excel comment to ANY cell on any tab and I will read it - comments are preserved too.</t>
       </text>
     </comment>
     <comment ref="N2" authorId="0" shapeId="0">
       <text>
-        <t>Other calculations that use it.</t>
+        <t>YOURS. For rows where Fix needed? is Y: FIX / LEAVE / LATER, or your own word. This is the column I work from - it is your answer to my recommendation, and I will not start a fix that does not have one.</t>
       </text>
     </comment>
     <comment ref="O2" authorId="0" shapeId="0">
       <text>
+        <t>Screens in scope that import it directly.</t>
+      </text>
+    </comment>
+    <comment ref="P2" authorId="0" shapeId="0">
+      <text>
+        <t>Other calculations that use it.</t>
+      </text>
+    </comment>
+    <comment ref="Q2" authorId="0" shapeId="0">
+      <text>
         <t>Declared return type.</t>
       </text>
     </comment>
-    <comment ref="P2" authorId="0" shapeId="0">
+    <comment ref="R2" authorId="0" shapeId="0">
       <text>
         <t>file:line at the stamped commit.</t>
       </text>
@@ -385,20 +403,30 @@
     </comment>
     <comment ref="M2" authorId="0" shapeId="0">
       <text>
-        <t>Screens in scope that import it directly.</t>
+        <t>YOURS. Write anything here - a question, a disagreement, 'this is not what I meant', 'where does this number show up'. Nothing I run ever writes to this column or clears it; it survives every regeneration. You can also attach an Excel comment to ANY cell on any tab and I will read it - comments are preserved too.</t>
       </text>
     </comment>
     <comment ref="N2" authorId="0" shapeId="0">
       <text>
-        <t>Other calculations that use it.</t>
+        <t>YOURS. For rows where Fix needed? is Y: FIX / LEAVE / LATER, or your own word. This is the column I work from - it is your answer to my recommendation, and I will not start a fix that does not have one.</t>
       </text>
     </comment>
     <comment ref="O2" authorId="0" shapeId="0">
       <text>
+        <t>Screens in scope that import it directly.</t>
+      </text>
+    </comment>
+    <comment ref="P2" authorId="0" shapeId="0">
+      <text>
+        <t>Other calculations that use it.</t>
+      </text>
+    </comment>
+    <comment ref="Q2" authorId="0" shapeId="0">
+      <text>
         <t>Declared return type.</t>
       </text>
     </comment>
-    <comment ref="P2" authorId="0" shapeId="0">
+    <comment ref="R2" authorId="0" shapeId="0">
       <text>
         <t>file:line at the stamped commit.</t>
       </text>
@@ -697,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P160"/>
+  <dimension ref="A1:R160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -712,16 +740,18 @@
     <col width="52" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="52" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="26" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CALCULATION INVENTORY · Phase 1 — Net worth, Performance and the 8 screens they open · 158 calculations · generated from commit 09c3aaa on 2026-08-17  ⚠ TREE WAS DIRTY. EVERY FORMULA HERE DESCRIBES THE CODE AS IT IS TODAY, BUGS INCLUDED — you cannot fix what you have not described, and a probe can only execute what exists. Where the current behaviour is wrong, Status says DEFECT and the corrected version sits in WHAT IT SHOULD BE; the difference between those two columns is the work list. GREY columns are generated from the code and overwritten on every regeneration — never edit them. CREAM columns are written by hand and preserved. A row is not documented until its probe passes.</t>
+          <t>CALCULATION INVENTORY · Phase 1 — Net worth, Performance and the 8 screens they open · 158 calculations · generated from commit cf71d68 on 2026-08-17  ⚠ TREE WAS DIRTY. EVERY FORMULA HERE DESCRIBES THE CODE AS IT IS TODAY, BUGS INCLUDED — you cannot fix what you have not described, and a probe can only execute what exists. Where the current behaviour is wrong, Status says DEFECT and the corrected version sits in WHAT IT SHOULD BE; the difference between those two columns is the work list. GREY columns are generated from the code and overwritten on every regeneration — never edit them. CREAM columns are written by hand and preserved. THE TWO BLUE COLUMNS ARE YOURS - write your questions and your verdict there, and nothing I run will ever touch them. You can also attach an Excel comment to ANY cell on any tab; comments survive regeneration and I read them. A row is not documented until its probe passes.</t>
         </is>
       </c>
     </row>
@@ -788,20 +818,30 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
+          <t>YOUR COMMENT / QUESTION</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>YOUR VERDICT</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
           <t>Screens</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Called by</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>Returns</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -840,22 +880,24 @@
           <t>currencySymbol</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
         <is>
           <t>currencySymbol</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>src/domain/_shared/money.ts:49</t>
         </is>
@@ -894,22 +936,24 @@
           <t>money</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>money</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>src/domain/_shared/money.ts:58</t>
         </is>
@@ -948,22 +992,24 @@
           <t>money2</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
         <is>
           <t>money2</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>src/domain/_shared/money.ts:74</t>
         </is>
@@ -1002,22 +1048,24 @@
           <t>assetsFromOnboarding, debtsFromOnboarding, ingestSync</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="6" t="inlineStr">
         <is>
           <t>ImportHoldings</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="P6" s="6" t="inlineStr">
         <is>
           <t>assetsFromOnboarding, debtsFromOnboarding, ingestSync</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>EntityId</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>src/domain/_shared/ids.ts:6</t>
         </is>
@@ -1056,22 +1104,24 @@
           <t>assetsFromOnboarding, debtsFromOnboarding, employerMatchMonthly, equityRowValue, monthlyContributionsFromOnboarding, plannedMonthlySpend, retirementIncomeMonthly, retirementSpendMonthly, rsuAnnual, salaryGrossByMonth, stateRateOf, tipsAnnual, totalGrossAnnual</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
         <is>
           <t>assetsFromOnboarding, debtsFromOnboarding, employerMatchMonthly, equityRowValue, monthlyContributionsFromOnboarding, plannedMonthlySpend, retirementIncomeMonthly, retirementSpendMonthly, rsuAnnual, salaryGrossByMonth, stateRateOf, tipsAnnual, totalGrossAnnual</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>src/domain/_shared/num.ts:4</t>
         </is>
@@ -1110,22 +1160,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="6" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr">
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>src/domain/alternatives/index.ts:15</t>
         </is>
@@ -1164,22 +1216,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="6" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="P9" s="5" t="inlineStr">
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:116</t>
         </is>
@@ -1218,22 +1272,24 @@
           <t>assetAllocation, cashTotal</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="M10" s="5" t="inlineStr"/>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="6" t="inlineStr">
         <is>
           <t>AccountDetail, NetWorth</t>
         </is>
       </c>
-      <c r="N10" s="5" t="inlineStr">
+      <c r="P10" s="6" t="inlineStr">
         <is>
           <t>assetAllocation, cashTotal</t>
         </is>
       </c>
-      <c r="O10" s="5" t="inlineStr">
+      <c r="Q10" s="6" t="inlineStr">
         <is>
           <t>Record&lt;AssetClass, number&gt; | null</t>
         </is>
       </c>
-      <c r="P10" s="5" t="inlineStr">
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:416</t>
         </is>
@@ -1272,22 +1328,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="6" t="inlineStr">
         <is>
           <t>AccountDetail, NetWorth, Performance</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
         <is>
           <t>Map&lt;string, string&gt;</t>
         </is>
       </c>
-      <c r="P11" s="5" t="inlineStr">
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:394</t>
         </is>
@@ -1353,22 +1411,24 @@
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="M12" s="5" t="inlineStr"/>
+      <c r="N12" s="5" t="inlineStr"/>
+      <c r="O12" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N12" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O12" s="5" t="inlineStr">
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
         <is>
           <t>Record&lt;AssetClass, number&gt;</t>
         </is>
       </c>
-      <c r="P12" s="5" t="inlineStr">
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:517</t>
         </is>
@@ -1453,22 +1513,24 @@
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="M13" s="5" t="inlineStr"/>
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="6" t="inlineStr">
         <is>
           <t>AccountDetail, NetWorth, Performance</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="P13" s="6" t="inlineStr">
         <is>
           <t>accountAllowsTicker, accountClassBreakdown, assetAllocation, cashTotal, earmarkDefault, investmentsTotal, isBond, isRealAsset, primaryCarIdOf</t>
         </is>
       </c>
-      <c r="O13" s="5" t="inlineStr">
+      <c r="Q13" s="6" t="inlineStr">
         <is>
           <t>AssetClass</t>
         </is>
       </c>
-      <c r="P13" s="5" t="inlineStr">
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:236</t>
         </is>
@@ -1507,22 +1569,24 @@
           <t>benchmarkReturn, isCashKind</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="6" t="inlineStr">
         <is>
           <t>AccountDetail, NetWorth, Performance</t>
         </is>
       </c>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="P14" s="6" t="inlineStr">
         <is>
           <t>benchmarkReturn, isCashKind</t>
         </is>
       </c>
-      <c r="O14" s="5" t="inlineStr">
+      <c r="Q14" s="6" t="inlineStr">
         <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="P14" s="5" t="inlineStr">
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:165</t>
         </is>
@@ -1561,22 +1625,24 @@
           <t>resolveNetWorthRows</t>
         </is>
       </c>
-      <c r="M15" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
         <is>
           <t>resolveNetWorthRows</t>
         </is>
       </c>
-      <c r="O15" s="5" t="inlineStr">
+      <c r="Q15" s="6" t="inlineStr">
         <is>
           <t>AssetsDoc</t>
         </is>
       </c>
-      <c r="P15" s="5" t="inlineStr">
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:690</t>
         </is>
@@ -1638,22 +1704,24 @@
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="6" t="inlineStr">
         <is>
           <t>AccountDetail, Performance</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="P16" s="6" t="inlineStr">
         <is>
           <t>blendedReturn</t>
         </is>
       </c>
-      <c r="O16" s="5" t="inlineStr">
+      <c r="Q16" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P16" s="5" t="inlineStr">
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:569</t>
         </is>
@@ -1722,22 +1790,24 @@
           <t>Not a defect, but it must never be hidden: any screen or document quoting odds should be able to show the return behind them, because the same balance at 5.85% and 8.65% gives completely different answers.</t>
         </is>
       </c>
-      <c r="M17" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="O17" s="5" t="inlineStr">
+      <c r="Q17" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P17" s="5" t="inlineStr">
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:653</t>
         </is>
@@ -1802,22 +1872,24 @@
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="M18" s="5" t="inlineStr"/>
+      <c r="N18" s="5" t="inlineStr"/>
+      <c r="O18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="O18" s="5" t="inlineStr">
+      <c r="Q18" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P18" s="5" t="inlineStr">
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:612</t>
         </is>
@@ -1856,22 +1928,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O19" s="5" t="inlineStr">
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
         <is>
           <t>AssetsState</t>
         </is>
       </c>
-      <c r="P19" s="5" t="inlineStr">
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:678</t>
         </is>
@@ -1910,22 +1984,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="M20" s="5" t="inlineStr"/>
+      <c r="N20" s="5" t="inlineStr"/>
+      <c r="O20" s="6" t="inlineStr">
         <is>
           <t>Itemize</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O20" s="5" t="inlineStr">
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
         <is>
           <t>Omit&lt;AssetAccount, 'asset_id'&gt;[]</t>
         </is>
       </c>
-      <c r="P20" s="5" t="inlineStr">
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/itemize.ts:48</t>
         </is>
@@ -1988,22 +2064,24 @@
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O21" s="5" t="inlineStr">
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P21" s="5" t="inlineStr">
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:286</t>
         </is>
@@ -2042,22 +2120,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="M22" s="5" t="inlineStr"/>
+      <c r="N22" s="5" t="inlineStr"/>
+      <c r="O22" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N22" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O22" s="5" t="inlineStr">
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="P22" s="5" t="inlineStr">
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:480</t>
         </is>
@@ -2126,22 +2206,24 @@
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="5" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
         <is>
           <t>earmarkedAmount</t>
         </is>
       </c>
-      <c r="O23" s="5" t="inlineStr">
+      <c r="Q23" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P23" s="5" t="inlineStr">
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:543</t>
         </is>
@@ -2207,22 +2289,24 @@
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr"/>
-      <c r="M24" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N24" s="5" t="inlineStr">
+      <c r="M24" s="5" t="inlineStr"/>
+      <c r="N24" s="5" t="inlineStr"/>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
         <is>
           <t>blendedReturn, blendedVolatility, portfolioActualReturn, retirementEarmarkedValue, taxBucketSplit</t>
         </is>
       </c>
-      <c r="O24" s="5" t="inlineStr">
+      <c r="Q24" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P24" s="5" t="inlineStr">
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:558</t>
         </is>
@@ -2287,22 +2371,24 @@
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr"/>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
         <is>
           <t>accountClassBreakdown, assetClassOf, classifyHolding</t>
         </is>
       </c>
-      <c r="O25" s="5" t="inlineStr">
+      <c r="Q25" s="6" t="inlineStr">
         <is>
           <t>AssetClass | null</t>
         </is>
       </c>
-      <c r="P25" s="5" t="inlineStr">
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:202</t>
         </is>
@@ -2365,22 +2451,24 @@
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr"/>
-      <c r="M26" s="5" t="inlineStr">
+      <c r="M26" s="5" t="inlineStr"/>
+      <c r="N26" s="5" t="inlineStr"/>
+      <c r="O26" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N26" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O26" s="5" t="inlineStr">
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P26" s="5" t="inlineStr">
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:311</t>
         </is>
@@ -2443,22 +2531,24 @@
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="6" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="N27" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O27" s="5" t="inlineStr">
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P27" s="5" t="inlineStr">
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:306</t>
         </is>
@@ -2527,22 +2617,24 @@
           <t>Change money_market in ASSET_KINDS from bucket CASH / section Cash to the investments section, then run the existing reclassify migration so accounts ALREADY stored under the old rule move too. A rule change that only affects new data leaves the founder looking at the old answer.</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr">
+      <c r="M28" s="5" t="inlineStr"/>
+      <c r="N28" s="5" t="inlineStr"/>
+      <c r="O28" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N28" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O28" s="5" t="inlineStr">
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
         <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="P28" s="5" t="inlineStr">
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:164</t>
         </is>
@@ -2602,22 +2694,24 @@
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N29" s="5" t="inlineStr">
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
         <is>
           <t>investableAssets</t>
         </is>
       </c>
-      <c r="O29" s="5" t="inlineStr">
+      <c r="Q29" s="6" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="P29" s="5" t="inlineStr">
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:268</t>
         </is>
@@ -2656,22 +2750,24 @@
           <t>itemizeRemainder</t>
         </is>
       </c>
-      <c r="M30" s="5" t="inlineStr">
+      <c r="M30" s="5" t="inlineStr"/>
+      <c r="N30" s="5" t="inlineStr"/>
+      <c r="O30" s="6" t="inlineStr">
         <is>
           <t>Itemize</t>
         </is>
       </c>
-      <c r="N30" s="5" t="inlineStr">
+      <c r="P30" s="6" t="inlineStr">
         <is>
           <t>itemizeRemainder</t>
         </is>
       </c>
-      <c r="O30" s="5" t="inlineStr">
+      <c r="Q30" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P30" s="5" t="inlineStr">
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/itemize.ts:28</t>
         </is>
@@ -2710,22 +2806,24 @@
           <t>buildItemizedAccounts</t>
         </is>
       </c>
-      <c r="M31" s="5" t="inlineStr">
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="6" t="inlineStr">
         <is>
           <t>Itemize</t>
         </is>
       </c>
-      <c r="N31" s="5" t="inlineStr">
+      <c r="P31" s="6" t="inlineStr">
         <is>
           <t>buildItemizedAccounts</t>
         </is>
       </c>
-      <c r="O31" s="5" t="inlineStr">
+      <c r="Q31" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P31" s="5" t="inlineStr">
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/itemize.ts:32</t>
         </is>
@@ -2785,22 +2883,24 @@
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr"/>
-      <c r="M32" s="5" t="inlineStr">
+      <c r="M32" s="5" t="inlineStr"/>
+      <c r="N32" s="5" t="inlineStr"/>
+      <c r="O32" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N32" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O32" s="5" t="inlineStr">
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
         <is>
           <t>'cash' | 'bonds'</t>
         </is>
       </c>
-      <c r="P32" s="5" t="inlineStr">
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:215</t>
         </is>
@@ -2839,22 +2939,24 @@
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="M33" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N33" s="5" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="O33" s="5" t="inlineStr">
+      <c r="Q33" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P33" s="5" t="inlineStr">
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:710</t>
         </is>
@@ -2893,22 +2995,24 @@
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="M34" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="M34" s="5" t="inlineStr"/>
+      <c r="N34" s="5" t="inlineStr"/>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="O34" s="5" t="inlineStr">
+      <c r="Q34" s="6" t="inlineStr">
         <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="P34" s="5" t="inlineStr">
+      <c r="R34" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:106</t>
         </is>
@@ -2972,22 +3076,24 @@
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N35" s="5" t="inlineStr">
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr"/>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
         <is>
           <t>blendedReturn, blendedVolatility, retirementEarmarkedValue</t>
         </is>
       </c>
-      <c r="O35" s="5" t="inlineStr">
+      <c r="Q35" s="6" t="inlineStr">
         <is>
           <t>string | undefined</t>
         </is>
       </c>
-      <c r="P35" s="5" t="inlineStr">
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:552</t>
         </is>
@@ -3026,22 +3132,24 @@
           <t>earmarkDefault</t>
         </is>
       </c>
-      <c r="M36" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N36" s="5" t="inlineStr">
+      <c r="M36" s="5" t="inlineStr"/>
+      <c r="N36" s="5" t="inlineStr"/>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
         <is>
           <t>earmarkDefault</t>
         </is>
       </c>
-      <c r="O36" s="5" t="inlineStr">
+      <c r="Q36" s="6" t="inlineStr">
         <is>
           <t>RealEstateUse</t>
         </is>
       </c>
-      <c r="P36" s="5" t="inlineStr">
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:262</t>
         </is>
@@ -3100,22 +3208,24 @@
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr"/>
-      <c r="M37" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N37" s="5" t="inlineStr">
+      <c r="M37" s="5" t="inlineStr"/>
+      <c r="N37" s="5" t="inlineStr"/>
+      <c r="O37" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
         <is>
           <t>planDoor, selectWillItLast, willItLastInputs</t>
         </is>
       </c>
-      <c r="O37" s="5" t="inlineStr">
+      <c r="Q37" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P37" s="5" t="inlineStr">
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:563</t>
         </is>
@@ -3154,22 +3264,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M38" s="5" t="inlineStr">
+      <c r="M38" s="5" t="inlineStr"/>
+      <c r="N38" s="5" t="inlineStr"/>
+      <c r="O38" s="6" t="inlineStr">
         <is>
           <t>AccountDetail, NetWorth</t>
         </is>
       </c>
-      <c r="N38" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O38" s="5" t="inlineStr">
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="P38" s="5" t="inlineStr">
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:726</t>
         </is>
@@ -3229,22 +3341,24 @@
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="inlineStr"/>
+      <c r="O39" s="6" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="N39" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O39" s="5" t="inlineStr">
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
         <is>
           <t>TaxTreatment</t>
         </is>
       </c>
-      <c r="P39" s="5" t="inlineStr">
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:253</t>
         </is>
@@ -3283,22 +3397,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M40" s="5" t="inlineStr">
+      <c r="M40" s="5" t="inlineStr"/>
+      <c r="N40" s="5" t="inlineStr"/>
+      <c r="O40" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N40" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O40" s="5" t="inlineStr">
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
         <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="P40" s="5" t="inlineStr">
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:794</t>
         </is>
@@ -3337,22 +3453,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M41" s="5" t="inlineStr">
+      <c r="M41" s="5" t="inlineStr"/>
+      <c r="N41" s="5" t="inlineStr"/>
+      <c r="O41" s="6" t="inlineStr">
         <is>
           <t>AccountDetail, Performance</t>
         </is>
       </c>
-      <c r="N41" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O41" s="5" t="inlineStr">
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
         <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="P41" s="5" t="inlineStr">
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:95</t>
         </is>
@@ -3391,22 +3509,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M42" s="5" t="inlineStr">
+      <c r="M42" s="5" t="inlineStr"/>
+      <c r="N42" s="5" t="inlineStr"/>
+      <c r="O42" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N42" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O42" s="5" t="inlineStr">
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
         <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="P42" s="5" t="inlineStr">
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>src/domain/assets/index.ts:223</t>
         </is>
@@ -3466,22 +3586,24 @@
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="5" t="inlineStr">
+      <c r="M43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="inlineStr"/>
+      <c r="O43" s="6" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="P43" s="6" t="inlineStr">
         <is>
           <t>approxYTM, currentYield</t>
         </is>
       </c>
-      <c r="O43" s="5" t="inlineStr">
+      <c r="Q43" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P43" s="5" t="inlineStr">
+      <c r="R43" s="6" t="inlineStr">
         <is>
           <t>src/domain/bonds/index.ts:21</t>
         </is>
@@ -3546,22 +3668,24 @@
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="5" t="inlineStr">
+      <c r="M44" s="5" t="inlineStr"/>
+      <c r="N44" s="5" t="inlineStr"/>
+      <c r="O44" s="6" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="N44" s="5" t="inlineStr">
+      <c r="P44" s="6" t="inlineStr">
         <is>
           <t>bondRateSensitivity</t>
         </is>
       </c>
-      <c r="O44" s="5" t="inlineStr">
+      <c r="Q44" s="6" t="inlineStr">
         <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="P44" s="5" t="inlineStr">
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>src/domain/bonds/index.ts:33</t>
         </is>
@@ -3620,22 +3744,24 @@
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="5" t="inlineStr">
+      <c r="M45" s="5" t="inlineStr"/>
+      <c r="N45" s="5" t="inlineStr"/>
+      <c r="O45" s="6" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="N45" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O45" s="5" t="inlineStr">
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
         <is>
           <t>BondInfo</t>
         </is>
       </c>
-      <c r="P45" s="5" t="inlineStr">
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>src/domain/bonds/index.ts:16</t>
         </is>
@@ -3674,22 +3800,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M46" s="5" t="inlineStr">
+      <c r="M46" s="5" t="inlineStr"/>
+      <c r="N46" s="5" t="inlineStr"/>
+      <c r="O46" s="6" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="N46" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O46" s="5" t="inlineStr">
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
         <is>
           <t>RateSensitivity | null</t>
         </is>
       </c>
-      <c r="P46" s="5" t="inlineStr">
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>src/domain/bonds/index.ts:97</t>
         </is>
@@ -3750,22 +3878,24 @@
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr"/>
-      <c r="M47" s="5" t="inlineStr">
+      <c r="M47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr"/>
+      <c r="O47" s="6" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="N47" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O47" s="5" t="inlineStr">
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
         <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="P47" s="5" t="inlineStr">
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>src/domain/bonds/index.ts:29</t>
         </is>
@@ -3824,22 +3954,24 @@
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr"/>
-      <c r="M48" s="5" t="inlineStr">
+      <c r="M48" s="5" t="inlineStr"/>
+      <c r="N48" s="5" t="inlineStr"/>
+      <c r="O48" s="6" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="N48" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O48" s="5" t="inlineStr">
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="P48" s="5" t="inlineStr">
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>src/domain/bonds/index.ts:13</t>
         </is>
@@ -3899,22 +4031,24 @@
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr"/>
-      <c r="M49" s="5" t="inlineStr">
+      <c r="M49" s="5" t="inlineStr"/>
+      <c r="N49" s="5" t="inlineStr"/>
+      <c r="O49" s="6" t="inlineStr">
         <is>
           <t>AccountDetail</t>
         </is>
       </c>
-      <c r="N49" s="5" t="inlineStr">
+      <c r="P49" s="6" t="inlineStr">
         <is>
           <t>approxYTM</t>
         </is>
       </c>
-      <c r="O49" s="5" t="inlineStr">
+      <c r="Q49" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P49" s="5" t="inlineStr">
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>src/domain/bonds/index.ts:24</t>
         </is>
@@ -3953,22 +4087,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M50" s="5" t="inlineStr">
+      <c r="M50" s="5" t="inlineStr"/>
+      <c r="N50" s="5" t="inlineStr"/>
+      <c r="O50" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N50" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O50" s="5" t="inlineStr">
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P50" s="5" t="inlineStr">
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>src/domain/budget/index.ts:45</t>
         </is>
@@ -4007,22 +4143,24 @@
           <t>plannedMonthlySpend</t>
         </is>
       </c>
-      <c r="M51" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N51" s="5" t="inlineStr">
+      <c r="M51" s="5" t="inlineStr"/>
+      <c r="N51" s="5" t="inlineStr"/>
+      <c r="O51" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
         <is>
           <t>plannedMonthlySpend</t>
         </is>
       </c>
-      <c r="O51" s="5" t="inlineStr">
+      <c r="Q51" s="6" t="inlineStr">
         <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="P51" s="5" t="inlineStr">
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>src/domain/budget/index.ts:72</t>
         </is>
@@ -4061,22 +4199,24 @@
           <t>buildDebtState</t>
         </is>
       </c>
-      <c r="M52" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N52" s="5" t="inlineStr">
+      <c r="M52" s="5" t="inlineStr"/>
+      <c r="N52" s="5" t="inlineStr"/>
+      <c r="O52" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
         <is>
           <t>buildDebtState</t>
         </is>
       </c>
-      <c r="O52" s="5" t="inlineStr">
+      <c r="Q52" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P52" s="5" t="inlineStr">
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:59</t>
         </is>
@@ -4115,22 +4255,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M53" s="5" t="inlineStr">
+      <c r="M53" s="5" t="inlineStr"/>
+      <c r="N53" s="5" t="inlineStr"/>
+      <c r="O53" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N53" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O53" s="5" t="inlineStr">
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
         <is>
           <t>DebtState</t>
         </is>
       </c>
-      <c r="P53" s="5" t="inlineStr">
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:214</t>
         </is>
@@ -4169,22 +4311,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M54" s="5" t="inlineStr">
+      <c r="M54" s="5" t="inlineStr"/>
+      <c r="N54" s="5" t="inlineStr"/>
+      <c r="O54" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N54" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O54" s="5" t="inlineStr">
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
         <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="P54" s="5" t="inlineStr">
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:197</t>
         </is>
@@ -4223,22 +4367,24 @@
           <t>resolveNetWorthRows</t>
         </is>
       </c>
-      <c r="M55" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N55" s="5" t="inlineStr">
+      <c r="M55" s="5" t="inlineStr"/>
+      <c r="N55" s="5" t="inlineStr"/>
+      <c r="O55" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
         <is>
           <t>resolveNetWorthRows</t>
         </is>
       </c>
-      <c r="O55" s="5" t="inlineStr">
+      <c r="Q55" s="6" t="inlineStr">
         <is>
           <t>DebtDoc</t>
         </is>
       </c>
-      <c r="P55" s="5" t="inlineStr">
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:240</t>
         </is>
@@ -4297,22 +4443,24 @@
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr"/>
-      <c r="M56" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N56" s="5" t="inlineStr">
+      <c r="M56" s="5" t="inlineStr"/>
+      <c r="N56" s="5" t="inlineStr"/>
+      <c r="O56" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
         <is>
           <t>paymentShape</t>
         </is>
       </c>
-      <c r="O56" s="5" t="inlineStr">
+      <c r="Q56" s="6" t="inlineStr">
         <is>
           <t>NonNullable&lt;Debt['payment_type']&gt;</t>
         </is>
       </c>
-      <c r="P56" s="5" t="inlineStr">
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:35</t>
         </is>
@@ -4351,22 +4499,24 @@
           <t>debtsFromOnboarding</t>
         </is>
       </c>
-      <c r="M57" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N57" s="5" t="inlineStr">
+      <c r="M57" s="5" t="inlineStr"/>
+      <c r="N57" s="5" t="inlineStr"/>
+      <c r="O57" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
         <is>
           <t>debtsFromOnboarding</t>
         </is>
       </c>
-      <c r="O57" s="5" t="inlineStr">
+      <c r="Q57" s="6" t="inlineStr">
         <is>
           <t>DebtType</t>
         </is>
       </c>
-      <c r="P57" s="5" t="inlineStr">
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:228</t>
         </is>
@@ -4426,22 +4576,24 @@
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr"/>
-      <c r="M58" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N58" s="5" t="inlineStr">
+      <c r="M58" s="5" t="inlineStr"/>
+      <c r="N58" s="5" t="inlineStr"/>
+      <c r="O58" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
         <is>
           <t>buildDebtState</t>
         </is>
       </c>
-      <c r="O58" s="5" t="inlineStr">
+      <c r="Q58" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P58" s="5" t="inlineStr">
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:55</t>
         </is>
@@ -4501,22 +4653,24 @@
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr"/>
-      <c r="M59" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N59" s="5" t="inlineStr">
+      <c r="M59" s="5" t="inlineStr"/>
+      <c r="N59" s="5" t="inlineStr"/>
+      <c r="O59" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
         <is>
           <t>minimumDebtService, requiredPayment</t>
         </is>
       </c>
-      <c r="O59" s="5" t="inlineStr">
+      <c r="Q59" s="6" t="inlineStr">
         <is>
           <t>NonNullable&lt;Debt['payment_type']&gt;</t>
         </is>
       </c>
-      <c r="P59" s="5" t="inlineStr">
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:38</t>
         </is>
@@ -4577,22 +4731,24 @@
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr"/>
-      <c r="M60" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N60" s="5" t="inlineStr">
+      <c r="M60" s="5" t="inlineStr"/>
+      <c r="N60" s="5" t="inlineStr"/>
+      <c r="O60" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
         <is>
           <t>totalDebtMonthly</t>
         </is>
       </c>
-      <c r="O60" s="5" t="inlineStr">
+      <c r="Q60" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P60" s="5" t="inlineStr">
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:44</t>
         </is>
@@ -4651,22 +4807,24 @@
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr"/>
-      <c r="M61" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N61" s="5" t="inlineStr">
+      <c r="M61" s="5" t="inlineStr"/>
+      <c r="N61" s="5" t="inlineStr"/>
+      <c r="O61" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
         <is>
           <t>actualDebtPayment</t>
         </is>
       </c>
-      <c r="O61" s="5" t="inlineStr">
+      <c r="Q61" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P61" s="5" t="inlineStr">
+      <c r="R61" s="6" t="inlineStr">
         <is>
           <t>src/domain/debt/index.ts:49</t>
         </is>
@@ -4705,22 +4863,24 @@
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="M62" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N62" s="5" t="inlineStr">
+      <c r="M62" s="5" t="inlineStr"/>
+      <c r="N62" s="5" t="inlineStr"/>
+      <c r="O62" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="O62" s="5" t="inlineStr">
+      <c r="Q62" s="6" t="inlineStr">
         <is>
           <t>BucketSplit</t>
         </is>
       </c>
-      <c r="P62" s="5" t="inlineStr">
+      <c r="R62" s="6" t="inlineStr">
         <is>
           <t>src/domain/decumulation/index.ts:10</t>
         </is>
@@ -4759,22 +4919,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M63" s="5" t="inlineStr">
+      <c r="M63" s="5" t="inlineStr"/>
+      <c r="N63" s="5" t="inlineStr"/>
+      <c r="O63" s="6" t="inlineStr">
         <is>
           <t>NetWorth, Performance</t>
         </is>
       </c>
-      <c r="N63" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O63" s="5" t="inlineStr">
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
         <is>
           <t>DataGap[]</t>
         </is>
       </c>
-      <c r="P63" s="5" t="inlineStr">
+      <c r="R63" s="6" t="inlineStr">
         <is>
           <t>src/domain/gaps/index.ts:57</t>
         </is>
@@ -4848,22 +5010,24 @@
           <t>Split the function in two. Keep the balancing arithmetic (it is sound and the rows must always sum), but return the unexplained remainder under its own name — unexplained — and let the screen print it as such. Then add a SEPARATE measured market-movement figure sourced from stored per-holding values, shown only when that history exists. Two small changes, no new engine.</t>
         </is>
       </c>
-      <c r="M64" s="5" t="inlineStr">
+      <c r="M64" s="5" t="inlineStr"/>
+      <c r="N64" s="5" t="inlineStr"/>
+      <c r="O64" s="6" t="inlineStr">
         <is>
           <t>NetWorth, Performance</t>
         </is>
       </c>
-      <c r="N64" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O64" s="5" t="inlineStr">
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q64" s="6" t="inlineStr">
         <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="P64" s="5" t="inlineStr">
+      <c r="R64" s="6" t="inlineStr">
         <is>
           <t>src/domain/history.ts:144</t>
         </is>
@@ -4933,22 +5097,24 @@
           <t>Change the signature to take an explicit start date rather than inferring one, and return null with a reason when no snapshot exists at that date so the screen can say "no record that far back" instead of silently using a nearer one. Depends on the snapshot fix below — do that one first or the baseline keeps sliding toward today.</t>
         </is>
       </c>
-      <c r="M65" s="5" t="inlineStr">
+      <c r="M65" s="5" t="inlineStr"/>
+      <c r="N65" s="5" t="inlineStr"/>
+      <c r="O65" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N65" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O65" s="5" t="inlineStr">
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q65" s="6" t="inlineStr">
         <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="P65" s="5" t="inlineStr">
+      <c r="R65" s="6" t="inlineStr">
         <is>
           <t>src/domain/history.ts:118</t>
         </is>
@@ -4987,22 +5153,24 @@
           <t>readHistory</t>
         </is>
       </c>
-      <c r="M66" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N66" s="5" t="inlineStr">
+      <c r="M66" s="5" t="inlineStr"/>
+      <c r="N66" s="5" t="inlineStr"/>
+      <c r="O66" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P66" s="6" t="inlineStr">
         <is>
           <t>readHistory</t>
         </is>
       </c>
-      <c r="O66" s="5" t="inlineStr">
+      <c r="Q66" s="6" t="inlineStr">
         <is>
           <t>MonthlySnapshot | null</t>
         </is>
       </c>
-      <c r="P66" s="5" t="inlineStr">
+      <c r="R66" s="6" t="inlineStr">
         <is>
           <t>src/domain/history.ts:77</t>
         </is>
@@ -5041,22 +5209,24 @@
           <t>trendPoints</t>
         </is>
       </c>
-      <c r="M67" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N67" s="5" t="inlineStr">
+      <c r="M67" s="5" t="inlineStr"/>
+      <c r="N67" s="5" t="inlineStr"/>
+      <c r="O67" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P67" s="6" t="inlineStr">
         <is>
           <t>trendPoints</t>
         </is>
       </c>
-      <c r="O67" s="5" t="inlineStr">
+      <c r="Q67" s="6" t="inlineStr">
         <is>
           <t>MonthlySnapshot[]</t>
         </is>
       </c>
-      <c r="P67" s="5" t="inlineStr">
+      <c r="R67" s="6" t="inlineStr">
         <is>
           <t>src/domain/history.ts:107</t>
         </is>
@@ -5095,22 +5265,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M68" s="5" t="inlineStr">
+      <c r="M68" s="5" t="inlineStr"/>
+      <c r="N68" s="5" t="inlineStr"/>
+      <c r="O68" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N68" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O68" s="5" t="inlineStr">
+      <c r="P68" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q68" s="6" t="inlineStr">
         <is>
           <t>TrendPoint[]</t>
         </is>
       </c>
-      <c r="P68" s="5" t="inlineStr">
+      <c r="R68" s="6" t="inlineStr">
         <is>
           <t>src/domain/history.ts:43</t>
         </is>
@@ -5194,22 +5366,24 @@
           <t>Add a currency ticker list (FXE FXY FXB FXF FXA FXC UUP UDN) and loosen the word rule to match CURRENCYSHARES as well as CURRENCY. Ten minutes; the shape already exists twice over for crypto and commodities.</t>
         </is>
       </c>
-      <c r="M69" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N69" s="5" t="inlineStr">
+      <c r="M69" s="5" t="inlineStr"/>
+      <c r="N69" s="5" t="inlineStr"/>
+      <c r="O69" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P69" s="6" t="inlineStr">
         <is>
           <t>importHoldings</t>
         </is>
       </c>
-      <c r="O69" s="5" t="inlineStr">
+      <c r="Q69" s="6" t="inlineStr">
         <is>
           <t>AssetClass</t>
         </is>
       </c>
-      <c r="P69" s="5" t="inlineStr">
+      <c r="R69" s="6" t="inlineStr">
         <is>
           <t>src/domain/import/holdingsImport.ts:154</t>
         </is>
@@ -5272,22 +5446,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M70" s="5" t="inlineStr">
+      <c r="M70" s="5" t="inlineStr"/>
+      <c r="N70" s="5" t="inlineStr"/>
+      <c r="O70" s="6" t="inlineStr">
         <is>
           <t>ImportHoldings</t>
         </is>
       </c>
-      <c r="N70" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="5" t="inlineStr">
+      <c r="P70" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q70" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="P70" s="5" t="inlineStr">
+      <c r="R70" s="6" t="inlineStr">
         <is>
           <t>src/domain/import/holdingsImport.ts:61</t>
         </is>
@@ -5366,22 +5542,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M71" s="5" t="inlineStr">
+      <c r="M71" s="5" t="inlineStr"/>
+      <c r="N71" s="5" t="inlineStr"/>
+      <c r="O71" s="6" t="inlineStr">
         <is>
           <t>ImportHoldings</t>
         </is>
       </c>
-      <c r="N71" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O71" s="5" t="inlineStr">
+      <c r="P71" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q71" s="6" t="inlineStr">
         <is>
           <t>ImportResult</t>
         </is>
       </c>
-      <c r="P71" s="5" t="inlineStr">
+      <c r="R71" s="6" t="inlineStr">
         <is>
           <t>src/domain/import/holdingsImport.ts:183</t>
         </is>
@@ -5446,22 +5624,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M72" s="5" t="inlineStr">
+      <c r="M72" s="5" t="inlineStr"/>
+      <c r="N72" s="5" t="inlineStr"/>
+      <c r="O72" s="6" t="inlineStr">
         <is>
           <t>ImportHoldings</t>
         </is>
       </c>
-      <c r="N72" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="5" t="inlineStr">
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q72" s="6" t="inlineStr">
         <is>
           <t>AssetAccount | null</t>
         </is>
       </c>
-      <c r="P72" s="5" t="inlineStr">
+      <c r="R72" s="6" t="inlineStr">
         <is>
           <t>src/domain/import/holdingsImport.ts:254</t>
         </is>
@@ -5532,22 +5712,24 @@
           <t>importHoldings</t>
         </is>
       </c>
-      <c r="M73" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="5" t="inlineStr">
+      <c r="M73" s="5" t="inlineStr"/>
+      <c r="N73" s="5" t="inlineStr"/>
+      <c r="O73" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="6" t="inlineStr">
         <is>
           <t>importHoldings</t>
         </is>
       </c>
-      <c r="O73" s="5" t="inlineStr">
+      <c r="Q73" s="6" t="inlineStr">
         <is>
           <t>string[][]</t>
         </is>
       </c>
-      <c r="P73" s="5" t="inlineStr">
+      <c r="R73" s="6" t="inlineStr">
         <is>
           <t>src/domain/import/holdingsImport.ts:74</t>
         </is>
@@ -5586,22 +5768,24 @@
           <t>resolveLens, totalGrossAnnual</t>
         </is>
       </c>
-      <c r="M74" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="5" t="inlineStr">
+      <c r="M74" s="5" t="inlineStr"/>
+      <c r="N74" s="5" t="inlineStr"/>
+      <c r="O74" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="6" t="inlineStr">
         <is>
           <t>resolveLens, totalGrossAnnual</t>
         </is>
       </c>
-      <c r="O74" s="5" t="inlineStr">
+      <c r="Q74" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P74" s="5" t="inlineStr">
+      <c r="R74" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:191</t>
         </is>
@@ -5640,22 +5824,24 @@
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="M75" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="5" t="inlineStr">
+      <c r="M75" s="5" t="inlineStr"/>
+      <c r="N75" s="5" t="inlineStr"/>
+      <c r="O75" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P75" s="6" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="O75" s="5" t="inlineStr">
+      <c r="Q75" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P75" s="5" t="inlineStr">
+      <c r="R75" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/tax.ts:107</t>
         </is>
@@ -5694,22 +5880,24 @@
           <t>monthlyContributionsFromOnboarding</t>
         </is>
       </c>
-      <c r="M76" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N76" s="5" t="inlineStr">
+      <c r="M76" s="5" t="inlineStr"/>
+      <c r="N76" s="5" t="inlineStr"/>
+      <c r="O76" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P76" s="6" t="inlineStr">
         <is>
           <t>monthlyContributionsFromOnboarding</t>
         </is>
       </c>
-      <c r="O76" s="5" t="inlineStr">
+      <c r="Q76" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P76" s="5" t="inlineStr">
+      <c r="R76" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:242</t>
         </is>
@@ -5748,22 +5936,24 @@
           <t>rsuAnnual</t>
         </is>
       </c>
-      <c r="M77" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N77" s="5" t="inlineStr">
+      <c r="M77" s="5" t="inlineStr"/>
+      <c r="N77" s="5" t="inlineStr"/>
+      <c r="O77" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P77" s="6" t="inlineStr">
         <is>
           <t>rsuAnnual</t>
         </is>
       </c>
-      <c r="O77" s="5" t="inlineStr">
+      <c r="Q77" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P77" s="5" t="inlineStr">
+      <c r="R77" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:68</t>
         </is>
@@ -5802,22 +5992,24 @@
           <t>totalGrossAnnual</t>
         </is>
       </c>
-      <c r="M78" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N78" s="5" t="inlineStr">
+      <c r="M78" s="5" t="inlineStr"/>
+      <c r="N78" s="5" t="inlineStr"/>
+      <c r="O78" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P78" s="6" t="inlineStr">
         <is>
           <t>totalGrossAnnual</t>
         </is>
       </c>
-      <c r="O78" s="5" t="inlineStr">
+      <c r="Q78" s="6" t="inlineStr">
         <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="P78" s="5" t="inlineStr">
+      <c r="R78" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:161</t>
         </is>
@@ -5856,22 +6048,24 @@
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="M79" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N79" s="5" t="inlineStr">
+      <c r="M79" s="5" t="inlineStr"/>
+      <c r="N79" s="5" t="inlineStr"/>
+      <c r="O79" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P79" s="6" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="O79" s="5" t="inlineStr">
+      <c r="Q79" s="6" t="inlineStr">
         <is>
           <t>import('./tax').FilingStatus</t>
         </is>
       </c>
-      <c r="P79" s="5" t="inlineStr">
+      <c r="R79" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:333</t>
         </is>
@@ -5910,22 +6104,24 @@
           <t>salaryGrossByMonth</t>
         </is>
       </c>
-      <c r="M80" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N80" s="5" t="inlineStr">
+      <c r="M80" s="5" t="inlineStr"/>
+      <c r="N80" s="5" t="inlineStr"/>
+      <c r="O80" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" s="6" t="inlineStr">
         <is>
           <t>salaryGrossByMonth</t>
         </is>
       </c>
-      <c r="O80" s="5" t="inlineStr">
+      <c r="Q80" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P80" s="5" t="inlineStr">
+      <c r="R80" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/tax.ts:47</t>
         </is>
@@ -5964,22 +6160,24 @@
           <t>rentalNetAnnual</t>
         </is>
       </c>
-      <c r="M81" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N81" s="5" t="inlineStr">
+      <c r="M81" s="5" t="inlineStr"/>
+      <c r="N81" s="5" t="inlineStr"/>
+      <c r="O81" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P81" s="6" t="inlineStr">
         <is>
           <t>rentalNetAnnual</t>
         </is>
       </c>
-      <c r="O81" s="5" t="inlineStr">
+      <c r="Q81" s="6" t="inlineStr">
         <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="P81" s="5" t="inlineStr">
+      <c r="R81" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:129</t>
         </is>
@@ -6018,22 +6216,24 @@
           <t>totalGrossAnnual</t>
         </is>
       </c>
-      <c r="M82" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N82" s="5" t="inlineStr">
+      <c r="M82" s="5" t="inlineStr"/>
+      <c r="N82" s="5" t="inlineStr"/>
+      <c r="O82" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="6" t="inlineStr">
         <is>
           <t>totalGrossAnnual</t>
         </is>
       </c>
-      <c r="O82" s="5" t="inlineStr">
+      <c r="Q82" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P82" s="5" t="inlineStr">
+      <c r="R82" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:142</t>
         </is>
@@ -6072,22 +6272,24 @@
           <t>currentRetirementIncomeMonthly, willItLastInputs</t>
         </is>
       </c>
-      <c r="M83" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N83" s="5" t="inlineStr">
+      <c r="M83" s="5" t="inlineStr"/>
+      <c r="N83" s="5" t="inlineStr"/>
+      <c r="O83" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P83" s="6" t="inlineStr">
         <is>
           <t>currentRetirementIncomeMonthly, willItLastInputs</t>
         </is>
       </c>
-      <c r="O83" s="5" t="inlineStr">
+      <c r="Q83" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P83" s="5" t="inlineStr">
+      <c r="R83" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:213</t>
         </is>
@@ -6126,22 +6328,24 @@
           <t>rsuAnnual</t>
         </is>
       </c>
-      <c r="M84" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N84" s="5" t="inlineStr">
+      <c r="M84" s="5" t="inlineStr"/>
+      <c r="N84" s="5" t="inlineStr"/>
+      <c r="O84" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P84" s="6" t="inlineStr">
         <is>
           <t>rsuAnnual</t>
         </is>
       </c>
-      <c r="O84" s="5" t="inlineStr">
+      <c r="Q84" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P84" s="5" t="inlineStr">
+      <c r="R84" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:74</t>
         </is>
@@ -6180,22 +6384,24 @@
           <t>totalGrossAnnual</t>
         </is>
       </c>
-      <c r="M85" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N85" s="5" t="inlineStr">
+      <c r="M85" s="5" t="inlineStr"/>
+      <c r="N85" s="5" t="inlineStr"/>
+      <c r="O85" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P85" s="6" t="inlineStr">
         <is>
           <t>totalGrossAnnual</t>
         </is>
       </c>
-      <c r="O85" s="5" t="inlineStr">
+      <c r="Q85" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P85" s="5" t="inlineStr">
+      <c r="R85" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:114</t>
         </is>
@@ -6234,22 +6440,24 @@
           <t>tipsAnnual</t>
         </is>
       </c>
-      <c r="M86" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N86" s="5" t="inlineStr">
+      <c r="M86" s="5" t="inlineStr"/>
+      <c r="N86" s="5" t="inlineStr"/>
+      <c r="O86" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P86" s="6" t="inlineStr">
         <is>
           <t>tipsAnnual</t>
         </is>
       </c>
-      <c r="O86" s="5" t="inlineStr">
+      <c r="Q86" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P86" s="5" t="inlineStr">
+      <c r="R86" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:306</t>
         </is>
@@ -6288,22 +6496,24 @@
           <t>totalGrossAnnual</t>
         </is>
       </c>
-      <c r="M87" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N87" s="5" t="inlineStr">
+      <c r="M87" s="5" t="inlineStr"/>
+      <c r="N87" s="5" t="inlineStr"/>
+      <c r="O87" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P87" s="6" t="inlineStr">
         <is>
           <t>totalGrossAnnual</t>
         </is>
       </c>
-      <c r="O87" s="5" t="inlineStr">
+      <c r="Q87" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P87" s="5" t="inlineStr">
+      <c r="R87" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:310</t>
         </is>
@@ -6342,22 +6552,24 @@
           <t>salaryActiveMonths, salaryAnnual</t>
         </is>
       </c>
-      <c r="M88" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N88" s="5" t="inlineStr">
+      <c r="M88" s="5" t="inlineStr"/>
+      <c r="N88" s="5" t="inlineStr"/>
+      <c r="O88" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P88" s="6" t="inlineStr">
         <is>
           <t>salaryActiveMonths, salaryAnnual</t>
         </is>
       </c>
-      <c r="O88" s="5" t="inlineStr">
+      <c r="Q88" s="6" t="inlineStr">
         <is>
           <t>number[]</t>
         </is>
       </c>
-      <c r="P88" s="5" t="inlineStr">
+      <c r="R88" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:46</t>
         </is>
@@ -6396,22 +6608,24 @@
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="M89" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N89" s="5" t="inlineStr">
+      <c r="M89" s="5" t="inlineStr"/>
+      <c r="N89" s="5" t="inlineStr"/>
+      <c r="O89" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P89" s="6" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="O89" s="5" t="inlineStr">
+      <c r="Q89" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P89" s="5" t="inlineStr">
+      <c r="R89" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:337</t>
         </is>
@@ -6450,22 +6664,24 @@
           <t>taxOwed</t>
         </is>
       </c>
-      <c r="M90" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N90" s="5" t="inlineStr">
+      <c r="M90" s="5" t="inlineStr"/>
+      <c r="N90" s="5" t="inlineStr"/>
+      <c r="O90" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P90" s="6" t="inlineStr">
         <is>
           <t>taxOwed</t>
         </is>
       </c>
-      <c r="O90" s="5" t="inlineStr">
+      <c r="Q90" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P90" s="5" t="inlineStr">
+      <c r="R90" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/tax.ts:17</t>
         </is>
@@ -6504,22 +6720,24 @@
           <t>taxOwedFor</t>
         </is>
       </c>
-      <c r="M91" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N91" s="5" t="inlineStr">
+      <c r="M91" s="5" t="inlineStr"/>
+      <c r="N91" s="5" t="inlineStr"/>
+      <c r="O91" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P91" s="6" t="inlineStr">
         <is>
           <t>taxOwedFor</t>
         </is>
       </c>
-      <c r="O91" s="5" t="inlineStr">
+      <c r="Q91" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P91" s="5" t="inlineStr">
+      <c r="R91" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/tax.ts:88</t>
         </is>
@@ -6558,22 +6776,24 @@
           <t>grossFromNet</t>
         </is>
       </c>
-      <c r="M92" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N92" s="5" t="inlineStr">
+      <c r="M92" s="5" t="inlineStr"/>
+      <c r="N92" s="5" t="inlineStr"/>
+      <c r="O92" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P92" s="6" t="inlineStr">
         <is>
           <t>grossFromNet</t>
         </is>
       </c>
-      <c r="O92" s="5" t="inlineStr">
+      <c r="Q92" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P92" s="5" t="inlineStr">
+      <c r="R92" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/tax.ts:29</t>
         </is>
@@ -6612,22 +6832,24 @@
           <t>effectiveRateOnGrossFor</t>
         </is>
       </c>
-      <c r="M93" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N93" s="5" t="inlineStr">
+      <c r="M93" s="5" t="inlineStr"/>
+      <c r="N93" s="5" t="inlineStr"/>
+      <c r="O93" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P93" s="6" t="inlineStr">
         <is>
           <t>effectiveRateOnGrossFor</t>
         </is>
       </c>
-      <c r="O93" s="5" t="inlineStr">
+      <c r="Q93" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P93" s="5" t="inlineStr">
+      <c r="R93" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/tax.ts:94</t>
         </is>
@@ -6666,22 +6888,24 @@
           <t>totalGrossAnnual</t>
         </is>
       </c>
-      <c r="M94" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N94" s="5" t="inlineStr">
+      <c r="M94" s="5" t="inlineStr"/>
+      <c r="N94" s="5" t="inlineStr"/>
+      <c r="O94" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P94" s="6" t="inlineStr">
         <is>
           <t>totalGrossAnnual</t>
         </is>
       </c>
-      <c r="O94" s="5" t="inlineStr">
+      <c r="Q94" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P94" s="5" t="inlineStr">
+      <c r="R94" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:204</t>
         </is>
@@ -6720,22 +6944,24 @@
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="M95" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N95" s="5" t="inlineStr">
+      <c r="M95" s="5" t="inlineStr"/>
+      <c r="N95" s="5" t="inlineStr"/>
+      <c r="O95" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P95" s="6" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="O95" s="5" t="inlineStr">
+      <c r="Q95" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P95" s="5" t="inlineStr">
+      <c r="R95" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:316</t>
         </is>
@@ -6774,22 +7000,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M96" s="5" t="inlineStr">
+      <c r="M96" s="5" t="inlineStr"/>
+      <c r="N96" s="5" t="inlineStr"/>
+      <c r="O96" s="6" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="N96" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O96" s="5" t="inlineStr">
+      <c r="P96" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q96" s="6" t="inlineStr">
         <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="P96" s="5" t="inlineStr">
+      <c r="R96" s="6" t="inlineStr">
         <is>
           <t>src/domain/income/onboarding.ts:390</t>
         </is>
@@ -6828,22 +7056,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M97" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N97" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O97" s="5" t="inlineStr">
+      <c r="M97" s="5" t="inlineStr"/>
+      <c r="N97" s="5" t="inlineStr"/>
+      <c r="O97" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P97" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q97" s="6" t="inlineStr">
         <is>
           <t>Promise&lt;ExpenseAnalysis&gt;</t>
         </is>
       </c>
-      <c r="P97" s="5" t="inlineStr">
+      <c r="R97" s="6" t="inlineStr">
         <is>
           <t>src/services/economicData.ts:109</t>
         </is>
@@ -6882,22 +7112,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M98" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N98" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O98" s="5" t="inlineStr">
+      <c r="M98" s="5" t="inlineStr"/>
+      <c r="N98" s="5" t="inlineStr"/>
+      <c r="O98" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P98" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q98" s="6" t="inlineStr">
         <is>
           <t>Promise&lt;EconomicData&gt;</t>
         </is>
       </c>
-      <c r="P98" s="5" t="inlineStr">
+      <c r="R98" s="6" t="inlineStr">
         <is>
           <t>src/services/economicData.ts:47</t>
         </is>
@@ -6936,22 +7168,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M99" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N99" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O99" s="5" t="inlineStr">
+      <c r="M99" s="5" t="inlineStr"/>
+      <c r="N99" s="5" t="inlineStr"/>
+      <c r="O99" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P99" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q99" s="6" t="inlineStr">
         <is>
           <t>Promise&lt;</t>
         </is>
       </c>
-      <c r="P99" s="5" t="inlineStr">
+      <c r="R99" s="6" t="inlineStr">
         <is>
           <t>src/services/economicData.ts:158</t>
         </is>
@@ -6990,22 +7224,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M100" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N100" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O100" s="5" t="inlineStr">
+      <c r="M100" s="5" t="inlineStr"/>
+      <c r="N100" s="5" t="inlineStr"/>
+      <c r="O100" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P100" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q100" s="6" t="inlineStr">
         <is>
           <t>AssetAccount[]</t>
         </is>
       </c>
-      <c r="P100" s="5" t="inlineStr">
+      <c r="R100" s="6" t="inlineStr">
         <is>
           <t>src/services/sync/ingest.ts:173</t>
         </is>
@@ -7044,22 +7280,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M101" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N101" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O101" s="5" t="inlineStr">
+      <c r="M101" s="5" t="inlineStr"/>
+      <c r="N101" s="5" t="inlineStr"/>
+      <c r="O101" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P101" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q101" s="6" t="inlineStr">
         <is>
           <t>SyncResult</t>
         </is>
       </c>
-      <c r="P101" s="5" t="inlineStr">
+      <c r="R101" s="6" t="inlineStr">
         <is>
           <t>src/services/sync/ingest.ts:31</t>
         </is>
@@ -7098,22 +7336,24 @@
           <t>ingestSync</t>
         </is>
       </c>
-      <c r="M102" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N102" s="5" t="inlineStr">
+      <c r="M102" s="5" t="inlineStr"/>
+      <c r="N102" s="5" t="inlineStr"/>
+      <c r="O102" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P102" s="6" t="inlineStr">
         <is>
           <t>ingestSync</t>
         </is>
       </c>
-      <c r="O102" s="5" t="inlineStr">
+      <c r="Q102" s="6" t="inlineStr">
         <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="P102" s="5" t="inlineStr">
+      <c r="R102" s="6" t="inlineStr">
         <is>
           <t>src/services/sync/ingest.ts:29</t>
         </is>
@@ -7152,22 +7392,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M103" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N103" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O103" s="5" t="inlineStr">
+      <c r="M103" s="5" t="inlineStr"/>
+      <c r="N103" s="5" t="inlineStr"/>
+      <c r="O103" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P103" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q103" s="6" t="inlineStr">
         <is>
           <t>Promise&lt;Record&lt;string, PriceSeries&gt;&gt;</t>
         </is>
       </c>
-      <c r="P103" s="5" t="inlineStr">
+      <c r="R103" s="6" t="inlineStr">
         <is>
           <t>src/services/marketData.ts:71</t>
         </is>
@@ -7227,22 +7469,24 @@
         </is>
       </c>
       <c r="L104" s="3" t="inlineStr"/>
-      <c r="M104" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N104" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O104" s="5" t="inlineStr">
+      <c r="M104" s="5" t="inlineStr"/>
+      <c r="N104" s="5" t="inlineStr"/>
+      <c r="O104" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P104" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q104" s="6" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="P104" s="5" t="inlineStr">
+      <c r="R104" s="6" t="inlineStr">
         <is>
           <t>src/services/marketData.ts:53</t>
         </is>
@@ -7303,22 +7547,24 @@
         </is>
       </c>
       <c r="L105" s="3" t="inlineStr"/>
-      <c r="M105" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N105" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O105" s="5" t="inlineStr">
+      <c r="M105" s="5" t="inlineStr"/>
+      <c r="N105" s="5" t="inlineStr"/>
+      <c r="O105" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P105" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q105" s="6" t="inlineStr">
         <is>
           <t>PriceFreshness</t>
         </is>
       </c>
-      <c r="P105" s="5" t="inlineStr">
+      <c r="R105" s="6" t="inlineStr">
         <is>
           <t>src/services/marketData.ts:60</t>
         </is>
@@ -7380,22 +7626,24 @@
         </is>
       </c>
       <c r="L106" s="3" t="inlineStr"/>
-      <c r="M106" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N106" s="5" t="inlineStr">
+      <c r="M106" s="5" t="inlineStr"/>
+      <c r="N106" s="5" t="inlineStr"/>
+      <c r="O106" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P106" s="6" t="inlineStr">
         <is>
           <t>dedupeActivities, ingestSync</t>
         </is>
       </c>
-      <c r="O106" s="5" t="inlineStr">
+      <c r="Q106" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="P106" s="5" t="inlineStr">
+      <c r="R106" s="6" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:243</t>
         </is>
@@ -7454,22 +7702,24 @@
         </is>
       </c>
       <c r="L107" s="3" t="inlineStr"/>
-      <c r="M107" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N107" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O107" s="5" t="inlineStr">
+      <c r="M107" s="5" t="inlineStr"/>
+      <c r="N107" s="5" t="inlineStr"/>
+      <c r="O107" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P107" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q107" s="6" t="inlineStr">
         <is>
           <t>StActivity[]</t>
         </is>
       </c>
-      <c r="P107" s="5" t="inlineStr">
+      <c r="R107" s="6" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:255</t>
         </is>
@@ -7508,22 +7758,24 @@
           <t>ingestSync</t>
         </is>
       </c>
-      <c r="M108" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N108" s="5" t="inlineStr">
+      <c r="M108" s="5" t="inlineStr"/>
+      <c r="N108" s="5" t="inlineStr"/>
+      <c r="O108" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P108" s="6" t="inlineStr">
         <is>
           <t>ingestSync</t>
         </is>
       </c>
-      <c r="O108" s="5" t="inlineStr">
+      <c r="Q108" s="6" t="inlineStr">
         <is>
           <t>WrapperGuess</t>
         </is>
       </c>
-      <c r="P108" s="5" t="inlineStr">
+      <c r="R108" s="6" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:71</t>
         </is>
@@ -7591,22 +7843,24 @@
           <t>Nothing to change here. But it is the prime suspect for the $1.4m of phantom contributions and is proved innocent, so the search moves to whatever else writes DEPOSIT rows — manual entry, the CSV importer, or a transfer path. Trace that before touching anything.</t>
         </is>
       </c>
-      <c r="M109" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N109" s="5" t="inlineStr">
+      <c r="M109" s="5" t="inlineStr"/>
+      <c r="N109" s="5" t="inlineStr"/>
+      <c r="O109" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P109" s="6" t="inlineStr">
         <is>
           <t>ingestSync</t>
         </is>
       </c>
-      <c r="O109" s="5" t="inlineStr">
+      <c r="Q109" s="6" t="inlineStr">
         <is>
           <t>MappedActivity</t>
         </is>
       </c>
-      <c r="P109" s="5" t="inlineStr">
+      <c r="R109" s="6" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:184</t>
         </is>
@@ -7645,22 +7899,24 @@
           <t>ingestSync</t>
         </is>
       </c>
-      <c r="M110" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N110" s="5" t="inlineStr">
+      <c r="M110" s="5" t="inlineStr"/>
+      <c r="N110" s="5" t="inlineStr"/>
+      <c r="O110" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P110" s="6" t="inlineStr">
         <is>
           <t>ingestSync</t>
         </is>
       </c>
-      <c r="O110" s="5" t="inlineStr">
+      <c r="Q110" s="6" t="inlineStr">
         <is>
           <t>MappedOption | null</t>
         </is>
       </c>
-      <c r="P110" s="5" t="inlineStr">
+      <c r="R110" s="6" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:159</t>
         </is>
@@ -7738,22 +7994,24 @@
           <t>THE REAL FIX IS ONE CLASSIFIER, NOT TWO. The file path already knows commodities, crypto tickers, options and (once fixed) currencies; the broker path knows only the broker type code. Have the broker path call the same rules the file path uses, keeping the type code as a first pass where the broker is explicit. One engine, one answer — the whole point of this exercise.</t>
         </is>
       </c>
-      <c r="M111" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N111" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O111" s="5" t="inlineStr">
+      <c r="M111" s="5" t="inlineStr"/>
+      <c r="N111" s="5" t="inlineStr"/>
+      <c r="O111" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P111" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q111" s="6" t="inlineStr">
         <is>
           <t>MappedPosition | null</t>
         </is>
       </c>
-      <c r="P111" s="5" t="inlineStr">
+      <c r="R111" s="6" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:116</t>
         </is>
@@ -7792,22 +8050,24 @@
           <t>ingestSync</t>
         </is>
       </c>
-      <c r="M112" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N112" s="5" t="inlineStr">
+      <c r="M112" s="5" t="inlineStr"/>
+      <c r="N112" s="5" t="inlineStr"/>
+      <c r="O112" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P112" s="6" t="inlineStr">
         <is>
           <t>ingestSync</t>
         </is>
       </c>
-      <c r="O112" s="5" t="inlineStr">
+      <c r="Q112" s="6" t="inlineStr">
         <is>
           <t>string | undefined</t>
         </is>
       </c>
-      <c r="P112" s="5" t="inlineStr">
+      <c r="R112" s="6" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:282</t>
         </is>
@@ -7874,22 +8134,24 @@
           <t>FOUNDER DECISION FIRST, then a one-line change. Recommend: show the money-market fund as a holding (it pays dividends and belongs in the measured bucket per the 2026-08-04 rule), keep netCashSleeve exactly as it is, and DELETE the .filter((m) =&gt; !m.cashEquivalent) in ingest.ts:67. That leaves the money in exactly one place. The alternative — keep it in the sleeve and stop netting — contradicts the cash-means-cash rule, so I do not recommend it.</t>
         </is>
       </c>
-      <c r="M113" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N113" s="5" t="inlineStr">
+      <c r="M113" s="5" t="inlineStr"/>
+      <c r="N113" s="5" t="inlineStr"/>
+      <c r="O113" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P113" s="6" t="inlineStr">
         <is>
           <t>ingestSync</t>
         </is>
       </c>
-      <c r="O113" s="5" t="inlineStr">
+      <c r="Q113" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P113" s="5" t="inlineStr">
+      <c r="R113" s="6" t="inlineStr">
         <is>
           <t>src/services/sync/snaptrade.ts:269</t>
         </is>
@@ -7928,22 +8190,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M114" s="5" t="inlineStr">
+      <c r="M114" s="5" t="inlineStr"/>
+      <c r="N114" s="5" t="inlineStr"/>
+      <c r="O114" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N114" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O114" s="5" t="inlineStr">
+      <c r="P114" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q114" s="6" t="inlineStr">
         <is>
           <t>NetWorthState</t>
         </is>
       </c>
-      <c r="P114" s="5" t="inlineStr">
+      <c r="R114" s="6" t="inlineStr">
         <is>
           <t>src/domain/networth/index.ts:12</t>
         </is>
@@ -7982,22 +8246,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M115" s="5" t="inlineStr">
+      <c r="M115" s="5" t="inlineStr"/>
+      <c r="N115" s="5" t="inlineStr"/>
+      <c r="O115" s="6" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="N115" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O115" s="5" t="inlineStr">
+      <c r="P115" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q115" s="6" t="inlineStr">
         <is>
           <t>AllocSlice[]</t>
         </is>
       </c>
-      <c r="P115" s="5" t="inlineStr">
+      <c r="R115" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:226</t>
         </is>
@@ -8036,22 +8302,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M116" s="5" t="inlineStr">
+      <c r="M116" s="5" t="inlineStr"/>
+      <c r="N116" s="5" t="inlineStr"/>
+      <c r="O116" s="6" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="N116" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O116" s="5" t="inlineStr">
+      <c r="P116" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q116" s="6" t="inlineStr">
         <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="P116" s="5" t="inlineStr">
+      <c r="R116" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:215</t>
         </is>
@@ -8090,22 +8358,24 @@
           <t>buildPerformance</t>
         </is>
       </c>
-      <c r="M117" s="5" t="inlineStr">
+      <c r="M117" s="5" t="inlineStr"/>
+      <c r="N117" s="5" t="inlineStr"/>
+      <c r="O117" s="6" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="N117" s="5" t="inlineStr">
+      <c r="P117" s="6" t="inlineStr">
         <is>
           <t>buildPerformance</t>
         </is>
       </c>
-      <c r="O117" s="5" t="inlineStr">
+      <c r="Q117" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="P117" s="5" t="inlineStr">
+      <c r="R117" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:149</t>
         </is>
@@ -8144,22 +8414,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M118" s="5" t="inlineStr">
+      <c r="M118" s="5" t="inlineStr"/>
+      <c r="N118" s="5" t="inlineStr"/>
+      <c r="O118" s="6" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="N118" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O118" s="5" t="inlineStr">
+      <c r="P118" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q118" s="6" t="inlineStr">
         <is>
           <t>PerformanceRow[]</t>
         </is>
       </c>
-      <c r="P118" s="5" t="inlineStr">
+      <c r="R118" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:173</t>
         </is>
@@ -8223,22 +8495,24 @@
         </is>
       </c>
       <c r="L119" s="3" t="inlineStr"/>
-      <c r="M119" s="5" t="inlineStr">
+      <c r="M119" s="5" t="inlineStr"/>
+      <c r="N119" s="5" t="inlineStr"/>
+      <c r="O119" s="6" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="N119" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O119" s="5" t="inlineStr">
+      <c r="P119" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q119" s="6" t="inlineStr">
         <is>
           <t>CapGains</t>
         </is>
       </c>
-      <c r="P119" s="5" t="inlineStr">
+      <c r="R119" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:55</t>
         </is>
@@ -8299,22 +8573,24 @@
         </is>
       </c>
       <c r="L120" s="3" t="inlineStr"/>
-      <c r="M120" s="5" t="inlineStr">
+      <c r="M120" s="5" t="inlineStr"/>
+      <c r="N120" s="5" t="inlineStr"/>
+      <c r="O120" s="6" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="N120" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O120" s="5" t="inlineStr">
+      <c r="P120" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q120" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P120" s="5" t="inlineStr">
+      <c r="R120" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:69</t>
         </is>
@@ -8373,22 +8649,24 @@
         </is>
       </c>
       <c r="L121" s="3" t="inlineStr"/>
-      <c r="M121" s="5" t="inlineStr">
+      <c r="M121" s="5" t="inlineStr"/>
+      <c r="N121" s="5" t="inlineStr"/>
+      <c r="O121" s="6" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="N121" s="5" t="inlineStr">
+      <c r="P121" s="6" t="inlineStr">
         <is>
           <t>buildPerformance, totalROI, unrealizedGain</t>
         </is>
       </c>
-      <c r="O121" s="5" t="inlineStr">
+      <c r="Q121" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P121" s="5" t="inlineStr">
+      <c r="R121" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:38</t>
         </is>
@@ -8448,22 +8726,24 @@
         </is>
       </c>
       <c r="L122" s="3" t="inlineStr"/>
-      <c r="M122" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N122" s="5" t="inlineStr">
+      <c r="M122" s="5" t="inlineStr"/>
+      <c r="N122" s="5" t="inlineStr"/>
+      <c r="O122" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P122" s="6" t="inlineStr">
         <is>
           <t>buildPerformance</t>
         </is>
       </c>
-      <c r="O122" s="5" t="inlineStr">
+      <c r="Q122" s="6" t="inlineStr">
         <is>
           <t>string | null</t>
         </is>
       </c>
-      <c r="P122" s="5" t="inlineStr">
+      <c r="R122" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:128</t>
         </is>
@@ -8502,22 +8782,24 @@
           <t>lookBack</t>
         </is>
       </c>
-      <c r="M123" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N123" s="5" t="inlineStr">
+      <c r="M123" s="5" t="inlineStr"/>
+      <c r="N123" s="5" t="inlineStr"/>
+      <c r="O123" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P123" s="6" t="inlineStr">
         <is>
           <t>lookBack</t>
         </is>
       </c>
-      <c r="O123" s="5" t="inlineStr">
+      <c r="Q123" s="6" t="inlineStr">
         <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="P123" s="5" t="inlineStr">
+      <c r="R123" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/lookBack.ts:19</t>
         </is>
@@ -8556,22 +8838,24 @@
           <t>moneyWeightedReturn</t>
         </is>
       </c>
-      <c r="M124" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N124" s="5" t="inlineStr">
+      <c r="M124" s="5" t="inlineStr"/>
+      <c r="N124" s="5" t="inlineStr"/>
+      <c r="O124" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P124" s="6" t="inlineStr">
         <is>
           <t>moneyWeightedReturn</t>
         </is>
       </c>
-      <c r="O124" s="5" t="inlineStr">
+      <c r="Q124" s="6" t="inlineStr">
         <is>
           <t>boolean</t>
         </is>
       </c>
-      <c r="P124" s="5" t="inlineStr">
+      <c r="R124" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/moneyWeighted.ts:60</t>
         </is>
@@ -8610,22 +8894,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M125" s="5" t="inlineStr">
+      <c r="M125" s="5" t="inlineStr"/>
+      <c r="N125" s="5" t="inlineStr"/>
+      <c r="O125" s="6" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="N125" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O125" s="5" t="inlineStr">
+      <c r="P125" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q125" s="6" t="inlineStr">
         <is>
           <t>r is MoneyWeighted</t>
         </is>
       </c>
-      <c r="P125" s="5" t="inlineStr">
+      <c r="R125" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/moneyWeighted.ts:110</t>
         </is>
@@ -8684,22 +8970,24 @@
         </is>
       </c>
       <c r="L126" s="3" t="inlineStr"/>
-      <c r="M126" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N126" s="5" t="inlineStr">
+      <c r="M126" s="5" t="inlineStr"/>
+      <c r="N126" s="5" t="inlineStr"/>
+      <c r="O126" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P126" s="6" t="inlineStr">
         <is>
           <t>buildPerformance, periodReturn, periodReturnSince</t>
         </is>
       </c>
-      <c r="O126" s="5" t="inlineStr">
+      <c r="Q126" s="6" t="inlineStr">
         <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="P126" s="5" t="inlineStr">
+      <c r="R126" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:102</t>
         </is>
@@ -8738,22 +9026,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M127" s="5" t="inlineStr">
+      <c r="M127" s="5" t="inlineStr"/>
+      <c r="N127" s="5" t="inlineStr"/>
+      <c r="O127" s="6" t="inlineStr">
         <is>
           <t>LookBack</t>
         </is>
       </c>
-      <c r="N127" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O127" s="5" t="inlineStr">
+      <c r="P127" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q127" s="6" t="inlineStr">
         <is>
           <t>LookBackResult | null</t>
         </is>
       </c>
-      <c r="P127" s="5" t="inlineStr">
+      <c r="R127" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/lookBack.ts:32</t>
         </is>
@@ -8815,22 +9105,24 @@
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr"/>
-      <c r="M128" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N128" s="5" t="inlineStr">
+      <c r="M128" s="5" t="inlineStr"/>
+      <c r="N128" s="5" t="inlineStr"/>
+      <c r="O128" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P128" s="6" t="inlineStr">
         <is>
           <t>buildPerformance, unrealizedGain</t>
         </is>
       </c>
-      <c r="O128" s="5" t="inlineStr">
+      <c r="Q128" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P128" s="5" t="inlineStr">
+      <c r="R128" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:45</t>
         </is>
@@ -8869,22 +9161,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M129" s="5" t="inlineStr">
+      <c r="M129" s="5" t="inlineStr"/>
+      <c r="N129" s="5" t="inlineStr"/>
+      <c r="O129" s="6" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="N129" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O129" s="5" t="inlineStr">
+      <c r="P129" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q129" s="6" t="inlineStr">
         <is>
           <t>MoneyWeighted | MoneyWeightedMiss</t>
         </is>
       </c>
-      <c r="P129" s="5" t="inlineStr">
+      <c r="R129" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/moneyWeighted.ts:80</t>
         </is>
@@ -8951,22 +9245,24 @@
           <t>CHEAPER THAN IT LOOKS — the function already exists. periodReturnSince takes any two dates, is exported, and is called from nowhere. Wire it to a date-range option on the Performance chips. No new maths, and the Vanguard statement window becomes answerable.</t>
         </is>
       </c>
-      <c r="M130" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N130" s="5" t="inlineStr">
+      <c r="M130" s="5" t="inlineStr"/>
+      <c r="N130" s="5" t="inlineStr"/>
+      <c r="O130" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P130" s="6" t="inlineStr">
         <is>
           <t>buildPerformance</t>
         </is>
       </c>
-      <c r="O130" s="5" t="inlineStr">
+      <c r="Q130" s="6" t="inlineStr">
         <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="P130" s="5" t="inlineStr">
+      <c r="R130" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:107</t>
         </is>
@@ -9005,22 +9301,24 @@
           <t>buildPerformance</t>
         </is>
       </c>
-      <c r="M131" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N131" s="5" t="inlineStr">
+      <c r="M131" s="5" t="inlineStr"/>
+      <c r="N131" s="5" t="inlineStr"/>
+      <c r="O131" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P131" s="6" t="inlineStr">
         <is>
           <t>buildPerformance</t>
         </is>
       </c>
-      <c r="O131" s="5" t="inlineStr">
+      <c r="Q131" s="6" t="inlineStr">
         <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="P131" s="5" t="inlineStr">
+      <c r="R131" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:119</t>
         </is>
@@ -9059,22 +9357,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M132" s="5" t="inlineStr">
+      <c r="M132" s="5" t="inlineStr"/>
+      <c r="N132" s="5" t="inlineStr"/>
+      <c r="O132" s="6" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="N132" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O132" s="5" t="inlineStr">
+      <c r="P132" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q132" s="6" t="inlineStr">
         <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="P132" s="5" t="inlineStr">
+      <c r="R132" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:275</t>
         </is>
@@ -9113,22 +9413,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M133" s="5" t="inlineStr">
+      <c r="M133" s="5" t="inlineStr"/>
+      <c r="N133" s="5" t="inlineStr"/>
+      <c r="O133" s="6" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="N133" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O133" s="5" t="inlineStr">
+      <c r="P133" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q133" s="6" t="inlineStr">
         <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="P133" s="5" t="inlineStr">
+      <c r="R133" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:265</t>
         </is>
@@ -9167,22 +9469,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M134" s="5" t="inlineStr">
+      <c r="M134" s="5" t="inlineStr"/>
+      <c r="N134" s="5" t="inlineStr"/>
+      <c r="O134" s="6" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="N134" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O134" s="5" t="inlineStr">
+      <c r="P134" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q134" s="6" t="inlineStr">
         <is>
           <t>TrendPoint[]</t>
         </is>
       </c>
-      <c r="P134" s="5" t="inlineStr">
+      <c r="R134" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:239</t>
         </is>
@@ -9221,22 +9525,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M135" s="5" t="inlineStr">
+      <c r="M135" s="5" t="inlineStr"/>
+      <c r="N135" s="5" t="inlineStr"/>
+      <c r="O135" s="6" t="inlineStr">
         <is>
           <t>HoldingDetail</t>
         </is>
       </c>
-      <c r="N135" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O135" s="5" t="inlineStr">
+      <c r="P135" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q135" s="6" t="inlineStr">
         <is>
           <t>RealizedResult</t>
         </is>
       </c>
-      <c r="P135" s="5" t="inlineStr">
+      <c r="R135" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/realized.ts:14</t>
         </is>
@@ -9296,22 +9602,24 @@
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr"/>
-      <c r="M136" s="5" t="inlineStr">
+      <c r="M136" s="5" t="inlineStr"/>
+      <c r="N136" s="5" t="inlineStr"/>
+      <c r="O136" s="6" t="inlineStr">
         <is>
           <t>HoldingDetail</t>
         </is>
       </c>
-      <c r="N136" s="5" t="inlineStr">
+      <c r="P136" s="6" t="inlineStr">
         <is>
           <t>buildPerformance, periodReturn, portfolioTrend</t>
         </is>
       </c>
-      <c r="O136" s="5" t="inlineStr">
+      <c r="Q136" s="6" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="P136" s="5" t="inlineStr">
+      <c r="R136" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:81</t>
         </is>
@@ -9350,22 +9658,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M137" s="5" t="inlineStr">
+      <c r="M137" s="5" t="inlineStr"/>
+      <c r="N137" s="5" t="inlineStr"/>
+      <c r="O137" s="6" t="inlineStr">
         <is>
           <t>Performance</t>
         </is>
       </c>
-      <c r="N137" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O137" s="5" t="inlineStr">
+      <c r="P137" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q137" s="6" t="inlineStr">
         <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="P137" s="5" t="inlineStr">
+      <c r="R137" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:205</t>
         </is>
@@ -9430,22 +9740,24 @@
           <t>Not a defect, but the screen must never place this beside a period return without saying they measure different things.</t>
         </is>
       </c>
-      <c r="M138" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N138" s="5" t="inlineStr">
+      <c r="M138" s="5" t="inlineStr"/>
+      <c r="N138" s="5" t="inlineStr"/>
+      <c r="O138" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P138" s="6" t="inlineStr">
         <is>
           <t>buildPerformance</t>
         </is>
       </c>
-      <c r="O138" s="5" t="inlineStr">
+      <c r="Q138" s="6" t="inlineStr">
         <is>
           <t>number | null</t>
         </is>
       </c>
-      <c r="P138" s="5" t="inlineStr">
+      <c r="R138" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:74</t>
         </is>
@@ -9504,22 +9816,24 @@
         </is>
       </c>
       <c r="L139" s="3" t="inlineStr"/>
-      <c r="M139" s="5" t="inlineStr">
+      <c r="M139" s="5" t="inlineStr"/>
+      <c r="N139" s="5" t="inlineStr"/>
+      <c r="O139" s="6" t="inlineStr">
         <is>
           <t>HoldingDetail, Performance</t>
         </is>
       </c>
-      <c r="N139" s="5" t="inlineStr">
+      <c r="P139" s="6" t="inlineStr">
         <is>
           <t>marketValue, portfolioTrend</t>
         </is>
       </c>
-      <c r="O139" s="5" t="inlineStr">
+      <c r="Q139" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P139" s="5" t="inlineStr">
+      <c r="R139" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:35</t>
         </is>
@@ -9580,22 +9894,24 @@
         </is>
       </c>
       <c r="L140" s="3" t="inlineStr"/>
-      <c r="M140" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N140" s="5" t="inlineStr">
+      <c r="M140" s="5" t="inlineStr"/>
+      <c r="N140" s="5" t="inlineStr"/>
+      <c r="O140" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P140" s="6" t="inlineStr">
         <is>
           <t>buildPerformance, totalROI</t>
         </is>
       </c>
-      <c r="O140" s="5" t="inlineStr">
+      <c r="Q140" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P140" s="5" t="inlineStr">
+      <c r="R140" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/index.ts:49</t>
         </is>
@@ -9634,22 +9950,24 @@
           <t>moneyWeightedReturn</t>
         </is>
       </c>
-      <c r="M141" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N141" s="5" t="inlineStr">
+      <c r="M141" s="5" t="inlineStr"/>
+      <c r="N141" s="5" t="inlineStr"/>
+      <c r="O141" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P141" s="6" t="inlineStr">
         <is>
           <t>moneyWeightedReturn</t>
         </is>
       </c>
-      <c r="O141" s="5" t="inlineStr">
+      <c r="Q141" s="6" t="inlineStr">
         <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="P141" s="5" t="inlineStr">
+      <c r="R141" s="6" t="inlineStr">
         <is>
           <t>src/domain/performance/moneyWeighted.ts:27</t>
         </is>
@@ -9688,22 +10006,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M142" s="5" t="inlineStr">
+      <c r="M142" s="5" t="inlineStr"/>
+      <c r="N142" s="5" t="inlineStr"/>
+      <c r="O142" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N142" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O142" s="5" t="inlineStr">
+      <c r="P142" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q142" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="P142" s="5" t="inlineStr">
+      <c r="R142" s="6" t="inlineStr">
         <is>
           <t>src/domain/planning/hub.ts:30</t>
         </is>
@@ -9742,22 +10062,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M143" s="5" t="inlineStr">
+      <c r="M143" s="5" t="inlineStr"/>
+      <c r="N143" s="5" t="inlineStr"/>
+      <c r="O143" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N143" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O143" s="5" t="inlineStr">
+      <c r="P143" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q143" s="6" t="inlineStr">
         <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="P143" s="5" t="inlineStr">
+      <c r="R143" s="6" t="inlineStr">
         <is>
           <t>src/domain/planning/hub.ts:165</t>
         </is>
@@ -9796,22 +10118,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M144" s="5" t="inlineStr">
+      <c r="M144" s="5" t="inlineStr"/>
+      <c r="N144" s="5" t="inlineStr"/>
+      <c r="O144" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N144" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O144" s="5" t="inlineStr">
+      <c r="P144" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q144" s="6" t="inlineStr">
         <is>
           <t>PlanDoor</t>
         </is>
       </c>
-      <c r="P144" s="5" t="inlineStr">
+      <c r="R144" s="6" t="inlineStr">
         <is>
           <t>src/domain/planning/hub.ts:44</t>
         </is>
@@ -9850,22 +10174,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M145" s="5" t="inlineStr">
+      <c r="M145" s="5" t="inlineStr"/>
+      <c r="N145" s="5" t="inlineStr"/>
+      <c r="O145" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N145" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O145" s="5" t="inlineStr">
+      <c r="P145" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q145" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="P145" s="5" t="inlineStr">
+      <c r="R145" s="6" t="inlineStr">
         <is>
           <t>src/domain/planning/hub.ts:152</t>
         </is>
@@ -9904,22 +10230,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M146" s="5" t="inlineStr">
+      <c r="M146" s="5" t="inlineStr"/>
+      <c r="N146" s="5" t="inlineStr"/>
+      <c r="O146" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N146" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O146" s="5" t="inlineStr">
+      <c r="P146" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q146" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="P146" s="5" t="inlineStr">
+      <c r="R146" s="6" t="inlineStr">
         <is>
           <t>src/domain/planning/hub.ts:34</t>
         </is>
@@ -9958,22 +10286,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M147" s="5" t="inlineStr">
+      <c r="M147" s="5" t="inlineStr"/>
+      <c r="N147" s="5" t="inlineStr"/>
+      <c r="O147" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N147" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O147" s="5" t="inlineStr">
+      <c r="P147" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q147" s="6" t="inlineStr">
         <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="P147" s="5" t="inlineStr">
+      <c r="R147" s="6" t="inlineStr">
         <is>
           <t>src/domain/planning/hub.ts:162</t>
         </is>
@@ -10012,22 +10342,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M148" s="5" t="inlineStr">
+      <c r="M148" s="5" t="inlineStr"/>
+      <c r="N148" s="5" t="inlineStr"/>
+      <c r="O148" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N148" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O148" s="5" t="inlineStr">
+      <c r="P148" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q148" s="6" t="inlineStr">
         <is>
           <t>Lens</t>
         </is>
       </c>
-      <c r="P148" s="5" t="inlineStr">
+      <c r="R148" s="6" t="inlineStr">
         <is>
           <t>src/domain/profile/lens.ts:17</t>
         </is>
@@ -10066,22 +10398,24 @@
           <t>retirementSpendMonthly</t>
         </is>
       </c>
-      <c r="M149" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N149" s="5" t="inlineStr">
+      <c r="M149" s="5" t="inlineStr"/>
+      <c r="N149" s="5" t="inlineStr"/>
+      <c r="O149" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P149" s="6" t="inlineStr">
         <is>
           <t>retirementSpendMonthly</t>
         </is>
       </c>
-      <c r="O149" s="5" t="inlineStr">
+      <c r="Q149" s="6" t="inlineStr">
         <is>
           <t>ColMatch</t>
         </is>
       </c>
-      <c r="P149" s="5" t="inlineStr">
+      <c r="R149" s="6" t="inlineStr">
         <is>
           <t>src/domain/retirement/col.ts:53</t>
         </is>
@@ -10120,22 +10454,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M150" s="5" t="inlineStr">
+      <c r="M150" s="5" t="inlineStr"/>
+      <c r="N150" s="5" t="inlineStr"/>
+      <c r="O150" s="6" t="inlineStr">
         <is>
           <t>NetWorth, WhatIf</t>
         </is>
       </c>
-      <c r="N150" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O150" s="5" t="inlineStr">
+      <c r="P150" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q150" s="6" t="inlineStr">
         <is>
           <t>NestEggProjection</t>
         </is>
       </c>
-      <c r="P150" s="5" t="inlineStr">
+      <c r="R150" s="6" t="inlineStr">
         <is>
           <t>src/domain/retirement/index.ts:294</t>
         </is>
@@ -10174,22 +10510,24 @@
           <t>selectWillItLast, willItLastInputs</t>
         </is>
       </c>
-      <c r="M151" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N151" s="5" t="inlineStr">
+      <c r="M151" s="5" t="inlineStr"/>
+      <c r="N151" s="5" t="inlineStr"/>
+      <c r="O151" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P151" s="6" t="inlineStr">
         <is>
           <t>selectWillItLast, willItLastInputs</t>
         </is>
       </c>
-      <c r="O151" s="5" t="inlineStr">
+      <c r="Q151" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P151" s="5" t="inlineStr">
+      <c r="R151" s="6" t="inlineStr">
         <is>
           <t>src/domain/retirement/index.ts:48</t>
         </is>
@@ -10228,22 +10566,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M152" s="5" t="inlineStr">
+      <c r="M152" s="5" t="inlineStr"/>
+      <c r="N152" s="5" t="inlineStr"/>
+      <c r="O152" s="6" t="inlineStr">
         <is>
           <t>NetWorth</t>
         </is>
       </c>
-      <c r="N152" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O152" s="5" t="inlineStr">
+      <c r="P152" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q152" s="6" t="inlineStr">
         <is>
           <t>WillItLastResult</t>
         </is>
       </c>
-      <c r="P152" s="5" t="inlineStr">
+      <c r="R152" s="6" t="inlineStr">
         <is>
           <t>src/domain/retirement/willItLast.ts:115</t>
         </is>
@@ -10282,22 +10622,24 @@
           <t>selectWillItLast</t>
         </is>
       </c>
-      <c r="M153" s="5" t="inlineStr">
+      <c r="M153" s="5" t="inlineStr"/>
+      <c r="N153" s="5" t="inlineStr"/>
+      <c r="O153" s="6" t="inlineStr">
         <is>
           <t>NetWorth, WhatIf</t>
         </is>
       </c>
-      <c r="N153" s="5" t="inlineStr">
+      <c r="P153" s="6" t="inlineStr">
         <is>
           <t>selectWillItLast</t>
         </is>
       </c>
-      <c r="O153" s="5" t="inlineStr">
+      <c r="Q153" s="6" t="inlineStr">
         <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="P153" s="5" t="inlineStr">
+      <c r="R153" s="6" t="inlineStr">
         <is>
           <t>src/domain/retirement/index.ts:160</t>
         </is>
@@ -10336,22 +10678,24 @@
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="M154" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N154" s="5" t="inlineStr">
+      <c r="M154" s="5" t="inlineStr"/>
+      <c r="N154" s="5" t="inlineStr"/>
+      <c r="O154" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P154" s="6" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="O154" s="5" t="inlineStr">
+      <c r="Q154" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P154" s="5" t="inlineStr">
+      <c r="R154" s="6" t="inlineStr">
         <is>
           <t>src/domain/retirement/ssTiming.ts:25</t>
         </is>
@@ -10390,22 +10734,24 @@
           <t>ssBenefitAtClaimAge</t>
         </is>
       </c>
-      <c r="M155" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N155" s="5" t="inlineStr">
+      <c r="M155" s="5" t="inlineStr"/>
+      <c r="N155" s="5" t="inlineStr"/>
+      <c r="O155" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P155" s="6" t="inlineStr">
         <is>
           <t>ssBenefitAtClaimAge</t>
         </is>
       </c>
-      <c r="O155" s="5" t="inlineStr">
+      <c r="Q155" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P155" s="5" t="inlineStr">
+      <c r="R155" s="6" t="inlineStr">
         <is>
           <t>src/domain/retirement/ssTiming.ts:12</t>
         </is>
@@ -10444,22 +10790,24 @@
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="M156" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N156" s="5" t="inlineStr">
+      <c r="M156" s="5" t="inlineStr"/>
+      <c r="N156" s="5" t="inlineStr"/>
+      <c r="O156" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P156" s="6" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="O156" s="5" t="inlineStr">
+      <c r="Q156" s="6" t="inlineStr">
         <is>
           <t>(inferred)</t>
         </is>
       </c>
-      <c r="P156" s="5" t="inlineStr">
+      <c r="R156" s="6" t="inlineStr">
         <is>
           <t>src/domain/retirement/willItLast.ts:19</t>
         </is>
@@ -10498,22 +10846,24 @@
           <t>selectWillItLast</t>
         </is>
       </c>
-      <c r="M157" s="5" t="inlineStr">
+      <c r="M157" s="5" t="inlineStr"/>
+      <c r="N157" s="5" t="inlineStr"/>
+      <c r="O157" s="6" t="inlineStr">
         <is>
           <t>NetWorth, WhatIf</t>
         </is>
       </c>
-      <c r="N157" s="5" t="inlineStr">
+      <c r="P157" s="6" t="inlineStr">
         <is>
           <t>selectWillItLast</t>
         </is>
       </c>
-      <c r="O157" s="5" t="inlineStr">
+      <c r="Q157" s="6" t="inlineStr">
         <is>
           <t>RetirementInputs | null</t>
         </is>
       </c>
-      <c r="P157" s="5" t="inlineStr">
+      <c r="R157" s="6" t="inlineStr">
         <is>
           <t>src/domain/retirement/willItLast.ts:47</t>
         </is>
@@ -10552,22 +10902,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M158" s="5" t="inlineStr">
+      <c r="M158" s="5" t="inlineStr"/>
+      <c r="N158" s="5" t="inlineStr"/>
+      <c r="O158" s="6" t="inlineStr">
         <is>
           <t>Performance, WhatIf</t>
         </is>
       </c>
-      <c r="N158" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O158" s="5" t="inlineStr">
+      <c r="P158" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q158" s="6" t="inlineStr">
         <is>
           <t>NetWorthRows</t>
         </is>
       </c>
-      <c r="P158" s="5" t="inlineStr">
+      <c r="R158" s="6" t="inlineStr">
         <is>
           <t>src/domain/snapshot.ts:121</t>
         </is>
@@ -10606,22 +10958,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M159" s="5" t="inlineStr">
+      <c r="M159" s="5" t="inlineStr"/>
+      <c r="N159" s="5" t="inlineStr"/>
+      <c r="O159" s="6" t="inlineStr">
         <is>
           <t>AccountDetail, Performance</t>
         </is>
       </c>
-      <c r="N159" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O159" s="5" t="inlineStr">
+      <c r="P159" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q159" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P159" s="5" t="inlineStr">
+      <c r="R159" s="6" t="inlineStr">
         <is>
           <t>src/domain/transactions/index.ts:227</t>
         </is>
@@ -10660,22 +11014,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M160" s="5" t="inlineStr">
+      <c r="M160" s="5" t="inlineStr"/>
+      <c r="N160" s="5" t="inlineStr"/>
+      <c r="O160" s="6" t="inlineStr">
         <is>
           <t>AccountDetail, Performance</t>
         </is>
       </c>
-      <c r="N160" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O160" s="5" t="inlineStr">
+      <c r="P160" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q160" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="P160" s="5" t="inlineStr">
+      <c r="R160" s="6" t="inlineStr">
         <is>
           <t>src/domain/transactions/index.ts:224</t>
         </is>
@@ -10683,7 +11039,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -10697,7 +11053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10712,10 +11068,12 @@
     <col width="52" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="52" customWidth="1" min="12" max="12"/>
-    <col width="28" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="26" customWidth="1" min="15" max="15"/>
-    <col width="40" customWidth="1" min="16" max="16"/>
+    <col width="46" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="46" customHeight="1">
@@ -10788,20 +11146,30 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
+          <t>YOUR COMMENT / QUESTION</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>YOUR VERDICT</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
           <t>Screens</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Called by</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>Returns</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -10840,22 +11208,24 @@
           <t>formatMoney, formatMoneyCents, moneyCompact</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>AccountDetail, Itemize, LookBack, NetWorth</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="P3" s="6" t="inlineStr">
         <is>
           <t>formatMoney, formatMoneyCents, moneyCompact</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>src/domain/_shared/money.ts:52</t>
         </is>
@@ -10894,22 +11264,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="6" t="inlineStr">
         <is>
           <t>HoldingDetail, Itemize, NetWorth, Performance</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>src/domain/_shared/num.ts:9</t>
         </is>
@@ -10948,22 +11320,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>ImportHoldings, Performance</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>src/domain/_shared/num.ts:11</t>
         </is>
@@ -11002,22 +11376,24 @@
           <t>—</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="6" t="inlineStr">
         <is>
           <t>NetWorth, Performance</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>src/domain/_shared/money.ts:88</t>
         </is>
@@ -11056,22 +11432,24 @@
           <t>accountClassBreakdown, actualDebtPayment, allocation, annualCoupon, assetAllocation, buildAssetsState, buildDebtState, buildItemizedAccounts, buildNetWorth, capGains, capGainsTax, cashTotal, costBasis, earmarkedAmount, itemizeRemainder, itemizedTotal, lookBack, marketValue, minimumDebtService, normalizeSnapshot, planDoor, projectNestEgg, retirementEarmarkedValue, retirementSpendMonthly, salaryGrossByMonth, simulate, taxBucketSplit, trendPoints, unrealizedGain</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="6" t="inlineStr">
         <is>
           <t>ImportHoldings</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="P7" s="6" t="inlineStr">
         <is>
           <t>accountClassBreakdown, actualDebtPayment, allocation, annualCoupon, assetAllocation, buildAssetsState, buildDebtState, buildItemizedAccounts, buildNetWorth, capGains, capGainsTax, cashTotal, costBasis, earmarkedAmount, itemizeRemainder, itemizedTotal, lookBack, marketValue, minimumDebtService, normalizeSnapshot, planDoor, projectNestEgg, retirementEarmarkedValue, retirementSpendMonthly, salaryGrossByMonth, simulate, taxBucketSplit, trendPoints, unrealizedGain</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>number</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>src/domain/_shared/num.ts:12</t>
         </is>
@@ -11079,7 +11457,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -11106,7 +11484,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="60" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>HOW A LINE BECOMES A CLASS — every row below is a real holding as an institution actually sends it, run through the live code. The last two columns are what the app decides, and they do not always agree: a holding you UPLOAD and the same holding from a CONNECTED broker go through two different classifiers. Where they differ, the row is a defect and it is named as one. Proved by probes/classification-crosspath.probe.test.ts.</t>
         </is>
@@ -11150,555 +11528,555 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>A share in a company</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>APPLE INC</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>nothing else matches → the default is Stocks / Funds</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>Stocks / Funds</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>Stocks / Funds</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>nothing else matches → the default is Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>A stock-market ETF</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>VTI</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>VANGUARD TOTAL STOCK MARKET ETF</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>nothing else matches → the default is Stocks / Funds</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="inlineStr">
-        <is>
-          <t>Stocks / Funds</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>Stocks / Funds</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>nothing else matches → the default is Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>A money-market fund</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>VMFXX</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>VANGUARD FEDERAL MONEY MARKET FUND</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>the ticker is on the money-market list, AND the name contains MONEY MARKET → Stocks / Funds (founder rule 2026-08-04: it pays dividends, so it must be measured)</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>Stocks / Funds</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Stocks / Funds</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>the ticker is on the money-market list, AND the name contains MONEY MARKET → Stocks / ETFs (founder rule 2026-08-04: it pays dividends, so it must be measured)</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Uninvested cash at the broker</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>SETTLEMENT FUND / SWEEP</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>the name contains SWEEP or SETTLEMENT → Cash. This is the only thing that counts as cash.</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>Cash</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>A brokered CD</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>06418AAA1</t>
         </is>
       </c>
-      <c r="C7" s="7" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>KEYBANK NA 4.00% CD 08/24/26</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>the description contains CD → Bonds &amp; CDs. Note it arrives with an equity type code and a CUSIP, not a ticker — the words in the description are the only thing that identifies it.</t>
         </is>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Bonds &amp; CDs</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>Bonds &amp; CDs</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>A Treasury bill</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>912797TZ8</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>US TREASURY BILL 02/12/27</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>the description contains TREASURY or T-BILL → Bonds &amp; CDs</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t>Bonds &amp; CDs</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>Bonds &amp; CDs</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>A short-Treasury ETF</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>SGOV</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>ISHARES 0-3 MONTH TREASURY BOND ETF</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>the ticker is on the T-bill ETF list (SGOV, BIL) → Bonds &amp; CDs</t>
         </is>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr">
         <is>
           <t>Bonds &amp; CDs</t>
         </is>
       </c>
-      <c r="F9" s="7" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>Bonds &amp; CDs</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>A corporate bond</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>APPLE INC 3.85% DUE 2043</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>a percentage followed by DUE or a year → Bonds &amp; CDs. This pattern is what catches a bond whose description never uses the word 'bond'.</t>
         </is>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t>Bonds &amp; CDs</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>Bonds &amp; CDs</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Bitcoin held at the broker</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>BTC</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>BITCOIN</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>the broker's own type code says crypto → Alternatives</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F11" s="8" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>A gold fund</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>GLD</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>SPDR GOLD SHARES</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>FILE: the ticker is on the commodity list → Alternatives. BROKER: no commodity rule exists, so it falls through to the equity default.</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>Stocks / Funds</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>NO — defect</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>A spot-bitcoin ETF</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>IBIT</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>ISHARES BITCOIN TRUST</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>FILE: the ticker is on the crypto list → Alternatives. BROKER: it arrives with the ordinary equity type code, and only the type code is checked.</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>Stocks / Funds</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>NO — defect</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>An option contract</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>AAPL250117C00220000</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>AAPL JAN 17 25 CALL 220</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>FILE: the symbol matches the standard option shape (root + date + C/P + strike) → Alternatives. BROKER: options normally arrive on a separate feed and are handled correctly there; one written into the ordinary positions list is read as a share.</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Stocks / Funds</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>NO — defect</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>A currency fund</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>FXE</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>INVESCO CURRENCYSHARES EURO TRUST</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>NEITHER path catches it. The only currency rule looks for the word CURRENCY standing alone, and brokers shorten the name to CURRENCYSHARES — one word. There is no currency ticker list, unlike crypto and commodities.</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Stocks / Funds</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>Stocks / Funds</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>NO — both wrong</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>A gold mining company</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>GOLD</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>BARRICK GOLD CORP</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>the name contains GOLD, but also CORP — a company word, so the commodity rule is deliberately skipped and it stays a share. This one is RIGHT and worth keeping.</t>
         </is>
       </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Stocks / Funds</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Stocks / Funds</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Stocks / ETFs</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>A whole account with nothing itemised</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>e.g. a 401(k) with no holdings listed</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>no positions, no explicit class → Unclassified. It is NOT assumed to be stocks — the honest answer is that we do not know what is inside it.</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F17" s="8" t="inlineStr">
         <is>
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -11730,34 +12108,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>FIELD DICTIONARY — one canonical name per concept, used identically on every screen. Filled during Phase 3, for founder approval BEFORE any renaming happens.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Canonical name</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>What it means, plainly</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>Names it replaces</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>Where it is shown</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>Decided</t>
         </is>
@@ -11788,29 +12166,29 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>OPEN QUESTIONS — anything I could not settle from the code alone. A question here is better than a guess in the inventory.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>Why it matters</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -5077,21 +5077,50 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr"/>
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>ALLOCATION_BY_HOLDING_KIND</t>
+        </is>
+      </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
           <t>allocation</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr"/>
-      <c r="D59" s="3" t="inlineStr"/>
-      <c r="E59" s="3" t="inlineStr"/>
-      <c r="F59" s="3" t="inlineStr"/>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>How is my invested money spread?  Answers: a slice per account type plus one for cash, each with a dollar figure and a percentage, biggest first.</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Add up the value of the holdings in each account type, add cash as its own slice, and express each as a percentage of the whole. Percentages to one decimal.
+Negative cash is treated as zero rather than eating into the total.
+This groups by the ACCOUNT TYPE of each holding, which is a different question from ALLOCATION_BY_CLASS on Net worth — that one groups by asset class across every account, including the house. The two answer different questions and will not match.</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>each holding → rows[].position.kind
+its value → rows[].marketValue
+cash → cash</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>The per-holding rows from PERFORMANCE_TABLE — each already carrying its value, its return and its benchmark. See that row for where each of those comes from.
+cash: the uninvested balance, after CASH_SLEEVE has removed the double-counted money-market funds.</t>
+        </is>
+      </c>
       <c r="G59" s="3" t="inlineStr"/>
-      <c r="H59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-portfolio.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -5101,7 +5130,7 @@
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
@@ -5143,21 +5172,50 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr"/>
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>WHAT_DROVE_THE_RETURN</t>
+        </is>
+      </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
           <t>attribution</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr"/>
-      <c r="D60" s="3" t="inlineStr"/>
-      <c r="E60" s="3" t="inlineStr"/>
-      <c r="F60" s="3" t="inlineStr"/>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Which holdings moved my portfolio, and by how much?
+Answers: a list, best first, each with its share of the portfolio and how many points of the overall return it accounts for.</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>For each holding: its share of the total value × its own return for the period. The results add up (near enough) to the portfolio return, and are sorted best to worst so winners and drags both read off the top and bottom.
+A holding with NO return is left out entirely rather than counted as zero — counting an unpriced holding as flat would drag the portfolio figure down for no reason.
+Nothing invested → an empty list, not a division by zero.</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>each holding → rows[].position
+its value → rows[].marketValue
+its return → rows[].periodReturn</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>The per-holding rows from PERFORMANCE_TABLE — each already carrying its value, its return and its benchmark. See that row for where each of those comes from.</t>
+        </is>
+      </c>
       <c r="G60" s="3" t="inlineStr"/>
-      <c r="H60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-portfolio.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -5167,7 +5225,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
@@ -5209,21 +5267,46 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr"/>
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>BENCHMARK_FOR_KIND</t>
+        </is>
+      </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
           <t>benchmarkTicker</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr"/>
-      <c r="D61" s="3" t="inlineStr"/>
-      <c r="E61" s="3" t="inlineStr"/>
-      <c r="F61" s="3" t="inlineStr"/>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>What should this holding be compared against?  Answers: a fund ticker — SPY for shares and funds, AGG for bonds and annuities, AOR (a 60/40 mix) for retirement wrappers, GLD for commodities, BTC for crypto, PSP for private equity, QAI for hedge funds. Anything unrecognised gets SPY.</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Look the account type up in our own benchmark table. No match → SPY.
+This decides what "you beat the market by" means for each holding, so the choice is a judgement, not a fact: comparing a bond fund to the S&amp;P would make it look permanently terrible.</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>account type → kind</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>OUR OWN TABLE — BENCHMARK_TICKER in src/domain/performance. We chose these; no institution supplies them. The price for whichever ticker it names then comes from the market-data feed.</t>
+        </is>
+      </c>
       <c r="G61" s="3" t="inlineStr"/>
-      <c r="H61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-portfolio.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>HoldingDetail, Performance</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -5233,7 +5316,7 @@
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>HoldingDetail, Performance</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
@@ -5627,21 +5710,48 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr"/>
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>PRICE_FACTOR_OVER_WINDOW</t>
+        </is>
+      </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
           <t>factorOverMonths</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr"/>
-      <c r="D66" s="3" t="inlineStr"/>
-      <c r="E66" s="3" t="inlineStr"/>
-      <c r="F66" s="3" t="inlineStr"/>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>By what multiple did this price move over the last N months?  Answers: a multiple such as 1.10 for a 10% rise — or nothing when the history does not reach that far back.</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Latest close ÷ the close on or before the date N months ago.
+IF THE SERIES DOES NOT START ON OR BEFORE THAT DATE, THE ANSWER IS NOTHING. A price is never extrapolated backwards, because a made-up starting price makes the whole comparison a fiction.</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>the price series → series
+how far back → months
+today → now</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>The market-data cache (Tiingo / Yahoo), keyed by ticker, with the timestamp of the last successful fetch. Not from the broker.</t>
+        </is>
+      </c>
       <c r="G66" s="3" t="inlineStr"/>
-      <c r="H66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-portfolio.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
@@ -5651,7 +5761,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
@@ -5693,21 +5803,49 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr"/>
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>PERSONAL_RETURN_POSSIBLE</t>
+        </is>
+      </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
           <t>historyIsComplete</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr"/>
-      <c r="D67" s="3" t="inlineStr"/>
-      <c r="E67" s="3" t="inlineStr"/>
-      <c r="F67" s="3" t="inlineStr"/>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Can a personal return honestly be worked out for these accounts?  Answers: yes · no.</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>For every measured account, find its earliest transaction. It must be an opening balance, an opening position, or a deposit. An account whose first record is a sale had a balance before the ledger began, and that balance cannot be reconstructed — so no.
+No transactions at all → no.
+This is a REFUSAL RULE, and it is the right kind: a balance older than its own history cannot be measured, and inventing a starting point is exactly the mistake that produced a negative beginning market value in the net-worth walk.</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>the ledger → transactions
+the accounts → accounts
+which are measured → accountIds</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>The transaction ledger — every activity, built from the broker feed by INGEST_ACTIVITY_TYPE (SnapTrade activities[]: type, date, amount), plus anything logged by hand. This is the same ledger the change walk uses, so an error here shows up in BOTH the personal return and the net-worth change.</t>
+        </is>
+      </c>
       <c r="G67" s="3" t="inlineStr"/>
-      <c r="H67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-portfolio.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
@@ -5717,7 +5855,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
@@ -5759,21 +5897,45 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr"/>
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>PERSONAL_RETURN_ANSWERED</t>
+        </is>
+      </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
           <t>isMoneyWeighted</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr"/>
-      <c r="D68" s="3" t="inlineStr"/>
-      <c r="E68" s="3" t="inlineStr"/>
-      <c r="F68" s="3" t="inlineStr"/>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Did the personal return produce a number, or a reason it could not?  Answers: yes · no.</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Answers yes when a rate came back, no when a reason came back. It exists so a screen must handle the refusal explicitly and cannot accidentally print a missing rate as 0%.</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>the result → r</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Nothing external at all — its only input is what PERSONAL_RETURN handed back. See that row for the ledger and the balances underneath it. Listed here because a screen that skips this check would print a refusal as if it were a number.</t>
+        </is>
+      </c>
       <c r="G68" s="3" t="inlineStr"/>
-      <c r="H68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-portfolio.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
@@ -5783,7 +5945,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
@@ -5911,21 +6073,46 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr"/>
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>BENCHMARK_RETURN_BLENDED</t>
+        </is>
+      </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
           <t>portfolioBenchReturn</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr"/>
-      <c r="D70" s="3" t="inlineStr"/>
-      <c r="E70" s="3" t="inlineStr"/>
-      <c r="F70" s="3" t="inlineStr"/>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>What would the matching benchmarks have done over the same period?  Answers: a percentage, or nothing.</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>The same money-weighted blend, over each holding's own benchmark rather than the holding itself. Blending the benchmarks the same way is what makes "you beat it by" a fair statement rather than a comparison against a single index nobody holds.</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>each holding's benchmark return → rows[].benchReturn
+its value → rows[].marketValue</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>The per-holding rows from PERFORMANCE_TABLE — each already carrying its value, its return and its benchmark. See that row for where each of those comes from.</t>
+        </is>
+      </c>
       <c r="G70" s="3" t="inlineStr"/>
-      <c r="H70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-portfolio.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
@@ -5935,7 +6122,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
@@ -5977,21 +6164,50 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr"/>
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>PORTFOLIO_RETURN</t>
+        </is>
+      </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
           <t>portfolioPeriodReturn</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr"/>
-      <c r="D71" s="3" t="inlineStr"/>
-      <c r="E71" s="3" t="inlineStr"/>
-      <c r="F71" s="3" t="inlineStr"/>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>How did everything I hold do over the chosen period?  Answers: a percentage, or nothing when no holding has both a value and a return.</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Weight each holding's return by how much money is in it, and add: Σ(return × value) ÷ Σ(value).
+Money-weighted, not an equal average: $90,000 up 10% and $10,000 flat is +9%, where averaging the two would say +5% and be badly wrong.
+A holding with no return is dropped from BOTH the top and the bottom of the sum, so it neither drags the answer down nor distorts the weights.
+Nothing usable → nothing, never 0%.
+This is a PRICE-based return. It does not know when you added money, which is what PERSONAL_RETURN answers — the two will differ, and both are right about different questions.</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>each holding's return → rows[].periodReturn
+its value → rows[].marketValue</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>The per-holding rows from PERFORMANCE_TABLE — each already carrying its value, its return and its benchmark. See that row for where each of those comes from.</t>
+        </is>
+      </c>
       <c r="G71" s="3" t="inlineStr"/>
-      <c r="H71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-portfolio.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
@@ -6001,7 +6217,7 @@
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
@@ -6043,21 +6259,51 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr"/>
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>REALISED_GAIN</t>
+        </is>
+      </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
           <t>realizedFromLedger</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr"/>
-      <c r="D72" s="3" t="inlineStr"/>
-      <c r="E72" s="3" t="inlineStr"/>
-      <c r="F72" s="3" t="inlineStr"/>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>How much profit have I actually taken?  Answers: realised gain all-time, realised gain this year, how many sales were counted, and how many could NOT be priced.</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Walk buys and sells in date order. Each sale consumes the OLDEST buy lots first, and the gain is proceeds minus the cost of the shares it consumed.
+Lots are kept separately per account AND per ticker, so a Schwab holding never covers a Robinhood sale of the same share.
+A SALE WITH NO RECORDED BUY CONTRIBUTES NOTHING and is counted separately, so the screen can say how much it could not see. A cost is never invented — inventing one would report the entire sale as profit.</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>the ledger → txns
+optionally one ticker → opts.ticker
+optionally one account → opts.accountId
+today → opts.now</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>The transaction ledger — buys, opening positions and sells, each needing a ticker, a share count and a price. Built from the broker feed (SnapTrade activities[]) or logged by hand.
+The year boundary comes from the device clock.</t>
+        </is>
+      </c>
       <c r="G72" s="3" t="inlineStr"/>
-      <c r="H72" s="3" t="inlineStr"/>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-portfolio.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>HoldingDetail</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
@@ -6067,7 +6313,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>HoldingDetail</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
@@ -6196,21 +6442,47 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr"/>
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>CONCENTRATION</t>
+        </is>
+      </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
           <t>topHoldingConcentration</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr"/>
-      <c r="D74" s="3" t="inlineStr"/>
-      <c r="E74" s="3" t="inlineStr"/>
-      <c r="F74" s="3" t="inlineStr"/>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Is too much of my money in one holding?  Answers: the ticker and its percentage — or nothing, when there is no fact worth reporting.</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Take the LARGEST holding by value and express it as a percentage of everything invested. Report it only at 25% or more, and only when there are at least two holdings — one holding is not a concentration, it is a portfolio of one.
+It is a FACT and never advice: the number and the ticker, with no recommendation attached.</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>each holding → rows[].marketValue
+its ticker → rows[].position.ticker</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>The per-holding rows from PERFORMANCE_TABLE — each already carrying its value, its return and its benchmark. See that row for where each of those comes from.</t>
+        </is>
+      </c>
       <c r="G74" s="3" t="inlineStr"/>
-      <c r="H74" s="3" t="inlineStr"/>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-portfolio.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I74" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr">
@@ -6220,7 +6492,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
@@ -6348,21 +6620,54 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr"/>
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>PERSONAL_FLOWS</t>
+        </is>
+      </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
           <t>userFlows</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr"/>
-      <c r="D76" s="3" t="inlineStr"/>
-      <c r="E76" s="3" t="inlineStr"/>
-      <c r="F76" s="3" t="inlineStr"/>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Which movements count as MY money going in or coming out?
+Answers: a dated list, each amount negative for money you put in and positive for money you took out.</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Only money CROSSING THE EDGE of the measured accounts counts:
+• an opening balance, an opening position, or a DEPOSIT → money in (negative)
+• a WITHDRAWAL → money out (positive)
+• a TRANSFER between two measured accounts → cancels, it never left
+• a TRANSFER to or from somewhere outside → a real flow
+• a BUY, SELL, DIVIDEND, INTEREST or FEE → NOT a flow. Cash became shares or shares became cash; nothing entered or left.
+Amounts under half a cent are dropped, and the list is sorted oldest first.
+The sign convention is the investor one — money in is NEGATIVE — because that is what the rate solver needs. Inverting it would flip every return.</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>the ledger → transactions
+which accounts are measured → accountIds</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>The transaction ledger — every activity, built from the broker feed by INGEST_ACTIVITY_TYPE (SnapTrade activities[]: type, date, amount), plus anything logged by hand. This is the same ledger the change walk uses, so an error here shows up in BOTH the personal return and the net-worth change.</t>
+        </is>
+      </c>
       <c r="G76" s="3" t="inlineStr"/>
-      <c r="H76" s="3" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-portfolio.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I76" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr">
@@ -6372,7 +6677,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
@@ -8825,21 +9130,51 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="inlineStr"/>
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>LOOK_BACK</t>
+        </is>
+      </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
           <t>lookBack</t>
         </is>
       </c>
-      <c r="C110" s="3" t="inlineStr"/>
-      <c r="D110" s="3" t="inlineStr"/>
-      <c r="E110" s="3" t="inlineStr"/>
-      <c r="F110" s="3" t="inlineStr"/>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>What if I had moved this money?  Answers: what it became where it sat, what it would have become moved, and the difference — or nothing when either price history is too short.</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Grow the amount by each holding's real price movement over the window, and subtract one from the other. Every figure comes from ACTUAL PAST PRICES.
+A move that would have lost money returns a real negative — it never quietly reports zero.
+Nothing to compare, or a history too short on either side → nothing at all.
+It is explicitly BACKWARD-looking: a fact about what did happen, never a suggestion about what to do next.</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>the amount → amount
+where it sat → fromSeries
+where it might have gone → toSeries
+how far back → months</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>The market-data cache (Tiingo / Yahoo), keyed by ticker, with the timestamp of the last successful fetch. Not from the broker.</t>
+        </is>
+      </c>
       <c r="G110" s="3" t="inlineStr"/>
-      <c r="H110" s="3" t="inlineStr"/>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-portfolio.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I110" s="3" t="inlineStr">
         <is>
-          <t>LookBack</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J110" s="3" t="inlineStr">
@@ -8849,7 +9184,7 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>LookBack</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L110" s="3" t="inlineStr">
@@ -8980,21 +9315,58 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="inlineStr"/>
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>PERSONAL_RETURN</t>
+        </is>
+      </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
           <t>moneyWeightedReturn</t>
         </is>
       </c>
-      <c r="C112" s="3" t="inlineStr"/>
-      <c r="D112" s="3" t="inlineStr"/>
-      <c r="E112" s="3" t="inlineStr"/>
-      <c r="F112" s="3" t="inlineStr"/>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>What return have I actually earned, counting when I added money?
+Answers: a yearly rate — OR one of three plain refusals: no usable history · too short a period · no sensible answer exists.</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>Find the single yearly rate that makes all your dated flows, grown at that rate, equal what the accounts are worth today. Solved by repeated halving between −95% and +1000% a year, up to 100 passes — no guessing and the same answer every time.
+IT REFUSES IN FOUR WAYS, and the refusals are the feature:
+1. the history does not start in the ledger → "no usable history"
+2. nothing was ever put in → "no usable history"
+3. under 30 days → "too short". Annualising three days of movement produces a huge number that means nothing.
+4. no rate in that range fits → "no sensible answer".
+WHY IT DIFFERS FROM A PRICE RETURN: this one counts TIMING. The same money added later worked for less time, so the same ending value implies a higher yearly rate. That is the honest answer to "how did I do", and no price-based figure can see it.
+IT DEPENDS ENTIRELY ON THE LEDGER BEING RIGHT. Phantom deposits do not make it refuse — they make it answer confidently and wrongly, which is what happened on the Vanguard account.</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>the ledger → transactions
+the accounts → accounts
+which are measured → accountIds
+today's value → currentValue
+today → now</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="inlineStr">
+        <is>
+          <t>The transaction ledger — every activity, built from the broker feed by INGEST_ACTIVITY_TYPE (SnapTrade activities[]: type, date, amount), plus anything logged by hand. This is the same ledger the change walk uses, so an error here shows up in BOTH the personal return and the net-worth change.
+currentValue: the accounts' value today, from the balances.</t>
+        </is>
+      </c>
       <c r="G112" s="3" t="inlineStr"/>
-      <c r="H112" s="3" t="inlineStr"/>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-portfolio.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I112" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J112" s="3" t="inlineStr">
@@ -9004,7 +9376,7 @@
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L112" s="3" t="inlineStr">
@@ -9140,36 +9512,63 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="inlineStr"/>
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>RETURN_SINCE_A_DATE</t>
+        </is>
+      </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
           <t>periodReturnSince</t>
         </is>
       </c>
-      <c r="C114" s="3" t="inlineStr"/>
-      <c r="D114" s="3" t="inlineStr"/>
-      <c r="E114" s="3" t="inlineStr"/>
-      <c r="F114" s="3" t="inlineStr"/>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>What did this do between a given date and today?  Answers: a percentage, or nothing when the price history does not reach back to that date.</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>Latest price ÷ the closing price on or before that date − 1. Any date is allowed, unlike the named-period version.
+THIS IS THE ANSWER TO THE STATEMENT PROBLEM AND IT IS ALREADY WRITTEN. It takes an arbitrary window, so it could line the app up against a brokerage statement covering any dates. It is exported and CALLED FROM NOWHERE except inside the performance table.</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>the price series → series
+the start date → sinceISO
+today → now</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>The market-data cache (Tiingo / Yahoo), keyed by ticker, with the time of the last successful fetch. Not from the broker.</t>
+        </is>
+      </c>
       <c r="G114" s="3" t="inlineStr"/>
-      <c r="H114" s="3" t="inlineStr"/>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-portfolio.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>UNRESOLVED</t>
         </is>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>buildPerformance</t>
+          <t>A person should be able to ask for the exact window their statement covers, so the app's number can be laid beside the institution's and checked.</t>
         </is>
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr">
         <is>
-          <t>buildPerformance</t>
+          <t>Not a code fix — a product decision. The engine exists and works. Someone has to decide where the date-range control lives on the Performance screen. Paired with the PERIOD_RETURN row, which names the same gap from the other side.</t>
         </is>
       </c>
       <c r="M114" s="5" t="inlineStr"/>
@@ -9206,36 +9605,66 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="inlineStr"/>
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>PORTFOLIO_TREND_LINE</t>
+        </is>
+      </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
           <t>portfolioTrend</t>
         </is>
       </c>
-      <c r="C115" s="3" t="inlineStr"/>
-      <c r="D115" s="3" t="inlineStr"/>
-      <c r="E115" s="3" t="inlineStr"/>
-      <c r="F115" s="3" t="inlineStr"/>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>How has my portfolio moved over the period, against its benchmark?  Answers: 13 dated points, each with your value and the benchmark rebased to start at the same place.</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>Split the window into 12 equal steps. At each date, add up (shares × the closing price on or before that date) for every holding. The benchmark line is scaled so it STARTS at your starting value, which is what makes the two shapes comparable rather than two lines at different heights.
+A holding with no price on a date contributes zero rather than breaking the line.
+THE DEFECT: every past date is valued using TODAY'S SHARE COUNT. Shares bought last week are drawn as though they were held all year, so the line rises from a year ago on money that was not there. A holding bought yesterday and one held all year produce an identical line.</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>the holdings → positions
+prices → priceOf(ticker)
+the chosen chip → period
+the benchmark → benchTickerSym
+today → now</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>The market-data cache (Tiingo / Yahoo), keyed by ticker, with the time of the last successful fetch. Not from the broker.</t>
+        </is>
+      </c>
       <c r="G115" s="3" t="inlineStr"/>
-      <c r="H115" s="3" t="inlineStr"/>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-portfolio.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I115" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>DEFECT</t>
         </is>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A history line must show what you ACTUALLY held on each date — shares bought last month must not appear in last year's value. A chart of a position you never had is worse than no chart.</t>
         </is>
       </c>
       <c r="K115" s="3" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="L115" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Two options, and the cheap one is worth doing first. CHEAP: use each lot's purchase date, which is already on the record, and count only lots owned on or before each point. Roughly an hour, and it fixes the common case. THOROUGH: rebuild share counts from the ledger, which also handles sales and transfers — but that needs the ledger to be trustworthy, so it should wait until the phantom contributions are settled.</t>
         </is>
       </c>
       <c r="M115" s="5" t="inlineStr"/>
@@ -12229,21 +12658,52 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="3" t="inlineStr"/>
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>PERFORMANCE_TABLE</t>
+        </is>
+      </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
           <t>buildPerformance</t>
         </is>
       </c>
-      <c r="C154" s="3" t="inlineStr"/>
-      <c r="D154" s="3" t="inlineStr"/>
-      <c r="E154" s="3" t="inlineStr"/>
-      <c r="F154" s="3" t="inlineStr"/>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>What is the full picture for every holding?  Answers: one row each — price, value, cost, gain, return since purchase, return for the chosen period, its benchmark, how it compares, and whether the period had to be shortened.</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>For each holding: fetch its price series; work out value, cost and gain from its lots; then choose HOW to measure its period return —
+• bought BEFORE the period started → the ordinary period return from the price series
+• bought DURING the period → return since purchase instead, and the row is marked as shortened, because measuring a full year on something owned for a month would be nonsense
+The benchmark is measured over THE SAME window, shortened the same way, so the comparison is like for like. Beat-by is simply one minus the other, and is left blank when either side is missing.</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>the holdings → positions
+prices → priceOf(ticker)
+the chosen chip → period
+today → now</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>The market-data cache (Tiingo / Yahoo), keyed by ticker, with the time of the last successful fetch. Not from the broker.
+The holdings and their lots come from the broker feed, an uploaded file, or the Add holding form — see HOLDING_SHARES and HOLDING_COST_BASIS.</t>
+        </is>
+      </c>
       <c r="G154" s="3" t="inlineStr"/>
-      <c r="H154" s="3" t="inlineStr"/>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>probes/performance-lot-math.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>HoldingDetail, Performance</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J154" s="3" t="inlineStr">
@@ -12253,7 +12713,7 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>HoldingDetail, Performance</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L154" s="3" t="inlineStr">

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -4203,21 +4203,51 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr"/>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>SNAPSHOT_READ_ONE</t>
+        </is>
+      </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
           <t>normalizeSnapshot</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr"/>
-      <c r="D47" s="3" t="inlineStr"/>
-      <c r="E47" s="3" t="inlineStr"/>
-      <c r="F47" s="3" t="inlineStr"/>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Is this stored snapshot usable, and what does it say?  Answers: a clean snapshot, or nothing at all when it cannot be trusted.</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Take the stored entry and make it safe to chart:
+• no real month, or no usable net worth → DROP it. A bad point is never charted.
+• net worth missing but assets and debts present → assets − debts
+• only a net worth present → keep it, assume assets equal it and DEBT IS ZERO. That last part is a guess, not a record, and it makes an old snapshot look debt-free.
+• every other field missing → zero
+Old snapshots written before the format was versioned are read best-effort rather than thrown away.</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>the month key → ym
+the stored entry → raw</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Snapshots the app writes about ITSELF. NOBODY SENDS US HISTORY — no institution supplies what an account was worth last month — so this is the only record of yesterday that exists. Two kinds: a MONTHLY snapshot (the deep record: assets, debts, income, spending, per-account rows) and a DAILY point (one number, net worth, written once per day the app is opened).</t>
+        </is>
+      </c>
       <c r="G47" s="3" t="inlineStr"/>
-      <c r="H47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>probes/history-snapshots.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -4227,7 +4257,7 @@
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
@@ -8491,21 +8521,45 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="inlineStr"/>
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>SNAPSHOT_READ_ALL</t>
+        </is>
+      </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
           <t>readHistory</t>
         </is>
       </c>
-      <c r="C101" s="3" t="inlineStr"/>
-      <c r="D101" s="3" t="inlineStr"/>
-      <c r="E101" s="3" t="inlineStr"/>
-      <c r="F101" s="3" t="inlineStr"/>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>What history do we hold?  Answer: every usable monthly snapshot, oldest first.</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>Run every stored entry through SNAPSHOT_READ_ONE, drop whatever comes back unusable, and sort by month. This is the ONE reader every history surface uses, so no screen can invent its own idea of what the past looked like.</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>the stored snapshots → raw</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="inlineStr">
+        <is>
+          <t>Snapshots the app writes about ITSELF. NOBODY SENDS US HISTORY — no institution supplies what an account was worth last month — so this is the only record of yesterday that exists. Two kinds: a MONTHLY snapshot (the deep record: assets, debts, income, spending, per-account rows) and a DAILY point (one number, net worth, written once per day the app is opened).</t>
+        </is>
+      </c>
       <c r="G101" s="3" t="inlineStr"/>
-      <c r="H101" s="3" t="inlineStr"/>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>probes/history-snapshots.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I101" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J101" s="3" t="inlineStr">
@@ -8515,7 +8569,7 @@
       </c>
       <c r="K101" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L101" s="3" t="inlineStr">
@@ -10788,36 +10842,64 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="inlineStr"/>
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>TREND_SERIES</t>
+        </is>
+      </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
           <t>trendPoints</t>
         </is>
       </c>
-      <c r="C130" s="3" t="inlineStr"/>
-      <c r="D130" s="3" t="inlineStr"/>
-      <c r="E130" s="3" t="inlineStr"/>
-      <c r="F130" s="3" t="inlineStr"/>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>What points does the net-worth graph draw?  Answer: a dated list of net-worth values, oldest first — or an empty list when there is no history.</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>Monthly snapshots and daily points merged into one series and sorted by their date text. A month ("2026-07") sorts before its own days ("2026-07-04"), which is what makes plain text sorting safe.
+A daily value that is not a real date or not a real number is ignored rather than drawn as zero.
+No history → an empty series, NOT a flat line at zero.
+THE LIMIT THAT MATTERS, and it is the mechanism behind the founder's F15: a daily point is ONE NUMBER — total net worth. There is no per-account daily history anywhere in the app, so "what was my Vanguard account worth in April" has no answer to read, and a beginning value gets BACK-SOLVED from today minus whatever the ledger claims happened. It also only ever starts the day the app was first opened: an account connected today has no yesterday, whatever the market did before that.</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>monthly snapshots → monthly
+daily points → daily</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="inlineStr">
+        <is>
+          <t>Snapshots the app writes about ITSELF. NOBODY SENDS US HISTORY — no institution supplies what an account was worth last month — so this is the only record of yesterday that exists. Two kinds: a MONTHLY snapshot (the deep record: assets, debts, income, spending, per-account rows) and a DAILY point (one number, net worth, written once per day the app is opened).</t>
+        </is>
+      </c>
       <c r="G130" s="3" t="inlineStr"/>
-      <c r="H130" s="3" t="inlineStr"/>
+      <c r="H130" s="3" t="inlineStr">
+        <is>
+          <t>probes/history-snapshots.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I130" s="3" t="inlineStr">
         <is>
-          <t>NetWorth</t>
+          <t>DEFECT</t>
         </is>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A change figure must be measured from a date the PERSON chose — the start of the year, or the window their statement covers — not from whenever the app happened to be installed. And where no history exists for the requested window, the screen must say so rather than measuring from the first day it has.</t>
         </is>
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>NetWorth</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="L130" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Two parts, and they are separable. FIRST, cheap and worth doing now: label the change line with the date it is actually measured from, so a figure measured from install day says so. That is honest immediately and costs almost nothing. SECOND, the real fix: store per-account daily values, not one total. That is what makes a beginning value readable instead of back-solved, and it is the precondition for ever matching a brokerage statement. Needs a decision about storage size first.</t>
         </is>
       </c>
       <c r="M130" s="5" t="inlineStr"/>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -123,7 +123,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -145,11 +145,55 @@
         <color rgb="00DDDDDD"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -200,6 +244,8 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1119,21 +1165,47 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr"/>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>WRAPPER_CONFIRMED</t>
+        </is>
+      </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>confirmWrapper</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>The person told us what this account really is — how is that recorded?  Answer: the account, with its type and wrapper set and marked as confirmed.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Set the type and wrapper on that one account and mark it confirmed. FUTURE SYNCS NEVER OVERRIDE A CONFIRMED WRAPPER, so the broker's label can never quietly undo the person's own answer on the next refresh.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>the accounts → accounts
+which one → assetId
+what it really is → kind, taxBucket</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>The Held-in chooser in the connect flow — the question the app asks whenever WRAPPER_GUESS comes back not confident.</t>
+        </is>
+      </c>
       <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>probes/sync-identity.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1143,7 +1215,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -1185,36 +1257,63 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr"/>
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>ACCOUNT_IDENTITY</t>
+        </is>
+      </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
           <t>stAssetId</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>What do we call this connected account internally?  Answer: one id — the broker's own account id with 'st-' in front of it.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>'st-' + the broker's account id. That is the whole rule.
+IT MATTERS FAR MORE THAN IT LOOKS. Our identity for an account IS the broker's identity for it, and the key that stops an activity being recorded twice BEGINS with our account id. So if the broker's id ever changes — a reconnect, a re-linked login, a migrated or renumbered account — every key changes with it, nothing matches what we have already seen, and the ENTIRE history re-imports as brand-new money arriving.
+This is the last standing explanation for $1,462,462 of contributions on an account whose statement says nothing moved. Proved as a mechanism by probe: the same 40 events, deduplicated correctly under one id, all come back as new under another.</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>the broker's account id → snapTradeAccountId</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>The SnapTrade payload for a connected account: accounts[].id (the broker's own account id), accounts[].type (the broker's raw label for the account), balances, positions[] and activities[].
+The id is SnapTrade's, not ours, and nothing in our code controls whether it stays the same.</t>
+        </is>
+      </c>
       <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>probes/sync-identity.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DEFECT</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>ingestSync</t>
+          <t>An account's identity must survive a reconnection. Our record of an account should be tied to something durable — the institution plus the account number mask, say — rather than to a broker id we do not control, so that re-linking a login updates an account instead of duplicating its entire history.</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>ingestSync</t>
+          <t>FIRST, PROVE IT ON THE REAL DATA before changing anything: check whether the Vanguard account's stored id changed. If it did, this is the cause of the $1.4m and the fix is worth doing properly. THEN the fix has two parts — key the dedupe on the broker's own activity id where one is sent, rather than prefixing ours to it; and match a reconnected account to the existing one on institution plus mask before creating a new record. Neither is large. Both need the real ledger first, because a fix aimed at the wrong cause is worse than none.</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr"/>
@@ -1581,21 +1680,57 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>WRAPPER_GUESS</t>
+        </is>
+      </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
           <t>mapAccountType</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr"/>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr"/>
-      <c r="F12" s="3" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>What kind of account is this, and how is it taxed?
+Answers: an account type and a wrapper — Roth IRA · 401(k) · Traditional IRA · HSA · Checking · Brokerage · 529 — TOGETHER WITH whether we are confident. Not confident means the app asks rather than assuming.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>SnapTrade sends no standard wrapper — only the broker's own words — so the words are read, first match winning:
+• contains ROTH → Roth IRA, or a Roth 401(k) if it also says 401
+• 401K / 401(K) / 403B / 457 → 401(k), pre-tax
+• ROLLOVER / TRADITIONAL / SEP / SIMPLE IRA → Traditional IRA, pre-tax
+• any other IRA → Traditional. A GUESS — the commoner case — and it is marked confident, though a Roth labelled plainly "IRA" would be taxed wrongly
+• HSA → HSA · CHECKING → Checking
+• SAVINGS → Brokerage, and NOT confident. This broker is brokerage-only, so an account labelled savings is a brokerage wearing the wrong label — founder-verified against real E*TRADE data, 2026-08-04. Labels lose to reality.
+• 529 / EDUCATION → 529
+• INDIVIDUAL / JOINT / BROKERAGE / MARGIN / CASH / TAXABLE / TRUST → Brokerage, taxable
+• anything else → Brokerage for display, NOT confident, and the connect flow asks.
+The confidence flag is the honest part: a wrong wrapper is wrong tax maths on every projection, so an unrecognised type is never guessed silently.</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>the broker's label → rawType
+its category → category</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>The SnapTrade payload for a connected account: accounts[].id (the broker's own account id), accounts[].type (the broker's raw label for the account), balances, positions[] and activities[].</t>
+        </is>
+      </c>
       <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>probes/sync-identity.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1605,7 +1740,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
@@ -1913,21 +2048,47 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr"/>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>HISTORY_DEPTH</t>
+        </is>
+      </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
           <t>mergeHistoryFrom</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr"/>
-      <c r="F16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>How far back does this source's activity history go?  Answer: the earliest date it has ever sent us, or nothing when it has sent none.</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Take the earliest valid date in this sync and keep whichever is earlier — it or what we already had. Depth only ever grows; a shallower sync never shortens it. Unreadable dates are ignored, and a sync with no activity leaves the answer untouched.
+It exists because brokers back-fill DIFFERENT depths — one sends a year, the next ninety days. Without knowing the depth, a "past year" income figure silently understates, so year-scale figures label themselves with this date.</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>what we knew → existing
+the dates in this sync → activityDates</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>The SnapTrade payload for a connected account: accounts[].id (the broker's own account id), accounts[].type (the broker's raw label for the account), balances, positions[] and activities[].</t>
+        </is>
+      </c>
       <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>probes/sync-identity.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1937,7 +2098,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
@@ -13784,6 +13945,11 @@
           <t>TYPED BY THE PERSON — nothing external supplies these, so they are only as right as the question that asked for them</t>
         </is>
       </c>
+      <c r="B3" s="18" t="n"/>
+      <c r="C3" s="18" t="n"/>
+      <c r="D3" s="18" t="n"/>
+      <c r="E3" s="18" t="n"/>
+      <c r="F3" s="19" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -14127,6 +14293,11 @@
           <t>SENT BY A CONNECTED BROKER (SnapTrade) — the exact payload paths, as the live E*TRADE and Vanguard connections deliver them</t>
         </is>
       </c>
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="19" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -14498,6 +14669,11 @@
           <t>READ FROM A FILE YOU UPLOAD — no two institutions name a column the same way, so every column is found by PATTERN and the importer reports which header it used</t>
         </is>
       </c>
+      <c r="B30" s="18" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="18" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="19" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
@@ -14657,6 +14833,11 @@
           <t>FETCHED FROM AN OUTSIDE FEED — not from your institution, and each carries its own freshness</t>
         </is>
       </c>
+      <c r="B37" s="18" t="n"/>
+      <c r="C37" s="18" t="n"/>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="19" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
@@ -14748,6 +14929,11 @@
           <t>NUMBERS WE CHOSE — no institution sent these. They are assumptions, every projection stands on them, and they belong on this tab precisely because they look like facts</t>
         </is>
       </c>
+      <c r="B41" s="18" t="n"/>
+      <c r="C41" s="18" t="n"/>
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="19" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
@@ -15671,7 +15857,7 @@
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>This is the last standing explanation for the $1.4m of contributions Vanguard says never happened. Everything else has been ruled out by running the code: the activity mapping is correct, option trades stay internal, the dedupe set persists across syncs, and nothing in the connect flow writes opening rows.</t>
+          <t>NOW PROVED AS A MECHANISM, not just suspected (probes/sync-identity.probe.test.ts). Our account id IS the broker's account id with 'st-' in front, and the key that stops an activity being recorded twice BEGINS with our account id. The probe runs the same 40 events twice: deduplicated correctly under one id, and ALL 40 come back as new under another. So a changed broker id re-imports the entire history as new money arriving. Everything else has been ruled out by running the code: the activity mapping is correct, option trades stay internal, the dedupe set persists across syncs, and nothing in the connect flow writes opening rows. What is still needed is your ledger, to confirm the id actually changed — a fix aimed at the wrong cause is worse than none.</t>
         </is>
       </c>
       <c r="D3" s="13" t="n"/>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -123,7 +123,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -145,55 +145,11 @@
         <color rgb="00DDDDDD"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00DDDDDD"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00DDDDDD"/>
-      </right>
-      <top style="thin">
-        <color rgb="00DDDDDD"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00DDDDDD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00DDDDDD"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00DDDDDD"/>
-      </right>
-      <top style="thin">
-        <color rgb="00DDDDDD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00DDDDDD"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -244,8 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2630,21 +2584,45 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr"/>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>ACCOUNT_NAMES</t>
+        </is>
+      </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
           <t>accountDisplayNames</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr"/>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>What do we call each account on screen when two look alike?  Answer: a name per account, with duplicates numbered — "Vanguard Brokerage · 1", "Vanguard Brokerage · 2".</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Build each account's display name, count how many share it, and number only those that collide. Numbering is assigned in account-id order, so the same account keeps the same number between screens and between app launches rather than shuffling.</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>the accounts → accounts (id, name, institution, mask)</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>The name and institution come from the broker at connect time, from an uploaded file, or from the Add account form. The mask ("••4821") is how banks disambiguate accounts and arrives with the feed.</t>
+        </is>
+      </c>
       <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>probes/account-breakdown.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>AccountDetail, NetWorth, Performance</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -2654,7 +2632,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>AccountDetail, NetWorth, Performance</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -2828,36 +2806,63 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr"/>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>SLICE_WORDING</t>
+        </is>
+      </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
           <t>classPortionLabel</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>What do we say about this slice of an account?  Answer: a short phrase — "cash in this account", "2 CDs", and so on.</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Gather the holdings in that class and describe them. Cash is said plainly as the sweep balance, because under the founder's rule cash means cash only.
+THE DEFECT: it decides which holdings are in a class using the BROKER'S TAG ALONE, while ACCOUNT_SPLIT decides using the NAME first. The two therefore disagree on exactly the holdings the name rule was written for. A money-market fund the broker tagged as cash has its VALUE counted under Stocks / Funds while the WORDS under that slice never mention it.</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>the account → a
+which class → cls</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>The connected account's payload: balance.total.amount (the broker's authoritative total), balances.cash, and positions[] each with symbol.raw_symbol, symbol.description, units and price. Option positions arrive on their own feed.
+The holding names are the same field ACCOUNT_SPLIT reads — which is what makes the disagreement avoidable.</t>
+        </is>
+      </c>
       <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>probes/account-breakdown.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>NetWorth</t>
+          <t>DEFECT</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>The words under a slice must describe the money actually in it. One classification rule, used by both the amounts and the wording.</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>NetWorth</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Have this call the same name-first rule ACCOUNT_SPLIT uses, instead of reading the broker tag on its own. Small and self-contained — and it is the third place today where the same idea was implemented twice and drifted, after the class LABEL in eight places and the class VOCABULARY in four. Worth fixing as one job with those.</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr"/>
@@ -3424,21 +3429,48 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr"/>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>HAND_VALUE_AGE</t>
+        </is>
+      </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
           <t>valueFreshness</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="3" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr"/>
-      <c r="F35" s="3" t="inlineStr"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>How old is this hand-entered value?  Answers: the date it was set, how many months ago that was, and whether it counts as stale — or nothing at all when the question does not apply.</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Months between the date the value was set and today. Six months or more → stale.
+A LIVE-PRICED account returns nothing: its value comes from today's prices, so staleness is not a question that applies to it. A value with no date recorded also returns nothing rather than being assumed fresh.</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>the account → a
+when the value was set → value_as_of
+today → now</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>value_as_of is stamped when someone types or confirms a balance on the account screen. Nothing external supplies it — it is a record of when a person last vouched for the number.</t>
+        </is>
+      </c>
       <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>probes/account-breakdown.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>AccountDetail, Performance</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -3448,7 +3480,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>AccountDetail, Performance</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
@@ -10114,21 +10146,55 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="inlineStr"/>
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>ACCOUNT_SPLIT</t>
+        </is>
+      </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
           <t>accountClassBreakdown</t>
         </is>
       </c>
-      <c r="C119" s="3" t="inlineStr"/>
-      <c r="D119" s="3" t="inlineStr"/>
-      <c r="E119" s="3" t="inlineStr"/>
-      <c r="F119" s="3" t="inlineStr"/>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>How does ONE connected account split across the classes it actually holds?
+Answer: a dollar figure for each of Cash · Bonds &amp; CDs · Stocks / Funds · Alternatives — adding up EXACTLY to the total the broker states. A typed or imported account returns nothing and stays whole.</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>Start with the uninvested cash. Then place every holding by reading its NAME first — money-market funds to Stocks / Funds, CDs and T-bills to Bonds &amp; CDs — and only falling back to the broker's own tag when the name says nothing. Options go to Alternatives.
+Then compare the pieces with the broker's stated total, and place whatever is left over:
+• a SMALL POSITIVE leftover → CASH. It is money the broker's total includes but its holdings do not account for: settlement cash, a dividend just received, a pending trade.
+• a SMALL NEGATIVE leftover → the largest class. The priced holdings exceed the stated total, which is a pricing artifact rather than money; writing it into cash would show a negative cash balance, which reads worse than a rounding nudge.
+• a LARGE leftover → Unclassified, honestly.
+THE LEFTOVER RULE IS A FOUNDER FINDING ("why is cash added to CD and not cash?"). It used to go to the LARGEST class, so on a CD-heavy account uninvested money was counted as MORE CDs — overstating bonds and understating cash, both silently.</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>the account → a
+its total → balance
+uninvested → cash_balance
+holdings → positions[]
+options → option_holdings[]</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="inlineStr">
+        <is>
+          <t>The connected account's payload: balance.total.amount (the broker's authoritative total), balances.cash, and positions[] each with symbol.raw_symbol, symbol.description, units and price. Option positions arrive on their own feed.</t>
+        </is>
+      </c>
       <c r="G119" s="3" t="inlineStr"/>
-      <c r="H119" s="3" t="inlineStr"/>
+      <c r="H119" s="3" t="inlineStr">
+        <is>
+          <t>probes/account-breakdown.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I119" s="3" t="inlineStr">
         <is>
-          <t>AccountDetail, NetWorth</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J119" s="3" t="inlineStr">
@@ -10138,7 +10204,7 @@
       </c>
       <c r="K119" s="3" t="inlineStr">
         <is>
-          <t>AccountDetail, NetWorth</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L119" s="3" t="inlineStr">
@@ -13945,11 +14011,6 @@
           <t>TYPED BY THE PERSON — nothing external supplies these, so they are only as right as the question that asked for them</t>
         </is>
       </c>
-      <c r="B3" s="18" t="n"/>
-      <c r="C3" s="18" t="n"/>
-      <c r="D3" s="18" t="n"/>
-      <c r="E3" s="18" t="n"/>
-      <c r="F3" s="19" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -14293,11 +14354,6 @@
           <t>SENT BY A CONNECTED BROKER (SnapTrade) — the exact payload paths, as the live E*TRADE and Vanguard connections deliver them</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n"/>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="18" t="n"/>
-      <c r="E16" s="18" t="n"/>
-      <c r="F16" s="19" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -14669,11 +14725,6 @@
           <t>READ FROM A FILE YOU UPLOAD — no two institutions name a column the same way, so every column is found by PATTERN and the importer reports which header it used</t>
         </is>
       </c>
-      <c r="B30" s="18" t="n"/>
-      <c r="C30" s="18" t="n"/>
-      <c r="D30" s="18" t="n"/>
-      <c r="E30" s="18" t="n"/>
-      <c r="F30" s="19" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
@@ -14833,11 +14884,6 @@
           <t>FETCHED FROM AN OUTSIDE FEED — not from your institution, and each carries its own freshness</t>
         </is>
       </c>
-      <c r="B37" s="18" t="n"/>
-      <c r="C37" s="18" t="n"/>
-      <c r="D37" s="18" t="n"/>
-      <c r="E37" s="18" t="n"/>
-      <c r="F37" s="19" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
@@ -14929,11 +14975,6 @@
           <t>NUMBERS WE CHOSE — no institution sent these. They are assumptions, every projection stands on them, and they belong on this tab precisely because they look like facts</t>
         </is>
       </c>
-      <c r="B41" s="18" t="n"/>
-      <c r="C41" s="18" t="n"/>
-      <c r="D41" s="18" t="n"/>
-      <c r="E41" s="18" t="n"/>
-      <c r="F41" s="19" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="17" t="inlineStr">

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -4772,21 +4772,45 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr"/>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>OTHER_INCOME</t>
+        </is>
+      </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
           <t>extraIncome</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr"/>
-      <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr"/>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>What else comes in?  Answer: four figures — taxable monthly, non-taxable monthly, one-off taxable, and one-off non-taxable.</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Total the other income rows, keeping taxable and non-taxable apart, and recurring apart from one-off. The split matters: non-taxable income is worth more per dollar, and a one-off must not be spread across every future year.</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>the other-income rows → the extra income question</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding answers — the questions asked when the app is first set up, and editable afterwards on the Income screen. NOTHING external supplies any of this: no institution tells us what a person earns, so every figure here is only as right as the question that asked for it.</t>
+        </is>
+      </c>
       <c r="G51" s="3" t="inlineStr"/>
-      <c r="H51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -4796,7 +4820,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
@@ -4838,21 +4862,46 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr"/>
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>FILING_STATUS</t>
+        </is>
+      </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
           <t>filingStatusOf</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr"/>
-      <c r="D52" s="3" t="inlineStr"/>
-      <c r="E52" s="3" t="inlineStr"/>
-      <c r="F52" s="3" t="inlineStr"/>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>How does this person file?  Answers: single · married · head of household.</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Use what they chose; anything unrecognised or unanswered falls back to SINGLE.
+Single is the cautious default — it assumes the higher tax bill rather than the lower one. Note that GROSS_FROM_TAKE_HOME never receives this value, though it exists.</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>their answer → filingStatus</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding answers — the questions asked when the app is first set up, and editable afterwards on the Income screen. NOTHING external supplies any of this: no institution tells us what a person earns, so every figure here is only as right as the question that asked for it.</t>
+        </is>
+      </c>
       <c r="G52" s="3" t="inlineStr"/>
-      <c r="H52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -4862,7 +4911,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L52" s="3" t="inlineStr">
@@ -4904,21 +4953,45 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr"/>
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>RENTALS</t>
+        </is>
+      </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
           <t>rentalList</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr"/>
-      <c r="D53" s="3" t="inlineStr"/>
-      <c r="E53" s="3" t="inlineStr"/>
-      <c r="F53" s="3" t="inlineStr"/>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>What rental properties are there, and what does each bring in?  Answer: a list, each with monthly income and monthly costs.</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Read the rental rows as entered. Nothing is inferred; a property with no figures contributes nothing.</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>the rental rows → the rentals question</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding answers — the questions asked when the app is first set up, and editable afterwards on the Income screen. NOTHING external supplies any of this: no institution tells us what a person earns, so every figure here is only as right as the question that asked for it.</t>
+        </is>
+      </c>
       <c r="G53" s="3" t="inlineStr"/>
-      <c r="H53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -4928,7 +5001,7 @@
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
@@ -4970,21 +5043,45 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr"/>
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>VESTING_YEAR</t>
+        </is>
+      </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
           <t>rowVestYear</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr"/>
-      <c r="D54" s="3" t="inlineStr"/>
-      <c r="E54" s="3" t="inlineStr"/>
-      <c r="F54" s="3" t="inlineStr"/>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Which year does this line vest in?  Answer: a calendar year.</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>The first four-digit number in the date. No date → this year.</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>the date → row.date</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding answers — the questions asked when the app is first set up, and editable afterwards on the Income screen. NOTHING external supplies any of this: no institution tells us what a person earns, so every figure here is only as right as the question that asked for it.</t>
+        </is>
+      </c>
       <c r="G54" s="3" t="inlineStr"/>
-      <c r="H54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -4994,7 +5091,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
@@ -5036,21 +5133,47 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr"/>
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>TAXABLE_INCOME_SINGLE</t>
+        </is>
+      </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
           <t>taxableIncome</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr"/>
-      <c r="D55" s="3" t="inlineStr"/>
-      <c r="E55" s="3" t="inlineStr"/>
-      <c r="F55" s="3" t="inlineStr"/>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>What income is actually taxed?  Answer: a dollar figure, never below zero.</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>gross − the standard deduction ($16,100 for 2026). Below the deduction, taxable income is zero rather than negative.
+SINGLE FILER ONLY — the version that takes a filing status is a separate row.</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>gross income → gross</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>PUBLISHED IRS TABLES, held in our code: the 2026 single-filer brackets and standard deduction from IRS Rev. Proc. 2025-32. Married thresholds are exactly double the single ones through the 35% band; head-of-household uses the IRS's wider 10% and 12% bands. THESE MUST BE UPDATED EVERY YEAR — the table stamps its own year so a stale one is visible rather than silent.
+The gross comes from TOTAL_INCOME.</t>
+        </is>
+      </c>
       <c r="G55" s="3" t="inlineStr"/>
-      <c r="H55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -5060,7 +5183,7 @@
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
@@ -5102,21 +5225,47 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr"/>
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>TAXABLE_INCOME</t>
+        </is>
+      </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
           <t>taxableIncomeFor</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr"/>
-      <c r="D56" s="3" t="inlineStr"/>
-      <c r="E56" s="3" t="inlineStr"/>
-      <c r="F56" s="3" t="inlineStr"/>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>What income is taxed, given how this person files?  Answer: a dollar figure, never below zero.</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>gross − the deduction for that filing status: $16,100 single · $32,200 married · $24,150 head of household.</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>gross → gross
+how they file → status</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>PUBLISHED IRS TABLES, held in our code: the 2026 single-filer brackets and standard deduction from IRS Rev. Proc. 2025-32. Married thresholds are exactly double the single ones through the 35% band; head-of-household uses the IRS's wider 10% and 12% bands. THESE MUST BE UPDATED EVERY YEAR — the table stamps its own year so a stale one is visible rather than silent.
+The filing status comes from FILING_STATUS.</t>
+        </is>
+      </c>
       <c r="G56" s="3" t="inlineStr"/>
-      <c r="H56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -5126,7 +5275,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
@@ -5168,21 +5317,48 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr"/>
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>CAP_GAINS_RATES</t>
+        </is>
+      </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
           <t>userCapGainsRates</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr"/>
-      <c r="D57" s="3" t="inlineStr"/>
-      <c r="E57" s="3" t="inlineStr"/>
-      <c r="F57" s="3" t="inlineStr"/>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>What capital-gains rates apply to this person?  Answer: two rates — long-term and short-term.</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Long-term: the long-term capital-gains rate for their income and filing status, plus their state rate. Short-term: their ordinary marginal band, plus their state rate — because a short-term gain is taxed as ordinary income.
+Both rise with total income, so they depend on TOTAL_INCOME being right.</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>total income → totalGrossAnnual
+how they file → filingStatusOf
+state rate → stateRateOf</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding answers — the questions asked when the app is first set up, and editable afterwards on the Income screen. NOTHING external supplies any of this: no institution tells us what a person earns, so every figure here is only as right as the question that asked for it.</t>
+        </is>
+      </c>
       <c r="G57" s="3" t="inlineStr"/>
-      <c r="H57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>HoldingDetail, Performance</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -5192,7 +5368,7 @@
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>HoldingDetail, Performance</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
@@ -8915,21 +9091,47 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="inlineStr"/>
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>EMPLOYER_MATCH</t>
+        </is>
+      </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
           <t>employerMatchMonthly</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr"/>
-      <c r="D103" s="3" t="inlineStr"/>
-      <c r="E103" s="3" t="inlineStr"/>
-      <c r="F103" s="3" t="inlineStr"/>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>How much does the employer add each month?  Answer: a dollar figure.</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>Either a percentage of what the person contributes to their 401(k), or a flat monthly amount — whichever way they described it.</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>the match → employerMatchValue
+percent or dollars → employerMatchMode
+their own contribution → c_401k</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding answers — the questions asked when the app is first set up, and editable afterwards on the Income screen. NOTHING external supplies any of this: no institution tells us what a person earns, so every figure here is only as right as the question that asked for it.</t>
+        </is>
+      </c>
       <c r="G103" s="3" t="inlineStr"/>
-      <c r="H103" s="3" t="inlineStr"/>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I103" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J103" s="3" t="inlineStr">
@@ -8939,7 +9141,7 @@
       </c>
       <c r="K103" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L103" s="3" t="inlineStr">
@@ -8981,21 +9183,49 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr"/>
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>EQUITY_ROW_VALUE</t>
+        </is>
+      </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
           <t>equityRowValue</t>
         </is>
       </c>
-      <c r="C104" s="3" t="inlineStr"/>
-      <c r="D104" s="3" t="inlineStr"/>
-      <c r="E104" s="3" t="inlineStr"/>
-      <c r="F104" s="3" t="inlineStr"/>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>What is one line of a vesting schedule worth?  Answer: a dollar figure, never negative.</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>RSUs: shares × price — they vest at full value.
+Options: shares × (market price − strike price), FLOORED AT ZERO. An option struck above the market is worth nothing, not a negative amount.</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>shares → row.shares
+price → row.price
+kind → type
+strike and market → strike, market</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding answers — the questions asked when the app is first set up, and editable afterwards on the Income screen. NOTHING external supplies any of this: no institution tells us what a person earns, so every figure here is only as right as the question that asked for it.</t>
+        </is>
+      </c>
       <c r="G104" s="3" t="inlineStr"/>
-      <c r="H104" s="3" t="inlineStr"/>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J104" s="3" t="inlineStr">
@@ -9005,7 +9235,7 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L104" s="3" t="inlineStr">
@@ -9047,21 +9277,46 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="inlineStr"/>
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>RENTAL_INCOME_A_YEAR</t>
+        </is>
+      </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
           <t>rentalNetAnnual</t>
         </is>
       </c>
-      <c r="C105" s="3" t="inlineStr"/>
-      <c r="D105" s="3" t="inlineStr"/>
-      <c r="E105" s="3" t="inlineStr"/>
-      <c r="F105" s="3" t="inlineStr"/>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>What do the rentals net over a year?  Answer: a dollar figure, which can be negative.</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>(income − costs) each month, added across properties, × 12.
+A property that costs more than it earns REDUCES income rather than being floored at zero — a loss-making rental is a real fact about a plan.</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>each rental → rentalList</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding answers — the questions asked when the app is first set up, and editable afterwards on the Income screen. NOTHING external supplies any of this: no institution tells us what a person earns, so every figure here is only as right as the question that asked for it.</t>
+        </is>
+      </c>
       <c r="G105" s="3" t="inlineStr"/>
-      <c r="H105" s="3" t="inlineStr"/>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I105" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J105" s="3" t="inlineStr">
@@ -9071,7 +9326,7 @@
       </c>
       <c r="K105" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L105" s="3" t="inlineStr">
@@ -9113,21 +9368,46 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="inlineStr"/>
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME</t>
+        </is>
+      </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
           <t>retirementIncomeMonthly</t>
         </is>
       </c>
-      <c r="C106" s="3" t="inlineStr"/>
-      <c r="D106" s="3" t="inlineStr"/>
-      <c r="E106" s="3" t="inlineStr"/>
-      <c r="F106" s="3" t="inlineStr"/>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>How much retirement income arrives monthly?  Answer: a dollar figure.</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>Add Social Security, pension, withdrawals, required minimum distributions, annuities and other — each converted to a monthly figure from however it was entered (yearly, quarterly, monthly).</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>each source → ri_ss · ri_pension · ri_withdrawals · ri_rmd · ri_annuities · ri_other
+and how often each arrives → the matching frequency</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding answers — the questions asked when the app is first set up, and editable afterwards on the Income screen. NOTHING external supplies any of this: no institution tells us what a person earns, so every figure here is only as right as the question that asked for it.</t>
+        </is>
+      </c>
       <c r="G106" s="3" t="inlineStr"/>
-      <c r="H106" s="3" t="inlineStr"/>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I106" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J106" s="3" t="inlineStr">
@@ -9137,7 +9417,7 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L106" s="3" t="inlineStr">
@@ -9179,21 +9459,45 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="inlineStr"/>
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>STATE_TAX_RATE</t>
+        </is>
+      </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
           <t>stateRateOf</t>
         </is>
       </c>
-      <c r="C107" s="3" t="inlineStr"/>
-      <c r="D107" s="3" t="inlineStr"/>
-      <c r="E107" s="3" t="inlineStr"/>
-      <c r="F107" s="3" t="inlineStr"/>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>What state tax rate applies?  Answer: a rate between 0 and 15%.</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>The percentage the person entered, divided by 100, capped at 15% and floored at zero. No state table is consulted — one honest number from the person beats fifty guessed tables, and it is clamped so a typo cannot produce a wild figure.</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>their answer → stateTaxRate</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding answers — the questions asked when the app is first set up, and editable afterwards on the Income screen. NOTHING external supplies any of this: no institution tells us what a person earns, so every figure here is only as right as the question that asked for it.</t>
+        </is>
+      </c>
       <c r="G107" s="3" t="inlineStr"/>
-      <c r="H107" s="3" t="inlineStr"/>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I107" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J107" s="3" t="inlineStr">
@@ -9203,7 +9507,7 @@
       </c>
       <c r="K107" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L107" s="3" t="inlineStr">
@@ -9245,21 +9549,47 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="inlineStr"/>
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>TAX_OWED_SINGLE</t>
+        </is>
+      </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
           <t>taxOwed</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr"/>
-      <c r="D108" s="3" t="inlineStr"/>
-      <c r="E108" s="3" t="inlineStr"/>
-      <c r="F108" s="3" t="inlineStr"/>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>What federal tax is owed?  Answer: a dollar figure.</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>Fill the brackets in order, each rate applying ONLY to the slice of income inside it: 10% on the first $12,400 of taxable income, 12% to $50,400, 22% to $105,700, 24% to $201,775, 32% to $256,225, 35% to $640,600, 37% above.
+That is why the rate you are "in" is never the rate you pay overall — one more dollar at the top of a band costs the higher rate on THAT DOLLAR, not on everything.
+SINGLE FILER ONLY.</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>gross income → gross</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>PUBLISHED IRS TABLES, held in our code: the 2026 single-filer brackets and standard deduction from IRS Rev. Proc. 2025-32. Married thresholds are exactly double the single ones through the 35% band; head-of-household uses the IRS's wider 10% and 12% bands. THESE MUST BE UPDATED EVERY YEAR — the table stamps its own year so a stale one is visible rather than silent.</t>
+        </is>
+      </c>
       <c r="G108" s="3" t="inlineStr"/>
-      <c r="H108" s="3" t="inlineStr"/>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I108" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J108" s="3" t="inlineStr">
@@ -9269,7 +9599,7 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L108" s="3" t="inlineStr">
@@ -9311,21 +9641,49 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="inlineStr"/>
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>TAX_OWED</t>
+        </is>
+      </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
           <t>taxOwedFor</t>
         </is>
       </c>
-      <c r="C109" s="3" t="inlineStr"/>
-      <c r="D109" s="3" t="inlineStr"/>
-      <c r="E109" s="3" t="inlineStr"/>
-      <c r="F109" s="3" t="inlineStr"/>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>What tax is owed, federal and state together?  Answer: a dollar figure.</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>The same progressive fill, using that status's brackets — married bands are double the single ones — then ONE FLAT STATE RATE applied to gross and added on.
+A single honest percentage the person enters beats fifty guessed state tables, and it is capped at 15% and floored at zero so a typo cannot produce a wild bill.</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>gross → gross
+how they file → status
+their state rate → stateRate</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="inlineStr">
+        <is>
+          <t>PUBLISHED IRS TABLES, held in our code: the 2026 single-filer brackets and standard deduction from IRS Rev. Proc. 2025-32. Married thresholds are exactly double the single ones through the 35% band; head-of-household uses the IRS's wider 10% and 12% bands. THESE MUST BE UPDATED EVERY YEAR — the table stamps its own year so a stale one is visible rather than silent.
+The state rate is TYPED by the person — no table is consulted.</t>
+        </is>
+      </c>
       <c r="G109" s="3" t="inlineStr"/>
-      <c r="H109" s="3" t="inlineStr"/>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I109" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J109" s="3" t="inlineStr">
@@ -9335,7 +9693,7 @@
       </c>
       <c r="K109" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L109" s="3" t="inlineStr">
@@ -11269,21 +11627,47 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="inlineStr"/>
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>RETIREMENT_INCOME_NOW</t>
+        </is>
+      </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
           <t>currentRetirementIncomeMonthly</t>
         </is>
       </c>
-      <c r="C132" s="3" t="inlineStr"/>
-      <c r="D132" s="3" t="inlineStr"/>
-      <c r="E132" s="3" t="inlineStr"/>
-      <c r="F132" s="3" t="inlineStr"/>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>How much retirement income is arriving TODAY?  Answer: a dollar figure, and zero for someone not yet retired.</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>Zero unless the person said retirement income is one of their current sources; otherwise the same total as above.
+The distinction stops a future pension being counted as money arriving now — which would overstate today's income and flatter every current figure built on it.</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>do they receive it now → incomeSources
+the amounts → retirementIncomeMonthly</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding answers — the questions asked when the app is first set up, and editable afterwards on the Income screen. NOTHING external supplies any of this: no institution tells us what a person earns, so every figure here is only as right as the question that asked for it.</t>
+        </is>
+      </c>
       <c r="G132" s="3" t="inlineStr"/>
-      <c r="H132" s="3" t="inlineStr"/>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I132" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J132" s="3" t="inlineStr">
@@ -11293,7 +11677,7 @@
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr">
@@ -11335,21 +11719,47 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="inlineStr"/>
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>EFFECTIVE_TAX_RATE</t>
+        </is>
+      </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
           <t>effectiveRateOnGrossFor</t>
         </is>
       </c>
-      <c r="C133" s="3" t="inlineStr"/>
-      <c r="D133" s="3" t="inlineStr"/>
-      <c r="E133" s="3" t="inlineStr"/>
-      <c r="F133" s="3" t="inlineStr"/>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>What share of my income actually goes in tax?  Answer: a percentage, or zero on no income.</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>total tax ÷ gross. ALWAYS LOWER than the bracket you are in, because the lower bands were filled at their own lower rates first. This is the number that belongs in a plan; the bracket is not.</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>gross → gross
+how they file → status
+their state rate → stateRate</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>PUBLISHED IRS TABLES, held in our code: the 2026 single-filer brackets and standard deduction from IRS Rev. Proc. 2025-32. Married thresholds are exactly double the single ones through the 35% band; head-of-household uses the IRS's wider 10% and 12% bands. THESE MUST BE UPDATED EVERY YEAR — the table stamps its own year so a stale one is visible rather than silent.</t>
+        </is>
+      </c>
       <c r="G133" s="3" t="inlineStr"/>
-      <c r="H133" s="3" t="inlineStr"/>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I133" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J133" s="3" t="inlineStr">
@@ -11359,7 +11769,7 @@
       </c>
       <c r="K133" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L133" s="3" t="inlineStr">
@@ -11401,36 +11811,66 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="3" t="inlineStr"/>
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>GROSS_FROM_TAKE_HOME</t>
+        </is>
+      </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
           <t>grossFromNet</t>
         </is>
       </c>
-      <c r="C134" s="3" t="inlineStr"/>
-      <c r="D134" s="3" t="inlineStr"/>
-      <c r="E134" s="3" t="inlineStr"/>
-      <c r="F134" s="3" t="inlineStr"/>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>Someone told us their take-home — what must they be earning before tax?  Answer: a dollar figure.</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>Work backwards through the tax schedule by repeated halving: try a gross, compute its take-home, and narrow until the take-home matches what was typed. Fifty passes, deterministic.
+THE DEFECT: it always uses the SINGLE-FILER schedule. It does not accept a filing status at all, so a married couple's gross is worked out as though they were single — and since a single filer pays MORE tax, it takes MORE gross to reach the same take-home. Their income is overstated:
+  take-home $60,000 → overstated by $2,478 (3.9%)
+  take-home $90,000 → overstated by $6,746 (6.9%)
+  take-home $120,000 → overstated by $11,662 (8.9%)
+That inflated income then flows into savings capacity, the surplus, and every projection built on them. The app already KNOWS the filing status — FILING_STATUS reads it — it simply is not passed in.</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>take-home pay → net</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>PUBLISHED IRS TABLES, held in our code: the 2026 single-filer brackets and standard deduction from IRS Rev. Proc. 2025-32. Married thresholds are exactly double the single ones through the 35% band; head-of-household uses the IRS's wider 10% and 12% bands. THESE MUST BE UPDATED EVERY YEAR — the table stamps its own year so a stale one is visible rather than silent.
+The take-home figure is TYPED by the person on the income question.</t>
+        </is>
+      </c>
       <c r="G134" s="3" t="inlineStr"/>
-      <c r="H134" s="3" t="inlineStr"/>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I134" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DEFECT</t>
         </is>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>salaryGrossByMonth</t>
+          <t>The gross behind a take-home figure must be worked out using the person's OWN filing status. A married couple's income must not be computed as though they were single.</t>
         </is>
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr">
         <is>
-          <t>salaryGrossByMonth</t>
+          <t>Pass the filing status through. FILING_STATUS already reads it and TAX_OWED already accepts it — the two ends exist and are simply not connected. Roughly fifteen minutes plus the call sites. Worth doing early: it inflates income by up to 9%, and everything downstream — savings capacity, surplus, goal timing, the odds — is built on that number.</t>
         </is>
       </c>
       <c r="M134" s="5" t="inlineStr"/>
@@ -11467,21 +11907,46 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="inlineStr"/>
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>EQUITY_THIS_YEAR</t>
+        </is>
+      </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
           <t>rsuAnnual</t>
         </is>
       </c>
-      <c r="C135" s="3" t="inlineStr"/>
-      <c r="D135" s="3" t="inlineStr"/>
-      <c r="E135" s="3" t="inlineStr"/>
-      <c r="F135" s="3" t="inlineStr"/>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>How much equity vests this year?  Answer: a dollar figure.</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>Add the value of every vesting line dated this year. Lines vesting in future years are excluded from this year's income — they are not money yet.</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>each line → equityRowValue
+its year → rowVestYear</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding answers — the questions asked when the app is first set up, and editable afterwards on the Income screen. NOTHING external supplies any of this: no institution tells us what a person earns, so every figure here is only as right as the question that asked for it.</t>
+        </is>
+      </c>
       <c r="G135" s="3" t="inlineStr"/>
-      <c r="H135" s="3" t="inlineStr"/>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I135" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J135" s="3" t="inlineStr">
@@ -11491,7 +11956,7 @@
       </c>
       <c r="K135" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L135" s="3" t="inlineStr">
@@ -12139,21 +12604,48 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="3" t="inlineStr"/>
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>SALARY_BY_MONTH</t>
+        </is>
+      </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
           <t>salaryGrossByMonth</t>
         </is>
       </c>
-      <c r="C143" s="3" t="inlineStr"/>
-      <c r="D143" s="3" t="inlineStr"/>
-      <c r="E143" s="3" t="inlineStr"/>
-      <c r="F143" s="3" t="inlineStr"/>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>What is the gross salary in each month of the year?  Answer: twelve figures.</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>If a month-by-month table was given, use it. Otherwise put the single figure entered into all twelve months.
+If the person said they were entering TAKE-HOME, gross the whole year up and scale every month by the same factor — so the SHAPE of the year survives. A month that was twice the others stays twice the others.</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>the twelve months → salaryByMonth
+or one figure → the monthly salary box
+gross or take-home → salaryMode</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding answers — the questions asked when the app is first set up, and editable afterwards on the Income screen. NOTHING external supplies any of this: no institution tells us what a person earns, so every figure here is only as right as the question that asked for it.</t>
+        </is>
+      </c>
       <c r="G143" s="3" t="inlineStr"/>
-      <c r="H143" s="3" t="inlineStr"/>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I143" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J143" s="3" t="inlineStr">
@@ -12163,7 +12655,7 @@
       </c>
       <c r="K143" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L143" s="3" t="inlineStr">
@@ -12835,21 +13327,45 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="3" t="inlineStr"/>
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>MONTHS_WORKED</t>
+        </is>
+      </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
           <t>salaryActiveMonths</t>
         </is>
       </c>
-      <c r="C152" s="3" t="inlineStr"/>
-      <c r="D152" s="3" t="inlineStr"/>
-      <c r="E152" s="3" t="inlineStr"/>
-      <c r="F152" s="3" t="inlineStr"/>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>How many months of the year is there actually pay?  Answer: a count from 0 to 12.</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>Count the months whose salary is above zero. Used so that anything quoted per working month — tips especially — is not multiplied across months with no work in them.</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>the twelve months → salaryGrossByMonth</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding answers — the questions asked when the app is first set up, and editable afterwards on the Income screen. NOTHING external supplies any of this: no institution tells us what a person earns, so every figure here is only as right as the question that asked for it.</t>
+        </is>
+      </c>
       <c r="G152" s="3" t="inlineStr"/>
-      <c r="H152" s="3" t="inlineStr"/>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I152" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J152" s="3" t="inlineStr">
@@ -12859,7 +13375,7 @@
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L152" s="3" t="inlineStr">
@@ -12901,21 +13417,46 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="3" t="inlineStr"/>
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>SALARY_A_YEAR</t>
+        </is>
+      </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
           <t>salaryAnnual</t>
         </is>
       </c>
-      <c r="C153" s="3" t="inlineStr"/>
-      <c r="D153" s="3" t="inlineStr"/>
-      <c r="E153" s="3" t="inlineStr"/>
-      <c r="F153" s="3" t="inlineStr"/>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>What is the salary for the year?  Answer: a dollar figure.</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>ADD THE TWELVE MONTHS. It does not multiply a representative month by twelve.
+This is bug B-34, pinned by probe so it cannot return. The old version took the HIGHEST month as representative and multiplied — so someone earning $10,000 in three months and nothing in the other nine was recorded as earning $120,000 instead of $30,000, roughly a fourfold overstatement that then inflated the budget, the savings rate and the goal capacity.</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>the twelve months → salaryGrossByMonth</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding answers — the questions asked when the app is first set up, and editable afterwards on the Income screen. NOTHING external supplies any of this: no institution tells us what a person earns, so every figure here is only as right as the question that asked for it.</t>
+        </is>
+      </c>
       <c r="G153" s="3" t="inlineStr"/>
-      <c r="H153" s="3" t="inlineStr"/>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I153" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J153" s="3" t="inlineStr">
@@ -12925,7 +13466,7 @@
       </c>
       <c r="K153" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L153" s="3" t="inlineStr">
@@ -13130,21 +13671,46 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="3" t="inlineStr"/>
+      <c r="A156" s="3" t="inlineStr">
+        <is>
+          <t>TIPS_A_YEAR</t>
+        </is>
+      </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
           <t>tipsAnnual</t>
         </is>
       </c>
-      <c r="C156" s="3" t="inlineStr"/>
-      <c r="D156" s="3" t="inlineStr"/>
-      <c r="E156" s="3" t="inlineStr"/>
-      <c r="F156" s="3" t="inlineStr"/>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>What do tips come to over the year?  Answer: a dollar figure.</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>monthly tips × the number of months actually worked — NOT × 12. Someone working three months does not earn tips in the other nine.</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>tips a month → tipsMonthly
+months worked → salaryActiveMonths</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding answers — the questions asked when the app is first set up, and editable afterwards on the Income screen. NOTHING external supplies any of this: no institution tells us what a person earns, so every figure here is only as right as the question that asked for it.</t>
+        </is>
+      </c>
       <c r="G156" s="3" t="inlineStr"/>
-      <c r="H156" s="3" t="inlineStr"/>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I156" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J156" s="3" t="inlineStr">
@@ -13154,7 +13720,7 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L156" s="3" t="inlineStr">
@@ -13262,21 +13828,46 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="3" t="inlineStr"/>
+      <c r="A158" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL_INCOME</t>
+        </is>
+      </c>
       <c r="B158" s="4" t="inlineStr">
         <is>
           <t>totalGrossAnnual</t>
         </is>
       </c>
-      <c r="C158" s="3" t="inlineStr"/>
-      <c r="D158" s="3" t="inlineStr"/>
-      <c r="E158" s="3" t="inlineStr"/>
-      <c r="F158" s="3" t="inlineStr"/>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>What is the whole household income for the year, before tax?  Answer: a dollar figure.</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>Salary + tips + bonus + a signing amount + vesting equity + net rental income + other income (recurring and one-off, taxable and not) + retirement income currently being received.
+This is the figure every tax calculation and every savings-capacity figure is built on, which is why each part above has its own row.</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>each part → its own engine above</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding answers — the questions asked when the app is first set up, and editable afterwards on the Income screen. NOTHING external supplies any of this: no institution tells us what a person earns, so every figure here is only as right as the question that asked for it.</t>
+        </is>
+      </c>
       <c r="G158" s="3" t="inlineStr"/>
-      <c r="H158" s="3" t="inlineStr"/>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>probes/income-tax.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I158" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J158" s="3" t="inlineStr">
@@ -13286,7 +13877,7 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L158" s="3" t="inlineStr">

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -7448,21 +7448,45 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="inlineStr"/>
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>COST_OF_LIVING</t>
+        </is>
+      </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
           <t>colFactor</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr"/>
-      <c r="D82" s="3" t="inlineStr"/>
-      <c r="E82" s="3" t="inlineStr"/>
-      <c r="F82" s="3" t="inlineStr"/>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>How much more or less does life cost where they plan to live?  Answer: a multiplier, and the place it matched.</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Look the place up in our own cost-of-living table and return its multiplier. No match → 1.0, meaning no adjustment, rather than a guess.</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>where they will live → location</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>OUR OWN TABLE in src/domain/retirement/col.ts. Not a live feed — a hand-maintained list, and a figure a person cannot check against anything.</t>
+        </is>
+      </c>
       <c r="G82" s="3" t="inlineStr"/>
-      <c r="H82" s="3" t="inlineStr"/>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>probes/retirement-engine.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I82" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr">
@@ -7472,7 +7496,7 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr">
@@ -7514,21 +7538,45 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr"/>
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>POT_AT_RETIREMENT</t>
+        </is>
+      </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
           <t>projectNestEgg</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr"/>
-      <c r="D83" s="3" t="inlineStr"/>
-      <c r="E83" s="3" t="inlineStr"/>
-      <c r="F83" s="3" t="inlineStr"/>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>What will the pot be worth at retirement?  Answer: a dollar figure, with a range around it.</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>The same year-by-year growth as the simulation, run over the years to retirement, reporting where the runs land. It answers "how much will I have", where the simulation answers "will it last".</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>the same inputs → inp</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>Everything upstream in this workbook. This engine sits at the TOP of the chain: the pot comes from NEST_EGG, the return and swing from EXPECTED_RETURN_BLENDED and EXPECTED_SWING_BLENDED, the spend from the retirement-spending answers, guaranteed income from RETIREMENT_INCOME and Social Security, tax from the income module. Every defect below it arrives here.</t>
+        </is>
+      </c>
       <c r="G83" s="3" t="inlineStr"/>
-      <c r="H83" s="3" t="inlineStr"/>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>probes/retirement-engine.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I83" s="3" t="inlineStr">
         <is>
-          <t>NetWorth, WhatIf</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr">
@@ -7538,7 +7586,7 @@
       </c>
       <c r="K83" s="3" t="inlineStr">
         <is>
-          <t>NetWorth, WhatIf</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L83" s="3" t="inlineStr">
@@ -7580,21 +7628,63 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="inlineStr"/>
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST</t>
+        </is>
+      </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
           <t>simulate</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr"/>
-      <c r="D84" s="3" t="inlineStr"/>
-      <c r="E84" s="3" t="inlineStr"/>
-      <c r="F84" s="3" t="inlineStr"/>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>What are the odds this money lasts?  Answer: a percentage, plus the projected pot at retirement, what is needed, the gap, and what extra saving would close it.</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Run the plan 400 times. Each run walks year by year:
+BEFORE RETIREMENT — the pot grows at a randomly drawn return each year (average and swing as given), plus what goes in; big one-off costs and any payments still running come out.
+AFTER RETIREMENT — spending comes out, guaranteed income goes in, and the pot keeps growing on what is left. A run SUCCEEDS if the money outlasts the horizon.
+The odds are the share of runs that succeeded.
+WHAT IS INFLATED AND WHAT IS NOT — the rule most easily got wrong:
+• SPENDING is inflated to the year it happens. Today's dollars are not tomorrow's.
+• A BIG ONE-OFF COST is inflated to its own year, and leaves the pot in that year — a roof in 2030 is paid in 2030. Costs already past, or beyond the horizon, are not simulated at all.
+• A PAYMENT THAT STOPS IS CHARGED FLAT AND NEVER INFLATED. A fixed mortgage payment is the same number of dollars every year until it ends. Inflating it would overstate its cost every single year, and then stop overstating it at the end — the worst of both.
+• GUARANTEED INCOME can start LATER than retirement but never earlier: asking for it sooner is clamped to the retirement year.
+It is DETERMINISTIC — the same inputs give the same odds every time, because the randomness is seeded. Two people with the same plan see the same number, and so does the same person tomorrow.</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>the pot → start_balance
+what goes in → annual_contribution
+return and swing → mean_return, vol_return
+inflation → inflation
+spend → retire_monthly_spend_today
+guaranteed → guaranteed_monthly_income
+ages → current_age, retire_age, horizon_age
+big costs → one_off_costs
+payments that stop → recurring_until
+changes to saving → contribution_adjustments</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>Everything upstream in this workbook. This engine sits at the TOP of the chain: the pot comes from NEST_EGG, the return and swing from EXPECTED_RETURN_BLENDED and EXPECTED_SWING_BLENDED, the spend from the retirement-spending answers, guaranteed income from RETIREMENT_INCOME and Social Security, tax from the income module. Every defect below it arrives here.</t>
+        </is>
+      </c>
       <c r="G84" s="3" t="inlineStr"/>
-      <c r="H84" s="3" t="inlineStr"/>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>probes/retirement-engine.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I84" s="3" t="inlineStr">
         <is>
-          <t>NetWorth, WhatIf</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr">
@@ -7604,7 +7694,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>NetWorth, WhatIf</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr">
@@ -7646,21 +7736,49 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr"/>
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>SS_CLAIM_FACTOR</t>
+        </is>
+      </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
           <t>ssClaimFactor</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr"/>
-      <c r="D85" s="3" t="inlineStr"/>
-      <c r="E85" s="3" t="inlineStr"/>
-      <c r="F85" s="3" t="inlineStr"/>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>How much does claiming at this age change the cheque?  Answer: a multiplier — 0.70 at 62, 1.00 at 67, 1.24 at 70.</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Relative to full retirement age 67 (everyone born 1960 or later):
+• claiming EARLY: about 6.67% less per year for the first three years, then 5% a year — so 64 is 80% and 62 is 70%
+• claiming at 67: exactly 1.00. The statement amount, unchanged. This anchors the whole table.
+• WAITING: 8% more per year to age 70 — 1.24 at 70
+Ages outside 62–70 are CLAMPED, never extrapolated: waiting past 70 earns nothing more, and 62 is the earliest you can claim.</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>the claim age → claimAge</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>The published Social Security Administration schedule, held in our code. The amount it is applied to is the person's OWN statement figure — the monthly benefit at full retirement age, typed in from their Social Security statement. We never estimate the benefit itself.</t>
+        </is>
+      </c>
       <c r="G85" s="3" t="inlineStr"/>
-      <c r="H85" s="3" t="inlineStr"/>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>probes/retirement-engine.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I85" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr">
@@ -7670,7 +7788,7 @@
       </c>
       <c r="K85" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L85" s="3" t="inlineStr">
@@ -10306,21 +10424,46 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="inlineStr"/>
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>RETIREMENT_SPENDING</t>
+        </is>
+      </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
           <t>retirementSpendMonthly</t>
         </is>
       </c>
-      <c r="C116" s="3" t="inlineStr"/>
-      <c r="D116" s="3" t="inlineStr"/>
-      <c r="E116" s="3" t="inlineStr"/>
-      <c r="F116" s="3" t="inlineStr"/>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>What will be spent each month in retirement?  Answer: a dollar figure in today's dollars.</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>What the person said they expect to spend, adjusted for where they plan to live. Stated in TODAY'S dollars — the simulation inflates it to each future year, so inflating it here as well would count inflation twice.</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>the answer → the retirement-spending question
+where they will live → the location answer</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding and Plan answers. Cost-of-living adjustment comes from our own location table.</t>
+        </is>
+      </c>
       <c r="G116" s="3" t="inlineStr"/>
-      <c r="H116" s="3" t="inlineStr"/>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>probes/retirement-engine.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I116" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J116" s="3" t="inlineStr">
@@ -10330,7 +10473,7 @@
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L116" s="3" t="inlineStr">
@@ -10372,21 +10515,46 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="inlineStr"/>
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>SS_BENEFIT_AT_AGE</t>
+        </is>
+      </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
           <t>ssBenefitAtClaimAge</t>
         </is>
       </c>
-      <c r="C117" s="3" t="inlineStr"/>
-      <c r="D117" s="3" t="inlineStr"/>
-      <c r="E117" s="3" t="inlineStr"/>
-      <c r="F117" s="3" t="inlineStr"/>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>What would the monthly cheque be if claimed at this age?  Answer: a whole dollar figure.</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>the statement amount × the factor above, rounded to whole dollars. Today's dollars, no opinion attached — the table shows the trade and the person chooses.</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>the statement amount → statementMonthly
+the claim age → claimAge</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="inlineStr">
+        <is>
+          <t>The published Social Security Administration schedule, held in our code. The amount it is applied to is the person's OWN statement figure — the monthly benefit at full retirement age, typed in from their Social Security statement. We never estimate the benefit itself.</t>
+        </is>
+      </c>
       <c r="G117" s="3" t="inlineStr"/>
-      <c r="H117" s="3" t="inlineStr"/>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>probes/retirement-engine.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I117" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>CORRECT</t>
         </is>
       </c>
       <c r="J117" s="3" t="inlineStr">
@@ -10396,7 +10564,7 @@
       </c>
       <c r="K117" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L117" s="3" t="inlineStr">

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -933,26 +933,10 @@
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr"/>
       <c r="N3" s="5" t="inlineStr"/>
       <c r="O3" s="6" t="inlineStr">
@@ -999,26 +983,10 @@
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
       <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="6" t="inlineStr">
@@ -1065,26 +1033,10 @@
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="5" t="inlineStr"/>
       <c r="N5" s="5" t="inlineStr"/>
       <c r="O5" s="6" t="inlineStr">
@@ -1119,64 +1071,22 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>WRAPPER_CONFIRMED</t>
-        </is>
-      </c>
+      <c r="A6" s="3" t="inlineStr"/>
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>confirmWrapper</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>The person told us what this account really is — how is that recorded?  Answer: the account, with its type and wrapper set and marked as confirmed.</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Set the type and wrapper on that one account and mark it confirmed. FUTURE SYNCS NEVER OVERRIDE A CONFIRMED WRAPPER, so the broker's label can never quietly undo the person's own answer on the next refresh.</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>the accounts → accounts
-which one → assetId
-what it really is → kind, taxBucket</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>The Held-in chooser in the connect flow — the question the app asks whenever WRAPPER_GUESS comes back not confident.</t>
-        </is>
-      </c>
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>probes/sync-identity.probe.test.ts</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="H6" s="3" t="inlineStr"/>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="6" t="inlineStr">
@@ -1230,7 +1140,7 @@
         <is>
           <t>'st-' + the broker's account id. That is the whole rule.
 IT MATTERS FAR MORE THAN IT LOOKS. Our identity for an account IS the broker's identity for it, and the key that stops an activity being recorded twice BEGINS with our account id. So if the broker's id ever changes — a reconnect, a re-linked login, a migrated or renumbered account — every key changes with it, nothing matches what we have already seen, and the ENTIRE history re-imports as brand-new money arriving.
-This is the last standing explanation for $1,462,462 of contributions on an account whose statement says nothing moved. Proved as a mechanism by probe: the same 40 events, deduplicated correctly under one id, all come back as new under another.</t>
+This is the last standing explanation for $1,462,462 of contributions on an account whose statement says nothing moved. Proved as a mechanism by probe: the same 40 events, correctly spotted as repeats correctly under one id, all come back as new under another.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -1240,7 +1150,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>The SnapTrade payload for a connected account: accounts[].id (the broker's own account id), accounts[].type (the broker's raw label for the account), balances, positions[] and activities[].
+          <t>The the data SnapTrade sends for a connected account: accounts[].id (the broker's own account id), accounts[].type (the broker's raw label for the account), balances, positions[] and activities[].
 The id is SnapTrade's, not ours, and nothing in our code controls whether it stays the same.</t>
         </is>
       </c>
@@ -1267,7 +1177,7 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>FIRST, PROVE IT ON THE REAL DATA before changing anything: check whether the Vanguard account's stored id changed. If it did, this is the cause of the $1.4m and the fix is worth doing properly. THEN the fix has two parts — key the dedupe on the broker's own activity id where one is sent, rather than prefixing ours to it; and match a reconnected account to the existing one on institution plus mask before creating a new record. Neither is large. Both need the real ledger first, because a fix aimed at the wrong cause is worse than none.</t>
+          <t>FIRST, PROVE IT ON THE REAL DATA before changing anything: check whether the Vanguard account's stored id changed. If it did, this is the cause of the $1.4m and the fix is worth doing properly. THEN the fix has two parts — key the duplicate check on the broker's own activity id where one is sent, rather than prefixing ours to it; and match a reconnected account to the existing one on institution plus mask before creating a new record. Neither is large. Both need the real ledger first, because a fix aimed at the wrong cause is worse than none.</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr"/>
@@ -1316,26 +1226,10 @@
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="5" t="inlineStr"/>
       <c r="N8" s="5" t="inlineStr"/>
       <c r="O8" s="6" t="inlineStr">
@@ -1547,7 +1441,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>INGEST_ACTIVITY_KEY</t>
+          <t>ACTIVITY_FINGERPRINT</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1636,7 +1530,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>WRAPPER_GUESS</t>
+          <t>ACCOUNT_TAX_TYPE_GUESS</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1647,12 +1541,12 @@
       <c r="C12" s="3" t="inlineStr">
         <is>
           <t>What kind of account is this, and how is it taxed?
-Answers: an account type and a wrapper — Roth IRA · 401(k) · Traditional IRA · HSA · Checking · Brokerage · 529 — TOGETHER WITH whether we are confident. Not confident means the app asks rather than assuming.</t>
+Answers: an account type and a tax type — Roth IRA · 401(k) · Traditional IRA · HSA · Checking · Brokerage · 529 — TOGETHER WITH whether we are confident. Not confident means the app asks rather than assuming.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>SnapTrade sends no standard wrapper — only the broker's own words — so the words are read, first match winning:
+          <t>SnapTrade sends no standard tax type — only the broker's own words — so the words are read, first match winning:
 • contains ROTH → Roth IRA, or a Roth 401(k) if it also says 401
 • 401K / 401(K) / 403B / 457 → 401(k), pre-tax
 • ROLLOVER / TRADITIONAL / SEP / SIMPLE IRA → Traditional IRA, pre-tax
@@ -1662,7 +1556,7 @@
 • 529 / EDUCATION → 529
 • INDIVIDUAL / JOINT / BROKERAGE / MARGIN / CASH / TAXABLE / TRUST → Brokerage, taxable
 • anything else → Brokerage for display, NOT confident, and the connect flow asks.
-The confidence flag is the honest part: a wrong wrapper is wrong tax maths on every projection, so an unrecognised type is never guessed silently.</t>
+The confidence flag is the honest part: the wrong tax type means the wrong tax maths on every projection, so an unrecognised type is never guessed silently.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1673,7 +1567,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>The SnapTrade payload for a connected account: accounts[].id (the broker's own account id), accounts[].type (the broker's raw label for the account), balances, positions[] and activities[].</t>
+          <t>The the data SnapTrade sends for a connected account: accounts[].id (the broker's own account id), accounts[].type (the broker's raw label for the account), balances, positions[] and activities[].</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -1687,21 +1581,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>ingestSync</t>
-        </is>
-      </c>
+      <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>ingestSync</t>
-        </is>
-      </c>
+      <c r="L12" s="3" t="inlineStr"/>
       <c r="M12" s="5" t="inlineStr"/>
       <c r="N12" s="5" t="inlineStr"/>
       <c r="O12" s="6" t="inlineStr">
@@ -1843,26 +1729,10 @@
       <c r="F14" s="3" t="inlineStr"/>
       <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>ingestSync</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>ingestSync</t>
-        </is>
-      </c>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
       <c r="M14" s="5" t="inlineStr"/>
       <c r="N14" s="5" t="inlineStr"/>
       <c r="O14" s="6" t="inlineStr">
@@ -1939,7 +1809,7 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>SnapTrade positions payload, per holding: symbol.raw_symbol (the ticker), symbol.description (the name — where a CD's maturity and coupon actually live), symbol.type.code (the broker's own type: cs = common share, et = ETF, mf = mutual fund, oef/cef = open/closed-end fund, bnd = bond, crypto), units, price, average_purchase_price, cash_equivalent, tax_lots[].</t>
+          <t>SnapTrade positions data, per holding: symbol.raw_symbol (the ticker), symbol.description (the name — where a CD's maturity and coupon actually live), symbol.type.code (the broker's own type: cs = common share, et = ETF, mf = mutual fund, oef/cef = open/closed-end fund, bnd = bond, crypto), units, price, average_purchase_price, cash_equivalent, tax_lots[].</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -2031,7 +1901,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>The SnapTrade payload for a connected account: accounts[].id (the broker's own account id), accounts[].type (the broker's raw label for the account), balances, positions[] and activities[].</t>
+          <t>The the data SnapTrade sends for a connected account: accounts[].id (the broker's own account id), accounts[].type (the broker's raw label for the account), balances, positions[] and activities[].</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr"/>
@@ -2045,21 +1915,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>ingestSync</t>
-        </is>
-      </c>
+      <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>ingestSync</t>
-        </is>
-      </c>
+      <c r="L16" s="3" t="inlineStr"/>
       <c r="M16" s="5" t="inlineStr"/>
       <c r="N16" s="5" t="inlineStr"/>
       <c r="O16" s="6" t="inlineStr">
@@ -2096,7 +1958,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>CASH_SLEEVE</t>
+          <t>UNINVESTED_CASH</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -2124,8 +1986,8 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>SnapTrade positions payload, per holding: symbol.raw_symbol (the ticker), symbol.description (the name — where a CD's maturity and coupon actually live), symbol.type.code (the broker's own type: cs = common share, et = ETF, mf = mutual fund, oef/cef = open/closed-end fund, bnd = bond, crypto), units, price, average_purchase_price, cash_equivalent, tax_lots[].
-balances.cash: the account's cash balance in the same payload.</t>
+          <t>SnapTrade positions data, per holding: symbol.raw_symbol (the ticker), symbol.description (the name — where a CD's maturity and coupon actually live), symbol.type.code (the broker's own type: cs = common share, et = ETF, mf = mutual fund, oef/cef = open/closed-end fund, bnd = bond, crypto), units, price, average_purchase_price, cash_equivalent, tax_lots[].
+balances.cash: the account's cash balance in the same the data they send.</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2141,7 +2003,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>The netting is right, but ingest.ts ALSO drops every cash-equivalent position from the holdings list. Both run, so for a broker that flags the fund, the money is subtracted from cash AND missing from holdings. One of the two must go: either show the fund as a holding and net the sleeve (the honest option), or keep it in the sleeve and do not net. Needs a decision, not a patch.</t>
+          <t>The netting is right, but ingest.ts ALSO drops every cash-equivalent position from the holdings list. Both run, so for a broker that flags the fund, the money is subtracted from cash AND missing from holdings. One of the two must go: either show the fund as a holding and net the uninvested cash (the honest option), or keep it in the uninvested cash and do not net. Needs a decision, not a patch.</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
@@ -2151,7 +2013,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>FOUNDER DECISION FIRST, then a one-line change. Recommend: show the money-market fund as a holding (it pays dividends and belongs in the measured bucket per the 2026-08-04 rule), keep netCashSleeve exactly as it is, and DELETE the .filter((m) =&gt; !m.cashEquivalent) in ingest.ts:67. That leaves the money in exactly one place. The alternative — keep it in the sleeve and stop netting — contradicts the cash-means-cash rule, so I do not recommend it.</t>
+          <t>FOUNDER DECISION FIRST, then a one-line change. Recommend: show the money-market fund as a holding (it pays dividends and belongs with the measured money under the 2026-08-04 rule), leave the uninvested-cash subtraction exactly as it is, and DELETE the line in the import step that drops cash-equivalent holdings (ingest.ts:67). That leaves the money in exactly one place. The alternative — keep it inside the uninvested cash and stop subtracting — contradicts the cash-means-cash rule, so I do not recommend it.</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr"/>
@@ -2200,26 +2062,10 @@
       <c r="F18" s="3" t="inlineStr"/>
       <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>currencySymbol</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>currencySymbol</t>
-        </is>
-      </c>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr"/>
       <c r="M18" s="5" t="inlineStr"/>
       <c r="N18" s="5" t="inlineStr"/>
       <c r="O18" s="6" t="inlineStr">
@@ -2266,26 +2112,10 @@
       <c r="F19" s="3" t="inlineStr"/>
       <c r="G19" s="3" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>money</t>
-        </is>
-      </c>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+      <c r="L19" s="3" t="inlineStr"/>
       <c r="M19" s="5" t="inlineStr"/>
       <c r="N19" s="5" t="inlineStr"/>
       <c r="O19" s="6" t="inlineStr">
@@ -2332,26 +2162,10 @@
       <c r="F20" s="3" t="inlineStr"/>
       <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>money2</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>money2</t>
-        </is>
-      </c>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
       <c r="M20" s="5" t="inlineStr"/>
       <c r="N20" s="5" t="inlineStr"/>
       <c r="O20" s="6" t="inlineStr">
@@ -2398,26 +2212,10 @@
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>ImportHoldings</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>assetsFromOnboarding, debtsFromOnboarding, ingestSync</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>ImportHoldings</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>assetsFromOnboarding, debtsFromOnboarding, ingestSync</t>
-        </is>
-      </c>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr"/>
       <c r="M21" s="5" t="inlineStr"/>
       <c r="N21" s="5" t="inlineStr"/>
       <c r="O21" s="6" t="inlineStr">
@@ -2464,26 +2262,10 @@
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr"/>
       <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>assetsFromOnboarding, debtsFromOnboarding, employerMatchMonthly, equityRowValue, monthlyContributionsFromOnboarding, plannedMonthlySpend, retirementIncomeMonthly, retirementSpendMonthly, rsuAnnual, salaryGrossByMonth, stateRateOf, tipsAnnual, totalGrossAnnual</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>assetsFromOnboarding, debtsFromOnboarding, employerMatchMonthly, equityRowValue, monthlyContributionsFromOnboarding, plannedMonthlySpend, retirementIncomeMonthly, retirementSpendMonthly, rsuAnnual, salaryGrossByMonth, stateRateOf, tipsAnnual, totalGrossAnnual</t>
-        </is>
-      </c>
+      <c r="I22" s="3" t="inlineStr"/>
+      <c r="J22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr"/>
       <c r="N22" s="5" t="inlineStr"/>
       <c r="O22" s="6" t="inlineStr">
@@ -2530,26 +2312,10 @@
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="3" t="inlineStr"/>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I23" s="3" t="inlineStr"/>
+      <c r="J23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr"/>
       <c r="N23" s="5" t="inlineStr"/>
       <c r="O23" s="6" t="inlineStr">
@@ -2625,21 +2391,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="J24" s="3" t="inlineStr"/>
       <c r="K24" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="5" t="inlineStr"/>
       <c r="N24" s="5" t="inlineStr"/>
       <c r="O24" s="6" t="inlineStr">
@@ -2686,26 +2444,10 @@
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>AccountDetail, NetWorth, Performance</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>benchmarkReturn, isCashKind</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t>AccountDetail, NetWorth, Performance</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>benchmarkReturn, isCashKind</t>
-        </is>
-      </c>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr"/>
       <c r="N25" s="5" t="inlineStr"/>
       <c r="O25" s="6" t="inlineStr">
@@ -2752,26 +2494,10 @@
       <c r="F26" s="3" t="inlineStr"/>
       <c r="G26" s="3" t="inlineStr"/>
       <c r="H26" s="3" t="inlineStr"/>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I26" s="3" t="inlineStr"/>
+      <c r="J26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr"/>
       <c r="M26" s="5" t="inlineStr"/>
       <c r="N26" s="5" t="inlineStr"/>
       <c r="O26" s="6" t="inlineStr">
@@ -2835,7 +2561,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>The connected account's payload: balance.total.amount (the broker's authoritative total), balances.cash, and positions[] each with symbol.raw_symbol, symbol.description, units and price. Option positions arrive on their own feed.
+          <t>The connected account's the data they send: balance.total.amount (the broker's authoritative total), balances.cash, and positions[] each with symbol.raw_symbol, symbol.description, units and price. Option positions arrive on their own feed.
 The holding names are the same field ACCOUNT_SPLIT reads — which is what makes the disagreement avoidable.</t>
         </is>
       </c>
@@ -2932,7 +2658,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>The account or holding NAME. Broker: symbol.description in the positions payload, else the account nickname. File: the name column, found by header pattern — Description / Security / Investment Name / Fund / Holding / Instrument. Typed: the Name box on Add account.</t>
+          <t>The account or holding NAME. Broker: symbol.description in the positions data, else the account nickname. File: the name column, found by header pattern — Description / Security / Investment Name / Fund / Holding / Instrument. Typed: the Name box on Add account.</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -3003,26 +2729,10 @@
       <c r="F29" s="3" t="inlineStr"/>
       <c r="G29" s="3" t="inlineStr"/>
       <c r="H29" s="3" t="inlineStr"/>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>Itemize</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>itemizeRemainder</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>Itemize</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>itemizeRemainder</t>
-        </is>
-      </c>
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr"/>
       <c r="N29" s="5" t="inlineStr"/>
       <c r="O29" s="6" t="inlineStr">
@@ -3156,26 +2866,10 @@
       <c r="F31" s="3" t="inlineStr"/>
       <c r="G31" s="3" t="inlineStr"/>
       <c r="H31" s="3" t="inlineStr"/>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>earmarkDefault</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t>earmarkDefault</t>
-        </is>
-      </c>
+      <c r="I31" s="3" t="inlineStr"/>
+      <c r="J31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="3" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
       <c r="N31" s="5" t="inlineStr"/>
       <c r="O31" s="6" t="inlineStr">
@@ -3222,26 +2916,10 @@
       <c r="F32" s="3" t="inlineStr"/>
       <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="3" t="inlineStr"/>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>AccountDetail, NetWorth</t>
-        </is>
-      </c>
-      <c r="J32" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t>AccountDetail, NetWorth</t>
-        </is>
-      </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I32" s="3" t="inlineStr"/>
+      <c r="J32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="inlineStr"/>
+      <c r="L32" s="3" t="inlineStr"/>
       <c r="M32" s="5" t="inlineStr"/>
       <c r="N32" s="5" t="inlineStr"/>
       <c r="O32" s="6" t="inlineStr">
@@ -3293,18 +2971,18 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>An explicitly set treatment wins. Otherwise: a PRE_TAX wrapper → tax-deferred; a ROTH wrapper → tax-free; everything else → taxable. Taxable is the default, which is the cautious side — it assumes tax is owed rather than assuming it is not.</t>
+          <t>An explicitly set treatment wins. Otherwise: a PRE_TAX tax type → tax-deferred; a ROTH tax type → tax-free; everything else → taxable. Taxable is the default, which is the cautious side — it assumes tax is owed rather than assuming it is not.</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
           <t>explicit treatment → tax_treatment
-wrapper → tax_bucket</t>
+how it is taxed → tax_bucket</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Both set from the wrapper picked on Add account (Taxable / 401(k) / Traditional IRA / Roth / HSA). No institution tells us this reliably, so it is always the person's own answer.</t>
+          <t>Both set from the tax type picked on Add account (Taxable / 401(k) / Traditional IRA / Roth / HSA). No institution tells us this reliably, so it is always the person's own answer.</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -3375,26 +3053,10 @@
       <c r="F34" s="3" t="inlineStr"/>
       <c r="G34" s="3" t="inlineStr"/>
       <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr"/>
+      <c r="K34" s="3" t="inlineStr"/>
+      <c r="L34" s="3" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr"/>
       <c r="N34" s="5" t="inlineStr"/>
       <c r="O34" s="6" t="inlineStr">
@@ -3473,21 +3135,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="J35" s="3" t="inlineStr"/>
       <c r="K35" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="L35" s="3" t="inlineStr"/>
       <c r="M35" s="5" t="inlineStr"/>
       <c r="N35" s="5" t="inlineStr"/>
       <c r="O35" s="6" t="inlineStr">
@@ -3534,26 +3188,10 @@
       <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" s="3" t="inlineStr"/>
       <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I36" s="3" t="inlineStr"/>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr"/>
+      <c r="L36" s="3" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr"/>
       <c r="N36" s="5" t="inlineStr"/>
       <c r="O36" s="6" t="inlineStr">
@@ -3860,26 +3498,10 @@
       <c r="F40" s="3" t="inlineStr"/>
       <c r="G40" s="3" t="inlineStr"/>
       <c r="H40" s="3" t="inlineStr"/>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>plannedMonthlySpend</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t>plannedMonthlySpend</t>
-        </is>
-      </c>
+      <c r="I40" s="3" t="inlineStr"/>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr"/>
+      <c r="L40" s="3" t="inlineStr"/>
       <c r="M40" s="5" t="inlineStr"/>
       <c r="N40" s="5" t="inlineStr"/>
       <c r="O40" s="6" t="inlineStr">
@@ -3926,26 +3548,10 @@
       <c r="F41" s="3" t="inlineStr"/>
       <c r="G41" s="3" t="inlineStr"/>
       <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I41" s="3" t="inlineStr"/>
+      <c r="J41" s="3" t="inlineStr"/>
+      <c r="K41" s="3" t="inlineStr"/>
+      <c r="L41" s="3" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr"/>
       <c r="N41" s="5" t="inlineStr"/>
       <c r="O41" s="6" t="inlineStr">
@@ -4078,26 +3684,10 @@
       <c r="F43" s="3" t="inlineStr"/>
       <c r="G43" s="3" t="inlineStr"/>
       <c r="H43" s="3" t="inlineStr"/>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>debtsFromOnboarding</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t>debtsFromOnboarding</t>
-        </is>
-      </c>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
       <c r="M43" s="5" t="inlineStr"/>
       <c r="N43" s="5" t="inlineStr"/>
       <c r="O43" s="6" t="inlineStr">
@@ -4144,26 +3734,10 @@
       <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth, Performance</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth, Performance</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
       <c r="M44" s="5" t="inlineStr"/>
       <c r="N44" s="5" t="inlineStr"/>
       <c r="O44" s="6" t="inlineStr">
@@ -4210,15 +3784,17 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>What drove my net worth from one date to the next?  Answer: a set of rows that add up — starting value · money you put in · money you took out · dividends · interest · debt paid down · change in investment value · ending value.</t>
+          <t>My net worth changed since last time — what actually caused it?
+Answer: a set of lines that add up — what you started with · money you put in · money you took out · dividends · interest · debt you paid down · how your investments moved · what you have now.</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>total       = ending − beginning
-wealth made = total − money in + money out − debt paid down
-change in investment value = wealth made − dividends − interest
-THE DEFECT IS IN THAT LAST LINE. "Change in investment value" is not measured against any price. It is whatever is left over once everything else is accounted for, so every error anywhere else in the ledger lands in it wearing the label of a market movement. With nothing actually moved, a $500 deposit manufactures a $500 "market loss" — and a real $500 loss looks identical.</t>
+          <t>WHAT IT IS TRYING TO DO. If you were worth $500,000 last month and $520,000 today, you gained $20,000 — but you want to know why. Did you save it? Did the market give it to you? Did you pay down a loan? Those feel completely different, and only one of them is luck.
+HOW IT WORKS OUT EACH LINE. Everything except the last one is a real record: your deposits, your withdrawals, dividends paid, interest received, loan payments made.
+THE PROBLEM IS THE LAST LINE. "How your investments moved" is not measured against a single share price. It is simply what is left over after everything else is accounted for. Whatever the app cannot explain lands there — wearing the label of a market movement.
+A WORKED EXAMPLE OF THE FAULT. You were worth $939,089. You are still worth $939,089. Nothing moved. But the app thinks you deposited $500. Now the sums must balance: you put in $500 and ended level, so the investments must have LOST $500. The screen tells you the market took $500 from you. It did not. The deposit was wrong.
+And a real $500 loss produces exactly the same line. You cannot tell them apart, which is why a wrong deposit anywhere becomes a market movement that never happened.</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -4252,7 +3828,7 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>STOP CALLING THE RESIDUAL A MEASUREMENT. Two changes. (1) The unexplained remainder gets its own honest row — "we could not account for $X" — instead of being printed as "change in investment value". A person can act on "unexplained"; they cannot act on a market loss that never happened. (2) Market movement is MEASURED where the evidence exists — from stored per-holding values — and the row is simply absent when it does not, rather than being inferred. Absent beats invented.</t>
+          <t>STOP CALLING A LEFTOVER A MEASUREMENT. Two changes. (1) The unexplained remainder gets its own honest row — "we could not account for $X" — instead of being printed as "change in investment value". A person can act on "unexplained"; they cannot act on a market loss that never happened. (2) Market movement is MEASURED where the evidence exists — from stored per-holding values — and the row is simply absent when it does not, rather than being inferred. Absent beats invented.</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -4443,21 +4019,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>readHistory</t>
-        </is>
-      </c>
+      <c r="J47" s="3" t="inlineStr"/>
       <c r="K47" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L47" s="3" t="inlineStr">
-        <is>
-          <t>readHistory</t>
-        </is>
-      </c>
+      <c r="L47" s="3" t="inlineStr"/>
       <c r="M47" s="5" t="inlineStr"/>
       <c r="N47" s="5" t="inlineStr"/>
       <c r="O47" s="6" t="inlineStr">
@@ -4528,26 +4096,10 @@
           <t>probes/classification-crosspath.probe.test.ts</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>ImportHoldings</t>
-        </is>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K48" s="3" t="inlineStr">
-        <is>
-          <t>ImportHoldings</t>
-        </is>
-      </c>
-      <c r="L48" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" s="3" t="inlineStr"/>
+      <c r="L48" s="3" t="inlineStr"/>
       <c r="M48" s="5" t="inlineStr"/>
       <c r="N48" s="5" t="inlineStr"/>
       <c r="O48" s="6" t="inlineStr">
@@ -4620,26 +4172,10 @@
           <t>probes/classification-crosspath.probe.test.ts</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>ImportHoldings</t>
-        </is>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>ImportHoldings</t>
-        </is>
-      </c>
-      <c r="L49" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I49" s="3" t="inlineStr"/>
+      <c r="J49" s="3" t="inlineStr"/>
+      <c r="K49" s="3" t="inlineStr"/>
+      <c r="L49" s="3" t="inlineStr"/>
       <c r="M49" s="5" t="inlineStr"/>
       <c r="N49" s="5" t="inlineStr"/>
       <c r="O49" s="6" t="inlineStr">
@@ -4718,26 +4254,10 @@
           <t>probes/classification-crosspath.probe.test.ts</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>importHoldings</t>
-        </is>
-      </c>
-      <c r="K50" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L50" s="3" t="inlineStr">
-        <is>
-          <t>importHoldings</t>
-        </is>
-      </c>
+      <c r="I50" s="3" t="inlineStr"/>
+      <c r="J50" s="3" t="inlineStr"/>
+      <c r="K50" s="3" t="inlineStr"/>
+      <c r="L50" s="3" t="inlineStr"/>
       <c r="M50" s="5" t="inlineStr"/>
       <c r="N50" s="5" t="inlineStr"/>
       <c r="O50" s="6" t="inlineStr">
@@ -4813,21 +4333,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>totalGrossAnnual</t>
-        </is>
-      </c>
+      <c r="J51" s="3" t="inlineStr"/>
       <c r="K51" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L51" s="3" t="inlineStr">
-        <is>
-          <t>totalGrossAnnual</t>
-        </is>
-      </c>
+      <c r="L51" s="3" t="inlineStr"/>
       <c r="M51" s="5" t="inlineStr"/>
       <c r="N51" s="5" t="inlineStr"/>
       <c r="O51" s="6" t="inlineStr">
@@ -4904,21 +4416,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
+      <c r="J52" s="3" t="inlineStr"/>
       <c r="K52" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L52" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
+      <c r="L52" s="3" t="inlineStr"/>
       <c r="M52" s="5" t="inlineStr"/>
       <c r="N52" s="5" t="inlineStr"/>
       <c r="O52" s="6" t="inlineStr">
@@ -4994,21 +4498,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J53" s="3" t="inlineStr">
-        <is>
-          <t>rentalNetAnnual</t>
-        </is>
-      </c>
+      <c r="J53" s="3" t="inlineStr"/>
       <c r="K53" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L53" s="3" t="inlineStr">
-        <is>
-          <t>rentalNetAnnual</t>
-        </is>
-      </c>
+      <c r="L53" s="3" t="inlineStr"/>
       <c r="M53" s="5" t="inlineStr"/>
       <c r="N53" s="5" t="inlineStr"/>
       <c r="O53" s="6" t="inlineStr">
@@ -5084,21 +4580,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>rsuAnnual</t>
-        </is>
-      </c>
+      <c r="J54" s="3" t="inlineStr"/>
       <c r="K54" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L54" s="3" t="inlineStr">
-        <is>
-          <t>rsuAnnual</t>
-        </is>
-      </c>
+      <c r="L54" s="3" t="inlineStr"/>
       <c r="M54" s="5" t="inlineStr"/>
       <c r="N54" s="5" t="inlineStr"/>
       <c r="O54" s="6" t="inlineStr">
@@ -5176,21 +4664,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>taxOwed</t>
-        </is>
-      </c>
+      <c r="J55" s="3" t="inlineStr"/>
       <c r="K55" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L55" s="3" t="inlineStr">
-        <is>
-          <t>taxOwed</t>
-        </is>
-      </c>
+      <c r="L55" s="3" t="inlineStr"/>
       <c r="M55" s="5" t="inlineStr"/>
       <c r="N55" s="5" t="inlineStr"/>
       <c r="O55" s="6" t="inlineStr">
@@ -5268,21 +4748,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>taxOwedFor</t>
-        </is>
-      </c>
+      <c r="J56" s="3" t="inlineStr"/>
       <c r="K56" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L56" s="3" t="inlineStr">
-        <is>
-          <t>taxOwedFor</t>
-        </is>
-      </c>
+      <c r="L56" s="3" t="inlineStr"/>
       <c r="M56" s="5" t="inlineStr"/>
       <c r="N56" s="5" t="inlineStr"/>
       <c r="O56" s="6" t="inlineStr">
@@ -5361,21 +4833,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="J57" s="3" t="inlineStr"/>
       <c r="K57" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L57" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="L57" s="3" t="inlineStr"/>
       <c r="M57" s="5" t="inlineStr"/>
       <c r="N57" s="5" t="inlineStr"/>
       <c r="O57" s="6" t="inlineStr">
@@ -5422,26 +4886,10 @@
       <c r="F58" s="3" t="inlineStr"/>
       <c r="G58" s="3" t="inlineStr"/>
       <c r="H58" s="3" t="inlineStr"/>
-      <c r="I58" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K58" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="L58" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I58" s="3" t="inlineStr"/>
+      <c r="J58" s="3" t="inlineStr"/>
+      <c r="K58" s="3" t="inlineStr"/>
+      <c r="L58" s="3" t="inlineStr"/>
       <c r="M58" s="5" t="inlineStr"/>
       <c r="N58" s="5" t="inlineStr"/>
       <c r="O58" s="6" t="inlineStr">
@@ -5508,7 +4956,7 @@
       <c r="F59" s="3" t="inlineStr">
         <is>
           <t>The per-holding rows from PERFORMANCE_TABLE — each already carrying its value, its return and its benchmark. See that row for where each of those comes from.
-cash: the uninvested balance, after CASH_SLEEVE has removed the double-counted money-market funds.</t>
+cash: the uninvested balance, after UNINVESTED_CASH has removed the double-counted money-market funds.</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr"/>
@@ -5522,21 +4970,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J59" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="J59" s="3" t="inlineStr"/>
       <c r="K59" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L59" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="L59" s="3" t="inlineStr"/>
       <c r="M59" s="5" t="inlineStr"/>
       <c r="N59" s="5" t="inlineStr"/>
       <c r="O59" s="6" t="inlineStr">
@@ -5617,21 +5057,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="J60" s="3" t="inlineStr"/>
       <c r="K60" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L60" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="L60" s="3" t="inlineStr"/>
       <c r="M60" s="5" t="inlineStr"/>
       <c r="N60" s="5" t="inlineStr"/>
       <c r="O60" s="6" t="inlineStr">
@@ -5678,7 +5110,7 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>What should this holding be compared against?  Answers: a fund ticker — SPY for shares and funds, AGG for bonds and annuities, AOR (a 60/40 mix) for retirement wrappers, GLD for commodities, BTC for crypto, PSP for private equity, QAI for hedge funds. Anything unrecognised gets SPY.</t>
+          <t>What should this holding be compared against?  Answers: a fund ticker — SPY for shares and funds, AGG for bonds and annuities, AOR (a 60/40 mix) for retirement accounts, GLD for commodities, BTC for crypto, PSP for private equity, QAI for hedge funds. Anything unrecognised gets SPY.</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -5708,21 +5140,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>buildPerformance</t>
-        </is>
-      </c>
+      <c r="J61" s="3" t="inlineStr"/>
       <c r="K61" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L61" s="3" t="inlineStr">
-        <is>
-          <t>buildPerformance</t>
-        </is>
-      </c>
+      <c r="L61" s="3" t="inlineStr"/>
       <c r="M61" s="5" t="inlineStr"/>
       <c r="N61" s="5" t="inlineStr"/>
       <c r="O61" s="6" t="inlineStr">
@@ -6153,21 +5577,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>lookBack</t>
-        </is>
-      </c>
+      <c r="J66" s="3" t="inlineStr"/>
       <c r="K66" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L66" s="3" t="inlineStr">
-        <is>
-          <t>lookBack</t>
-        </is>
-      </c>
+      <c r="L66" s="3" t="inlineStr"/>
       <c r="M66" s="5" t="inlineStr"/>
       <c r="N66" s="5" t="inlineStr"/>
       <c r="O66" s="6" t="inlineStr">
@@ -6247,21 +5663,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>moneyWeightedReturn</t>
-        </is>
-      </c>
+      <c r="J67" s="3" t="inlineStr"/>
       <c r="K67" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L67" s="3" t="inlineStr">
-        <is>
-          <t>moneyWeightedReturn</t>
-        </is>
-      </c>
+      <c r="L67" s="3" t="inlineStr"/>
       <c r="M67" s="5" t="inlineStr"/>
       <c r="N67" s="5" t="inlineStr"/>
       <c r="O67" s="6" t="inlineStr">
@@ -6337,21 +5745,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="J68" s="3" t="inlineStr"/>
       <c r="K68" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L68" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="L68" s="3" t="inlineStr"/>
       <c r="M68" s="5" t="inlineStr"/>
       <c r="N68" s="5" t="inlineStr"/>
       <c r="O68" s="6" t="inlineStr">
@@ -6514,21 +5914,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="J70" s="3" t="inlineStr"/>
       <c r="K70" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L70" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="L70" s="3" t="inlineStr"/>
       <c r="M70" s="5" t="inlineStr"/>
       <c r="N70" s="5" t="inlineStr"/>
       <c r="O70" s="6" t="inlineStr">
@@ -6609,21 +6001,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="J71" s="3" t="inlineStr"/>
       <c r="K71" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L71" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="L71" s="3" t="inlineStr"/>
       <c r="M71" s="5" t="inlineStr"/>
       <c r="N71" s="5" t="inlineStr"/>
       <c r="O71" s="6" t="inlineStr">
@@ -6705,21 +6089,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="J72" s="3" t="inlineStr"/>
       <c r="K72" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L72" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="L72" s="3" t="inlineStr"/>
       <c r="M72" s="5" t="inlineStr"/>
       <c r="N72" s="5" t="inlineStr"/>
       <c r="O72" s="6" t="inlineStr">
@@ -6884,21 +6260,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="J74" s="3" t="inlineStr"/>
       <c r="K74" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L74" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="L74" s="3" t="inlineStr"/>
       <c r="M74" s="5" t="inlineStr"/>
       <c r="N74" s="5" t="inlineStr"/>
       <c r="O74" s="6" t="inlineStr">
@@ -7069,21 +6437,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>moneyWeightedReturn</t>
-        </is>
-      </c>
+      <c r="J76" s="3" t="inlineStr"/>
       <c r="K76" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L76" s="3" t="inlineStr">
-        <is>
-          <t>moneyWeightedReturn</t>
-        </is>
-      </c>
+      <c r="L76" s="3" t="inlineStr"/>
       <c r="M76" s="5" t="inlineStr"/>
       <c r="N76" s="5" t="inlineStr"/>
       <c r="O76" s="6" t="inlineStr">
@@ -7130,26 +6490,10 @@
       <c r="F77" s="3" t="inlineStr"/>
       <c r="G77" s="3" t="inlineStr"/>
       <c r="H77" s="3" t="inlineStr"/>
-      <c r="I77" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J77" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K77" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="L77" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I77" s="3" t="inlineStr"/>
+      <c r="J77" s="3" t="inlineStr"/>
+      <c r="K77" s="3" t="inlineStr"/>
+      <c r="L77" s="3" t="inlineStr"/>
       <c r="M77" s="5" t="inlineStr"/>
       <c r="N77" s="5" t="inlineStr"/>
       <c r="O77" s="6" t="inlineStr">
@@ -7196,26 +6540,10 @@
       <c r="F78" s="3" t="inlineStr"/>
       <c r="G78" s="3" t="inlineStr"/>
       <c r="H78" s="3" t="inlineStr"/>
-      <c r="I78" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K78" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="L78" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I78" s="3" t="inlineStr"/>
+      <c r="J78" s="3" t="inlineStr"/>
+      <c r="K78" s="3" t="inlineStr"/>
+      <c r="L78" s="3" t="inlineStr"/>
       <c r="M78" s="5" t="inlineStr"/>
       <c r="N78" s="5" t="inlineStr"/>
       <c r="O78" s="6" t="inlineStr">
@@ -7262,26 +6590,10 @@
       <c r="F79" s="3" t="inlineStr"/>
       <c r="G79" s="3" t="inlineStr"/>
       <c r="H79" s="3" t="inlineStr"/>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K79" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="L79" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I79" s="3" t="inlineStr"/>
+      <c r="J79" s="3" t="inlineStr"/>
+      <c r="K79" s="3" t="inlineStr"/>
+      <c r="L79" s="3" t="inlineStr"/>
       <c r="M79" s="5" t="inlineStr"/>
       <c r="N79" s="5" t="inlineStr"/>
       <c r="O79" s="6" t="inlineStr">
@@ -7328,26 +6640,10 @@
       <c r="F80" s="3" t="inlineStr"/>
       <c r="G80" s="3" t="inlineStr"/>
       <c r="H80" s="3" t="inlineStr"/>
-      <c r="I80" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K80" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="L80" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I80" s="3" t="inlineStr"/>
+      <c r="J80" s="3" t="inlineStr"/>
+      <c r="K80" s="3" t="inlineStr"/>
+      <c r="L80" s="3" t="inlineStr"/>
       <c r="M80" s="5" t="inlineStr"/>
       <c r="N80" s="5" t="inlineStr"/>
       <c r="O80" s="6" t="inlineStr">
@@ -7394,26 +6690,10 @@
       <c r="F81" s="3" t="inlineStr"/>
       <c r="G81" s="3" t="inlineStr"/>
       <c r="H81" s="3" t="inlineStr"/>
-      <c r="I81" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K81" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="L81" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I81" s="3" t="inlineStr"/>
+      <c r="J81" s="3" t="inlineStr"/>
+      <c r="K81" s="3" t="inlineStr"/>
+      <c r="L81" s="3" t="inlineStr"/>
       <c r="M81" s="5" t="inlineStr"/>
       <c r="N81" s="5" t="inlineStr"/>
       <c r="O81" s="6" t="inlineStr">
@@ -7489,21 +6769,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>retirementSpendMonthly</t>
-        </is>
-      </c>
+      <c r="J82" s="3" t="inlineStr"/>
       <c r="K82" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L82" s="3" t="inlineStr">
-        <is>
-          <t>retirementSpendMonthly</t>
-        </is>
-      </c>
+      <c r="L82" s="3" t="inlineStr"/>
       <c r="M82" s="5" t="inlineStr"/>
       <c r="N82" s="5" t="inlineStr"/>
       <c r="O82" s="6" t="inlineStr">
@@ -7579,21 +6851,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J83" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="J83" s="3" t="inlineStr"/>
       <c r="K83" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L83" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="L83" s="3" t="inlineStr"/>
       <c r="M83" s="5" t="inlineStr"/>
       <c r="N83" s="5" t="inlineStr"/>
       <c r="O83" s="6" t="inlineStr">
@@ -7640,21 +6904,18 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>What are the odds this money lasts?  Answer: a percentage, plus the projected pot at retirement, what is needed, the gap, and what extra saving would close it.</t>
+          <t>Will my money last?
+Answer: the percentage of outcomes where it does — plus what the pot is likely to be worth when you retire, what you would need, the gap, and what extra saving would close it.</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Run the plan 400 times. Each run walks year by year:
-BEFORE RETIREMENT — the pot grows at a randomly drawn return each year (average and swing as given), plus what goes in; big one-off costs and any payments still running come out.
-AFTER RETIREMENT — spending comes out, guaranteed income goes in, and the pot keeps growing on what is left. A run SUCCEEDS if the money outlasts the horizon.
-The odds are the share of runs that succeeded.
-WHAT IS INFLATED AND WHAT IS NOT — the rule most easily got wrong:
-• SPENDING is inflated to the year it happens. Today's dollars are not tomorrow's.
-• A BIG ONE-OFF COST is inflated to its own year, and leaves the pot in that year — a roof in 2030 is paid in 2030. Costs already past, or beyond the horizon, are not simulated at all.
-• A PAYMENT THAT STOPS IS CHARGED FLAT AND NEVER INFLATED. A fixed mortgage payment is the same number of dollars every year until it ends. Inflating it would overstate its cost every single year, and then stop overstating it at the end — the worst of both.
-• GUARANTEED INCOME can start LATER than retirement but never earlier: asking for it sooner is clamped to the retirement year.
-It is DETERMINISTIC — the same inputs give the same odds every time, because the randomness is seeded. Two people with the same plan see the same number, and so does the same person tomorrow.</t>
+          <t>WHY IT IS NOT ONE SUM. Nobody knows what markets will do. A plan that assumes exactly 6% every year for thirty years gives one confident answer that is certainly wrong. So instead the app plays out your life 400 times, giving each year a different random return — some good, some terrible, averaging out to what your mix of accounts would normally earn.
+EACH RUN GOES LIKE THIS. Start with what you have. Every year until you retire: the pot grows or shrinks by that year's random return, your saving goes in, and any big planned cost comes out. From retirement on: your spending comes out, your pension and Social Security go in, and whatever is left keeps growing. If the money outlasts you, that run worked.
+Do that 400 times and count. 340 worked out of 400 → 85%.
+WHAT 85% MEANS. Not "you will have 85% of what you need". It means that in 85 out of 100 possible futures, the money lasted — and in 15, it ran out. It is a measure of how much room for bad luck you have.
+THE ONE RULE THAT IS EASY TO GET WRONG. Your SPENDING rises with inflation — groceries in 2040 cost more than groceries today. But your MORTGAGE PAYMENT DOES NOT. A fixed payment is the same dollars every year until the loan ends. Treating it like groceries would overstate what it costs you every single year, and then stop overstating it the moment it ends.
+It is repeatable: the same plan always gives the same percentage, today and tomorrow.</t>
         </is>
       </c>
       <c r="E84" s="3" t="inlineStr">
@@ -7687,21 +6948,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>selectWillItLast</t>
-        </is>
-      </c>
+      <c r="J84" s="3" t="inlineStr"/>
       <c r="K84" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L84" s="3" t="inlineStr">
-        <is>
-          <t>selectWillItLast</t>
-        </is>
-      </c>
+      <c r="L84" s="3" t="inlineStr"/>
       <c r="M84" s="5" t="inlineStr"/>
       <c r="N84" s="5" t="inlineStr"/>
       <c r="O84" s="6" t="inlineStr">
@@ -7781,21 +7034,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>ssBenefitAtClaimAge</t>
-        </is>
-      </c>
+      <c r="J85" s="3" t="inlineStr"/>
       <c r="K85" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L85" s="3" t="inlineStr">
-        <is>
-          <t>ssBenefitAtClaimAge</t>
-        </is>
-      </c>
+      <c r="L85" s="3" t="inlineStr"/>
       <c r="M85" s="5" t="inlineStr"/>
       <c r="N85" s="5" t="inlineStr"/>
       <c r="O85" s="6" t="inlineStr">
@@ -7842,26 +7087,10 @@
       <c r="F86" s="3" t="inlineStr"/>
       <c r="G86" s="3" t="inlineStr"/>
       <c r="H86" s="3" t="inlineStr"/>
-      <c r="I86" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
-      <c r="K86" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L86" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
+      <c r="I86" s="3" t="inlineStr"/>
+      <c r="J86" s="3" t="inlineStr"/>
+      <c r="K86" s="3" t="inlineStr"/>
+      <c r="L86" s="3" t="inlineStr"/>
       <c r="M86" s="5" t="inlineStr"/>
       <c r="N86" s="5" t="inlineStr"/>
       <c r="O86" s="6" t="inlineStr">
@@ -7908,26 +7137,10 @@
       <c r="F87" s="3" t="inlineStr"/>
       <c r="G87" s="3" t="inlineStr"/>
       <c r="H87" s="3" t="inlineStr"/>
-      <c r="I87" s="3" t="inlineStr">
-        <is>
-          <t>AccountDetail, Performance</t>
-        </is>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K87" s="3" t="inlineStr">
-        <is>
-          <t>AccountDetail, Performance</t>
-        </is>
-      </c>
-      <c r="L87" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I87" s="3" t="inlineStr"/>
+      <c r="J87" s="3" t="inlineStr"/>
+      <c r="K87" s="3" t="inlineStr"/>
+      <c r="L87" s="3" t="inlineStr"/>
       <c r="M87" s="5" t="inlineStr"/>
       <c r="N87" s="5" t="inlineStr"/>
       <c r="O87" s="6" t="inlineStr">
@@ -7974,26 +7187,10 @@
       <c r="F88" s="3" t="inlineStr"/>
       <c r="G88" s="3" t="inlineStr"/>
       <c r="H88" s="3" t="inlineStr"/>
-      <c r="I88" s="3" t="inlineStr">
-        <is>
-          <t>AccountDetail, Performance</t>
-        </is>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K88" s="3" t="inlineStr">
-        <is>
-          <t>AccountDetail, Performance</t>
-        </is>
-      </c>
-      <c r="L88" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I88" s="3" t="inlineStr"/>
+      <c r="J88" s="3" t="inlineStr"/>
+      <c r="K88" s="3" t="inlineStr"/>
+      <c r="L88" s="3" t="inlineStr"/>
       <c r="M88" s="5" t="inlineStr"/>
       <c r="N88" s="5" t="inlineStr"/>
       <c r="O88" s="6" t="inlineStr">
@@ -8040,26 +7237,10 @@
       <c r="F89" s="3" t="inlineStr"/>
       <c r="G89" s="3" t="inlineStr"/>
       <c r="H89" s="3" t="inlineStr"/>
-      <c r="I89" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K89" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L89" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I89" s="3" t="inlineStr"/>
+      <c r="J89" s="3" t="inlineStr"/>
+      <c r="K89" s="3" t="inlineStr"/>
+      <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="5" t="inlineStr"/>
       <c r="N89" s="5" t="inlineStr"/>
       <c r="O89" s="6" t="inlineStr">
@@ -8094,57 +7275,21 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="inlineStr">
-        <is>
-          <t>INGEST_DEDUPE</t>
-        </is>
-      </c>
+      <c r="A90" s="3" t="inlineStr"/>
       <c r="B90" s="4" t="inlineStr">
         <is>
           <t>dedupeActivities</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>Which of these activities are new since the last sync?  Answer: the new ones, plus the updated set of keys already seen.</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>Build a key for each incoming activity; keep only those whose key has not been seen before; add the kept keys to the seen set.
-The seen set PERSISTS ACROSS SYNCS — it is stored, not rebuilt each time. Deduping only within one batch would let every past activity re-import on the next connection.</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>our account id → accountId
-the new activities → incoming
-keys already seen → seenKeys</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="inlineStr">
-        <is>
-          <t>The broker feed. SnapTrade activities endpoint, one row per event, with `type` carrying the broker's own word for what happened (BUY, SELL, CONTRIBUTION, WITHDRAWAL, DIVIDEND, INTEREST, TRANSFER, OPTIONEXPIRATION…). Every institution uses its own vocabulary; this is the table that turns their word into ours.
-seenKeys: stored by the app between syncs (snaptradeSeenKeys). Our own record, not the broker's.</t>
-        </is>
-      </c>
-      <c r="G90" s="3" t="inlineStr">
-        <is>
-          <t>Calculation Module code/probes/broken-family.probe.test.ts</t>
-        </is>
-      </c>
+      <c r="C90" s="3" t="inlineStr"/>
+      <c r="D90" s="3" t="inlineStr"/>
+      <c r="E90" s="3" t="inlineStr"/>
+      <c r="F90" s="3" t="inlineStr"/>
+      <c r="G90" s="3" t="inlineStr"/>
       <c r="H90" s="3" t="inlineStr"/>
-      <c r="I90" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
+      <c r="I90" s="3" t="inlineStr"/>
       <c r="J90" s="3" t="inlineStr"/>
-      <c r="K90" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="K90" s="3" t="inlineStr"/>
       <c r="L90" s="3" t="inlineStr"/>
       <c r="M90" s="5" t="inlineStr"/>
       <c r="N90" s="5" t="inlineStr"/>
@@ -8192,28 +7337,23 @@
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>Which of the seven classes does a whole ACCOUNT belong to?
-The answer is one of: Cash · Bonds &amp; CDs · Stocks / Funds · Alternatives · Real estate · Personal property · Unclassified (we were never told what is inside it).</t>
+          <t>What kind of thing is this account — cash, a bond, shares, or something else?
+Answer: one of seven. Cash · Bonds &amp; CDs · Stocks / Funds · Alternatives · Real estate · Personal property · Unclassified (we were never told what is inside it).</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>The first rule that matches wins. Read top to bottom against a real account:
-1. A class was set by hand, or written by the file importer → use it. A person's own answer is never overridden.
-2. Otherwise read the NAME:
-   • contains SWEEP or SETTLEMENT → Cash
-   • contains MONEY MARKET / MMKT / MMF, or IS one of 17 known money-market tickers (VMFXX VMRXX VUSXX VMSXX SPAXX FDRXX FZFXX FZDXX SPRXX SWVXX SNVXX SNSXX SWGXX TTTXX MVRXX GOFXX FGXXX) → Stocks / Funds
-   • contains CD / CERTIFICATE OF DEPOSIT / T-BILL / TREASURY BILL → Bonds &amp; CDs
-3. Otherwise, if it carries a maturity date → Bonds &amp; CDs (that is what a maturity means)
-4. Otherwise read the account TYPE picked on Add account:
-   Checking · Savings · High-yield savings · Cash management → Cash
-   Money market → Stocks / Funds   |   CD · Fixed income → Bonds &amp; CDs
-   Stocks &amp; ETFs → Stocks / Funds
-   Private equity · Hedge funds · Commodities · Crypto · Annuities · Options · Other → Alternatives
-   Home → Real estate   |   Vehicle → Personal property
-5. Otherwise, if holdings are listed inside it → Stocks / Funds
-6. Otherwise, a cash wrapper → Cash; a property wrapper → Real estate
-7. Otherwise → Unclassified. NOT "stocks" — we do not guess what is in a 401(k) we cannot see.</t>
+          <t>WHY IT MATTERS BEFORE HOW IT WORKS. This one answer decides which total your money lands in, which colour it is on the chart, what return your plan assumes for it, and whether its income gets counted. Get it wrong and every number above it is wrong, quietly.
+THE RULES, IN ORDER — the first one that fits wins.
+1. DID YOU TELL US? If you set the type yourself, that is the answer. We never overrule you.
+2. WHAT IS IT CALLED? The name is real evidence, because institutions put the truth in the name even when their own labels are wrong.
+   • "sweep" or "settlement" → Cash. This is money sitting at your broker doing nothing. It is the only thing that counts as cash.
+   • "money market", or one of 17 known fund codes like VMFXX or SPAXX → Stocks / Funds. It sounds like cash and is not: it pays dividends, and if we filed it as cash those dividends would vanish from your return.
+   • "CD", "certificate of deposit", "T-bill", "treasury bill" → Bonds &amp; CDs.
+3. DOES IT HAVE AN END DATE? Anything with a maturity date is a bond. That is what a maturity means: a date on which you get your money back.
+4. WHAT DID YOU CALL IT WHEN YOU ADDED IT? Checking, savings, high-yield savings → Cash. CD or fixed income → Bonds &amp; CDs. Crypto, commodities, options, private equity, annuities → Alternatives. Home → Real estate. Car → Personal property.
+5. ARE THERE HOLDINGS INSIDE IT? Then it is Stocks / Funds.
+6. STILL NOTHING? Unclassified — NOT "shares". If you have a 401(k) and we cannot see inside it, the honest answer is that we do not know what is in it. Guessing "shares" would put a number in your plan that nobody chose.</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
@@ -8223,22 +7363,22 @@
 maturity → maturity_date
 account type → kind
 holdings inside → positions
-wrapper → tax_bucket</t>
+how it is taxed → tax_bucket</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
           <t>An explicit class on the account: either chosen by the person on the account screen, or set by the file importer when it recognised the holding (classifyHolding writes it).
-The account or holding NAME. Broker: symbol.description in the positions payload, else the account nickname. File: the name column, found by header pattern — Description / Security / Investment Name / Fund / Holding / Instrument. Typed: the Name box on Add account.
+The account or holding NAME. Broker: symbol.description in the positions data, else the account nickname. File: the name column, found by header pattern — Description / Security / Investment Name / Fund / Holding / Instrument. Typed: the Name box on Add account.
 maturity_date: typed on the bond form, or parsed out of the description text.
 The account TYPE, picked by the person from the list on Add account (Checking, Savings, High-yield savings, Money market, CD, Stocks &amp; ETFs, Fixed income, Crypto, Options, Home, Vehicle…). Never sent by an institution — a connected account is given a type at connect time.
 positions: the holdings list — from the broker feed, an uploaded file, or added by hand.
-tax_bucket — set from the wrapper chosen on Add account (Taxable / 401(k) / Traditional IRA / Roth / HSA → TAXABLE, PRE_TAX, ROTH, CASH, PROPERTY). Never sent by an institution.</t>
+tax_bucket — set from the tax type chosen on Add account (Taxable / 401(k) / Traditional IRA / Roth / HSA → TAXABLE, PRE_TAX, ROTH, CASH, PROPERTY). Never sent by an institution.</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>THE ORDER IS THE RULE. A person's own answer is never overridden. A wrapper whose contents are unknown becomes "mixed", never pretended to be stocks, so the allocation stays honest.</t>
+          <t>THE ORDER IS THE RULE. A person's own answer is never overridden. A tax type whose contents are unknown becomes "mixed", never pretended to be stocks, so the allocation stays honest.</t>
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr">
@@ -8304,26 +7444,10 @@
       <c r="F92" s="3" t="inlineStr"/>
       <c r="G92" s="3" t="inlineStr"/>
       <c r="H92" s="3" t="inlineStr"/>
-      <c r="I92" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>resolveNetWorthRows</t>
-        </is>
-      </c>
-      <c r="K92" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L92" s="3" t="inlineStr">
-        <is>
-          <t>resolveNetWorthRows</t>
-        </is>
-      </c>
+      <c r="I92" s="3" t="inlineStr"/>
+      <c r="J92" s="3" t="inlineStr"/>
+      <c r="K92" s="3" t="inlineStr"/>
+      <c r="L92" s="3" t="inlineStr"/>
       <c r="M92" s="5" t="inlineStr"/>
       <c r="N92" s="5" t="inlineStr"/>
       <c r="O92" s="6" t="inlineStr">
@@ -8555,26 +7679,10 @@
       <c r="F95" s="3" t="inlineStr"/>
       <c r="G95" s="3" t="inlineStr"/>
       <c r="H95" s="3" t="inlineStr"/>
-      <c r="I95" s="3" t="inlineStr">
-        <is>
-          <t>Itemize</t>
-        </is>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>buildItemizedAccounts</t>
-        </is>
-      </c>
-      <c r="K95" s="3" t="inlineStr">
-        <is>
-          <t>Itemize</t>
-        </is>
-      </c>
-      <c r="L95" s="3" t="inlineStr">
-        <is>
-          <t>buildItemizedAccounts</t>
-        </is>
-      </c>
+      <c r="I95" s="3" t="inlineStr"/>
+      <c r="J95" s="3" t="inlineStr"/>
+      <c r="K95" s="3" t="inlineStr"/>
+      <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="5" t="inlineStr"/>
       <c r="N95" s="5" t="inlineStr"/>
       <c r="O95" s="6" t="inlineStr">
@@ -8801,26 +7909,10 @@
       <c r="F98" s="3" t="inlineStr"/>
       <c r="G98" s="3" t="inlineStr"/>
       <c r="H98" s="3" t="inlineStr"/>
-      <c r="I98" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K98" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="L98" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I98" s="3" t="inlineStr"/>
+      <c r="J98" s="3" t="inlineStr"/>
+      <c r="K98" s="3" t="inlineStr"/>
+      <c r="L98" s="3" t="inlineStr"/>
       <c r="M98" s="5" t="inlineStr"/>
       <c r="N98" s="5" t="inlineStr"/>
       <c r="O98" s="6" t="inlineStr">
@@ -8867,26 +7959,10 @@
       <c r="F99" s="3" t="inlineStr"/>
       <c r="G99" s="3" t="inlineStr"/>
       <c r="H99" s="3" t="inlineStr"/>
-      <c r="I99" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>resolveNetWorthRows</t>
-        </is>
-      </c>
-      <c r="K99" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L99" s="3" t="inlineStr">
-        <is>
-          <t>resolveNetWorthRows</t>
-        </is>
-      </c>
+      <c r="I99" s="3" t="inlineStr"/>
+      <c r="J99" s="3" t="inlineStr"/>
+      <c r="K99" s="3" t="inlineStr"/>
+      <c r="L99" s="3" t="inlineStr"/>
       <c r="M99" s="5" t="inlineStr"/>
       <c r="N99" s="5" t="inlineStr"/>
       <c r="O99" s="6" t="inlineStr">
@@ -9049,21 +8125,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>trendPoints</t>
-        </is>
-      </c>
+      <c r="J101" s="3" t="inlineStr"/>
       <c r="K101" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L101" s="3" t="inlineStr">
-        <is>
-          <t>trendPoints</t>
-        </is>
-      </c>
+      <c r="L101" s="3" t="inlineStr"/>
       <c r="M101" s="5" t="inlineStr"/>
       <c r="N101" s="5" t="inlineStr"/>
       <c r="O101" s="6" t="inlineStr">
@@ -9252,21 +8320,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>monthlyContributionsFromOnboarding</t>
-        </is>
-      </c>
+      <c r="J103" s="3" t="inlineStr"/>
       <c r="K103" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L103" s="3" t="inlineStr">
-        <is>
-          <t>monthlyContributionsFromOnboarding</t>
-        </is>
-      </c>
+      <c r="L103" s="3" t="inlineStr"/>
       <c r="M103" s="5" t="inlineStr"/>
       <c r="N103" s="5" t="inlineStr"/>
       <c r="O103" s="6" t="inlineStr">
@@ -9346,21 +8406,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>rsuAnnual</t>
-        </is>
-      </c>
+      <c r="J104" s="3" t="inlineStr"/>
       <c r="K104" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L104" s="3" t="inlineStr">
-        <is>
-          <t>rsuAnnual</t>
-        </is>
-      </c>
+      <c r="L104" s="3" t="inlineStr"/>
       <c r="M104" s="5" t="inlineStr"/>
       <c r="N104" s="5" t="inlineStr"/>
       <c r="O104" s="6" t="inlineStr">
@@ -9437,21 +8489,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>totalGrossAnnual</t>
-        </is>
-      </c>
+      <c r="J105" s="3" t="inlineStr"/>
       <c r="K105" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L105" s="3" t="inlineStr">
-        <is>
-          <t>totalGrossAnnual</t>
-        </is>
-      </c>
+      <c r="L105" s="3" t="inlineStr"/>
       <c r="M105" s="5" t="inlineStr"/>
       <c r="N105" s="5" t="inlineStr"/>
       <c r="O105" s="6" t="inlineStr">
@@ -9528,21 +8572,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>currentRetirementIncomeMonthly, willItLastInputs</t>
-        </is>
-      </c>
+      <c r="J106" s="3" t="inlineStr"/>
       <c r="K106" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L106" s="3" t="inlineStr">
-        <is>
-          <t>currentRetirementIncomeMonthly, willItLastInputs</t>
-        </is>
-      </c>
+      <c r="L106" s="3" t="inlineStr"/>
       <c r="M106" s="5" t="inlineStr"/>
       <c r="N106" s="5" t="inlineStr"/>
       <c r="O106" s="6" t="inlineStr">
@@ -9618,21 +8654,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
+      <c r="J107" s="3" t="inlineStr"/>
       <c r="K107" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L107" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
+      <c r="L107" s="3" t="inlineStr"/>
       <c r="M107" s="5" t="inlineStr"/>
       <c r="N107" s="5" t="inlineStr"/>
       <c r="O107" s="6" t="inlineStr">
@@ -9710,21 +8738,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>grossFromNet</t>
-        </is>
-      </c>
+      <c r="J108" s="3" t="inlineStr"/>
       <c r="K108" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L108" s="3" t="inlineStr">
-        <is>
-          <t>grossFromNet</t>
-        </is>
-      </c>
+      <c r="L108" s="3" t="inlineStr"/>
       <c r="M108" s="5" t="inlineStr"/>
       <c r="N108" s="5" t="inlineStr"/>
       <c r="O108" s="6" t="inlineStr">
@@ -9804,21 +8824,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>effectiveRateOnGrossFor</t>
-        </is>
-      </c>
+      <c r="J109" s="3" t="inlineStr"/>
       <c r="K109" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L109" s="3" t="inlineStr">
-        <is>
-          <t>effectiveRateOnGrossFor</t>
-        </is>
-      </c>
+      <c r="L109" s="3" t="inlineStr"/>
       <c r="M109" s="5" t="inlineStr"/>
       <c r="N109" s="5" t="inlineStr"/>
       <c r="O109" s="6" t="inlineStr">
@@ -9900,21 +8912,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="J110" s="3" t="inlineStr"/>
       <c r="K110" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L110" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="L110" s="3" t="inlineStr"/>
       <c r="M110" s="5" t="inlineStr"/>
       <c r="N110" s="5" t="inlineStr"/>
       <c r="O110" s="6" t="inlineStr">
@@ -10050,20 +9054,21 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>What return have I actually earned, counting when I added money?
-Answers: a yearly rate — OR one of three plain refusals: no usable history · too short a period · no sensible answer exists.</t>
+          <t>Did my money actually grow, and by how much a year — counting the fact that I did not put it all in at once?
+Answer: a yearly percentage. Or one of three plain refusals: we do not have enough of your history · it has not been long enough to say · no sensible answer exists.</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Find the single yearly rate that makes all your dated flows, grown at that rate, equal what the accounts are worth today. Solved by repeated halving between −95% and +1000% a year, up to 100 passes — no guessing and the same answer every time.
-IT REFUSES IN FOUR WAYS, and the refusals are the feature:
-1. the history does not start in the ledger → "no usable history"
-2. nothing was ever put in → "no usable history"
-3. under 30 days → "too short". Annualising three days of movement produces a huge number that means nothing.
-4. no rate in that range fits → "no sensible answer".
-WHY IT DIFFERS FROM A PRICE RETURN: this one counts TIMING. The same money added later worked for less time, so the same ending value implies a higher yearly rate. That is the honest answer to "how did I do", and no price-based figure can see it.
-IT DEPENDS ENTIRELY ON THE LEDGER BEING RIGHT. Phantom deposits do not make it refuse — they make it answer confidently and wrongly, which is what happened on the Vanguard account.</t>
+          <t>WHY THIS EXISTS. Say you put in $10,000 five years ago, another $10,000 last month, and today you have $23,000. You are up $3,000. But up by what percentage? The first $10,000 had five years to work. The second had one month. Saying "I am up 15%" means nothing, because the two amounts were working for completely different lengths of time.
+This number answers it properly: the single yearly rate which, applied to each amount for exactly as long as that amount was actually invested, arrives at what you have today.
+HOW IT IS WORKED OUT. There is no formula that solves this in one go, so the app guesses and narrows down. Try 5% — do the deposits grow to $23,000? Too low. Try 20% — too high. Try 12.5%. Each guess halves the remaining range, and after a hundred rounds it lands on the rate that fits. The same inputs always give the same answer.
+WHEN IT REFUSES, AND WHY THAT IS RIGHT.
+1. Your account had money in it before our records start. We cannot know what you began with, so we say so instead of inventing a starting point.
+2. Nothing was ever paid in — there is nothing to measure growth against.
+3. Under 30 days. Stretching three days of movement into a yearly rate produces a huge number that means nothing.
+4. No rate between −95% and +1000% fits. Something is wrong with the history and we do not paper over it.
+THE CATCH. This is only as good as the record of your deposits and withdrawals. A deposit we wrongly think happened does not make it refuse — it makes it answer confidently and wrongly. That is exactly what happened on your Vanguard account.</t>
         </is>
       </c>
       <c r="E112" s="3" t="inlineStr">
@@ -10092,21 +9097,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="J112" s="3" t="inlineStr"/>
       <c r="K112" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L112" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="L112" s="3" t="inlineStr"/>
       <c r="M112" s="5" t="inlineStr"/>
       <c r="N112" s="5" t="inlineStr"/>
       <c r="O112" s="6" t="inlineStr">
@@ -10466,21 +9463,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>selectWillItLast, willItLastInputs</t>
-        </is>
-      </c>
+      <c r="J116" s="3" t="inlineStr"/>
       <c r="K116" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L116" s="3" t="inlineStr">
-        <is>
-          <t>selectWillItLast, willItLastInputs</t>
-        </is>
-      </c>
+      <c r="L116" s="3" t="inlineStr"/>
       <c r="M116" s="5" t="inlineStr"/>
       <c r="N116" s="5" t="inlineStr"/>
       <c r="O116" s="6" t="inlineStr">
@@ -10557,21 +9546,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
+      <c r="J117" s="3" t="inlineStr"/>
       <c r="K117" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L117" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
+      <c r="L117" s="3" t="inlineStr"/>
       <c r="M117" s="5" t="inlineStr"/>
       <c r="N117" s="5" t="inlineStr"/>
       <c r="O117" s="6" t="inlineStr">
@@ -10618,26 +9599,10 @@
       <c r="F118" s="3" t="inlineStr"/>
       <c r="G118" s="3" t="inlineStr"/>
       <c r="H118" s="3" t="inlineStr"/>
-      <c r="I118" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K118" s="3" t="inlineStr">
-        <is>
-          <t>Performance</t>
-        </is>
-      </c>
-      <c r="L118" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I118" s="3" t="inlineStr"/>
+      <c r="J118" s="3" t="inlineStr"/>
+      <c r="K118" s="3" t="inlineStr"/>
+      <c r="L118" s="3" t="inlineStr"/>
       <c r="M118" s="5" t="inlineStr"/>
       <c r="N118" s="5" t="inlineStr"/>
       <c r="O118" s="6" t="inlineStr">
@@ -10684,18 +9649,17 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>How does ONE connected account split across the classes it actually holds?
-Answer: a dollar figure for each of Cash · Bonds &amp; CDs · Stocks / Funds · Alternatives — adding up EXACTLY to the total the broker states. A typed or imported account returns nothing and stays whole.</t>
+          <t>This one brokerage account holds several different things — how much of it is each?
+Answer: a dollar amount for Cash, Bonds &amp; CDs, Stocks / Funds and Alternatives, adding up exactly to the total your broker states.</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
         <is>
-          <t>Start with the uninvested cash. Then place every holding by reading its NAME first — money-market funds to Stocks / Funds, CDs and T-bills to Bonds &amp; CDs — and only falling back to the broker's own tag when the name says nothing. Options go to Alternatives.
-Then compare the pieces with the broker's stated total, and place whatever is left over:
-• a SMALL POSITIVE leftover → CASH. It is money the broker's total includes but its holdings do not account for: settlement cash, a dividend just received, a pending trade.
-• a SMALL NEGATIVE leftover → the largest class. The priced holdings exceed the stated total, which is a pricing artifact rather than money; writing it into cash would show a negative cash balance, which reads worse than a rounding nudge.
-• a LARGE leftover → Unclassified, honestly.
-THE LEFTOVER RULE IS A FOUNDER FINDING ("why is cash added to CD and not cash?"). It used to go to the LARGEST class, so on a CD-heavy account uninvested money was counted as MORE CDs — overstating bonds and understating cash, both silently.</t>
+          <t>WHY IT EXISTS. Your Vanguard account is not one thing. It might hold a CD, a money-market fund, some shares, and a little uninvested cash. Showing it as one lump under a single heading would be wrong four ways at once.
+HOW IT SPLITS. Start with the uninvested cash. Then place each holding by reading its NAME first — a money-market fund goes with the shares, a CD goes with the bonds — and only fall back to the broker's own label when the name tells us nothing.
+THE LEFTOVER. Add the pieces up and they rarely match the broker's total to the penny. What to do with the difference matters more than it sounds.
+A WORKED EXAMPLE, AND IT IS YOUR OWN FINDING. Say the account totals $10,100 and holds one CD worth $10,000. There is $100 unaccounted for. The app used to add it to the biggest holding — so your $100 of spare cash was reported as MORE CD. You asked "why is cash added to CD and not cash?", and you were right: it is money sitting there, not another certificate you own. A small positive leftover is now cash.
+(If the pieces come to MORE than the broker's total, that is a pricing quirk rather than money, and it goes to the largest holding — putting it in cash would show you a negative cash balance, which reads worse than a rounding nudge.)</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
@@ -10709,7 +9673,7 @@
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>The connected account's payload: balance.total.amount (the broker's authoritative total), balances.cash, and positions[] each with symbol.raw_symbol, symbol.description, units and price. Option positions arrive on their own feed.</t>
+          <t>The connected account's the data they send: balance.total.amount (the broker's authoritative total), balances.cash, and positions[] each with symbol.raw_symbol, symbol.description, units and price. Option positions arrive on their own feed.</t>
         </is>
       </c>
       <c r="G119" s="3" t="inlineStr"/>
@@ -10723,21 +9687,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>assetAllocation, cashTotal</t>
-        </is>
-      </c>
+      <c r="J119" s="3" t="inlineStr"/>
       <c r="K119" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L119" s="3" t="inlineStr">
-        <is>
-          <t>assetAllocation, cashTotal</t>
-        </is>
-      </c>
+      <c r="L119" s="3" t="inlineStr"/>
       <c r="M119" s="5" t="inlineStr"/>
       <c r="N119" s="5" t="inlineStr"/>
       <c r="O119" s="6" t="inlineStr">
@@ -10784,26 +9740,10 @@
       <c r="F120" s="3" t="inlineStr"/>
       <c r="G120" s="3" t="inlineStr"/>
       <c r="H120" s="3" t="inlineStr"/>
-      <c r="I120" s="3" t="inlineStr">
-        <is>
-          <t>Itemize</t>
-        </is>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K120" s="3" t="inlineStr">
-        <is>
-          <t>Itemize</t>
-        </is>
-      </c>
-      <c r="L120" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I120" s="3" t="inlineStr"/>
+      <c r="J120" s="3" t="inlineStr"/>
+      <c r="K120" s="3" t="inlineStr"/>
+      <c r="L120" s="3" t="inlineStr"/>
       <c r="M120" s="5" t="inlineStr"/>
       <c r="N120" s="5" t="inlineStr"/>
       <c r="O120" s="6" t="inlineStr">
@@ -10838,67 +9778,21 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="inlineStr">
-        <is>
-          <t>EARMARK_DEFAULT</t>
-        </is>
-      </c>
+      <c r="A121" s="3" t="inlineStr"/>
       <c r="B121" s="4" t="inlineStr">
         <is>
           <t>earmarkDefault</t>
         </is>
       </c>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t>How much of this account counts toward retirement, before anyone changes it?  Answer: 0% or 100%.</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>FOUNDER RULE 2026-08-11 — everything you own counts, except the roof you live under and the car you drive:
-• a 529 → 0% (legally someone else's education, not a choice)
-• your PRIMARY home → 0%
-• your most valuable car → 0%
-• everything else, cash included → 100%
-A rental counts (you could sell it). A second car counts.</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="inlineStr">
-        <is>
-          <t>account type → kind
-class → assetClassOf
-home use → re_use
-the main car → primaryCarId</t>
-        </is>
-      </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>The account TYPE, picked by the person from the list on Add account (Checking, Savings, High-yield savings, Money market, CD, Stocks &amp; ETFs, Fixed income, Crypto, Options, Home, Vehicle…). Never sent by an institution — a connected account is given a type at connect time.
-re_use: picked on the property screen (primary / rental / second home / land), defaulting to primary — the cautious side.
-primaryCarId: computed by PRIMARY_CAR below.</t>
-        </is>
-      </c>
-      <c r="G121" s="3" t="inlineStr">
-        <is>
-          <t>Everything counts EXCEPT the home you live in, the car you drive and a 529. The default is only a default — a saved percentage always wins.</t>
-        </is>
-      </c>
-      <c r="H121" s="3" t="inlineStr">
-        <is>
-          <t>probes/assets-classification.probe.test.ts</t>
-        </is>
-      </c>
-      <c r="I121" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
+      <c r="C121" s="3" t="inlineStr"/>
+      <c r="D121" s="3" t="inlineStr"/>
+      <c r="E121" s="3" t="inlineStr"/>
+      <c r="F121" s="3" t="inlineStr"/>
+      <c r="G121" s="3" t="inlineStr"/>
+      <c r="H121" s="3" t="inlineStr"/>
+      <c r="I121" s="3" t="inlineStr"/>
       <c r="J121" s="3" t="inlineStr"/>
-      <c r="K121" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="K121" s="3" t="inlineStr"/>
       <c r="L121" s="3" t="inlineStr"/>
       <c r="M121" s="5" t="inlineStr"/>
       <c r="N121" s="5" t="inlineStr"/>
@@ -10963,14 +9857,14 @@
       <c r="F122" s="3" t="inlineStr">
         <is>
           <t>The account's balance. THREE doors, and the field differs by door:
-• CONNECTED BROKER — SnapTrade account payload, balance.total.amount
+• CONNECTED BROKER — SnapTrade account the data they send, balance.total.amount
 • FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
 • TYPED — the Balance box on Add account</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>Counts ACROSS wrappers, so a 401(k)'s stocks count. Excludes cash and real assets.</t>
+          <t>Counts ACROSS tax types, so a 401(k)'s stocks count. Excludes cash and real assets.</t>
         </is>
       </c>
       <c r="H122" s="3" t="inlineStr">
@@ -11123,26 +10017,10 @@
       <c r="F124" s="3" t="inlineStr"/>
       <c r="G124" s="3" t="inlineStr"/>
       <c r="H124" s="3" t="inlineStr"/>
-      <c r="I124" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
-      <c r="K124" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L124" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
+      <c r="I124" s="3" t="inlineStr"/>
+      <c r="J124" s="3" t="inlineStr"/>
+      <c r="K124" s="3" t="inlineStr"/>
+      <c r="L124" s="3" t="inlineStr"/>
       <c r="M124" s="5" t="inlineStr"/>
       <c r="N124" s="5" t="inlineStr"/>
       <c r="O124" s="6" t="inlineStr">
@@ -11206,7 +10084,7 @@
       <c r="F125" s="3" t="inlineStr">
         <is>
           <t>The account's balance. THREE doors, and the field differs by door:
-• CONNECTED BROKER — SnapTrade account payload, balance.total.amount
+• CONNECTED BROKER — SnapTrade account the data they send, balance.total.amount
 • FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
 • TYPED — the Balance box on Add account
 Vehicles are identified by the account type picked on Add account.</t>
@@ -11280,26 +10158,10 @@
       <c r="F126" s="3" t="inlineStr"/>
       <c r="G126" s="3" t="inlineStr"/>
       <c r="H126" s="3" t="inlineStr"/>
-      <c r="I126" s="3" t="inlineStr">
-        <is>
-          <t>AccountDetail</t>
-        </is>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K126" s="3" t="inlineStr">
-        <is>
-          <t>AccountDetail</t>
-        </is>
-      </c>
-      <c r="L126" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I126" s="3" t="inlineStr"/>
+      <c r="J126" s="3" t="inlineStr"/>
+      <c r="K126" s="3" t="inlineStr"/>
+      <c r="L126" s="3" t="inlineStr"/>
       <c r="M126" s="5" t="inlineStr"/>
       <c r="N126" s="5" t="inlineStr"/>
       <c r="O126" s="6" t="inlineStr">
@@ -11741,26 +10603,10 @@
           <t>probes/classification-crosspath.probe.test.ts</t>
         </is>
       </c>
-      <c r="I131" s="3" t="inlineStr">
-        <is>
-          <t>ImportHoldings</t>
-        </is>
-      </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K131" s="3" t="inlineStr">
-        <is>
-          <t>ImportHoldings</t>
-        </is>
-      </c>
-      <c r="L131" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I131" s="3" t="inlineStr"/>
+      <c r="J131" s="3" t="inlineStr"/>
+      <c r="K131" s="3" t="inlineStr"/>
+      <c r="L131" s="3" t="inlineStr"/>
       <c r="M131" s="5" t="inlineStr"/>
       <c r="N131" s="5" t="inlineStr"/>
       <c r="O131" s="6" t="inlineStr">
@@ -11838,21 +10684,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>resolveLens, totalGrossAnnual</t>
-        </is>
-      </c>
+      <c r="J132" s="3" t="inlineStr"/>
       <c r="K132" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L132" s="3" t="inlineStr">
-        <is>
-          <t>resolveLens, totalGrossAnnual</t>
-        </is>
-      </c>
+      <c r="L132" s="3" t="inlineStr"/>
       <c r="M132" s="5" t="inlineStr"/>
       <c r="N132" s="5" t="inlineStr"/>
       <c r="O132" s="6" t="inlineStr">
@@ -11930,21 +10768,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J133" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
+      <c r="J133" s="3" t="inlineStr"/>
       <c r="K133" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L133" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
+      <c r="L133" s="3" t="inlineStr"/>
       <c r="M133" s="5" t="inlineStr"/>
       <c r="N133" s="5" t="inlineStr"/>
       <c r="O133" s="6" t="inlineStr">
@@ -12117,21 +10947,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J135" s="3" t="inlineStr">
-        <is>
-          <t>totalGrossAnnual</t>
-        </is>
-      </c>
+      <c r="J135" s="3" t="inlineStr"/>
       <c r="K135" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L135" s="3" t="inlineStr">
-        <is>
-          <t>totalGrossAnnual</t>
-        </is>
-      </c>
+      <c r="L135" s="3" t="inlineStr"/>
       <c r="M135" s="5" t="inlineStr"/>
       <c r="N135" s="5" t="inlineStr"/>
       <c r="O135" s="6" t="inlineStr">
@@ -12266,26 +11088,10 @@
       <c r="F137" s="3" t="inlineStr"/>
       <c r="G137" s="3" t="inlineStr"/>
       <c r="H137" s="3" t="inlineStr"/>
-      <c r="I137" s="3" t="inlineStr">
-        <is>
-          <t>Performance, WhatIf</t>
-        </is>
-      </c>
-      <c r="J137" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K137" s="3" t="inlineStr">
-        <is>
-          <t>Performance, WhatIf</t>
-        </is>
-      </c>
-      <c r="L137" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I137" s="3" t="inlineStr"/>
+      <c r="J137" s="3" t="inlineStr"/>
+      <c r="K137" s="3" t="inlineStr"/>
+      <c r="L137" s="3" t="inlineStr"/>
       <c r="M137" s="5" t="inlineStr"/>
       <c r="N137" s="5" t="inlineStr"/>
       <c r="O137" s="6" t="inlineStr">
@@ -12351,7 +11157,7 @@
       <c r="F138" s="3" t="inlineStr">
         <is>
           <t>The account's balance. THREE doors, and the field differs by door:
-• CONNECTED BROKER — SnapTrade account payload, balance.total.amount
+• CONNECTED BROKER — SnapTrade account the data they send, balance.total.amount
 • FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
 • TYPED — the Balance box on Add account
 The class comes from ASSET_CLASS_OF_ACCOUNT (see that row).</t>
@@ -12442,7 +11248,7 @@
       <c r="F139" s="3" t="inlineStr">
         <is>
           <t>The account's balance. THREE doors, and the field differs by door:
-• CONNECTED BROKER — SnapTrade account payload, balance.total.amount
+• CONNECTED BROKER — SnapTrade account the data they send, balance.total.amount
 • FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
 • TYPED — the Balance box on Add account</t>
         </is>
@@ -12503,64 +11309,21 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="inlineStr">
-        <is>
-          <t>EARMARK_AMOUNT</t>
-        </is>
-      </c>
+      <c r="A140" s="3" t="inlineStr"/>
       <c r="B140" s="4" t="inlineStr">
         <is>
           <t>earmarkedAmount</t>
         </is>
       </c>
-      <c r="C140" s="3" t="inlineStr">
-        <is>
-          <t>How many dollars of this account count toward retirement?  Answer: a dollar figure.</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t>balance × (the saved percentage if there is one, otherwise the default above) ÷ 100.
-The saved percentage always beats the default, and is clamped to 0–100 so a typo cannot earmark three times an account.</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="inlineStr">
-        <is>
-          <t>money → balance
-saved share → retirement_pct
-fallback → EARMARK_DEFAULT</t>
-        </is>
-      </c>
-      <c r="F140" s="3" t="inlineStr">
-        <is>
-          <t>The account's balance. THREE doors, and the field differs by door:
-• CONNECTED BROKER — SnapTrade account payload, balance.total.amount
-• FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
-• TYPED — the Balance box on Add account
-retirement_pct: a slider on the Plan tab, per account. The person's own answer.</t>
-        </is>
-      </c>
-      <c r="G140" s="3" t="inlineStr">
-        <is>
-          <t>The saved percentage always beats the default, and is clamped to 0-100 so a bad value cannot exceed the balance or go negative.</t>
-        </is>
-      </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>probes/assets-classification.probe.test.ts</t>
-        </is>
-      </c>
-      <c r="I140" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
+      <c r="C140" s="3" t="inlineStr"/>
+      <c r="D140" s="3" t="inlineStr"/>
+      <c r="E140" s="3" t="inlineStr"/>
+      <c r="F140" s="3" t="inlineStr"/>
+      <c r="G140" s="3" t="inlineStr"/>
+      <c r="H140" s="3" t="inlineStr"/>
+      <c r="I140" s="3" t="inlineStr"/>
       <c r="J140" s="3" t="inlineStr"/>
-      <c r="K140" s="3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
+      <c r="K140" s="3" t="inlineStr"/>
       <c r="L140" s="3" t="inlineStr"/>
       <c r="M140" s="5" t="inlineStr"/>
       <c r="N140" s="5" t="inlineStr"/>
@@ -12613,7 +11376,7 @@
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Cash + investments — everything except the house and the car. Selling the roof you live under is not a plan, so physical assets are excluded by CLASS, not by wrapper.</t>
+          <t>Cash + investments — everything except the house and the car. Selling the roof you live under is not a plan, so physical assets are excluded by CLASS, not by tax type.</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
@@ -12625,7 +11388,7 @@
       <c r="F141" s="3" t="inlineStr">
         <is>
           <t>The account's balance. THREE doors, and the field differs by door:
-• CONNECTED BROKER — SnapTrade account payload, balance.total.amount
+• CONNECTED BROKER — SnapTrade account the data they send, balance.total.amount
 • FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
 • TYPED — the Balance box on Add account</t>
         </is>
@@ -12816,21 +11579,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J143" s="3" t="inlineStr">
-        <is>
-          <t>salaryActiveMonths, salaryAnnual</t>
-        </is>
-      </c>
+      <c r="J143" s="3" t="inlineStr"/>
       <c r="K143" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L143" s="3" t="inlineStr">
-        <is>
-          <t>salaryActiveMonths, salaryAnnual</t>
-        </is>
-      </c>
+      <c r="L143" s="3" t="inlineStr"/>
       <c r="M143" s="5" t="inlineStr"/>
       <c r="N143" s="5" t="inlineStr"/>
       <c r="O143" s="6" t="inlineStr">
@@ -12969,26 +11724,10 @@
       <c r="F145" s="3" t="inlineStr"/>
       <c r="G145" s="3" t="inlineStr"/>
       <c r="H145" s="3" t="inlineStr"/>
-      <c r="I145" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K145" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="L145" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I145" s="3" t="inlineStr"/>
+      <c r="J145" s="3" t="inlineStr"/>
+      <c r="K145" s="3" t="inlineStr"/>
+      <c r="L145" s="3" t="inlineStr"/>
       <c r="M145" s="5" t="inlineStr"/>
       <c r="N145" s="5" t="inlineStr"/>
       <c r="O145" s="6" t="inlineStr">
@@ -13053,7 +11792,7 @@
       <c r="F146" s="3" t="inlineStr">
         <is>
           <t>The account's balance. THREE doors, and the field differs by door:
-• CONNECTED BROKER — SnapTrade account payload, balance.total.amount
+• CONNECTED BROKER — SnapTrade account the data they send, balance.total.amount
 • FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
 • TYPED — the Balance box on Add account
 OUR OWN TABLE — ASSET_KINDS in src/domain/assets/index.ts. Not from any institution and not from the market: a hand-maintained list of account types, each with a bucket, a screen section and a long-run return. If a number here is wrong, every projection is wrong.</t>
@@ -13149,7 +11888,7 @@
       <c r="F147" s="3" t="inlineStr">
         <is>
           <t>The account's balance. THREE doors, and the field differs by door:
-• CONNECTED BROKER — SnapTrade account payload, balance.total.amount
+• CONNECTED BROKER — SnapTrade account the data they send, balance.total.amount
 • FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
 • TYPED — the Balance box on Add account
 OUR OWN TABLE — ASSET_KINDS in src/domain/assets/index.ts. Not from any institution and not from the market: a hand-maintained list of account types, each with a bucket, a screen section and a long-run return. If a number here is wrong, every projection is wrong.</t>
@@ -13223,26 +11962,10 @@
       <c r="F148" s="3" t="inlineStr"/>
       <c r="G148" s="3" t="inlineStr"/>
       <c r="H148" s="3" t="inlineStr"/>
-      <c r="I148" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
-      <c r="K148" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L148" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
+      <c r="I148" s="3" t="inlineStr"/>
+      <c r="J148" s="3" t="inlineStr"/>
+      <c r="K148" s="3" t="inlineStr"/>
+      <c r="L148" s="3" t="inlineStr"/>
       <c r="M148" s="5" t="inlineStr"/>
       <c r="N148" s="5" t="inlineStr"/>
       <c r="O148" s="6" t="inlineStr">
@@ -13294,17 +12017,17 @@
       </c>
       <c r="D149" s="3" t="inlineStr">
         <is>
-          <t>Add up the earmarked portion of every account. NOT net worth, and NOT total assets — the home and the main car are out at 0%, and debts are not subtracted here.</t>
+          <t>Add up the share counted toward retirement of every account. NOT net worth, and NOT total assets — the home and the main car are out at 0%, and debts are not subtracted here.</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>every account → accounts, via EARMARK_AMOUNT</t>
+          <t>every account → accounts, via RETIREMENT_SHARE_AMOUNT</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>Derived — see EARMARK_AMOUNT and EARMARK_DEFAULT for where each input comes from.</t>
+          <t>Derived — see RETIREMENT_SHARE_AMOUNT and RETIREMENT_SHARE_DEFAULT for where each input comes from.</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
@@ -13375,26 +12098,10 @@
       <c r="F150" s="3" t="inlineStr"/>
       <c r="G150" s="3" t="inlineStr"/>
       <c r="H150" s="3" t="inlineStr"/>
-      <c r="I150" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>buildDebtState</t>
-        </is>
-      </c>
-      <c r="K150" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L150" s="3" t="inlineStr">
-        <is>
-          <t>buildDebtState</t>
-        </is>
-      </c>
+      <c r="I150" s="3" t="inlineStr"/>
+      <c r="J150" s="3" t="inlineStr"/>
+      <c r="K150" s="3" t="inlineStr"/>
+      <c r="L150" s="3" t="inlineStr"/>
       <c r="M150" s="5" t="inlineStr"/>
       <c r="N150" s="5" t="inlineStr"/>
       <c r="O150" s="6" t="inlineStr">
@@ -13441,26 +12148,10 @@
       <c r="F151" s="3" t="inlineStr"/>
       <c r="G151" s="3" t="inlineStr"/>
       <c r="H151" s="3" t="inlineStr"/>
-      <c r="I151" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
-      <c r="K151" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L151" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
+      <c r="I151" s="3" t="inlineStr"/>
+      <c r="J151" s="3" t="inlineStr"/>
+      <c r="K151" s="3" t="inlineStr"/>
+      <c r="L151" s="3" t="inlineStr"/>
       <c r="M151" s="5" t="inlineStr"/>
       <c r="N151" s="5" t="inlineStr"/>
       <c r="O151" s="6" t="inlineStr">
@@ -13536,21 +12227,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>tipsAnnual</t>
-        </is>
-      </c>
+      <c r="J152" s="3" t="inlineStr"/>
       <c r="K152" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L152" s="3" t="inlineStr">
-        <is>
-          <t>tipsAnnual</t>
-        </is>
-      </c>
+      <c r="L152" s="3" t="inlineStr"/>
       <c r="M152" s="5" t="inlineStr"/>
       <c r="N152" s="5" t="inlineStr"/>
       <c r="O152" s="6" t="inlineStr">
@@ -13627,21 +12310,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J153" s="3" t="inlineStr">
-        <is>
-          <t>totalGrossAnnual</t>
-        </is>
-      </c>
+      <c r="J153" s="3" t="inlineStr"/>
       <c r="K153" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L153" s="3" t="inlineStr">
-        <is>
-          <t>totalGrossAnnual</t>
-        </is>
-      </c>
+      <c r="L153" s="3" t="inlineStr"/>
       <c r="M153" s="5" t="inlineStr"/>
       <c r="N153" s="5" t="inlineStr"/>
       <c r="O153" s="6" t="inlineStr">
@@ -13724,21 +12399,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="J154" s="3" t="inlineStr"/>
       <c r="K154" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L154" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="L154" s="3" t="inlineStr"/>
       <c r="M154" s="5" t="inlineStr"/>
       <c r="N154" s="5" t="inlineStr"/>
       <c r="O154" s="6" t="inlineStr">
@@ -13785,26 +12452,10 @@
       <c r="F155" s="3" t="inlineStr"/>
       <c r="G155" s="3" t="inlineStr"/>
       <c r="H155" s="3" t="inlineStr"/>
-      <c r="I155" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K155" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="L155" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I155" s="3" t="inlineStr"/>
+      <c r="J155" s="3" t="inlineStr"/>
+      <c r="K155" s="3" t="inlineStr"/>
+      <c r="L155" s="3" t="inlineStr"/>
       <c r="M155" s="5" t="inlineStr"/>
       <c r="N155" s="5" t="inlineStr"/>
       <c r="O155" s="6" t="inlineStr">
@@ -13881,21 +12532,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>totalGrossAnnual</t>
-        </is>
-      </c>
+      <c r="J156" s="3" t="inlineStr"/>
       <c r="K156" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L156" s="3" t="inlineStr">
-        <is>
-          <t>totalGrossAnnual</t>
-        </is>
-      </c>
+      <c r="L156" s="3" t="inlineStr"/>
       <c r="M156" s="5" t="inlineStr"/>
       <c r="N156" s="5" t="inlineStr"/>
       <c r="O156" s="6" t="inlineStr">
@@ -13942,26 +12585,10 @@
       <c r="F157" s="3" t="inlineStr"/>
       <c r="G157" s="3" t="inlineStr"/>
       <c r="H157" s="3" t="inlineStr"/>
-      <c r="I157" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K157" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="L157" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I157" s="3" t="inlineStr"/>
+      <c r="J157" s="3" t="inlineStr"/>
+      <c r="K157" s="3" t="inlineStr"/>
+      <c r="L157" s="3" t="inlineStr"/>
       <c r="M157" s="5" t="inlineStr"/>
       <c r="N157" s="5" t="inlineStr"/>
       <c r="O157" s="6" t="inlineStr">
@@ -14038,21 +12665,13 @@
           <t>CORRECT</t>
         </is>
       </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
+      <c r="J158" s="3" t="inlineStr"/>
       <c r="K158" s="3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L158" s="3" t="inlineStr">
-        <is>
-          <t>willItLastInputs</t>
-        </is>
-      </c>
+      <c r="L158" s="3" t="inlineStr"/>
       <c r="M158" s="5" t="inlineStr"/>
       <c r="N158" s="5" t="inlineStr"/>
       <c r="O158" s="6" t="inlineStr">
@@ -14099,26 +12718,10 @@
       <c r="F159" s="3" t="inlineStr"/>
       <c r="G159" s="3" t="inlineStr"/>
       <c r="H159" s="3" t="inlineStr"/>
-      <c r="I159" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth, WhatIf</t>
-        </is>
-      </c>
-      <c r="J159" s="3" t="inlineStr">
-        <is>
-          <t>selectWillItLast</t>
-        </is>
-      </c>
-      <c r="K159" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth, WhatIf</t>
-        </is>
-      </c>
-      <c r="L159" s="3" t="inlineStr">
-        <is>
-          <t>selectWillItLast</t>
-        </is>
-      </c>
+      <c r="I159" s="3" t="inlineStr"/>
+      <c r="J159" s="3" t="inlineStr"/>
+      <c r="K159" s="3" t="inlineStr"/>
+      <c r="L159" s="3" t="inlineStr"/>
       <c r="M159" s="5" t="inlineStr"/>
       <c r="N159" s="5" t="inlineStr"/>
       <c r="O159" s="6" t="inlineStr">
@@ -14165,26 +12768,10 @@
       <c r="F160" s="3" t="inlineStr"/>
       <c r="G160" s="3" t="inlineStr"/>
       <c r="H160" s="3" t="inlineStr"/>
-      <c r="I160" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K160" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth</t>
-        </is>
-      </c>
-      <c r="L160" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I160" s="3" t="inlineStr"/>
+      <c r="J160" s="3" t="inlineStr"/>
+      <c r="K160" s="3" t="inlineStr"/>
+      <c r="L160" s="3" t="inlineStr"/>
       <c r="M160" s="5" t="inlineStr"/>
       <c r="N160" s="5" t="inlineStr"/>
       <c r="O160" s="6" t="inlineStr">
@@ -14381,26 +12968,10 @@
       <c r="F3" s="3" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>AccountDetail, Itemize, LookBack, NetWorth</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>formatMoney, formatMoneyCents, moneyCompact</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>AccountDetail, Itemize, LookBack, NetWorth</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>formatMoney, formatMoneyCents, moneyCompact</t>
-        </is>
-      </c>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr"/>
       <c r="N3" s="5" t="inlineStr"/>
       <c r="O3" s="6" t="inlineStr">
@@ -14447,26 +13018,10 @@
       <c r="F4" s="3" t="inlineStr"/>
       <c r="G4" s="3" t="inlineStr"/>
       <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>HoldingDetail, Itemize, NetWorth, Performance</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>HoldingDetail, Itemize, NetWorth, Performance</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
       <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="6" t="inlineStr">
@@ -14513,26 +13068,10 @@
       <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="inlineStr"/>
       <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>ImportHoldings, Performance</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>ImportHoldings, Performance</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="5" t="inlineStr"/>
       <c r="N5" s="5" t="inlineStr"/>
       <c r="O5" s="6" t="inlineStr">
@@ -14579,26 +13118,10 @@
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth, Performance</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>NetWorth, Performance</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="I6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="6" t="inlineStr">
@@ -14645,26 +13168,10 @@
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>ImportHoldings</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>accountClassBreakdown, actualDebtPayment, allocation, annualCoupon, assetAllocation, buildAssetsState, buildDebtState, buildItemizedAccounts, buildNetWorth, capGains, capGainsTax, cashTotal, costBasis, earmarkedAmount, itemizeRemainder, itemizedTotal, lookBack, marketValue, minimumDebtService, normalizeSnapshot, planDoor, projectNestEgg, retirementEarmarkedValue, retirementSpendMonthly, salaryGrossByMonth, simulate, taxBucketSplit, trendPoints, unrealizedGain</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>ImportHoldings</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>accountClassBreakdown, actualDebtPayment, allocation, annualCoupon, assetAllocation, buildAssetsState, buildDebtState, buildItemizedAccounts, buildNetWorth, capGains, capGainsTax, cashTotal, costBasis, earmarkedAmount, itemizeRemainder, itemizedTotal, lookBack, marketValue, minimumDebtService, normalizeSnapshot, planDoor, projectNestEgg, retirementEarmarkedValue, retirementSpendMonthly, salaryGrossByMonth, simulate, taxBucketSplit, trendPoints, unrealizedGain</t>
-        </is>
-      </c>
+      <c r="I7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="5" t="inlineStr"/>
       <c r="N7" s="5" t="inlineStr"/>
       <c r="O7" s="6" t="inlineStr">
@@ -16652,12 +15159,12 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>The account id is first in the dedupe key. If a broker's internal account id changes between connections, every key changes and the whole history re-imports. Did the Vanguard account get disconnected and reconnected at any point?</t>
+          <t>The account id is first in the fingerprint that spots a repeat. If a broker's internal account id changes between connections, every key changes and the whole history re-imports. Did the Vanguard account get disconnected and reconnected at any point?</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>NOW PROVED AS A MECHANISM, not just suspected (probes/sync-identity.probe.test.ts). Our account id IS the broker's account id with 'st-' in front, and the key that stops an activity being recorded twice BEGINS with our account id. The probe runs the same 40 events twice: deduplicated correctly under one id, and ALL 40 come back as new under another. So a changed broker id re-imports the entire history as new money arriving. Everything else has been ruled out by running the code: the activity mapping is correct, option trades stay internal, the dedupe set persists across syncs, and nothing in the connect flow writes opening rows. What is still needed is your ledger, to confirm the id actually changed — a fix aimed at the wrong cause is worse than none.</t>
+          <t>NOW PROVED AS A MECHANISM, not just suspected (probes/sync-identity.probe.test.ts). Our account id IS the broker's account id with 'st-' in front, and the key that stops an activity being recorded twice BEGINS with our account id. The probe runs the same 40 events twice: correctly spotted as repeats correctly under one id, and ALL 40 come back as new under another. So a changed broker id re-imports the entire history as new money arriving. Everything else has been ruled out by running the code: the activity mapping is correct, option trades stay internal, the list of activities already seen persists across syncs, and nothing in the connect flow writes opening rows. What is still needed is your ledger, to confirm the id actually changed — a fix aimed at the wrong cause is worse than none.</t>
         </is>
       </c>
       <c r="D3" s="13" t="n"/>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -1634,20 +1634,24 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Is this broker activity money arriving from outside, money leaving, or a move inside the account?
-Answers: DEPOSIT · WITHDRAWAL · BUY · SELL · DIVIDEND · INTEREST · ADJUST (a note, no money) · SKIP (not recorded).</t>
+          <t>A line arrived from the broker. Is this money you paid IN, money you took OUT, or something that happened inside the account?
+Answer: money in · money out · a purchase · a sale · a dividend · interest · a fee · a note with no money attached · or ignored entirely.</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>The broker's own word decides, and only two of them mean money crossing the boundary:
-• CONTRIBUTION → DEPOSIT  — external money in
-• WITHDRAWAL → WITHDRAWAL — external money out
-• BUY → BUY, SELL → SELL  — INTERNAL. Cash became shares or shares became cash; nothing entered or left, so neither may ever be counted as a deposit or a withdrawal.
-• DIVIDEND → DIVIDEND, INTEREST → INTEREST — income, counted as income
-• option trades → BUY / SELL (internal), never deposits
-• OPTIONEXPIRATION, OPTIONEXERCISE → SKIP (no cash moves; shares arrive on the paired trade row)
-THIS IS THE RULE THAT BROKE VANGUARD. Deposits feed the personal-return figure, so anything wrongly called a deposit corrupts the return. The mapping table itself is correct — verified by probe.</t>
+          <t>THE PROBLEM THIS SOLVES. Your broker does not tell us "this was a deposit". It sends ONE WORD in its own vocabulary, and every broker uses different words. One of them has 261 of them. So the app keeps a translation table.
+THE TRANSLATION, and only two of these mean money crossing the boundary:
+   CONTRIBUTION → money IN.        WITHDRAWAL, WIRE OUT → money OUT.
+   BUY, SELL → neither. Your cash became shares, or shares became cash. Nothing entered or left the account, so counting either as a deposit would be inventing money.
+   DIVIDEND, REI, STOCK_DIVIDEND → a dividend.   INTEREST → interest.
+   REDEMPTION → a CD or bond matured and paid out. Treated as a SALE, because the money was already yours — it just changed form. Booking it as a deposit would add six figures of money you never paid in, which is what happened on a real E*TRADE account before this rule was added.
+   FEE, TAX → a cost.   SPLIT, ADJUSTMENT → a note, no money.
+   OPTION EXPIRY / EXERCISE → ignored; the shares arrive on the matching trade line.
+AND HERE IS THE DEFECT. If the word is NOT in that table, the app looks at the amount: positive means money in, negative means money out. That is a guess, and it is the exact guess the code warns against a few lines above, where it explains why a matured bond had to be handled specially.
+WHAT THAT COSTS YOU, with your own question as the example. A dividend that is automatically reinvested arrives as its own line. The app recognises ONE spelling of that word — "REI". Every other spelling a broker might use — REINVESTMENT, DIVIDEND REINVESTMENT, CAPITAL GAIN REINVESTMENT — is unrecognised, has a positive amount, and is therefore recorded as MONEY YOU PAID IN.
+Eighty quarterly reinvestments of $4,500 is $360,000 of deposits that never happened, from one holding on one account. Twenty years of a large account, and $1.4m stops looking surprising.
+PROVED ON THE FOUNDER'S OWN FILE (2026-08-17): Vanguard's words 'Sweep out', 'Sweep in' and 'Corp Action (Redemption)' all fell through to the sign rule. Result on one account, seven months, nothing actually moved in or out: $1,064,493 of contributions and $424,818 of withdrawals, from rolling the same ~$220k of Treasury bills. Note the REDEMPTION protection exists in the table and did not fire — Vanguard writes 'Corp Action (Redemption)', which is a different string. And every 'Reinvestment' line (negative) booked as money LEAVING. See probes/vanguard-real-file.probe.test.ts.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1666,21 +1670,33 @@
           <t>Calculation Module code/probes/broken-family.probe.test.ts</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>probes/unknown-activity-types.probe.test.ts</t>
+        </is>
+      </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>CORRECT</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr"/>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>A word the app does not recognise must never be counted as money you paid in or took out. Unclassified is a real answer and it belongs on the screen; a guess based on whether the number is positive is not. And the words brokers genuinely use — every spelling of reinvestment, dividend, capital gain, interest and maturity — should be recognised rather than one of them.</t>
+        </is>
+      </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Nothing to change here. But it is the prime suspect for the $1.4m of phantom contributions and is proved innocent, so the search moves to whatever else writes DEPOSIT rows — manual entry, the CSV importer, or a transfer path. Trace that before touching anything.</t>
+          <t>Three steps, cheapest first.
+1. STOP GUESSING FROM THE SIGN. When the app does not recognise a word, it should record the line as 'unknown' and leave it out of the money-in and money-out totals — not book it as a deposit. Money we cannot classify must not be counted as money you paid in. This is a few lines of code and it stops the bleeding immediately.
+2. RECOGNISE THE WORDS BROKERS ACTUALLY USE for a reinvested dividend, a capital-gains distribution, a matured bond and interest paid. Any word containing REINVEST is a reinvestment. Any word containing DIVIDEND is a dividend. Any word containing INTEREST or COUPON is interest. That is a handful of extra rules covering most of what is currently falling through.
+3. SHOW THE PERSON WHAT WE COULD NOT READ. A short line — "12 entries we could not classify" — with the broker's own wording beside each. Then an unrecognised word becomes something a person can point at, instead of a silent wrong number.
+HOW TO CONFIRM THIS IS YOUR $1.4m BEFORE CHANGING ANYTHING: every wrongly-booked line already carries a note with the broker's original word, in the form 'broker: DIVIDEND REINVESTMENT'. Open the Vanguard account's activity list and look for those notes on anything counted as money in. If they are there, this is the cause.</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr"/>
@@ -3810,9 +3826,15 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>beginning / ending: Net-worth snapshots the app writes itself — a dated map of what things were worth. Written on app open. NOT from any institution: nobody sends us history, so this is the only record of what yesterday looked like, which is why its gaps matter so much.
-money in, money out, dividends, interest: summed from the transaction ledger, which is built from the broker feed by the activity rules below. Any mis-mapping there arrives here as a fake market movement.
-debt paid down: from payments logged on the Debts screen.</t>
+          <t>WHAT YOU STARTED WITH and WHAT YOU HAVE NOW: from the app's own saved record of your net worth. No institution sends us history, so this is the only record of last month that exists.
+MONEY IN, MONEY OUT, DIVIDENDS, INTEREST — you are right that a ledger does not label these. What it sends is ONE WORD per line, in its own vocabulary, and the app translates that word:
+   CONTRIBUTION → money in        WITHDRAWAL → money out
+   DIVIDEND, REI → dividends      INTEREST → interest
+   BUY, SELL → neither. Cash became shares or shares became cash. Nothing entered or left.
+   REDEMPTION (a matured CD or bond paying out) → treated as a sale, NOT as money arriving.
+AND WHEN THE WORD IS NOT ONE OF THOSE, the app falls back to reading the SIGN of the amount: money in becomes a deposit, money out becomes a withdrawal. That fallback is the defect — see the row for INGEST_ACTIVITY_TYPE, and read it, because it is very likely the source of your $1.4m.
+REINVESTED DIVIDENDS, your second question: a reinvested dividend usually arrives as TWO lines — the dividend, then a purchase. Handled correctly that is income plus an internal move, and no new money. The app recognises exactly ONE spelling of the reinvestment word ('REI'). Every other spelling brokers use falls through to the sign rule and is booked as new money arriving.
+DEBT PAID DOWN: from payments you log on the Debts screen. No institution supplies debts.</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -3828,7 +3850,8 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>STOP CALLING A LEFTOVER A MEASUREMENT. Two changes. (1) The unexplained remainder gets its own honest row — "we could not account for $X" — instead of being printed as "change in investment value". A person can act on "unexplained"; they cannot act on a market loss that never happened. (2) Market movement is MEASURED where the evidence exists — from stored per-holding values — and the row is simply absent when it does not, rather than being inferred. Absent beats invented.</t>
+          <t>STOP CALLING A LEFTOVER A MEASUREMENT. Two changes. (1) The unexplained remainder gets its own honest row — "we could not account for $X" — instead of being printed as "change in investment value". A person can act on "unexplained"; they cannot act on a market loss that never happened. (2) Market movement is MEASURED where the evidence exists — from stored per-holding values — and the row is simply absent when it does not, rather than being inferred. Absent beats invented.
+ALSO: the walk has NO LINE FOR FEES. The two ADR custody fees on the founder's file ($460) have nowhere to go, so they land inside 'change in investment value' — small here, but it means the walk can never reconcile to a statement that itemises fees.</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
@@ -3838,7 +3861,10 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>Split the function in two. Keep the balancing arithmetic (it is sound and the rows must always sum), but return the unexplained remainder under its own name — unexplained — and let the screen print it as such. Then add a SEPARATE measured market-movement figure sourced from stored per-holding values, shown only when that history exists. Two small changes, no new engine.</t>
+          <t>Two changes, and the first one is small.
+1. STOP PRINTING A LEFTOVER AS IF IT WERE A MEASUREMENT. Today, anything the app cannot explain gets shown as 'change in investment value'. It should get its own line saying what it is: "$X we could not account for". You can do something about a line that says we could not account for it. You can do nothing about a market loss that never happened.
+2. ONLY SHOW A MARKET-MOVEMENT LINE WHEN WE ACTUALLY MEASURED ONE. That means comparing what each holding was worth then against what it is worth now — which needs per-account history the app does not currently keep. Until it does, the line should simply not appear. A missing line is honest; a made-up one is not.
+The first change is worth doing on its own and does not wait for the second.</t>
         </is>
       </c>
       <c r="M45" s="5" t="inlineStr"/>
@@ -15167,7 +15193,11 @@
           <t>NOW PROVED AS A MECHANISM, not just suspected (probes/sync-identity.probe.test.ts). Our account id IS the broker's account id with 'st-' in front, and the key that stops an activity being recorded twice BEGINS with our account id. The probe runs the same 40 events twice: correctly spotted as repeats correctly under one id, and ALL 40 come back as new under another. So a changed broker id re-imports the entire history as new money arriving. Everything else has been ruled out by running the code: the activity mapping is correct, option trades stay internal, the list of activities already seen persists across syncs, and nothing in the connect flow writes opening rows. What is still needed is your ledger, to confirm the id actually changed — a fix aimed at the wrong cause is worse than none.</t>
         </is>
       </c>
-      <c r="D3" s="13" t="n"/>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>ANSWERED 2026-08-17, by the founder's own activity file, run through the real code. The cause is the SIGN-GUESS RULE, not the account id. Vanguard's own words for internal moves — 'Sweep out', 'Sweep in', 'Corp Action (Redemption)' — are not in the translation table, so each falls through to "positive = money in, negative = money out". On one account over seven months, with NOTHING actually deposited or withdrawn, the real code produced over $1m of contributions and over $400k of withdrawals: the same ~$220k of Treasury bills, rolled three times, booked the full principal as new money on every roll (once at maturity, once at the sweep). The account-id theory is DEMOTED — still possible, no longer needed to explain the number. Proof: probes/vanguard-real-file.probe.test.ts (reads the file from disk; the file itself never enters git — founder standing order).</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="n">

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -10,9 +10,10 @@
     <sheet name="Calculations" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Formatting helpers" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Raw inputs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="How a line becomes a class" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Field dictionary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Open questions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Institution matrix" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="How a line becomes a class" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Field dictionary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Open questions" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,8 +65,17 @@
       <color rgb="001B3A5C"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="006B2D8F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -122,8 +132,13 @@
         <fgColor rgb="00FBE9E9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFDF0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -145,11 +160,55 @@
         <color rgb="00DDDDDD"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00DDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -198,6 +257,20 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -13303,6 +13376,11 @@
           <t>TYPED BY THE PERSON — nothing external supplies these, so they are only as right as the question that asked for them</t>
         </is>
       </c>
+      <c r="B3" s="18" t="n"/>
+      <c r="C3" s="18" t="n"/>
+      <c r="D3" s="18" t="n"/>
+      <c r="E3" s="18" t="n"/>
+      <c r="F3" s="19" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -13646,6 +13724,11 @@
           <t>SENT BY A CONNECTED BROKER (SnapTrade) — the exact payload paths, as the live E*TRADE and Vanguard connections deliver them</t>
         </is>
       </c>
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="19" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -14017,6 +14100,11 @@
           <t>READ FROM A FILE YOU UPLOAD — no two institutions name a column the same way, so every column is found by PATTERN and the importer reports which header it used</t>
         </is>
       </c>
+      <c r="B30" s="18" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="18" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="19" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
@@ -14176,6 +14264,11 @@
           <t>FETCHED FROM AN OUTSIDE FEED — not from your institution, and each carries its own freshness</t>
         </is>
       </c>
+      <c r="B37" s="18" t="n"/>
+      <c r="C37" s="18" t="n"/>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="19" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
@@ -14267,6 +14360,11 @@
           <t>NUMBERS WE CHOSE — no institution sent these. They are assumptions, every projection stands on them, and they belong on this tab precisely because they look like facts</t>
         </is>
       </c>
+      <c r="B41" s="18" t="n"/>
+      <c r="C41" s="18" t="n"/>
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="19" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="17" t="inlineStr">
@@ -14450,6 +14548,1407 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="006B2D8F"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="58" customHeight="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>INSTITUTION MATRIX — every raw input we need, against what each institution actually calls it. EVERY CELL SAYS HOW WE KNOW: ✓ seen on this machine (your file / a live connection) · ○ their published documentation · — documented as absent · ? NEVER SEEN — a red cell is a file worth downloading, never a thing to guess. The red cells ARE the download shopping list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>What we need</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>OUR name</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Vanguard — file</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Fidelity — file</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Schwab — file</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>E*TRADE — connected</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Chase — file</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>SnapTrade — connection</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Plaid — connection (beta plan)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>YOUR COMMENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>A · THE FIELDS — where each number lives, per institution</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>Account identifier</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>asset_id / mask</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>✓ 'Account Number', masked (xxxx6537) — founder's file</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>○ 'Account Number' + 'Account Name' on every row</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>○ per-account files; all-accounts export inserts section headers</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>✓ scrambled id, never the real number (live)</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t>— no holdings export exists at all</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>✓ accounts[].id + number</t>
+        </is>
+      </c>
+      <c r="I4" s="23" t="inlineStr">
+        <is>
+          <t>○ account_id + mask</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>ticker</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>✓ 'Symbol' — CUSIP for bonds/CDs, blank allowed (VMFXX row had one)</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>○ 'Symbol' — core cash arrives as 'SPAXX**', trailing asterisks are a footnote mark</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>○ 'Symbol'</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>✓ symbol.raw_symbol via connection; CUSIP for CDs</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>✓ positions[].symbol.raw_symbol</t>
+        </is>
+      </c>
+      <c r="I5" s="23" t="inlineStr">
+        <is>
+          <t>○ ticker_symbol — CAN BE NULL, especially fixed income</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>Holding name / description — THE field that identifies a CD</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>label / name</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>✓ 'Investment Name' — 'U S TREASURY BILL 0 11/10/26 07/14/26'</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>○ 'Description'</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>○ security name / description</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>✓ symbol.description — 'KEYBANK NA 4.00% CD 08/24/26' (live)</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>✓ positions[].symbol.description</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>○ security.name — institution text, not normalised</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>Shares held</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>shares</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>✓ 'Shares'</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>○ 'Quantity'</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>○ quantity</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>○ 'Qty #' in the positions file</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>✓ positions[].units (sells arrive NEGATIVE, live)</t>
+        </is>
+      </c>
+      <c r="I7" s="23" t="inlineStr">
+        <is>
+          <t>○ quantity</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>Price per share</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>last_price</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>✓ 'Share Price'</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>○ 'Last Price'</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>○ price</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>✓ via connection; bonds priced PER $100 OF FACE (live)</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>✓ positions[].price — only as fresh as the sync</t>
+        </is>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
+        <is>
+          <t>○ institution_price</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>What it is worth</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>value / balance</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>✓ 'Total Value'</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>○ 'Current Value'</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>○ market value</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>✓ account total CAN BE MISSING entirely (live)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>✓ balance.total.amount — can arrive null</t>
+        </is>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>○ institution_value</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>What was paid</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>cost_per_share</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>✓ ABSENT from the holdings section — the file simply does not carry cost</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>○ 'Cost Basis' + 'Cost Basis Per Share'</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>○ cost basis column</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>○ 'Price Paid $' — sounds like a price, IS the cost</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>✓ average_purchase_price</t>
+        </is>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>○ cost_basis</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Purchase history (lots)</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>lots[]</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>✓ none in the file</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>? not in the positions file — unverified beyond that</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
+        <is>
+          <t>? unknown</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>? unknown</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>✓ tax_lots[] exists in the spec and arrived EMPTY on both live brokers</t>
+        </is>
+      </c>
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>— not offered; reconstruct from 24 months of transactions</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Maturity date of a CD / bond</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>maturity_date</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>✓ NO COLUMN — only inside 'Investment Name' text: '… 11/10/26 07/14/26'</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>○ NO COLUMN — inside 'Description'</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>○ NO COLUMN — '… 4.00% due 08/24/2026' in description</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>✓ NO FIELD — description text only (live)</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>✓ NO FIELD — description text only</t>
+        </is>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>○ fixed-income record exists in spec (maturity, coupon) — UNVERIFIED against a real account</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Coupon rate</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>coupon_rate</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>✓ in the name text only ('CPN 1.62500')</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>○ description text</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>○ description text</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>✓ description text (live)</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>✓ description text</t>
+        </is>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t>○ in the spec's fixed-income record — unverified</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Uninvested cash / sweep</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>cash_balance</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>✓ a VMFXX HOLDING row — no cash flag anywhere</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>○ core position: SPAXX/FDRXX fund row</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>○ a special row: 'Cash &amp; Cash Investments'</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>✓ money-market fund ALSO counted inside the cash balance — double (live)</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>✓ balances.cash — includes the money-market funds (dedupe required)</t>
+        </is>
+      </c>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
+          <t>○ is_cash_equivalent flag — never trust it alone (live lesson)</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>How the account is taxed</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>tax_bucket</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>✓ 'Account Type' column says only CASH/MARGIN — not the tax type</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>? not in the positions file</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>? unknown</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>✓ raw broker string; 'savings' arrived meaning a BROKERAGE (live)</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>✓ account type string, unnormalised — we translate + ask when unsure</t>
+        </is>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>○ documented subtypes: ira, roth, 401k, sep ira… (the best of all sources)</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>Transaction date</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>✓ 'Trade Date' AND 'Settlement Date' — we use trade date</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>? need a transactions file</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>○ 'Date'</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>✓ trade_date / settlement_date (live)</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>○ CSV capped ~1 year per download</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>✓ trade_date ?? settlement_date</t>
+        </is>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>○ date</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="21" t="inlineStr">
+        <is>
+          <t>The transaction WORD — what kind of event this is</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>✓ 'Transaction Type' + 'Transaction Description' (both matter)</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>? need a transactions file</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>○ 'Action' column — exact vocabulary UNKNOWN, need a file</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>✓ type — 19 documented + undocumented arrivals (REDEMPTION, MISC…, live)</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>? need a file</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>✓ activities[].type — 'best effort', their own words</t>
+        </is>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>○ type (6) + subtype (50), fully documented — the strongest vocabulary</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>Amount of money moved</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>✓ 'Net Amount' (also 'Principal Amount'); SIGNED — reinvestments negative</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>? need a file</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>○ 'Amount'</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>✓ amount, SIGNED: a buy is NEGATIVE (live)</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>? need a file</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>✓ amount signed, buy negative</t>
+        </is>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>○ amount signed THE OTHER WAY: a buy is POSITIVE (debit) — per-road translation, with tests</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>Fees on a transaction</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>fee</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>✓ 'Commissions and Fees'</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>? need a file</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>○ 'Fees'</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>✓ fee field + FEE-typed rows (live)</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>? need a file</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>✓ fee</t>
+        </is>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
+        <is>
+          <t>○ fees</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>Accrued interest on a bond trade</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>(not yet captured)</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>✓ 'Accrued Interest' — a real column, $1,289.40 on the founder's T-note buy</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>? unknown</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>? unknown</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>? unknown</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>? not in the documented payload</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>? not documented</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>B · THE TRANSACTION WORDS — what each institution calls each kind of event. This is the table the $1.4m and the $2,387 both came from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>Money you put in</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>DEPOSIT</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>? NOT PRESENT in the founder's file — their word for a real deposit is still UNSEEN. Do not guess it.</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>? need a transactions file</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>? need a file</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>✓ CONTRIBUTION · WIRE IN (live)</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>? need a file</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="inlineStr">
+        <is>
+          <t>✓ CONTRIBUTION</t>
+        </is>
+      </c>
+      <c r="I22" s="23" t="inlineStr">
+        <is>
+          <t>○ subtypes: contribution · deposit</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>Money you took out</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>WITHDRAWAL</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>? not present in the file — unseen</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>✓ WITHDRAWAL · WIRE OUT (live)</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>✓ WITHDRAWAL</t>
+        </is>
+      </c>
+      <c r="I23" s="23" t="inlineStr">
+        <is>
+          <t>○ withdrawal</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>Dividend received</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>DIVIDEND</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>✓ 'Dividend' / 'Dividend Received'</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>✓ DIVIDEND (live)</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>✓ DIVIDEND</t>
+        </is>
+      </c>
+      <c r="I24" s="23" t="inlineStr">
+        <is>
+          <t>○ dividend · qualified dividend · non-qualified dividend</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Dividend REINVESTED — the pair that made your $2,387</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>DIVIDEND, reinvested + internal buy</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>✓ 'Reinvestment' / 'Dividend Reinvestment', amount NEGATIVE — the buying leg</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>○ REI in SnapTrade's documented list</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>✓ REI → dividend, flagged reinvested</t>
+        </is>
+      </c>
+      <c r="I25" s="23" t="inlineStr">
+        <is>
+          <t>○ dividend reinvestment · interest reinvestment · LT/ST capital gain reinvestment</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Interest received</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>INTEREST</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>✓ 'Interest' / 'Interest Received'</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>✓ INTEREST · margin interest arrives as MISC with negative amount (live)</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>✓ INTEREST</t>
+        </is>
+      </c>
+      <c r="I26" s="23" t="inlineStr">
+        <is>
+          <t>○ interest · interest receivable</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Sweep between settlement fund and cash</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>internal — NO flow</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>✓ 'Sweep out' / 'Sweep in' — the words behind $645,130 of the fake contributions</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>? not observed live</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>? no documented word — arrives as whatever the broker says</t>
+        </is>
+      </c>
+      <c r="I27" s="23" t="inlineStr">
+        <is>
+          <t>○ no dedicated subtype — type 'cash' + context</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>A bond or CD maturing and paying out</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>SELL (your own money back)</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>✓ 'Corp Action (Redemption)' — NOT the string 'REDEMPTION', which is why the guard missed</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>✓ REDEMPTION — undocumented, live-verified, six figures of it</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>✓ passes through as the broker's word</t>
+        </is>
+      </c>
+      <c r="I28" s="23" t="inlineStr">
+        <is>
+          <t>○ return of principal</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Buying / selling a security</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>BUY / SELL</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>✓ 'Buy'</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="E29" s="23" t="inlineStr">
+        <is>
+          <t>○ 'Buy' / 'Sell' under 'Action'</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>✓ BUY / SELL (live)</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>✓ BUY / SELL</t>
+        </is>
+      </c>
+      <c r="I29" s="23" t="inlineStr">
+        <is>
+          <t>○ buy · sell (+ subtypes)</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>A fee or tax</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>FEE</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>✓ 'Fee' / 'ADR Custody Fee'</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>✓ FEE · SERVICE FEE (positive = reversal) · TAX (live)</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>✓ FEE · TAX</t>
+        </is>
+      </c>
+      <c r="I30" s="23" t="inlineStr">
+        <is>
+          <t>○ account fee · management fee · misc fee · tax · tax withheld…</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Securities moved in kind (no cash)</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>position note — NO flow</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>✓ EXCHANGE RECEIVED IN / DELIVERED OUT · EXTERNAL_ASSET_TRANSFER_IN/OUT (live)</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr">
+        <is>
+          <t>✓ same words</t>
+        </is>
+      </c>
+      <c r="I31" s="23" t="inlineStr">
+        <is>
+          <t>○ transfer · merger · spin off</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A21:J21"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001B4D8F"/>
@@ -15075,7 +16574,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00854F0B"/>
@@ -15134,7 +16633,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00A32D2D"/>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -1755,7 +1755,8 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>A word the app does not recognise must never be counted as money you paid in or took out. Unclassified is a real answer and it belongs on the screen; a guess based on whether the number is positive is not. And the words brokers genuinely use — every spelling of reinvestment, dividend, capital gain, interest and maturity — should be recognised rather than one of them.</t>
+          <t>A word the app does not recognise must never be counted as money you paid in or took out. Unclassified is a real answer and it belongs on the screen; a guess based on whether the number is positive is not. And the words brokers genuinely use — every spelling of reinvestment, dividend, capital gain, interest and maturity — should be recognised rather than one of them.
+AND (founder challenge, 2026-08-17): a SKIP must only ever skip a row carrying NO money. A cash-settled option exercise, or cash-in-lieu on a split, carries real proceeds on the very row we skip today — the rule should be: any skipped-type row with a non-zero amount is recorded as internal proceeds or cost, never dropped.</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -14554,7 +14555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -14634,6 +14635,15 @@
           <t>A · THE FIELDS — where each number lives, per institution</t>
         </is>
       </c>
+      <c r="B3" s="18" t="n"/>
+      <c r="C3" s="18" t="n"/>
+      <c r="D3" s="18" t="n"/>
+      <c r="E3" s="18" t="n"/>
+      <c r="F3" s="18" t="n"/>
+      <c r="G3" s="18" t="n"/>
+      <c r="H3" s="18" t="n"/>
+      <c r="I3" s="18" t="n"/>
+      <c r="J3" s="19" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
@@ -15457,6 +15467,15 @@
           <t>B · THE TRANSACTION WORDS — what each institution calls each kind of event. This is the table the $1.4m and the $2,387 both came from.</t>
         </is>
       </c>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="n"/>
+      <c r="I21" s="18" t="n"/>
+      <c r="J21" s="19" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
@@ -15937,6 +15956,54 @@
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Option expiring / exercised — FOUNDER CHALLENGE: "could expire in the money"</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>SKIP if truly no cash; internal proceeds if cash rides the row</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>? unseen — no options at Vanguard via connection (live)</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>✓ OPTIONEXPIRATION · OPTIONEXERCISE · OPTIONASSIGNMENT (live). Share-settled: cash arrives on a PAIRED BUY/SELL row we keep. DEFECT: a CASH-SETTLED exercise (SPX family) or CASH-IN-LIEU adjustment carries its money ON the skipped row — dropped today</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>? unseen</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr">
+        <is>
+          <t>✓ same words pass through</t>
+        </is>
+      </c>
+      <c r="I32" s="23" t="inlineStr">
+        <is>
+          <t>○ exercise · expire · assignment subtypes</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -14555,7 +14555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -14635,15 +14635,6 @@
           <t>A · THE FIELDS — where each number lives, per institution</t>
         </is>
       </c>
-      <c r="B3" s="18" t="n"/>
-      <c r="C3" s="18" t="n"/>
-      <c r="D3" s="18" t="n"/>
-      <c r="E3" s="18" t="n"/>
-      <c r="F3" s="18" t="n"/>
-      <c r="G3" s="18" t="n"/>
-      <c r="H3" s="18" t="n"/>
-      <c r="I3" s="18" t="n"/>
-      <c r="J3" s="19" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
@@ -15467,15 +15458,6 @@
           <t>B · THE TRANSACTION WORDS — what each institution calls each kind of event. This is the table the $1.4m and the $2,387 both came from.</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n"/>
-      <c r="C21" s="18" t="n"/>
-      <c r="D21" s="18" t="n"/>
-      <c r="E21" s="18" t="n"/>
-      <c r="F21" s="18" t="n"/>
-      <c r="G21" s="18" t="n"/>
-      <c r="H21" s="18" t="n"/>
-      <c r="I21" s="18" t="n"/>
-      <c r="J21" s="19" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
@@ -15912,47 +15894,47 @@
     <row r="31">
       <c r="A31" s="21" t="inlineStr">
         <is>
-          <t>Securities moved in kind (no cash)</t>
+          <t>Option expiring / exercised — founder challenge: "could expire in the money"</t>
         </is>
       </c>
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>position note — NO flow</t>
+          <t>SKIP only when NO cash rides the row; internal proceeds when it does</t>
         </is>
       </c>
       <c r="C31" s="9" t="inlineStr">
         <is>
+          <t>? unseen — options do not come through Vanguard's connection (live)</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
           <t>? unseen</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>? unseen</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>✓ OPTIONEXPIRATION · OPTIONEXERCISE · OPTIONASSIGNMENT (live). Share-settled: cash arrives on a PAIRED BUY/SELL row we keep. DEFECT: a CASH-SETTLED exercise (SPX family) or CASH-IN-LIEU on a split carries its money ON the skipped row — dropped today</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
         <is>
           <t>? unseen</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>✓ EXCHANGE RECEIVED IN / DELIVERED OUT · EXTERNAL_ASSET_TRANSFER_IN/OUT (live)</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>? unseen</t>
-        </is>
-      </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>✓ same words</t>
+          <t>✓ the same words pass through</t>
         </is>
       </c>
       <c r="I31" s="23" t="inlineStr">
         <is>
-          <t>○ transfer · merger · spin off</t>
+          <t>○ exercise · expire · assignment subtypes</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr"/>
@@ -15960,17 +15942,17 @@
     <row r="32">
       <c r="A32" s="21" t="inlineStr">
         <is>
-          <t>Option expiring / exercised — FOUNDER CHALLENGE: "could expire in the money"</t>
+          <t>Securities moved in kind (no cash)</t>
         </is>
       </c>
       <c r="B32" s="22" t="inlineStr">
         <is>
-          <t>SKIP if truly no cash; internal proceeds if cash rides the row</t>
+          <t>position note — NO flow</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>? unseen — no options at Vanguard via connection (live)</t>
+          <t>? unseen</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
@@ -15985,7 +15967,7 @@
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>✓ OPTIONEXPIRATION · OPTIONEXERCISE · OPTIONASSIGNMENT (live). Share-settled: cash arrives on a PAIRED BUY/SELL row we keep. DEFECT: a CASH-SETTLED exercise (SPX family) or CASH-IN-LIEU adjustment carries its money ON the skipped row — dropped today</t>
+          <t>✓ EXCHANGE RECEIVED IN / DELIVERED OUT · EXTERNAL_ASSET_TRANSFER_IN/OUT (live)</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
@@ -15995,21 +15977,901 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>✓ same words pass through</t>
+          <t>✓ same words</t>
         </is>
       </c>
       <c r="I32" s="23" t="inlineStr">
         <is>
-          <t>○ exercise · expire · assignment subtypes</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="n"/>
+          <t>○ transfer · merger · spin off</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>C · THE ACCOUNT DETAIL PAGE — every input that page shows, and which road supplies it. Enumerated from the shipping screen, not from memory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>Account name + institution + mask ('••4821')</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>label · institution · mask</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>✓ file: 'Account Number' masked; name is the fund/brokerage grouping</t>
+        </is>
+      </c>
+      <c r="D34" s="23" t="inlineStr">
+        <is>
+          <t>○ 'Account Number' + 'Account Name' per row</t>
+        </is>
+      </c>
+      <c r="E34" s="23" t="inlineStr">
+        <is>
+          <t>○ per-account file naming</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>✓ broker-assigned name already contains 'E*Trade …'; number scrambled (live)</t>
+        </is>
+      </c>
+      <c r="G34" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>✓ accounts[].name · institution_name · number</t>
+        </is>
+      </c>
+      <c r="I34" s="23" t="inlineStr">
+        <is>
+          <t>○ official_name · mask</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="inlineStr">
+        <is>
+          <t>Where the value came from + when — 'connected · updated 2h ago' / 'you typed this in May'</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>source · last_synced · value_as_of</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>— a file is an IMPORT: our stamp, not theirs</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>— same</t>
+        </is>
+      </c>
+      <c r="E35" s="23" t="inlineStr">
+        <is>
+          <t>— same</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>✓ sync timestamp is OURS at ingest (live)</t>
+        </is>
+      </c>
+      <c r="G35" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>✓ we stamp last_synced on every successful sync</t>
+        </is>
+      </c>
+      <c r="I35" s="23" t="inlineStr">
+        <is>
+          <t>○ same pattern</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>The uninvested-cash line</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>cash_balance</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>✓ the VMFXX row IS the sweep (no cash flag)</t>
+        </is>
+      </c>
+      <c r="D36" s="23" t="inlineStr">
+        <is>
+          <t>○ SPAXX/FDRXX core row</t>
+        </is>
+      </c>
+      <c r="E36" s="23" t="inlineStr">
+        <is>
+          <t>○ 'Cash &amp; Cash Investments' row</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>✓ balances.cash DOUBLE-COUNTS the money-market fund (live)</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>✓ balances.cash minus money-market holdings (our dedupe)</t>
+        </is>
+      </c>
+      <c r="I36" s="23" t="inlineStr">
+        <is>
+          <t>○ is_cash_equivalent flag</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>How it is taxed ('tax-deferred — tax due when you take it out')</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>tax_bucket / tax_treatment</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>✓ file's 'Account Type' says CASH/MARGIN — NOT the tax type</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>? not in positions file</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>? unknown</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>✓ raw string, mistranslated 'savings' live — we ask when unsure</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>✓ raw account type string + our Held-in question</t>
+        </is>
+      </c>
+      <c r="I37" s="23" t="inlineStr">
+        <is>
+          <t>○ documented subtypes incl. every retirement type — best source</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>The activity list (every dated row on the page)</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>transactions[]</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>✓ full transactions section in the same file</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>? need a transactions file</t>
+        </is>
+      </c>
+      <c r="E38" s="23" t="inlineStr">
+        <is>
+          <t>○ separate transactions export</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>✓ activities[] (live)</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="inlineStr">
+        <is>
+          <t>○ CSV capped ~1yr</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>✓ activities[] — the words are section B</t>
+        </is>
+      </c>
+      <c r="I38" s="23" t="inlineStr">
+        <is>
+          <t>○ investment transactions, 24 months</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="21" t="inlineStr">
+        <is>
+          <t>How far back the history goes ('activity since Mar 2025')</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>history_from</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>✓ the file's own earliest row — visible</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>? unknown</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>? unknown</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>✓ brokers back-fill DIFFERENT depths (live: 1yr vs 90d)</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>? unknown</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>✓ we track earliest-ever-seen per account</t>
+        </is>
+      </c>
+      <c r="I39" s="23" t="inlineStr">
+        <is>
+          <t>○ 'up to 24 months' stated</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>The per-class split of one account (its own mini-allocation)</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>accountClassBreakdown</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>✓ derivable: names + values are in the file</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>○ derivable from columns</t>
+        </is>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>○ derivable</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="inlineStr">
+        <is>
+          <t>✓ derived from positions + names (live rules)</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>✓ derived — see ACCOUNT_SPLIT row on Calculations tab</t>
+        </is>
+      </c>
+      <c r="I40" s="23" t="inlineStr">
+        <is>
+          <t>○ derived; security types help</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>D · THE HOLDING DETAIL PAGE, BY ASSET CLASS — shares and funds, bonds and CDs, options, crypto, cash. A dash means NO institution supplies it on any road — it is our feed or our assumption, and it belongs here precisely because it looks like institution data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="21" t="inlineStr">
+        <is>
+          <t>EVERY CLASS · live price + how fresh it is</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>last_price · priceFreshness</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>✓ file 'Share Price' = that day only</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>○ 'Last Price'</t>
+        </is>
+      </c>
+      <c r="E42" s="23" t="inlineStr">
+        <is>
+          <t>○ price column</t>
+        </is>
+      </c>
+      <c r="F42" s="8" t="inlineStr">
+        <is>
+          <t>✓ positions[].price — as fresh as the sync (live)</t>
+        </is>
+      </c>
+      <c r="G42" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t>✓ price per sync; our market feed (Tiingo/Yahoo) refreshes tickers it can</t>
+        </is>
+      </c>
+      <c r="I42" s="23" t="inlineStr">
+        <is>
+          <t>○ institution_price + as-of date</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
+          <t>EVERY CLASS · the price GRAPH + period chips (1M…3Y)</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>price series → periodReturn</t>
+        </is>
+      </c>
+      <c r="C43" s="23" t="inlineStr">
+        <is>
+          <t>— no institution sends a price HISTORY; the graph is our market feed, by ticker</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>— same</t>
+        </is>
+      </c>
+      <c r="E43" s="23" t="inlineStr">
+        <is>
+          <t>— same</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>— same (live: broker sends one price, not a series)</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H43" s="23" t="inlineStr">
+        <is>
+          <t>— not in the payload</t>
+        </is>
+      </c>
+      <c r="I43" s="23" t="inlineStr">
+        <is>
+          <t>— not offered; our feed. A CD/CUSIP has NO series — the graph must honestly not draw</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="21" t="inlineStr">
+        <is>
+          <t>EVERY CLASS · what you paid, per lot ('bought Mar 2021 at $102')</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>lots[] · avgCost · costBasis</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>✓ ABSENT from Vanguard's file — cost simply is not there</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="inlineStr">
+        <is>
+          <t>○ 'Cost Basis' + per-share</t>
+        </is>
+      </c>
+      <c r="E44" s="23" t="inlineStr">
+        <is>
+          <t>○ cost basis</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>✓ average only; tax_lots EMPTY on both live brokers → ONE synthetic lot</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>✓ average_purchase_price</t>
+        </is>
+      </c>
+      <c r="I44" s="23" t="inlineStr">
+        <is>
+          <t>○ cost_basis; lots reconstructable from 24mo of buys</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
+          <t>EVERY CLASS · gain since purchase · %-return · long/short-term tax split</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>unrealizedGain · totalROI · capGains</t>
+        </is>
+      </c>
+      <c r="C45" s="23" t="inlineStr">
+        <is>
+          <t>— derived from shares × price − cost; the tax split needs LOT DATES, which only synthetic-lot accuracy allows (one date, not per-lot truth)</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="inlineStr">
+        <is>
+          <t>○ derivable — Fidelity even ships Total Gain/Loss columns to check AGAINST</t>
+        </is>
+      </c>
+      <c r="E45" s="23" t="inlineStr">
+        <is>
+          <t>○ gain/loss column shipped too</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>✓ derived; dates missing live → 'unknown = short-term, the cautious side'</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>✓ derived from their average cost</t>
+        </is>
+      </c>
+      <c r="I45" s="23" t="inlineStr">
+        <is>
+          <t>○ derived</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="21" t="inlineStr">
+        <is>
+          <t>EVERY CLASS · dividends this holding paid you</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>ledger DIVIDEND rows by ticker</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>✓ 'Dividend Received' rows carry the fund name + symbol</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>? need a transactions file</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>? unknown words</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
+        <is>
+          <t>✓ DIVIDEND rows with symbol (live)</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>? unknown</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>✓ activities filtered by symbol</t>
+        </is>
+      </c>
+      <c r="I46" s="23" t="inlineStr">
+        <is>
+          <t>○ dividend subtypes, security_id attached</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="21" t="inlineStr">
+        <is>
+          <t>STOCKS / FUNDS · 'you beat the market by…' benchmark line</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>benchmarkTicker · benchReturn</t>
+        </is>
+      </c>
+      <c r="C47" s="23" t="inlineStr">
+        <is>
+          <t>— OUR choice of benchmark + OUR feed; no institution participates</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
+        <is>
+          <t>— same</t>
+        </is>
+      </c>
+      <c r="E47" s="23" t="inlineStr">
+        <is>
+          <t>— same</t>
+        </is>
+      </c>
+      <c r="F47" s="23" t="inlineStr">
+        <is>
+          <t>— same</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H47" s="23" t="inlineStr">
+        <is>
+          <t>— same</t>
+        </is>
+      </c>
+      <c r="I47" s="23" t="inlineStr">
+        <is>
+          <t>— same</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="21" t="inlineStr">
+        <is>
+          <t>BONDS &amp; CDs · face value · coupon · maturity · yield-to-maturity</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>face_value · coupon_rate · maturity_date</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>✓ ALL inside 'Investment Name' text: 'U S TREASURY NOTE CPN 1.62500 MTD 2026-02-15' — parsed or typed, never a column</t>
+        </is>
+      </c>
+      <c r="D48" s="23" t="inlineStr">
+        <is>
+          <t>○ inside 'Description'</t>
+        </is>
+      </c>
+      <c r="E48" s="23" t="inlineStr">
+        <is>
+          <t>○ '… 4.00% due 08/24/2026' text</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>✓ description text only (live: 'KEYBANK NA 4.00% CD 08/24/26')</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>✓ description text only</t>
+        </is>
+      </c>
+      <c r="I48" s="23" t="inlineStr">
+        <is>
+          <t>○ spec has real maturity/coupon fields — UNVERIFIED on a live account; would be the first road with columns</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="21" t="inlineStr">
+        <is>
+          <t>BONDS &amp; CDs · accrued interest paid on purchase</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>(not yet captured anywhere)</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>✓ a REAL COLUMN in the file — $1,289.40 on the T-note buy. We capture it NOWHERE; it silently inflates the buy's cost today</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>? unknown</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="inlineStr">
+        <is>
+          <t>? unknown</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>? unknown</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="inlineStr">
+        <is>
+          <t>? not in the documented payload</t>
+        </is>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>? not documented</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="21" t="inlineStr">
+        <is>
+          <t>OPTIONS · underlying · strike · call/put · expiry · contracts</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>option_holdings[]</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>? options do not arrive via Vanguard connection (live) and none in the file</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>? unknown</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>? unknown</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="inlineStr">
+        <is>
+          <t>✓ separate options list; price PER SHARE (×100) but cost already PER CONTRACT — mixed units, live-verified to the cent</t>
+        </is>
+      </c>
+      <c r="G50" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>✓ option_symbol: underlying, strike, type, expiration</t>
+        </is>
+      </c>
+      <c r="I50" s="23" t="inlineStr">
+        <is>
+          <t>○ security type derivative + fields</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="21" t="inlineStr">
+        <is>
+          <t>CRYPTO · fractional quantity + a price our feed can find</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>shares (fractional) · price mapping</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>? unseen at Vanguard</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>? unknown</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>? unknown</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>? not held live</t>
+        </is>
+      </c>
+      <c r="G51" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>✓ type code 'crypto' when the broker says so; ticker mapped to our feed (BTC → btcusd)</t>
+        </is>
+      </c>
+      <c r="I51" s="23" t="inlineStr">
+        <is>
+          <t>○ security type cryptocurrency</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="21" t="inlineStr">
+        <is>
+          <t>CASH · balance + rate it earns</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>balance · benchmarkReturn('savings'…)</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>✓ balance visible; the RATE is OUR assumption table — no institution sends their APY on any road we have</t>
+        </is>
+      </c>
+      <c r="D52" s="23" t="inlineStr">
+        <is>
+          <t>○ same</t>
+        </is>
+      </c>
+      <c r="E52" s="23" t="inlineStr">
+        <is>
+          <t>○ same</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>✓ same (live)</t>
+        </is>
+      </c>
+      <c r="G52" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>✓ same</t>
+        </is>
+      </c>
+      <c r="I52" s="23" t="inlineStr">
+        <is>
+          <t>○ Plaid liabilities carry card APRs — but deposit APY still absent</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A33:J33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -1514,7 +1514,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>ACTIVITY_FINGERPRINT</t>
+          <t>ACTIVITY_IDENTITY</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1697,7 +1697,7 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>INGEST_ACTIVITY_TYPE</t>
+          <t>TRANSLATE_BROKER_WORD</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -3906,7 +3906,7 @@
    DIVIDEND, REI → dividends      INTEREST → interest
    BUY, SELL → neither. Cash became shares or shares became cash. Nothing entered or left.
    REDEMPTION (a matured CD or bond paying out) → treated as a sale, NOT as money arriving.
-AND WHEN THE WORD IS NOT ONE OF THOSE, the app falls back to reading the SIGN of the amount: money in becomes a deposit, money out becomes a withdrawal. That fallback is the defect — see the row for INGEST_ACTIVITY_TYPE, and read it, because it is very likely the source of your $1.4m.
+AND WHEN THE WORD IS NOT ONE OF THOSE, the app falls back to reading the SIGN of the amount: money in becomes a deposit, money out becomes a withdrawal. That fallback is the defect — see the row for TRANSLATE_BROKER_WORD, and read it, because it is very likely the source of your $1.4m.
 REINVESTED DIVIDENDS, your second question: a reinvested dividend usually arrives as TWO lines — the dividend, then a purchase. Handled correctly that is income plus an internal move, and no new money. The app recognises exactly ONE spelling of the reinvestment word ('REI'). Every other spelling brokers use falls through to the sign rule and is booked as new money arriving.
 DEBT PAID DOWN: from payments you log on the Debts screen. No institution supplies debts.</t>
         </is>
@@ -5749,7 +5749,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>The transaction ledger — every activity, built from the broker feed by INGEST_ACTIVITY_TYPE (SnapTrade activities[]: type, date, amount), plus anything logged by hand. This is the same ledger the change walk uses, so an error here shows up in BOTH the personal return and the net-worth change.</t>
+          <t>The transaction ledger — every activity, built from the broker feed by TRANSLATE_BROKER_WORD (SnapTrade activities[]: type, date, amount), plus anything logged by hand. This is the same ledger the change walk uses, so an error here shows up in BOTH the personal return and the net-worth change.</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr"/>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>The transaction ledger — every activity, built from the broker feed by INGEST_ACTIVITY_TYPE (SnapTrade activities[]: type, date, amount), plus anything logged by hand. This is the same ledger the change walk uses, so an error here shows up in BOTH the personal return and the net-worth change.</t>
+          <t>The transaction ledger — every activity, built from the broker feed by TRANSLATE_BROKER_WORD (SnapTrade activities[]: type, date, amount), plus anything logged by hand. This is the same ledger the change walk uses, so an error here shows up in BOTH the personal return and the net-worth change.</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr"/>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>The transaction ledger — every activity, built from the broker feed by INGEST_ACTIVITY_TYPE (SnapTrade activities[]: type, date, amount), plus anything logged by hand. This is the same ledger the change walk uses, so an error here shows up in BOTH the personal return and the net-worth change.
+          <t>The transaction ledger — every activity, built from the broker feed by TRANSLATE_BROKER_WORD (SnapTrade activities[]: type, date, amount), plus anything logged by hand. This is the same ledger the change walk uses, so an error here shows up in BOTH the personal return and the net-worth change.
 currentValue: the accounts' value today, from the balances.</t>
         </is>
       </c>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>INGEST_ACTIVITY_TYPE · INGEST_DEDUPE · NW_CHANGE_WALK · the money-weighted return</t>
+          <t>TRANSLATE_BROKER_WORD · INGEST_DEDUPE · NW_CHANGE_WALK · the money-weighted return</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr"/>
@@ -14635,6 +14635,15 @@
           <t>A · THE FIELDS — where each number lives, per institution</t>
         </is>
       </c>
+      <c r="B3" s="18" t="n"/>
+      <c r="C3" s="18" t="n"/>
+      <c r="D3" s="18" t="n"/>
+      <c r="E3" s="18" t="n"/>
+      <c r="F3" s="18" t="n"/>
+      <c r="G3" s="18" t="n"/>
+      <c r="H3" s="18" t="n"/>
+      <c r="I3" s="18" t="n"/>
+      <c r="J3" s="19" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
@@ -15458,6 +15467,15 @@
           <t>B · THE TRANSACTION WORDS — what each institution calls each kind of event. This is the table the $1.4m and the $2,387 both came from.</t>
         </is>
       </c>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="18" t="n"/>
+      <c r="I21" s="18" t="n"/>
+      <c r="J21" s="19" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
@@ -15993,6 +16011,15 @@
           <t>C · THE ACCOUNT DETAIL PAGE — every input that page shows, and which road supplies it. Enumerated from the shipping screen, not from memory.</t>
         </is>
       </c>
+      <c r="B33" s="18" t="n"/>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="18" t="n"/>
+      <c r="I33" s="18" t="n"/>
+      <c r="J33" s="19" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="21" t="inlineStr">
@@ -16336,6 +16363,15 @@
           <t>D · THE HOLDING DETAIL PAGE, BY ASSET CLASS — shares and funds, bonds and CDs, options, crypto, cash. A dash means NO institution supplies it on any road — it is our feed or our assumption, and it belongs here precisely because it looks like institution data.</t>
         </is>
       </c>
+      <c r="B41" s="18" t="n"/>
+      <c r="C41" s="18" t="n"/>
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="18" t="n"/>
+      <c r="G41" s="18" t="n"/>
+      <c r="H41" s="18" t="n"/>
+      <c r="I41" s="18" t="n"/>
+      <c r="J41" s="19" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="21" t="inlineStr">

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -75,7 +75,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -135,6 +135,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFDF0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6EAD9"/>
       </patternFill>
     </fill>
   </fills>
@@ -208,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -271,6 +281,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -397,7 +413,13 @@
     </comment>
     <comment ref="I2" authorId="0" shapeId="0">
       <text>
-        <t>CORRECT · DEFECT · UNRESOLVED. What the code does today, judged against what it should do. Everything left of this column describes the code AS IT IS — including its bugs — because a probe can only execute what exists.</t>
+        <t>HOW MUCH DO WE ACTUALLY KNOW ABOUT THIS ROW?
+CHECKED vs REAL DATA - compared against a real institution file or statement. The only level that shows the number is RIGHT rather than merely consistent with itself.
+PINNED - a test runs the real code and confirms it does what this row says. That proves the DESCRIPTION is true. It does NOT prove the behaviour is what it should be.
+YOUR CALL - pinned, but resting on a number or rule WE chose, which a reasonable person could choose differently. Not a defect: a decision worth your eye.
+DEFECT - I believe this is wrong. WHAT IT SHOULD BE and RECOMMENDED FIX say why and what to do.
+UNRESOLVED - needs a decision from you before it needs code.
+'CORRECT' used to appear here. It was removed on 2026-08-18 because it claimed more than any evidence supported.</t>
       </text>
     </comment>
     <comment ref="J2" authorId="0" shapeId="0">
@@ -1233,7 +1255,7 @@
           <t>probes/sync-identity.probe.test.ts</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -1378,9 +1400,9 @@
           <t>probes/bonds-and-freshness.probe.test.ts</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
@@ -1466,9 +1488,9 @@
           <t>probes/bonds-and-freshness.probe.test.ts</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>YOUR CALL</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr"/>
@@ -1555,9 +1577,9 @@
           <t>Calculation Module code/probes/broken-family.probe.test.ts</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr"/>
@@ -1649,9 +1671,9 @@
           <t>probes/sync-identity.probe.test.ts</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>YOUR CALL</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr"/>
@@ -1748,7 +1770,7 @@
           <t>probes/unknown-activity-types.probe.test.ts</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -1908,7 +1930,7 @@
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -2000,9 +2022,9 @@
           <t>probes/sync-identity.probe.test.ts</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr"/>
@@ -2086,7 +2108,7 @@
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" s="24" t="inlineStr">
         <is>
           <t>UNRESOLVED</t>
         </is>
@@ -2476,9 +2498,9 @@
           <t>probes/account-breakdown.probe.test.ts</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr"/>
@@ -2661,7 +2683,7 @@
           <t>probes/account-breakdown.probe.test.ts</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -2761,9 +2783,9 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr"/>
@@ -2898,9 +2920,9 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr"/>
@@ -3085,9 +3107,9 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>YOUR CALL</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr"/>
@@ -3220,9 +3242,9 @@
           <t>probes/account-breakdown.probe.test.ts</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>YOUR CALL</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr"/>
@@ -3357,9 +3379,9 @@
           <t>probes/bonds-and-freshness.probe.test.ts</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr"/>
@@ -3443,9 +3465,9 @@
           <t>probes/bonds-and-freshness.probe.test.ts</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr"/>
@@ -3530,9 +3552,9 @@
           <t>probes/bonds-and-freshness.probe.test.ts</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I39" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr"/>
@@ -3716,9 +3738,9 @@
           <t>probes/debt.probe.test.ts</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I42" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr"/>
@@ -3917,7 +3939,7 @@
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr"/>
-      <c r="I45" s="3" t="inlineStr">
+      <c r="I45" s="9" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -4018,7 +4040,7 @@
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr"/>
-      <c r="I46" s="3" t="inlineStr">
+      <c r="I46" s="9" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -4114,9 +4136,9 @@
           <t>probes/history-snapshots.probe.test.ts</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I47" s="24" t="inlineStr">
+        <is>
+          <t>YOUR CALL</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr"/>
@@ -4428,9 +4450,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr"/>
@@ -4511,9 +4533,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I52" s="24" t="inlineStr">
+        <is>
+          <t>YOUR CALL</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr"/>
@@ -4593,9 +4615,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I53" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr"/>
@@ -4675,9 +4697,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr"/>
@@ -4759,9 +4781,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr"/>
@@ -4843,9 +4865,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I56" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr"/>
@@ -4928,9 +4950,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr"/>
@@ -5065,9 +5087,9 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I59" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr"/>
@@ -5152,9 +5174,9 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr"/>
@@ -5235,9 +5257,9 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I61" s="24" t="inlineStr">
+        <is>
+          <t>YOUR CALL</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr"/>
@@ -5326,9 +5348,9 @@
           <t>probes/performance-lot-math.probe.test.ts</t>
         </is>
       </c>
-      <c r="I62" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I62" s="24" t="inlineStr">
+        <is>
+          <t>YOUR CALL</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr"/>
@@ -5414,9 +5436,9 @@
           <t>probes/performance-lot-math.probe.test.ts</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I63" s="24" t="inlineStr">
+        <is>
+          <t>YOUR CALL</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr"/>
@@ -5500,9 +5522,9 @@
           <t>probes/performance-lot-math.probe.test.ts</t>
         </is>
       </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J64" s="3" t="inlineStr"/>
@@ -5587,9 +5609,9 @@
           <t>probes/performance-lot-math.probe.test.ts</t>
         </is>
       </c>
-      <c r="I65" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I65" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr"/>
@@ -5672,9 +5694,9 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I66" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I66" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr"/>
@@ -5758,9 +5780,9 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I67" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I67" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr"/>
@@ -5840,9 +5862,9 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I68" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr"/>
@@ -5926,9 +5948,9 @@
           <t>probes/performance-lot-math.probe.test.ts</t>
         </is>
       </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I69" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr"/>
@@ -6009,9 +6031,9 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I70" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I70" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr"/>
@@ -6096,9 +6118,9 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I71" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I71" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr"/>
@@ -6184,9 +6206,9 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I72" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I72" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr"/>
@@ -6271,9 +6293,9 @@
           <t>probes/performance-lot-math.probe.test.ts</t>
         </is>
       </c>
-      <c r="I73" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr"/>
@@ -6355,9 +6377,9 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I74" s="24" t="inlineStr">
+        <is>
+          <t>YOUR CALL</t>
         </is>
       </c>
       <c r="J74" s="3" t="inlineStr"/>
@@ -6441,9 +6463,9 @@
           <t>probes/performance-lot-math.probe.test.ts</t>
         </is>
       </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I75" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J75" s="3" t="inlineStr"/>
@@ -6532,9 +6554,9 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I76" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J76" s="3" t="inlineStr"/>
@@ -6864,9 +6886,9 @@
           <t>probes/retirement-engine.probe.test.ts</t>
         </is>
       </c>
-      <c r="I82" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I82" s="24" t="inlineStr">
+        <is>
+          <t>YOUR CALL</t>
         </is>
       </c>
       <c r="J82" s="3" t="inlineStr"/>
@@ -6946,9 +6968,9 @@
           <t>probes/retirement-engine.probe.test.ts</t>
         </is>
       </c>
-      <c r="I83" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J83" s="3" t="inlineStr"/>
@@ -7043,9 +7065,9 @@
           <t>probes/retirement-engine.probe.test.ts</t>
         </is>
       </c>
-      <c r="I84" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J84" s="3" t="inlineStr"/>
@@ -7129,9 +7151,9 @@
           <t>probes/retirement-engine.probe.test.ts</t>
         </is>
       </c>
-      <c r="I85" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I85" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J85" s="3" t="inlineStr"/>
@@ -7486,9 +7508,9 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I91" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I91" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J91" s="3" t="inlineStr"/>
@@ -7625,9 +7647,9 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I93" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I93" s="24" t="inlineStr">
+        <is>
+          <t>YOUR CALL</t>
         </is>
       </c>
       <c r="J93" s="3" t="inlineStr"/>
@@ -7713,7 +7735,7 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I94" s="3" t="inlineStr">
+      <c r="I94" s="9" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -7863,9 +7885,9 @@
           <t>probes/bonds-and-freshness.probe.test.ts</t>
         </is>
       </c>
-      <c r="I96" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I96" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J96" s="3" t="inlineStr"/>
@@ -7951,9 +7973,9 @@
           <t>probes/bonds-and-freshness.probe.test.ts</t>
         </is>
       </c>
-      <c r="I97" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I97" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J97" s="3" t="inlineStr"/>
@@ -8138,9 +8160,9 @@
           <t>probes/debt.probe.test.ts</t>
         </is>
       </c>
-      <c r="I100" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J100" s="3" t="inlineStr"/>
@@ -8220,9 +8242,9 @@
           <t>probes/history-snapshots.probe.test.ts</t>
         </is>
       </c>
-      <c r="I101" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I101" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J101" s="3" t="inlineStr"/>
@@ -8323,7 +8345,7 @@
           <t>probes/classification-crosspath.probe.test.ts</t>
         </is>
       </c>
-      <c r="I102" s="3" t="inlineStr">
+      <c r="I102" s="9" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -8415,9 +8437,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I103" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I103" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J103" s="3" t="inlineStr"/>
@@ -8501,9 +8523,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I104" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I104" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J104" s="3" t="inlineStr"/>
@@ -8584,9 +8606,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I105" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I105" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J105" s="3" t="inlineStr"/>
@@ -8667,9 +8689,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I106" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I106" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J106" s="3" t="inlineStr"/>
@@ -8749,9 +8771,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I107" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I107" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J107" s="3" t="inlineStr"/>
@@ -8833,9 +8855,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I108" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I108" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J108" s="3" t="inlineStr"/>
@@ -8919,9 +8941,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I109" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I109" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J109" s="3" t="inlineStr"/>
@@ -9007,9 +9029,9 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I110" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I110" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J110" s="3" t="inlineStr"/>
@@ -9096,9 +9118,9 @@
           <t>probes/performance-lot-math.probe.test.ts</t>
         </is>
       </c>
-      <c r="I111" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I111" s="24" t="inlineStr">
+        <is>
+          <t>YOUR CALL</t>
         </is>
       </c>
       <c r="J111" s="3" t="inlineStr"/>
@@ -9192,9 +9214,9 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I112" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I112" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J112" s="3" t="inlineStr"/>
@@ -9278,7 +9300,7 @@
         </is>
       </c>
       <c r="H113" s="3" t="inlineStr"/>
-      <c r="I113" s="3" t="inlineStr">
+      <c r="I113" s="9" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -9371,7 +9393,7 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I114" s="3" t="inlineStr">
+      <c r="I114" s="24" t="inlineStr">
         <is>
           <t>UNRESOLVED</t>
         </is>
@@ -9467,7 +9489,7 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I115" s="3" t="inlineStr">
+      <c r="I115" s="9" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -9558,9 +9580,9 @@
           <t>probes/retirement-engine.probe.test.ts</t>
         </is>
       </c>
-      <c r="I116" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I116" s="24" t="inlineStr">
+        <is>
+          <t>YOUR CALL</t>
         </is>
       </c>
       <c r="J116" s="3" t="inlineStr"/>
@@ -9641,9 +9663,9 @@
           <t>probes/retirement-engine.probe.test.ts</t>
         </is>
       </c>
-      <c r="I117" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I117" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J117" s="3" t="inlineStr"/>
@@ -9782,9 +9804,9 @@
           <t>probes/account-breakdown.probe.test.ts</t>
         </is>
       </c>
-      <c r="I119" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I119" s="25" t="inlineStr">
+        <is>
+          <t>CHECKED vs REAL DATA</t>
         </is>
       </c>
       <c r="J119" s="3" t="inlineStr"/>
@@ -9972,9 +9994,9 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I122" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I122" s="24" t="inlineStr">
+        <is>
+          <t>YOUR CALL</t>
         </is>
       </c>
       <c r="J122" s="3" t="inlineStr"/>
@@ -10059,9 +10081,9 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I123" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I123" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J123" s="3" t="inlineStr"/>
@@ -10200,9 +10222,9 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I125" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I125" s="24" t="inlineStr">
+        <is>
+          <t>YOUR CALL</t>
         </is>
       </c>
       <c r="J125" s="3" t="inlineStr"/>
@@ -10336,9 +10358,9 @@
           <t>probes/bonds-and-freshness.probe.test.ts</t>
         </is>
       </c>
-      <c r="I127" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I127" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J127" s="3" t="inlineStr"/>
@@ -10423,9 +10445,9 @@
           <t>probes/debt.probe.test.ts</t>
         </is>
       </c>
-      <c r="I128" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I128" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J128" s="3" t="inlineStr"/>
@@ -10511,9 +10533,9 @@
           <t>probes/debt.probe.test.ts</t>
         </is>
       </c>
-      <c r="I129" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I129" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J129" s="3" t="inlineStr"/>
@@ -10597,7 +10619,7 @@
           <t>probes/history-snapshots.probe.test.ts</t>
         </is>
       </c>
-      <c r="I130" s="3" t="inlineStr">
+      <c r="I130" s="9" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -10779,9 +10801,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I132" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I132" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J132" s="3" t="inlineStr"/>
@@ -10863,9 +10885,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I133" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I133" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J133" s="3" t="inlineStr"/>
@@ -10951,7 +10973,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I134" s="3" t="inlineStr">
+      <c r="I134" s="9" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -11042,9 +11064,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I135" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I135" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J135" s="3" t="inlineStr"/>
@@ -11130,9 +11152,9 @@
           <t>probes/performance-lot-math.probe.test.ts</t>
         </is>
       </c>
-      <c r="I136" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I136" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J136" s="3" t="inlineStr"/>
@@ -11273,9 +11295,9 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I138" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I138" s="24" t="inlineStr">
+        <is>
+          <t>YOUR CALL</t>
         </is>
       </c>
       <c r="J138" s="3" t="inlineStr"/>
@@ -11363,9 +11385,9 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I139" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I139" s="24" t="inlineStr">
+        <is>
+          <t>YOUR CALL</t>
         </is>
       </c>
       <c r="J139" s="3" t="inlineStr"/>
@@ -11503,9 +11525,9 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I141" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I141" s="25" t="inlineStr">
+        <is>
+          <t>CHECKED vs REAL DATA</t>
         </is>
       </c>
       <c r="J141" s="3" t="inlineStr"/>
@@ -11589,9 +11611,9 @@
           <t>probes/debt.probe.test.ts</t>
         </is>
       </c>
-      <c r="I142" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I142" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J142" s="3" t="inlineStr"/>
@@ -11674,9 +11696,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I143" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I143" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J143" s="3" t="inlineStr"/>
@@ -11762,9 +11784,9 @@
           <t>probes/performance-lot-math.probe.test.ts</t>
         </is>
       </c>
-      <c r="I144" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I144" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J144" s="3" t="inlineStr"/>
@@ -11908,9 +11930,9 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I146" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I146" s="24" t="inlineStr">
+        <is>
+          <t>YOUR CALL</t>
         </is>
       </c>
       <c r="J146" s="3" t="inlineStr"/>
@@ -12004,9 +12026,9 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I147" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I147" s="24" t="inlineStr">
+        <is>
+          <t>YOUR CALL</t>
         </is>
       </c>
       <c r="J147" s="3" t="inlineStr"/>
@@ -12140,9 +12162,9 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I149" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I149" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J149" s="3" t="inlineStr"/>
@@ -12322,9 +12344,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I152" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I152" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J152" s="3" t="inlineStr"/>
@@ -12405,9 +12427,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I153" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I153" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J153" s="3" t="inlineStr"/>
@@ -12494,9 +12516,9 @@
           <t>probes/performance-lot-math.probe.test.ts</t>
         </is>
       </c>
-      <c r="I154" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I154" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J154" s="3" t="inlineStr"/>
@@ -12627,9 +12649,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I156" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I156" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J156" s="3" t="inlineStr"/>
@@ -12760,9 +12782,9 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I158" s="3" t="inlineStr">
-        <is>
-          <t>CORRECT</t>
+      <c r="I158" s="8" t="inlineStr">
+        <is>
+          <t>PINNED</t>
         </is>
       </c>
       <c r="J158" s="3" t="inlineStr"/>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -5345,21 +5345,29 @@
       </c>
       <c r="H62" s="3" t="inlineStr">
         <is>
-          <t>probes/performance-lot-math.probe.test.ts</t>
+          <t>probes/holding-period.probe.test.ts</t>
         </is>
       </c>
       <c r="I62" s="24" t="inlineStr">
         <is>
-          <t>YOUR CALL</t>
-        </is>
-      </c>
-      <c r="J62" s="3" t="inlineStr"/>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>A gain is long-term only when the shares were held MORE THAN one year, counting from the day AFTER purchase. Sold on the one-year anniversary is SHORT term.</t>
+        </is>
+      </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L62" s="3" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>Found by Claude's v2 review, and it is worse than he described. Our code never looks at the DAY — it subtracts calendar month numbers, so anything bought in January and sold the following January counts as a full year however late in the month it was bought. Buy on 31 January, sell on 1 January: 335 days held, reported LONG term. The error reaches a full month and always runs the same way — toward the lower tax rate, which understates the bill, the mistake this sheet itself calls the worse one. FIX: count actual days. Long-term is more than 365 days from the day after purchase. Roughly ten minutes. Two further rules worth adding while it is open: an inherited holding is long-term however briefly it was held (common at this age), and a wash sale extends the holding period.</t>
+        </is>
+      </c>
       <c r="M62" s="5" t="inlineStr"/>
       <c r="N62" s="5" t="inlineStr"/>
       <c r="O62" s="6" t="inlineStr">

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -75,7 +75,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -135,16 +135,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFDF0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6EAD9"/>
       </patternFill>
     </fill>
   </fills>
@@ -218,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -281,12 +271,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -413,13 +397,7 @@
     </comment>
     <comment ref="I2" authorId="0" shapeId="0">
       <text>
-        <t>HOW MUCH DO WE ACTUALLY KNOW ABOUT THIS ROW?
-CHECKED vs REAL DATA - compared against a real institution file or statement. The only level that shows the number is RIGHT rather than merely consistent with itself.
-PINNED - a test runs the real code and confirms it does what this row says. That proves the DESCRIPTION is true. It does NOT prove the behaviour is what it should be.
-YOUR CALL - pinned, but resting on a number or rule WE chose, which a reasonable person could choose differently. Not a defect: a decision worth your eye.
-DEFECT - I believe this is wrong. WHAT IT SHOULD BE and RECOMMENDED FIX say why and what to do.
-UNRESOLVED - needs a decision from you before it needs code.
-'CORRECT' used to appear here. It was removed on 2026-08-18 because it claimed more than any evidence supported.</t>
+        <t>CORRECT · DEFECT · UNRESOLVED. What the code does today, judged against what it should do. Everything left of this column describes the code AS IT IS — including its bugs — because a probe can only execute what exists.</t>
       </text>
     </comment>
     <comment ref="J2" authorId="0" shapeId="0">
@@ -909,7 +887,7 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CALCULATION INVENTORY · Phase 1 — Net worth, Performance and the 8 screens they open · 158 calculations · generated from commit cf71d68 on 2026-08-17  ⚠ TREE WAS DIRTY. EVERY FORMULA HERE DESCRIBES THE CODE AS IT IS TODAY, BUGS INCLUDED — you cannot fix what you have not described, and a probe can only execute what exists. Where the current behaviour is wrong, Status says DEFECT and the corrected version sits in WHAT IT SHOULD BE; the difference between those two columns is the work list. GREY columns are generated from the code and overwritten on every regeneration — never edit them. CREAM columns are written by hand and preserved. THE TWO BLUE COLUMNS ARE YOURS - write your questions and your verdict there, and nothing I run will ever touch them. You can also attach an Excel comment to ANY cell on any tab; comments survive regeneration and I read them. A row is not documented until its probe passes.</t>
+          <t>CALCULATION INVENTORY · Phase 1 — Net worth, Performance and the 8 screens they open · 158 calculations · generated from commit cf71d68 on 2026-08-18  ⚠ TREE WAS DIRTY. EVERY FORMULA HERE DESCRIBES THE CODE AS IT IS TODAY, BUGS INCLUDED — you cannot fix what you have not described, and a probe can only execute what exists. Where the current behaviour is wrong, Status says DEFECT and the corrected version sits in WHAT IT SHOULD BE; the difference between those two columns is the work list. GREY columns are generated from the code and overwritten on every regeneration — never edit them. CREAM columns are written by hand and preserved. THE TWO BLUE COLUMNS ARE YOURS - write your questions and your verdict there, and nothing I run will ever touch them. You can also attach an Excel comment to ANY cell on any tab; comments survive regeneration and I read them. A row is not documented until its probe passes.</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1233,7 @@
           <t>probes/sync-identity.probe.test.ts</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -1400,7 +1378,7 @@
           <t>probes/bonds-and-freshness.probe.test.ts</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -1488,7 +1466,7 @@
           <t>probes/bonds-and-freshness.probe.test.ts</t>
         </is>
       </c>
-      <c r="I10" s="24" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>YOUR CALL</t>
         </is>
@@ -1577,7 +1555,7 @@
           <t>Calculation Module code/probes/broken-family.probe.test.ts</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -1671,7 +1649,7 @@
           <t>probes/sync-identity.probe.test.ts</t>
         </is>
       </c>
-      <c r="I12" s="24" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>YOUR CALL</t>
         </is>
@@ -1770,7 +1748,7 @@
           <t>probes/unknown-activity-types.probe.test.ts</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -1930,7 +1908,7 @@
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -2022,7 +2000,7 @@
           <t>probes/sync-identity.probe.test.ts</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -2108,7 +2086,7 @@
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="24" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>UNRESOLVED</t>
         </is>
@@ -2498,7 +2476,7 @@
           <t>probes/account-breakdown.probe.test.ts</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -2544,21 +2522,53 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr"/>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>ACCOUNT_TYPE_FACTS</t>
+        </is>
+      </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
           <t>assetKind</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
-      <c r="D25" s="3" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr"/>
-      <c r="F25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>What do we know about this kind of account?  Answer: its label, the heading it appears under, its tax bucket and the return we assume for it — or nothing at all if the type is unrecognised.</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Look the type up in our own table. No match returns NOTHING rather than a stand-in, so a bad type shows as missing instead of quietly inheriting somebody else's return.</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>account type → id</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>OUR OWN TABLE — ASSET_KINDS in the code. Not from any institution and not from the market: a hand-maintained list of account types, each with a label, the heading it sits under on screen, and the long-run return we assume for it.</t>
+        </is>
+      </c>
       <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-remaining.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J25" s="3" t="inlineStr"/>
-      <c r="K25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L25" s="3" t="inlineStr"/>
       <c r="M25" s="5" t="inlineStr"/>
       <c r="N25" s="5" t="inlineStr"/>
@@ -2594,21 +2604,55 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr"/>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>ACCOUNT_SHARE_OF_TOTAL</t>
+        </is>
+      </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
           <t>buildAssetsState</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr"/>
-      <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>How much of everything sits in each account, and what return do they blend to?  Answer: a share of the total per account, the total itself, and one blended assumed return.</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Each account's share = its balance ÷ the total, so the shares add to 100. The blended return is weighted by money, not an average of the rates.
+No money at all → every share is 0 and a stated default return is used, rather than dividing by nothing.</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>each balance → balance
+each assumed return → target_return</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>The account's own record: what you typed on Add account, or what a broker sent at connect time. Balance comes from the broker's total, an uploaded file's value column, or the Balance box.</t>
+        </is>
+      </c>
       <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr"/>
-      <c r="I26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-remaining.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J26" s="3" t="inlineStr"/>
-      <c r="K26" s="3" t="inlineStr"/>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L26" s="3" t="inlineStr"/>
       <c r="M26" s="5" t="inlineStr"/>
       <c r="N26" s="5" t="inlineStr"/>
@@ -2683,7 +2727,7 @@
           <t>probes/account-breakdown.probe.test.ts</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -2783,7 +2827,7 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -2829,21 +2873,53 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr"/>
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>ITEMISED_TOTAL</t>
+        </is>
+      </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
           <t>itemizedTotal</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr"/>
-      <c r="D29" s="3" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>What do the named holdings inside this account add up to?  Answer: a dollar figure.</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Add the value of each itemised holding. Nothing itemised is zero.</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>each holding's value → items[].value</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Typed on the Itemise screen, or read from an uploaded file when the account was imported.</t>
+        </is>
+      </c>
       <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="inlineStr"/>
-      <c r="I29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-remaining.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J29" s="3" t="inlineStr"/>
-      <c r="K29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L29" s="3" t="inlineStr"/>
       <c r="M29" s="5" t="inlineStr"/>
       <c r="N29" s="5" t="inlineStr"/>
@@ -2920,7 +2996,7 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -2966,21 +3042,53 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr"/>
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>HOW_A_HOME_IS_USED</t>
+        </is>
+      </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
           <t>realEstateUseOf</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
-      <c r="D31" s="3" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr"/>
-      <c r="F31" s="3" t="inlineStr"/>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Is this the home they live in, a rental, a second home or land?  Answer: one of those four.</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Use what was chosen. Unanswered defaults to the home they live in — the cautious answer, because only a primary home is excluded from the retirement pot by default. Assuming a rental would quietly add a house to the money someone plans to live on.</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>the choice → re_use</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>The property question on the Add account and property screens — primary home, rental, second home or land. Nothing external supplies it: no institution knows which house you live in, and the answer changes whether that house counts toward your retirement money.</t>
+        </is>
+      </c>
       <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="3" t="inlineStr"/>
-      <c r="I31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-remaining.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J31" s="3" t="inlineStr"/>
-      <c r="K31" s="3" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr"/>
       <c r="M31" s="5" t="inlineStr"/>
       <c r="N31" s="5" t="inlineStr"/>
@@ -3016,21 +3124,55 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr"/>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>WHERE_THE_VALUE_CAME_FROM</t>
+        </is>
+      </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
           <t>sourceWording</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr"/>
-      <c r="D32" s="3" t="inlineStr"/>
-      <c r="E32" s="3" t="inlineStr"/>
-      <c r="F32" s="3" t="inlineStr"/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Where did this account's value come from, and when?  Answer: one short line — "Connected · 2026-08-18", "Imported · —", or "By hand · you update it".</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>A connected account shows the date of its last successful update. An imported one shows its import date. Anything else is hand-entered and says so plainly, including that keeping it current is the person's job.
+No source recorded means hand-entered — every account created before connections existed.</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>where it came from → source
+when it last updated → last_synced</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>The account's own record: what you typed on Add account, or what a broker sent at connect time. Balance comes from the broker's total, an uploaded file's value column, or the Balance box.</t>
+        </is>
+      </c>
       <c r="G32" s="3" t="inlineStr"/>
-      <c r="H32" s="3" t="inlineStr"/>
-      <c r="I32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-remaining.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J32" s="3" t="inlineStr"/>
-      <c r="K32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L32" s="3" t="inlineStr"/>
       <c r="M32" s="5" t="inlineStr"/>
       <c r="N32" s="5" t="inlineStr"/>
@@ -3107,7 +3249,7 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I33" s="24" t="inlineStr">
+      <c r="I33" s="3" t="inlineStr">
         <is>
           <t>YOUR CALL</t>
         </is>
@@ -3153,21 +3295,53 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr"/>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>NET_WORTH_GROUPING</t>
+        </is>
+      </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
           <t>uberGroupRows</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="3" t="inlineStr"/>
-      <c r="E34" s="3" t="inlineStr"/>
-      <c r="F34" s="3" t="inlineStr"/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>How are the classes grouped on the Net worth screen?  Answer: a list of groups, each with its own classes and a total.</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Put each class into its group, add the classes inside it, and DROP any group with nothing in it — so a person with no property never sees an empty Property heading reading $0.</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>the class rows → classRows</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Derived from ALLOCATION_BY_CLASS; the grouping itself is our own arrangement, not an institution's.</t>
+        </is>
+      </c>
       <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-remaining.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J34" s="3" t="inlineStr"/>
-      <c r="K34" s="3" t="inlineStr"/>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L34" s="3" t="inlineStr"/>
       <c r="M34" s="5" t="inlineStr"/>
       <c r="N34" s="5" t="inlineStr"/>
@@ -3242,7 +3416,7 @@
           <t>probes/account-breakdown.probe.test.ts</t>
         </is>
       </c>
-      <c r="I35" s="24" t="inlineStr">
+      <c r="I35" s="3" t="inlineStr">
         <is>
           <t>YOUR CALL</t>
         </is>
@@ -3288,21 +3462,54 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr"/>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TAX_TYPE_TO_ACCOUNT</t>
+        </is>
+      </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
           <t>wrapperAccount</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="3" t="inlineStr"/>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>The person picked how this account is taxed — what does that make it?  Answer: an account type and a tax treatment together.</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Taxable → a brokerage, taxed normally. 401(k) → pre-tax. Traditional IRA → pre-tax. Roth → tax already paid. HSA → pre-tax.
+Anything unanswered falls back to TAXABLE, the cautious side: it assumes tax is owed rather than assuming it is not.</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>the choice → w</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>The tax-type question on Add account. No institution supplies this reliably.</t>
+        </is>
+      </c>
       <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-remaining.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J36" s="3" t="inlineStr"/>
-      <c r="K36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L36" s="3" t="inlineStr"/>
       <c r="M36" s="5" t="inlineStr"/>
       <c r="N36" s="5" t="inlineStr"/>
@@ -3379,7 +3586,7 @@
           <t>probes/bonds-and-freshness.probe.test.ts</t>
         </is>
       </c>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="I37" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -3465,7 +3672,7 @@
           <t>probes/bonds-and-freshness.probe.test.ts</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="I38" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -3552,7 +3759,7 @@
           <t>probes/bonds-and-freshness.probe.test.ts</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="I39" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -3738,7 +3945,7 @@
           <t>probes/debt.probe.test.ts</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr">
+      <c r="I42" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -3939,7 +4146,7 @@
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr"/>
-      <c r="I45" s="9" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -4040,7 +4247,7 @@
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr"/>
-      <c r="I46" s="9" t="inlineStr">
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -4136,7 +4343,7 @@
           <t>probes/history-snapshots.probe.test.ts</t>
         </is>
       </c>
-      <c r="I47" s="24" t="inlineStr">
+      <c r="I47" s="3" t="inlineStr">
         <is>
           <t>YOUR CALL</t>
         </is>
@@ -4450,7 +4657,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="I51" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -4533,7 +4740,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I52" s="24" t="inlineStr">
+      <c r="I52" s="3" t="inlineStr">
         <is>
           <t>YOUR CALL</t>
         </is>
@@ -4615,7 +4822,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I53" s="8" t="inlineStr">
+      <c r="I53" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -4697,7 +4904,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I54" s="8" t="inlineStr">
+      <c r="I54" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -4781,7 +4988,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I55" s="8" t="inlineStr">
+      <c r="I55" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -4865,7 +5072,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I56" s="8" t="inlineStr">
+      <c r="I56" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -4950,7 +5157,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I57" s="8" t="inlineStr">
+      <c r="I57" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -5087,7 +5294,7 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I59" s="8" t="inlineStr">
+      <c r="I59" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -5174,7 +5381,7 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I60" s="8" t="inlineStr">
+      <c r="I60" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -5257,7 +5464,7 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I61" s="24" t="inlineStr">
+      <c r="I61" s="3" t="inlineStr">
         <is>
           <t>YOUR CALL</t>
         </is>
@@ -5348,7 +5555,7 @@
           <t>probes/holding-period.probe.test.ts</t>
         </is>
       </c>
-      <c r="I62" s="24" t="inlineStr">
+      <c r="I62" s="3" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -5444,7 +5651,7 @@
           <t>probes/performance-lot-math.probe.test.ts</t>
         </is>
       </c>
-      <c r="I63" s="24" t="inlineStr">
+      <c r="I63" s="3" t="inlineStr">
         <is>
           <t>YOUR CALL</t>
         </is>
@@ -5530,7 +5737,7 @@
           <t>probes/performance-lot-math.probe.test.ts</t>
         </is>
       </c>
-      <c r="I64" s="8" t="inlineStr">
+      <c r="I64" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -5617,7 +5824,7 @@
           <t>probes/performance-lot-math.probe.test.ts</t>
         </is>
       </c>
-      <c r="I65" s="8" t="inlineStr">
+      <c r="I65" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -5702,7 +5909,7 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I66" s="8" t="inlineStr">
+      <c r="I66" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -5788,7 +5995,7 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I67" s="8" t="inlineStr">
+      <c r="I67" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -5870,7 +6077,7 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I68" s="8" t="inlineStr">
+      <c r="I68" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -5956,7 +6163,7 @@
           <t>probes/performance-lot-math.probe.test.ts</t>
         </is>
       </c>
-      <c r="I69" s="8" t="inlineStr">
+      <c r="I69" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -6039,7 +6246,7 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I70" s="8" t="inlineStr">
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -6126,7 +6333,7 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I71" s="8" t="inlineStr">
+      <c r="I71" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -6214,7 +6421,7 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I72" s="8" t="inlineStr">
+      <c r="I72" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -6301,7 +6508,7 @@
           <t>probes/performance-lot-math.probe.test.ts</t>
         </is>
       </c>
-      <c r="I73" s="8" t="inlineStr">
+      <c r="I73" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -6385,7 +6592,7 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I74" s="24" t="inlineStr">
+      <c r="I74" s="3" t="inlineStr">
         <is>
           <t>YOUR CALL</t>
         </is>
@@ -6471,7 +6678,7 @@
           <t>probes/performance-lot-math.probe.test.ts</t>
         </is>
       </c>
-      <c r="I75" s="8" t="inlineStr">
+      <c r="I75" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -6562,7 +6769,7 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I76" s="8" t="inlineStr">
+      <c r="I76" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -6894,7 +7101,7 @@
           <t>probes/retirement-engine.probe.test.ts</t>
         </is>
       </c>
-      <c r="I82" s="24" t="inlineStr">
+      <c r="I82" s="3" t="inlineStr">
         <is>
           <t>YOUR CALL</t>
         </is>
@@ -6976,7 +7183,7 @@
           <t>probes/retirement-engine.probe.test.ts</t>
         </is>
       </c>
-      <c r="I83" s="8" t="inlineStr">
+      <c r="I83" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -7073,7 +7280,7 @@
           <t>probes/retirement-engine.probe.test.ts</t>
         </is>
       </c>
-      <c r="I84" s="8" t="inlineStr">
+      <c r="I84" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -7159,7 +7366,7 @@
           <t>probes/retirement-engine.probe.test.ts</t>
         </is>
       </c>
-      <c r="I85" s="8" t="inlineStr">
+      <c r="I85" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -7516,7 +7723,7 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I91" s="8" t="inlineStr">
+      <c r="I91" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -7655,7 +7862,7 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I93" s="24" t="inlineStr">
+      <c r="I93" s="3" t="inlineStr">
         <is>
           <t>YOUR CALL</t>
         </is>
@@ -7743,7 +7950,7 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I94" s="9" t="inlineStr">
+      <c r="I94" s="3" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -7797,21 +8004,55 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="inlineStr"/>
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>ITEMISED_REMAINDER</t>
+        </is>
+      </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
           <t>itemizeRemainder</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr"/>
-      <c r="D95" s="3" t="inlineStr"/>
-      <c r="E95" s="3" t="inlineStr"/>
-      <c r="F95" s="3" t="inlineStr"/>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>How much of the typed total is still unaccounted for?  Answer: a dollar figure, which may be NEGATIVE.</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>the typed account total − the itemised holdings.
+A NEGATIVE remainder means the named holdings are worth more than the total that was typed — the original estimate was low. That is a real fact about the account and it is shown, not floored at zero, because hiding it would leave a person's own figures silently disagreeing.</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>the typed total → lumpBalance
+the holdings → items</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="inlineStr">
+        <is>
+          <t>The account's own record: what you typed on Add account, or what a broker sent at connect time. Balance comes from the broker's total, an uploaded file's value column, or the Balance box.</t>
+        </is>
+      </c>
       <c r="G95" s="3" t="inlineStr"/>
-      <c r="H95" s="3" t="inlineStr"/>
-      <c r="I95" s="3" t="inlineStr"/>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-remaining.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J95" s="3" t="inlineStr"/>
-      <c r="K95" s="3" t="inlineStr"/>
+      <c r="K95" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L95" s="3" t="inlineStr"/>
       <c r="M95" s="5" t="inlineStr"/>
       <c r="N95" s="5" t="inlineStr"/>
@@ -7893,7 +8134,7 @@
           <t>probes/bonds-and-freshness.probe.test.ts</t>
         </is>
       </c>
-      <c r="I96" s="8" t="inlineStr">
+      <c r="I96" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -7981,7 +8222,7 @@
           <t>probes/bonds-and-freshness.probe.test.ts</t>
         </is>
       </c>
-      <c r="I97" s="8" t="inlineStr">
+      <c r="I97" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -8168,7 +8409,7 @@
           <t>probes/debt.probe.test.ts</t>
         </is>
       </c>
-      <c r="I100" s="8" t="inlineStr">
+      <c r="I100" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -8250,7 +8491,7 @@
           <t>probes/history-snapshots.probe.test.ts</t>
         </is>
       </c>
-      <c r="I101" s="8" t="inlineStr">
+      <c r="I101" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -8353,7 +8594,7 @@
           <t>probes/classification-crosspath.probe.test.ts</t>
         </is>
       </c>
-      <c r="I102" s="9" t="inlineStr">
+      <c r="I102" s="3" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -8445,7 +8686,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I103" s="8" t="inlineStr">
+      <c r="I103" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -8531,7 +8772,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I104" s="8" t="inlineStr">
+      <c r="I104" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -8614,7 +8855,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I105" s="8" t="inlineStr">
+      <c r="I105" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -8697,7 +8938,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I106" s="8" t="inlineStr">
+      <c r="I106" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -8779,7 +9020,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I107" s="8" t="inlineStr">
+      <c r="I107" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -8863,7 +9104,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I108" s="8" t="inlineStr">
+      <c r="I108" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -8949,7 +9190,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I109" s="8" t="inlineStr">
+      <c r="I109" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -9037,7 +9278,7 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I110" s="8" t="inlineStr">
+      <c r="I110" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -9126,7 +9367,7 @@
           <t>probes/performance-lot-math.probe.test.ts</t>
         </is>
       </c>
-      <c r="I111" s="24" t="inlineStr">
+      <c r="I111" s="3" t="inlineStr">
         <is>
           <t>YOUR CALL</t>
         </is>
@@ -9222,7 +9463,7 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I112" s="8" t="inlineStr">
+      <c r="I112" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -9308,7 +9549,7 @@
         </is>
       </c>
       <c r="H113" s="3" t="inlineStr"/>
-      <c r="I113" s="9" t="inlineStr">
+      <c r="I113" s="3" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -9401,7 +9642,7 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I114" s="24" t="inlineStr">
+      <c r="I114" s="3" t="inlineStr">
         <is>
           <t>UNRESOLVED</t>
         </is>
@@ -9497,7 +9738,7 @@
           <t>probes/performance-portfolio.probe.test.ts</t>
         </is>
       </c>
-      <c r="I115" s="9" t="inlineStr">
+      <c r="I115" s="3" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -9588,7 +9829,7 @@
           <t>probes/retirement-engine.probe.test.ts</t>
         </is>
       </c>
-      <c r="I116" s="24" t="inlineStr">
+      <c r="I116" s="3" t="inlineStr">
         <is>
           <t>YOUR CALL</t>
         </is>
@@ -9671,7 +9912,7 @@
           <t>probes/retirement-engine.probe.test.ts</t>
         </is>
       </c>
-      <c r="I117" s="8" t="inlineStr">
+      <c r="I117" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -9717,21 +9958,56 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="inlineStr"/>
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>CAN_HOLD_TICKERS</t>
+        </is>
+      </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
           <t>accountAllowsTicker</t>
         </is>
       </c>
-      <c r="C118" s="3" t="inlineStr"/>
-      <c r="D118" s="3" t="inlineStr"/>
-      <c r="E118" s="3" t="inlineStr"/>
-      <c r="F118" s="3" t="inlineStr"/>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>Can shares be tracked in this account?  Answers: yes · no.</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>No for property and plain cash accounts. No for a 529 — that money is not the household's to trade. No for checking or savings. No for a dedicated bond or alternatives account, which holds those instruments rather than shares. Yes for everything else.
+It decides whether an account appears as somewhere to put a stock, so a wrong answer offers a place that makes no sense.</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>tax bucket → tax_bucket
+account type → kind
+its class → assetClassOf</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="inlineStr">
+        <is>
+          <t>The account's own record: what you typed on Add account, or what a broker sent at connect time. Balance comes from the broker's total, an uploaded file's value column, or the Balance box.</t>
+        </is>
+      </c>
       <c r="G118" s="3" t="inlineStr"/>
-      <c r="H118" s="3" t="inlineStr"/>
-      <c r="I118" s="3" t="inlineStr"/>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-remaining.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I118" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J118" s="3" t="inlineStr"/>
-      <c r="K118" s="3" t="inlineStr"/>
+      <c r="K118" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L118" s="3" t="inlineStr"/>
       <c r="M118" s="5" t="inlineStr"/>
       <c r="N118" s="5" t="inlineStr"/>
@@ -9812,7 +10088,7 @@
           <t>probes/account-breakdown.probe.test.ts</t>
         </is>
       </c>
-      <c r="I119" s="25" t="inlineStr">
+      <c r="I119" s="3" t="inlineStr">
         <is>
           <t>CHECKED vs REAL DATA</t>
         </is>
@@ -10002,7 +10278,7 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I122" s="24" t="inlineStr">
+      <c r="I122" s="3" t="inlineStr">
         <is>
           <t>YOUR CALL</t>
         </is>
@@ -10089,7 +10365,7 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I123" s="8" t="inlineStr">
+      <c r="I123" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -10230,7 +10506,7 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I125" s="24" t="inlineStr">
+      <c r="I125" s="3" t="inlineStr">
         <is>
           <t>YOUR CALL</t>
         </is>
@@ -10366,7 +10642,7 @@
           <t>probes/bonds-and-freshness.probe.test.ts</t>
         </is>
       </c>
-      <c r="I127" s="8" t="inlineStr">
+      <c r="I127" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -10453,7 +10729,7 @@
           <t>probes/debt.probe.test.ts</t>
         </is>
       </c>
-      <c r="I128" s="8" t="inlineStr">
+      <c r="I128" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -10541,7 +10817,7 @@
           <t>probes/debt.probe.test.ts</t>
         </is>
       </c>
-      <c r="I129" s="8" t="inlineStr">
+      <c r="I129" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -10627,7 +10903,7 @@
           <t>probes/history-snapshots.probe.test.ts</t>
         </is>
       </c>
-      <c r="I130" s="9" t="inlineStr">
+      <c r="I130" s="3" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -10809,7 +11085,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I132" s="8" t="inlineStr">
+      <c r="I132" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -10893,7 +11169,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I133" s="8" t="inlineStr">
+      <c r="I133" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -10981,7 +11257,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I134" s="9" t="inlineStr">
+      <c r="I134" s="3" t="inlineStr">
         <is>
           <t>DEFECT</t>
         </is>
@@ -11072,7 +11348,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I135" s="8" t="inlineStr">
+      <c r="I135" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -11160,7 +11436,7 @@
           <t>probes/performance-lot-math.probe.test.ts</t>
         </is>
       </c>
-      <c r="I136" s="8" t="inlineStr">
+      <c r="I136" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -11303,7 +11579,7 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I138" s="24" t="inlineStr">
+      <c r="I138" s="3" t="inlineStr">
         <is>
           <t>YOUR CALL</t>
         </is>
@@ -11393,7 +11669,7 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I139" s="24" t="inlineStr">
+      <c r="I139" s="3" t="inlineStr">
         <is>
           <t>YOUR CALL</t>
         </is>
@@ -11533,7 +11809,7 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I141" s="25" t="inlineStr">
+      <c r="I141" s="3" t="inlineStr">
         <is>
           <t>CHECKED vs REAL DATA</t>
         </is>
@@ -11619,7 +11895,7 @@
           <t>probes/debt.probe.test.ts</t>
         </is>
       </c>
-      <c r="I142" s="8" t="inlineStr">
+      <c r="I142" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -11704,7 +11980,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I143" s="8" t="inlineStr">
+      <c r="I143" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -11792,7 +12068,7 @@
           <t>probes/performance-lot-math.probe.test.ts</t>
         </is>
       </c>
-      <c r="I144" s="8" t="inlineStr">
+      <c r="I144" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -11938,7 +12214,7 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I146" s="24" t="inlineStr">
+      <c r="I146" s="3" t="inlineStr">
         <is>
           <t>YOUR CALL</t>
         </is>
@@ -12034,7 +12310,7 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I147" s="24" t="inlineStr">
+      <c r="I147" s="3" t="inlineStr">
         <is>
           <t>YOUR CALL</t>
         </is>
@@ -12080,21 +12356,56 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="3" t="inlineStr"/>
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>REPORTED_RETURN</t>
+        </is>
+      </c>
       <c r="B148" s="4" t="inlineStr">
         <is>
           <t>portfolioActualReturn</t>
         </is>
       </c>
-      <c r="C148" s="3" t="inlineStr"/>
-      <c r="D148" s="3" t="inlineStr"/>
-      <c r="E148" s="3" t="inlineStr"/>
-      <c r="F148" s="3" t="inlineStr"/>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>What return did the person say they actually earned over the past year?  Answer: one rate, or NOTHING when nobody has reported one.</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>Weighted by the share of each account that counts toward retirement: Σ(reported rate × that money) ÷ Σ(that money). Property is left out — a house has no trailing-year return to report.
+Nobody reported one → NOTHING, so the screen can ask rather than showing a confident 0%.</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>each account's reported rate → actual_ttm
+the share of it counted toward retirement → RETIREMENT_SHARE_AMOUNT</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>The account's own record: what you typed on Add account, or what a broker sent at connect time. Balance comes from the broker's total, an uploaded file's value column, or the Balance box.
+actual_ttm is TYPED by the person — no institution sends a trailing-year return on any road we have.</t>
+        </is>
+      </c>
       <c r="G148" s="3" t="inlineStr"/>
-      <c r="H148" s="3" t="inlineStr"/>
-      <c r="I148" s="3" t="inlineStr"/>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-remaining.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I148" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J148" s="3" t="inlineStr"/>
-      <c r="K148" s="3" t="inlineStr"/>
+      <c r="K148" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L148" s="3" t="inlineStr"/>
       <c r="M148" s="5" t="inlineStr"/>
       <c r="N148" s="5" t="inlineStr"/>
@@ -12170,7 +12481,7 @@
           <t>probes/assets-classification.probe.test.ts</t>
         </is>
       </c>
-      <c r="I149" s="8" t="inlineStr">
+      <c r="I149" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -12352,7 +12663,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I152" s="8" t="inlineStr">
+      <c r="I152" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -12435,7 +12746,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I153" s="8" t="inlineStr">
+      <c r="I153" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -12524,7 +12835,7 @@
           <t>probes/performance-lot-math.probe.test.ts</t>
         </is>
       </c>
-      <c r="I154" s="8" t="inlineStr">
+      <c r="I154" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -12657,7 +12968,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I156" s="8" t="inlineStr">
+      <c r="I156" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -12790,7 +13101,7 @@
           <t>probes/income-tax.probe.test.ts</t>
         </is>
       </c>
-      <c r="I158" s="8" t="inlineStr">
+      <c r="I158" s="3" t="inlineStr">
         <is>
           <t>PINNED</t>
         </is>
@@ -14064,7 +14375,7 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>TRANSLATE_BROKER_WORD · INGEST_DEDUPE · NW_CHANGE_WALK · the money-weighted return</t>
+          <t>INGEST_ACTIVITY_TYPE · INGEST_DEDUPE · NW_CHANGE_WALK · the money-weighted return</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr"/>
@@ -14665,15 +14976,6 @@
           <t>A · THE FIELDS — where each number lives, per institution</t>
         </is>
       </c>
-      <c r="B3" s="18" t="n"/>
-      <c r="C3" s="18" t="n"/>
-      <c r="D3" s="18" t="n"/>
-      <c r="E3" s="18" t="n"/>
-      <c r="F3" s="18" t="n"/>
-      <c r="G3" s="18" t="n"/>
-      <c r="H3" s="18" t="n"/>
-      <c r="I3" s="18" t="n"/>
-      <c r="J3" s="19" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
@@ -15497,15 +15799,6 @@
           <t>B · THE TRANSACTION WORDS — what each institution calls each kind of event. This is the table the $1.4m and the $2,387 both came from.</t>
         </is>
       </c>
-      <c r="B21" s="18" t="n"/>
-      <c r="C21" s="18" t="n"/>
-      <c r="D21" s="18" t="n"/>
-      <c r="E21" s="18" t="n"/>
-      <c r="F21" s="18" t="n"/>
-      <c r="G21" s="18" t="n"/>
-      <c r="H21" s="18" t="n"/>
-      <c r="I21" s="18" t="n"/>
-      <c r="J21" s="19" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
@@ -16041,15 +16334,6 @@
           <t>C · THE ACCOUNT DETAIL PAGE — every input that page shows, and which road supplies it. Enumerated from the shipping screen, not from memory.</t>
         </is>
       </c>
-      <c r="B33" s="18" t="n"/>
-      <c r="C33" s="18" t="n"/>
-      <c r="D33" s="18" t="n"/>
-      <c r="E33" s="18" t="n"/>
-      <c r="F33" s="18" t="n"/>
-      <c r="G33" s="18" t="n"/>
-      <c r="H33" s="18" t="n"/>
-      <c r="I33" s="18" t="n"/>
-      <c r="J33" s="19" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="21" t="inlineStr">
@@ -16393,15 +16677,6 @@
           <t>D · THE HOLDING DETAIL PAGE, BY ASSET CLASS — shares and funds, bonds and CDs, options, crypto, cash. A dash means NO institution supplies it on any road — it is our feed or our assumption, and it belongs here precisely because it looks like institution data.</t>
         </is>
       </c>
-      <c r="B41" s="18" t="n"/>
-      <c r="C41" s="18" t="n"/>
-      <c r="D41" s="18" t="n"/>
-      <c r="E41" s="18" t="n"/>
-      <c r="F41" s="18" t="n"/>
-      <c r="G41" s="18" t="n"/>
-      <c r="H41" s="18" t="n"/>
-      <c r="I41" s="18" t="n"/>
-      <c r="J41" s="19" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="21" t="inlineStr">

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -6815,21 +6815,54 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr"/>
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>ODDS_SENTENCE</t>
+        </is>
+      </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
           <t>oddsLine</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr"/>
-      <c r="D77" s="3" t="inlineStr"/>
-      <c r="E77" s="3" t="inlineStr"/>
-      <c r="F77" s="3" t="inlineStr"/>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>How do we state the odds in words?  Answer: one sentence — "82% odds of lasting to age 92".</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>The chance, then the age it is measured to. THE AGE IS NEVER LEFT OFF: 82% lasting to 92 and 82% lasting to 100 are completely different plans, and a bare percentage lets a person read the better one.</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>the chance → chance
+the age it must last to → horizonAge</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>The odds come from WILL_IT_LAST, which is built on everything else in this workbook. See that row for where each of its inputs comes from.</t>
+        </is>
+      </c>
       <c r="G77" s="3" t="inlineStr"/>
-      <c r="H77" s="3" t="inlineStr"/>
-      <c r="I77" s="3" t="inlineStr"/>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t>probes/planning-words.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J77" s="3" t="inlineStr"/>
-      <c r="K77" s="3" t="inlineStr"/>
+      <c r="K77" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L77" s="3" t="inlineStr"/>
       <c r="M77" s="5" t="inlineStr"/>
       <c r="N77" s="5" t="inlineStr"/>
@@ -6865,21 +6898,60 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="inlineStr"/>
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>ARE_YOU_ON_COURSE</t>
+        </is>
+      </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
           <t>onCourseSentence</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr"/>
-      <c r="D78" s="3" t="inlineStr"/>
-      <c r="E78" s="3" t="inlineStr"/>
-      <c r="F78" s="3" t="inlineStr"/>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>In one sentence, how is this plan doing?  Answer: a sentence — or NOTHING when the odds have not been worked out yet.</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Reads the odds, the pot at retirement, what is left at the end, and the age the money runs out if it does, and states the position in one line.
+No odds yet → NO sentence. Nothing is invented to fill the space.
+A plan that falls short names the age it runs out, so the sentence carries something to act on.</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>the odds → chance
+retirement age → retireAge
+the age it must last to → horizonAge
+the pot at retirement → potAtRetire
+what is left at the end → leftoverAtHorizon
+the age it runs out → shortfallAge</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>The odds come from WILL_IT_LAST, which is built on everything else in this workbook. See that row for where each of its inputs comes from.</t>
+        </is>
+      </c>
       <c r="G78" s="3" t="inlineStr"/>
-      <c r="H78" s="3" t="inlineStr"/>
-      <c r="I78" s="3" t="inlineStr"/>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>probes/planning-words.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J78" s="3" t="inlineStr"/>
-      <c r="K78" s="3" t="inlineStr"/>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L78" s="3" t="inlineStr"/>
       <c r="M78" s="5" t="inlineStr"/>
       <c r="N78" s="5" t="inlineStr"/>
@@ -6915,21 +6987,54 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr"/>
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>SAMPLE_ASK_SENTENCE</t>
+        </is>
+      </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
           <t>sampleAskLine</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr"/>
-      <c r="D79" s="3" t="inlineStr"/>
-      <c r="E79" s="3" t="inlineStr"/>
-      <c r="F79" s="3" t="inlineStr"/>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>What do we ask for to turn the sample into their own number?  Answer: one sentence naming exactly what is missing, and how many answers it takes.</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>One thing missing: "a sample, not your number — add your age and it becomes yours". More than one: it says how many and lists them.
+The VERB fits the question — you CHOOSE what counts toward retirement, you ADD your age. Nothing missing produces no sentence at all rather than an empty prompt.</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>what is still missing → missing</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding and Plan answers — age, what you expect to spend, and which accounts count toward retirement. Nothing external supplies any of it.</t>
+        </is>
+      </c>
       <c r="G79" s="3" t="inlineStr"/>
-      <c r="H79" s="3" t="inlineStr"/>
-      <c r="I79" s="3" t="inlineStr"/>
+      <c r="H79" s="3" t="inlineStr">
+        <is>
+          <t>probes/planning-words.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J79" s="3" t="inlineStr"/>
-      <c r="K79" s="3" t="inlineStr"/>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L79" s="3" t="inlineStr"/>
       <c r="M79" s="5" t="inlineStr"/>
       <c r="N79" s="5" t="inlineStr"/>
@@ -6965,21 +7070,53 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="inlineStr"/>
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>SAMPLE_ODDS_SENTENCE</t>
+        </is>
+      </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
           <t>sampleOddsLine</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr"/>
-      <c r="D80" s="3" t="inlineStr"/>
-      <c r="E80" s="3" t="inlineStr"/>
-      <c r="F80" s="3" t="inlineStr"/>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>What do we show before a person has answered enough?  Answer: one sentence beginning with the word Sample.</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>The word SAMPLE comes FIRST, before any figure, so the number can never be read as theirs at a glance. A sample presented like a result is the most damaging thing a planning screen can do.</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>the age it must last to → horizonAge</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>Nothing external — the sample figures are ours, chosen to be plainly typical rather than flattering.</t>
+        </is>
+      </c>
       <c r="G80" s="3" t="inlineStr"/>
-      <c r="H80" s="3" t="inlineStr"/>
-      <c r="I80" s="3" t="inlineStr"/>
+      <c r="H80" s="3" t="inlineStr">
+        <is>
+          <t>probes/planning-words.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I80" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J80" s="3" t="inlineStr"/>
-      <c r="K80" s="3" t="inlineStr"/>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L80" s="3" t="inlineStr"/>
       <c r="M80" s="5" t="inlineStr"/>
       <c r="N80" s="5" t="inlineStr"/>
@@ -7015,21 +7152,56 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr"/>
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>AGE_THE_MONEY_RUNS_OUT</t>
+        </is>
+      </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
           <t>shortfallAgeFromBand</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr"/>
-      <c r="D81" s="3" t="inlineStr"/>
-      <c r="E81" s="3" t="inlineStr"/>
-      <c r="F81" s="3" t="inlineStr"/>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>If the plan falls short, at what age?  Answer: an age, or nothing when it does not fall short.</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Walk the middle path year by year and report the first age at which it reaches zero.
+A plan that never runs out returns NOTHING rather than a zero — because zero is an age, and "runs out at 0" is nonsense on a screen.
+Founder finding 2026-08-11: a plan that falls short must say WHEN, not merely that it does. "You run short at 84" is something a person can act on; "your plan may not last" is not.</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>the middle path year by year → band[].p50
+the age at each point → band[].age</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>The odds come from WILL_IT_LAST, which is built on everything else in this workbook. See that row for where each of its inputs comes from.</t>
+        </is>
+      </c>
       <c r="G81" s="3" t="inlineStr"/>
-      <c r="H81" s="3" t="inlineStr"/>
-      <c r="I81" s="3" t="inlineStr"/>
+      <c r="H81" s="3" t="inlineStr">
+        <is>
+          <t>probes/planning-words.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J81" s="3" t="inlineStr"/>
-      <c r="K81" s="3" t="inlineStr"/>
+      <c r="K81" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L81" s="3" t="inlineStr"/>
       <c r="M81" s="5" t="inlineStr"/>
       <c r="N81" s="5" t="inlineStr"/>
@@ -13014,21 +13186,56 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="3" t="inlineStr"/>
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>WHAT_THE_PLAN_STILL_NEEDS</t>
+        </is>
+      </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
           <t>planDoor</t>
         </is>
       </c>
-      <c r="C157" s="3" t="inlineStr"/>
-      <c r="D157" s="3" t="inlineStr"/>
-      <c r="E157" s="3" t="inlineStr"/>
-      <c r="F157" s="3" t="inlineStr"/>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>Is there enough to show this person their own odds?  Answer: the list of what is still missing — empty when there is enough.</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>Three things are needed: their age, what they expect to spend, and money that actually counts toward retirement.
+THAT LAST ONE IS A FOUNDER FINDING (2026-08-11). It used to accept ANY account with a balance, so someone whose only asset was the home they live in looked complete here — and then produced no odds at all, because the odds run on the money counted toward retirement, and a primary home is not. The question this asks now means the same thing the odds mean.</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>their age → birthYear or age
+what they spend → monthlySpending
+money that counts toward retirement → NEST_EGG</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding and Plan answers — age, what you expect to spend, and which accounts count toward retirement. Nothing external supplies any of it.</t>
+        </is>
+      </c>
       <c r="G157" s="3" t="inlineStr"/>
-      <c r="H157" s="3" t="inlineStr"/>
-      <c r="I157" s="3" t="inlineStr"/>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>probes/planning-words.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J157" s="3" t="inlineStr"/>
-      <c r="K157" s="3" t="inlineStr"/>
+      <c r="K157" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L157" s="3" t="inlineStr"/>
       <c r="M157" s="5" t="inlineStr"/>
       <c r="N157" s="5" t="inlineStr"/>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -3805,21 +3805,54 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr"/>
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>SPENDING_BY_KIND</t>
+        </is>
+      </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
           <t>spendBuckets</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr"/>
-      <c r="D40" s="3" t="inlineStr"/>
-      <c r="E40" s="3" t="inlineStr"/>
-      <c r="F40" s="3" t="inlineStr"/>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>What is spent each month, split by kind?  Answer: three figures — fixed, non-monthly, flexible — and their total.</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>If the person answered category by category, total each category into its bucket. If they gave three summary figures instead, use those. Nothing answered is zero — never a guessed household average, which would put a number in their plan that nobody chose.</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>the categories → spendCats
+or the three summary figures → b_fixed, b_nonmonthly, b_flexible</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding and Budget answers — either one monthly spending figure, or a category-by-category breakdown. Nothing external supplies these.</t>
+        </is>
+      </c>
       <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="3" t="inlineStr"/>
-      <c r="I40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>probes/debt-budget-txn.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L40" s="3" t="inlineStr"/>
       <c r="M40" s="5" t="inlineStr"/>
       <c r="N40" s="5" t="inlineStr"/>
@@ -3855,21 +3888,53 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr"/>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_TYPE_FACTS</t>
+        </is>
+      </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
           <t>debtKind</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr"/>
-      <c r="D41" s="3" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr"/>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>What do we know about this kind of debt?  Answer: its label and how it is normally repaid — or nothing when the type is unrecognised.</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Look the type up in our own list of debt types. No match returns NOTHING rather than a stand-in.</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>debt type → id</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>OUR OWN LIST in the code — the debt types offered on the Debts screen. Not from any institution.</t>
+        </is>
+      </c>
       <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>probes/debt-budget-txn.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J41" s="3" t="inlineStr"/>
-      <c r="K41" s="3" t="inlineStr"/>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L41" s="3" t="inlineStr"/>
       <c r="M41" s="5" t="inlineStr"/>
       <c r="N41" s="5" t="inlineStr"/>
@@ -3991,21 +4056,62 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr"/>
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_TYPE_FROM_NAME</t>
+        </is>
+      </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
           <t>inferDebtType</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr"/>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>What kind of debt is this, judging by what they called it?  Answers: mortgage · home equity line · car loan · student loan · credit card · medical · personal · other.</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Read the name, first match winning:
+• HOME EQUITY or HELOC → a home equity line
+• MORTGAGE or HOME LOAN → a mortgage
+• AUTO, CAR LOAN or VEHICLE → a car loan
+• STUDENT or TUITION → a student loan
+• CREDIT CARD, VISA, MASTERCARD or AMEX → a credit card
+• MEDICAL, HOSPITAL or DENTAL → medical
+• PERSONAL → a personal loan
+• anything else → OTHER, never a guessed mortgage
+THE ORDER MATTERS: home equity is tested BEFORE mortgage, because both contain the word "home". The other way round, a home equity line would be read as a mortgage and modelled as one — a different repayment shape and a different interest rate.</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>what they called it → label</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>The debt as entered on the Debts screen: name, balance, interest rate, minimum payment and the repayment shape. NO institution supplies debts on any road we have — every debt in the app is typed by hand.</t>
+        </is>
+      </c>
       <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="3" t="inlineStr"/>
-      <c r="I43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>probes/debt-budget-txn.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L43" s="3" t="inlineStr"/>
       <c r="M43" s="5" t="inlineStr"/>
       <c r="N43" s="5" t="inlineStr"/>
@@ -7634,21 +7740,58 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="inlineStr"/>
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>CASH_EFFECT_OF_A_ROW</t>
+        </is>
+      </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
           <t>cashEffect</t>
         </is>
       </c>
-      <c r="C87" s="3" t="inlineStr"/>
-      <c r="D87" s="3" t="inlineStr"/>
-      <c r="E87" s="3" t="inlineStr"/>
-      <c r="F87" s="3" t="inlineStr"/>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>How much did this one ledger row move the cash in the account?  Answer: a dollar figure — positive in, negative out, or zero.</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Money arriving is positive; money leaving is negative. A trade moves cash by shares × price, which is the true cash either way.
+A REINVESTED DIVIDEND HAS NO CASH EFFECT AT ALL. The money never reached the person's cash — it bought more shares. Counting it as cash arriving would overstate what actually came in, which is the same fault that doubled the founder's interest figure one layer up.
+A row that moves no money — a split, an adjustment — reports none.</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>what kind of row → type
+the amount → amount
+shares and price → shares, price
+was it reinvested → reinvested</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>The transaction ledger — one row per event, built from a connected broker by TRANSLATE_BROKER_WORD, from an uploaded file, or logged by hand.</t>
+        </is>
+      </c>
       <c r="G87" s="3" t="inlineStr"/>
-      <c r="H87" s="3" t="inlineStr"/>
-      <c r="I87" s="3" t="inlineStr"/>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>probes/debt-budget-txn.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J87" s="3" t="inlineStr"/>
-      <c r="K87" s="3" t="inlineStr"/>
+      <c r="K87" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L87" s="3" t="inlineStr"/>
       <c r="M87" s="5" t="inlineStr"/>
       <c r="N87" s="5" t="inlineStr"/>
@@ -7684,21 +7827,53 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr"/>
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>LEDGER_ROW_NAME</t>
+        </is>
+      </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
           <t>txnLabel</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr"/>
-      <c r="D88" s="3" t="inlineStr"/>
-      <c r="E88" s="3" t="inlineStr"/>
-      <c r="F88" s="3" t="inlineStr"/>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>What do we call this kind of row on screen?  Answer: a short readable name.</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Look the type up in the label table; anything unrecognised shows its own type rather than a blank, so an unfamiliar row is still identifiable rather than invisible.</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>the row type → t</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>Our own labels — the words shown to the person, not an institution's.</t>
+        </is>
+      </c>
       <c r="G88" s="3" t="inlineStr"/>
-      <c r="H88" s="3" t="inlineStr"/>
-      <c r="I88" s="3" t="inlineStr"/>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>probes/debt-budget-txn.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I88" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J88" s="3" t="inlineStr"/>
-      <c r="K88" s="3" t="inlineStr"/>
+      <c r="K88" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L88" s="3" t="inlineStr"/>
       <c r="M88" s="5" t="inlineStr"/>
       <c r="N88" s="5" t="inlineStr"/>
@@ -8440,21 +8615,55 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="inlineStr"/>
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>PLANNED_SPENDING</t>
+        </is>
+      </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
           <t>plannedMonthlySpend</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr"/>
-      <c r="D98" s="3" t="inlineStr"/>
-      <c r="E98" s="3" t="inlineStr"/>
-      <c r="F98" s="3" t="inlineStr"/>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>What does this person plan to spend each month?  Answer: a dollar figure.</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>The LARGER of two answers: the categories added up, or the single monthly figure they typed.
+The larger wins deliberately. Someone may answer both and the two rarely agree, and understating spending is the direction that FLATTERS a plan — it makes the odds look better than they are. Taking the larger errs toward the cautious side.</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>the categories → SPENDING_BY_KIND
+the single figure → monthlySpending</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding and Budget answers — either one monthly spending figure, or a category-by-category breakdown. Nothing external supplies these.</t>
+        </is>
+      </c>
       <c r="G98" s="3" t="inlineStr"/>
-      <c r="H98" s="3" t="inlineStr"/>
-      <c r="I98" s="3" t="inlineStr"/>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>probes/debt-budget-txn.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J98" s="3" t="inlineStr"/>
-      <c r="K98" s="3" t="inlineStr"/>
+      <c r="K98" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L98" s="3" t="inlineStr"/>
       <c r="M98" s="5" t="inlineStr"/>
       <c r="N98" s="5" t="inlineStr"/>
@@ -12699,21 +12908,54 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="3" t="inlineStr"/>
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_PAYMENTS_ACTUAL</t>
+        </is>
+      </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
           <t>actualDebtPayment</t>
         </is>
       </c>
-      <c r="C150" s="3" t="inlineStr"/>
-      <c r="D150" s="3" t="inlineStr"/>
-      <c r="E150" s="3" t="inlineStr"/>
-      <c r="F150" s="3" t="inlineStr"/>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>What is actually going out on debt each month?  Answer: a dollar figure.</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>Add the required payment on every debt, which counts the chosen payment wherever one is set — so someone deliberately overpaying sees that reflected rather than only their minimums.
+No debts is zero, not an error.</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>every debt → debts, via DEBT_REQUIRED_PAYMENT</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>The debt as entered on the Debts screen: name, balance, interest rate, minimum payment and the repayment shape. NO institution supplies debts on any road we have — every debt in the app is typed by hand.</t>
+        </is>
+      </c>
       <c r="G150" s="3" t="inlineStr"/>
-      <c r="H150" s="3" t="inlineStr"/>
-      <c r="I150" s="3" t="inlineStr"/>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>probes/debt-budget-txn.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I150" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J150" s="3" t="inlineStr"/>
-      <c r="K150" s="3" t="inlineStr"/>
+      <c r="K150" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L150" s="3" t="inlineStr"/>
       <c r="M150" s="5" t="inlineStr"/>
       <c r="N150" s="5" t="inlineStr"/>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -2140,21 +2140,53 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>CURRENCY</t>
+        </is>
+      </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
           <t>activeCurrency</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr"/>
-      <c r="D18" s="3" t="inlineStr"/>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Which currency is the app showing?  Answer: the whole currency record — its code, its symbol and how it groups digits.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Use the chosen currency; if the choice is unrecognised, fall back to the first in the list rather than showing an amount with no symbol at all.</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>the chosen currency → the setting</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>A setting in the app. Not from any institution.</t>
+        </is>
+      </c>
       <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>probes/willitlast-assembly.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J18" s="3" t="inlineStr"/>
-      <c r="K18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L18" s="3" t="inlineStr"/>
       <c r="M18" s="5" t="inlineStr"/>
       <c r="N18" s="5" t="inlineStr"/>
@@ -2190,21 +2222,56 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>MONEY_IN_WORDS</t>
+        </is>
+      </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
           <t>formatMoney</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr"/>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>How is an amount written?  Answer: whole dollars with separators and a currency symbol — or the masking characters when balances are hidden.</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Whole dollars, grouped the way the currency groups them, with its symbol. Cents are not shown, matching the app's whole-number style.
+When balances are hidden it returns the mask — hiding happens HERE, in one place, so no screen can forget to hide something.
+A figure that could not be computed must never print as a real $0.</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>the amount → n
+are balances hidden → the hide setting</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Derived — the figure comes from whichever calculation produced it.</t>
+        </is>
+      </c>
       <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>probes/willitlast-assembly.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J19" s="3" t="inlineStr"/>
-      <c r="K19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L19" s="3" t="inlineStr"/>
       <c r="M19" s="5" t="inlineStr"/>
       <c r="N19" s="5" t="inlineStr"/>
@@ -2240,21 +2307,53 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>MONEY_IN_WORDS_WITH_CENTS</t>
+        </is>
+      </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
           <t>formatMoneyCents</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr"/>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>How is an amount written where cents matter?  Answer: the same, to two decimal places.</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>As above, but showing cents — used where a person checks against a statement and the pennies are part of the check.</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>the amount → n</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Derived — the amount comes from whichever calculation produced it. The currency and its grouping come from the app setting; whether balances are hidden comes from the hide-balances switch. Nothing external supplies any of it.</t>
+        </is>
+      </c>
       <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>probes/willitlast-assembly.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L20" s="3" t="inlineStr"/>
       <c r="M20" s="5" t="inlineStr"/>
       <c r="N20" s="5" t="inlineStr"/>
@@ -7690,21 +7789,54 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="inlineStr"/>
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>SWING_FROM_RETURN</t>
+        </is>
+      </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
           <t>volOf</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr"/>
-      <c r="D86" s="3" t="inlineStr"/>
-      <c r="E86" s="3" t="inlineStr"/>
-      <c r="F86" s="3" t="inlineStr"/>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>How much might a year's return swing, judged from the return alone?  Answer: a figure between 5% and 20%.</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>return × 1.7, held between 5% and 20%.
+THIS IS THE OLD RULE OF THUMB and it is now only a last resort — used when there are no accounts to look at. With accounts, the real per-type swing is blended instead. The founder replaced this in August 2026 because deriving the swing from the return made a cash-heavy pot look almost risk-free, which flattered exactly the people who could least afford a surprise.</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>the return → ret</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>Derived. The real figures come from our own ASSET_KINDS table.</t>
+        </is>
+      </c>
       <c r="G86" s="3" t="inlineStr"/>
-      <c r="H86" s="3" t="inlineStr"/>
-      <c r="I86" s="3" t="inlineStr"/>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>probes/willitlast-assembly.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I86" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J86" s="3" t="inlineStr"/>
-      <c r="K86" s="3" t="inlineStr"/>
+      <c r="K86" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L86" s="3" t="inlineStr"/>
       <c r="M86" s="5" t="inlineStr"/>
       <c r="N86" s="5" t="inlineStr"/>
@@ -13596,22 +13728,74 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="3" t="inlineStr"/>
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_INPUTS</t>
+        </is>
+      </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
           <t>willItLastInputs</t>
         </is>
       </c>
-      <c r="C159" s="3" t="inlineStr"/>
-      <c r="D159" s="3" t="inlineStr"/>
-      <c r="E159" s="3" t="inlineStr"/>
-      <c r="F159" s="3" t="inlineStr"/>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>What goes into working out the odds?  Answer: one complete set of inputs — ages, the pot, what goes in, the return and its swing, spending, guaranteed income, inflation — or NOTHING when we do not know enough.</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>Gather everything the odds need. The person's own choices override every default, one by one.
+NO AGE MEANS NO ANSWER — the odds are never computed from a guessed age.
+SOCIAL SECURITY USES THE CHEQUE THE CHOSEN CLAIM AGE ACTUALLY PAYS. The figure on a statement is the age-67 amount; claiming at 62 pays about 70% of it. Using the statement figure regardless would overstate guaranteed income for everyone claiming early.
+Not eligible means ZERO guaranteed income, not a default.
+A LEGACY TARGET — money someone means to leave behind — is taken off the pot, but ONLY once they are retired. See the defect note.</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>their age → birthYear
+the pot → NEST_EGG
+return and swing → EXPECTED_RETURN_BLENDED, EXPECTED_SWING_BLENDED
+spending → RETIREMENT_SPENDING
+guaranteed income → RETIREMENT_INCOME, SS_BENEFIT_AT_AGE
+money to leave behind → legacyTarget
+their own overrides → the Plan screen</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>Everything upstream in this workbook. The pot from NEST_EGG, the return from EXPECTED_RETURN_BLENDED, the swing from EXPECTED_SWING_BLENDED, spending from RETIREMENT_SPENDING, guaranteed income from RETIREMENT_INCOME and Social Security, plus the person's own answers on the Plan screen where they have overridden a default.</t>
+        </is>
+      </c>
       <c r="G159" s="3" t="inlineStr"/>
-      <c r="H159" s="3" t="inlineStr"/>
-      <c r="I159" s="3" t="inlineStr"/>
-      <c r="J159" s="3" t="inlineStr"/>
-      <c r="K159" s="3" t="inlineStr"/>
-      <c r="L159" s="3" t="inlineStr"/>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>probes/willitlast-assembly.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I159" s="3" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>Money someone means to leave behind should reduce what they can spend from the day they say so, not from the day they retire.</t>
+        </is>
+      </c>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>Found while documenting, not while looking. A legacy target is subtracted from the pot ONLY when a person is already retired. For anyone still working it never reaches the odds at all: on a test plan the odds were 38% with and without a $200,000 legacy. The same person, once retired, drops from 26% to 8%.
+So the odds fall sharply on the day someone retires, purely because a promise they made years earlier finally starts counting. For a 55-to-70 audience, where leaving something behind is a common goal, that is the wrong way round — the years when the plan could still be changed are exactly the years it says nothing.
+FIX: subtract the legacy target from the spendable pot in both cases. One line. Worth checking with the founder whether a legacy should instead be modelled as a target to REACH at the end rather than money removed at the start — the two produce different plans, and the second is closer to how most people think about it.</t>
+        </is>
+      </c>
       <c r="M159" s="5" t="inlineStr"/>
       <c r="N159" s="5" t="inlineStr"/>
       <c r="O159" s="6" t="inlineStr">
@@ -13646,21 +13830,55 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="3" t="inlineStr"/>
+      <c r="A160" s="3" t="inlineStr">
+        <is>
+          <t>WILL_IT_LAST_RESULT</t>
+        </is>
+      </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
           <t>selectWillItLast</t>
         </is>
       </c>
-      <c r="C160" s="3" t="inlineStr"/>
-      <c r="D160" s="3" t="inlineStr"/>
-      <c r="E160" s="3" t="inlineStr"/>
-      <c r="F160" s="3" t="inlineStr"/>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>What are the odds, and can we honestly show them?  Answer: the chance, a best-to-worst range, and whether there was enough to answer at all.</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>If age, spending and a pot are all known, run the simulation and report the chance. Otherwise report that it could not be answered — NOT a confident zero.
+The best-to-worst range re-runs the same plan at a lower and a higher return, so it reads as a range rather than a promise. It always contains the headline figure, and it is repeatable.</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>everything → WILL_IT_LAST_INPUTS
+is a range wanted → withBand</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>Everything upstream in this workbook. The pot from NEST_EGG, the return from EXPECTED_RETURN_BLENDED, the swing from EXPECTED_SWING_BLENDED, spending from RETIREMENT_SPENDING, guaranteed income from RETIREMENT_INCOME and Social Security, plus the person's own answers on the Plan screen where they have overridden a default.</t>
+        </is>
+      </c>
       <c r="G160" s="3" t="inlineStr"/>
-      <c r="H160" s="3" t="inlineStr"/>
-      <c r="I160" s="3" t="inlineStr"/>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>probes/willitlast-assembly.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I160" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J160" s="3" t="inlineStr"/>
-      <c r="K160" s="3" t="inlineStr"/>
+      <c r="K160" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L160" s="3" t="inlineStr"/>
       <c r="M160" s="5" t="inlineStr"/>
       <c r="N160" s="5" t="inlineStr"/>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -1144,21 +1144,55 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr"/>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>CONFIRM_TAX_TYPE</t>
+        </is>
+      </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
           <t>confirmWrapper</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>The person told us what an account really is — how is that recorded?  Answer: that account, with its type and tax treatment set and marked as confirmed.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Set both on that one account and mark it confirmed. FUTURE SYNCS NEVER OVERRIDE A CONFIRMED ANSWER, so a broker's label cannot quietly undo what the person told us on the next refresh.</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>the accounts → accounts
+which one → assetId
+what it really is → kind, taxBucket</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>The Held-in question in the connect flow — asked whenever the type could not be recognised.</t>
+        </is>
+      </c>
       <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>probes/sync-and-networth.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr"/>
@@ -1807,21 +1841,59 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>OPTION_HOLDING</t>
+        </is>
+      </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
           <t>mapOptionHolding</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>What is this option position worth, and what do we call it?  Answer: a readable label, the number of contracts, its value and what was paid — or nothing when it is not a real position.</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Value = contracts × price × 100, because THE PRICE IS PER SHARE and one contract covers 100 shares.
+BUT THE COST IS ALREADY PER CONTRACT and must NOT be multiplied again — doing so overstates what was paid a hundredfold. Verified against a real E*TRADE account on 2026-07-19, where it matched the actual purchase cash to the cent.
+A SHORT position keeps its negative contract count and says "(short)" in its label: it is a liability, not something owned, and reading it as a holding would add money that is owed.
+No contracts, or no option details, returns nothing rather than a zero-value row.</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>contracts → units
+price per share → price
+cost per contract → average_purchase_price
+the option itself → symbol.option_symbol (underlying, strike, call/put, expiry)</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>The connected account's data: accounts[].balance.total.amount, its raw type string, positions[], option_positions[] and activities[]. Nothing here is normalised by the institution — every field is the broker's own shape.</t>
+        </is>
+      </c>
       <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>probes/sync-and-networth.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J14" s="3" t="inlineStr"/>
-      <c r="K14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L14" s="3" t="inlineStr"/>
       <c r="M14" s="5" t="inlineStr"/>
       <c r="N14" s="5" t="inlineStr"/>
@@ -2489,21 +2561,53 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr"/>
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>IS_ALTERNATIVE</t>
+        </is>
+      </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
           <t>isAlternative</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Is this account an alternative holding?  Answers: yes · no.</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Yes when the account's class resolves to Alternatives — crypto, commodities, private equity, hedge funds, annuities and options. It reads the ACCOUNT rather than its type word alone, so an account the person reclassified is judged on what it now is.</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>the account → a, via ASSET_CLASS_OF_ACCOUNT</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Derived from the account records — see the rows for the totals it is built from.</t>
+        </is>
+      </c>
       <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr"/>
-      <c r="I23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>probes/sync-and-networth.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J23" s="3" t="inlineStr"/>
-      <c r="K23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L23" s="3" t="inlineStr"/>
       <c r="M23" s="5" t="inlineStr"/>
       <c r="N23" s="5" t="inlineStr"/>
@@ -4246,21 +4350,57 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr"/>
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>WHAT_IS_MISSING</t>
+        </is>
+      </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
           <t>dataGaps</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="3" t="inlineStr"/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>What is missing or stale in this picture?  Answer: a list of gaps — accounts that have not updated, connections that failed, windows with no history.</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Check the accounts and the ledger against the window being shown, and report what would make the figures on screen incomplete.
+It runs against THE SAME WINDOW the change figure reports, so the warning can never imply that older data sits inside a number it does not.</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>the accounts → assets
+the window → the change line's own start
+the ledger → transactions
+failed syncs → syncFailures</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Derived from the account records — see the rows for the totals it is built from.</t>
+        </is>
+      </c>
       <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>probes/sync-and-networth.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L44" s="3" t="inlineStr"/>
       <c r="M44" s="5" t="inlineStr"/>
       <c r="N44" s="5" t="inlineStr"/>
@@ -5408,21 +5548,55 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr"/>
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>NET_WORTH</t>
+        </is>
+      </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
           <t>buildNetWorth</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr"/>
-      <c r="D58" s="3" t="inlineStr"/>
-      <c r="E58" s="3" t="inlineStr"/>
-      <c r="F58" s="3" t="inlineStr"/>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>What is this household worth?  Answer: one dollar figure, which can be negative.</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>total assets − total debts, computed here and never stored as a third number that could disagree with its own two halves.
+Owing more than you own gives a REAL negative — it is never floored at zero, because someone early in a mortgage genuinely has a negative net worth and hiding it would be a lie about their position.</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>everything owned → grossAssets
+everything owed → grossDebt</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>grossAssets comes from the account balances; grossDebt from the debts typed on the Debts screen. See TOTAL_INVESTABLE and DEBT_TOTAL_OWED.</t>
+        </is>
+      </c>
       <c r="G58" s="3" t="inlineStr"/>
-      <c r="H58" s="3" t="inlineStr"/>
-      <c r="I58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>probes/sync-and-networth.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J58" s="3" t="inlineStr"/>
-      <c r="K58" s="3" t="inlineStr"/>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L58" s="3" t="inlineStr"/>
       <c r="M58" s="5" t="inlineStr"/>
       <c r="N58" s="5" t="inlineStr"/>
@@ -8041,21 +8215,58 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="inlineStr"/>
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>SYNC_ONE_ACCOUNT</t>
+        </is>
+      </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
           <t>ingestSync</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr"/>
-      <c r="D89" s="3" t="inlineStr"/>
-      <c r="E89" s="3" t="inlineStr"/>
-      <c r="F89" s="3" t="inlineStr"/>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>A broker just sent us data — what changes?  Answer: the updated accounts, any new ledger rows, an updated record of what we have already seen, and a list of accounts whose tax type the person needs to confirm.</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>For each account in what the broker sent: create it or update it, replace its holdings, and turn its activities into ledger rows through the Calculation Module.
+Syncing the same data twice changes nothing — the account is matched rather than twinned, and activities already seen are skipped.
+AN UNRECOGNISED ACCOUNT TYPE IS NEVER ASSUMED. It is flagged for the person to confirm, because a wrong tax type is wrong tax maths on every projection. Once they confirm, later syncs never override their answer.</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>what we already have → existingAccounts
+what we have already seen → existingSeenKeys
+what the broker sent → payloads
+now → nowIso</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>The connected account's data: accounts[].balance.total.amount, its raw type string, positions[], option_positions[] and activities[]. Nothing here is normalised by the institution — every field is the broker's own shape.</t>
+        </is>
+      </c>
       <c r="G89" s="3" t="inlineStr"/>
-      <c r="H89" s="3" t="inlineStr"/>
-      <c r="I89" s="3" t="inlineStr"/>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>probes/sync-and-networth.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J89" s="3" t="inlineStr"/>
-      <c r="K89" s="3" t="inlineStr"/>
+      <c r="K89" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L89" s="3" t="inlineStr"/>
       <c r="M89" s="5" t="inlineStr"/>
       <c r="N89" s="5" t="inlineStr"/>
@@ -12631,21 +12842,55 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="inlineStr"/>
+      <c r="A145" s="3" t="inlineStr">
+        <is>
+          <t>WHICH_VIEW</t>
+        </is>
+      </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
           <t>resolveLens</t>
         </is>
       </c>
-      <c r="C145" s="3" t="inlineStr"/>
-      <c r="D145" s="3" t="inlineStr"/>
-      <c r="E145" s="3" t="inlineStr"/>
-      <c r="F145" s="3" t="inlineStr"/>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>Which version of the app should this person see?  Answers: the saver view · the retiree view.</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>An explicit choice always wins. Otherwise it is inferred from whether retirement income is currently being received.
+It decides the wording and the ordering on several screens, so a wrong answer makes the app talk to the wrong person — asking someone already retired when they plan to retire.</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>their own choice → the lens override
+are they drawing retirement income → RETIREMENT_INCOME_NOW</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>The onboarding answers and the Plan screen. Nothing external supplies these.</t>
+        </is>
+      </c>
       <c r="G145" s="3" t="inlineStr"/>
-      <c r="H145" s="3" t="inlineStr"/>
-      <c r="I145" s="3" t="inlineStr"/>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>probes/sync-and-networth.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J145" s="3" t="inlineStr"/>
-      <c r="K145" s="3" t="inlineStr"/>
+      <c r="K145" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L145" s="3" t="inlineStr"/>
       <c r="M145" s="5" t="inlineStr"/>
       <c r="N145" s="5" t="inlineStr"/>
@@ -13123,21 +13368,56 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="3" t="inlineStr"/>
+      <c r="A151" s="3" t="inlineStr">
+        <is>
+          <t>SPLIT_BY_HOW_IT_IS_TAXED</t>
+        </is>
+      </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
           <t>taxBucketSplit</t>
         </is>
       </c>
-      <c r="C151" s="3" t="inlineStr"/>
-      <c r="D151" s="3" t="inlineStr"/>
-      <c r="E151" s="3" t="inlineStr"/>
-      <c r="F151" s="3" t="inlineStr"/>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>How is the retirement money split by the tax that will be owed on it?  Answer: three dollar figures — pre-tax, Roth, and ordinary taxable.</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>Add up the share of each account that counts toward retirement, grouped by its tax treatment.
+The split matters because the retirement engine charges tax on forced withdrawals from the pre-tax slice. A pot that is all Roth and a pot that is all pre-tax are not the same money.</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>each account → accounts
+its tax treatment → tax_bucket
+the share counted toward retirement → RETIREMENT_SHARE_AMOUNT</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>Derived from the account records — see the rows for the totals it is built from.</t>
+        </is>
+      </c>
       <c r="G151" s="3" t="inlineStr"/>
-      <c r="H151" s="3" t="inlineStr"/>
-      <c r="I151" s="3" t="inlineStr"/>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>probes/sync-and-networth.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J151" s="3" t="inlineStr"/>
-      <c r="K151" s="3" t="inlineStr"/>
+      <c r="K151" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L151" s="3" t="inlineStr"/>
       <c r="M151" s="5" t="inlineStr"/>
       <c r="N151" s="5" t="inlineStr"/>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -8302,21 +8302,57 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="inlineStr"/>
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>ALREADY_SEEN_CHECK</t>
+        </is>
+      </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
           <t>dedupeActivities</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr"/>
-      <c r="D90" s="3" t="inlineStr"/>
-      <c r="E90" s="3" t="inlineStr"/>
-      <c r="F90" s="3" t="inlineStr"/>
-      <c r="G90" s="3" t="inlineStr"/>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Which of these activities are new since the last sync?  Answer: the new ones, plus the updated set of keys already seen.</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Build a key for each incoming activity; keep only those whose key has not been seen before; add the kept keys to the seen set.
+The seen set PERSISTS ACROSS SYNCS — it is stored, not rebuilt each time. Deduping only within one batch would let every past activity re-import on the next connection.</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>our account id → accountId
+the new activities → incoming
+keys already seen → seenKeys</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>The broker feed. SnapTrade activities endpoint, one row per event, with `type` carrying the broker's own word for what happened (BUY, SELL, CONTRIBUTION, WITHDRAWAL, DIVIDEND, INTEREST, TRANSFER, OPTIONEXPIRATION…). Every institution uses its own vocabulary; this is the table that turns their word into ours.
+seenKeys: stored by the app between syncs (snaptradeSeenKeys). Our own record, not the broker's.</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>Calculation Module code/probes/broken-family.probe.test.ts</t>
+        </is>
+      </c>
       <c r="H90" s="3" t="inlineStr"/>
-      <c r="I90" s="3" t="inlineStr"/>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J90" s="3" t="inlineStr"/>
-      <c r="K90" s="3" t="inlineStr"/>
+      <c r="K90" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L90" s="3" t="inlineStr"/>
       <c r="M90" s="5" t="inlineStr"/>
       <c r="N90" s="5" t="inlineStr"/>
@@ -10908,21 +10944,67 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="inlineStr"/>
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>RETIREMENT_SHARE_DEFAULT</t>
+        </is>
+      </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
           <t>earmarkDefault</t>
         </is>
       </c>
-      <c r="C121" s="3" t="inlineStr"/>
-      <c r="D121" s="3" t="inlineStr"/>
-      <c r="E121" s="3" t="inlineStr"/>
-      <c r="F121" s="3" t="inlineStr"/>
-      <c r="G121" s="3" t="inlineStr"/>
-      <c r="H121" s="3" t="inlineStr"/>
-      <c r="I121" s="3" t="inlineStr"/>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>How much of this account counts toward retirement, before anyone changes it?  Answer: 0% or 100%.</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>FOUNDER RULE 2026-08-11 — everything you own counts, except the roof you live under and the car you drive:
+• a 529 → 0% (legally someone else's education, not a choice)
+• your PRIMARY home → 0%
+• your most valuable car → 0%
+• everything else, cash included → 100%
+A rental counts (you could sell it). A second car counts.</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>account type → kind
+class → assetClassOf
+home use → re_use
+the main car → primaryCarId</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="inlineStr">
+        <is>
+          <t>The account TYPE, picked by the person from the list on Add account (Checking, Savings, High-yield savings, Money market, CD, Stocks &amp; ETFs, Fixed income, Crypto, Options, Home, Vehicle…). Never sent by an institution — a connected account is given a type at connect time.
+re_use: picked on the property screen (primary / rental / second home / land), defaulting to primary — the cautious side.
+primaryCarId: computed by PRIMARY_CAR below.</t>
+        </is>
+      </c>
+      <c r="G121" s="3" t="inlineStr">
+        <is>
+          <t>Everything counts EXCEPT the home you live in, the car you drive and a 529. The default is only a default — a saved percentage always wins.</t>
+        </is>
+      </c>
+      <c r="H121" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-classification.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J121" s="3" t="inlineStr"/>
-      <c r="K121" s="3" t="inlineStr"/>
+      <c r="K121" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L121" s="3" t="inlineStr"/>
       <c r="M121" s="5" t="inlineStr"/>
       <c r="N121" s="5" t="inlineStr"/>
@@ -12439,21 +12521,64 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="inlineStr"/>
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>RETIREMENT_SHARE_AMOUNT</t>
+        </is>
+      </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
           <t>earmarkedAmount</t>
         </is>
       </c>
-      <c r="C140" s="3" t="inlineStr"/>
-      <c r="D140" s="3" t="inlineStr"/>
-      <c r="E140" s="3" t="inlineStr"/>
-      <c r="F140" s="3" t="inlineStr"/>
-      <c r="G140" s="3" t="inlineStr"/>
-      <c r="H140" s="3" t="inlineStr"/>
-      <c r="I140" s="3" t="inlineStr"/>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>How many dollars of this account count toward retirement?  Answer: a dollar figure.</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>balance × (the saved percentage if there is one, otherwise the default above) ÷ 100.
+The saved percentage always beats the default, and is clamped to 0–100 so a typo cannot retirement share three times an account.</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>money → balance
+saved share → retirement_pct
+fallback → RETIREMENT_SHARE_DEFAULT</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>The account's balance. THREE doors, and the field differs by door:
+• CONNECTED BROKER — SnapTrade account the data they send, balance.total.amount
+• FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
+• TYPED — the Balance box on Add account
+retirement_pct: a slider on the Plan tab, per account. The person's own answer.</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>The saved percentage always beats the default, and is clamped to 0-100 so a bad value cannot exceed the balance or go negative.</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>probes/assets-classification.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I140" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J140" s="3" t="inlineStr"/>
-      <c r="K140" s="3" t="inlineStr"/>
+      <c r="K140" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L140" s="3" t="inlineStr"/>
       <c r="M140" s="5" t="inlineStr"/>
       <c r="N140" s="5" t="inlineStr"/>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -994,21 +994,56 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>EXPENSE_COMMENTARY</t>
+        </is>
+      </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
           <t>analyzeExpenses</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>What is worth saying about this spending?  Answer: a short written analysis, or nothing when the service is unavailable.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Send the categories and totals to OUR OWN server, which holds the provider key and owns the wording. The app never calls the provider directly and never carries the key — a privileged credential in the app can be extracted from the installed app.
+It produces WORDS, not figures: nothing it returns feeds any total.</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>the spending → expenses
+income → monthlyIncome
+inflation → inflationRate</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>The spending comes from the ledger and the budget answers. The commentary comes from our own server-side service, never from the phone.</t>
+        </is>
+      </c>
       <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>probes/feeds-and-seeds.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr"/>
       <c r="N3" s="5" t="inlineStr"/>
@@ -1044,21 +1079,55 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr"/>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ECONOMIC_FIGURES</t>
+        </is>
+      </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
           <t>fetchEconomicData</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr"/>
-      <c r="D4" s="3" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr"/>
-      <c r="F4" s="3" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>What are inflation and the 10-year Treasury yield?  Answer: both figures, when each was fetched, AND whether either one is a stated fallback rather than a live number.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Ask for both independently. If one fails, use a stated fallback for that one only — and SAY SO, through a flag the screen must carry.
+Marking a fallback matters more than the number: a plan built on a stand-in figure should say it is, and the Treasury endpoint has already been silently dead once.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>inflation → the published series
+the 10-year yield → FRED DGS10</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>An outside feed, not an institution: the market-data provider for prices (Tiingo / Yahoo), and the published series for inflation and the 10-year Treasury yield (FRED). Each can fail independently.</t>
+        </is>
+      </c>
       <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>probes/feeds-and-seeds.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
       <c r="N4" s="5" t="inlineStr"/>
@@ -1094,21 +1163,53 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr"/>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>READ_A_RECEIPT</t>
+        </is>
+      </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
           <t>parseReceipt</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>What is on this receipt?  Answer: the merchant, the total and a suggested category — or nothing when it cannot be read.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Read the photographed text and pull out the merchant and the total. Unreadable returns NOTHING, so the person types it rather than being handed a wrong figure that looks confident.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>the photograph → the image</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>The phone camera, read by an outside text service through our own server.</t>
+        </is>
+      </c>
       <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>probes/feeds-and-seeds.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="5" t="inlineStr"/>
       <c r="N5" s="5" t="inlineStr"/>
@@ -1321,21 +1422,56 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr"/>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>FETCH_PRICES</t>
+        </is>
+      </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>fetchPriceSeries</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
-      <c r="D8" s="3" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>What are these holdings worth?  Answer: a price history per ticker — with any that failed simply ABSENT.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Ask the provider for each ticker once — duplicates and different capitalisations are the same request. Every request is settled on its own.
+ONE FAILING TICKER MUST NEVER LOSE THE OTHERS. A ticker that fails is left out entirely rather than returned empty, because an empty price series reads as worth nothing, and a holding priced at zero is a worse answer than a holding with no price.</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>the tickers → tickers
+where prices come from → provider
+how far back → range</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>An outside feed, not an institution: the market-data provider for prices (Tiingo / Yahoo), and the published series for inflation and the 10-year Treasury yield (FRED). Each can fail independently.</t>
+        </is>
+      </c>
       <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>probes/feeds-and-seeds.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="5" t="inlineStr"/>
       <c r="N8" s="5" t="inlineStr"/>
@@ -2461,21 +2597,53 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr"/>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>NEW_ID</t>
+        </is>
+      </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
           <t>newEntityId</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>What do we call this new thing?  Answer: one id, unique, prefixed with the kind of thing it is.</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>A kind prefix plus a unique suffix, so an id says what it belongs to when it turns up in a log or a ledger row rather than being an opaque string.</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>the kind of thing → prefix</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Nothing external. The id is created by us at the moment a thing is first recorded — an account added, a transaction imported, a goal created. No institution supplies it, and it never leaves the app. Note this is OUR id for our own record; the separate id a broker uses for an account is ACCOUNT_IDENTITY, and confusing the two is what re-imported a whole history as new money.</t>
+        </is>
+      </c>
       <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>probes/feeds-and-seeds.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L21" s="3" t="inlineStr"/>
       <c r="M21" s="5" t="inlineStr"/>
       <c r="N21" s="5" t="inlineStr"/>
@@ -2511,21 +2679,55 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr"/>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>READ_A_NUMBER</t>
+        </is>
+      </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
           <t>toNum</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>What number did the person actually type?  Answer: a number — and ZERO when nothing usable was typed.</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Strip the decorations people type — commas, currency symbols, spaces — and read the number.
+Anything unreadable is ZERO, never a partial guess: reading "5,0oo" as 5 would be worse than reading it as nothing.
+A NEGATIVE STAYS NEGATIVE. A debt or a loss entered as a minus is not quietly made positive here, which is a mistake that would flip the meaning of the figure downstream.</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>what they typed → v</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Typed by the person — every box in the app that takes a number goes through this first.</t>
+        </is>
+      </c>
       <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>probes/feeds-and-seeds.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J22" s="3" t="inlineStr"/>
-      <c r="K22" s="3" t="inlineStr"/>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L22" s="3" t="inlineStr"/>
       <c r="M22" s="5" t="inlineStr"/>
       <c r="N22" s="5" t="inlineStr"/>
@@ -8495,21 +8697,55 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="inlineStr"/>
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>ACCOUNTS_FROM_SETUP</t>
+        </is>
+      </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
           <t>assetsFromOnboarding</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr"/>
-      <c r="D92" s="3" t="inlineStr"/>
-      <c r="E92" s="3" t="inlineStr"/>
-      <c r="F92" s="3" t="inlineStr"/>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>What accounts should exist from the setup answers?  Answer: one account per thing they told us about — or none at all.</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Create an account for each balance given. EVERY ONE IS TAGGED as coming from setup.
+That tag is what lets someone run setup again safely: re-running replaces exactly those rows and never touches an account they added by hand.
+Nothing answered creates NOTHING — no placeholder accounts sitting at zero.</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>their answers → the setup profile (savings, investments, retirement balances)</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>The setup answers. Nothing external supplies them.</t>
+        </is>
+      </c>
       <c r="G92" s="3" t="inlineStr"/>
-      <c r="H92" s="3" t="inlineStr"/>
-      <c r="I92" s="3" t="inlineStr"/>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>probes/feeds-and-seeds.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J92" s="3" t="inlineStr"/>
-      <c r="K92" s="3" t="inlineStr"/>
+      <c r="K92" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L92" s="3" t="inlineStr"/>
       <c r="M92" s="5" t="inlineStr"/>
       <c r="N92" s="5" t="inlineStr"/>
@@ -9078,21 +9314,57 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr"/>
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>DEBTS_FROM_SETUP</t>
+        </is>
+      </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
           <t>debtsFromOnboarding</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr"/>
-      <c r="D99" s="3" t="inlineStr"/>
-      <c r="E99" s="3" t="inlineStr"/>
-      <c r="F99" s="3" t="inlineStr"/>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>What debts should exist from the setup answers?  Answer: the debts described, or none.</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>Create a debt from the balance, rate and payment given, and read its KIND from the name they typed — "Chase Mortgage" becomes a mortgage, which decides how it is repaid and modelled.
+No debt answered creates no debt.</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>name → debtName
+balance → debtBalance
+rate → debtRate
+payment → debtPayment</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>The setup answers. Nothing external supplies them.</t>
+        </is>
+      </c>
       <c r="G99" s="3" t="inlineStr"/>
-      <c r="H99" s="3" t="inlineStr"/>
-      <c r="I99" s="3" t="inlineStr"/>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>probes/feeds-and-seeds.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J99" s="3" t="inlineStr"/>
-      <c r="K99" s="3" t="inlineStr"/>
+      <c r="K99" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L99" s="3" t="inlineStr"/>
       <c r="M99" s="5" t="inlineStr"/>
       <c r="N99" s="5" t="inlineStr"/>
@@ -10894,21 +11166,55 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="inlineStr"/>
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>ITEMISE_AN_ACCOUNT</t>
+        </is>
+      </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
           <t>buildItemizedAccounts</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr"/>
-      <c r="D120" s="3" t="inlineStr"/>
-      <c r="E120" s="3" t="inlineStr"/>
-      <c r="F120" s="3" t="inlineStr"/>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>This typed lump is really several holdings — what does the account become?  Answer: the account with its named holdings, and whatever is left over handled explicitly.</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>Replace the single balance with the named holdings, keeping the account total intact where the leftover is positive. Where the holdings come to MORE than the typed total, the total rises — the original estimate was simply low, and that is shown rather than hidden.</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>the account → lump
+the holdings → items
+keep the remainder as cash → keepRemainderAsCash</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="inlineStr">
+        <is>
+          <t>Typed on the Itemise screen, or read from an uploaded file.</t>
+        </is>
+      </c>
       <c r="G120" s="3" t="inlineStr"/>
-      <c r="H120" s="3" t="inlineStr"/>
-      <c r="I120" s="3" t="inlineStr"/>
+      <c r="H120" s="3" t="inlineStr">
+        <is>
+          <t>probes/feeds-and-seeds.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I120" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J120" s="3" t="inlineStr"/>
-      <c r="K120" s="3" t="inlineStr"/>
+      <c r="K120" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L120" s="3" t="inlineStr"/>
       <c r="M120" s="5" t="inlineStr"/>
       <c r="N120" s="5" t="inlineStr"/>
@@ -11217,21 +11523,55 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="inlineStr"/>
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>MONTHLY_SAVING</t>
+        </is>
+      </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
           <t>monthlyContributionsFromOnboarding</t>
         </is>
       </c>
-      <c r="C124" s="3" t="inlineStr"/>
-      <c r="D124" s="3" t="inlineStr"/>
-      <c r="E124" s="3" t="inlineStr"/>
-      <c r="F124" s="3" t="inlineStr"/>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>How much goes in each month?  Answer: a dollar figure.</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>What the person puts in, plus the employer match — because the match is real money arriving in the account, and leaving it out understates what is actually being saved.</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>their own contribution → c_401k
+the match → EMPLOYER_MATCH
+other regular saving → the answers</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="inlineStr">
+        <is>
+          <t>The setup answers. Nothing external supplies them.</t>
+        </is>
+      </c>
       <c r="G124" s="3" t="inlineStr"/>
-      <c r="H124" s="3" t="inlineStr"/>
-      <c r="I124" s="3" t="inlineStr"/>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>probes/feeds-and-seeds.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I124" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J124" s="3" t="inlineStr"/>
-      <c r="K124" s="3" t="inlineStr"/>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L124" s="3" t="inlineStr"/>
       <c r="M124" s="5" t="inlineStr"/>
       <c r="N124" s="5" t="inlineStr"/>
@@ -11358,21 +11698,57 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="inlineStr"/>
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>IF_RATES_MOVE</t>
+        </is>
+      </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
           <t>bondRateSensitivity</t>
         </is>
       </c>
-      <c r="C126" s="3" t="inlineStr"/>
-      <c r="D126" s="3" t="inlineStr"/>
-      <c r="E126" s="3" t="inlineStr"/>
-      <c r="F126" s="3" t="inlineStr"/>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>What happens to this bond if interest rates move?  Answer: two outcomes — one for rates rising a point, one for falling — each a rough band and a dollar change. Nothing when it is not really a bond.</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>Re-price the bond at a yield one point higher and one point lower, and report each as a BAND rather than a single figure — the exact number would be false precision on an estimate.
+Falling rates lift a bond's value and rising rates cut it, which is the thing most people find surprising and the reason to show it.
+A LONGER BOND MOVES MORE. That is the whole point of the figure: a 20-year bond and a 2-year bond respond very differently to the same move.
+No face value or no coupon returns NOTHING rather than a meaningless zero.</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>the bond → face, couponRate, maturity, value
+today → now</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="inlineStr">
+        <is>
+          <t>Bond facts parsed out of the description text for a brokered bond, or typed on the bond form. See BOND_FACTS.</t>
+        </is>
+      </c>
       <c r="G126" s="3" t="inlineStr"/>
-      <c r="H126" s="3" t="inlineStr"/>
-      <c r="I126" s="3" t="inlineStr"/>
+      <c r="H126" s="3" t="inlineStr">
+        <is>
+          <t>probes/feeds-and-seeds.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I126" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J126" s="3" t="inlineStr"/>
-      <c r="K126" s="3" t="inlineStr"/>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L126" s="3" t="inlineStr"/>
       <c r="M126" s="5" t="inlineStr"/>
       <c r="N126" s="5" t="inlineStr"/>
@@ -12288,21 +12664,54 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="inlineStr"/>
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>NET_WORTH_ROWS</t>
+        </is>
+      </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
           <t>resolveNetWorthRows</t>
         </is>
       </c>
-      <c r="C137" s="3" t="inlineStr"/>
-      <c r="D137" s="3" t="inlineStr"/>
-      <c r="E137" s="3" t="inlineStr"/>
-      <c r="F137" s="3" t="inlineStr"/>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>What rows make up the net-worth picture?  Answer: the accounts and debts to show, resolved from whatever the person has told us.</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>Gather the accounts and debts, including anything seeded from setup, into the one list every net-worth surface reads — so no screen builds its own idea of what the person holds.</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>accounts → ACCOUNTS_FROM_SETUP and anything added since
+debts → DEBTS_FROM_SETUP and anything added since</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>The account and debt records. See those rows for where each field comes from.</t>
+        </is>
+      </c>
       <c r="G137" s="3" t="inlineStr"/>
-      <c r="H137" s="3" t="inlineStr"/>
-      <c r="I137" s="3" t="inlineStr"/>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>probes/feeds-and-seeds.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J137" s="3" t="inlineStr"/>
-      <c r="K137" s="3" t="inlineStr"/>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L137" s="3" t="inlineStr"/>
       <c r="M137" s="5" t="inlineStr"/>
       <c r="N137" s="5" t="inlineStr"/>
@@ -13832,21 +14241,57 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="3" t="inlineStr"/>
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>DEBT_PICTURE</t>
+        </is>
+      </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
           <t>buildDebtState</t>
         </is>
       </c>
-      <c r="C155" s="3" t="inlineStr"/>
-      <c r="D155" s="3" t="inlineStr"/>
-      <c r="E155" s="3" t="inlineStr"/>
-      <c r="F155" s="3" t="inlineStr"/>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>What is the whole debt picture?  Answer: everything owed, what must be paid monthly, what is actually being paid, the costliest debt, and how much sits at a dangerous rate.</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>Total the balances. Find the highest-rate debt. Add up separately the balances above the rate we treat as dangerous.
+TWO MONTHLY FIGURES ARE KEPT DELIBERATELY: the minimum that must be paid to stay current, and what is actually going out. Confusing them misstates affordability in one direction or the other.
+No debts gives zero and nothing to point at.</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>every debt → debts
+rates → interest_rate_apr
+payments → the minimum and chosen payments</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>The debts as typed on the Debts screen. No institution supplies debts on any road we have.</t>
+        </is>
+      </c>
       <c r="G155" s="3" t="inlineStr"/>
-      <c r="H155" s="3" t="inlineStr"/>
-      <c r="I155" s="3" t="inlineStr"/>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>probes/feeds-and-seeds.probe.test.ts</t>
+        </is>
+      </c>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>PINNED</t>
+        </is>
+      </c>
       <c r="J155" s="3" t="inlineStr"/>
-      <c r="K155" s="3" t="inlineStr"/>
+      <c r="K155" s="3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="L155" s="3" t="inlineStr"/>
       <c r="M155" s="5" t="inlineStr"/>
       <c r="N155" s="5" t="inlineStr"/>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -1439,8 +1439,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Ask the provider for each ticker once — duplicates and different capitalisations are the same request. Every request is settled on its own.
-ONE FAILING TICKER MUST NEVER LOSE THE OTHERS. A ticker that fails is left out entirely rather than returned empty, because an empty price series reads as worth nothing, and a holding priced at zero is a worse answer than a holding with no price.</t>
+          <t>Ask the price service for each ticker once — asking for "vti", "VTI" and " vti " is one request. Each request is handled on its own, so one going wrong does not affect the rest.
+WHEN ONE FAILS, IT IS LEFT OUT — NOT RETURNED EMPTY. Worked through with a real holding from the founder's Fidelity file:
+We ask for VTI, SLV and 912810TQ1 — the last being his Treasury bond, identified by a CUSIP. No price service in the world carries Treasuries by CUSIP, so that one request fails.
+If we handed back an EMPTY answer for it, the app would read "no prices" as $0. His $8,502 Treasury would show as worth nothing and his net worth would silently drop by $8,502 — with no explanation on screen, because as far as the app is concerned it HAS a price and that price is zero.
+Leaving it out instead means the app knows it has NO PRICE for that holding, which is a different thing entirely. It can show the last known value, or say the price is unavailable, and the total is unaffected. VTI and SLV still come back fine.
+"We do not know what this is worth" and "this is worth nothing" are completely different answers, and they must never be confused.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -8714,8 +8718,12 @@
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Create an account for each balance given. EVERY ONE IS TAGGED as coming from setup.
-That tag is what lets someone run setup again safely: re-running replaces exactly those rows and never touches an account they added by hand.
+          <t>Create an account for each balance the person gave during setup, and STAMP each one as having come from setup.
+WHY THE STAMP MATTERS, worked through:
+In setup you say "I have $25,000 in savings", so the app creates a Savings account and stamps it. Later you add your Vanguard brokerage by hand — that one has no stamp.
+Now you run setup again and say "actually, $30,000 in savings". Because of the stamp, the app knows exactly which accounts IT created and replaces only those. Savings updates to $30,000. Vanguard is untouched.
+Without the stamp there would be only bad options: wipe everything and rebuild, losing the Vanguard account entirely — or create a SECOND savings account and leave the person with two.
+The stamp is how the app tells "I made this from your answers" apart from "you added this yourself", so re-running setup can never destroy someone's own work.
 Nothing answered creates NOTHING — no placeholder accounts sitting at zero.</t>
         </is>
       </c>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -1539,7 +1539,8 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Typed into the holding form, or read from the Symbol / Ticker column of an uploaded file.</t>
+          <t>Typed into the holding form, or read from the Symbol / Ticker column of an uploaded file.
+ROAD NOTE (founder, 2026-08-18): a downloaded FILE and a live CONNECTION are different roads with different fields. The sample files show how an institution WORDS things; they are not what its API returns. Evidence from a file proves the file road only.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -2876,7 +2877,8 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>The name and institution come from the broker at connect time, from an uploaded file, or from the Add account form. The mask ("••4821") is how banks disambiguate accounts and arrives with the feed.</t>
+          <t>The name and institution come from the broker at connect time, from an uploaded file, or from the Add account form. The mask ("••4821") is how banks disambiguate accounts and arrives with the feed.
+ROAD NOTE (founder, 2026-08-18): a downloaded FILE and a live CONNECTION are different roads with different fields. The sample files show how an institution WORDS things; they are not what its API returns. Evidence from a file proves the file road only.</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr"/>
@@ -3042,7 +3044,8 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>The account's own record: what you typed on Add account, or what a broker sent at connect time. Balance comes from the broker's total, an uploaded file's value column, or the Balance box.</t>
+          <t>The account's own record: what you typed on Add account, or what a broker sent at connect time. Balance comes from the broker's total, an uploaded file's value column, or the Balance box.
+ROAD NOTE (founder, 2026-08-18): a downloaded FILE and a live CONNECTION are different roads with different fields. The sample files show how an institution WORDS things; they are not what its API returns. Evidence from a file proves the file road only.</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr"/>
@@ -3309,7 +3312,8 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Typed on the Itemise screen, or read from an uploaded file when the account was imported.</t>
+          <t>Typed on the Itemise screen, or read from an uploaded file when the account was imported.
+ROAD NOTE (founder, 2026-08-18): a downloaded FILE and a live CONNECTION are different roads with different fields. The sample files show how an institution WORDS things; they are not what its API returns. Evidence from a file proves the file road only.</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr"/>
@@ -3562,7 +3566,8 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>The account's own record: what you typed on Add account, or what a broker sent at connect time. Balance comes from the broker's total, an uploaded file's value column, or the Balance box.</t>
+          <t>The account's own record: what you typed on Add account, or what a broker sent at connect time. Balance comes from the broker's total, an uploaded file's value column, or the Balance box.
+ROAD NOTE (founder, 2026-08-18): a downloaded FILE and a live CONNECTION are different roads with different fields. The sample files show how an institution WORDS things; they are not what its API returns. Evidence from a file proves the file road only.</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr"/>
@@ -6324,16 +6329,26 @@
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>PINNED</t>
-        </is>
-      </c>
-      <c r="J64" s="3" t="inlineStr"/>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>A cost we were never told must read as NOT KNOWN, never as zero. Zero means "you paid nothing", which reports the entire holding as profit.</t>
+        </is>
+      </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L64" s="3" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>The file importer turns a missing cost into 0 (holdingsImport.ts, the costPerShare fallback). On the founder's own Fidelity file, a Treasury with "--" in the cost column imports at 0 and its gain reads $8,502 — the whole value, reported as profit on a holding we know nothing about.
+FIX: keep it null. The field already allows null and the connection path already sets it that way — only the file importer forces a zero. One line.
+WORTH KNOWING (founder, 2026-08-18): this is a ROAD problem, not an institution one. Vanguard's connection sends an average purchase price; its file export has no cost column at all. Fidelity's file carries cost for shares and leaves it blank for bonds. So the honest prompt where a file lost it is often "connect this account and we will have it", not "type it in".</t>
+        </is>
+      </c>
       <c r="M64" s="5" t="inlineStr"/>
       <c r="N64" s="5" t="inlineStr"/>
       <c r="O64" s="6" t="inlineStr">
@@ -8284,7 +8299,8 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>The transaction ledger — one row per event, built from a connected broker by TRANSLATE_BROKER_WORD, from an uploaded file, or logged by hand.</t>
+          <t>The transaction ledger — one row per event, built from a connected broker by TRANSLATE_BROKER_WORD, from an uploaded file, or logged by hand.
+ROAD NOTE (founder, 2026-08-18): a downloaded FILE and a live CONNECTION are different roads with different fields. The sample files show how an institution WORDS things; they are not what its API returns. Evidence from a file proves the file road only.</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr"/>
@@ -8642,7 +8658,8 @@
 maturity_date: typed on the bond form, or parsed out of the description text.
 The account TYPE, picked by the person from the list on Add account (Checking, Savings, High-yield savings, Money market, CD, Stocks &amp; ETFs, Fixed income, Crypto, Options, Home, Vehicle…). Never sent by an institution — a connected account is given a type at connect time.
 positions: the holdings list — from the broker feed, an uploaded file, or added by hand.
-tax_bucket — set from the tax type chosen on Add account (Taxable / 401(k) / Traditional IRA / Roth / HSA → TAXABLE, PRE_TAX, ROTH, CASH, PROPERTY). Never sent by an institution.</t>
+tax_bucket — set from the tax type chosen on Add account (Taxable / 401(k) / Traditional IRA / Roth / HSA → TAXABLE, PRE_TAX, ROTH, CASH, PROPERTY). Never sent by an institution.
+ROAD NOTE (founder, 2026-08-18): a downloaded FILE and a live CONNECTION are different roads with different fields. The sample files show how an institution WORDS things; they are not what its API returns. Evidence from a file proves the file road only.</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
@@ -9003,7 +9020,8 @@
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>The account's own record: what you typed on Add account, or what a broker sent at connect time. Balance comes from the broker's total, an uploaded file's value column, or the Balance box.</t>
+          <t>The account's own record: what you typed on Add account, or what a broker sent at connect time. Balance comes from the broker's total, an uploaded file's value column, or the Balance box.
+ROAD NOTE (founder, 2026-08-18): a downloaded FILE and a live CONNECTION are different roads with different fields. The sample files show how an institution WORDS things; they are not what its API returns. Evidence from a file proves the file road only.</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr"/>
@@ -11028,7 +11046,8 @@
       </c>
       <c r="F118" s="3" t="inlineStr">
         <is>
-          <t>The account's own record: what you typed on Add account, or what a broker sent at connect time. Balance comes from the broker's total, an uploaded file's value column, or the Balance box.</t>
+          <t>The account's own record: what you typed on Add account, or what a broker sent at connect time. Balance comes from the broker's total, an uploaded file's value column, or the Balance box.
+ROAD NOTE (founder, 2026-08-18): a downloaded FILE and a live CONNECTION are different roads with different fields. The sample files show how an institution WORDS things; they are not what its API returns. Evidence from a file proves the file road only.</t>
         </is>
       </c>
       <c r="G118" s="3" t="inlineStr"/>
@@ -11203,7 +11222,8 @@
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
-          <t>Typed on the Itemise screen, or read from an uploaded file.</t>
+          <t>Typed on the Itemise screen, or read from an uploaded file.
+ROAD NOTE (founder, 2026-08-18): a downloaded FILE and a live CONNECTION are different roads with different fields. The sample files show how an institution WORDS things; they are not what its API returns. Evidence from a file proves the file road only.</t>
         </is>
       </c>
       <c r="G120" s="3" t="inlineStr"/>
@@ -11385,7 +11405,8 @@
           <t>The account's balance. THREE doors, and the field differs by door:
 • CONNECTED BROKER — SnapTrade account the data they send, balance.total.amount
 • FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
-• TYPED — the Balance box on Add account</t>
+• TYPED — the Balance box on Add account
+ROAD NOTE (founder, 2026-08-18): a downloaded FILE and a live CONNECTION are different roads with different fields. The sample files show how an institution WORDS things; they are not what its API returns. Evidence from a file proves the file road only.</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -11647,7 +11668,8 @@
 • CONNECTED BROKER — SnapTrade account the data they send, balance.total.amount
 • FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
 • TYPED — the Balance box on Add account
-Vehicles are identified by the account type picked on Add account.</t>
+Vehicles are identified by the account type picked on Add account.
+ROAD NOTE (founder, 2026-08-18): a downloaded FILE and a live CONNECTION are different roads with different fields. The sample files show how an institution WORDS things; they are not what its API returns. Evidence from a file proves the file road only.</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
@@ -12199,10 +12221,26 @@
           <t>probes/classification-crosspath.probe.test.ts</t>
         </is>
       </c>
-      <c r="I131" s="3" t="inlineStr"/>
-      <c r="J131" s="3" t="inlineStr"/>
-      <c r="K131" s="3" t="inlineStr"/>
-      <c r="L131" s="3" t="inlineStr"/>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>A file that carries no cost must import as cost UNKNOWN, and the import should say how many holdings arrived without one.</t>
+        </is>
+      </c>
+      <c r="K131" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L131" s="3" t="inlineStr">
+        <is>
+          <t>The importer forces a missing cost to 0 rather than leaving it unknown. It already reports "found 17 holdings · skipped 2 rows we could not read", so one more line fits where a person can still act on it: "3 holdings came without a cost — shown as not entered until you add it".</t>
+        </is>
+      </c>
       <c r="M131" s="5" t="inlineStr"/>
       <c r="N131" s="5" t="inlineStr"/>
       <c r="O131" s="6" t="inlineStr">
@@ -12628,16 +12666,25 @@
       </c>
       <c r="I136" s="3" t="inlineStr">
         <is>
-          <t>PINNED</t>
-        </is>
-      </c>
-      <c r="J136" s="3" t="inlineStr"/>
+          <t>DEFECT</t>
+        </is>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>No cost known means NO GAIN FIGURE — not a gain equal to the whole value.</t>
+        </is>
+      </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L136" s="3" t="inlineStr"/>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L136" s="3" t="inlineStr">
+        <is>
+          <t>value − cost, with cost defaulting to zero, so an unpriced-cost holding reports 100% profit. Two sibling functions already get this right by REFUSING: total return returns nothing, and capital gains skips the lot. Three functions, three different answers to the same missing data.
+FIX: return nothing when the cost is unknown, matching what its siblings already do. Then the screen shows "Not entered · Add it ›" rather than a number.</t>
+        </is>
+      </c>
       <c r="M136" s="5" t="inlineStr"/>
       <c r="N136" s="5" t="inlineStr"/>
       <c r="O136" s="6" t="inlineStr">
@@ -12789,7 +12836,8 @@
 • CONNECTED BROKER — SnapTrade account the data they send, balance.total.amount
 • FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
 • TYPED — the Balance box on Add account
-The class comes from ASSET_CLASS_OF_ACCOUNT (see that row).</t>
+The class comes from ASSET_CLASS_OF_ACCOUNT (see that row).
+ROAD NOTE (founder, 2026-08-18): a downloaded FILE and a live CONNECTION are different roads with different fields. The sample files show how an institution WORDS things; they are not what its API returns. Evidence from a file proves the file road only.</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
@@ -12879,7 +12927,8 @@
           <t>The account's balance. THREE doors, and the field differs by door:
 • CONNECTED BROKER — SnapTrade account the data they send, balance.total.amount
 • FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
-• TYPED — the Balance box on Add account</t>
+• TYPED — the Balance box on Add account
+ROAD NOTE (founder, 2026-08-18): a downloaded FILE and a live CONNECTION are different roads with different fields. The sample files show how an institution WORDS things; they are not what its API returns. Evidence from a file proves the file road only.</t>
         </is>
       </c>
       <c r="G139" s="3" t="inlineStr">
@@ -12972,7 +13021,8 @@
 • CONNECTED BROKER — SnapTrade account the data they send, balance.total.amount
 • FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
 • TYPED — the Balance box on Add account
-retirement_pct: a slider on the Plan tab, per account. The person's own answer.</t>
+retirement_pct: a slider on the Plan tab, per account. The person's own answer.
+ROAD NOTE (founder, 2026-08-18): a downloaded FILE and a live CONNECTION are different roads with different fields. The sample files show how an institution WORDS things; they are not what its API returns. Evidence from a file proves the file road only.</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
@@ -13062,7 +13112,8 @@
           <t>The account's balance. THREE doors, and the field differs by door:
 • CONNECTED BROKER — SnapTrade account the data they send, balance.total.amount
 • FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
-• TYPED — the Balance box on Add account</t>
+• TYPED — the Balance box on Add account
+ROAD NOTE (founder, 2026-08-18): a downloaded FILE and a live CONNECTION are different roads with different fields. The sample files show how an institution WORDS things; they are not what its API returns. Evidence from a file proves the file road only.</t>
         </is>
       </c>
       <c r="G141" s="3" t="inlineStr">
@@ -13501,7 +13552,8 @@
 • CONNECTED BROKER — SnapTrade account the data they send, balance.total.amount
 • FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
 • TYPED — the Balance box on Add account
-OUR OWN TABLE — ASSET_KINDS in src/domain/assets/index.ts. Not from any institution and not from the market: a hand-maintained list of account types, each with a bucket, a screen section and a long-run return. If a number here is wrong, every projection is wrong.</t>
+OUR OWN TABLE — ASSET_KINDS in src/domain/assets/index.ts. Not from any institution and not from the market: a hand-maintained list of account types, each with a bucket, a screen section and a long-run return. If a number here is wrong, every projection is wrong.
+ROAD NOTE (founder, 2026-08-18): a downloaded FILE and a live CONNECTION are different roads with different fields. The sample files show how an institution WORDS things; they are not what its API returns. Evidence from a file proves the file road only.</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
@@ -13597,7 +13649,8 @@
 • CONNECTED BROKER — SnapTrade account the data they send, balance.total.amount
 • FILE YOU UPLOAD — the money column, found by header pattern: Value / Market Value / Current Value (institutions all name it differently, so it is matched, not assumed)
 • TYPED — the Balance box on Add account
-OUR OWN TABLE — ASSET_KINDS in src/domain/assets/index.ts. Not from any institution and not from the market: a hand-maintained list of account types, each with a bucket, a screen section and a long-run return. If a number here is wrong, every projection is wrong.</t>
+OUR OWN TABLE — ASSET_KINDS in src/domain/assets/index.ts. Not from any institution and not from the market: a hand-maintained list of account types, each with a bucket, a screen section and a long-run return. If a number here is wrong, every projection is wrong.
+ROAD NOTE (founder, 2026-08-18): a downloaded FILE and a live CONNECTION are different roads with different fields. The sample files show how an institution WORDS things; they are not what its API returns. Evidence from a file proves the file road only.</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
@@ -13686,7 +13739,8 @@
       <c r="F148" s="3" t="inlineStr">
         <is>
           <t>The account's own record: what you typed on Add account, or what a broker sent at connect time. Balance comes from the broker's total, an uploaded file's value column, or the Balance box.
-actual_ttm is TYPED by the person — no institution sends a trailing-year return on any road we have.</t>
+actual_ttm is TYPED by the person — no institution sends a trailing-year return on any road we have.
+ROAD NOTE (founder, 2026-08-18): a downloaded FILE and a live CONNECTION are different roads with different fields. The sample files show how an institution WORDS things; they are not what its API returns. Evidence from a file proves the file road only.</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr"/>
@@ -14194,7 +14248,8 @@
       <c r="F154" s="3" t="inlineStr">
         <is>
           <t>The market-data cache (Tiingo / Yahoo), keyed by ticker, with the time of the last successful fetch. Not from the broker.
-The holdings and their lots come from the broker feed, an uploaded file, or the Add holding form — see HOLDING_SHARES and HOLDING_COST_BASIS.</t>
+The holdings and their lots come from the broker feed, an uploaded file, or the Add holding form — see HOLDING_SHARES and HOLDING_COST_BASIS.
+ROAD NOTE (founder, 2026-08-18): a downloaded FILE and a live CONNECTION are different roads with different fields. The sample files show how an institution WORDS things; they are not what its API returns. Evidence from a file proves the file road only.</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr"/>
@@ -16439,7 +16494,7 @@
     <row r="1" ht="58" customHeight="1">
       <c r="A1" s="20" t="inlineStr">
         <is>
-          <t>INSTITUTION MATRIX — every raw input we need, against what each institution actually calls it. EVERY CELL SAYS HOW WE KNOW: ✓ seen on this machine (your file / a live connection) · ○ their published documentation · — documented as absent · ? NEVER SEEN — a red cell is a file worth downloading, never a thing to guess. The red cells ARE the download shopping list.</t>
+          <t>INSTITUTION MATRIX — every raw input we need, against what each institution actually calls it. EVERY CELL SAYS HOW WE KNOW: ✓ seen on this machine · ○ their published documentation · — documented as absent · ? NEVER SEEN, and a red cell is a file worth getting rather than a thing to guess.  ⚠ A FILE AND A CONNECTION ARE DIFFERENT ROADS. The sample files show how an institution WORDS things; they are NOT what its API returns, and a ✓ in a file column says nothing about the connection column beside it. Read each column on its own.</t>
         </is>
       </c>
     </row>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -887,7 +887,7 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CALCULATION INVENTORY · Phase 1 — Net worth, Performance and the 8 screens they open · 158 calculations · generated from commit cf71d68 on 2026-08-18  ⚠ TREE WAS DIRTY. EVERY FORMULA HERE DESCRIBES THE CODE AS IT IS TODAY, BUGS INCLUDED — you cannot fix what you have not described, and a probe can only execute what exists. Where the current behaviour is wrong, Status says DEFECT and the corrected version sits in WHAT IT SHOULD BE; the difference between those two columns is the work list. GREY columns are generated from the code and overwritten on every regeneration — never edit them. CREAM columns are written by hand and preserved. THE TWO BLUE COLUMNS ARE YOURS - write your questions and your verdict there, and nothing I run will ever touch them. You can also attach an Excel comment to ANY cell on any tab; comments survive regeneration and I read them. A row is not documented until its probe passes.</t>
+          <t>CALCULATION INVENTORY · Phase 1 — Net worth, Performance and the 8 screens they open · 158 calculations · generated from commit bc1456f on 2026-08-18  ⚠ TREE WAS DIRTY. EVERY FORMULA HERE DESCRIBES THE CODE AS IT IS TODAY, BUGS INCLUDED — you cannot fix what you have not described, and a probe can only execute what exists. Where the current behaviour is wrong, Status says DEFECT and the corrected version sits in WHAT IT SHOULD BE; the difference between those two columns is the work list. GREY columns are generated from the code and overwritten on every regeneration — never edit them. CREAM columns are written by hand and preserved. THE TWO BLUE COLUMNS ARE YOURS - write your questions and your verdict there, and nothing I run will ever touch them. You can also attach an Excel comment to ANY cell on any tab; comments survive regeneration and I read them. A row is not documented until its probe passes.</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>src/services/sync/ingest.ts:173</t>
+          <t>src/services/sync/ingest.ts:185</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>src/services/sync/ingest.ts:29</t>
+          <t>src/services/sync/ingest.ts:34</t>
         </is>
       </c>
     </row>
@@ -1967,7 +1967,7 @@
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>ingestSync</t>
+          <t>—</t>
         </is>
       </c>
       <c r="S13" s="6" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="T59" s="6" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:226</t>
+          <t>src/domain/performance/index.ts:229</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="T60" s="6" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:215</t>
+          <t>src/domain/performance/index.ts:218</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="T61" s="6" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:149</t>
+          <t>src/domain/performance/index.ts:152</t>
         </is>
       </c>
     </row>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="T65" s="6" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:128</t>
+          <t>src/domain/performance/index.ts:131</t>
         </is>
       </c>
     </row>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="T70" s="6" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:275</t>
+          <t>src/domain/performance/index.ts:278</t>
         </is>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="T71" s="6" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:265</t>
+          <t>src/domain/performance/index.ts:268</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="T74" s="6" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:205</t>
+          <t>src/domain/performance/index.ts:208</t>
         </is>
       </c>
     </row>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="P89" s="6" t="inlineStr">
         <is>
-          <t>activityKey, mapAccountType, mapActivityType, mapOptionHolding, mergeHistoryFrom, netCashSleeve, newEntityId, stAssetId</t>
+          <t>activityKey, mapAccountType, mapOptionHolding, mergeHistoryFrom, netCashSleeve, newEntityId, stAssetId</t>
         </is>
       </c>
       <c r="Q89" s="6" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="T89" s="6" t="inlineStr">
         <is>
-          <t>src/services/sync/ingest.ts:31</t>
+          <t>src/services/sync/ingest.ts:36</t>
         </is>
       </c>
     </row>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="T114" s="6" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:119</t>
+          <t>src/domain/performance/index.ts:122</t>
         </is>
       </c>
     </row>
@@ -10845,7 +10845,7 @@
       </c>
       <c r="T115" s="6" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:239</t>
+          <t>src/domain/performance/index.ts:242</t>
         </is>
       </c>
     </row>
@@ -14299,7 +14299,7 @@
       </c>
       <c r="T154" s="6" t="inlineStr">
         <is>
-          <t>src/domain/performance/index.ts:173</t>
+          <t>src/domain/performance/index.ts:176</t>
         </is>
       </c>
     </row>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="T160" s="6" t="inlineStr">
         <is>
-          <t>src/domain/retirement/willItLast.ts:115</t>
+          <t>src/domain/retirement/willItLast.ts:121</t>
         </is>
       </c>
     </row>

--- a/Calculation Module/calculation-inventory-v1.xlsx
+++ b/Calculation Module/calculation-inventory-v1.xlsx
@@ -887,7 +887,7 @@
     <row r="1" ht="46" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CALCULATION INVENTORY · Phase 1 — Net worth, Performance and the 8 screens they open · 161 calculations · generated from commit 764ca16 on 2026-08-20  ⚠ TREE WAS DIRTY. EVERY FORMULA HERE DESCRIBES THE CODE AS IT IS TODAY, BUGS INCLUDED — you cannot fix what you have not described, and a probe can only execute what exists. Where the current behaviour is wrong, Status says DEFECT and the corrected version sits in WHAT IT SHOULD BE; the difference between those two columns is the work list. GREY columns are generated from the code and overwritten on every regeneration — never edit them. CREAM columns are written by hand and preserved. THE TWO BLUE COLUMNS ARE YOURS - write your questions and your verdict there, and nothing I run will ever touch them. You can also attach an Excel comment to ANY cell on any tab; comments survive regeneration and I read them. A row is not documented until its probe passes.</t>
+          <t>CALCULATION INVENTORY · Phase 1 — Net worth, Performance and the 8 screens they open · 161 calculations · generated from commit b4c573b on 2026-08-21  ⚠ TREE WAS DIRTY. EVERY FORMULA HERE DESCRIBES THE CODE AS IT IS TODAY, BUGS INCLUDED — you cannot fix what you have not described, and a probe can only execute what exists. Where the current behaviour is wrong, Status says DEFECT and the corrected version sits in WHAT IT SHOULD BE; the difference between those two columns is the work list. GREY columns are generated from the code and overwritten on every regeneration — never edit them. CREAM columns are written by hand and preserved. THE TWO BLUE COLUMNS ARE YOURS - write your questions and your verdict there, and nothing I run will ever touch them. You can also attach an Excel comment to ANY cell on any tab; comments survive regeneration and I read them. A row is not documented until its probe passes.</t>
         </is>
       </c>
     </row>
@@ -8038,10 +8038,12 @@
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>WHY IT IS NOT ONE SUM. Nobody knows what markets will do. A plan that assumes exactly 6% every year for thirty years gives one confident answer that is certainly wrong. So instead the app plays out your life 400 times, giving each year a different random return — some good, some terrible, averaging out to what your mix of accounts would normally earn.
+          <t>WHY IT IS NOT ONE SUM. Nobody knows what markets will do. A plan that assumes exactly 6% every year for thirty years gives one confident answer that is certainly wrong. So instead the app plays out your life 1,000 times, giving each year a different random return — some good, some terrible, averaging out to what your mix of accounts would normally earn.
 EACH RUN GOES LIKE THIS. Start with what you have. Every year until you retire: the pot grows or shrinks by that year's random return, your saving goes in, and any big planned cost comes out. From retirement on: your spending comes out, your pension and Social Security go in, and whatever is left keeps growing. If the money outlasts you, that run worked.
-Do that 400 times and count. 340 worked out of 400 → 85%.
-WHAT 85% MEANS. Not "you will have 85% of what you need". It means that in 85 out of 100 possible futures, the money lasted — and in 15, it ran out. It is a measure of how much room for bad luck you have.
+Do that 1,000 times and count. It lasted in 770 of 1,000 (77%). Rounded to the nearest 5 → 75%. A real 100 (all 1,000 lasted) shows 100%; a real 0 shows 0%; rounding never creates them — 98% shows as 95, never 100.
+WHAT 75% MEANS. Not "you will have 75% of what you need". It means that in 75 out of 100 possible futures, the money lasted — and in 25, it ran out. It is a measure of how much room for bad luck you have.
+THE RECOMMENDED NEST EGG, in the same breath. Alongside the odds this reports a target pot: 25 x the yearly spending your guaranteed income does not cover, measured in the dollars of your retirement year. Worked: spending $6,000 a month at retirement is $72,000 a year; Social Security of $2,600 a month is $31,200; the yearly gap is $40,800; 25 x that is $1,020,000. The 25 comes from the old rule of thumb that a pot lasts if you draw about 4% of it a year (25 = 1 / 4%). It is a YARDSTICK, deliberately crude: it ignores how long you plan for and what your money earns. The odds figure is the real answer; this is the number the "to close the gap" line is measured against.
+BOTH GUARANTEED-INCOME RULES APPLY HERE. Social Security rises with inflation; a pension stays flat. Your own withdrawals are never counted as guaranteed income — the run works those out.
 THE ONE RULE THAT IS EASY TO GET WRONG. Your SPENDING rises with inflation — groceries in 2040 cost more than groceries today. But your MORTGAGE PAYMENT DOES NOT. A fixed payment is the same dollars every year until the loan ends. Treating it like groceries would overstate what it costs you every single year, and then stop overstating it the moment it ends.
 It is repeatable: the same plan always gives the same percentage, today and tomorrow.</t>
         </is>
@@ -10956,12 +10958,18 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>What will the pot be worth at retirement?  Answer: a dollar figure, with a range around it.</t>
+          <t>What will the pot be worth at retirement, and how big does it need to be? Answer: two dollar figures — what you will have, and the target pot that pays for the whole plan.</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>The same year-by-year growth as the simulation, run over the years to retirement, reporting where the runs land. It answers "how much will I have", where the simulation answers "will it last".</t>
+          <t>TWO FIGURES, no random runs anywhere in this one — it is the straight-line check beside the 1,000-run odds.
+WHAT YOU WILL HAVE. Today's pot grown at your expected return for the years until you retire, plus every year's saving grown for however many years it has left. Worked at 6%: $600,000 today over 7 years becomes $902,000; $24,000 saved each of those years adds about $201,000; $1,103,000 in all.
+WHAT YOU WILL NEED — the target pot. Walk every retirement year one at a time, from the year you retire to the age you plan to. In each year: take that year's spending, take off the guaranteed income you receive that year, and that difference is what the pot must hand you. Bring each of those amounts back to a retirement-year value by dividing by your expected return once for every year you have to wait for it. Add them all up. That total is the pot that pays for the whole plan.
+Two rules ride along: spending rises with inflation every year, and so does Social Security, but a pension stays flat.
+WHY THE NUMBER IS SMALLER THAN THE SUM OF THE SPENDING. Money you do not need until year fifteen keeps earning until then, so you need less than fifteen years' spending set aside today.
+MONEY IS NEEDED AT THE START OF ITS YEAR. The first retirement year's spending is not discounted at all — January's groceries cannot be paid out of December's growth. Some published calculators charge each year at its END, which gives every year one more year of growth and reports a target about (1 + return) / (1 + inflation) smaller — roughly 3% lower at a 6% return and 2.5% inflation. Neither is wrong; ours is the cautious side, and the difference is a timing convention, not a disagreement about the arithmetic.
+HOW IT DIFFERS FROM THE 25 x YARDSTICK reported by the odds engine: this one knows how long you plan for and what your money earns; the yardstick knows neither.</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
